--- a/files/NRL_anytime_tryscorers.xlsx
+++ b/files/NRL_anytime_tryscorers.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
   <si>
     <t xml:space="preserve">Date Local</t>
   </si>
@@ -39,14 +39,493 @@
   </si>
   <si>
     <t xml:space="preserve">Anytimeodds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100132087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josiah Karapani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesse Arthars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reece Walsh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kotoni Staggs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grant Anderson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brendan Piakura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Gosiewski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Reynolds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Talty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Willison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Duffy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cory Paix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payne Haas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preston Riki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Johnston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edward Kosi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jye Gray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campbell Graham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cody Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">David Fifita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tallis Duncan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latrell Siegwalt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keaon Koloamatangi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashton Ward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron Murray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brandon Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euan Aitken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tevita Tatola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lachlan Hubner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bronson Garlick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100068094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamiso Tabuai-Fidow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selwyn Cobbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamayne Isaako</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herbie Farnworth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Bostock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connelly Lemuelu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kulikefu Finefeuiaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kodi Nikorima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremy Marshall-King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ray Stone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Flegler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiya Katoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morgan Knowles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Plath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark Nawaqanitawase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Tedesco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugo Savala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robert Toia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daly Cherry-Evans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angus Crichton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siua Wong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Watson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Victor Radley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reece Robson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nat Butcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egan Butcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lindsay Collins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spencer Leniu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100113687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronaldo Mulitalo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samuel Stonestreet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mawene Hiroti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">William Kennedy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braydon Trindall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayal Iro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Briton Nikora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teig Wilton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niwhai Puru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Addin Fonua-Blake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hohepa Puru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Hazelton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siosifa Talakai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron McInnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toby Rudolf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesse Colquhoun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Burns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Berrell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oregon Kaufusi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100097428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Savage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Savelio Tamale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaeo Weekes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Strange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Timoko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daine Laurie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hudson Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zac Hosking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Sanders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Starling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corey Horsburgh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joseph Tapine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Brailey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owen Pattie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Addo-Carr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian Kelly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiah Iongi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Samrani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sean Russell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kelma Tuilagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kitione Kautoga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronald Volkman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joash Papalii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apa Twidle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tallyn Da Silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack De Belin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harrison Edwards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luca Moretti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100089245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wests tigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phillip Sami</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jensen Taumoepeau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jojo Fifita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Campbell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keano Kini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AJ Brimson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arama Hau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beau Fermor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zane Harrison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver Pascoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tino Fa'asuamaleaui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurtis Morrin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Bai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeral Skelton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faaletino Tavana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jahream Bula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunia Turuva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heamasi Makasini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mavrik Geyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kai Pearce-Paul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jock Madden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apisai Koroisau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jarome Luai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Royce Hunt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terrell May</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fonua Pole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charlie Murray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latu Fainu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Seyfarth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bunty Afoa</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="0.00"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -59,6 +538,11 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -81,9 +565,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -376,11 +863,11 @@
   <cols>
     <col min="1" max="1" width="9.285" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="9.285" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="7.57" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="8.4275" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="8.4275" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="4.14" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="5.855" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.4275" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="19.575" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="23.005" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="23.005" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="21.29" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="6.7125" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="10.1425" hidden="0" customWidth="1"/>
   </cols>
@@ -414,6 +901,4037 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>2.67</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>2.83</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>3.35</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>4.69</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>4.69</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>5.92</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>7.35</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>7.87</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>7.89</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>9.18</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>13.76</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>19.09</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H17" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H19" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>2.98</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H21" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H22" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H23" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>3.91</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H24" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>5.53</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H25" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H26" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H27" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>8.56</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H28" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>9.79</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H29" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>10.63</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H30" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>16.34</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H31" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>18.42</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H32" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H33" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>2.32</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H34" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H35" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H36" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H37" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H38" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H39" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>6.08</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H40" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>7.56</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H41" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>10.11</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H42" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>10.83</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H43" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>12.33</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H44" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>14.11</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H45" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>15.16</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H46" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H47" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H48" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H49" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H50" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H51" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>4.69</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H52" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>4.85</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H53" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>4.85</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H54" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>4.92</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H55" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H56" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>8.39</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H57" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>9.85</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H58" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>11.21</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H59" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>12.35</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H60" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>15.59</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H61" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>15.98</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H62" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H63" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H64" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I64" s="4" t="n">
+        <v>3.44</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H65" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I65" s="4" t="n">
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H66" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I66" s="4" t="n">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="H67" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I67" s="4" t="n">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H68" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I68" s="4" t="n">
+        <v>4.78</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="H69" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I69" s="4" t="n">
+        <v>4.78</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H70" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I70" s="4" t="n">
+        <v>4.87</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="H71" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I71" s="4" t="n">
+        <v>6.27</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H72" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I72" s="4" t="n">
+        <v>6.71</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H73" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I73" s="4" t="n">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H74" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I74" s="4" t="n">
+        <v>11.52</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="H75" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I75" s="4" t="n">
+        <v>13.63</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H76" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I76" s="4" t="n">
+        <v>19.06</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H77" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I77" s="4" t="n">
+        <v>19.69</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H78" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I78" s="4" t="n">
+        <v>25.24</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H79" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I79" s="4" t="n">
+        <v>39.6</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H80" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I80" s="4" t="n">
+        <v>43.61</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H81" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I81" s="4" t="n">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H82" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I82" s="4" t="n">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H83" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I83" s="4" t="n">
+        <v>2.53</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H84" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I84" s="4" t="n">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="H85" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I85" s="4" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H86" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I86" s="4" t="n">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="H87" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I87" s="4" t="n">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H88" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I88" s="4" t="n">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H89" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I89" s="4" t="n">
+        <v>5.77</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="H90" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I90" s="4" t="n">
+        <v>7.49</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="H91" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I91" s="4" t="n">
+        <v>9.34</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="H92" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I92" s="4" t="n">
+        <v>12.38</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="H93" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I93" s="4" t="n">
+        <v>12.67</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H94" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I94" s="4" t="n">
+        <v>14.21</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="H95" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I95" s="4" t="n">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H96" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I96" s="4" t="n">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="H97" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I97" s="4" t="n">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H98" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I98" s="4" t="n">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H99" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I99" s="4" t="n">
+        <v>4.03</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H100" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I100" s="4" t="n">
+        <v>4.05</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H101" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I101" s="4" t="n">
+        <v>4.05</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H102" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I102" s="4" t="n">
+        <v>4.45</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="H103" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I103" s="4" t="n">
+        <v>5.16</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H104" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I104" s="4" t="n">
+        <v>6.79</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H105" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I105" s="4" t="n">
+        <v>7.53</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="H106" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I106" s="4" t="n">
+        <v>9.41</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H107" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I107" s="4" t="n">
+        <v>10.33</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="H108" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I108" s="4" t="n">
+        <v>11.43</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H109" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I109" s="4" t="n">
+        <v>11.79</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H110" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I110" s="4" t="n">
+        <v>12.45</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H111" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I111" s="4" t="n">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H112" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I112" s="4" t="n">
+        <v>2.81</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H113" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I113" s="4" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="H114" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I114" s="4" t="n">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H115" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I115" s="4" t="n">
+        <v>3.37</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="H116" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I116" s="4" t="n">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="H117" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I117" s="4" t="n">
+        <v>3.86</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="H118" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I118" s="4" t="n">
+        <v>3.86</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="H119" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I119" s="4" t="n">
+        <v>5.77</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H120" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I120" s="4" t="n">
+        <v>6.06</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="H121" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I121" s="4" t="n">
+        <v>7.31</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="H122" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I122" s="4" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="H123" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I123" s="4" t="n">
+        <v>16.32</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="H124" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I124" s="4" t="n">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="H125" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I125" s="4" t="n">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H126" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I126" s="4" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="H127" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I127" s="4" t="n">
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="H128" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I128" s="4" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="H129" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I129" s="4" t="n">
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="H130" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I130" s="4" t="n">
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G131" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="H131" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I131" s="4" t="n">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H132" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I132" s="4" t="n">
+        <v>4.77</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F133" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G133" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H133" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I133" s="4" t="n">
+        <v>5.36</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G134" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H134" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I134" s="4" t="n">
+        <v>8.2</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F135" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G135" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H135" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I135" s="4" t="n">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F136" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="H136" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I136" s="4" t="n">
+        <v>9.2</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G137" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H137" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I137" s="4" t="n">
+        <v>11.32</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G138" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="H138" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I138" s="4" t="n">
+        <v>11.45</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F139" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G139" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H139" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I139" s="4" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H140" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I140" s="4" t="n">
+        <v>16.44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/files/NRL_anytime_tryscorers.xlsx
+++ b/files/NRL_anytime_tryscorers.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="247">
   <si>
     <t xml:space="preserve">Date Local</t>
   </si>
@@ -41,177 +41,687 @@
     <t xml:space="preserve">Anytimeodds</t>
   </si>
   <si>
-    <t xml:space="preserve">19:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100132087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">south sydney rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josiah Karapani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jesse Arthars</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reece Walsh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kotoni Staggs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grant Anderson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brendan Piakura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Gosiewski</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Reynolds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben Talty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Willison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Duffy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cory Paix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payne Haas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preston Riki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Johnston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edward Kosi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jye Gray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campbell Graham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cody Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">David Fifita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tallis Duncan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latrell Siegwalt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keaon Koloamatangi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashton Ward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameron Murray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brandon Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Euan Aitken</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tevita Tatola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lachlan Hubner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bronson Garlick</t>
-  </si>
-  <si>
     <t xml:space="preserve">20:00</t>
   </si>
   <si>
-    <t xml:space="preserve">100068094</t>
+    <t xml:space="preserve">100164057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george-illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominic Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greg Marzhew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fletcher Sharpe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fletcher Hunt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bradman Best</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Lucas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Cant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trey Mooney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dane Gagai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phoenix Crossland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harrison Graham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyson Frizell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mat Croker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Saifiti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setu Tu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinton Gutherson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valentine Holmes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mathew Feagai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Egan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamish Stewart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Liddle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyle Flanagan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Atkinson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mosese Suli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damien Cook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luciano Leilua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loko Pasifiki Tonga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan Couchman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Kerr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100056475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wests tigers</t>
   </si>
   <si>
     <t xml:space="preserve">dolphins</t>
   </si>
   <si>
+    <t xml:space="preserve">Tevita Naufahu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamayne Isaako</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herbie Farnworth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trai Fuller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Bostock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connelly Lemuelu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oryn Keeley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kodi Nikorima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremy Marshall-King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ray Stone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiya Katoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morgan Knowles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Plath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kulikefu Finefeuiaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunia Turuva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jahream Bula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taylan May</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starford To'a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tony Sukkar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sione Fainu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick Herbert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jarome Luai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apisai Koroisau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jock Madden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Seyfarth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terrell May</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fonua Pole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latu Fainu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bunty Afoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Doueihi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100108054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penrith panthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phillip Sami</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jensen Taumoepeau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jojo Fifita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Campbell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keano Kini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AJ Brimson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arama Hau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beau Fermor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zane Harrison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver Pascoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tino Fa'asuamaleaui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurtis Morrin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Verrills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klese Haas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Bai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Jenkins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paul Alamoti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Edwards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Izack Tago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Garner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blaize Talagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiah Papali'i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freddy Lussick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lindsay Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathan Cleary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Cogger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moses Leota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Phillips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scott Sorensen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100231031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manly-warringah sea eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Kiraz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enari Tuala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stephen Crichton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bronson Xerri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Tracey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sitili Tupouniua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaeman Salmon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matt Burton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lachlan Galvin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Mann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Curran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harry Hayes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logan Spinks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lipoi Hopoi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jed Reardon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leo Thompson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Trbojevic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jason Saab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lehi Hopoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tolutau Koula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reuben Garrick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haumole Olakau'atu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Trbojevic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Brooks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamal Fogarty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brandon Wakeham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Bullemor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Trbojevic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taniela Paseka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugo Hart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100104775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murray Taulagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braidon Burns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scott Drinkwater</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zac Laybutt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Chester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heilum Luki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremiah Nanai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Clifford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reed Mahoney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaxon Purdue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reuben Cotter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam McIntyre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Griffin Neame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soni Luke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John Bateman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Sutton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Mikaele</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dallin Watene-Zelezniak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ali Leiataua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charnze Nicoll-Klokstad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Laban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marata Niukore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Te Maire Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taine Tuaupiki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chanel Harris-Tavita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Pompey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wayde Egan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson Ford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erin Clark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Metcalf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100098190</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Savage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Savelio Tamale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaeo Weekes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sebastian Kris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Timoko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Strange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hudson Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zac Hosking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Sanders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Starling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corey Horsburgh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joseph Tapine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Brailey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daine Laurie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moses Leo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Warbrick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sualauvi Faalogo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jahrome Hughes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harry Grant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Clarke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ativalu Lisati</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron Munster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Howarth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe Chan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyran Wishart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stefano Utoikamanu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shawn Blore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trent Loiero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trent Toelau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100149884</t>
+  </si>
+  <si>
     <t xml:space="preserve">sydney roosters</t>
   </si>
   <si>
-    <t xml:space="preserve">Hamiso Tabuai-Fidow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selwyn Cobbo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamayne Isaako</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herbie Farnworth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Bostock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connelly Lemuelu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kulikefu Finefeuiaki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kodi Nikorima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremy Marshall-King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ray Stone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Flegler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiya Katoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morgan Knowles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Plath</t>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronaldo Mulitalo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sione Katoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">William Kennedy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braydon Trindall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayal Iro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesse Ramien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Briton Nikora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teig Wilton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niwhai Puru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Addin Fonua-Blake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Berrell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Hazelton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesse Colquhoun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siosifa Talakai</t>
   </si>
   <si>
     <t xml:space="preserve">Mark Nawaqanitawase</t>
   </si>
   <si>
+    <t xml:space="preserve">Tommy Talau</t>
+  </si>
+  <si>
     <t xml:space="preserve">James Tedesco</t>
   </si>
   <si>
-    <t xml:space="preserve">Hugo Savala</t>
+    <t xml:space="preserve">Robert Toia</t>
   </si>
   <si>
     <t xml:space="preserve">Billy Smith</t>
   </si>
   <si>
-    <t xml:space="preserve">Robert Toia</t>
-  </si>
-  <si>
     <t xml:space="preserve">Daly Cherry-Evans</t>
   </si>
   <si>
@@ -224,13 +734,16 @@
     <t xml:space="preserve">Sam Walker</t>
   </si>
   <si>
+    <t xml:space="preserve">Victor Radley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reece Robson</t>
+  </si>
+  <si>
     <t xml:space="preserve">Connor Watson</t>
   </si>
   <si>
-    <t xml:space="preserve">Victor Radley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reece Robson</t>
+    <t xml:space="preserve">Toby Rodwell</t>
   </si>
   <si>
     <t xml:space="preserve">Nat Butcher</t>
@@ -239,283 +752,7 @@
     <t xml:space="preserve">Egan Butcher</t>
   </si>
   <si>
-    <t xml:space="preserve">Lindsay Collins</t>
-  </si>
-  <si>
     <t xml:space="preserve">Spencer Leniu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100113687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronaldo Mulitalo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samuel Stonestreet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mawene Hiroti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">William Kennedy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Braydon Trindall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kayal Iro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Briton Nikora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teig Wilton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niwhai Puru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Addin Fonua-Blake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hohepa Puru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Hazelton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siosifa Talakai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameron McInnes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toby Rudolf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jesse Colquhoun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Burns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Berrell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oregon Kaufusi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100097428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Savage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Savelio Tamale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaeo Weekes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan Strange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Timoko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daine Laurie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hudson Young</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zac Hosking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan Sanders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Starling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corey Horsburgh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joseph Tapine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Brailey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owen Pattie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Addo-Carr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian Kelly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiah Iongi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan Samrani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sean Russell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kelma Tuilagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitione Kautoga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronald Volkman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joash Papalii</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apa Twidle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tallyn Da Silva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack De Belin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harrison Edwards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luca Moretti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100089245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phillip Sami</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jensen Taumoepeau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jojo Fifita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Campbell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keano Kini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AJ Brimson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arama Hau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beau Fermor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zane Harrison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oliver Pascoe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tino Fa'asuamaleaui</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurtis Morrin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Bai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeral Skelton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Faaletino Tavana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jahream Bula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunia Turuva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heamasi Makasini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mavrik Geyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kai Pearce-Paul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jock Madden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apisai Koroisau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jarome Luai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Royce Hunt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terrell May</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fonua Pole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charlie Murray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latu Fainu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Seyfarth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bunty Afoa</t>
   </si>
 </sst>
 </file>
@@ -864,9 +1101,9 @@
     <col min="1" max="1" width="9.285" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="9.285" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="8.4275" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="19.575" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="23.005" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="23.005" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="25.5775" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="23.8625" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="25.5775" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="21.29" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="6.7125" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="10.1425" hidden="0" customWidth="1"/>
@@ -903,7 +1140,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>9</v>
@@ -918,7 +1155,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>13</v>
@@ -927,12 +1164,12 @@
         <v>1</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>2.67</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>9</v>
@@ -947,7 +1184,7 @@
         <v>12</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>14</v>
@@ -956,12 +1193,12 @@
         <v>1</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>2.83</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>9</v>
@@ -976,7 +1213,7 @@
         <v>12</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>15</v>
@@ -985,12 +1222,12 @@
         <v>1</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>2.87</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>9</v>
@@ -1005,7 +1242,7 @@
         <v>12</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>16</v>
@@ -1014,12 +1251,12 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>3.35</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>9</v>
@@ -1034,7 +1271,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>17</v>
@@ -1043,12 +1280,12 @@
         <v>1</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>3.61</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>9</v>
@@ -1063,7 +1300,7 @@
         <v>12</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>18</v>
@@ -1072,12 +1309,12 @@
         <v>1</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.69</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>9</v>
@@ -1092,7 +1329,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>19</v>
@@ -1101,12 +1338,12 @@
         <v>1</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4.69</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>9</v>
@@ -1121,7 +1358,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>20</v>
@@ -1130,12 +1367,12 @@
         <v>1</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>5.92</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>9</v>
@@ -1150,21 +1387,21 @@
         <v>12</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H10" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>7.35</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>9</v>
@@ -1179,7 +1416,7 @@
         <v>12</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>22</v>
@@ -1188,12 +1425,12 @@
         <v>1</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>7.87</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>9</v>
@@ -1208,7 +1445,7 @@
         <v>12</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>23</v>
@@ -1217,12 +1454,12 @@
         <v>1</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>7.89</v>
+        <v>8.11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>9</v>
@@ -1237,21 +1474,21 @@
         <v>12</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H13" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>9.18</v>
+        <v>8.78</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>9</v>
@@ -1266,21 +1503,21 @@
         <v>12</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H14" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>13.76</v>
+        <v>10.73</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>9</v>
@@ -1295,7 +1532,7 @@
         <v>12</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>26</v>
@@ -1304,12 +1541,12 @@
         <v>1</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>19.09</v>
+        <v>18.69</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>9</v>
@@ -1333,12 +1570,12 @@
         <v>1</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.56</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>9</v>
@@ -1353,7 +1590,7 @@
         <v>12</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>28</v>
@@ -1362,12 +1599,12 @@
         <v>1</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.29</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>9</v>
@@ -1382,7 +1619,7 @@
         <v>12</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>29</v>
@@ -1391,12 +1628,12 @@
         <v>1</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>9</v>
@@ -1411,7 +1648,7 @@
         <v>12</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>30</v>
@@ -1420,12 +1657,12 @@
         <v>1</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>9</v>
@@ -1440,7 +1677,7 @@
         <v>12</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>31</v>
@@ -1449,12 +1686,12 @@
         <v>1</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.98</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>9</v>
@@ -1469,7 +1706,7 @@
         <v>12</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>32</v>
@@ -1478,12 +1715,12 @@
         <v>1</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>3.81</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>9</v>
@@ -1498,7 +1735,7 @@
         <v>12</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>33</v>
@@ -1507,12 +1744,12 @@
         <v>1</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3.81</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>9</v>
@@ -1527,21 +1764,21 @@
         <v>12</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>34</v>
       </c>
       <c r="H23" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.91</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>9</v>
@@ -1556,7 +1793,7 @@
         <v>12</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>35</v>
@@ -1565,12 +1802,12 @@
         <v>1</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>5.53</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>9</v>
@@ -1585,7 +1822,7 @@
         <v>12</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>36</v>
@@ -1594,12 +1831,12 @@
         <v>1</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>5.8</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>9</v>
@@ -1614,7 +1851,7 @@
         <v>12</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>37</v>
@@ -1623,12 +1860,12 @@
         <v>1</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>6.35</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>9</v>
@@ -1643,7 +1880,7 @@
         <v>12</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>38</v>
@@ -1652,12 +1889,12 @@
         <v>1</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>8.56</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>9</v>
@@ -1672,7 +1909,7 @@
         <v>12</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>39</v>
@@ -1681,12 +1918,12 @@
         <v>0</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>9.79</v>
+        <v>8.93</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>9</v>
@@ -1701,7 +1938,7 @@
         <v>12</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>40</v>
@@ -1710,12 +1947,12 @@
         <v>1</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>10.63</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>9</v>
@@ -1730,21 +1967,21 @@
         <v>12</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>41</v>
       </c>
       <c r="H30" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>16.34</v>
+        <v>16.95</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>9</v>
@@ -1759,7 +1996,7 @@
         <v>12</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>42</v>
@@ -1768,12 +2005,12 @@
         <v>0</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>18.42</v>
+        <v>26.65</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>43</v>
@@ -1788,7 +2025,7 @@
         <v>46</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>47</v>
@@ -1797,12 +2034,12 @@
         <v>1</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>43</v>
@@ -1817,7 +2054,7 @@
         <v>46</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>48</v>
@@ -1826,12 +2063,12 @@
         <v>1</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>43</v>
@@ -1846,7 +2083,7 @@
         <v>46</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>49</v>
@@ -1855,12 +2092,12 @@
         <v>1</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>43</v>
@@ -1875,7 +2112,7 @@
         <v>46</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>50</v>
@@ -1884,12 +2121,12 @@
         <v>1</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>43</v>
@@ -1904,7 +2141,7 @@
         <v>46</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>51</v>
@@ -1913,12 +2150,12 @@
         <v>1</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>43</v>
@@ -1933,7 +2170,7 @@
         <v>46</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>52</v>
@@ -1942,12 +2179,12 @@
         <v>1</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>4.72</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>43</v>
@@ -1962,7 +2199,7 @@
         <v>46</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>53</v>
@@ -1971,12 +2208,12 @@
         <v>1</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>4.72</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>43</v>
@@ -1991,7 +2228,7 @@
         <v>46</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>54</v>
@@ -2000,12 +2237,12 @@
         <v>1</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>6.08</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>43</v>
@@ -2020,7 +2257,7 @@
         <v>46</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>55</v>
@@ -2029,12 +2266,12 @@
         <v>1</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>7.56</v>
+        <v>7.02</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>43</v>
@@ -2049,7 +2286,7 @@
         <v>46</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>56</v>
@@ -2058,12 +2295,12 @@
         <v>0</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>10.11</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>43</v>
@@ -2078,7 +2315,7 @@
         <v>46</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>57</v>
@@ -2087,12 +2324,12 @@
         <v>1</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>10.83</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>43</v>
@@ -2107,7 +2344,7 @@
         <v>46</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>58</v>
@@ -2116,12 +2353,12 @@
         <v>1</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>12.33</v>
+        <v>14.35</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>43</v>
@@ -2136,21 +2373,21 @@
         <v>46</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>59</v>
       </c>
       <c r="H44" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>14.11</v>
+        <v>14.76</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>43</v>
@@ -2165,7 +2402,7 @@
         <v>46</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>60</v>
@@ -2174,12 +2411,12 @@
         <v>0</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>15.16</v>
+        <v>15.93</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>43</v>
@@ -2194,7 +2431,7 @@
         <v>46</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>61</v>
@@ -2203,12 +2440,12 @@
         <v>1</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>1.81</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>43</v>
@@ -2223,7 +2460,7 @@
         <v>46</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>62</v>
@@ -2232,12 +2469,12 @@
         <v>1</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>2.82</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>43</v>
@@ -2252,7 +2489,7 @@
         <v>46</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>63</v>
@@ -2261,12 +2498,12 @@
         <v>1</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>2.96</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>43</v>
@@ -2281,7 +2518,7 @@
         <v>46</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>64</v>
@@ -2290,12 +2527,12 @@
         <v>1</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>3.1</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>43</v>
@@ -2310,7 +2547,7 @@
         <v>46</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>65</v>
@@ -2319,12 +2556,12 @@
         <v>1</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>3.75</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>43</v>
@@ -2339,7 +2576,7 @@
         <v>46</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>66</v>
@@ -2348,12 +2585,12 @@
         <v>1</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>4.69</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>43</v>
@@ -2368,7 +2605,7 @@
         <v>46</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>67</v>
@@ -2377,12 +2614,12 @@
         <v>1</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>4.85</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>43</v>
@@ -2397,7 +2634,7 @@
         <v>46</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>68</v>
@@ -2406,12 +2643,12 @@
         <v>1</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>4.85</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>43</v>
@@ -2426,7 +2663,7 @@
         <v>46</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>69</v>
@@ -2435,12 +2672,12 @@
         <v>1</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>4.92</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>43</v>
@@ -2455,7 +2692,7 @@
         <v>46</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>70</v>
@@ -2464,12 +2701,12 @@
         <v>1</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>7.8</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>43</v>
@@ -2484,7 +2721,7 @@
         <v>46</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>71</v>
@@ -2493,12 +2730,12 @@
         <v>1</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>8.39</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>43</v>
@@ -2513,21 +2750,21 @@
         <v>46</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>72</v>
       </c>
       <c r="H57" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>9.85</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>43</v>
@@ -2542,21 +2779,21 @@
         <v>46</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>73</v>
       </c>
       <c r="H58" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>11.21</v>
+        <v>8.36</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>43</v>
@@ -2571,7 +2808,7 @@
         <v>46</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>74</v>
@@ -2580,12 +2817,12 @@
         <v>0</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>12.35</v>
+        <v>10.65</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>43</v>
@@ -2600,7 +2837,7 @@
         <v>46</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>75</v>
@@ -2609,12 +2846,12 @@
         <v>0</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>15.59</v>
+        <v>14.87</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>43</v>
@@ -2629,21 +2866,21 @@
         <v>46</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>76</v>
       </c>
       <c r="H61" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>15.98</v>
+        <v>15.51</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>77</v>
@@ -2658,7 +2895,7 @@
         <v>80</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>81</v>
@@ -2667,12 +2904,12 @@
         <v>1</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>2.14</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>77</v>
@@ -2687,7 +2924,7 @@
         <v>80</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>82</v>
@@ -2696,12 +2933,12 @@
         <v>1</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>2.36</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>77</v>
@@ -2716,7 +2953,7 @@
         <v>80</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>83</v>
@@ -2725,12 +2962,12 @@
         <v>1</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>3.44</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>77</v>
@@ -2745,7 +2982,7 @@
         <v>80</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>84</v>
@@ -2754,12 +2991,12 @@
         <v>1</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>3.51</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>77</v>
@@ -2774,7 +3011,7 @@
         <v>80</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>85</v>
@@ -2783,12 +3020,12 @@
         <v>1</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>3.56</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>77</v>
@@ -2803,7 +3040,7 @@
         <v>80</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>86</v>
@@ -2812,12 +3049,12 @@
         <v>1</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>3.64</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>77</v>
@@ -2832,7 +3069,7 @@
         <v>80</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>87</v>
@@ -2841,12 +3078,12 @@
         <v>1</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>4.78</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>77</v>
@@ -2861,7 +3098,7 @@
         <v>80</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>88</v>
@@ -2870,12 +3107,12 @@
         <v>1</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>4.78</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>77</v>
@@ -2890,7 +3127,7 @@
         <v>80</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>89</v>
@@ -2899,12 +3136,12 @@
         <v>1</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>4.87</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>77</v>
@@ -2919,7 +3156,7 @@
         <v>80</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>90</v>
@@ -2928,12 +3165,12 @@
         <v>1</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>6.27</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>77</v>
@@ -2948,7 +3185,7 @@
         <v>80</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>91</v>
@@ -2957,12 +3194,12 @@
         <v>1</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>6.71</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>77</v>
@@ -2977,7 +3214,7 @@
         <v>80</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>92</v>
@@ -2986,12 +3223,12 @@
         <v>0</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>9.81</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>77</v>
@@ -3006,7 +3243,7 @@
         <v>80</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>93</v>
@@ -3015,12 +3252,12 @@
         <v>0</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>11.52</v>
+        <v>14.76</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>77</v>
@@ -3035,21 +3272,21 @@
         <v>80</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>94</v>
       </c>
       <c r="H75" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>13.63</v>
+        <v>15.41</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>77</v>
@@ -3064,7 +3301,7 @@
         <v>80</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>95</v>
@@ -3073,12 +3310,12 @@
         <v>1</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>19.06</v>
+        <v>15.43</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>77</v>
@@ -3099,15 +3336,15 @@
         <v>96</v>
       </c>
       <c r="H77" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>19.69</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>77</v>
@@ -3128,15 +3365,15 @@
         <v>97</v>
       </c>
       <c r="H78" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>25.24</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>77</v>
@@ -3157,15 +3394,15 @@
         <v>98</v>
       </c>
       <c r="H79" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>39.6</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>77</v>
@@ -3186,349 +3423,349 @@
         <v>99</v>
       </c>
       <c r="H80" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>43.61</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B81" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G81" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C81" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="H81" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>2.18</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="C82" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G82" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D82" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="H82" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>2.39</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="D83" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G83" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="H83" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>2.53</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="E84" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G84" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="F84" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G84" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="H84" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>3.12</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H85" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>3.16</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H86" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>3.31</v>
+        <v>8.38</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H87" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>3.64</v>
+        <v>8.91</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H88" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>3.64</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H89" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I89" s="4" t="n">
-        <v>5.77</v>
+        <v>16.38</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H90" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>7.49</v>
+        <v>16.65</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H91" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>9.34</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>115</v>
@@ -3537,27 +3774,27 @@
         <v>1</v>
       </c>
       <c r="I92" s="4" t="n">
-        <v>12.38</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>116</v>
@@ -3566,56 +3803,56 @@
         <v>1</v>
       </c>
       <c r="I93" s="4" t="n">
-        <v>12.67</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>117</v>
       </c>
       <c r="H94" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I94" s="4" t="n">
-        <v>14.21</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="G95" s="3" t="s">
         <v>118</v>
@@ -3624,27 +3861,27 @@
         <v>1</v>
       </c>
       <c r="I95" s="4" t="n">
-        <v>1.97</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>119</v>
@@ -3653,27 +3890,27 @@
         <v>1</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>2.27</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>120</v>
@@ -3682,27 +3919,27 @@
         <v>1</v>
       </c>
       <c r="I97" s="4" t="n">
-        <v>2.88</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>121</v>
@@ -3711,27 +3948,27 @@
         <v>1</v>
       </c>
       <c r="I98" s="4" t="n">
-        <v>3.47</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>122</v>
@@ -3740,27 +3977,27 @@
         <v>1</v>
       </c>
       <c r="I99" s="4" t="n">
-        <v>4.03</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>123</v>
@@ -3769,27 +4006,27 @@
         <v>1</v>
       </c>
       <c r="I100" s="4" t="n">
-        <v>4.05</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>124</v>
@@ -3798,56 +4035,56 @@
         <v>1</v>
       </c>
       <c r="I101" s="4" t="n">
-        <v>4.05</v>
+        <v>8.37</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>125</v>
       </c>
       <c r="H102" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I102" s="4" t="n">
-        <v>4.45</v>
+        <v>11.14</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="G103" s="3" t="s">
         <v>126</v>
@@ -3856,27 +4093,27 @@
         <v>1</v>
       </c>
       <c r="I103" s="4" t="n">
-        <v>5.16</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="G104" s="3" t="s">
         <v>127</v>
@@ -3885,27 +4122,27 @@
         <v>0</v>
       </c>
       <c r="I104" s="4" t="n">
-        <v>6.79</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="G105" s="3" t="s">
         <v>128</v>
@@ -3914,56 +4151,56 @@
         <v>0</v>
       </c>
       <c r="I105" s="4" t="n">
-        <v>7.53</v>
+        <v>19.56</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="G106" s="3" t="s">
         <v>129</v>
       </c>
       <c r="H106" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I106" s="4" t="n">
-        <v>9.41</v>
+        <v>19.57</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>130</v>
@@ -3972,27 +4209,27 @@
         <v>1</v>
       </c>
       <c r="I107" s="4" t="n">
-        <v>10.33</v>
+        <v>20.15</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>131</v>
@@ -4001,27 +4238,27 @@
         <v>1</v>
       </c>
       <c r="I108" s="4" t="n">
-        <v>11.43</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="G109" s="3" t="s">
         <v>132</v>
@@ -4030,404 +4267,404 @@
         <v>1</v>
       </c>
       <c r="I109" s="4" t="n">
-        <v>11.79</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>133</v>
       </c>
       <c r="H110" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I110" s="4" t="n">
-        <v>12.45</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B111" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G111" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C111" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="F111" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="G111" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="H111" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I111" s="4" t="n">
-        <v>2.06</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C112" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G112" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D112" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E112" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="F112" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="G112" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="H112" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I112" s="4" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="D113" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G113" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="E113" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="F113" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="G113" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="H113" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I113" s="4" t="n">
-        <v>3.1</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="E114" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G114" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="F114" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="G114" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="H114" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I114" s="4" t="n">
-        <v>3.29</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H115" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I115" s="4" t="n">
-        <v>3.37</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="H116" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I116" s="4" t="n">
-        <v>3.43</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="H117" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I117" s="4" t="n">
-        <v>3.86</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="H118" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I118" s="4" t="n">
-        <v>3.86</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="H119" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I119" s="4" t="n">
-        <v>5.77</v>
+        <v>17.97</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="H120" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I120" s="4" t="n">
-        <v>6.06</v>
+        <v>18.11</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H121" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I121" s="4" t="n">
-        <v>7.31</v>
+        <v>18.91</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>46187</v>
+        <v>46194</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="G122" s="3" t="s">
         <v>149</v>
       </c>
       <c r="H122" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I122" s="4" t="n">
-        <v>11.1</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>46187</v>
+        <v>46194</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="G123" s="3" t="s">
         <v>150</v>
@@ -4436,27 +4673,27 @@
         <v>1</v>
       </c>
       <c r="I123" s="4" t="n">
-        <v>16.32</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>46187</v>
+        <v>46194</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>151</v>
@@ -4465,27 +4702,27 @@
         <v>1</v>
       </c>
       <c r="I124" s="4" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>46187</v>
+        <v>46194</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G125" s="3" t="s">
         <v>152</v>
@@ -4494,27 +4731,27 @@
         <v>1</v>
       </c>
       <c r="I125" s="4" t="n">
-        <v>2.05</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>46187</v>
+        <v>46194</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G126" s="3" t="s">
         <v>153</v>
@@ -4523,27 +4760,27 @@
         <v>1</v>
       </c>
       <c r="I126" s="4" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>46187</v>
+        <v>46194</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G127" s="3" t="s">
         <v>154</v>
@@ -4552,27 +4789,27 @@
         <v>1</v>
       </c>
       <c r="I127" s="4" t="n">
-        <v>2.42</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>46187</v>
+        <v>46194</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G128" s="3" t="s">
         <v>155</v>
@@ -4581,27 +4818,27 @@
         <v>1</v>
       </c>
       <c r="I128" s="4" t="n">
-        <v>3.49</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>46187</v>
+        <v>46194</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G129" s="3" t="s">
         <v>156</v>
@@ -4610,27 +4847,27 @@
         <v>1</v>
       </c>
       <c r="I129" s="4" t="n">
-        <v>3.51</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>46187</v>
+        <v>46194</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G130" s="3" t="s">
         <v>157</v>
@@ -4639,27 +4876,27 @@
         <v>1</v>
       </c>
       <c r="I130" s="4" t="n">
-        <v>3.51</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>46187</v>
+        <v>46194</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G131" s="3" t="s">
         <v>158</v>
@@ -4668,27 +4905,27 @@
         <v>1</v>
       </c>
       <c r="I131" s="4" t="n">
-        <v>4.71</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>46187</v>
+        <v>46194</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G132" s="3" t="s">
         <v>159</v>
@@ -4697,56 +4934,56 @@
         <v>1</v>
       </c>
       <c r="I132" s="4" t="n">
-        <v>4.77</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>46187</v>
+        <v>46194</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G133" s="3" t="s">
         <v>160</v>
       </c>
       <c r="H133" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I133" s="4" t="n">
-        <v>5.36</v>
+        <v>9.89</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>46187</v>
+        <v>46194</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G134" s="3" t="s">
         <v>161</v>
@@ -4755,181 +4992,2240 @@
         <v>0</v>
       </c>
       <c r="I134" s="4" t="n">
-        <v>8.2</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>46187</v>
+        <v>46194</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G135" s="3" t="s">
         <v>162</v>
       </c>
       <c r="H135" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I135" s="4" t="n">
-        <v>8.25</v>
+        <v>11.98</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>46187</v>
+        <v>46194</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G136" s="3" t="s">
         <v>163</v>
       </c>
       <c r="H136" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I136" s="4" t="n">
-        <v>9.2</v>
+        <v>15.43</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>46187</v>
+        <v>46194</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G137" s="3" t="s">
         <v>164</v>
       </c>
       <c r="H137" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I137" s="4" t="n">
-        <v>11.32</v>
+        <v>16.58</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>46187</v>
+        <v>46194</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G138" s="3" t="s">
         <v>165</v>
       </c>
       <c r="H138" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I138" s="4" t="n">
-        <v>11.45</v>
+        <v>17.44</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>46187</v>
+        <v>46194</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="G139" s="3" t="s">
         <v>166</v>
       </c>
       <c r="H139" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I139" s="4" t="n">
-        <v>14</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>46187</v>
+        <v>46194</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="G140" s="3" t="s">
         <v>167</v>
       </c>
       <c r="H140" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I140" s="4" t="n">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F141" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H141" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I141" s="4" t="n">
+        <v>4.31</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F142" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H142" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I142" s="4" t="n">
+        <v>4.42</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H143" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I143" s="4" t="n">
+        <v>4.42</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H144" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I144" s="4" t="n">
+        <v>4.78</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G145" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H145" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I145" s="4" t="n">
+        <v>4.79</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H146" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I146" s="4" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G147" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H147" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I147" s="4" t="n">
+        <v>5.15</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G148" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H148" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I148" s="4" t="n">
+        <v>7.68</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E149" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F149" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G149" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H149" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I149" s="4" t="n">
+        <v>8.45</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F150" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G150" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H150" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I150" s="4" t="n">
+        <v>12.09</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E151" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G151" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H151" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="I140" s="4" t="n">
-        <v>16.44</v>
+      <c r="I151" s="4" t="n">
+        <v>12.77</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G152" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H152" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I152" s="4" t="n">
+        <v>2.51</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E153" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F153" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G153" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H153" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I153" s="4" t="n">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F154" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G154" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="H154" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I154" s="4" t="n">
+        <v>2.95</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G155" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="H155" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I155" s="4" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G156" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="H156" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I156" s="4" t="n">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F157" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G157" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H157" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I157" s="4" t="n">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F158" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G158" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="H158" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I158" s="4" t="n">
+        <v>4.24</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E159" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F159" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G159" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="H159" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I159" s="4" t="n">
+        <v>4.24</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F160" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="H160" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I160" s="4" t="n">
+        <v>6.98</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F161" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G161" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="H161" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I161" s="4" t="n">
+        <v>8.98</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="H162" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I162" s="4" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E163" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G163" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="H163" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I163" s="4" t="n">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E164" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G164" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="H164" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I164" s="4" t="n">
+        <v>16.11</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F165" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H165" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I165" s="4" t="n">
+        <v>16.86</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E166" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F166" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G166" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H166" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I166" s="4" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E167" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F167" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G167" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="H167" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I167" s="4" t="n">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E168" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F168" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G168" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H168" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I168" s="4" t="n">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E169" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F169" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G169" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H169" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I169" s="4" t="n">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E170" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F170" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="H170" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I170" s="4" t="n">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E171" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F171" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G171" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="H171" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I171" s="4" t="n">
+        <v>3.87</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E172" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F172" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="H172" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I172" s="4" t="n">
+        <v>3.87</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E173" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F173" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G173" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="H173" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I173" s="4" t="n">
+        <v>4.01</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E174" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F174" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G174" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="H174" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I174" s="4" t="n">
+        <v>4.02</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E175" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F175" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G175" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="H175" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I175" s="4" t="n">
+        <v>4.42</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E176" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F176" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G176" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="H176" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I176" s="4" t="n">
+        <v>8.04</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E177" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F177" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G177" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="H177" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I177" s="4" t="n">
+        <v>8.05</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E178" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F178" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G178" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="H178" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I178" s="4" t="n">
+        <v>10.52</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D179" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E179" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F179" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G179" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="H179" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I179" s="4" t="n">
+        <v>14.93</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D180" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E180" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F180" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G180" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H180" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I180" s="4" t="n">
+        <v>15.89</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D181" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E181" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F181" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G181" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="H181" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I181" s="4" t="n">
+        <v>16.59</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E182" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F182" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G182" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="H182" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I182" s="4" t="n">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D183" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E183" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F183" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G183" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="H183" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I183" s="4" t="n">
+        <v>2.56</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E184" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F184" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G184" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="H184" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I184" s="4" t="n">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D185" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E185" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F185" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G185" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="H185" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I185" s="4" t="n">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E186" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F186" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G186" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="H186" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I186" s="4" t="n">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D187" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E187" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F187" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G187" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="H187" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I187" s="4" t="n">
+        <v>4.32</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E188" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F188" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G188" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="H188" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I188" s="4" t="n">
+        <v>4.81</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E189" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F189" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G189" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="H189" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I189" s="4" t="n">
+        <v>4.81</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E190" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F190" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G190" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="H190" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I190" s="4" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C191" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D191" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E191" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F191" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G191" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="H191" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I191" s="4" t="n">
+        <v>6.31</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C192" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D192" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E192" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F192" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G192" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="H192" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I192" s="4" t="n">
+        <v>8.95</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C193" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E193" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F193" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G193" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="H193" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I193" s="4" t="n">
+        <v>10.01</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E194" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F194" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G194" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H194" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I194" s="4" t="n">
+        <v>11.01</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F195" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G195" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="H195" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I195" s="4" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E196" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F196" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G196" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="H196" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I196" s="4" t="n">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E197" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F197" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G197" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="H197" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I197" s="4" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B198" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C198" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D198" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E198" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F198" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G198" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="H198" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I198" s="4" t="n">
+        <v>2.73</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C199" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D199" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E199" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F199" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G199" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="H199" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I199" s="4" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C200" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E200" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F200" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G200" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H200" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I200" s="4" t="n">
+        <v>4.17</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D201" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E201" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F201" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G201" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="H201" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I201" s="4" t="n">
+        <v>4.56</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D202" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E202" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F202" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G202" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="H202" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I202" s="4" t="n">
+        <v>4.68</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D203" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E203" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F203" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G203" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="H203" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I203" s="4" t="n">
+        <v>4.68</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D204" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E204" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F204" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G204" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="H204" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I204" s="4" t="n">
+        <v>4.74</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D205" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E205" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F205" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G205" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="H205" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I205" s="4" t="n">
+        <v>8.08</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E206" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F206" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G206" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="H206" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I206" s="4" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C207" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D207" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E207" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F207" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G207" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="H207" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I207" s="4" t="n">
+        <v>10.18</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C208" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D208" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E208" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F208" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G208" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="H208" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I208" s="4" t="n">
+        <v>10.85</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B209" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C209" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D209" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E209" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F209" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G209" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="H209" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I209" s="4" t="n">
+        <v>11.03</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B210" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C210" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D210" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E210" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F210" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G210" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="H210" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I210" s="4" t="n">
+        <v>12.08</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B211" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C211" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E211" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F211" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G211" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="H211" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I211" s="4" t="n">
+        <v>12.3</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_anytime_tryscorers.xlsx
+++ b/files/NRL_anytime_tryscorers.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="281">
   <si>
     <t xml:space="preserve">Date Local</t>
   </si>
@@ -41,16 +41,730 @@
     <t xml:space="preserve">Anytimeodds</t>
   </si>
   <si>
+    <t xml:space="preserve">19:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100127679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Addo-Carr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian Kelly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiah Iongi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Samrani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitchell Moses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kelma Tuilagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kitione Kautoga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sean Russell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tallyn Da Silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronald Volkman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apa Twidle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack De Belin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luca Moretti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Johnston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edward Kosi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tallis Duncan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jye Gray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cody Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">David Fifita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euan Aitken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latrell Siegwalt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keaon Koloamatangi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashton Ward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron Murray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John Radel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Sullivan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brandon Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamie Humphreys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tevita Tatola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100178920</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jethro Rinakama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Kiraz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matt Burton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Tracey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enari Tuala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Curran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaeman Salmon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lachlan Galvin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stephen Crichton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Preston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Mann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bailey Hayward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harry Hayes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phillip Sami</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaylan De Groot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jojo Fifita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Campbell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keano Kini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AJ Brimson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arama Hau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beau Fermor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zane Harrison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver Pascoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tino Fa'asuamaleaui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chris Randall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurtis Morrin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Verrills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klese Haas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lachlan Ilias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dean Ieremia</t>
+  </si>
+  <si>
     <t xml:space="preserve">20:00</t>
   </si>
   <si>
-    <t xml:space="preserve">100164057</t>
+    <t xml:space="preserve">100100698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josiah Karapani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesse Arthars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reece Walsh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kotoni Staggs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grant Anderson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brendan Piakura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Riki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Hunt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Talty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Willison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Duffy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cory Paix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payne Haas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blake Mozer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark Nawaqanitawase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Tedesco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugo Savala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robert Toia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daly Cherry-Evans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nat Butcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siua Wong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reece Robson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Victor Radley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Watson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toby Rodwell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egan Butcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spencer Leniu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lindsay Collins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100044684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamiso Tabuai-Fidow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selwyn Cobbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamayne Isaako</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herbie Farnworth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Bostock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connelly Lemuelu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kulikefu Finefeuiaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kodi Nikorima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremy Marshall-King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ray Stone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Flegler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiya Katoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Plath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morgan Knowles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trai Fuller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francis Molo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Donoghoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dallin Watene-Zelezniak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ali Leiataua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charnze Nicoll-Klokstad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Laban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Capewell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taine Tuaupiki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Te Maire Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chanel Harris-Tavita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Pompey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wayde Egan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erin Clark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Metcalf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tanner Stowers-Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100144696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penrith panthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braidon Burns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murray Taulagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scott Drinkwater</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zac Laybutt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Chester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heilum Luki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremiah Nanai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Clifford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reed Mahoney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaxon Purdue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reuben Cotter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam McIntyre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Griffin Neame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soni Luke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Jenkins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian To'o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Edwards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Izack Tago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paul Alamoti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathan Cleary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiah Papali'i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blaize Talagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freddy Lussick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lindsay Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaah Yeo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Garner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Henry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moses Leota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scott Sorensen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100147430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manly-warringah sea eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Trbojevic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lehi Hopoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jason Saab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tolutau Koula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Feledy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haumole Olakau'atu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Trbojevic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Brooks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamal Fogarty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Simpkin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aaron Schoupp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clayton Faulalo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Trbojevic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taniela Paseka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugo Hart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Bullemor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moses Leo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Warbrick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sualauvi Faalogo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harry Grant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyran Wishart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Clarke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ativalu Lisati</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron Munster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Howarth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe Chan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stefano Utoikamanu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shawn Blore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trent Loiero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100157762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george-illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Savage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Savelio Tamale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaeo Weekes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simi Sasagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Timoko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Strange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hudson Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zac Hosking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owen Pattie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Sanders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corey Horsburgh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joseph Tapine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Starling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Brailey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Clydsdale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coby Black</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sebastian Kris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyrell Sloan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setu Tu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mathew Feagai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinton Gutherson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valentine Holmes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Egan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamish Stewart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Liddle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyle Flanagan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Atkinson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damien Cook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luciano Leilua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loko Pasifiki Tonga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100090974</t>
   </si>
   <si>
     <t xml:space="preserve">newcastle knights</t>
   </si>
   <si>
-    <t xml:space="preserve">st george-illawarra dragons</t>
+    <t xml:space="preserve">wests tigers</t>
   </si>
   <si>
     <t xml:space="preserve">Dominic Young</t>
@@ -62,27 +776,30 @@
     <t xml:space="preserve">Fletcher Sharpe</t>
   </si>
   <si>
+    <t xml:space="preserve">Bradman Best</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kalyn Ponga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Lucas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jermaine McEwen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trey Mooney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dane Gagai</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fletcher Hunt</t>
   </si>
   <si>
-    <t xml:space="preserve">Bradman Best</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Lucas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Cant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trey Mooney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dane Gagai</t>
-  </si>
-  <si>
     <t xml:space="preserve">Phoenix Crossland</t>
   </si>
   <si>
@@ -98,103 +815,7 @@
     <t xml:space="preserve">Jacob Saifiti</t>
   </si>
   <si>
-    <t xml:space="preserve">Setu Tu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clinton Gutherson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valentine Holmes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mathew Feagai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Egan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamish Stewart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Liddle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyle Flanagan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel Atkinson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mosese Suli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Damien Cook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luciano Leilua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loko Pasifiki Tonga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan Couchman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Kerr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100056475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tevita Naufahu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamayne Isaako</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herbie Farnworth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trai Fuller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Bostock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connelly Lemuelu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oryn Keeley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kodi Nikorima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremy Marshall-King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ray Stone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiya Katoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morgan Knowles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Plath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kulikefu Finefeuiaki</t>
+    <t xml:space="preserve">Jeral Skelton</t>
   </si>
   <si>
     <t xml:space="preserve">Sunia Turuva</t>
@@ -206,6 +827,9 @@
     <t xml:space="preserve">Taylan May</t>
   </si>
   <si>
+    <t xml:space="preserve">Adam Doueihi</t>
+  </si>
+  <si>
     <t xml:space="preserve">Starford To'a</t>
   </si>
   <si>
@@ -215,544 +839,22 @@
     <t xml:space="preserve">Sione Fainu</t>
   </si>
   <si>
-    <t xml:space="preserve">Patrick Herbert</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jarome Luai</t>
   </si>
   <si>
     <t xml:space="preserve">Apisai Koroisau</t>
   </si>
   <si>
-    <t xml:space="preserve">Jock Madden</t>
+    <t xml:space="preserve">Terrell May</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fonua Pole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latu Fainu</t>
   </si>
   <si>
     <t xml:space="preserve">Alex Seyfarth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terrell May</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fonua Pole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latu Fainu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bunty Afoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Doueihi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100108054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penrith panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phillip Sami</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jensen Taumoepeau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jojo Fifita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Campbell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keano Kini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AJ Brimson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arama Hau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beau Fermor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zane Harrison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oliver Pascoe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tino Fa'asuamaleaui</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurtis Morrin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Verrills</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Klese Haas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Bai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Jenkins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paul Alamoti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Edwards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Izack Tago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Garner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blaize Talagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiah Papali'i</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freddy Lussick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lindsay Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nathan Cleary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Cogger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moses Leota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Phillips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scott Sorensen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100231031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manly-warringah sea eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Kiraz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enari Tuala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stephen Crichton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bronson Xerri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Tracey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sitili Tupouniua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaeman Salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matt Burton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lachlan Galvin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurt Mann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Curran</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harry Hayes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logan Spinks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lipoi Hopoi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jed Reardon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leo Thompson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Trbojevic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jason Saab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lehi Hopoate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tolutau Koula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reuben Garrick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haumole Olakau'atu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben Trbojevic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Brooks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamal Fogarty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brandon Wakeham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan Bullemor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Trbojevic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taniela Paseka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hugo Hart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100104775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Murray Taulagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Braidon Burns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scott Drinkwater</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zac Laybutt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Chester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heilum Luki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremiah Nanai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Clifford</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reed Mahoney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaxon Purdue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reuben Cotter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam McIntyre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Griffin Neame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soni Luke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">John Bateman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Sutton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Mikaele</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dallin Watene-Zelezniak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ali Leiataua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charnze Nicoll-Klokstad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Laban</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marata Niukore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Te Maire Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taine Tuaupiki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chanel Harris-Tavita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Pompey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wayde Egan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson Ford</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erin Clark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Metcalf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100098190</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Savage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Savelio Tamale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaeo Weekes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sebastian Kris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Timoko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan Strange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hudson Young</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zac Hosking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan Sanders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Starling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corey Horsburgh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joseph Tapine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Brailey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daine Laurie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moses Leo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Will Warbrick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sualauvi Faalogo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jahrome Hughes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harry Grant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Clarke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ativalu Lisati</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameron Munster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Howarth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joe Chan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyran Wishart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stefano Utoikamanu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shawn Blore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trent Loiero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trent Toelau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100149884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronaldo Mulitalo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sione Katoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">William Kennedy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Braydon Trindall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kayal Iro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jesse Ramien</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Briton Nikora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teig Wilton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niwhai Puru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Addin Fonua-Blake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Berrell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Hazelton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jesse Colquhoun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siosifa Talakai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mark Nawaqanitawase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tommy Talau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Tedesco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robert Toia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daly Cherry-Evans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angus Crichton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siua Wong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Victor Radley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reece Robson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Watson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toby Rodwell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nat Butcher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Egan Butcher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spencer Leniu</t>
   </si>
 </sst>
 </file>
@@ -1101,8 +1203,8 @@
     <col min="1" max="1" width="9.285" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="9.285" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="8.4275" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="25.5775" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="23.8625" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="23.005" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="25.5775" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="25.5775" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="21.29" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="6.7125" hidden="0" customWidth="1"/>
@@ -1140,7 +1242,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>9</v>
@@ -1164,12 +1266,12 @@
         <v>1</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>1.79</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>9</v>
@@ -1193,12 +1295,12 @@
         <v>1</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>2.09</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>9</v>
@@ -1222,12 +1324,12 @@
         <v>1</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>2.47</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>9</v>
@@ -1251,12 +1353,12 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>2.77</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>9</v>
@@ -1280,12 +1382,12 @@
         <v>1</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>3.01</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>9</v>
@@ -1309,12 +1411,12 @@
         <v>1</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.01</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>9</v>
@@ -1338,12 +1440,12 @@
         <v>1</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4.01</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>9</v>
@@ -1367,12 +1469,12 @@
         <v>1</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.21</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>9</v>
@@ -1396,12 +1498,12 @@
         <v>1</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.64</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>9</v>
@@ -1425,12 +1527,12 @@
         <v>1</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>4.95</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>9</v>
@@ -1451,15 +1553,15 @@
         <v>23</v>
       </c>
       <c r="H12" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>8.11</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>9</v>
@@ -1480,15 +1582,15 @@
         <v>24</v>
       </c>
       <c r="H13" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>8.78</v>
+        <v>11.07</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>9</v>
@@ -1509,15 +1611,15 @@
         <v>25</v>
       </c>
       <c r="H14" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>10.73</v>
+        <v>13.93</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>9</v>
@@ -1541,12 +1643,12 @@
         <v>1</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>18.69</v>
+        <v>14.16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>9</v>
@@ -1561,7 +1663,7 @@
         <v>12</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>27</v>
@@ -1570,12 +1672,12 @@
         <v>1</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>19</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>9</v>
@@ -1599,12 +1701,12 @@
         <v>1</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.44</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>9</v>
@@ -1628,12 +1730,12 @@
         <v>1</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.68</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>9</v>
@@ -1657,12 +1759,12 @@
         <v>1</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2.75</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>9</v>
@@ -1686,12 +1788,12 @@
         <v>1</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>9</v>
@@ -1715,12 +1817,12 @@
         <v>1</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>4.2</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>9</v>
@@ -1744,12 +1846,12 @@
         <v>1</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>4.2</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>9</v>
@@ -1770,15 +1872,15 @@
         <v>34</v>
       </c>
       <c r="H23" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>5.15</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>9</v>
@@ -1802,12 +1904,12 @@
         <v>1</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>5.5</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>9</v>
@@ -1831,12 +1933,12 @@
         <v>1</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>5.54</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>9</v>
@@ -1860,12 +1962,12 @@
         <v>1</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.68</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>9</v>
@@ -1886,15 +1988,15 @@
         <v>38</v>
       </c>
       <c r="H27" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>6.6</v>
+        <v>9.63</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>9</v>
@@ -1918,12 +2020,12 @@
         <v>0</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>8.93</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>9</v>
@@ -1947,12 +2049,12 @@
         <v>1</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>12.84</v>
+        <v>11.01</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>9</v>
@@ -1973,15 +2075,15 @@
         <v>41</v>
       </c>
       <c r="H30" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>16.95</v>
+        <v>12.43</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>9</v>
@@ -2002,15 +2104,15 @@
         <v>42</v>
       </c>
       <c r="H31" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>26.65</v>
+        <v>13.66</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>43</v>
@@ -2034,12 +2136,12 @@
         <v>1</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>43</v>
@@ -2063,12 +2165,12 @@
         <v>1</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.42</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>43</v>
@@ -2092,12 +2194,12 @@
         <v>1</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>2.67</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>43</v>
@@ -2121,12 +2223,12 @@
         <v>1</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>2.92</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>43</v>
@@ -2150,12 +2252,12 @@
         <v>1</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>2.95</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>43</v>
@@ -2179,12 +2281,12 @@
         <v>1</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>4.62</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>43</v>
@@ -2208,12 +2310,12 @@
         <v>1</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>4.62</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>43</v>
@@ -2237,12 +2339,12 @@
         <v>1</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>5.68</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>43</v>
@@ -2266,12 +2368,12 @@
         <v>1</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>7.02</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>43</v>
@@ -2295,12 +2397,12 @@
         <v>0</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>9.98</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>43</v>
@@ -2321,15 +2423,15 @@
         <v>57</v>
       </c>
       <c r="H42" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>10.96</v>
+        <v>10.72</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>43</v>
@@ -2353,12 +2455,12 @@
         <v>1</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>14.35</v>
+        <v>11.87</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>43</v>
@@ -2379,15 +2481,15 @@
         <v>59</v>
       </c>
       <c r="H44" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>14.76</v>
+        <v>17.38</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>43</v>
@@ -2402,21 +2504,21 @@
         <v>46</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>60</v>
       </c>
       <c r="H45" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>15.93</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>43</v>
@@ -2440,12 +2542,12 @@
         <v>1</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>2.06</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>43</v>
@@ -2469,12 +2571,12 @@
         <v>1</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>2.24</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>43</v>
@@ -2498,12 +2600,12 @@
         <v>1</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>2.26</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>43</v>
@@ -2527,12 +2629,12 @@
         <v>1</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>2.44</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>43</v>
@@ -2556,12 +2658,12 @@
         <v>1</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>3.22</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>43</v>
@@ -2585,12 +2687,12 @@
         <v>1</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>3.22</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>43</v>
@@ -2614,12 +2716,12 @@
         <v>1</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>4.26</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>43</v>
@@ -2643,12 +2745,12 @@
         <v>1</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>4.33</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>43</v>
@@ -2672,12 +2774,12 @@
         <v>1</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>4.36</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>43</v>
@@ -2701,12 +2803,12 @@
         <v>1</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>4.39</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>43</v>
@@ -2730,12 +2832,12 @@
         <v>1</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>6.96</v>
+        <v>7.77</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>43</v>
@@ -2756,15 +2858,15 @@
         <v>72</v>
       </c>
       <c r="H57" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>7.63</v>
+        <v>8.56</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>43</v>
@@ -2785,15 +2887,15 @@
         <v>73</v>
       </c>
       <c r="H58" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>8.36</v>
+        <v>16.49</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>43</v>
@@ -2817,12 +2919,12 @@
         <v>0</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>10.65</v>
+        <v>16.64</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>43</v>
@@ -2846,12 +2948,12 @@
         <v>0</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>14.87</v>
+        <v>19.78</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>43</v>
@@ -2875,12 +2977,12 @@
         <v>0</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>15.51</v>
+        <v>19.78</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>77</v>
@@ -2904,12 +3006,12 @@
         <v>1</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>1.89</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>77</v>
@@ -2933,12 +3035,12 @@
         <v>1</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>77</v>
@@ -2962,12 +3064,12 @@
         <v>1</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>77</v>
@@ -2991,12 +3093,12 @@
         <v>1</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>77</v>
@@ -3020,12 +3122,12 @@
         <v>1</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>3.12</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>77</v>
@@ -3049,12 +3151,12 @@
         <v>1</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>77</v>
@@ -3078,12 +3180,12 @@
         <v>1</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>3.49</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>77</v>
@@ -3107,12 +3209,12 @@
         <v>1</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>3.49</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>77</v>
@@ -3133,15 +3235,15 @@
         <v>89</v>
       </c>
       <c r="H70" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>5.46</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>77</v>
@@ -3165,12 +3267,12 @@
         <v>1</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>5.76</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>77</v>
@@ -3194,12 +3296,12 @@
         <v>1</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>6.55</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>77</v>
@@ -3220,15 +3322,15 @@
         <v>92</v>
       </c>
       <c r="H73" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>8.81</v>
+        <v>8.34</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>77</v>
@@ -3249,15 +3351,15 @@
         <v>93</v>
       </c>
       <c r="H74" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>14.76</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>77</v>
@@ -3281,12 +3383,12 @@
         <v>0</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>15.41</v>
+        <v>14.56</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>77</v>
@@ -3301,7 +3403,7 @@
         <v>80</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>95</v>
@@ -3310,12 +3412,12 @@
         <v>1</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>15.43</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>77</v>
@@ -3339,12 +3441,12 @@
         <v>1</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>1.89</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>77</v>
@@ -3368,12 +3470,12 @@
         <v>1</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>2.05</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>77</v>
@@ -3397,12 +3499,12 @@
         <v>1</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>2.97</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>77</v>
@@ -3426,12 +3528,12 @@
         <v>1</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>3.16</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>77</v>
@@ -3455,12 +3557,12 @@
         <v>1</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>3.79</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>77</v>
@@ -3484,12 +3586,12 @@
         <v>1</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>4.34</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>77</v>
@@ -3513,12 +3615,12 @@
         <v>1</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>4.42</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>77</v>
@@ -3542,12 +3644,12 @@
         <v>1</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>4.42</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>77</v>
@@ -3571,12 +3673,12 @@
         <v>1</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>6.43</v>
+        <v>8.47</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>77</v>
@@ -3600,12 +3702,12 @@
         <v>1</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>8.38</v>
+        <v>8.47</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>77</v>
@@ -3629,12 +3731,12 @@
         <v>0</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>8.91</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>77</v>
@@ -3655,15 +3757,15 @@
         <v>107</v>
       </c>
       <c r="H88" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>10.64</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>77</v>
@@ -3684,15 +3786,15 @@
         <v>108</v>
       </c>
       <c r="H89" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I89" s="4" t="n">
-        <v>16.38</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>77</v>
@@ -3716,12 +3818,12 @@
         <v>0</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>16.65</v>
+        <v>12.92</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>77</v>
@@ -3742,15 +3844,15 @@
         <v>110</v>
       </c>
       <c r="H91" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>16.9</v>
+        <v>15.05</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>111</v>
@@ -3774,12 +3876,12 @@
         <v>1</v>
       </c>
       <c r="I92" s="4" t="n">
-        <v>2.22</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>111</v>
@@ -3803,12 +3905,12 @@
         <v>1</v>
       </c>
       <c r="I93" s="4" t="n">
-        <v>2.47</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>111</v>
@@ -3832,12 +3934,12 @@
         <v>1</v>
       </c>
       <c r="I94" s="4" t="n">
-        <v>2.61</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>111</v>
@@ -3861,12 +3963,12 @@
         <v>1</v>
       </c>
       <c r="I95" s="4" t="n">
-        <v>2.88</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>111</v>
@@ -3890,12 +3992,12 @@
         <v>1</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>3.39</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>111</v>
@@ -3919,12 +4021,12 @@
         <v>1</v>
       </c>
       <c r="I97" s="4" t="n">
-        <v>3.72</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>111</v>
@@ -3948,12 +4050,12 @@
         <v>1</v>
       </c>
       <c r="I98" s="4" t="n">
-        <v>3.72</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>111</v>
@@ -3977,12 +4079,12 @@
         <v>1</v>
       </c>
       <c r="I99" s="4" t="n">
-        <v>3.95</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>111</v>
@@ -4006,12 +4108,12 @@
         <v>1</v>
       </c>
       <c r="I100" s="4" t="n">
-        <v>4.4</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>111</v>
@@ -4032,15 +4134,15 @@
         <v>124</v>
       </c>
       <c r="H101" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I101" s="4" t="n">
-        <v>8.37</v>
+        <v>8.54</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>111</v>
@@ -4061,15 +4163,15 @@
         <v>125</v>
       </c>
       <c r="H102" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I102" s="4" t="n">
-        <v>11.14</v>
+        <v>8.91</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>111</v>
@@ -4093,12 +4195,12 @@
         <v>1</v>
       </c>
       <c r="I103" s="4" t="n">
-        <v>13.9</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>111</v>
@@ -4122,12 +4224,12 @@
         <v>0</v>
       </c>
       <c r="I104" s="4" t="n">
-        <v>18.3</v>
+        <v>12.45</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>111</v>
@@ -4148,15 +4250,15 @@
         <v>128</v>
       </c>
       <c r="H105" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I105" s="4" t="n">
-        <v>19.56</v>
+        <v>12.57</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>111</v>
@@ -4180,12 +4282,12 @@
         <v>0</v>
       </c>
       <c r="I106" s="4" t="n">
-        <v>19.57</v>
+        <v>14.16</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>111</v>
@@ -4209,12 +4311,12 @@
         <v>1</v>
       </c>
       <c r="I107" s="4" t="n">
-        <v>20.15</v>
+        <v>14.89</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>111</v>
@@ -4229,21 +4331,21 @@
         <v>114</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>131</v>
       </c>
       <c r="H108" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I108" s="4" t="n">
-        <v>2.06</v>
+        <v>17.01</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>111</v>
@@ -4267,12 +4369,12 @@
         <v>1</v>
       </c>
       <c r="I109" s="4" t="n">
-        <v>2.26</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>111</v>
@@ -4296,12 +4398,12 @@
         <v>1</v>
       </c>
       <c r="I110" s="4" t="n">
-        <v>2.32</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>111</v>
@@ -4325,12 +4427,12 @@
         <v>1</v>
       </c>
       <c r="I111" s="4" t="n">
-        <v>2.67</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>111</v>
@@ -4354,12 +4456,12 @@
         <v>1</v>
       </c>
       <c r="I112" s="4" t="n">
-        <v>2.78</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>111</v>
@@ -4383,12 +4485,12 @@
         <v>1</v>
       </c>
       <c r="I113" s="4" t="n">
-        <v>4.08</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>111</v>
@@ -4412,12 +4514,12 @@
         <v>1</v>
       </c>
       <c r="I114" s="4" t="n">
-        <v>4.08</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B115" s="3" t="s">
         <v>111</v>
@@ -4441,12 +4543,12 @@
         <v>1</v>
       </c>
       <c r="I115" s="4" t="n">
-        <v>6.29</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>111</v>
@@ -4470,12 +4572,12 @@
         <v>1</v>
       </c>
       <c r="I116" s="4" t="n">
-        <v>7.29</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>111</v>
@@ -4499,12 +4601,12 @@
         <v>1</v>
       </c>
       <c r="I117" s="4" t="n">
-        <v>7.91</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>111</v>
@@ -4525,15 +4627,15 @@
         <v>141</v>
       </c>
       <c r="H118" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I118" s="4" t="n">
-        <v>8.99</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>111</v>
@@ -4557,12 +4659,12 @@
         <v>1</v>
       </c>
       <c r="I119" s="4" t="n">
-        <v>17.97</v>
+        <v>11.66</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>111</v>
@@ -4583,15 +4685,15 @@
         <v>143</v>
       </c>
       <c r="H120" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I120" s="4" t="n">
-        <v>18.11</v>
+        <v>12.77</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>111</v>
@@ -4612,15 +4714,15 @@
         <v>144</v>
       </c>
       <c r="H121" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I121" s="4" t="n">
-        <v>18.91</v>
+        <v>17.03</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>145</v>
@@ -4635,7 +4737,7 @@
         <v>148</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G122" s="3" t="s">
         <v>149</v>
@@ -4644,12 +4746,12 @@
         <v>1</v>
       </c>
       <c r="I122" s="4" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>145</v>
@@ -4664,7 +4766,7 @@
         <v>148</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G123" s="3" t="s">
         <v>150</v>
@@ -4673,12 +4775,12 @@
         <v>1</v>
       </c>
       <c r="I123" s="4" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>145</v>
@@ -4693,7 +4795,7 @@
         <v>148</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>151</v>
@@ -4702,12 +4804,12 @@
         <v>1</v>
       </c>
       <c r="I124" s="4" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>145</v>
@@ -4722,7 +4824,7 @@
         <v>148</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G125" s="3" t="s">
         <v>152</v>
@@ -4731,12 +4833,12 @@
         <v>1</v>
       </c>
       <c r="I125" s="4" t="n">
-        <v>2.66</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>145</v>
@@ -4751,7 +4853,7 @@
         <v>148</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G126" s="3" t="s">
         <v>153</v>
@@ -4760,12 +4862,12 @@
         <v>1</v>
       </c>
       <c r="I126" s="4" t="n">
-        <v>2.67</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>145</v>
@@ -4780,7 +4882,7 @@
         <v>148</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G127" s="3" t="s">
         <v>154</v>
@@ -4789,12 +4891,12 @@
         <v>1</v>
       </c>
       <c r="I127" s="4" t="n">
-        <v>3.41</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>145</v>
@@ -4809,7 +4911,7 @@
         <v>148</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G128" s="3" t="s">
         <v>155</v>
@@ -4818,12 +4920,12 @@
         <v>1</v>
       </c>
       <c r="I128" s="4" t="n">
-        <v>3.41</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>145</v>
@@ -4838,7 +4940,7 @@
         <v>148</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G129" s="3" t="s">
         <v>156</v>
@@ -4847,12 +4949,12 @@
         <v>1</v>
       </c>
       <c r="I129" s="4" t="n">
-        <v>3.62</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>145</v>
@@ -4867,7 +4969,7 @@
         <v>148</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G130" s="3" t="s">
         <v>157</v>
@@ -4876,12 +4978,12 @@
         <v>1</v>
       </c>
       <c r="I130" s="4" t="n">
-        <v>4.7</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>145</v>
@@ -4896,7 +4998,7 @@
         <v>148</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G131" s="3" t="s">
         <v>158</v>
@@ -4905,12 +5007,12 @@
         <v>1</v>
       </c>
       <c r="I131" s="4" t="n">
-        <v>4.72</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>145</v>
@@ -4925,7 +5027,7 @@
         <v>148</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G132" s="3" t="s">
         <v>159</v>
@@ -4934,12 +5036,12 @@
         <v>1</v>
       </c>
       <c r="I132" s="4" t="n">
-        <v>7.55</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>145</v>
@@ -4954,7 +5056,7 @@
         <v>148</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G133" s="3" t="s">
         <v>160</v>
@@ -4963,12 +5065,12 @@
         <v>0</v>
       </c>
       <c r="I133" s="4" t="n">
-        <v>9.89</v>
+        <v>11.48</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>145</v>
@@ -4983,7 +5085,7 @@
         <v>148</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G134" s="3" t="s">
         <v>161</v>
@@ -4992,12 +5094,12 @@
         <v>0</v>
       </c>
       <c r="I134" s="4" t="n">
-        <v>10.49</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>145</v>
@@ -5012,7 +5114,7 @@
         <v>148</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G135" s="3" t="s">
         <v>162</v>
@@ -5021,12 +5123,12 @@
         <v>0</v>
       </c>
       <c r="I135" s="4" t="n">
-        <v>11.98</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>145</v>
@@ -5047,15 +5149,15 @@
         <v>163</v>
       </c>
       <c r="H136" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I136" s="4" t="n">
-        <v>15.43</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>145</v>
@@ -5076,15 +5178,15 @@
         <v>164</v>
       </c>
       <c r="H137" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I137" s="4" t="n">
-        <v>16.58</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>145</v>
@@ -5108,12 +5210,12 @@
         <v>1</v>
       </c>
       <c r="I138" s="4" t="n">
-        <v>17.44</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>145</v>
@@ -5128,7 +5230,7 @@
         <v>148</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G139" s="3" t="s">
         <v>166</v>
@@ -5137,12 +5239,12 @@
         <v>1</v>
       </c>
       <c r="I139" s="4" t="n">
-        <v>2.03</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>145</v>
@@ -5157,7 +5259,7 @@
         <v>148</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G140" s="3" t="s">
         <v>167</v>
@@ -5166,12 +5268,12 @@
         <v>1</v>
       </c>
       <c r="I140" s="4" t="n">
-        <v>3.64</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>145</v>
@@ -5186,7 +5288,7 @@
         <v>148</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G141" s="3" t="s">
         <v>168</v>
@@ -5195,12 +5297,12 @@
         <v>1</v>
       </c>
       <c r="I141" s="4" t="n">
-        <v>4.31</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>145</v>
@@ -5215,7 +5317,7 @@
         <v>148</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G142" s="3" t="s">
         <v>169</v>
@@ -5224,12 +5326,12 @@
         <v>1</v>
       </c>
       <c r="I142" s="4" t="n">
-        <v>4.42</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>145</v>
@@ -5244,7 +5346,7 @@
         <v>148</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G143" s="3" t="s">
         <v>170</v>
@@ -5253,12 +5355,12 @@
         <v>1</v>
       </c>
       <c r="I143" s="4" t="n">
-        <v>4.42</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>145</v>
@@ -5273,7 +5375,7 @@
         <v>148</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G144" s="3" t="s">
         <v>171</v>
@@ -5282,12 +5384,12 @@
         <v>1</v>
       </c>
       <c r="I144" s="4" t="n">
-        <v>4.78</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>145</v>
@@ -5302,7 +5404,7 @@
         <v>148</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G145" s="3" t="s">
         <v>172</v>
@@ -5311,12 +5413,12 @@
         <v>1</v>
       </c>
       <c r="I145" s="4" t="n">
-        <v>4.79</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>145</v>
@@ -5331,7 +5433,7 @@
         <v>148</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G146" s="3" t="s">
         <v>173</v>
@@ -5340,12 +5442,12 @@
         <v>1</v>
       </c>
       <c r="I146" s="4" t="n">
-        <v>4.9</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>145</v>
@@ -5360,7 +5462,7 @@
         <v>148</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G147" s="3" t="s">
         <v>174</v>
@@ -5369,12 +5471,12 @@
         <v>1</v>
       </c>
       <c r="I147" s="4" t="n">
-        <v>5.15</v>
+        <v>9.79</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>145</v>
@@ -5389,21 +5491,21 @@
         <v>148</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G148" s="3" t="s">
         <v>175</v>
       </c>
       <c r="H148" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I148" s="4" t="n">
-        <v>7.68</v>
+        <v>12.52</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>145</v>
@@ -5418,21 +5520,21 @@
         <v>148</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G149" s="3" t="s">
         <v>176</v>
       </c>
       <c r="H149" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I149" s="4" t="n">
-        <v>8.45</v>
+        <v>12.59</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>145</v>
@@ -5447,7 +5549,7 @@
         <v>148</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>177</v>
@@ -5456,12 +5558,12 @@
         <v>1</v>
       </c>
       <c r="I150" s="4" t="n">
-        <v>12.09</v>
+        <v>16.87</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>145</v>
@@ -5476,7 +5578,7 @@
         <v>148</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G151" s="3" t="s">
         <v>178</v>
@@ -5485,12 +5587,12 @@
         <v>0</v>
       </c>
       <c r="I151" s="4" t="n">
-        <v>12.77</v>
+        <v>17.58</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>179</v>
@@ -5505,7 +5607,7 @@
         <v>182</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G152" s="3" t="s">
         <v>183</v>
@@ -5514,12 +5616,12 @@
         <v>1</v>
       </c>
       <c r="I152" s="4" t="n">
-        <v>2.51</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>179</v>
@@ -5534,7 +5636,7 @@
         <v>182</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G153" s="3" t="s">
         <v>184</v>
@@ -5543,12 +5645,12 @@
         <v>1</v>
       </c>
       <c r="I153" s="4" t="n">
-        <v>2.74</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>179</v>
@@ -5563,7 +5665,7 @@
         <v>182</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G154" s="3" t="s">
         <v>185</v>
@@ -5572,12 +5674,12 @@
         <v>1</v>
       </c>
       <c r="I154" s="4" t="n">
-        <v>2.95</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>179</v>
@@ -5592,7 +5694,7 @@
         <v>182</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G155" s="3" t="s">
         <v>186</v>
@@ -5601,12 +5703,12 @@
         <v>1</v>
       </c>
       <c r="I155" s="4" t="n">
-        <v>2.99</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>179</v>
@@ -5621,7 +5723,7 @@
         <v>182</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G156" s="3" t="s">
         <v>187</v>
@@ -5630,12 +5732,12 @@
         <v>1</v>
       </c>
       <c r="I156" s="4" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>179</v>
@@ -5650,7 +5752,7 @@
         <v>182</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G157" s="3" t="s">
         <v>188</v>
@@ -5659,12 +5761,12 @@
         <v>1</v>
       </c>
       <c r="I157" s="4" t="n">
-        <v>3.62</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>179</v>
@@ -5679,7 +5781,7 @@
         <v>182</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G158" s="3" t="s">
         <v>189</v>
@@ -5688,12 +5790,12 @@
         <v>1</v>
       </c>
       <c r="I158" s="4" t="n">
-        <v>4.24</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>179</v>
@@ -5708,7 +5810,7 @@
         <v>182</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G159" s="3" t="s">
         <v>190</v>
@@ -5717,12 +5819,12 @@
         <v>1</v>
       </c>
       <c r="I159" s="4" t="n">
-        <v>4.24</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>179</v>
@@ -5737,7 +5839,7 @@
         <v>182</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G160" s="3" t="s">
         <v>191</v>
@@ -5746,12 +5848,12 @@
         <v>1</v>
       </c>
       <c r="I160" s="4" t="n">
-        <v>6.98</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>179</v>
@@ -5766,7 +5868,7 @@
         <v>182</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G161" s="3" t="s">
         <v>192</v>
@@ -5775,12 +5877,12 @@
         <v>1</v>
       </c>
       <c r="I161" s="4" t="n">
-        <v>8.98</v>
+        <v>11.98</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>179</v>
@@ -5795,21 +5897,21 @@
         <v>182</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G162" s="3" t="s">
         <v>193</v>
       </c>
       <c r="H162" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I162" s="4" t="n">
-        <v>11.2</v>
+        <v>14.12</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>179</v>
@@ -5824,21 +5926,21 @@
         <v>182</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G163" s="3" t="s">
         <v>194</v>
       </c>
       <c r="H163" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I163" s="4" t="n">
-        <v>14.8</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>179</v>
@@ -5853,7 +5955,7 @@
         <v>182</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G164" s="3" t="s">
         <v>195</v>
@@ -5862,12 +5964,12 @@
         <v>1</v>
       </c>
       <c r="I164" s="4" t="n">
-        <v>16.11</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>179</v>
@@ -5882,21 +5984,21 @@
         <v>182</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G165" s="3" t="s">
         <v>196</v>
       </c>
       <c r="H165" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I165" s="4" t="n">
-        <v>16.86</v>
+        <v>16.96</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>179</v>
@@ -5917,15 +6019,15 @@
         <v>197</v>
       </c>
       <c r="H166" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I166" s="4" t="n">
-        <v>1.95</v>
+        <v>17.58</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>179</v>
@@ -5949,12 +6051,12 @@
         <v>1</v>
       </c>
       <c r="I167" s="4" t="n">
-        <v>1.98</v>
+        <v>19.76</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>179</v>
@@ -5969,7 +6071,7 @@
         <v>182</v>
       </c>
       <c r="F168" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G168" s="3" t="s">
         <v>199</v>
@@ -5978,12 +6080,12 @@
         <v>1</v>
       </c>
       <c r="I168" s="4" t="n">
-        <v>2.03</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>179</v>
@@ -5998,7 +6100,7 @@
         <v>182</v>
       </c>
       <c r="F169" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G169" s="3" t="s">
         <v>200</v>
@@ -6007,12 +6109,12 @@
         <v>1</v>
       </c>
       <c r="I169" s="4" t="n">
-        <v>2.89</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>179</v>
@@ -6027,7 +6129,7 @@
         <v>182</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G170" s="3" t="s">
         <v>201</v>
@@ -6036,12 +6138,12 @@
         <v>1</v>
       </c>
       <c r="I170" s="4" t="n">
-        <v>3.11</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>179</v>
@@ -6056,7 +6158,7 @@
         <v>182</v>
       </c>
       <c r="F171" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G171" s="3" t="s">
         <v>202</v>
@@ -6065,12 +6167,12 @@
         <v>1</v>
       </c>
       <c r="I171" s="4" t="n">
-        <v>3.87</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>179</v>
@@ -6085,7 +6187,7 @@
         <v>182</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G172" s="3" t="s">
         <v>203</v>
@@ -6094,12 +6196,12 @@
         <v>1</v>
       </c>
       <c r="I172" s="4" t="n">
-        <v>3.87</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B173" s="3" t="s">
         <v>179</v>
@@ -6114,7 +6216,7 @@
         <v>182</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G173" s="3" t="s">
         <v>204</v>
@@ -6123,12 +6225,12 @@
         <v>1</v>
       </c>
       <c r="I173" s="4" t="n">
-        <v>4.01</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>179</v>
@@ -6143,7 +6245,7 @@
         <v>182</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G174" s="3" t="s">
         <v>205</v>
@@ -6152,12 +6254,12 @@
         <v>1</v>
       </c>
       <c r="I174" s="4" t="n">
-        <v>4.02</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B175" s="3" t="s">
         <v>179</v>
@@ -6172,7 +6274,7 @@
         <v>182</v>
       </c>
       <c r="F175" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G175" s="3" t="s">
         <v>206</v>
@@ -6181,12 +6283,12 @@
         <v>1</v>
       </c>
       <c r="I175" s="4" t="n">
-        <v>4.42</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>179</v>
@@ -6201,7 +6303,7 @@
         <v>182</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G176" s="3" t="s">
         <v>207</v>
@@ -6210,12 +6312,12 @@
         <v>1</v>
       </c>
       <c r="I176" s="4" t="n">
-        <v>8.04</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>179</v>
@@ -6230,21 +6332,21 @@
         <v>182</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G177" s="3" t="s">
         <v>208</v>
       </c>
       <c r="H177" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I177" s="4" t="n">
-        <v>8.05</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>179</v>
@@ -6259,7 +6361,7 @@
         <v>182</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G178" s="3" t="s">
         <v>209</v>
@@ -6268,12 +6370,12 @@
         <v>1</v>
       </c>
       <c r="I178" s="4" t="n">
-        <v>10.52</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>179</v>
@@ -6288,21 +6390,21 @@
         <v>182</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G179" s="3" t="s">
         <v>210</v>
       </c>
       <c r="H179" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I179" s="4" t="n">
-        <v>14.93</v>
+        <v>13.57</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>179</v>
@@ -6317,21 +6419,21 @@
         <v>182</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G180" s="3" t="s">
         <v>211</v>
       </c>
       <c r="H180" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I180" s="4" t="n">
-        <v>15.89</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>179</v>
@@ -6346,21 +6448,21 @@
         <v>182</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G181" s="3" t="s">
         <v>212</v>
       </c>
       <c r="H181" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I181" s="4" t="n">
-        <v>16.59</v>
+        <v>20.68</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B182" s="3" t="s">
         <v>213</v>
@@ -6375,7 +6477,7 @@
         <v>216</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G182" s="3" t="s">
         <v>217</v>
@@ -6384,12 +6486,12 @@
         <v>1</v>
       </c>
       <c r="I182" s="4" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B183" s="3" t="s">
         <v>213</v>
@@ -6404,7 +6506,7 @@
         <v>216</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G183" s="3" t="s">
         <v>218</v>
@@ -6413,12 +6515,12 @@
         <v>1</v>
       </c>
       <c r="I183" s="4" t="n">
-        <v>2.56</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B184" s="3" t="s">
         <v>213</v>
@@ -6433,7 +6535,7 @@
         <v>216</v>
       </c>
       <c r="F184" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G184" s="3" t="s">
         <v>219</v>
@@ -6442,12 +6544,12 @@
         <v>1</v>
       </c>
       <c r="I184" s="4" t="n">
-        <v>3.56</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B185" s="3" t="s">
         <v>213</v>
@@ -6462,7 +6564,7 @@
         <v>216</v>
       </c>
       <c r="F185" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G185" s="3" t="s">
         <v>220</v>
@@ -6471,12 +6573,12 @@
         <v>1</v>
       </c>
       <c r="I185" s="4" t="n">
-        <v>3.62</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B186" s="3" t="s">
         <v>213</v>
@@ -6491,7 +6593,7 @@
         <v>216</v>
       </c>
       <c r="F186" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G186" s="3" t="s">
         <v>221</v>
@@ -6500,12 +6602,12 @@
         <v>1</v>
       </c>
       <c r="I186" s="4" t="n">
-        <v>3.66</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>213</v>
@@ -6520,7 +6622,7 @@
         <v>216</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G187" s="3" t="s">
         <v>222</v>
@@ -6529,12 +6631,12 @@
         <v>1</v>
       </c>
       <c r="I187" s="4" t="n">
-        <v>4.32</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B188" s="3" t="s">
         <v>213</v>
@@ -6549,7 +6651,7 @@
         <v>216</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G188" s="3" t="s">
         <v>223</v>
@@ -6558,12 +6660,12 @@
         <v>1</v>
       </c>
       <c r="I188" s="4" t="n">
-        <v>4.81</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B189" s="3" t="s">
         <v>213</v>
@@ -6578,7 +6680,7 @@
         <v>216</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G189" s="3" t="s">
         <v>224</v>
@@ -6587,12 +6689,12 @@
         <v>1</v>
       </c>
       <c r="I189" s="4" t="n">
-        <v>4.81</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B190" s="3" t="s">
         <v>213</v>
@@ -6607,7 +6709,7 @@
         <v>216</v>
       </c>
       <c r="F190" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>225</v>
@@ -6616,12 +6718,12 @@
         <v>1</v>
       </c>
       <c r="I190" s="4" t="n">
-        <v>5.2</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B191" s="3" t="s">
         <v>213</v>
@@ -6636,7 +6738,7 @@
         <v>216</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G191" s="3" t="s">
         <v>226</v>
@@ -6645,12 +6747,12 @@
         <v>1</v>
       </c>
       <c r="I191" s="4" t="n">
-        <v>6.31</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>213</v>
@@ -6665,7 +6767,7 @@
         <v>216</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G192" s="3" t="s">
         <v>227</v>
@@ -6674,12 +6776,12 @@
         <v>1</v>
       </c>
       <c r="I192" s="4" t="n">
-        <v>8.95</v>
+        <v>9.13</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B193" s="3" t="s">
         <v>213</v>
@@ -6694,21 +6796,21 @@
         <v>216</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>228</v>
       </c>
       <c r="H193" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I193" s="4" t="n">
-        <v>10.01</v>
+        <v>11.96</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B194" s="3" t="s">
         <v>213</v>
@@ -6723,21 +6825,21 @@
         <v>216</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G194" s="3" t="s">
         <v>229</v>
       </c>
       <c r="H194" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I194" s="4" t="n">
-        <v>11.01</v>
+        <v>13.52</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B195" s="3" t="s">
         <v>213</v>
@@ -6752,21 +6854,21 @@
         <v>216</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>230</v>
       </c>
       <c r="H195" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I195" s="4" t="n">
-        <v>11.8</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>213</v>
@@ -6787,15 +6889,15 @@
         <v>231</v>
       </c>
       <c r="H196" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I196" s="4" t="n">
-        <v>1.76</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B197" s="3" t="s">
         <v>213</v>
@@ -6816,15 +6918,15 @@
         <v>232</v>
       </c>
       <c r="H197" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I197" s="4" t="n">
-        <v>2.49</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>213</v>
@@ -6845,15 +6947,15 @@
         <v>233</v>
       </c>
       <c r="H198" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I198" s="4" t="n">
-        <v>2.73</v>
+        <v>18.28</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>213</v>
@@ -6868,7 +6970,7 @@
         <v>216</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G199" s="3" t="s">
         <v>234</v>
@@ -6877,12 +6979,12 @@
         <v>1</v>
       </c>
       <c r="I199" s="4" t="n">
-        <v>3.63</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>213</v>
@@ -6897,7 +6999,7 @@
         <v>216</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G200" s="3" t="s">
         <v>235</v>
@@ -6906,12 +7008,12 @@
         <v>1</v>
       </c>
       <c r="I200" s="4" t="n">
-        <v>4.17</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>213</v>
@@ -6926,7 +7028,7 @@
         <v>216</v>
       </c>
       <c r="F201" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G201" s="3" t="s">
         <v>236</v>
@@ -6935,12 +7037,12 @@
         <v>1</v>
       </c>
       <c r="I201" s="4" t="n">
-        <v>4.56</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>213</v>
@@ -6955,7 +7057,7 @@
         <v>216</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G202" s="3" t="s">
         <v>237</v>
@@ -6964,12 +7066,12 @@
         <v>1</v>
       </c>
       <c r="I202" s="4" t="n">
-        <v>4.68</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B203" s="3" t="s">
         <v>213</v>
@@ -6984,7 +7086,7 @@
         <v>216</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G203" s="3" t="s">
         <v>238</v>
@@ -6993,12 +7095,12 @@
         <v>1</v>
       </c>
       <c r="I203" s="4" t="n">
-        <v>4.68</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>213</v>
@@ -7013,7 +7115,7 @@
         <v>216</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G204" s="3" t="s">
         <v>239</v>
@@ -7022,12 +7124,12 @@
         <v>1</v>
       </c>
       <c r="I204" s="4" t="n">
-        <v>4.74</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>213</v>
@@ -7042,7 +7144,7 @@
         <v>216</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G205" s="3" t="s">
         <v>240</v>
@@ -7051,12 +7153,12 @@
         <v>1</v>
       </c>
       <c r="I205" s="4" t="n">
-        <v>8.08</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>213</v>
@@ -7071,21 +7173,21 @@
         <v>216</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G206" s="3" t="s">
         <v>241</v>
       </c>
       <c r="H206" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I206" s="4" t="n">
-        <v>8.1</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>213</v>
@@ -7100,21 +7202,21 @@
         <v>216</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G207" s="3" t="s">
         <v>242</v>
       </c>
       <c r="H207" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I207" s="4" t="n">
-        <v>10.18</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>213</v>
@@ -7129,21 +7231,21 @@
         <v>216</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G208" s="3" t="s">
         <v>243</v>
       </c>
       <c r="H208" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I208" s="4" t="n">
-        <v>10.85</v>
+        <v>6.08</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>213</v>
@@ -7158,21 +7260,21 @@
         <v>216</v>
       </c>
       <c r="F209" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G209" s="3" t="s">
         <v>244</v>
       </c>
       <c r="H209" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I209" s="4" t="n">
-        <v>11.03</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B210" s="3" t="s">
         <v>213</v>
@@ -7187,7 +7289,7 @@
         <v>216</v>
       </c>
       <c r="F210" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G210" s="3" t="s">
         <v>245</v>
@@ -7196,12 +7298,12 @@
         <v>0</v>
       </c>
       <c r="I210" s="4" t="n">
-        <v>12.08</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>213</v>
@@ -7216,16 +7318,886 @@
         <v>216</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G211" s="3" t="s">
         <v>246</v>
       </c>
       <c r="H211" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I211" s="4" t="n">
+        <v>13.83</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B212" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C212" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D212" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E212" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F212" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G212" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="H212" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I212" s="4" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E213" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F213" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G213" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="H213" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I213" s="4" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C214" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D214" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E214" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F214" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G214" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="H214" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I214" s="4" t="n">
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D215" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E215" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F215" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G215" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H215" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I215" s="4" t="n">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C216" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E216" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F216" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G216" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="H216" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I216" s="4" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E217" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F217" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G217" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H217" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I217" s="4" t="n">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E218" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F218" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G218" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="H218" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I218" s="4" t="n">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E219" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F219" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G219" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="H219" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I219" s="4" t="n">
+        <v>4.22</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D220" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E220" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F220" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G220" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="H220" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I220" s="4" t="n">
+        <v>4.77</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C221" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D221" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E221" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F221" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G221" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="H221" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I221" s="4" t="n">
+        <v>4.96</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C222" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E222" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F222" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G222" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="H222" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="I211" s="4" t="n">
-        <v>12.3</v>
+      <c r="I222" s="4" t="n">
+        <v>7.41</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C223" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E223" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F223" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G223" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="H223" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I223" s="4" t="n">
+        <v>8.17</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C224" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E224" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F224" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G224" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H224" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I224" s="4" t="n">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E225" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F225" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G225" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="H225" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I225" s="4" t="n">
+        <v>11.03</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E226" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F226" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G226" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="H226" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I226" s="4" t="n">
+        <v>19.05</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E227" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G227" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="H227" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I227" s="4" t="n">
+        <v>19.11</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E228" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G228" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="H228" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I228" s="4" t="n">
+        <v>2.26</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E229" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F229" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G229" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="H229" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I229" s="4" t="n">
+        <v>2.57</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C230" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E230" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F230" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G230" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="H230" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I230" s="4" t="n">
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E231" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F231" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G231" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="H231" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I231" s="4" t="n">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E232" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F232" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G232" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="H232" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I232" s="4" t="n">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E233" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F233" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G233" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="H233" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I233" s="4" t="n">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C234" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E234" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F234" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G234" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="H234" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I234" s="4" t="n">
+        <v>4.11</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B235" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C235" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E235" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F235" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G235" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="H235" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I235" s="4" t="n">
+        <v>4.11</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C236" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E236" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F236" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G236" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="H236" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I236" s="4" t="n">
+        <v>5.64</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B237" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C237" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E237" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F237" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G237" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H237" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I237" s="4" t="n">
+        <v>5.68</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C238" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E238" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F238" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G238" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="H238" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I238" s="4" t="n">
+        <v>10.17</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B239" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C239" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D239" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E239" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F239" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G239" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="H239" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I239" s="4" t="n">
+        <v>10.97</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B240" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C240" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D240" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E240" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F240" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G240" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="H240" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I240" s="4" t="n">
+        <v>14.06</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C241" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D241" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E241" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F241" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G241" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="H241" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I241" s="4" t="n">
+        <v>16.75</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_anytime_tryscorers.xlsx
+++ b/files/NRL_anytime_tryscorers.xlsx
@@ -1266,7 +1266,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="3">
@@ -1295,7 +1295,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="4">
@@ -1324,7 +1324,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="5">
@@ -1353,7 +1353,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="6">
@@ -1382,7 +1382,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.27</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="7">
@@ -1411,7 +1411,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.66</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="8">
@@ -1440,7 +1440,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4.66</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="9">
@@ -1469,7 +1469,7 @@
         <v>1</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.72</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="10">
@@ -1498,7 +1498,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.99</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="11">
@@ -1527,7 +1527,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>5.3</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="12">
@@ -1556,7 +1556,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>8.32</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="13">
@@ -1585,7 +1585,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>11.07</v>
+        <v>10.88</v>
       </c>
     </row>
     <row r="14">
@@ -1614,7 +1614,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>13.93</v>
+        <v>13.68</v>
       </c>
     </row>
     <row r="15">
@@ -1643,7 +1643,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>14.16</v>
+        <v>13.91</v>
       </c>
     </row>
     <row r="16">
@@ -1672,7 +1672,7 @@
         <v>1</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="17">
@@ -1701,7 +1701,7 @@
         <v>1</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="18">
@@ -1730,7 +1730,7 @@
         <v>1</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3.33</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="19">
@@ -1759,7 +1759,7 @@
         <v>1</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3.37</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="20">
@@ -1788,7 +1788,7 @@
         <v>1</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.7</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="21">
@@ -1817,7 +1817,7 @@
         <v>1</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>4.74</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="22">
@@ -1846,7 +1846,7 @@
         <v>1</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>4.74</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="23">
@@ -1875,7 +1875,7 @@
         <v>1</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>5.14</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="24">
@@ -1904,7 +1904,7 @@
         <v>1</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>7.09</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="25">
@@ -1933,7 +1933,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>7.6</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="26">
@@ -1962,7 +1962,7 @@
         <v>1</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>7.99</v>
+        <v>7.82</v>
       </c>
     </row>
     <row r="27">
@@ -1991,7 +1991,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>9.63</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="28">
@@ -2020,7 +2020,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>10.18</v>
+        <v>9.96</v>
       </c>
     </row>
     <row r="29">
@@ -2049,7 +2049,7 @@
         <v>1</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>11.01</v>
+        <v>10.77</v>
       </c>
     </row>
     <row r="30">
@@ -2078,7 +2078,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>12.43</v>
+        <v>12.16</v>
       </c>
     </row>
     <row r="31">
@@ -2107,7 +2107,7 @@
         <v>1</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>13.66</v>
+        <v>13.36</v>
       </c>
     </row>
     <row r="32">

--- a/files/NRL_anytime_tryscorers.xlsx
+++ b/files/NRL_anytime_tryscorers.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="247">
   <si>
     <t xml:space="preserve">Date Local</t>
   </si>
@@ -44,70 +44,478 @@
     <t xml:space="preserve">20:00</t>
   </si>
   <si>
-    <t xml:space="preserve">100133433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penrith panthers</t>
+    <t xml:space="preserve">100057040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wests tigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alofiana Khan-Pereira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charnze Nicoll-Klokstad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ali Leiataua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leka Halasima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Laban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taine Tuaupiki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Te Maire Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chanel Harris-Tavita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Pompey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wayde Egan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Fisher-Harris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erin Clark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Metcalf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Healey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tanner Stowers-Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeral Skelton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunia Turuva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jahream Bula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Doueihi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starford To'a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samuela Fainu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sione Fainu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heamasi Makasini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jarome Luai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josese Lanyon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terrell May</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latu Fainu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Seyfarth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fonua Pole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faaletino Tavana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100113380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronaldo Mulitalo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sione Katoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">William Kennedy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braydon Trindall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayal Iro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesse Ramien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Burns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teig Wilton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicholas Hynes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Hazelton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Berrell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesse Colquhoun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siosifa Talakai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron McInnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuku Hau Tapuha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamayne Isaako</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tevita Naufahu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herbie Farnworth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trai Fuller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Averillo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connelly Lemuelu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kulikefu Finefeuiaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kodi Nikorima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brad Schneider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremy Marshall-King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ray Stone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamiso Tabuai-Fidow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Plath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Donoghoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morgan Knowles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100170602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Savage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaeo Weekes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sebastian Kris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simi Sasagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Timoko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Strange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hudson Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noah Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owen Pattie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zac Hosking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Sanders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe Roddy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corey Horsburgh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Starling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joseph Tapine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daine Laurie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jethro Rinakama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Kiraz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matt Burton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Tracey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enari Tuala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Curran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaeman Salmon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lachlan Galvin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stephen Crichton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Preston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Mann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bailey Hayward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harry Hayes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logan Spinks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100094582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Addo-Carr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian Kelly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiah Iongi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Samrani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Araz Nanva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitchell Moses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kelma Tuilagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kitione Kautoga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronald Volkman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tallyn Da Silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack De Belin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Tuivaiti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark Nawaqanitawase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Tupou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Tedesco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robert Toia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daly Cherry-Evans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salesi Foketi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siua Wong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugo Savala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Watson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Victor Radley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reece Robson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toby Rodwell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egan Butcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spencer Leniu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naufahu Whyte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100138451</t>
   </si>
   <si>
     <t xml:space="preserve">south sydney rabbitohs</t>
   </si>
   <si>
-    <t xml:space="preserve">Thomas Jenkins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian To'o</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Edwards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Izack Tago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paul Alamoti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nathan Cleary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiah Papali'i</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blaize Talagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freddy Lussick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaah Yeo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Garner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moses Leota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scott Sorensen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Johnston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edward Kosi</t>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominic Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greg Marzhew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fletcher Sharpe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bradman Best</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kalyn Ponga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Lucas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jermaine McEwen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trey Mooney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dane Gagai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fletcher Hunt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phoenix Crossland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harrison Graham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyson Frizell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dayne Jennings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campbell Graham</t>
   </si>
   <si>
     <t xml:space="preserve">Tallis Duncan</t>
   </si>
   <si>
-    <t xml:space="preserve">Jye Gray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cody Walker</t>
+    <t xml:space="preserve">Matthew Dufty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Wighton</t>
   </si>
   <si>
     <t xml:space="preserve">David Fifita</t>
@@ -116,24 +524,21 @@
     <t xml:space="preserve">Euan Aitken</t>
   </si>
   <si>
-    <t xml:space="preserve">Latrell Siegwalt</t>
-  </si>
-  <si>
     <t xml:space="preserve">Keaon Koloamatangi</t>
   </si>
   <si>
+    <t xml:space="preserve">Cameron Murray</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ashton Ward</t>
   </si>
   <si>
-    <t xml:space="preserve">Cameron Murray</t>
+    <t xml:space="preserve">Jayden Sullivan</t>
   </si>
   <si>
     <t xml:space="preserve">John Radel</t>
   </si>
   <si>
-    <t xml:space="preserve">Jayden Sullivan</t>
-  </si>
-  <si>
     <t xml:space="preserve">Brandon Smith</t>
   </si>
   <si>
@@ -143,202 +548,37 @@
     <t xml:space="preserve">Tevita Tatola</t>
   </si>
   <si>
-    <t xml:space="preserve">17:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100137333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george-illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyrell Sloan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Setu Tu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mathew Feagai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clinton Gutherson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valentine Holmes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Egan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamish Stewart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Liddle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyle Flanagan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel Atkinson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Damien Cook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luciano Leilua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loko Pasifiki Tonga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan Couchman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeral Skelton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunia Turuva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jahream Bula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taylan May</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Doueihi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Starford To'a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tony Sukkar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sione Fainu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jarome Luai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apisai Koroisau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Seyfarth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terrell May</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latu Fainu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fonua Pole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Faaletino Tavana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heamasi Makasini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100154488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josiah Karapani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jesse Arthars</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reece Walsh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kotoni Staggs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grant Anderson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brendan Piakura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan Riki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben Hunt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Duffy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben Talty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Willison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cory Paix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payne Haas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blake Mozer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Gosiewski</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preston Riki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Rogers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hayze Perham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aublix Tawha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100144613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
+    <t xml:space="preserve">Thomas Fletcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100200791</t>
   </si>
   <si>
     <t xml:space="preserve">manly-warringah sea eagles</t>
   </si>
   <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tom Trbojevic</t>
   </si>
   <si>
+    <t xml:space="preserve">Lehi Hopoate</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jason Saab</t>
   </si>
   <si>
-    <t xml:space="preserve">Lehi Hopoate</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tolutau Koula</t>
   </si>
   <si>
-    <t xml:space="preserve">Josh Feledy</t>
+    <t xml:space="preserve">Reuben Garrick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joey Walsh</t>
   </si>
   <si>
     <t xml:space="preserve">Haumole Olakau'atu</t>
@@ -347,21 +587,18 @@
     <t xml:space="preserve">Ben Trbojevic</t>
   </si>
   <si>
-    <t xml:space="preserve">Luke Brooks</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jamal Fogarty</t>
   </si>
   <si>
     <t xml:space="preserve">Ethan Bullemor</t>
   </si>
   <si>
+    <t xml:space="preserve">Corey Waddell</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jake Simpkin</t>
   </si>
   <si>
-    <t xml:space="preserve">Simione Laiafi</t>
-  </si>
-  <si>
     <t xml:space="preserve">Aaron Schoupp</t>
   </si>
   <si>
@@ -371,151 +608,151 @@
     <t xml:space="preserve">Taniela Paseka</t>
   </si>
   <si>
-    <t xml:space="preserve">Josh Addo-Carr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian Kelly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiah Iongi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan Samrani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitchell Moses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kelma Tuilagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitione Kautoga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sean Russell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronald Volkman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tallyn Da Silva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack De Belin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harrison Edwards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Tuivaiti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100074722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamiso Tabuai-Fidow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selwyn Cobbo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamayne Isaako</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herbie Farnworth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Bostock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connelly Lemuelu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kulikefu Finefeuiaki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kodi Nikorima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremy Marshall-King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ray Stone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Flegler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiya Katoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Plath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morgan Knowles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dominic Young</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greg Marzhew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fletcher Sharpe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bradman Best</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kalyn Ponga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Lucas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jermaine McEwen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trey Mooney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dane Gagai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fletcher Hunt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phoenix Crossland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyson Frizell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lachlan Crouch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Saifiti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mat Croker</t>
+    <t xml:space="preserve">Nicholas Lenaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braidon Burns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murray Taulagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scott Drinkwater</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zac Laybutt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Chester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heilum Luki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremiah Nanai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Clifford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reed Mahoney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaxon Purdue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reuben Cotter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam McIntyre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Griffin Neame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soni Luke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100102458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phillip Sami</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dean Ieremia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jojo Fifita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Campbell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keano Kini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AJ Brimson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arama Hau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beau Fermor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zane Harrison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver Pascoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tino Fa'asuamaleaui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Bai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chris Randall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurtis Morrin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Warbrick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sualauvi Faalogo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manaia Waitere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jahrome Hughes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harry Grant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Clarke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alec MacDonald</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron Munster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nick Meaney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Howarth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyran Wishart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stefano Utoikamanu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe Chan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trent Loiero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trent Toelau</t>
   </si>
 </sst>
 </file>
@@ -864,10 +1101,10 @@
     <col min="1" max="1" width="9.285" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="9.285" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="8.4275" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="23.8625" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="25.5775" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="23.005" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="23.8625" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="20.4325" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="25.5775" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="21.29" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="6.7125" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="10.1425" hidden="0" customWidth="1"/>
   </cols>
@@ -903,7 +1140,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>9</v>
@@ -918,7 +1155,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>13</v>
@@ -927,12 +1164,12 @@
         <v>1</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>9</v>
@@ -947,7 +1184,7 @@
         <v>12</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>14</v>
@@ -956,12 +1193,12 @@
         <v>1</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>1.96</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>9</v>
@@ -976,7 +1213,7 @@
         <v>12</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>15</v>
@@ -985,12 +1222,12 @@
         <v>1</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>2.67</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>9</v>
@@ -1005,7 +1242,7 @@
         <v>12</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>16</v>
@@ -1014,12 +1251,12 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>2.84</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>9</v>
@@ -1034,7 +1271,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>17</v>
@@ -1043,12 +1280,12 @@
         <v>1</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>3.67</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>9</v>
@@ -1063,7 +1300,7 @@
         <v>12</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>18</v>
@@ -1072,12 +1309,12 @@
         <v>1</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.86</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>9</v>
@@ -1092,7 +1329,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>19</v>
@@ -1101,12 +1338,12 @@
         <v>1</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>3.87</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>9</v>
@@ -1121,7 +1358,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>20</v>
@@ -1130,12 +1367,12 @@
         <v>1</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3.87</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>9</v>
@@ -1150,7 +1387,7 @@
         <v>12</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>21</v>
@@ -1159,12 +1396,12 @@
         <v>1</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3.94</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>9</v>
@@ -1179,7 +1416,7 @@
         <v>12</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>22</v>
@@ -1188,12 +1425,12 @@
         <v>1</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>5.88</v>
+        <v>8.08</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>9</v>
@@ -1208,7 +1445,7 @@
         <v>12</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>23</v>
@@ -1217,12 +1454,12 @@
         <v>1</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>8.37</v>
+        <v>12.04</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>9</v>
@@ -1237,21 +1474,21 @@
         <v>12</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H13" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>10.79</v>
+        <v>12.88</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>9</v>
@@ -1266,21 +1503,21 @@
         <v>12</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H14" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>14.37</v>
+        <v>14.61</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>9</v>
@@ -1295,7 +1532,7 @@
         <v>12</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>26</v>
@@ -1304,12 +1541,12 @@
         <v>0</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>15.1</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>9</v>
@@ -1333,12 +1570,12 @@
         <v>1</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.86</v>
+        <v>19.84</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>9</v>
@@ -1353,7 +1590,7 @@
         <v>12</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>28</v>
@@ -1362,12 +1599,12 @@
         <v>1</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.81</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>9</v>
@@ -1382,7 +1619,7 @@
         <v>12</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>29</v>
@@ -1391,12 +1628,12 @@
         <v>1</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3.03</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>9</v>
@@ -1411,7 +1648,7 @@
         <v>12</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>30</v>
@@ -1420,12 +1657,12 @@
         <v>1</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3.59</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>9</v>
@@ -1440,7 +1677,7 @@
         <v>12</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>31</v>
@@ -1449,12 +1686,12 @@
         <v>1</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.74</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>9</v>
@@ -1469,7 +1706,7 @@
         <v>12</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>32</v>
@@ -1478,12 +1715,12 @@
         <v>1</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>4.98</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>9</v>
@@ -1498,7 +1735,7 @@
         <v>12</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>33</v>
@@ -1507,12 +1744,12 @@
         <v>1</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>4.98</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>9</v>
@@ -1527,7 +1764,7 @@
         <v>12</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>34</v>
@@ -1536,12 +1773,12 @@
         <v>1</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>5.72</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>9</v>
@@ -1556,7 +1793,7 @@
         <v>12</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>35</v>
@@ -1565,12 +1802,12 @@
         <v>1</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>7.62</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>9</v>
@@ -1585,7 +1822,7 @@
         <v>12</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>36</v>
@@ -1594,12 +1831,12 @@
         <v>1</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>8.33</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>9</v>
@@ -1614,7 +1851,7 @@
         <v>12</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>37</v>
@@ -1623,12 +1860,12 @@
         <v>1</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>8.52</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>9</v>
@@ -1643,21 +1880,21 @@
         <v>12</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>38</v>
       </c>
       <c r="H27" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>10.89</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>9</v>
@@ -1672,7 +1909,7 @@
         <v>12</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>39</v>
@@ -1681,12 +1918,12 @@
         <v>0</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>10.99</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>9</v>
@@ -1701,21 +1938,21 @@
         <v>12</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H29" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>11.81</v>
+        <v>14.06</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>9</v>
@@ -1730,7 +1967,7 @@
         <v>12</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>41</v>
@@ -1739,12 +1976,12 @@
         <v>0</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>13.86</v>
+        <v>14.16</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>9</v>
@@ -1759,21 +1996,21 @@
         <v>12</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>42</v>
       </c>
       <c r="H31" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>14.58</v>
+        <v>17.23</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>43</v>
@@ -1788,7 +2025,7 @@
         <v>46</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>47</v>
@@ -1797,12 +2034,12 @@
         <v>1</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>43</v>
@@ -1817,7 +2054,7 @@
         <v>46</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>48</v>
@@ -1826,12 +2063,12 @@
         <v>1</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>43</v>
@@ -1846,7 +2083,7 @@
         <v>46</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>49</v>
@@ -1855,12 +2092,12 @@
         <v>1</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>2.45</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>43</v>
@@ -1875,7 +2112,7 @@
         <v>46</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>50</v>
@@ -1884,12 +2121,12 @@
         <v>1</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>2.62</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>43</v>
@@ -1904,7 +2141,7 @@
         <v>46</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>51</v>
@@ -1913,12 +2150,12 @@
         <v>1</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>2.65</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>43</v>
@@ -1933,7 +2170,7 @@
         <v>46</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>52</v>
@@ -1942,12 +2179,12 @@
         <v>1</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>4.04</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>43</v>
@@ -1962,7 +2199,7 @@
         <v>46</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>53</v>
@@ -1971,12 +2208,12 @@
         <v>1</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>4.04</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>43</v>
@@ -1991,21 +2228,21 @@
         <v>46</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>54</v>
       </c>
       <c r="H39" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>5.13</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>43</v>
@@ -2020,7 +2257,7 @@
         <v>46</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>55</v>
@@ -2029,12 +2266,12 @@
         <v>1</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>5.39</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>43</v>
@@ -2049,7 +2286,7 @@
         <v>46</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>56</v>
@@ -2058,12 +2295,12 @@
         <v>1</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>5.59</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>43</v>
@@ -2078,7 +2315,7 @@
         <v>46</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>57</v>
@@ -2087,12 +2324,12 @@
         <v>1</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>6.44</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>43</v>
@@ -2107,21 +2344,21 @@
         <v>46</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>58</v>
       </c>
       <c r="H43" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>9.01</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>43</v>
@@ -2136,21 +2373,21 @@
         <v>46</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>59</v>
       </c>
       <c r="H44" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>12.4</v>
+        <v>10.68</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>43</v>
@@ -2165,7 +2402,7 @@
         <v>46</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>60</v>
@@ -2174,12 +2411,12 @@
         <v>1</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>18.35</v>
+        <v>12.37</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>43</v>
@@ -2200,15 +2437,15 @@
         <v>61</v>
       </c>
       <c r="H46" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>2.13</v>
+        <v>13.39</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>43</v>
@@ -2223,7 +2460,7 @@
         <v>46</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>62</v>
@@ -2232,12 +2469,12 @@
         <v>1</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>43</v>
@@ -2252,7 +2489,7 @@
         <v>46</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>63</v>
@@ -2261,12 +2498,12 @@
         <v>1</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>43</v>
@@ -2281,7 +2518,7 @@
         <v>46</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>64</v>
@@ -2290,12 +2527,12 @@
         <v>1</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>2.72</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>43</v>
@@ -2310,7 +2547,7 @@
         <v>46</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>65</v>
@@ -2319,12 +2556,12 @@
         <v>1</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>3.23</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>43</v>
@@ -2339,7 +2576,7 @@
         <v>46</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>66</v>
@@ -2348,12 +2585,12 @@
         <v>1</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>3.26</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>43</v>
@@ -2368,7 +2605,7 @@
         <v>46</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>67</v>
@@ -2377,12 +2614,12 @@
         <v>1</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>3.75</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>43</v>
@@ -2397,7 +2634,7 @@
         <v>46</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>68</v>
@@ -2406,12 +2643,12 @@
         <v>1</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>3.75</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>43</v>
@@ -2426,7 +2663,7 @@
         <v>46</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>69</v>
@@ -2435,12 +2672,12 @@
         <v>1</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>5.17</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>43</v>
@@ -2455,7 +2692,7 @@
         <v>46</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>70</v>
@@ -2464,12 +2701,12 @@
         <v>1</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>5.21</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>43</v>
@@ -2484,7 +2721,7 @@
         <v>46</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>71</v>
@@ -2493,12 +2730,12 @@
         <v>1</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>6.3</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>43</v>
@@ -2513,21 +2750,21 @@
         <v>46</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>72</v>
       </c>
       <c r="H57" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>9.36</v>
+        <v>9.35</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>43</v>
@@ -2542,7 +2779,7 @@
         <v>46</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>73</v>
@@ -2551,12 +2788,12 @@
         <v>0</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>13.04</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>43</v>
@@ -2571,7 +2808,7 @@
         <v>46</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>74</v>
@@ -2580,12 +2817,12 @@
         <v>0</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>15.07</v>
+        <v>14.13</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>43</v>
@@ -2600,7 +2837,7 @@
         <v>46</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>75</v>
@@ -2609,12 +2846,12 @@
         <v>0</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>17.4</v>
+        <v>14.17</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>43</v>
@@ -2629,21 +2866,21 @@
         <v>46</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>76</v>
       </c>
       <c r="H61" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>18.7</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>77</v>
@@ -2658,7 +2895,7 @@
         <v>80</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>81</v>
@@ -2667,12 +2904,12 @@
         <v>1</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>77</v>
@@ -2687,7 +2924,7 @@
         <v>80</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>82</v>
@@ -2696,12 +2933,12 @@
         <v>1</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>2.61</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>77</v>
@@ -2716,7 +2953,7 @@
         <v>80</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>83</v>
@@ -2725,12 +2962,12 @@
         <v>1</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>2.61</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>77</v>
@@ -2745,7 +2982,7 @@
         <v>80</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>84</v>
@@ -2754,12 +2991,12 @@
         <v>1</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>3.03</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>77</v>
@@ -2774,7 +3011,7 @@
         <v>80</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>85</v>
@@ -2783,12 +3020,12 @@
         <v>1</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>3.19</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>77</v>
@@ -2803,7 +3040,7 @@
         <v>80</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>86</v>
@@ -2812,12 +3049,12 @@
         <v>1</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>4.19</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>77</v>
@@ -2832,7 +3069,7 @@
         <v>80</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>87</v>
@@ -2841,12 +3078,12 @@
         <v>1</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>4.19</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>77</v>
@@ -2861,7 +3098,7 @@
         <v>80</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>88</v>
@@ -2870,12 +3107,12 @@
         <v>1</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>5.02</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>77</v>
@@ -2890,7 +3127,7 @@
         <v>80</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>89</v>
@@ -2899,12 +3136,12 @@
         <v>1</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>5.87</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>77</v>
@@ -2919,21 +3156,21 @@
         <v>80</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>90</v>
       </c>
       <c r="H71" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>6.89</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>77</v>
@@ -2948,7 +3185,7 @@
         <v>80</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>91</v>
@@ -2957,12 +3194,12 @@
         <v>1</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>7.51</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>77</v>
@@ -2977,21 +3214,21 @@
         <v>80</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>92</v>
       </c>
       <c r="H73" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>8.51</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>77</v>
@@ -3006,7 +3243,7 @@
         <v>80</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>93</v>
@@ -3015,12 +3252,12 @@
         <v>1</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>12.28</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>77</v>
@@ -3035,7 +3272,7 @@
         <v>80</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>94</v>
@@ -3044,12 +3281,12 @@
         <v>0</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>15.14</v>
+        <v>14.15</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>77</v>
@@ -3064,21 +3301,21 @@
         <v>80</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>95</v>
       </c>
       <c r="H76" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>15.49</v>
+        <v>14.98</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>77</v>
@@ -3093,21 +3330,21 @@
         <v>80</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>96</v>
       </c>
       <c r="H77" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>19.06</v>
+        <v>17.23</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>77</v>
@@ -3128,15 +3365,15 @@
         <v>97</v>
       </c>
       <c r="H78" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>28.51</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>77</v>
@@ -3157,15 +3394,15 @@
         <v>98</v>
       </c>
       <c r="H79" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>35.88</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>77</v>
@@ -3186,349 +3423,349 @@
         <v>99</v>
       </c>
       <c r="H80" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>43.25</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B81" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G81" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C81" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="H81" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>1.89</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="C82" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G82" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D82" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="H82" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>2.02</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="D83" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G83" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="H83" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>2.03</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="E84" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G84" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="F84" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G84" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="H84" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>2.37</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H85" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>3.56</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H86" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>3.57</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H87" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>3.57</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H88" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>5.55</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H89" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I89" s="4" t="n">
-        <v>6.43</v>
+        <v>9.21</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H90" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>7.93</v>
+        <v>13.82</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H91" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>11.43</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>115</v>
@@ -3537,56 +3774,56 @@
         <v>1</v>
       </c>
       <c r="I92" s="4" t="n">
-        <v>11.64</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>116</v>
       </c>
       <c r="H93" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I93" s="4" t="n">
-        <v>13.68</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>117</v>
@@ -3595,27 +3832,27 @@
         <v>1</v>
       </c>
       <c r="I94" s="4" t="n">
-        <v>15.74</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="G95" s="3" t="s">
         <v>118</v>
@@ -3624,27 +3861,27 @@
         <v>1</v>
       </c>
       <c r="I95" s="4" t="n">
-        <v>16.02</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>119</v>
@@ -3653,27 +3890,27 @@
         <v>1</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>120</v>
@@ -3682,27 +3919,27 @@
         <v>1</v>
       </c>
       <c r="I97" s="4" t="n">
-        <v>2.24</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>121</v>
@@ -3711,27 +3948,27 @@
         <v>1</v>
       </c>
       <c r="I98" s="4" t="n">
-        <v>2.93</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>122</v>
@@ -3740,27 +3977,27 @@
         <v>1</v>
       </c>
       <c r="I99" s="4" t="n">
-        <v>3.28</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>123</v>
@@ -3769,27 +4006,27 @@
         <v>1</v>
       </c>
       <c r="I100" s="4" t="n">
-        <v>3.66</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>124</v>
@@ -3798,27 +4035,27 @@
         <v>1</v>
       </c>
       <c r="I101" s="4" t="n">
-        <v>3.95</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>125</v>
@@ -3827,27 +4064,27 @@
         <v>1</v>
       </c>
       <c r="I102" s="4" t="n">
-        <v>3.95</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="G103" s="3" t="s">
         <v>126</v>
@@ -3856,85 +4093,85 @@
         <v>1</v>
       </c>
       <c r="I103" s="4" t="n">
-        <v>4.07</v>
+        <v>13.69</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="G104" s="3" t="s">
         <v>127</v>
       </c>
       <c r="H104" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I104" s="4" t="n">
-        <v>4.61</v>
+        <v>13.76</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="G105" s="3" t="s">
         <v>128</v>
       </c>
       <c r="H105" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I105" s="4" t="n">
-        <v>6.76</v>
+        <v>15.42</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="G106" s="3" t="s">
         <v>129</v>
@@ -3943,27 +4180,27 @@
         <v>1</v>
       </c>
       <c r="I106" s="4" t="n">
-        <v>9.34</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>130</v>
@@ -3972,27 +4209,27 @@
         <v>1</v>
       </c>
       <c r="I107" s="4" t="n">
-        <v>11.26</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>131</v>
@@ -4001,56 +4238,56 @@
         <v>1</v>
       </c>
       <c r="I108" s="4" t="n">
-        <v>12.13</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="G109" s="3" t="s">
         <v>132</v>
       </c>
       <c r="H109" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I109" s="4" t="n">
-        <v>12.39</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>133</v>
@@ -4059,346 +4296,346 @@
         <v>1</v>
       </c>
       <c r="I110" s="4" t="n">
-        <v>13.03</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B111" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G111" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C111" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="F111" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="G111" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="H111" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I111" s="4" t="n">
-        <v>2.28</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C112" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G112" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D112" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E112" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="F112" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="G112" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="H112" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I112" s="4" t="n">
-        <v>2.39</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="D113" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G113" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="E113" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="F113" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="G113" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="H113" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I113" s="4" t="n">
-        <v>2.55</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="E114" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G114" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="F114" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="G114" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="H114" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I114" s="4" t="n">
-        <v>2.84</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H115" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I115" s="4" t="n">
-        <v>3.46</v>
+        <v>7.61</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="H116" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I116" s="4" t="n">
-        <v>5.01</v>
+        <v>8.13</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="H117" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I117" s="4" t="n">
-        <v>5.01</v>
+        <v>9.36</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="H118" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I118" s="4" t="n">
-        <v>6.01</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="H119" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I119" s="4" t="n">
-        <v>7.82</v>
+        <v>12.29</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="H120" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I120" s="4" t="n">
-        <v>11.21</v>
+        <v>15.54</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H121" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I121" s="4" t="n">
-        <v>11.76</v>
+        <v>17.57</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>46208</v>
+        <v>46215</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="G122" s="3" t="s">
         <v>149</v>
@@ -4407,56 +4644,56 @@
         <v>1</v>
       </c>
       <c r="I122" s="4" t="n">
-        <v>12.13</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>46208</v>
+        <v>46215</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="G123" s="3" t="s">
         <v>150</v>
       </c>
       <c r="H123" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I123" s="4" t="n">
-        <v>16.97</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>46208</v>
+        <v>46215</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>151</v>
@@ -4465,27 +4702,27 @@
         <v>1</v>
       </c>
       <c r="I124" s="4" t="n">
-        <v>17.03</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>46208</v>
+        <v>46215</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G125" s="3" t="s">
         <v>152</v>
@@ -4494,27 +4731,27 @@
         <v>1</v>
       </c>
       <c r="I125" s="4" t="n">
-        <v>1.76</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>46208</v>
+        <v>46215</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G126" s="3" t="s">
         <v>153</v>
@@ -4523,27 +4760,27 @@
         <v>1</v>
       </c>
       <c r="I126" s="4" t="n">
-        <v>2.05</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>46208</v>
+        <v>46215</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G127" s="3" t="s">
         <v>154</v>
@@ -4552,27 +4789,27 @@
         <v>1</v>
       </c>
       <c r="I127" s="4" t="n">
-        <v>2.45</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>46208</v>
+        <v>46215</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G128" s="3" t="s">
         <v>155</v>
@@ -4581,27 +4818,27 @@
         <v>1</v>
       </c>
       <c r="I128" s="4" t="n">
-        <v>2.89</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>46208</v>
+        <v>46215</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G129" s="3" t="s">
         <v>156</v>
@@ -4610,27 +4847,27 @@
         <v>1</v>
       </c>
       <c r="I129" s="4" t="n">
-        <v>3.74</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>46208</v>
+        <v>46215</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G130" s="3" t="s">
         <v>157</v>
@@ -4639,27 +4876,27 @@
         <v>1</v>
       </c>
       <c r="I130" s="4" t="n">
-        <v>3.86</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>46208</v>
+        <v>46215</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G131" s="3" t="s">
         <v>158</v>
@@ -4668,56 +4905,56 @@
         <v>1</v>
       </c>
       <c r="I131" s="4" t="n">
-        <v>3.86</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>46208</v>
+        <v>46215</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G132" s="3" t="s">
         <v>159</v>
       </c>
       <c r="H132" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I132" s="4" t="n">
-        <v>4.12</v>
+        <v>8.53</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>46208</v>
+        <v>46215</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G133" s="3" t="s">
         <v>160</v>
@@ -4726,56 +4963,56 @@
         <v>1</v>
       </c>
       <c r="I133" s="4" t="n">
-        <v>4.77</v>
+        <v>9.22</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>46208</v>
+        <v>46215</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G134" s="3" t="s">
         <v>161</v>
       </c>
       <c r="H134" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I134" s="4" t="n">
-        <v>4.83</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>46208</v>
+        <v>46215</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G135" s="3" t="s">
         <v>162</v>
@@ -4784,27 +5021,27 @@
         <v>0</v>
       </c>
       <c r="I135" s="4" t="n">
-        <v>7.51</v>
+        <v>12.94</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>46208</v>
+        <v>46215</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="G136" s="3" t="s">
         <v>163</v>
@@ -4813,85 +5050,85 @@
         <v>1</v>
       </c>
       <c r="I136" s="4" t="n">
-        <v>8</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>46208</v>
+        <v>46215</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="G137" s="3" t="s">
         <v>164</v>
       </c>
       <c r="H137" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I137" s="4" t="n">
-        <v>11.01</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>46208</v>
+        <v>46215</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="G138" s="3" t="s">
         <v>165</v>
       </c>
       <c r="H138" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I138" s="4" t="n">
-        <v>17.95</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>46208</v>
+        <v>46215</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="G139" s="3" t="s">
         <v>166</v>
@@ -4900,27 +5137,27 @@
         <v>1</v>
       </c>
       <c r="I139" s="4" t="n">
-        <v>18.69</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>46208</v>
+        <v>46215</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="G140" s="3" t="s">
         <v>167</v>
@@ -4929,7 +5166,2066 @@
         <v>1</v>
       </c>
       <c r="I140" s="4" t="n">
-        <v>18.89</v>
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F141" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H141" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I141" s="4" t="n">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F142" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H142" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I142" s="4" t="n">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H143" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I143" s="4" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H144" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I144" s="4" t="n">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G145" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H145" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I145" s="4" t="n">
+        <v>6.54</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H146" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I146" s="4" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G147" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H147" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I147" s="4" t="n">
+        <v>8.77</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G148" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H148" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I148" s="4" t="n">
+        <v>9.03</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E149" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F149" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G149" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H149" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I149" s="4" t="n">
+        <v>10.97</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F150" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G150" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H150" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I150" s="4" t="n">
+        <v>11.08</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E151" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G151" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H151" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I151" s="4" t="n">
+        <v>13.17</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G152" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H152" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I152" s="4" t="n">
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E153" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F153" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G153" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H153" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I153" s="4" t="n">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F154" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G154" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="H154" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I154" s="4" t="n">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G155" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="H155" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I155" s="4" t="n">
+        <v>2.68</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G156" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="H156" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I156" s="4" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F157" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G157" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H157" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I157" s="4" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F158" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G158" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="H158" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I158" s="4" t="n">
+        <v>4.11</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E159" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F159" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G159" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="H159" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I159" s="4" t="n">
+        <v>4.11</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F160" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="H160" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I160" s="4" t="n">
+        <v>7.55</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F161" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G161" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="H161" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I161" s="4" t="n">
+        <v>9.35</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="H162" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I162" s="4" t="n">
+        <v>11.54</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E163" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G163" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="H163" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I163" s="4" t="n">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E164" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G164" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="H164" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I164" s="4" t="n">
+        <v>16.64</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F165" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H165" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I165" s="4" t="n">
+        <v>18.63</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E166" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F166" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G166" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H166" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I166" s="4" t="n">
+        <v>19.04</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E167" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F167" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G167" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="H167" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I167" s="4" t="n">
+        <v>19.33</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E168" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F168" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G168" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H168" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I168" s="4" t="n">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E169" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F169" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G169" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H169" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I169" s="4" t="n">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E170" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F170" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="H170" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I170" s="4" t="n">
+        <v>2.67</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E171" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F171" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G171" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="H171" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I171" s="4" t="n">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E172" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F172" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="H172" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I172" s="4" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E173" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F173" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G173" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="H173" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I173" s="4" t="n">
+        <v>4.14</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E174" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F174" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G174" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="H174" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I174" s="4" t="n">
+        <v>4.14</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E175" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F175" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G175" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="H175" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I175" s="4" t="n">
+        <v>4.29</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E176" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F176" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G176" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="H176" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I176" s="4" t="n">
+        <v>5.83</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E177" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F177" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G177" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="H177" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I177" s="4" t="n">
+        <v>6.32</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E178" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F178" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G178" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="H178" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I178" s="4" t="n">
+        <v>9.52</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D179" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E179" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F179" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G179" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="H179" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I179" s="4" t="n">
+        <v>12.71</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D180" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E180" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F180" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G180" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H180" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I180" s="4" t="n">
+        <v>13.15</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D181" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E181" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F181" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G181" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="H181" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I181" s="4" t="n">
+        <v>15.46</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E182" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F182" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G182" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="H182" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I182" s="4" t="n">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D183" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E183" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F183" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G183" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="H183" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I183" s="4" t="n">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E184" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F184" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G184" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="H184" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I184" s="4" t="n">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D185" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E185" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F185" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G185" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="H185" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I185" s="4" t="n">
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E186" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F186" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G186" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="H186" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I186" s="4" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D187" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E187" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F187" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G187" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="H187" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I187" s="4" t="n">
+        <v>4.53</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E188" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F188" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G188" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="H188" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I188" s="4" t="n">
+        <v>4.68</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E189" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F189" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G189" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="H189" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I189" s="4" t="n">
+        <v>4.68</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E190" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F190" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G190" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="H190" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I190" s="4" t="n">
+        <v>8.27</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C191" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D191" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E191" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F191" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G191" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="H191" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I191" s="4" t="n">
+        <v>8.76</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C192" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D192" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E192" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F192" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G192" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="H192" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I192" s="4" t="n">
+        <v>9.08</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C193" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E193" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F193" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G193" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="H193" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I193" s="4" t="n">
+        <v>9.67</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E194" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F194" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G194" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H194" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I194" s="4" t="n">
+        <v>10.22</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F195" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G195" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="H195" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I195" s="4" t="n">
+        <v>11.08</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E196" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F196" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G196" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="H196" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I196" s="4" t="n">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E197" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F197" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G197" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="H197" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I197" s="4" t="n">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B198" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C198" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D198" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E198" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F198" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G198" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="H198" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I198" s="4" t="n">
+        <v>2.43</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C199" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D199" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E199" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F199" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G199" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="H199" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I199" s="4" t="n">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C200" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E200" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F200" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G200" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H200" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I200" s="4" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D201" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E201" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F201" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G201" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="H201" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I201" s="4" t="n">
+        <v>4.21</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D202" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E202" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F202" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G202" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="H202" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I202" s="4" t="n">
+        <v>4.21</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D203" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E203" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F203" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G203" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="H203" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I203" s="4" t="n">
+        <v>4.31</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D204" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E204" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F204" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G204" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="H204" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I204" s="4" t="n">
+        <v>4.42</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D205" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E205" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F205" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G205" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="H205" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I205" s="4" t="n">
+        <v>4.45</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E206" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F206" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G206" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="H206" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I206" s="4" t="n">
+        <v>8.92</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C207" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D207" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E207" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F207" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G207" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="H207" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I207" s="4" t="n">
+        <v>8.95</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C208" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D208" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E208" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F208" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G208" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="H208" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I208" s="4" t="n">
+        <v>11.78</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B209" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C209" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D209" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E209" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F209" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G209" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="H209" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I209" s="4" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B210" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C210" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D210" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E210" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F210" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G210" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="H210" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I210" s="4" t="n">
+        <v>18.02</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B211" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C211" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E211" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F211" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G211" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="H211" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I211" s="4" t="n">
+        <v>18.96</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_anytime_tryscorers.xlsx
+++ b/files/NRL_anytime_tryscorers.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="281">
   <si>
     <t xml:space="preserve">Date Local</t>
   </si>
@@ -41,61 +41,571 @@
     <t xml:space="preserve">Anytimeodds</t>
   </si>
   <si>
+    <t xml:space="preserve">19:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100103489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penrith panthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deine Mariner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josiah Karapani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reece Walsh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezra Mam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gehamat Shibasaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kotoni Staggs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brendan Piakura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Riki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Reynolds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Walters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Talty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cory Paix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Willison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Jenkins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian To'o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casey McLean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Edwards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paul Alamoti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathan Cleary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiah Papali'i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blaize Talagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freddy Lussick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Izack Tago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lindsay Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaah Yeo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Henry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moses Leota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scott Sorensen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Cole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100160565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronaldo Mulitalo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sione Katoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">William Kennedy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braydon Trindall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayal Iro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesse Ramien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Briton Nikora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teig Wilton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicholas Hynes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Addin Fonua-Blake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Hazelton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siosifa Talakai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blayke Brailey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron McInnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuku Hau Tapuha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominic Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greg Marzhew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fletcher Sharpe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bradman Best</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kalyn Ponga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Lucas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francis Manuleleua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dane Gagai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trey Mooney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harrison Graham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fletcher Hunt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phoenix Crossland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elijah Salesa-Leaumoana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brodie Jones</t>
+  </si>
+  <si>
     <t xml:space="preserve">20:00</t>
   </si>
   <si>
-    <t xml:space="preserve">100057040</t>
+    <t xml:space="preserve">100096315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Warbrick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moses Leo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sualauvi Faalogo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harry Grant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyran Wishart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Clarke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oryn Keeley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nick Meaney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Howarth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trent Toelau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stefano Utoikamanu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trent Loiero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gabriel Satrick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark Nawaqanitawase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Tupou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugo Savala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cody Ramsey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daly Cherry-Evans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nat Butcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siua Wong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reece Robson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Victor Radley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Watson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toby Rodwell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egan Butcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spencer Leniu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naufahu Whyte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100132986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Savage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaeo Weekes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jed Stuart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simi Sasagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zac Hosking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Timoko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Strange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hudson Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noah Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owen Pattie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Sanders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe Roddy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corey Horsburgh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Johnston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campbell Graham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tallis Duncan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cody Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Dufty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Wighton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">David Fifita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euan Aitken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keaon Koloamatangi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron Murray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashton Ward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brandon Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John Radel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tevita Tatola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jye Gray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamie Humphreys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Fletcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100117079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george-illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyrell Sloan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setu Tu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mathew Feagai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valentine Holmes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinton Gutherson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Egan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamish Stewart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Liddle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyle Flanagan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Atkinson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damien Cook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luciano Leilua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loko Pasifiki Tonga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alofiana Khan-Pereira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dallin Watene-Zelezniak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ali Leiataua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Capewell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Laban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leka Halasima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taine Tuaupiki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Te Maire Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Pompey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chanel Harris-Tavita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wayde Egan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Fisher-Harris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Healey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erin Clark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Metcalf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitchell Barnett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demitric Vaimauga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100150328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
   </si>
   <si>
     <t xml:space="preserve">wests tigers</t>
   </si>
   <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alofiana Khan-Pereira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charnze Nicoll-Klokstad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ali Leiataua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leka Halasima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Laban</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taine Tuaupiki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Te Maire Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chanel Harris-Tavita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Pompey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wayde Egan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Fisher-Harris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erin Clark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Metcalf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Healey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tanner Stowers-Smith</t>
+    <t xml:space="preserve">Jethro Rinakama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Kiraz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matt Burton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Tracey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enari Tuala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaeman Salmon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Preston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lachlan Galvin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sean O'Sullivan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Mann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bailey Hayward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Curran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gordon Chan Kum Tong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harry Hayes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marcelo Montoya</t>
   </si>
   <si>
     <t xml:space="preserve">Jeral Skelton</t>
@@ -125,492 +635,183 @@
     <t xml:space="preserve">Jarome Luai</t>
   </si>
   <si>
-    <t xml:space="preserve">Josese Lanyon</t>
+    <t xml:space="preserve">Jared Haywood</t>
   </si>
   <si>
     <t xml:space="preserve">Terrell May</t>
   </si>
   <si>
+    <t xml:space="preserve">Fonua Pole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apisai Koroisau</t>
+  </si>
+  <si>
     <t xml:space="preserve">Latu Fainu</t>
   </si>
   <si>
     <t xml:space="preserve">Alex Seyfarth</t>
   </si>
   <si>
-    <t xml:space="preserve">Fonua Pole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Faaletino Tavana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100113380</t>
+    <t xml:space="preserve">14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100155797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manly-warringah sea eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phillip Sami</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dean Ieremia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Campbell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jojo Fifita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keano Kini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AJ Brimson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arama Hau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beau Fermor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zane Harrison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tino Fa'asuamaleaui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver Pascoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Bai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chris Randall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurtis Morrin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klese Haas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Verrills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Trbojevic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lehi Hopoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jason Saab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tolutau Koula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reuben Garrick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joey Walsh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haumole Olakau'atu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Bullemor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamal Fogarty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Simpkin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simione Laiafi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aaron Schoupp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Trbojevic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taniela Paseka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100104912</t>
   </si>
   <si>
     <t xml:space="preserve">dolphins</t>
   </si>
   <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronaldo Mulitalo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sione Katoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">William Kennedy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Braydon Trindall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kayal Iro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jesse Ramien</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Burns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teig Wilton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicholas Hynes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Hazelton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Berrell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jesse Colquhoun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siosifa Talakai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameron McInnes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tuku Hau Tapuha</t>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamiso Tabuai-Fidow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selwyn Cobbo</t>
   </si>
   <si>
     <t xml:space="preserve">Jamayne Isaako</t>
   </si>
   <si>
-    <t xml:space="preserve">Tevita Naufahu</t>
-  </si>
-  <si>
     <t xml:space="preserve">Herbie Farnworth</t>
   </si>
   <si>
+    <t xml:space="preserve">Jack Bostock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connelly Lemuelu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kulikefu Finefeuiaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kodi Nikorima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brad Schneider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremy Marshall-King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Flegler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Donoghoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Plath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morgan Knowles</t>
+  </si>
+  <si>
     <t xml:space="preserve">Trai Fuller</t>
   </si>
   <si>
-    <t xml:space="preserve">Jake Averillo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connelly Lemuelu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kulikefu Finefeuiaki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kodi Nikorima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brad Schneider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremy Marshall-King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ray Stone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamiso Tabuai-Fidow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Plath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurt Donoghoe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morgan Knowles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100170602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Savage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaeo Weekes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sebastian Kris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simi Sasagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Timoko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan Strange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hudson Young</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noah Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owen Pattie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zac Hosking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan Sanders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joe Roddy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corey Horsburgh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Starling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joseph Tapine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daine Laurie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jethro Rinakama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Kiraz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matt Burton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Tracey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enari Tuala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Curran</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaeman Salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lachlan Galvin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stephen Crichton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Preston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurt Mann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bailey Hayward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harry Hayes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logan Spinks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100094582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Addo-Carr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian Kelly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiah Iongi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan Samrani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Araz Nanva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitchell Moses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kelma Tuilagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitione Kautoga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronald Volkman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tallyn Da Silva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack De Belin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Tuivaiti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mark Nawaqanitawase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel Tupou</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Tedesco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robert Toia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daly Cherry-Evans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salesi Foketi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siua Wong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hugo Savala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Watson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Victor Radley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reece Robson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toby Rodwell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Egan Butcher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spencer Leniu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Naufahu Whyte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100138451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">south sydney rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dominic Young</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greg Marzhew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fletcher Sharpe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bradman Best</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kalyn Ponga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Lucas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jermaine McEwen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trey Mooney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dane Gagai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fletcher Hunt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phoenix Crossland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harrison Graham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyson Frizell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dayne Jennings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campbell Graham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tallis Duncan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Dufty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Wighton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">David Fifita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Euan Aitken</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keaon Koloamatangi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameron Murray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashton Ward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Sullivan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">John Radel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brandon Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamie Humphreys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tevita Tatola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Fletcher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100200791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manly-warringah sea eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Trbojevic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lehi Hopoate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jason Saab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tolutau Koula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reuben Garrick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joey Walsh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haumole Olakau'atu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben Trbojevic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamal Fogarty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan Bullemor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corey Waddell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Simpkin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aaron Schoupp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Trbojevic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taniela Paseka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicholas Lenaz</t>
-  </si>
-  <si>
     <t xml:space="preserve">Braidon Burns</t>
   </si>
   <si>
@@ -620,12 +821,12 @@
     <t xml:space="preserve">Scott Drinkwater</t>
   </si>
   <si>
+    <t xml:space="preserve">Tom Chester</t>
+  </si>
+  <si>
     <t xml:space="preserve">Zac Laybutt</t>
   </si>
   <si>
-    <t xml:space="preserve">Tom Chester</t>
-  </si>
-  <si>
     <t xml:space="preserve">Heilum Luki</t>
   </si>
   <si>
@@ -647,112 +848,13 @@
     <t xml:space="preserve">Sam McIntyre</t>
   </si>
   <si>
+    <t xml:space="preserve">Soni Luke</t>
+  </si>
+  <si>
     <t xml:space="preserve">Griffin Neame</t>
   </si>
   <si>
-    <t xml:space="preserve">Soni Luke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100102458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phillip Sami</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dean Ieremia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jojo Fifita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Campbell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keano Kini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AJ Brimson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arama Hau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beau Fermor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zane Harrison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oliver Pascoe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tino Fa'asuamaleaui</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Bai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chris Randall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurtis Morrin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Will Warbrick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sualauvi Faalogo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manaia Waitere</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jahrome Hughes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harry Grant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Clarke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alec MacDonald</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameron Munster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nick Meaney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Howarth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyran Wishart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stefano Utoikamanu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joe Chan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trent Loiero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trent Toelau</t>
+    <t xml:space="preserve">Liam Sutton</t>
   </si>
 </sst>
 </file>
@@ -1102,7 +1204,7 @@
     <col min="2" max="2" width="9.285" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="8.4275" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="25.5775" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="23.005" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="23.8625" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="25.5775" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="21.29" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="6.7125" hidden="0" customWidth="1"/>
@@ -1140,7 +1242,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>9</v>
@@ -1164,12 +1266,12 @@
         <v>1</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>1.8</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>9</v>
@@ -1193,12 +1295,12 @@
         <v>1</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>3.84</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>9</v>
@@ -1222,12 +1324,12 @@
         <v>1</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>9</v>
@@ -1251,12 +1353,12 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>4.55</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>9</v>
@@ -1280,12 +1382,12 @@
         <v>1</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.55</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>9</v>
@@ -1309,12 +1411,12 @@
         <v>1</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.76</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>9</v>
@@ -1338,12 +1440,12 @@
         <v>1</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>5.14</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>9</v>
@@ -1367,12 +1469,12 @@
         <v>1</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>5.19</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>9</v>
@@ -1396,12 +1498,12 @@
         <v>1</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>5.21</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>9</v>
@@ -1422,15 +1524,15 @@
         <v>22</v>
       </c>
       <c r="H11" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>8.08</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>9</v>
@@ -1451,15 +1553,15 @@
         <v>23</v>
       </c>
       <c r="H12" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>12.04</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>9</v>
@@ -1483,12 +1585,12 @@
         <v>1</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>12.88</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>9</v>
@@ -1509,15 +1611,15 @@
         <v>25</v>
       </c>
       <c r="H14" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>14.61</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>9</v>
@@ -1532,21 +1634,21 @@
         <v>12</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H15" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>17.3</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>9</v>
@@ -1561,7 +1663,7 @@
         <v>12</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>27</v>
@@ -1570,12 +1672,12 @@
         <v>1</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>19.84</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>9</v>
@@ -1599,12 +1701,12 @@
         <v>1</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.04</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>9</v>
@@ -1628,12 +1730,12 @@
         <v>1</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.26</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>9</v>
@@ -1657,12 +1759,12 @@
         <v>1</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2.47</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>9</v>
@@ -1686,12 +1788,12 @@
         <v>1</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.74</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>9</v>
@@ -1715,12 +1817,12 @@
         <v>1</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>3.07</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>9</v>
@@ -1744,12 +1846,12 @@
         <v>1</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3.48</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>9</v>
@@ -1773,12 +1875,12 @@
         <v>1</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.48</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>9</v>
@@ -1802,12 +1904,12 @@
         <v>1</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>3.64</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>9</v>
@@ -1828,15 +1930,15 @@
         <v>36</v>
       </c>
       <c r="H25" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>4.77</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>9</v>
@@ -1860,12 +1962,12 @@
         <v>1</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>6.87</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>9</v>
@@ -1889,12 +1991,12 @@
         <v>1</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>8.75</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>9</v>
@@ -1918,12 +2020,12 @@
         <v>0</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>12.3</v>
+        <v>10.86</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>9</v>
@@ -1944,15 +2046,15 @@
         <v>40</v>
       </c>
       <c r="H29" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>14.06</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>9</v>
@@ -1976,12 +2078,12 @@
         <v>0</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>14.16</v>
+        <v>15.41</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>9</v>
@@ -2005,12 +2107,12 @@
         <v>0</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>17.23</v>
+        <v>15.86</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>43</v>
@@ -2025,7 +2127,7 @@
         <v>46</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>47</v>
@@ -2034,12 +2136,12 @@
         <v>1</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>43</v>
@@ -2054,7 +2156,7 @@
         <v>46</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>48</v>
@@ -2063,12 +2165,12 @@
         <v>1</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>43</v>
@@ -2083,7 +2185,7 @@
         <v>46</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>49</v>
@@ -2092,12 +2194,12 @@
         <v>1</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>43</v>
@@ -2112,7 +2214,7 @@
         <v>46</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>50</v>
@@ -2121,12 +2223,12 @@
         <v>1</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>3.19</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>43</v>
@@ -2141,7 +2243,7 @@
         <v>46</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>51</v>
@@ -2150,12 +2252,12 @@
         <v>1</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>43</v>
@@ -2170,7 +2272,7 @@
         <v>46</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>52</v>
@@ -2179,12 +2281,12 @@
         <v>1</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>3.88</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>43</v>
@@ -2199,7 +2301,7 @@
         <v>46</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>53</v>
@@ -2208,12 +2310,12 @@
         <v>1</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>4.24</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>43</v>
@@ -2228,7 +2330,7 @@
         <v>46</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>54</v>
@@ -2237,12 +2339,12 @@
         <v>1</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>4.24</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>43</v>
@@ -2257,7 +2359,7 @@
         <v>46</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>55</v>
@@ -2266,12 +2368,12 @@
         <v>1</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>4.79</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>43</v>
@@ -2286,7 +2388,7 @@
         <v>46</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>56</v>
@@ -2295,12 +2397,12 @@
         <v>1</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>6.42</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>43</v>
@@ -2315,7 +2417,7 @@
         <v>46</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>57</v>
@@ -2324,12 +2426,12 @@
         <v>1</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>7.9</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>43</v>
@@ -2344,21 +2446,21 @@
         <v>46</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>58</v>
       </c>
       <c r="H43" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>10.34</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>43</v>
@@ -2373,21 +2475,21 @@
         <v>46</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>59</v>
       </c>
       <c r="H44" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>10.68</v>
+        <v>11.09</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>43</v>
@@ -2402,7 +2504,7 @@
         <v>46</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>60</v>
@@ -2411,12 +2513,12 @@
         <v>1</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>12.37</v>
+        <v>12.62</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>43</v>
@@ -2431,7 +2533,7 @@
         <v>46</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>61</v>
@@ -2440,12 +2542,12 @@
         <v>0</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>13.39</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>43</v>
@@ -2460,7 +2562,7 @@
         <v>46</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>62</v>
@@ -2469,12 +2571,12 @@
         <v>1</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>43</v>
@@ -2489,7 +2591,7 @@
         <v>46</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>63</v>
@@ -2498,12 +2600,12 @@
         <v>1</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>43</v>
@@ -2518,7 +2620,7 @@
         <v>46</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>64</v>
@@ -2527,12 +2629,12 @@
         <v>1</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>2.46</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>43</v>
@@ -2547,7 +2649,7 @@
         <v>46</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>65</v>
@@ -2556,12 +2658,12 @@
         <v>1</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>2.7</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>43</v>
@@ -2576,7 +2678,7 @@
         <v>46</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>66</v>
@@ -2585,12 +2687,12 @@
         <v>1</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>3.02</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>43</v>
@@ -2605,7 +2707,7 @@
         <v>46</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>67</v>
@@ -2614,12 +2716,12 @@
         <v>1</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>4.24</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>43</v>
@@ -2634,7 +2736,7 @@
         <v>46</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>68</v>
@@ -2643,12 +2745,12 @@
         <v>1</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>4.24</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>43</v>
@@ -2663,7 +2765,7 @@
         <v>46</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>69</v>
@@ -2672,12 +2774,12 @@
         <v>1</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>5.11</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>43</v>
@@ -2692,7 +2794,7 @@
         <v>46</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>70</v>
@@ -2701,12 +2803,12 @@
         <v>1</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>5.86</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>43</v>
@@ -2721,7 +2823,7 @@
         <v>46</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>71</v>
@@ -2730,12 +2832,12 @@
         <v>1</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>6.62</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>43</v>
@@ -2750,7 +2852,7 @@
         <v>46</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>72</v>
@@ -2759,12 +2861,12 @@
         <v>0</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>9.35</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>43</v>
@@ -2779,7 +2881,7 @@
         <v>46</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>73</v>
@@ -2788,12 +2890,12 @@
         <v>0</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>9.48</v>
+        <v>10.52</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>43</v>
@@ -2808,21 +2910,21 @@
         <v>46</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>74</v>
       </c>
       <c r="H59" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>14.13</v>
+        <v>11.01</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>43</v>
@@ -2837,7 +2939,7 @@
         <v>46</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>75</v>
@@ -2846,12 +2948,12 @@
         <v>0</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>14.17</v>
+        <v>17.15</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>43</v>
@@ -2866,21 +2968,21 @@
         <v>46</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>76</v>
       </c>
       <c r="H61" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>14.7</v>
+        <v>17.49</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>77</v>
@@ -2904,12 +3006,12 @@
         <v>1</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>77</v>
@@ -2933,12 +3035,12 @@
         <v>1</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>3.02</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>77</v>
@@ -2962,12 +3064,12 @@
         <v>1</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>3.3</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>77</v>
@@ -2991,12 +3093,12 @@
         <v>1</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>77</v>
@@ -3020,12 +3122,12 @@
         <v>1</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>3.57</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>77</v>
@@ -3049,12 +3151,12 @@
         <v>1</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>3.7</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>77</v>
@@ -3078,12 +3180,12 @@
         <v>1</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>4.23</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>77</v>
@@ -3107,12 +3209,12 @@
         <v>1</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>4.23</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>77</v>
@@ -3136,12 +3238,12 @@
         <v>1</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>6.71</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>77</v>
@@ -3165,12 +3267,12 @@
         <v>1</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>7.33</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>77</v>
@@ -3194,12 +3296,12 @@
         <v>1</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>7.4</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>77</v>
@@ -3220,15 +3322,15 @@
         <v>92</v>
       </c>
       <c r="H73" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>7.9</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>77</v>
@@ -3252,12 +3354,12 @@
         <v>1</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>11.46</v>
+        <v>21.97</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>77</v>
@@ -3281,12 +3383,12 @@
         <v>0</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>14.15</v>
+        <v>23.97</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>77</v>
@@ -3301,7 +3403,7 @@
         <v>80</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>95</v>
@@ -3310,12 +3412,12 @@
         <v>1</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>14.98</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>77</v>
@@ -3330,21 +3432,21 @@
         <v>80</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>96</v>
       </c>
       <c r="H77" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>17.23</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>77</v>
@@ -3368,12 +3470,12 @@
         <v>1</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>1.83</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>77</v>
@@ -3397,12 +3499,12 @@
         <v>1</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>2.04</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>77</v>
@@ -3426,12 +3528,12 @@
         <v>1</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>2.84</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>77</v>
@@ -3455,12 +3557,12 @@
         <v>1</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>3.08</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>77</v>
@@ -3484,12 +3586,12 @@
         <v>1</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>3.29</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>77</v>
@@ -3513,12 +3615,12 @@
         <v>1</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>3.31</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>77</v>
@@ -3542,12 +3644,12 @@
         <v>1</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>3.31</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>77</v>
@@ -3571,12 +3673,12 @@
         <v>1</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>3.79</v>
+        <v>8.63</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>77</v>
@@ -3600,12 +3702,12 @@
         <v>1</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>4.07</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>77</v>
@@ -3629,12 +3731,12 @@
         <v>0</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>5.47</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>77</v>
@@ -3658,12 +3760,12 @@
         <v>0</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>8.15</v>
+        <v>12.16</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>77</v>
@@ -3684,15 +3786,15 @@
         <v>108</v>
       </c>
       <c r="H89" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I89" s="4" t="n">
-        <v>9.21</v>
+        <v>13.34</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>77</v>
@@ -3716,12 +3818,12 @@
         <v>1</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>13.82</v>
+        <v>16.95</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>77</v>
@@ -3742,15 +3844,15 @@
         <v>110</v>
       </c>
       <c r="H91" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>16.2</v>
+        <v>19.03</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>111</v>
@@ -3765,7 +3867,7 @@
         <v>114</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>115</v>
@@ -3774,12 +3876,12 @@
         <v>1</v>
       </c>
       <c r="I92" s="4" t="n">
-        <v>2.11</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>111</v>
@@ -3794,7 +3896,7 @@
         <v>114</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>116</v>
@@ -3803,12 +3905,12 @@
         <v>1</v>
       </c>
       <c r="I93" s="4" t="n">
-        <v>2.49</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>111</v>
@@ -3823,7 +3925,7 @@
         <v>114</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>117</v>
@@ -3832,12 +3934,12 @@
         <v>1</v>
       </c>
       <c r="I94" s="4" t="n">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>111</v>
@@ -3852,7 +3954,7 @@
         <v>114</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G95" s="3" t="s">
         <v>118</v>
@@ -3861,12 +3963,12 @@
         <v>1</v>
       </c>
       <c r="I95" s="4" t="n">
-        <v>3.69</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>111</v>
@@ -3881,7 +3983,7 @@
         <v>114</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>119</v>
@@ -3890,12 +3992,12 @@
         <v>1</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>3.9</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>111</v>
@@ -3910,7 +4012,7 @@
         <v>114</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>120</v>
@@ -3919,12 +4021,12 @@
         <v>1</v>
       </c>
       <c r="I97" s="4" t="n">
-        <v>3.98</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>111</v>
@@ -3939,7 +4041,7 @@
         <v>114</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>121</v>
@@ -3948,12 +4050,12 @@
         <v>1</v>
       </c>
       <c r="I98" s="4" t="n">
-        <v>4.3</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>111</v>
@@ -3968,7 +4070,7 @@
         <v>114</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>122</v>
@@ -3977,12 +4079,12 @@
         <v>1</v>
       </c>
       <c r="I99" s="4" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>111</v>
@@ -3997,7 +4099,7 @@
         <v>114</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>123</v>
@@ -4006,12 +4108,12 @@
         <v>1</v>
       </c>
       <c r="I100" s="4" t="n">
-        <v>4.59</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>111</v>
@@ -4026,7 +4128,7 @@
         <v>114</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>124</v>
@@ -4035,12 +4137,12 @@
         <v>1</v>
       </c>
       <c r="I101" s="4" t="n">
-        <v>4.83</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>111</v>
@@ -4055,7 +4157,7 @@
         <v>114</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>125</v>
@@ -4064,12 +4166,12 @@
         <v>1</v>
       </c>
       <c r="I102" s="4" t="n">
-        <v>10.35</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>111</v>
@@ -4084,21 +4186,21 @@
         <v>114</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G103" s="3" t="s">
         <v>126</v>
       </c>
       <c r="H103" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I103" s="4" t="n">
-        <v>13.69</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>111</v>
@@ -4113,21 +4215,21 @@
         <v>114</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G104" s="3" t="s">
         <v>127</v>
       </c>
       <c r="H104" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I104" s="4" t="n">
-        <v>13.76</v>
+        <v>11.66</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>111</v>
@@ -4151,12 +4253,12 @@
         <v>1</v>
       </c>
       <c r="I105" s="4" t="n">
-        <v>15.42</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>111</v>
@@ -4171,7 +4273,7 @@
         <v>114</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G106" s="3" t="s">
         <v>129</v>
@@ -4180,12 +4282,12 @@
         <v>1</v>
       </c>
       <c r="I106" s="4" t="n">
-        <v>1.74</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>111</v>
@@ -4200,7 +4302,7 @@
         <v>114</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>130</v>
@@ -4209,12 +4311,12 @@
         <v>1</v>
       </c>
       <c r="I107" s="4" t="n">
-        <v>2.13</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>111</v>
@@ -4229,7 +4331,7 @@
         <v>114</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>131</v>
@@ -4238,12 +4340,12 @@
         <v>1</v>
       </c>
       <c r="I108" s="4" t="n">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>111</v>
@@ -4258,7 +4360,7 @@
         <v>114</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G109" s="3" t="s">
         <v>132</v>
@@ -4267,12 +4369,12 @@
         <v>1</v>
       </c>
       <c r="I109" s="4" t="n">
-        <v>3.38</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>111</v>
@@ -4287,7 +4389,7 @@
         <v>114</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>133</v>
@@ -4296,12 +4398,12 @@
         <v>1</v>
       </c>
       <c r="I110" s="4" t="n">
-        <v>3.98</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>111</v>
@@ -4316,7 +4418,7 @@
         <v>114</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>134</v>
@@ -4325,12 +4427,12 @@
         <v>1</v>
       </c>
       <c r="I111" s="4" t="n">
-        <v>4.55</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>111</v>
@@ -4345,7 +4447,7 @@
         <v>114</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>135</v>
@@ -4354,12 +4456,12 @@
         <v>1</v>
       </c>
       <c r="I112" s="4" t="n">
-        <v>4.6</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>111</v>
@@ -4374,7 +4476,7 @@
         <v>114</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G113" s="3" t="s">
         <v>136</v>
@@ -4383,12 +4485,12 @@
         <v>1</v>
       </c>
       <c r="I113" s="4" t="n">
-        <v>4.6</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>111</v>
@@ -4403,7 +4505,7 @@
         <v>114</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>137</v>
@@ -4412,12 +4514,12 @@
         <v>1</v>
       </c>
       <c r="I114" s="4" t="n">
-        <v>5.73</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B115" s="3" t="s">
         <v>111</v>
@@ -4432,7 +4534,7 @@
         <v>114</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G115" s="3" t="s">
         <v>138</v>
@@ -4441,12 +4543,12 @@
         <v>1</v>
       </c>
       <c r="I115" s="4" t="n">
-        <v>7.61</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>111</v>
@@ -4461,7 +4563,7 @@
         <v>114</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G116" s="3" t="s">
         <v>139</v>
@@ -4470,12 +4572,12 @@
         <v>1</v>
       </c>
       <c r="I116" s="4" t="n">
-        <v>8.13</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>111</v>
@@ -4490,7 +4592,7 @@
         <v>114</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G117" s="3" t="s">
         <v>140</v>
@@ -4499,12 +4601,12 @@
         <v>0</v>
       </c>
       <c r="I117" s="4" t="n">
-        <v>9.36</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>111</v>
@@ -4519,21 +4621,21 @@
         <v>114</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G118" s="3" t="s">
         <v>141</v>
       </c>
       <c r="H118" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I118" s="4" t="n">
-        <v>11.4</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>111</v>
@@ -4548,7 +4650,7 @@
         <v>114</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>142</v>
@@ -4557,12 +4659,12 @@
         <v>0</v>
       </c>
       <c r="I119" s="4" t="n">
-        <v>12.29</v>
+        <v>11.07</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>111</v>
@@ -4577,21 +4679,21 @@
         <v>114</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G120" s="3" t="s">
         <v>143</v>
       </c>
       <c r="H120" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I120" s="4" t="n">
-        <v>15.54</v>
+        <v>12.24</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>111</v>
@@ -4606,21 +4708,21 @@
         <v>114</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G121" s="3" t="s">
         <v>144</v>
       </c>
       <c r="H121" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I121" s="4" t="n">
-        <v>17.57</v>
+        <v>14</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>145</v>
@@ -4644,12 +4746,12 @@
         <v>1</v>
       </c>
       <c r="I122" s="4" t="n">
-        <v>1.94</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>145</v>
@@ -4673,12 +4775,12 @@
         <v>1</v>
       </c>
       <c r="I123" s="4" t="n">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>145</v>
@@ -4702,12 +4804,12 @@
         <v>1</v>
       </c>
       <c r="I124" s="4" t="n">
-        <v>2.72</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>145</v>
@@ -4731,12 +4833,12 @@
         <v>1</v>
       </c>
       <c r="I125" s="4" t="n">
-        <v>3.23</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>145</v>
@@ -4760,12 +4862,12 @@
         <v>1</v>
       </c>
       <c r="I126" s="4" t="n">
-        <v>4.21</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>145</v>
@@ -4789,12 +4891,12 @@
         <v>1</v>
       </c>
       <c r="I127" s="4" t="n">
-        <v>4.34</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>145</v>
@@ -4818,12 +4920,12 @@
         <v>1</v>
       </c>
       <c r="I128" s="4" t="n">
-        <v>4.34</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>145</v>
@@ -4844,15 +4946,15 @@
         <v>156</v>
       </c>
       <c r="H129" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I129" s="4" t="n">
-        <v>4.68</v>
+        <v>5.96</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>145</v>
@@ -4876,12 +4978,12 @@
         <v>1</v>
       </c>
       <c r="I130" s="4" t="n">
-        <v>5.39</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>145</v>
@@ -4905,12 +5007,12 @@
         <v>1</v>
       </c>
       <c r="I131" s="4" t="n">
-        <v>5.5</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>145</v>
@@ -4931,15 +5033,15 @@
         <v>159</v>
       </c>
       <c r="H132" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I132" s="4" t="n">
-        <v>8.53</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>145</v>
@@ -4960,15 +5062,15 @@
         <v>160</v>
       </c>
       <c r="H133" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I133" s="4" t="n">
-        <v>9.22</v>
+        <v>10.61</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>145</v>
@@ -4989,15 +5091,15 @@
         <v>161</v>
       </c>
       <c r="H134" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I134" s="4" t="n">
-        <v>10.17</v>
+        <v>14.18</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>145</v>
@@ -5012,21 +5114,21 @@
         <v>148</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G135" s="3" t="s">
         <v>162</v>
       </c>
       <c r="H135" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I135" s="4" t="n">
-        <v>12.94</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>145</v>
@@ -5050,12 +5152,12 @@
         <v>1</v>
       </c>
       <c r="I136" s="4" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>145</v>
@@ -5079,12 +5181,12 @@
         <v>1</v>
       </c>
       <c r="I137" s="4" t="n">
-        <v>2.16</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>145</v>
@@ -5108,12 +5210,12 @@
         <v>1</v>
       </c>
       <c r="I138" s="4" t="n">
-        <v>2.4</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>145</v>
@@ -5137,12 +5239,12 @@
         <v>1</v>
       </c>
       <c r="I139" s="4" t="n">
-        <v>3.25</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>145</v>
@@ -5163,15 +5265,15 @@
         <v>167</v>
       </c>
       <c r="H140" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I140" s="4" t="n">
-        <v>3.32</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>145</v>
@@ -5195,12 +5297,12 @@
         <v>1</v>
       </c>
       <c r="I141" s="4" t="n">
-        <v>3.83</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>145</v>
@@ -5224,12 +5326,12 @@
         <v>1</v>
       </c>
       <c r="I142" s="4" t="n">
-        <v>3.83</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>145</v>
@@ -5253,12 +5355,12 @@
         <v>1</v>
       </c>
       <c r="I143" s="4" t="n">
-        <v>5.9</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>145</v>
@@ -5282,12 +5384,12 @@
         <v>1</v>
       </c>
       <c r="I144" s="4" t="n">
-        <v>6.45</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>145</v>
@@ -5311,12 +5413,12 @@
         <v>1</v>
       </c>
       <c r="I145" s="4" t="n">
-        <v>6.54</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>145</v>
@@ -5340,12 +5442,12 @@
         <v>1</v>
       </c>
       <c r="I146" s="4" t="n">
-        <v>7.99</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>145</v>
@@ -5369,12 +5471,12 @@
         <v>0</v>
       </c>
       <c r="I147" s="4" t="n">
-        <v>8.77</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>145</v>
@@ -5398,12 +5500,12 @@
         <v>1</v>
       </c>
       <c r="I148" s="4" t="n">
-        <v>9.03</v>
+        <v>12.04</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>145</v>
@@ -5427,12 +5529,12 @@
         <v>0</v>
       </c>
       <c r="I149" s="4" t="n">
-        <v>10.97</v>
+        <v>14.09</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>145</v>
@@ -5456,12 +5558,12 @@
         <v>1</v>
       </c>
       <c r="I150" s="4" t="n">
-        <v>11.08</v>
+        <v>20.37</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>145</v>
@@ -5485,12 +5587,12 @@
         <v>0</v>
       </c>
       <c r="I151" s="4" t="n">
-        <v>13.17</v>
+        <v>20.73</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>179</v>
@@ -5514,12 +5616,12 @@
         <v>1</v>
       </c>
       <c r="I152" s="4" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>179</v>
@@ -5543,12 +5645,12 @@
         <v>1</v>
       </c>
       <c r="I153" s="4" t="n">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>179</v>
@@ -5572,12 +5674,12 @@
         <v>1</v>
       </c>
       <c r="I154" s="4" t="n">
-        <v>2.29</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>179</v>
@@ -5601,12 +5703,12 @@
         <v>1</v>
       </c>
       <c r="I155" s="4" t="n">
-        <v>2.68</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>179</v>
@@ -5630,12 +5732,12 @@
         <v>1</v>
       </c>
       <c r="I156" s="4" t="n">
-        <v>2.79</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>179</v>
@@ -5659,12 +5761,12 @@
         <v>1</v>
       </c>
       <c r="I157" s="4" t="n">
-        <v>3.65</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>179</v>
@@ -5688,12 +5790,12 @@
         <v>1</v>
       </c>
       <c r="I158" s="4" t="n">
-        <v>4.11</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>179</v>
@@ -5717,12 +5819,12 @@
         <v>1</v>
       </c>
       <c r="I159" s="4" t="n">
-        <v>4.11</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>179</v>
@@ -5746,12 +5848,12 @@
         <v>1</v>
       </c>
       <c r="I160" s="4" t="n">
-        <v>7.55</v>
+        <v>7.57</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>179</v>
@@ -5775,12 +5877,12 @@
         <v>0</v>
       </c>
       <c r="I161" s="4" t="n">
-        <v>9.35</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>179</v>
@@ -5801,15 +5903,15 @@
         <v>193</v>
       </c>
       <c r="H162" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I162" s="4" t="n">
-        <v>11.54</v>
+        <v>11.18</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>179</v>
@@ -5830,15 +5932,15 @@
         <v>194</v>
       </c>
       <c r="H163" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I163" s="4" t="n">
-        <v>13.65</v>
+        <v>12</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>179</v>
@@ -5862,12 +5964,12 @@
         <v>0</v>
       </c>
       <c r="I164" s="4" t="n">
-        <v>16.64</v>
+        <v>16.92</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>179</v>
@@ -5891,12 +5993,12 @@
         <v>1</v>
       </c>
       <c r="I165" s="4" t="n">
-        <v>18.63</v>
+        <v>17.57</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>179</v>
@@ -5917,15 +6019,15 @@
         <v>197</v>
       </c>
       <c r="H166" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I166" s="4" t="n">
-        <v>19.04</v>
+        <v>18.34</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>179</v>
@@ -5940,21 +6042,21 @@
         <v>182</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G167" s="3" t="s">
         <v>198</v>
       </c>
       <c r="H167" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I167" s="4" t="n">
-        <v>19.33</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>179</v>
@@ -5978,12 +6080,12 @@
         <v>1</v>
       </c>
       <c r="I168" s="4" t="n">
-        <v>2.06</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>179</v>
@@ -6007,12 +6109,12 @@
         <v>1</v>
       </c>
       <c r="I169" s="4" t="n">
-        <v>2.08</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>179</v>
@@ -6036,12 +6138,12 @@
         <v>1</v>
       </c>
       <c r="I170" s="4" t="n">
-        <v>2.67</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>179</v>
@@ -6065,12 +6167,12 @@
         <v>1</v>
       </c>
       <c r="I171" s="4" t="n">
-        <v>3.34</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>179</v>
@@ -6094,12 +6196,12 @@
         <v>1</v>
       </c>
       <c r="I172" s="4" t="n">
-        <v>3.39</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B173" s="3" t="s">
         <v>179</v>
@@ -6123,12 +6225,12 @@
         <v>1</v>
       </c>
       <c r="I173" s="4" t="n">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>179</v>
@@ -6152,12 +6254,12 @@
         <v>1</v>
       </c>
       <c r="I174" s="4" t="n">
-        <v>4.14</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B175" s="3" t="s">
         <v>179</v>
@@ -6181,12 +6283,12 @@
         <v>1</v>
       </c>
       <c r="I175" s="4" t="n">
-        <v>4.29</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>179</v>
@@ -6210,12 +6312,12 @@
         <v>1</v>
       </c>
       <c r="I176" s="4" t="n">
-        <v>5.83</v>
+        <v>7.53</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>179</v>
@@ -6239,12 +6341,12 @@
         <v>1</v>
       </c>
       <c r="I177" s="4" t="n">
-        <v>6.32</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>179</v>
@@ -6268,12 +6370,12 @@
         <v>1</v>
       </c>
       <c r="I178" s="4" t="n">
-        <v>9.52</v>
+        <v>10.76</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>179</v>
@@ -6297,12 +6399,12 @@
         <v>0</v>
       </c>
       <c r="I179" s="4" t="n">
-        <v>12.71</v>
+        <v>11.66</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>179</v>
@@ -6326,12 +6428,12 @@
         <v>0</v>
       </c>
       <c r="I180" s="4" t="n">
-        <v>13.15</v>
+        <v>14.93</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>179</v>
@@ -6355,12 +6457,12 @@
         <v>0</v>
       </c>
       <c r="I181" s="4" t="n">
-        <v>15.46</v>
+        <v>16.87</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B182" s="3" t="s">
         <v>213</v>
@@ -6375,7 +6477,7 @@
         <v>216</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G182" s="3" t="s">
         <v>217</v>
@@ -6384,12 +6486,12 @@
         <v>1</v>
       </c>
       <c r="I182" s="4" t="n">
-        <v>2.29</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B183" s="3" t="s">
         <v>213</v>
@@ -6404,7 +6506,7 @@
         <v>216</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G183" s="3" t="s">
         <v>218</v>
@@ -6413,12 +6515,12 @@
         <v>1</v>
       </c>
       <c r="I183" s="4" t="n">
-        <v>3.34</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B184" s="3" t="s">
         <v>213</v>
@@ -6433,7 +6535,7 @@
         <v>216</v>
       </c>
       <c r="F184" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G184" s="3" t="s">
         <v>219</v>
@@ -6442,12 +6544,12 @@
         <v>1</v>
       </c>
       <c r="I184" s="4" t="n">
-        <v>3.88</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B185" s="3" t="s">
         <v>213</v>
@@ -6462,7 +6564,7 @@
         <v>216</v>
       </c>
       <c r="F185" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G185" s="3" t="s">
         <v>220</v>
@@ -6471,12 +6573,12 @@
         <v>1</v>
       </c>
       <c r="I185" s="4" t="n">
-        <v>3.96</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B186" s="3" t="s">
         <v>213</v>
@@ -6491,7 +6593,7 @@
         <v>216</v>
       </c>
       <c r="F186" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G186" s="3" t="s">
         <v>221</v>
@@ -6500,12 +6602,12 @@
         <v>1</v>
       </c>
       <c r="I186" s="4" t="n">
-        <v>4.3</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>213</v>
@@ -6520,7 +6622,7 @@
         <v>216</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G187" s="3" t="s">
         <v>222</v>
@@ -6529,12 +6631,12 @@
         <v>1</v>
       </c>
       <c r="I187" s="4" t="n">
-        <v>4.53</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B188" s="3" t="s">
         <v>213</v>
@@ -6549,7 +6651,7 @@
         <v>216</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G188" s="3" t="s">
         <v>223</v>
@@ -6558,12 +6660,12 @@
         <v>1</v>
       </c>
       <c r="I188" s="4" t="n">
-        <v>4.68</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B189" s="3" t="s">
         <v>213</v>
@@ -6578,7 +6680,7 @@
         <v>216</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G189" s="3" t="s">
         <v>224</v>
@@ -6587,12 +6689,12 @@
         <v>1</v>
       </c>
       <c r="I189" s="4" t="n">
-        <v>4.68</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B190" s="3" t="s">
         <v>213</v>
@@ -6607,7 +6709,7 @@
         <v>216</v>
       </c>
       <c r="F190" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>225</v>
@@ -6616,12 +6718,12 @@
         <v>1</v>
       </c>
       <c r="I190" s="4" t="n">
-        <v>8.27</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B191" s="3" t="s">
         <v>213</v>
@@ -6636,7 +6738,7 @@
         <v>216</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G191" s="3" t="s">
         <v>226</v>
@@ -6645,12 +6747,12 @@
         <v>1</v>
       </c>
       <c r="I191" s="4" t="n">
-        <v>8.76</v>
+        <v>7.62</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>213</v>
@@ -6665,7 +6767,7 @@
         <v>216</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G192" s="3" t="s">
         <v>227</v>
@@ -6674,12 +6776,12 @@
         <v>1</v>
       </c>
       <c r="I192" s="4" t="n">
-        <v>9.08</v>
+        <v>7.66</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B193" s="3" t="s">
         <v>213</v>
@@ -6694,7 +6796,7 @@
         <v>216</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>228</v>
@@ -6703,12 +6805,12 @@
         <v>0</v>
       </c>
       <c r="I193" s="4" t="n">
-        <v>9.67</v>
+        <v>8.39</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B194" s="3" t="s">
         <v>213</v>
@@ -6723,7 +6825,7 @@
         <v>216</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G194" s="3" t="s">
         <v>229</v>
@@ -6732,12 +6834,12 @@
         <v>1</v>
       </c>
       <c r="I194" s="4" t="n">
-        <v>10.22</v>
+        <v>8.7</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B195" s="3" t="s">
         <v>213</v>
@@ -6752,7 +6854,7 @@
         <v>216</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>230</v>
@@ -6761,12 +6863,12 @@
         <v>0</v>
       </c>
       <c r="I195" s="4" t="n">
-        <v>11.08</v>
+        <v>9.29</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>213</v>
@@ -6787,15 +6889,15 @@
         <v>231</v>
       </c>
       <c r="H196" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I196" s="4" t="n">
-        <v>2.05</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B197" s="3" t="s">
         <v>213</v>
@@ -6816,15 +6918,15 @@
         <v>232</v>
       </c>
       <c r="H197" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I197" s="4" t="n">
-        <v>2.19</v>
+        <v>18.69</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>213</v>
@@ -6839,7 +6941,7 @@
         <v>216</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G198" s="3" t="s">
         <v>233</v>
@@ -6848,12 +6950,12 @@
         <v>1</v>
       </c>
       <c r="I198" s="4" t="n">
-        <v>2.43</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>213</v>
@@ -6868,7 +6970,7 @@
         <v>216</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G199" s="3" t="s">
         <v>234</v>
@@ -6877,12 +6979,12 @@
         <v>1</v>
       </c>
       <c r="I199" s="4" t="n">
-        <v>3.14</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>213</v>
@@ -6897,7 +6999,7 @@
         <v>216</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G200" s="3" t="s">
         <v>235</v>
@@ -6906,12 +7008,12 @@
         <v>1</v>
       </c>
       <c r="I200" s="4" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>213</v>
@@ -6926,7 +7028,7 @@
         <v>216</v>
       </c>
       <c r="F201" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G201" s="3" t="s">
         <v>236</v>
@@ -6935,12 +7037,12 @@
         <v>1</v>
       </c>
       <c r="I201" s="4" t="n">
-        <v>4.21</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>213</v>
@@ -6955,7 +7057,7 @@
         <v>216</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G202" s="3" t="s">
         <v>237</v>
@@ -6964,12 +7066,12 @@
         <v>1</v>
       </c>
       <c r="I202" s="4" t="n">
-        <v>4.21</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B203" s="3" t="s">
         <v>213</v>
@@ -6984,7 +7086,7 @@
         <v>216</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G203" s="3" t="s">
         <v>238</v>
@@ -6993,12 +7095,12 @@
         <v>1</v>
       </c>
       <c r="I203" s="4" t="n">
-        <v>4.31</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>213</v>
@@ -7013,7 +7115,7 @@
         <v>216</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G204" s="3" t="s">
         <v>239</v>
@@ -7027,7 +7129,7 @@
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>213</v>
@@ -7042,7 +7144,7 @@
         <v>216</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G205" s="3" t="s">
         <v>240</v>
@@ -7051,12 +7153,12 @@
         <v>1</v>
       </c>
       <c r="I205" s="4" t="n">
-        <v>4.45</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>213</v>
@@ -7071,21 +7173,21 @@
         <v>216</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G206" s="3" t="s">
         <v>241</v>
       </c>
       <c r="H206" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I206" s="4" t="n">
-        <v>8.92</v>
+        <v>8.24</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>213</v>
@@ -7100,7 +7202,7 @@
         <v>216</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G207" s="3" t="s">
         <v>242</v>
@@ -7109,12 +7211,12 @@
         <v>1</v>
       </c>
       <c r="I207" s="4" t="n">
-        <v>8.95</v>
+        <v>15.12</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>213</v>
@@ -7129,7 +7231,7 @@
         <v>216</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G208" s="3" t="s">
         <v>243</v>
@@ -7138,12 +7240,12 @@
         <v>1</v>
       </c>
       <c r="I208" s="4" t="n">
-        <v>11.78</v>
+        <v>16.83</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>213</v>
@@ -7158,7 +7260,7 @@
         <v>216</v>
       </c>
       <c r="F209" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G209" s="3" t="s">
         <v>244</v>
@@ -7167,12 +7269,12 @@
         <v>0</v>
       </c>
       <c r="I209" s="4" t="n">
-        <v>16</v>
+        <v>18.04</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B210" s="3" t="s">
         <v>213</v>
@@ -7187,7 +7289,7 @@
         <v>216</v>
       </c>
       <c r="F210" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G210" s="3" t="s">
         <v>245</v>
@@ -7196,12 +7298,12 @@
         <v>1</v>
       </c>
       <c r="I210" s="4" t="n">
-        <v>18.02</v>
+        <v>20.36</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>213</v>
@@ -7216,16 +7318,886 @@
         <v>216</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G211" s="3" t="s">
         <v>246</v>
       </c>
       <c r="H211" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I211" s="4" t="n">
+        <v>20.88</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B212" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C212" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D212" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E212" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F212" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G212" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="H212" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I212" s="4" t="n">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E213" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F213" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G213" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="H213" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I213" s="4" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C214" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D214" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E214" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F214" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G214" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="H214" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I214" s="4" t="n">
+        <v>2.67</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D215" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E215" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F215" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G215" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H215" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I215" s="4" t="n">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C216" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E216" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F216" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G216" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="H216" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I216" s="4" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E217" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F217" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G217" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H217" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I217" s="4" t="n">
+        <v>5.28</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E218" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F218" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G218" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="H218" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I218" s="4" t="n">
+        <v>5.28</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E219" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F219" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G219" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="H219" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I219" s="4" t="n">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D220" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E220" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F220" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G220" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="H220" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I220" s="4" t="n">
+        <v>7.38</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C221" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D221" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E221" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F221" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G221" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="H221" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I221" s="4" t="n">
+        <v>8.43</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C222" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E222" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F222" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G222" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="H222" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I222" s="4" t="n">
+        <v>12.64</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C223" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E223" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F223" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G223" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="H223" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="I211" s="4" t="n">
-        <v>18.96</v>
+      <c r="I223" s="4" t="n">
+        <v>18.39</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C224" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E224" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F224" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G224" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H224" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I224" s="4" t="n">
+        <v>18.76</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E225" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F225" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G225" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="H225" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I225" s="4" t="n">
+        <v>19.27</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E226" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F226" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G226" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="H226" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I226" s="4" t="n">
+        <v>19.56</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E227" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G227" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="H227" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I227" s="4" t="n">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E228" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G228" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="H228" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I228" s="4" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E229" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F229" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G229" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="H229" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I229" s="4" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C230" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E230" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F230" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G230" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="H230" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I230" s="4" t="n">
+        <v>2.98</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E231" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F231" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G231" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="H231" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I231" s="4" t="n">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E232" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F232" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G232" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="H232" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I232" s="4" t="n">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E233" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F233" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G233" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="H233" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I233" s="4" t="n">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C234" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E234" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F234" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G234" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="H234" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I234" s="4" t="n">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B235" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C235" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E235" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F235" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G235" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="H235" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I235" s="4" t="n">
+        <v>5.36</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C236" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E236" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F236" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G236" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="H236" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I236" s="4" t="n">
+        <v>6.02</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B237" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C237" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E237" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F237" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G237" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H237" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I237" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C238" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E238" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F238" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G238" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="H238" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I238" s="4" t="n">
+        <v>11.74</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B239" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C239" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D239" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E239" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F239" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G239" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="H239" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I239" s="4" t="n">
+        <v>14.27</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B240" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C240" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D240" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E240" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F240" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G240" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="H240" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I240" s="4" t="n">
+        <v>14.75</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C241" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D241" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E241" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F241" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G241" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="H241" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I241" s="4" t="n">
+        <v>18.97</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_anytime_tryscorers.xlsx
+++ b/files/NRL_anytime_tryscorers.xlsx
@@ -44,12 +44,522 @@
     <t xml:space="preserve">19:50</t>
   </si>
   <si>
-    <t xml:space="preserve">100103489</t>
+    <t xml:space="preserve">sched-2026-20260723-1950-parramatta-eels-penrith-panthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
   </si>
   <si>
     <t xml:space="preserve">penrith panthers</t>
   </si>
   <si>
+    <t xml:space="preserve">Josh Addo-Carr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian Kelly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiah Iongi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Penisini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Samrani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitchell Moses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kitione Kautoga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luca Moretti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronald Volkman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tallyn Da Silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack De Belin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joash Papalii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Jenkins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian To'o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaxen Edgar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casey McLean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paul Alamoti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiah Papali'i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathan Cleary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blaize Talagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freddy Lussick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lindsay Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Izack Tago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaah Yeo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Henry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moses Leota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scott Sorensen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Phillips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Cole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260724-1800-newcastle-knights-sydney-roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominic Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fletcher Sharpe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greg Marzhew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fletcher Hunt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bradman Best</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Lucas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francis Manuleleua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trey Mooney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandon Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harrison Graham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phoenix Crossland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyson Frizell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elijah Salesa-Leaumoana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brodie Jones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark Nawaqanitawase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Tupou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Tedesco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robert Toia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nat Butcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siua Wong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daly Cherry-Evans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reece Robson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Victor Radley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Watson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egan Butcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spencer Leniu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naufahu Whyte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260724-2000-south-sydney-rabbitohs-melbourne-storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moses Leo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sualauvi Faalogo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jahrome Hughes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siulagi Tuimalatu-Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyran Wishart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Clarke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oryn Keeley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nick Meaney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Howarth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trent Toelau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harry Grant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stefano Utoikamanu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Johnston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campbell Graham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cody Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Dufty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Wighton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latrell Siegwalt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euan Aitken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John Radel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashton Ward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keaon Koloamatangi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Sullivan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brandon Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tevita Tatola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jye Gray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bronson Garlick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamie Humphreys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Fletcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260725-1500-canberra-raiders-wests-tigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wests tigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Savage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaeo Weekes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jed Stuart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simi Sasagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Timoko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Strange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zac Hosking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matty Nicholson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Sanders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Starling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corey Horsburgh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joseph Tapine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daine Laurie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Papalii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coby Black</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sebastian Kris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vena Patuki-Case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faaletino Tavana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunia Turuva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jahream Bula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Tupou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samuela Fainu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Roberts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Javon Andrews</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick Herbert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jarome Luai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apisai Koroisau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terrell May</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fonua Pole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sione Fainu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260725-1730-canterbury-bankstown-bulldogs-warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jethro Rinakama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Kiraz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matt Burton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Tracey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enari Tuala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viliame Kikau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Preston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lachlan Galvin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stephen Crichton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bailey Hayward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Curran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaeman Salmon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gordon Chan Kum Tong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alofiana Khan-Pereira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dallin Watene-Zelezniak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ali Leiataua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Capewell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Laban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leka Halasima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taine Tuaupiki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Pompey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chanel Harris-Tavita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Te Maire Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wayde Egan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Fisher-Harris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Healey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erin Clark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Metcalf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitchell Barnett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demitric Vaimauga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260725-1935-north-queensland-cowboys-brisbane-broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
     <t xml:space="preserve">brisbane broncos</t>
   </si>
   <si>
@@ -71,7 +581,7 @@
     <t xml:space="preserve">Kotoni Staggs</t>
   </si>
   <si>
-    <t xml:space="preserve">Brendan Piakura</t>
+    <t xml:space="preserve">Xavier Willison</t>
   </si>
   <si>
     <t xml:space="preserve">Jordan Riki</t>
@@ -89,72 +599,174 @@
     <t xml:space="preserve">Cory Paix</t>
   </si>
   <si>
-    <t xml:space="preserve">Xavier Willison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Jenkins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian To'o</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casey McLean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Edwards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paul Alamoti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nathan Cleary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiah Papali'i</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blaize Talagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freddy Lussick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Izack Tago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lindsay Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaah Yeo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Henry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moses Leota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scott Sorensen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Cole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100160565</t>
+    <t xml:space="preserve">Payne Haas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Gale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braidon Burns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murray Taulagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaxon Purdue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scott Drinkwater</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Chester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Dearden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heilum Luki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremiah Nanai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Clifford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reed Mahoney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reuben Cotter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam McIntyre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Griffin Neame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soni Luke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Sutton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Mikaele</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260726-1400-st-george-illawarra-dragons-gold-coast-titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george-illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phillip Sami</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dean Ieremia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jojo Fifita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Campbell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keano Kini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arama Hau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beau Fermor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaylan De Groot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver Pascoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zane Harrison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tino Fa'asuamaleaui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Bai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chris Randall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurtis Morrin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klese Haas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Verrills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyrell Sloan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setu Tu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mathew Feagai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valentine Holmes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinton Gutherson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Egan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamish Stewart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Liddle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyle Flanagan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Atkinson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damien Cook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luciano Leilua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loko Jnr Pasifiki Tonga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan Couchman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260726-1605-manly-warringah-sea-eagles-cronulla-sutherland-sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manly-warringah sea eagles</t>
   </si>
   <si>
     <t xml:space="preserve">cronulla-sutherland sharks</t>
   </si>
   <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ronaldo Mulitalo</t>
   </si>
   <si>
@@ -164,12 +776,12 @@
     <t xml:space="preserve">William Kennedy</t>
   </si>
   <si>
+    <t xml:space="preserve">Kayal Iro</t>
+  </si>
+  <si>
     <t xml:space="preserve">Braydon Trindall</t>
   </si>
   <si>
-    <t xml:space="preserve">Kayal Iro</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jesse Ramien</t>
   </si>
   <si>
@@ -200,528 +812,15 @@
     <t xml:space="preserve">Tuku Hau Tapuha</t>
   </si>
   <si>
-    <t xml:space="preserve">Dominic Young</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greg Marzhew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fletcher Sharpe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bradman Best</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kalyn Ponga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Lucas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Francis Manuleleua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dane Gagai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trey Mooney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harrison Graham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fletcher Hunt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phoenix Crossland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elijah Salesa-Leaumoana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brodie Jones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100096315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Will Warbrick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moses Leo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sualauvi Faalogo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harry Grant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyran Wishart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Clarke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oryn Keeley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nick Meaney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Howarth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trent Toelau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stefano Utoikamanu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trent Loiero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gabriel Satrick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mark Nawaqanitawase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel Tupou</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hugo Savala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cody Ramsey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daly Cherry-Evans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nat Butcher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siua Wong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reece Robson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Victor Radley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Watson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toby Rodwell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Egan Butcher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spencer Leniu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Naufahu Whyte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100132986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">south sydney rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Savage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaeo Weekes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jed Stuart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simi Sasagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zac Hosking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Timoko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan Strange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hudson Young</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noah Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owen Pattie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan Sanders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joe Roddy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corey Horsburgh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Johnston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campbell Graham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tallis Duncan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cody Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Dufty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Wighton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">David Fifita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Euan Aitken</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keaon Koloamatangi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameron Murray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashton Ward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brandon Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">John Radel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tevita Tatola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jye Gray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamie Humphreys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Fletcher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100117079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george-illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyrell Sloan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Setu Tu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mathew Feagai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valentine Holmes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clinton Gutherson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Egan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamish Stewart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Liddle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyle Flanagan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel Atkinson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Damien Cook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luciano Leilua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loko Pasifiki Tonga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alofiana Khan-Pereira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dallin Watene-Zelezniak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ali Leiataua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurt Capewell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Laban</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leka Halasima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taine Tuaupiki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Te Maire Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Pompey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chanel Harris-Tavita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wayde Egan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Fisher-Harris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Healey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erin Clark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Metcalf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitchell Barnett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demitric Vaimauga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100150328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jethro Rinakama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Kiraz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matt Burton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Tracey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enari Tuala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaeman Salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Preston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lachlan Galvin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sean O'Sullivan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurt Mann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bailey Hayward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Curran</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gordon Chan Kum Tong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harry Hayes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marcelo Montoya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeral Skelton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunia Turuva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jahream Bula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Doueihi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Starford To'a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samuela Fainu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sione Fainu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heamasi Makasini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jarome Luai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jared Haywood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terrell May</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fonua Pole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apisai Koroisau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latu Fainu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Seyfarth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100155797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manly-warringah sea eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phillip Sami</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dean Ieremia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Campbell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jojo Fifita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keano Kini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AJ Brimson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arama Hau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beau Fermor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zane Harrison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tino Fa'asuamaleaui</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oliver Pascoe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Bai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chris Randall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurtis Morrin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Klese Haas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Verrills</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Trbojevic</t>
+    <t xml:space="preserve">Jesse Colquhoun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jason Saab</t>
   </si>
   <si>
     <t xml:space="preserve">Lehi Hopoate</t>
   </si>
   <si>
-    <t xml:space="preserve">Jason Saab</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tolutau Koula</t>
   </si>
   <si>
@@ -731,15 +830,21 @@
     <t xml:space="preserve">Joey Walsh</t>
   </si>
   <si>
+    <t xml:space="preserve">Josh Feledy</t>
+  </si>
+  <si>
     <t xml:space="preserve">Haumole Olakau'atu</t>
   </si>
   <si>
+    <t xml:space="preserve">Ben Trbojevic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamal Fogarty</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ethan Bullemor</t>
   </si>
   <si>
-    <t xml:space="preserve">Jamal Fogarty</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jake Simpkin</t>
   </si>
   <si>
@@ -750,111 +855,6 @@
   </si>
   <si>
     <t xml:space="preserve">Jake Trbojevic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taniela Paseka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100104912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamiso Tabuai-Fidow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selwyn Cobbo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamayne Isaako</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herbie Farnworth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Bostock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connelly Lemuelu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kulikefu Finefeuiaki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kodi Nikorima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brad Schneider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremy Marshall-King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Flegler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurt Donoghoe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Plath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morgan Knowles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trai Fuller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Braidon Burns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Murray Taulagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scott Drinkwater</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Chester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zac Laybutt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heilum Luki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremiah Nanai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Clifford</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reed Mahoney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaxon Purdue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reuben Cotter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam McIntyre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soni Luke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Griffin Neame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Sutton</t>
   </si>
 </sst>
 </file>
@@ -1202,9 +1202,9 @@
   <cols>
     <col min="1" max="1" width="9.285" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="9.285" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="8.4275" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="67.595" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="25.5775" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="23.8625" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="23.005" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="25.5775" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="21.29" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="6.7125" hidden="0" customWidth="1"/>
@@ -1242,7 +1242,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>9</v>
@@ -1257,7 +1257,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>13</v>
@@ -1266,12 +1266,12 @@
         <v>1</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>2.46</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>9</v>
@@ -1286,7 +1286,7 @@
         <v>12</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>14</v>
@@ -1295,12 +1295,12 @@
         <v>1</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>3.23</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>9</v>
@@ -1315,7 +1315,7 @@
         <v>12</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>15</v>
@@ -1324,12 +1324,12 @@
         <v>1</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>3.5</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>9</v>
@@ -1344,7 +1344,7 @@
         <v>12</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>16</v>
@@ -1353,12 +1353,12 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>3.59</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>9</v>
@@ -1373,7 +1373,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>17</v>
@@ -1382,12 +1382,12 @@
         <v>1</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>3.62</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>9</v>
@@ -1402,7 +1402,7 @@
         <v>12</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>18</v>
@@ -1411,12 +1411,12 @@
         <v>1</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.13</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>9</v>
@@ -1431,7 +1431,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>19</v>
@@ -1440,12 +1440,12 @@
         <v>1</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>5.77</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>9</v>
@@ -1460,7 +1460,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>20</v>
@@ -1469,12 +1469,12 @@
         <v>1</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>5.77</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>9</v>
@@ -1489,7 +1489,7 @@
         <v>12</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>21</v>
@@ -1498,12 +1498,12 @@
         <v>1</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>7.4</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>9</v>
@@ -1518,21 +1518,21 @@
         <v>12</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H11" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>9.66</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>9</v>
@@ -1547,21 +1547,21 @@
         <v>12</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H12" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>9.92</v>
+        <v>15.64</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>9</v>
@@ -1576,21 +1576,21 @@
         <v>12</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H13" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>10.51</v>
+        <v>19.23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>9</v>
@@ -1614,12 +1614,12 @@
         <v>1</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>10.9</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>9</v>
@@ -1634,7 +1634,7 @@
         <v>12</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>26</v>
@@ -1643,12 +1643,12 @@
         <v>1</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.67</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>9</v>
@@ -1663,7 +1663,7 @@
         <v>12</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>27</v>
@@ -1672,12 +1672,12 @@
         <v>1</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>9</v>
@@ -1692,7 +1692,7 @@
         <v>12</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>28</v>
@@ -1701,12 +1701,12 @@
         <v>1</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.39</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>9</v>
@@ -1721,7 +1721,7 @@
         <v>12</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>29</v>
@@ -1730,12 +1730,12 @@
         <v>1</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.69</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>9</v>
@@ -1750,7 +1750,7 @@
         <v>12</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>30</v>
@@ -1759,12 +1759,12 @@
         <v>1</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3.78</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>9</v>
@@ -1779,7 +1779,7 @@
         <v>12</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>31</v>
@@ -1788,12 +1788,12 @@
         <v>1</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.93</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>9</v>
@@ -1808,7 +1808,7 @@
         <v>12</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>32</v>
@@ -1817,12 +1817,12 @@
         <v>1</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>3.94</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>9</v>
@@ -1837,7 +1837,7 @@
         <v>12</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>33</v>
@@ -1846,12 +1846,12 @@
         <v>1</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3.94</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>9</v>
@@ -1866,7 +1866,7 @@
         <v>12</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>34</v>
@@ -1875,12 +1875,12 @@
         <v>1</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>4.08</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>9</v>
@@ -1895,7 +1895,7 @@
         <v>12</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>35</v>
@@ -1904,12 +1904,12 @@
         <v>1</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>6.14</v>
+        <v>7.64</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>9</v>
@@ -1924,7 +1924,7 @@
         <v>12</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>36</v>
@@ -1933,12 +1933,12 @@
         <v>0</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>6.79</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>9</v>
@@ -1953,7 +1953,7 @@
         <v>12</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>37</v>
@@ -1962,12 +1962,12 @@
         <v>1</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>6.85</v>
+        <v>9.45</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>9</v>
@@ -1982,21 +1982,21 @@
         <v>12</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>38</v>
       </c>
       <c r="H27" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>8.52</v>
+        <v>12.16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>9</v>
@@ -2011,21 +2011,21 @@
         <v>12</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>39</v>
       </c>
       <c r="H28" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>10.86</v>
+        <v>16.41</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>9</v>
@@ -2040,21 +2040,21 @@
         <v>12</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H29" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>14.75</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>9</v>
@@ -2069,7 +2069,7 @@
         <v>12</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>41</v>
@@ -2078,12 +2078,12 @@
         <v>0</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>15.41</v>
+        <v>18.15</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>9</v>
@@ -2098,7 +2098,7 @@
         <v>12</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>42</v>
@@ -2107,12 +2107,12 @@
         <v>0</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>15.86</v>
+        <v>18.15</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>43</v>
@@ -2136,12 +2136,12 @@
         <v>1</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>1.98</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>43</v>
@@ -2165,12 +2165,12 @@
         <v>1</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.21</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>43</v>
@@ -2194,12 +2194,12 @@
         <v>1</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>3.2</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>43</v>
@@ -2223,12 +2223,12 @@
         <v>1</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>3.25</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>43</v>
@@ -2252,12 +2252,12 @@
         <v>1</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>3.28</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>43</v>
@@ -2281,12 +2281,12 @@
         <v>1</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>3.77</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>43</v>
@@ -2310,12 +2310,12 @@
         <v>1</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>4.28</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>43</v>
@@ -2339,12 +2339,12 @@
         <v>1</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>4.28</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>43</v>
@@ -2368,12 +2368,12 @@
         <v>1</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>4.85</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>43</v>
@@ -2397,12 +2397,12 @@
         <v>1</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>5.64</v>
+        <v>8.03</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>43</v>
@@ -2423,15 +2423,15 @@
         <v>57</v>
       </c>
       <c r="H42" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>5.66</v>
+        <v>11.13</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>43</v>
@@ -2452,15 +2452,15 @@
         <v>58</v>
       </c>
       <c r="H43" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>10.99</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>43</v>
@@ -2481,15 +2481,15 @@
         <v>59</v>
       </c>
       <c r="H44" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>11.09</v>
+        <v>17.42</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>43</v>
@@ -2510,15 +2510,15 @@
         <v>60</v>
       </c>
       <c r="H45" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>12.62</v>
+        <v>18.97</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>43</v>
@@ -2542,12 +2542,12 @@
         <v>0</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>13.94</v>
+        <v>19.63</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>43</v>
@@ -2571,12 +2571,12 @@
         <v>1</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>2.19</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>43</v>
@@ -2600,12 +2600,12 @@
         <v>1</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>43</v>
@@ -2629,12 +2629,12 @@
         <v>1</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>3.13</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>43</v>
@@ -2658,12 +2658,12 @@
         <v>1</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>3.74</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>43</v>
@@ -2687,12 +2687,12 @@
         <v>1</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>4.6</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>43</v>
@@ -2716,12 +2716,12 @@
         <v>1</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>5.06</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>43</v>
@@ -2745,12 +2745,12 @@
         <v>1</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>5.06</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>43</v>
@@ -2774,12 +2774,12 @@
         <v>1</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>5.51</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>43</v>
@@ -2803,12 +2803,12 @@
         <v>1</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>6.49</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>43</v>
@@ -2832,12 +2832,12 @@
         <v>1</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>6.51</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>43</v>
@@ -2858,15 +2858,15 @@
         <v>72</v>
       </c>
       <c r="H57" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>9.82</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>43</v>
@@ -2890,12 +2890,12 @@
         <v>0</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>10.52</v>
+        <v>10.98</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>43</v>
@@ -2916,15 +2916,15 @@
         <v>74</v>
       </c>
       <c r="H59" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>11.01</v>
+        <v>13.24</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>43</v>
@@ -2945,15 +2945,15 @@
         <v>75</v>
       </c>
       <c r="H60" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>17.15</v>
+        <v>16.95</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>43</v>
@@ -2974,15 +2974,15 @@
         <v>76</v>
       </c>
       <c r="H61" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>17.49</v>
+        <v>18.88</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>77</v>
@@ -3006,12 +3006,12 @@
         <v>1</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>2.35</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>77</v>
@@ -3035,12 +3035,12 @@
         <v>1</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>77</v>
@@ -3064,12 +3064,12 @@
         <v>1</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>2.58</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>77</v>
@@ -3093,12 +3093,12 @@
         <v>1</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>4</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>77</v>
@@ -3122,12 +3122,12 @@
         <v>1</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>4.27</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>77</v>
@@ -3151,12 +3151,12 @@
         <v>1</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>4.99</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>77</v>
@@ -3180,12 +3180,12 @@
         <v>1</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>4.99</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>77</v>
@@ -3209,12 +3209,12 @@
         <v>1</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>5.03</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>77</v>
@@ -3238,12 +3238,12 @@
         <v>1</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>5.04</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>77</v>
@@ -3267,12 +3267,12 @@
         <v>1</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>6.25</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>77</v>
@@ -3293,15 +3293,15 @@
         <v>91</v>
       </c>
       <c r="H72" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>10.81</v>
+        <v>8.72</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>77</v>
@@ -3325,12 +3325,12 @@
         <v>1</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>14.29</v>
+        <v>9.16</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>77</v>
@@ -3354,12 +3354,12 @@
         <v>1</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>21.97</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>77</v>
@@ -3374,21 +3374,21 @@
         <v>80</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>94</v>
       </c>
       <c r="H75" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>23.97</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>77</v>
@@ -3412,12 +3412,12 @@
         <v>1</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>1.85</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>77</v>
@@ -3441,12 +3441,12 @@
         <v>1</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>77</v>
@@ -3470,12 +3470,12 @@
         <v>1</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>3.1</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>77</v>
@@ -3499,12 +3499,12 @@
         <v>1</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>3.43</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>77</v>
@@ -3528,12 +3528,12 @@
         <v>1</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>4.09</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>77</v>
@@ -3557,12 +3557,12 @@
         <v>1</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>4.88</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>77</v>
@@ -3586,12 +3586,12 @@
         <v>1</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>4.88</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>77</v>
@@ -3615,12 +3615,12 @@
         <v>1</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>4.89</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>77</v>
@@ -3644,12 +3644,12 @@
         <v>1</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>4.89</v>
+        <v>7.53</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>77</v>
@@ -3670,15 +3670,15 @@
         <v>104</v>
       </c>
       <c r="H85" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>8.63</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>77</v>
@@ -3702,12 +3702,12 @@
         <v>1</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>8.77</v>
+        <v>11.51</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>77</v>
@@ -3728,15 +3728,15 @@
         <v>106</v>
       </c>
       <c r="H87" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>11.05</v>
+        <v>12.36</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>77</v>
@@ -3760,12 +3760,12 @@
         <v>0</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>12.16</v>
+        <v>13.62</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>77</v>
@@ -3786,15 +3786,15 @@
         <v>108</v>
       </c>
       <c r="H89" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I89" s="4" t="n">
-        <v>13.34</v>
+        <v>14.35</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>77</v>
@@ -3815,15 +3815,15 @@
         <v>109</v>
       </c>
       <c r="H90" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>16.95</v>
+        <v>15</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>77</v>
@@ -3844,15 +3844,15 @@
         <v>110</v>
       </c>
       <c r="H91" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>19.03</v>
+        <v>16.38</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>111</v>
@@ -3876,12 +3876,12 @@
         <v>1</v>
       </c>
       <c r="I92" s="4" t="n">
-        <v>2.41</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>111</v>
@@ -3905,12 +3905,12 @@
         <v>1</v>
       </c>
       <c r="I93" s="4" t="n">
-        <v>3.07</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>111</v>
@@ -3934,12 +3934,12 @@
         <v>1</v>
       </c>
       <c r="I94" s="4" t="n">
-        <v>3.25</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>111</v>
@@ -3963,12 +3963,12 @@
         <v>1</v>
       </c>
       <c r="I95" s="4" t="n">
-        <v>3.31</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>111</v>
@@ -3992,12 +3992,12 @@
         <v>1</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>3.48</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>111</v>
@@ -4021,12 +4021,12 @@
         <v>1</v>
       </c>
       <c r="I97" s="4" t="n">
-        <v>3.61</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>111</v>
@@ -4050,12 +4050,12 @@
         <v>1</v>
       </c>
       <c r="I98" s="4" t="n">
-        <v>3.72</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>111</v>
@@ -4079,12 +4079,12 @@
         <v>1</v>
       </c>
       <c r="I99" s="4" t="n">
-        <v>4.25</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>111</v>
@@ -4108,12 +4108,12 @@
         <v>1</v>
       </c>
       <c r="I100" s="4" t="n">
-        <v>4.25</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>111</v>
@@ -4137,12 +4137,12 @@
         <v>1</v>
       </c>
       <c r="I101" s="4" t="n">
-        <v>7.15</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>111</v>
@@ -4166,12 +4166,12 @@
         <v>1</v>
       </c>
       <c r="I102" s="4" t="n">
-        <v>7.67</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>111</v>
@@ -4192,15 +4192,15 @@
         <v>126</v>
       </c>
       <c r="H103" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I103" s="4" t="n">
-        <v>7.94</v>
+        <v>10.83</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>111</v>
@@ -4221,15 +4221,15 @@
         <v>127</v>
       </c>
       <c r="H104" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I104" s="4" t="n">
-        <v>11.66</v>
+        <v>12.55</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>111</v>
@@ -4244,21 +4244,21 @@
         <v>114</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G105" s="3" t="s">
         <v>128</v>
       </c>
       <c r="H105" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I105" s="4" t="n">
-        <v>1.6</v>
+        <v>14.85</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>111</v>
@@ -4273,21 +4273,21 @@
         <v>114</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G106" s="3" t="s">
         <v>129</v>
       </c>
       <c r="H106" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I106" s="4" t="n">
-        <v>2.21</v>
+        <v>16.35</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>111</v>
@@ -4302,21 +4302,21 @@
         <v>114</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>130</v>
       </c>
       <c r="H107" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I107" s="4" t="n">
-        <v>2.43</v>
+        <v>17.41</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>111</v>
@@ -4331,21 +4331,21 @@
         <v>114</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>131</v>
       </c>
       <c r="H108" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I108" s="4" t="n">
-        <v>3.1</v>
+        <v>17.41</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>111</v>
@@ -4369,12 +4369,12 @@
         <v>1</v>
       </c>
       <c r="I109" s="4" t="n">
-        <v>3.53</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>111</v>
@@ -4398,12 +4398,12 @@
         <v>1</v>
       </c>
       <c r="I110" s="4" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>111</v>
@@ -4427,12 +4427,12 @@
         <v>1</v>
       </c>
       <c r="I111" s="4" t="n">
-        <v>4.04</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>111</v>
@@ -4456,12 +4456,12 @@
         <v>1</v>
       </c>
       <c r="I112" s="4" t="n">
-        <v>4.04</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>111</v>
@@ -4485,12 +4485,12 @@
         <v>1</v>
       </c>
       <c r="I113" s="4" t="n">
-        <v>6.37</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>111</v>
@@ -4514,12 +4514,12 @@
         <v>1</v>
       </c>
       <c r="I114" s="4" t="n">
-        <v>6.91</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B115" s="3" t="s">
         <v>111</v>
@@ -4543,12 +4543,12 @@
         <v>1</v>
       </c>
       <c r="I115" s="4" t="n">
-        <v>7.22</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>111</v>
@@ -4572,12 +4572,12 @@
         <v>1</v>
       </c>
       <c r="I116" s="4" t="n">
-        <v>9.74</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>111</v>
@@ -4598,15 +4598,15 @@
         <v>140</v>
       </c>
       <c r="H117" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I117" s="4" t="n">
-        <v>9.9</v>
+        <v>7.57</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>111</v>
@@ -4630,12 +4630,12 @@
         <v>1</v>
       </c>
       <c r="I118" s="4" t="n">
-        <v>10.48</v>
+        <v>7.57</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>111</v>
@@ -4656,15 +4656,15 @@
         <v>142</v>
       </c>
       <c r="H119" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I119" s="4" t="n">
-        <v>11.07</v>
+        <v>14.34</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>111</v>
@@ -4685,15 +4685,15 @@
         <v>143</v>
       </c>
       <c r="H120" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I120" s="4" t="n">
-        <v>12.24</v>
+        <v>14.51</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>111</v>
@@ -4717,12 +4717,12 @@
         <v>0</v>
       </c>
       <c r="I121" s="4" t="n">
-        <v>14</v>
+        <v>14.74</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>145</v>
@@ -4737,7 +4737,7 @@
         <v>148</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G122" s="3" t="s">
         <v>149</v>
@@ -4746,12 +4746,12 @@
         <v>1</v>
       </c>
       <c r="I122" s="4" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>145</v>
@@ -4766,7 +4766,7 @@
         <v>148</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G123" s="3" t="s">
         <v>150</v>
@@ -4775,12 +4775,12 @@
         <v>1</v>
       </c>
       <c r="I123" s="4" t="n">
-        <v>2.6</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>145</v>
@@ -4795,7 +4795,7 @@
         <v>148</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>151</v>
@@ -4804,12 +4804,12 @@
         <v>1</v>
       </c>
       <c r="I124" s="4" t="n">
-        <v>2.67</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>145</v>
@@ -4824,7 +4824,7 @@
         <v>148</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G125" s="3" t="s">
         <v>152</v>
@@ -4833,12 +4833,12 @@
         <v>1</v>
       </c>
       <c r="I125" s="4" t="n">
-        <v>2.91</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>145</v>
@@ -4853,7 +4853,7 @@
         <v>148</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G126" s="3" t="s">
         <v>153</v>
@@ -4862,12 +4862,12 @@
         <v>1</v>
       </c>
       <c r="I126" s="4" t="n">
-        <v>2.96</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>145</v>
@@ -4882,7 +4882,7 @@
         <v>148</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G127" s="3" t="s">
         <v>154</v>
@@ -4891,12 +4891,12 @@
         <v>1</v>
       </c>
       <c r="I127" s="4" t="n">
-        <v>4.6</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>145</v>
@@ -4911,7 +4911,7 @@
         <v>148</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G128" s="3" t="s">
         <v>155</v>
@@ -4920,12 +4920,12 @@
         <v>1</v>
       </c>
       <c r="I128" s="4" t="n">
-        <v>4.6</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>145</v>
@@ -4940,21 +4940,21 @@
         <v>148</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G129" s="3" t="s">
         <v>156</v>
       </c>
       <c r="H129" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I129" s="4" t="n">
-        <v>5.96</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>145</v>
@@ -4969,7 +4969,7 @@
         <v>148</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G130" s="3" t="s">
         <v>157</v>
@@ -4978,12 +4978,12 @@
         <v>1</v>
       </c>
       <c r="I130" s="4" t="n">
-        <v>6.23</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>145</v>
@@ -4998,7 +4998,7 @@
         <v>148</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G131" s="3" t="s">
         <v>158</v>
@@ -5007,12 +5007,12 @@
         <v>1</v>
       </c>
       <c r="I131" s="4" t="n">
-        <v>6.54</v>
+        <v>15.26</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>145</v>
@@ -5027,21 +5027,21 @@
         <v>148</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G132" s="3" t="s">
         <v>159</v>
       </c>
       <c r="H132" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I132" s="4" t="n">
-        <v>7.45</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>145</v>
@@ -5056,21 +5056,21 @@
         <v>148</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G133" s="3" t="s">
         <v>160</v>
       </c>
       <c r="H133" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I133" s="4" t="n">
-        <v>10.61</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>145</v>
@@ -5085,21 +5085,21 @@
         <v>148</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G134" s="3" t="s">
         <v>161</v>
       </c>
       <c r="H134" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I134" s="4" t="n">
-        <v>14.18</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>145</v>
@@ -5114,7 +5114,7 @@
         <v>148</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G135" s="3" t="s">
         <v>162</v>
@@ -5123,12 +5123,12 @@
         <v>1</v>
       </c>
       <c r="I135" s="4" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>145</v>
@@ -5143,7 +5143,7 @@
         <v>148</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G136" s="3" t="s">
         <v>163</v>
@@ -5152,12 +5152,12 @@
         <v>1</v>
       </c>
       <c r="I136" s="4" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>145</v>
@@ -5172,7 +5172,7 @@
         <v>148</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G137" s="3" t="s">
         <v>164</v>
@@ -5181,12 +5181,12 @@
         <v>1</v>
       </c>
       <c r="I137" s="4" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>145</v>
@@ -5201,7 +5201,7 @@
         <v>148</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G138" s="3" t="s">
         <v>165</v>
@@ -5210,12 +5210,12 @@
         <v>1</v>
       </c>
       <c r="I138" s="4" t="n">
-        <v>4.23</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>145</v>
@@ -5230,7 +5230,7 @@
         <v>148</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G139" s="3" t="s">
         <v>166</v>
@@ -5239,12 +5239,12 @@
         <v>1</v>
       </c>
       <c r="I139" s="4" t="n">
-        <v>4.23</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>145</v>
@@ -5259,7 +5259,7 @@
         <v>148</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G140" s="3" t="s">
         <v>167</v>
@@ -5268,12 +5268,12 @@
         <v>0</v>
       </c>
       <c r="I140" s="4" t="n">
-        <v>4.34</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>145</v>
@@ -5288,7 +5288,7 @@
         <v>148</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G141" s="3" t="s">
         <v>168</v>
@@ -5297,12 +5297,12 @@
         <v>1</v>
       </c>
       <c r="I141" s="4" t="n">
-        <v>4.51</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>145</v>
@@ -5317,7 +5317,7 @@
         <v>148</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G142" s="3" t="s">
         <v>169</v>
@@ -5326,12 +5326,12 @@
         <v>1</v>
       </c>
       <c r="I142" s="4" t="n">
-        <v>4.87</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>145</v>
@@ -5346,7 +5346,7 @@
         <v>148</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G143" s="3" t="s">
         <v>170</v>
@@ -5355,12 +5355,12 @@
         <v>1</v>
       </c>
       <c r="I143" s="4" t="n">
-        <v>4.87</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>145</v>
@@ -5375,7 +5375,7 @@
         <v>148</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G144" s="3" t="s">
         <v>171</v>
@@ -5384,12 +5384,12 @@
         <v>1</v>
       </c>
       <c r="I144" s="4" t="n">
-        <v>4.88</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>145</v>
@@ -5404,7 +5404,7 @@
         <v>148</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G145" s="3" t="s">
         <v>172</v>
@@ -5413,12 +5413,12 @@
         <v>1</v>
       </c>
       <c r="I145" s="4" t="n">
-        <v>7.12</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>145</v>
@@ -5433,7 +5433,7 @@
         <v>148</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G146" s="3" t="s">
         <v>173</v>
@@ -5442,12 +5442,12 @@
         <v>1</v>
       </c>
       <c r="I146" s="4" t="n">
-        <v>10.31</v>
+        <v>11.47</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>145</v>
@@ -5462,7 +5462,7 @@
         <v>148</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G147" s="3" t="s">
         <v>174</v>
@@ -5471,12 +5471,12 @@
         <v>0</v>
       </c>
       <c r="I147" s="4" t="n">
-        <v>10.62</v>
+        <v>12.16</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>145</v>
@@ -5491,7 +5491,7 @@
         <v>148</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G148" s="3" t="s">
         <v>175</v>
@@ -5500,12 +5500,12 @@
         <v>1</v>
       </c>
       <c r="I148" s="4" t="n">
-        <v>12.04</v>
+        <v>13.49</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>145</v>
@@ -5520,7 +5520,7 @@
         <v>148</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G149" s="3" t="s">
         <v>176</v>
@@ -5529,12 +5529,12 @@
         <v>0</v>
       </c>
       <c r="I149" s="4" t="n">
-        <v>14.09</v>
+        <v>15.59</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>145</v>
@@ -5549,7 +5549,7 @@
         <v>148</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>177</v>
@@ -5558,12 +5558,12 @@
         <v>1</v>
       </c>
       <c r="I150" s="4" t="n">
-        <v>20.37</v>
+        <v>22.91</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>145</v>
@@ -5578,7 +5578,7 @@
         <v>148</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G151" s="3" t="s">
         <v>178</v>
@@ -5587,12 +5587,12 @@
         <v>0</v>
       </c>
       <c r="I151" s="4" t="n">
-        <v>20.73</v>
+        <v>23.39</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>179</v>
@@ -5607,7 +5607,7 @@
         <v>182</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G152" s="3" t="s">
         <v>183</v>
@@ -5616,12 +5616,12 @@
         <v>1</v>
       </c>
       <c r="I152" s="4" t="n">
-        <v>2.07</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>179</v>
@@ -5636,7 +5636,7 @@
         <v>182</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G153" s="3" t="s">
         <v>184</v>
@@ -5645,12 +5645,12 @@
         <v>1</v>
       </c>
       <c r="I153" s="4" t="n">
-        <v>2.38</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>179</v>
@@ -5665,7 +5665,7 @@
         <v>182</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G154" s="3" t="s">
         <v>185</v>
@@ -5674,12 +5674,12 @@
         <v>1</v>
       </c>
       <c r="I154" s="4" t="n">
-        <v>3.04</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>179</v>
@@ -5694,7 +5694,7 @@
         <v>182</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G155" s="3" t="s">
         <v>186</v>
@@ -5703,12 +5703,12 @@
         <v>1</v>
       </c>
       <c r="I155" s="4" t="n">
-        <v>3.56</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>179</v>
@@ -5723,7 +5723,7 @@
         <v>182</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G156" s="3" t="s">
         <v>187</v>
@@ -5732,12 +5732,12 @@
         <v>1</v>
       </c>
       <c r="I156" s="4" t="n">
-        <v>3.9</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>179</v>
@@ -5752,7 +5752,7 @@
         <v>182</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G157" s="3" t="s">
         <v>188</v>
@@ -5761,12 +5761,12 @@
         <v>1</v>
       </c>
       <c r="I157" s="4" t="n">
-        <v>3.92</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>179</v>
@@ -5781,7 +5781,7 @@
         <v>182</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G158" s="3" t="s">
         <v>189</v>
@@ -5790,12 +5790,12 @@
         <v>1</v>
       </c>
       <c r="I158" s="4" t="n">
-        <v>3.92</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>179</v>
@@ -5810,7 +5810,7 @@
         <v>182</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G159" s="3" t="s">
         <v>190</v>
@@ -5819,12 +5819,12 @@
         <v>1</v>
       </c>
       <c r="I159" s="4" t="n">
-        <v>4.58</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>179</v>
@@ -5839,7 +5839,7 @@
         <v>182</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G160" s="3" t="s">
         <v>191</v>
@@ -5848,12 +5848,12 @@
         <v>1</v>
       </c>
       <c r="I160" s="4" t="n">
-        <v>7.57</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>179</v>
@@ -5868,7 +5868,7 @@
         <v>182</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G161" s="3" t="s">
         <v>192</v>
@@ -5877,12 +5877,12 @@
         <v>0</v>
       </c>
       <c r="I161" s="4" t="n">
-        <v>9.85</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>179</v>
@@ -5897,21 +5897,21 @@
         <v>182</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G162" s="3" t="s">
         <v>193</v>
       </c>
       <c r="H162" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I162" s="4" t="n">
-        <v>11.18</v>
+        <v>9.23</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>179</v>
@@ -5926,21 +5926,21 @@
         <v>182</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G163" s="3" t="s">
         <v>194</v>
       </c>
       <c r="H163" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I163" s="4" t="n">
-        <v>12</v>
+        <v>9.72</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>179</v>
@@ -5955,21 +5955,21 @@
         <v>182</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G164" s="3" t="s">
         <v>195</v>
       </c>
       <c r="H164" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I164" s="4" t="n">
-        <v>16.92</v>
+        <v>15.86</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>179</v>
@@ -5984,21 +5984,21 @@
         <v>182</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G165" s="3" t="s">
         <v>196</v>
       </c>
       <c r="H165" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I165" s="4" t="n">
-        <v>17.57</v>
+        <v>25.48</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>179</v>
@@ -6019,15 +6019,15 @@
         <v>197</v>
       </c>
       <c r="H166" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I166" s="4" t="n">
-        <v>18.34</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>179</v>
@@ -6042,7 +6042,7 @@
         <v>182</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G167" s="3" t="s">
         <v>198</v>
@@ -6051,12 +6051,12 @@
         <v>1</v>
       </c>
       <c r="I167" s="4" t="n">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>179</v>
@@ -6071,7 +6071,7 @@
         <v>182</v>
       </c>
       <c r="F168" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G168" s="3" t="s">
         <v>199</v>
@@ -6080,12 +6080,12 @@
         <v>1</v>
       </c>
       <c r="I168" s="4" t="n">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>179</v>
@@ -6100,7 +6100,7 @@
         <v>182</v>
       </c>
       <c r="F169" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G169" s="3" t="s">
         <v>200</v>
@@ -6109,12 +6109,12 @@
         <v>1</v>
       </c>
       <c r="I169" s="4" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>179</v>
@@ -6129,7 +6129,7 @@
         <v>182</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G170" s="3" t="s">
         <v>201</v>
@@ -6138,12 +6138,12 @@
         <v>1</v>
       </c>
       <c r="I170" s="4" t="n">
-        <v>3.22</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>179</v>
@@ -6158,7 +6158,7 @@
         <v>182</v>
       </c>
       <c r="F171" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G171" s="3" t="s">
         <v>202</v>
@@ -6167,12 +6167,12 @@
         <v>1</v>
       </c>
       <c r="I171" s="4" t="n">
-        <v>3.59</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>179</v>
@@ -6187,7 +6187,7 @@
         <v>182</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G172" s="3" t="s">
         <v>203</v>
@@ -6196,12 +6196,12 @@
         <v>1</v>
       </c>
       <c r="I172" s="4" t="n">
-        <v>4.05</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B173" s="3" t="s">
         <v>179</v>
@@ -6216,7 +6216,7 @@
         <v>182</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G173" s="3" t="s">
         <v>204</v>
@@ -6225,12 +6225,12 @@
         <v>1</v>
       </c>
       <c r="I173" s="4" t="n">
-        <v>4.05</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>179</v>
@@ -6245,7 +6245,7 @@
         <v>182</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G174" s="3" t="s">
         <v>205</v>
@@ -6254,12 +6254,12 @@
         <v>1</v>
       </c>
       <c r="I174" s="4" t="n">
-        <v>4.41</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B175" s="3" t="s">
         <v>179</v>
@@ -6274,7 +6274,7 @@
         <v>182</v>
       </c>
       <c r="F175" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G175" s="3" t="s">
         <v>206</v>
@@ -6283,12 +6283,12 @@
         <v>1</v>
       </c>
       <c r="I175" s="4" t="n">
-        <v>5.63</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>179</v>
@@ -6303,7 +6303,7 @@
         <v>182</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G176" s="3" t="s">
         <v>207</v>
@@ -6312,12 +6312,12 @@
         <v>1</v>
       </c>
       <c r="I176" s="4" t="n">
-        <v>7.53</v>
+        <v>9.23</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>179</v>
@@ -6332,21 +6332,21 @@
         <v>182</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G177" s="3" t="s">
         <v>208</v>
       </c>
       <c r="H177" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I177" s="4" t="n">
-        <v>10.47</v>
+        <v>13.69</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>179</v>
@@ -6361,21 +6361,21 @@
         <v>182</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G178" s="3" t="s">
         <v>209</v>
       </c>
       <c r="H178" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I178" s="4" t="n">
-        <v>10.76</v>
+        <v>13.82</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>179</v>
@@ -6390,7 +6390,7 @@
         <v>182</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G179" s="3" t="s">
         <v>210</v>
@@ -6399,12 +6399,12 @@
         <v>0</v>
       </c>
       <c r="I179" s="4" t="n">
-        <v>11.66</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>179</v>
@@ -6419,7 +6419,7 @@
         <v>182</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G180" s="3" t="s">
         <v>211</v>
@@ -6428,12 +6428,12 @@
         <v>0</v>
       </c>
       <c r="I180" s="4" t="n">
-        <v>14.93</v>
+        <v>21.88</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>179</v>
@@ -6448,21 +6448,21 @@
         <v>182</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G181" s="3" t="s">
         <v>212</v>
       </c>
       <c r="H181" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I181" s="4" t="n">
-        <v>16.87</v>
+        <v>24.67</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B182" s="3" t="s">
         <v>213</v>
@@ -6477,7 +6477,7 @@
         <v>216</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G182" s="3" t="s">
         <v>217</v>
@@ -6486,12 +6486,12 @@
         <v>1</v>
       </c>
       <c r="I182" s="4" t="n">
-        <v>2.01</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B183" s="3" t="s">
         <v>213</v>
@@ -6506,7 +6506,7 @@
         <v>216</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G183" s="3" t="s">
         <v>218</v>
@@ -6515,12 +6515,12 @@
         <v>1</v>
       </c>
       <c r="I183" s="4" t="n">
-        <v>2.94</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B184" s="3" t="s">
         <v>213</v>
@@ -6535,7 +6535,7 @@
         <v>216</v>
       </c>
       <c r="F184" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G184" s="3" t="s">
         <v>219</v>
@@ -6544,12 +6544,12 @@
         <v>1</v>
       </c>
       <c r="I184" s="4" t="n">
-        <v>3.26</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B185" s="3" t="s">
         <v>213</v>
@@ -6564,7 +6564,7 @@
         <v>216</v>
       </c>
       <c r="F185" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G185" s="3" t="s">
         <v>220</v>
@@ -6573,12 +6573,12 @@
         <v>1</v>
       </c>
       <c r="I185" s="4" t="n">
-        <v>3.34</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B186" s="3" t="s">
         <v>213</v>
@@ -6593,7 +6593,7 @@
         <v>216</v>
       </c>
       <c r="F186" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G186" s="3" t="s">
         <v>221</v>
@@ -6602,12 +6602,12 @@
         <v>1</v>
       </c>
       <c r="I186" s="4" t="n">
-        <v>3.49</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>213</v>
@@ -6622,7 +6622,7 @@
         <v>216</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G187" s="3" t="s">
         <v>222</v>
@@ -6631,12 +6631,12 @@
         <v>1</v>
       </c>
       <c r="I187" s="4" t="n">
-        <v>3.91</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B188" s="3" t="s">
         <v>213</v>
@@ -6651,7 +6651,7 @@
         <v>216</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G188" s="3" t="s">
         <v>223</v>
@@ -6660,12 +6660,12 @@
         <v>1</v>
       </c>
       <c r="I188" s="4" t="n">
-        <v>3.93</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B189" s="3" t="s">
         <v>213</v>
@@ -6680,7 +6680,7 @@
         <v>216</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G189" s="3" t="s">
         <v>224</v>
@@ -6689,12 +6689,12 @@
         <v>1</v>
       </c>
       <c r="I189" s="4" t="n">
-        <v>3.93</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B190" s="3" t="s">
         <v>213</v>
@@ -6709,7 +6709,7 @@
         <v>216</v>
       </c>
       <c r="F190" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>225</v>
@@ -6718,12 +6718,12 @@
         <v>1</v>
       </c>
       <c r="I190" s="4" t="n">
-        <v>7.24</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B191" s="3" t="s">
         <v>213</v>
@@ -6738,7 +6738,7 @@
         <v>216</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G191" s="3" t="s">
         <v>226</v>
@@ -6747,12 +6747,12 @@
         <v>1</v>
       </c>
       <c r="I191" s="4" t="n">
-        <v>7.62</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>213</v>
@@ -6767,7 +6767,7 @@
         <v>216</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G192" s="3" t="s">
         <v>227</v>
@@ -6776,12 +6776,12 @@
         <v>1</v>
       </c>
       <c r="I192" s="4" t="n">
-        <v>7.66</v>
+        <v>8.63</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B193" s="3" t="s">
         <v>213</v>
@@ -6796,7 +6796,7 @@
         <v>216</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>228</v>
@@ -6805,12 +6805,12 @@
         <v>0</v>
       </c>
       <c r="I193" s="4" t="n">
-        <v>8.39</v>
+        <v>9.8</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B194" s="3" t="s">
         <v>213</v>
@@ -6825,7 +6825,7 @@
         <v>216</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G194" s="3" t="s">
         <v>229</v>
@@ -6834,12 +6834,12 @@
         <v>1</v>
       </c>
       <c r="I194" s="4" t="n">
-        <v>8.7</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B195" s="3" t="s">
         <v>213</v>
@@ -6854,7 +6854,7 @@
         <v>216</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>230</v>
@@ -6863,12 +6863,12 @@
         <v>0</v>
       </c>
       <c r="I195" s="4" t="n">
-        <v>9.29</v>
+        <v>10.41</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>213</v>
@@ -6883,7 +6883,7 @@
         <v>216</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G196" s="3" t="s">
         <v>231</v>
@@ -6892,12 +6892,12 @@
         <v>0</v>
       </c>
       <c r="I196" s="4" t="n">
-        <v>18.4</v>
+        <v>21.11</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B197" s="3" t="s">
         <v>213</v>
@@ -6912,7 +6912,7 @@
         <v>216</v>
       </c>
       <c r="F197" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G197" s="3" t="s">
         <v>232</v>
@@ -6921,12 +6921,12 @@
         <v>0</v>
       </c>
       <c r="I197" s="4" t="n">
-        <v>18.69</v>
+        <v>21.69</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>213</v>
@@ -6941,7 +6941,7 @@
         <v>216</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G198" s="3" t="s">
         <v>233</v>
@@ -6950,12 +6950,12 @@
         <v>1</v>
       </c>
       <c r="I198" s="4" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>213</v>
@@ -6970,7 +6970,7 @@
         <v>216</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G199" s="3" t="s">
         <v>234</v>
@@ -6979,12 +6979,12 @@
         <v>1</v>
       </c>
       <c r="I199" s="4" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>213</v>
@@ -6999,7 +6999,7 @@
         <v>216</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G200" s="3" t="s">
         <v>235</v>
@@ -7008,12 +7008,12 @@
         <v>1</v>
       </c>
       <c r="I200" s="4" t="n">
-        <v>2.4</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>213</v>
@@ -7028,7 +7028,7 @@
         <v>216</v>
       </c>
       <c r="F201" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G201" s="3" t="s">
         <v>236</v>
@@ -7037,12 +7037,12 @@
         <v>1</v>
       </c>
       <c r="I201" s="4" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>213</v>
@@ -7057,7 +7057,7 @@
         <v>216</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G202" s="3" t="s">
         <v>237</v>
@@ -7066,12 +7066,12 @@
         <v>1</v>
       </c>
       <c r="I202" s="4" t="n">
-        <v>3.02</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B203" s="3" t="s">
         <v>213</v>
@@ -7086,7 +7086,7 @@
         <v>216</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G203" s="3" t="s">
         <v>238</v>
@@ -7095,12 +7095,12 @@
         <v>1</v>
       </c>
       <c r="I203" s="4" t="n">
-        <v>4.15</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>213</v>
@@ -7115,7 +7115,7 @@
         <v>216</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G204" s="3" t="s">
         <v>239</v>
@@ -7124,12 +7124,12 @@
         <v>1</v>
       </c>
       <c r="I204" s="4" t="n">
-        <v>4.42</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>213</v>
@@ -7144,21 +7144,21 @@
         <v>216</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G205" s="3" t="s">
         <v>240</v>
       </c>
       <c r="H205" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I205" s="4" t="n">
-        <v>4.42</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>213</v>
@@ -7173,7 +7173,7 @@
         <v>216</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G206" s="3" t="s">
         <v>241</v>
@@ -7182,12 +7182,12 @@
         <v>1</v>
       </c>
       <c r="I206" s="4" t="n">
-        <v>8.24</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>213</v>
@@ -7202,7 +7202,7 @@
         <v>216</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G207" s="3" t="s">
         <v>242</v>
@@ -7211,12 +7211,12 @@
         <v>1</v>
       </c>
       <c r="I207" s="4" t="n">
-        <v>15.12</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>213</v>
@@ -7231,7 +7231,7 @@
         <v>216</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G208" s="3" t="s">
         <v>243</v>
@@ -7240,12 +7240,12 @@
         <v>1</v>
       </c>
       <c r="I208" s="4" t="n">
-        <v>16.83</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>213</v>
@@ -7260,7 +7260,7 @@
         <v>216</v>
       </c>
       <c r="F209" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G209" s="3" t="s">
         <v>244</v>
@@ -7269,12 +7269,12 @@
         <v>0</v>
       </c>
       <c r="I209" s="4" t="n">
-        <v>18.04</v>
+        <v>10.73</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B210" s="3" t="s">
         <v>213</v>
@@ -7289,7 +7289,7 @@
         <v>216</v>
       </c>
       <c r="F210" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G210" s="3" t="s">
         <v>245</v>
@@ -7298,12 +7298,12 @@
         <v>1</v>
       </c>
       <c r="I210" s="4" t="n">
-        <v>20.36</v>
+        <v>23.01</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>213</v>
@@ -7318,7 +7318,7 @@
         <v>216</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G211" s="3" t="s">
         <v>246</v>
@@ -7327,12 +7327,12 @@
         <v>1</v>
       </c>
       <c r="I211" s="4" t="n">
-        <v>20.88</v>
+        <v>23.01</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B212" s="3" t="s">
         <v>247</v>
@@ -7347,7 +7347,7 @@
         <v>250</v>
       </c>
       <c r="F212" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G212" s="3" t="s">
         <v>251</v>
@@ -7356,12 +7356,12 @@
         <v>1</v>
       </c>
       <c r="I212" s="4" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B213" s="3" t="s">
         <v>247</v>
@@ -7376,7 +7376,7 @@
         <v>250</v>
       </c>
       <c r="F213" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G213" s="3" t="s">
         <v>252</v>
@@ -7385,12 +7385,12 @@
         <v>1</v>
       </c>
       <c r="I213" s="4" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B214" s="3" t="s">
         <v>247</v>
@@ -7405,7 +7405,7 @@
         <v>250</v>
       </c>
       <c r="F214" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G214" s="3" t="s">
         <v>253</v>
@@ -7414,12 +7414,12 @@
         <v>1</v>
       </c>
       <c r="I214" s="4" t="n">
-        <v>2.67</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B215" s="3" t="s">
         <v>247</v>
@@ -7434,7 +7434,7 @@
         <v>250</v>
       </c>
       <c r="F215" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G215" s="3" t="s">
         <v>254</v>
@@ -7443,12 +7443,12 @@
         <v>1</v>
       </c>
       <c r="I215" s="4" t="n">
-        <v>3.02</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B216" s="3" t="s">
         <v>247</v>
@@ -7463,7 +7463,7 @@
         <v>250</v>
       </c>
       <c r="F216" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G216" s="3" t="s">
         <v>255</v>
@@ -7477,7 +7477,7 @@
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B217" s="3" t="s">
         <v>247</v>
@@ -7492,7 +7492,7 @@
         <v>250</v>
       </c>
       <c r="F217" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G217" s="3" t="s">
         <v>256</v>
@@ -7501,12 +7501,12 @@
         <v>1</v>
       </c>
       <c r="I217" s="4" t="n">
-        <v>5.28</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B218" s="3" t="s">
         <v>247</v>
@@ -7521,7 +7521,7 @@
         <v>250</v>
       </c>
       <c r="F218" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G218" s="3" t="s">
         <v>257</v>
@@ -7530,12 +7530,12 @@
         <v>1</v>
       </c>
       <c r="I218" s="4" t="n">
-        <v>5.28</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B219" s="3" t="s">
         <v>247</v>
@@ -7550,7 +7550,7 @@
         <v>250</v>
       </c>
       <c r="F219" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G219" s="3" t="s">
         <v>258</v>
@@ -7559,12 +7559,12 @@
         <v>1</v>
       </c>
       <c r="I219" s="4" t="n">
-        <v>6.49</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B220" s="3" t="s">
         <v>247</v>
@@ -7579,7 +7579,7 @@
         <v>250</v>
       </c>
       <c r="F220" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G220" s="3" t="s">
         <v>259</v>
@@ -7588,12 +7588,12 @@
         <v>1</v>
       </c>
       <c r="I220" s="4" t="n">
-        <v>7.38</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B221" s="3" t="s">
         <v>247</v>
@@ -7608,7 +7608,7 @@
         <v>250</v>
       </c>
       <c r="F221" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G221" s="3" t="s">
         <v>260</v>
@@ -7617,12 +7617,12 @@
         <v>1</v>
       </c>
       <c r="I221" s="4" t="n">
-        <v>8.43</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B222" s="3" t="s">
         <v>247</v>
@@ -7637,7 +7637,7 @@
         <v>250</v>
       </c>
       <c r="F222" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G222" s="3" t="s">
         <v>261</v>
@@ -7646,12 +7646,12 @@
         <v>1</v>
       </c>
       <c r="I222" s="4" t="n">
-        <v>12.64</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B223" s="3" t="s">
         <v>247</v>
@@ -7666,7 +7666,7 @@
         <v>250</v>
       </c>
       <c r="F223" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G223" s="3" t="s">
         <v>262</v>
@@ -7675,12 +7675,12 @@
         <v>0</v>
       </c>
       <c r="I223" s="4" t="n">
-        <v>18.39</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B224" s="3" t="s">
         <v>247</v>
@@ -7695,21 +7695,21 @@
         <v>250</v>
       </c>
       <c r="F224" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G224" s="3" t="s">
         <v>263</v>
       </c>
       <c r="H224" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I224" s="4" t="n">
-        <v>18.76</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B225" s="3" t="s">
         <v>247</v>
@@ -7724,7 +7724,7 @@
         <v>250</v>
       </c>
       <c r="F225" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G225" s="3" t="s">
         <v>264</v>
@@ -7733,12 +7733,12 @@
         <v>1</v>
       </c>
       <c r="I225" s="4" t="n">
-        <v>19.27</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B226" s="3" t="s">
         <v>247</v>
@@ -7753,7 +7753,7 @@
         <v>250</v>
       </c>
       <c r="F226" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G226" s="3" t="s">
         <v>265</v>
@@ -7762,12 +7762,12 @@
         <v>0</v>
       </c>
       <c r="I226" s="4" t="n">
-        <v>19.56</v>
+        <v>16.07</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B227" s="3" t="s">
         <v>247</v>
@@ -7788,15 +7788,15 @@
         <v>266</v>
       </c>
       <c r="H227" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I227" s="4" t="n">
-        <v>1.86</v>
+        <v>19.63</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B228" s="3" t="s">
         <v>247</v>
@@ -7811,7 +7811,7 @@
         <v>250</v>
       </c>
       <c r="F228" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G228" s="3" t="s">
         <v>267</v>
@@ -7820,12 +7820,12 @@
         <v>1</v>
       </c>
       <c r="I228" s="4" t="n">
-        <v>1.95</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B229" s="3" t="s">
         <v>247</v>
@@ -7840,7 +7840,7 @@
         <v>250</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G229" s="3" t="s">
         <v>268</v>
@@ -7849,12 +7849,12 @@
         <v>1</v>
       </c>
       <c r="I229" s="4" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B230" s="3" t="s">
         <v>247</v>
@@ -7869,7 +7869,7 @@
         <v>250</v>
       </c>
       <c r="F230" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G230" s="3" t="s">
         <v>269</v>
@@ -7878,12 +7878,12 @@
         <v>1</v>
       </c>
       <c r="I230" s="4" t="n">
-        <v>2.98</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B231" s="3" t="s">
         <v>247</v>
@@ -7898,7 +7898,7 @@
         <v>250</v>
       </c>
       <c r="F231" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G231" s="3" t="s">
         <v>270</v>
@@ -7907,12 +7907,12 @@
         <v>1</v>
       </c>
       <c r="I231" s="4" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B232" s="3" t="s">
         <v>247</v>
@@ -7927,7 +7927,7 @@
         <v>250</v>
       </c>
       <c r="F232" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G232" s="3" t="s">
         <v>271</v>
@@ -7936,12 +7936,12 @@
         <v>1</v>
       </c>
       <c r="I232" s="4" t="n">
-        <v>3.79</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B233" s="3" t="s">
         <v>247</v>
@@ -7956,7 +7956,7 @@
         <v>250</v>
       </c>
       <c r="F233" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G233" s="3" t="s">
         <v>272</v>
@@ -7965,12 +7965,12 @@
         <v>1</v>
       </c>
       <c r="I233" s="4" t="n">
-        <v>3.79</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B234" s="3" t="s">
         <v>247</v>
@@ -7985,7 +7985,7 @@
         <v>250</v>
       </c>
       <c r="F234" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G234" s="3" t="s">
         <v>273</v>
@@ -7994,12 +7994,12 @@
         <v>1</v>
       </c>
       <c r="I234" s="4" t="n">
-        <v>3.98</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B235" s="3" t="s">
         <v>247</v>
@@ -8014,7 +8014,7 @@
         <v>250</v>
       </c>
       <c r="F235" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G235" s="3" t="s">
         <v>274</v>
@@ -8023,12 +8023,12 @@
         <v>1</v>
       </c>
       <c r="I235" s="4" t="n">
-        <v>5.36</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B236" s="3" t="s">
         <v>247</v>
@@ -8043,7 +8043,7 @@
         <v>250</v>
       </c>
       <c r="F236" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G236" s="3" t="s">
         <v>275</v>
@@ -8052,12 +8052,12 @@
         <v>1</v>
       </c>
       <c r="I236" s="4" t="n">
-        <v>6.02</v>
+        <v>8.56</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B237" s="3" t="s">
         <v>247</v>
@@ -8072,21 +8072,21 @@
         <v>250</v>
       </c>
       <c r="F237" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G237" s="3" t="s">
         <v>276</v>
       </c>
       <c r="H237" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I237" s="4" t="n">
-        <v>8</v>
+        <v>10.52</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B238" s="3" t="s">
         <v>247</v>
@@ -8101,21 +8101,21 @@
         <v>250</v>
       </c>
       <c r="F238" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G238" s="3" t="s">
         <v>277</v>
       </c>
       <c r="H238" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I238" s="4" t="n">
-        <v>11.74</v>
+        <v>15.85</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B239" s="3" t="s">
         <v>247</v>
@@ -8130,21 +8130,21 @@
         <v>250</v>
       </c>
       <c r="F239" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G239" s="3" t="s">
         <v>278</v>
       </c>
       <c r="H239" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I239" s="4" t="n">
-        <v>14.27</v>
+        <v>18.44</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B240" s="3" t="s">
         <v>247</v>
@@ -8159,21 +8159,21 @@
         <v>250</v>
       </c>
       <c r="F240" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G240" s="3" t="s">
         <v>279</v>
       </c>
       <c r="H240" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I240" s="4" t="n">
-        <v>14.75</v>
+        <v>19.28</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="B241" s="3" t="s">
         <v>247</v>
@@ -8188,16 +8188,16 @@
         <v>250</v>
       </c>
       <c r="F241" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G241" s="3" t="s">
         <v>280</v>
       </c>
       <c r="H241" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I241" s="4" t="n">
-        <v>18.97</v>
+        <v>21.15</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_anytime_tryscorers.xlsx
+++ b/files/NRL_anytime_tryscorers.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="247">
   <si>
     <t xml:space="preserve">Date Local</t>
   </si>
@@ -41,108 +41,6 @@
     <t xml:space="preserve">Anytimeodds</t>
   </si>
   <si>
-    <t xml:space="preserve">19:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched-2026-20260723-1950-parramatta-eels-penrith-panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penrith panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Addo-Carr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian Kelly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiah Iongi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Will Penisini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan Samrani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitchell Moses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitione Kautoga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luca Moretti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronald Volkman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tallyn Da Silva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack De Belin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joash Papalii</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Jenkins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian To'o</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaxen Edgar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casey McLean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paul Alamoti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiah Papali'i</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nathan Cleary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blaize Talagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freddy Lussick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lindsay Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Izack Tago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaah Yeo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Henry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moses Leota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scott Sorensen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Phillips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Cole</t>
-  </si>
-  <si>
     <t xml:space="preserve">18:00</t>
   </si>
   <si>
@@ -380,30 +278,30 @@
     <t xml:space="preserve">Zac Hosking</t>
   </si>
   <si>
+    <t xml:space="preserve">Ata Mariota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Sanders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Starling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corey Horsburgh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joseph Tapine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daine Laurie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Papalii</t>
+  </si>
+  <si>
     <t xml:space="preserve">Matty Nicholson</t>
   </si>
   <si>
-    <t xml:space="preserve">Ethan Sanders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Starling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corey Horsburgh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joseph Tapine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daine Laurie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Papalii</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coby Black</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sebastian Kris</t>
   </si>
   <si>
@@ -611,30 +509,30 @@
     <t xml:space="preserve">Murray Taulagi</t>
   </si>
   <si>
+    <t xml:space="preserve">Scott Drinkwater</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Chester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zac Laybutt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heilum Luki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremiah Nanai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Clifford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reed Mahoney</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jaxon Purdue</t>
   </si>
   <si>
-    <t xml:space="preserve">Scott Drinkwater</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Chester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Dearden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heilum Luki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremiah Nanai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Clifford</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reed Mahoney</t>
-  </si>
-  <si>
     <t xml:space="preserve">Reuben Cotter</t>
   </si>
   <si>
@@ -704,13 +602,13 @@
     <t xml:space="preserve">Chris Randall</t>
   </si>
   <si>
-    <t xml:space="preserve">Kurtis Morrin</t>
-  </si>
-  <si>
     <t xml:space="preserve">Klese Haas</t>
   </si>
   <si>
     <t xml:space="preserve">Sam Verrills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lachlan Ilias</t>
   </si>
   <si>
     <t xml:space="preserve">Tyrell Sloan</t>
@@ -1242,7 +1140,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>9</v>
@@ -1266,12 +1164,12 @@
         <v>1</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>2.92</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>9</v>
@@ -1295,12 +1193,12 @@
         <v>1</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>3.62</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>9</v>
@@ -1324,12 +1222,12 @@
         <v>1</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>4.49</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>9</v>
@@ -1353,12 +1251,12 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>4.92</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>9</v>
@@ -1382,12 +1280,12 @@
         <v>1</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>5.53</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>9</v>
@@ -1411,12 +1309,12 @@
         <v>1</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>5.78</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>9</v>
@@ -1440,12 +1338,12 @@
         <v>1</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>6.26</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>9</v>
@@ -1469,12 +1367,12 @@
         <v>1</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>6.26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>9</v>
@@ -1498,12 +1396,12 @@
         <v>1</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>6.94</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>9</v>
@@ -1527,12 +1425,12 @@
         <v>1</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>7.43</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>9</v>
@@ -1553,15 +1451,15 @@
         <v>23</v>
       </c>
       <c r="H12" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>15.64</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>9</v>
@@ -1582,15 +1480,15 @@
         <v>24</v>
       </c>
       <c r="H13" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>19.23</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>9</v>
@@ -1605,21 +1503,21 @@
         <v>12</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H14" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.81</v>
+        <v>17.13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>9</v>
@@ -1634,21 +1532,21 @@
         <v>12</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H15" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2.12</v>
+        <v>18.67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>9</v>
@@ -1663,21 +1561,21 @@
         <v>12</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>27</v>
       </c>
       <c r="H16" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.48</v>
+        <v>19.31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>9</v>
@@ -1701,12 +1599,12 @@
         <v>1</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.63</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>9</v>
@@ -1730,12 +1628,12 @@
         <v>1</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>4.18</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>9</v>
@@ -1759,12 +1657,12 @@
         <v>1</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>4.3</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>9</v>
@@ -1788,12 +1686,12 @@
         <v>1</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>4.3</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>9</v>
@@ -1817,12 +1715,12 @@
         <v>1</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>4.33</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>9</v>
@@ -1846,12 +1744,12 @@
         <v>1</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>4.54</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>9</v>
@@ -1875,12 +1773,12 @@
         <v>1</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>6.9</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>9</v>
@@ -1904,12 +1802,12 @@
         <v>1</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>7.64</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>9</v>
@@ -1930,15 +1828,15 @@
         <v>36</v>
       </c>
       <c r="H25" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>7.75</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>9</v>
@@ -1962,12 +1860,12 @@
         <v>1</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>9.45</v>
+        <v>8.37</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>9</v>
@@ -1988,15 +1886,15 @@
         <v>38</v>
       </c>
       <c r="H27" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>12.16</v>
+        <v>8.53</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>9</v>
@@ -2017,15 +1915,15 @@
         <v>39</v>
       </c>
       <c r="H28" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>16.41</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>9</v>
@@ -2049,12 +1947,12 @@
         <v>0</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>17.3</v>
+        <v>13.03</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>9</v>
@@ -2075,15 +1973,15 @@
         <v>41</v>
       </c>
       <c r="H30" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>18.15</v>
+        <v>16.68</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>9</v>
@@ -2104,10 +2002,10 @@
         <v>42</v>
       </c>
       <c r="H31" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>18.15</v>
+        <v>18.57</v>
       </c>
     </row>
     <row r="32">
@@ -2127,7 +2025,7 @@
         <v>46</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>47</v>
@@ -2136,7 +2034,7 @@
         <v>1</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2.37</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="33">
@@ -2156,7 +2054,7 @@
         <v>46</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>48</v>
@@ -2165,7 +2063,7 @@
         <v>1</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.54</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="34">
@@ -2185,7 +2083,7 @@
         <v>46</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>49</v>
@@ -2194,7 +2092,7 @@
         <v>1</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>2.79</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="35">
@@ -2214,7 +2112,7 @@
         <v>46</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>50</v>
@@ -2223,7 +2121,7 @@
         <v>1</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>3.09</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="36">
@@ -2243,7 +2141,7 @@
         <v>46</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>51</v>
@@ -2252,7 +2150,7 @@
         <v>1</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>4.11</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="37">
@@ -2272,7 +2170,7 @@
         <v>46</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>52</v>
@@ -2281,7 +2179,7 @@
         <v>1</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>5.55</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="38">
@@ -2301,7 +2199,7 @@
         <v>46</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>53</v>
@@ -2310,7 +2208,7 @@
         <v>1</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>5.55</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="39">
@@ -2330,7 +2228,7 @@
         <v>46</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>54</v>
@@ -2339,7 +2237,7 @@
         <v>1</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>6.1</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="40">
@@ -2359,7 +2257,7 @@
         <v>46</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>55</v>
@@ -2368,7 +2266,7 @@
         <v>1</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>7.39</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="41">
@@ -2388,7 +2286,7 @@
         <v>46</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>56</v>
@@ -2397,7 +2295,7 @@
         <v>1</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>8.03</v>
+        <v>7.02</v>
       </c>
     </row>
     <row r="42">
@@ -2417,7 +2315,7 @@
         <v>46</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>57</v>
@@ -2426,7 +2324,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>11.13</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="43">
@@ -2446,7 +2344,7 @@
         <v>46</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>58</v>
@@ -2455,7 +2353,7 @@
         <v>1</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>12.3</v>
+        <v>9.01</v>
       </c>
     </row>
     <row r="44">
@@ -2475,16 +2373,16 @@
         <v>46</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>59</v>
       </c>
       <c r="H44" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>17.42</v>
+        <v>10.77</v>
       </c>
     </row>
     <row r="45">
@@ -2510,10 +2408,10 @@
         <v>60</v>
       </c>
       <c r="H45" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>18.97</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="46">
@@ -2539,10 +2437,10 @@
         <v>61</v>
       </c>
       <c r="H46" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>19.63</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="47">
@@ -2562,7 +2460,7 @@
         <v>46</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>62</v>
@@ -2571,7 +2469,7 @@
         <v>1</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>1.85</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="48">
@@ -2591,7 +2489,7 @@
         <v>46</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>63</v>
@@ -2600,7 +2498,7 @@
         <v>1</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>2.15</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="49">
@@ -2620,7 +2518,7 @@
         <v>46</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>64</v>
@@ -2629,7 +2527,7 @@
         <v>1</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>2.82</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="50">
@@ -2649,7 +2547,7 @@
         <v>46</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>65</v>
@@ -2658,7 +2556,7 @@
         <v>1</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>3.41</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="51">
@@ -2678,7 +2576,7 @@
         <v>46</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>66</v>
@@ -2687,7 +2585,7 @@
         <v>1</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>3.89</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="52">
@@ -2707,7 +2605,7 @@
         <v>46</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>67</v>
@@ -2716,7 +2614,7 @@
         <v>1</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>4.79</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="53">
@@ -2736,7 +2634,7 @@
         <v>46</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>68</v>
@@ -2745,7 +2643,7 @@
         <v>1</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>4.79</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="54">
@@ -2765,7 +2663,7 @@
         <v>46</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>69</v>
@@ -2774,7 +2672,7 @@
         <v>1</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>4.81</v>
+        <v>7.42</v>
       </c>
     </row>
     <row r="55">
@@ -2794,16 +2692,16 @@
         <v>46</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>70</v>
       </c>
       <c r="H55" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>4.82</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="56">
@@ -2823,7 +2721,7 @@
         <v>46</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>71</v>
@@ -2832,7 +2730,7 @@
         <v>1</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>8.5</v>
+        <v>11.33</v>
       </c>
     </row>
     <row r="57">
@@ -2852,7 +2750,7 @@
         <v>46</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>72</v>
@@ -2861,7 +2759,7 @@
         <v>1</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>8.67</v>
+        <v>12.16</v>
       </c>
     </row>
     <row r="58">
@@ -2881,7 +2779,7 @@
         <v>46</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>73</v>
@@ -2890,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>10.98</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="59">
@@ -2910,16 +2808,16 @@
         <v>46</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>74</v>
       </c>
       <c r="H59" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>13.24</v>
+        <v>14.12</v>
       </c>
     </row>
     <row r="60">
@@ -2939,16 +2837,16 @@
         <v>46</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>75</v>
       </c>
       <c r="H60" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>16.95</v>
+        <v>14.76</v>
       </c>
     </row>
     <row r="61">
@@ -2968,21 +2866,21 @@
         <v>46</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>76</v>
       </c>
       <c r="H61" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>18.88</v>
+        <v>16.11</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>77</v>
@@ -2997,7 +2895,7 @@
         <v>80</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>81</v>
@@ -3006,12 +2904,12 @@
         <v>1</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>77</v>
@@ -3026,7 +2924,7 @@
         <v>80</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>82</v>
@@ -3035,12 +2933,12 @@
         <v>1</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>77</v>
@@ -3055,7 +2953,7 @@
         <v>80</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>83</v>
@@ -3064,12 +2962,12 @@
         <v>1</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>3.19</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>77</v>
@@ -3084,7 +2982,7 @@
         <v>80</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>84</v>
@@ -3093,12 +2991,12 @@
         <v>1</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>3.23</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>77</v>
@@ -3113,7 +3011,7 @@
         <v>80</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>85</v>
@@ -3122,12 +3020,12 @@
         <v>1</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>3.73</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>77</v>
@@ -3142,7 +3040,7 @@
         <v>80</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>86</v>
@@ -3151,12 +3049,12 @@
         <v>1</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>4.25</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>77</v>
@@ -3171,7 +3069,7 @@
         <v>80</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>87</v>
@@ -3180,12 +3078,12 @@
         <v>1</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>4.25</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>77</v>
@@ -3200,7 +3098,7 @@
         <v>80</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>88</v>
@@ -3209,12 +3107,12 @@
         <v>1</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>4.34</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>77</v>
@@ -3229,7 +3127,7 @@
         <v>80</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>89</v>
@@ -3238,12 +3136,12 @@
         <v>1</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>4.36</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>77</v>
@@ -3258,7 +3156,7 @@
         <v>80</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>90</v>
@@ -3267,12 +3165,12 @@
         <v>1</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>7.13</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>77</v>
@@ -3287,21 +3185,21 @@
         <v>80</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>91</v>
       </c>
       <c r="H72" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>8.72</v>
+        <v>8.28</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>77</v>
@@ -3316,7 +3214,7 @@
         <v>80</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>92</v>
@@ -3325,12 +3223,12 @@
         <v>1</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>9.16</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>77</v>
@@ -3345,21 +3243,21 @@
         <v>80</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>93</v>
       </c>
       <c r="H74" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>10.94</v>
+        <v>12.51</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>77</v>
@@ -3380,15 +3278,15 @@
         <v>94</v>
       </c>
       <c r="H75" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>1.77</v>
+        <v>14.81</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>77</v>
@@ -3409,15 +3307,15 @@
         <v>95</v>
       </c>
       <c r="H76" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>2.58</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>77</v>
@@ -3438,15 +3336,15 @@
         <v>96</v>
       </c>
       <c r="H77" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>3.5</v>
+        <v>17.35</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>77</v>
@@ -3467,15 +3365,15 @@
         <v>97</v>
       </c>
       <c r="H78" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>4.17</v>
+        <v>17.35</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>77</v>
@@ -3490,7 +3388,7 @@
         <v>80</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>98</v>
@@ -3499,12 +3397,12 @@
         <v>1</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>4.17</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>77</v>
@@ -3519,7 +3417,7 @@
         <v>80</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>99</v>
@@ -3528,12 +3426,12 @@
         <v>1</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>4.63</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>77</v>
@@ -3548,7 +3446,7 @@
         <v>80</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>100</v>
@@ -3557,12 +3455,12 @@
         <v>1</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>4.66</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>77</v>
@@ -3577,7 +3475,7 @@
         <v>80</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>101</v>
@@ -3586,12 +3484,12 @@
         <v>1</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>4.66</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>77</v>
@@ -3606,7 +3504,7 @@
         <v>80</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>102</v>
@@ -3615,12 +3513,12 @@
         <v>1</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>7.03</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>77</v>
@@ -3635,7 +3533,7 @@
         <v>80</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G84" s="3" t="s">
         <v>103</v>
@@ -3644,12 +3542,12 @@
         <v>1</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>7.53</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>77</v>
@@ -3664,21 +3562,21 @@
         <v>80</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G85" s="3" t="s">
         <v>104</v>
       </c>
       <c r="H85" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>10.49</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>77</v>
@@ -3693,7 +3591,7 @@
         <v>80</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>105</v>
@@ -3702,12 +3600,12 @@
         <v>1</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>11.51</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>77</v>
@@ -3722,7 +3620,7 @@
         <v>80</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>106</v>
@@ -3731,12 +3629,12 @@
         <v>1</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>12.36</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>77</v>
@@ -3751,21 +3649,21 @@
         <v>80</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G88" s="3" t="s">
         <v>107</v>
       </c>
       <c r="H88" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>13.62</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>77</v>
@@ -3780,7 +3678,7 @@
         <v>80</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>108</v>
@@ -3789,12 +3687,12 @@
         <v>1</v>
       </c>
       <c r="I89" s="4" t="n">
-        <v>14.35</v>
+        <v>13.44</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>77</v>
@@ -3809,21 +3707,21 @@
         <v>80</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>109</v>
       </c>
       <c r="H90" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>15</v>
+        <v>13.59</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>77</v>
@@ -3838,7 +3736,7 @@
         <v>80</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>110</v>
@@ -3847,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>16.38</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="92">
@@ -3876,7 +3774,7 @@
         <v>1</v>
       </c>
       <c r="I92" s="4" t="n">
-        <v>1.88</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="93">
@@ -3905,7 +3803,7 @@
         <v>1</v>
       </c>
       <c r="I93" s="4" t="n">
-        <v>2.23</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="94">
@@ -3934,7 +3832,7 @@
         <v>1</v>
       </c>
       <c r="I94" s="4" t="n">
-        <v>2.36</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="95">
@@ -3963,7 +3861,7 @@
         <v>1</v>
       </c>
       <c r="I95" s="4" t="n">
-        <v>2.56</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="96">
@@ -3992,7 +3890,7 @@
         <v>1</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>2.71</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="97">
@@ -4021,7 +3919,7 @@
         <v>1</v>
       </c>
       <c r="I97" s="4" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
@@ -4050,7 +3948,7 @@
         <v>1</v>
       </c>
       <c r="I98" s="4" t="n">
-        <v>3.14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99">
@@ -4079,7 +3977,7 @@
         <v>1</v>
       </c>
       <c r="I99" s="4" t="n">
-        <v>3.14</v>
+        <v>5.94</v>
       </c>
     </row>
     <row r="100">
@@ -4108,7 +4006,7 @@
         <v>1</v>
       </c>
       <c r="I100" s="4" t="n">
-        <v>5.68</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="101">
@@ -4137,7 +4035,7 @@
         <v>1</v>
       </c>
       <c r="I101" s="4" t="n">
-        <v>6.45</v>
+        <v>15.02</v>
       </c>
     </row>
     <row r="102">
@@ -4163,10 +4061,10 @@
         <v>125</v>
       </c>
       <c r="H102" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I102" s="4" t="n">
-        <v>8.3</v>
+        <v>15.65</v>
       </c>
     </row>
     <row r="103">
@@ -4195,7 +4093,7 @@
         <v>1</v>
       </c>
       <c r="I103" s="4" t="n">
-        <v>10.83</v>
+        <v>20.71</v>
       </c>
     </row>
     <row r="104">
@@ -4224,7 +4122,7 @@
         <v>0</v>
       </c>
       <c r="I104" s="4" t="n">
-        <v>12.55</v>
+        <v>22.92</v>
       </c>
     </row>
     <row r="105">
@@ -4244,16 +4142,16 @@
         <v>114</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G105" s="3" t="s">
         <v>128</v>
       </c>
       <c r="H105" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I105" s="4" t="n">
-        <v>14.85</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="106">
@@ -4273,16 +4171,16 @@
         <v>114</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G106" s="3" t="s">
         <v>129</v>
       </c>
       <c r="H106" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I106" s="4" t="n">
-        <v>16.35</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="107">
@@ -4302,16 +4200,16 @@
         <v>114</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>130</v>
       </c>
       <c r="H107" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I107" s="4" t="n">
-        <v>17.41</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="108">
@@ -4331,16 +4229,16 @@
         <v>114</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>131</v>
       </c>
       <c r="H108" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I108" s="4" t="n">
-        <v>17.41</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="109">
@@ -4369,7 +4267,7 @@
         <v>1</v>
       </c>
       <c r="I109" s="4" t="n">
-        <v>2.94</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="110">
@@ -4395,10 +4293,10 @@
         <v>133</v>
       </c>
       <c r="H110" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I110" s="4" t="n">
-        <v>3.55</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="111">
@@ -4427,7 +4325,7 @@
         <v>1</v>
       </c>
       <c r="I111" s="4" t="n">
-        <v>3.74</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="112">
@@ -4456,7 +4354,7 @@
         <v>1</v>
       </c>
       <c r="I112" s="4" t="n">
-        <v>4.29</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="113">
@@ -4485,7 +4383,7 @@
         <v>1</v>
       </c>
       <c r="I113" s="4" t="n">
-        <v>5.33</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="114">
@@ -4514,7 +4412,7 @@
         <v>1</v>
       </c>
       <c r="I114" s="4" t="n">
-        <v>5.33</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="115">
@@ -4543,7 +4441,7 @@
         <v>1</v>
       </c>
       <c r="I115" s="4" t="n">
-        <v>6.24</v>
+        <v>7.78</v>
       </c>
     </row>
     <row r="116">
@@ -4572,7 +4470,7 @@
         <v>1</v>
       </c>
       <c r="I116" s="4" t="n">
-        <v>7.41</v>
+        <v>11.28</v>
       </c>
     </row>
     <row r="117">
@@ -4598,10 +4496,10 @@
         <v>140</v>
       </c>
       <c r="H117" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I117" s="4" t="n">
-        <v>7.57</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="118">
@@ -4630,7 +4528,7 @@
         <v>1</v>
       </c>
       <c r="I118" s="4" t="n">
-        <v>7.57</v>
+        <v>13.27</v>
       </c>
     </row>
     <row r="119">
@@ -4656,10 +4554,10 @@
         <v>142</v>
       </c>
       <c r="H119" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I119" s="4" t="n">
-        <v>14.34</v>
+        <v>15.34</v>
       </c>
     </row>
     <row r="120">
@@ -4688,7 +4586,7 @@
         <v>1</v>
       </c>
       <c r="I120" s="4" t="n">
-        <v>14.51</v>
+        <v>22.54</v>
       </c>
     </row>
     <row r="121">
@@ -4717,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="I121" s="4" t="n">
-        <v>14.74</v>
+        <v>23.01</v>
       </c>
     </row>
     <row r="122">
@@ -4737,7 +4635,7 @@
         <v>148</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G122" s="3" t="s">
         <v>149</v>
@@ -4746,7 +4644,7 @@
         <v>1</v>
       </c>
       <c r="I122" s="4" t="n">
-        <v>2.52</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="123">
@@ -4766,7 +4664,7 @@
         <v>148</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G123" s="3" t="s">
         <v>150</v>
@@ -4775,7 +4673,7 @@
         <v>1</v>
       </c>
       <c r="I123" s="4" t="n">
-        <v>3.02</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="124">
@@ -4795,7 +4693,7 @@
         <v>148</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>151</v>
@@ -4804,7 +4702,7 @@
         <v>1</v>
       </c>
       <c r="I124" s="4" t="n">
-        <v>3.6</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="125">
@@ -4824,7 +4722,7 @@
         <v>148</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G125" s="3" t="s">
         <v>152</v>
@@ -4833,7 +4731,7 @@
         <v>1</v>
       </c>
       <c r="I125" s="4" t="n">
-        <v>4.64</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="126">
@@ -4853,7 +4751,7 @@
         <v>148</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G126" s="3" t="s">
         <v>153</v>
@@ -4862,7 +4760,7 @@
         <v>1</v>
       </c>
       <c r="I126" s="4" t="n">
-        <v>4.78</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="127">
@@ -4882,7 +4780,7 @@
         <v>148</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G127" s="3" t="s">
         <v>154</v>
@@ -4891,7 +4789,7 @@
         <v>1</v>
       </c>
       <c r="I127" s="4" t="n">
-        <v>5.07</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="128">
@@ -4911,7 +4809,7 @@
         <v>148</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G128" s="3" t="s">
         <v>155</v>
@@ -4920,7 +4818,7 @@
         <v>1</v>
       </c>
       <c r="I128" s="4" t="n">
-        <v>5.07</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="129">
@@ -4940,7 +4838,7 @@
         <v>148</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G129" s="3" t="s">
         <v>156</v>
@@ -4949,7 +4847,7 @@
         <v>1</v>
       </c>
       <c r="I129" s="4" t="n">
-        <v>6.03</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="130">
@@ -4969,7 +4867,7 @@
         <v>148</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G130" s="3" t="s">
         <v>157</v>
@@ -4978,7 +4876,7 @@
         <v>1</v>
       </c>
       <c r="I130" s="4" t="n">
-        <v>6.83</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="131">
@@ -4998,16 +4896,16 @@
         <v>148</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G131" s="3" t="s">
         <v>158</v>
       </c>
       <c r="H131" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I131" s="4" t="n">
-        <v>15.26</v>
+        <v>8.07</v>
       </c>
     </row>
     <row r="132">
@@ -5027,7 +4925,7 @@
         <v>148</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G132" s="3" t="s">
         <v>159</v>
@@ -5036,7 +4934,7 @@
         <v>0</v>
       </c>
       <c r="I132" s="4" t="n">
-        <v>15.91</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="133">
@@ -5056,7 +4954,7 @@
         <v>148</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G133" s="3" t="s">
         <v>160</v>
@@ -5065,7 +4963,7 @@
         <v>1</v>
       </c>
       <c r="I133" s="4" t="n">
-        <v>21.05</v>
+        <v>8.94</v>
       </c>
     </row>
     <row r="134">
@@ -5085,16 +4983,16 @@
         <v>148</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G134" s="3" t="s">
         <v>161</v>
       </c>
       <c r="H134" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I134" s="4" t="n">
-        <v>23.3</v>
+        <v>14.56</v>
       </c>
     </row>
     <row r="135">
@@ -5120,10 +5018,10 @@
         <v>162</v>
       </c>
       <c r="H135" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I135" s="4" t="n">
-        <v>1.8</v>
+        <v>23.37</v>
       </c>
     </row>
     <row r="136">
@@ -5143,7 +5041,7 @@
         <v>148</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G136" s="3" t="s">
         <v>163</v>
@@ -5152,7 +5050,7 @@
         <v>1</v>
       </c>
       <c r="I136" s="4" t="n">
-        <v>2.09</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="137">
@@ -5172,7 +5070,7 @@
         <v>148</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G137" s="3" t="s">
         <v>164</v>
@@ -5181,7 +5079,7 @@
         <v>1</v>
       </c>
       <c r="I137" s="4" t="n">
-        <v>3.9</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="138">
@@ -5201,7 +5099,7 @@
         <v>148</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G138" s="3" t="s">
         <v>165</v>
@@ -5210,7 +5108,7 @@
         <v>1</v>
       </c>
       <c r="I138" s="4" t="n">
-        <v>4.63</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="139">
@@ -5230,7 +5128,7 @@
         <v>148</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G139" s="3" t="s">
         <v>166</v>
@@ -5239,7 +5137,7 @@
         <v>1</v>
       </c>
       <c r="I139" s="4" t="n">
-        <v>4.63</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="140">
@@ -5259,16 +5157,16 @@
         <v>148</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G140" s="3" t="s">
         <v>167</v>
       </c>
       <c r="H140" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I140" s="4" t="n">
-        <v>4.91</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="141">
@@ -5288,7 +5186,7 @@
         <v>148</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G141" s="3" t="s">
         <v>168</v>
@@ -5297,7 +5195,7 @@
         <v>1</v>
       </c>
       <c r="I141" s="4" t="n">
-        <v>5.03</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="142">
@@ -5317,7 +5215,7 @@
         <v>148</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G142" s="3" t="s">
         <v>169</v>
@@ -5326,7 +5224,7 @@
         <v>1</v>
       </c>
       <c r="I142" s="4" t="n">
-        <v>5.2</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="143">
@@ -5346,7 +5244,7 @@
         <v>148</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G143" s="3" t="s">
         <v>170</v>
@@ -5355,7 +5253,7 @@
         <v>1</v>
       </c>
       <c r="I143" s="4" t="n">
-        <v>5.42</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="144">
@@ -5375,7 +5273,7 @@
         <v>148</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G144" s="3" t="s">
         <v>171</v>
@@ -5384,7 +5282,7 @@
         <v>1</v>
       </c>
       <c r="I144" s="4" t="n">
-        <v>5.45</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="145">
@@ -5404,7 +5302,7 @@
         <v>148</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G145" s="3" t="s">
         <v>172</v>
@@ -5413,7 +5311,7 @@
         <v>1</v>
       </c>
       <c r="I145" s="4" t="n">
-        <v>7.9</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="146">
@@ -5433,7 +5331,7 @@
         <v>148</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G146" s="3" t="s">
         <v>173</v>
@@ -5442,7 +5340,7 @@
         <v>1</v>
       </c>
       <c r="I146" s="4" t="n">
-        <v>11.47</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="147">
@@ -5462,7 +5360,7 @@
         <v>148</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G147" s="3" t="s">
         <v>174</v>
@@ -5471,7 +5369,7 @@
         <v>0</v>
       </c>
       <c r="I147" s="4" t="n">
-        <v>12.16</v>
+        <v>12.82</v>
       </c>
     </row>
     <row r="148">
@@ -5491,16 +5389,16 @@
         <v>148</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G148" s="3" t="s">
         <v>175</v>
       </c>
       <c r="H148" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I148" s="4" t="n">
-        <v>13.49</v>
+        <v>12.94</v>
       </c>
     </row>
     <row r="149">
@@ -5520,7 +5418,7 @@
         <v>148</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G149" s="3" t="s">
         <v>176</v>
@@ -5529,7 +5427,7 @@
         <v>0</v>
       </c>
       <c r="I149" s="4" t="n">
-        <v>15.59</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="150">
@@ -5549,16 +5447,16 @@
         <v>148</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>177</v>
       </c>
       <c r="H150" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I150" s="4" t="n">
-        <v>22.91</v>
+        <v>20.47</v>
       </c>
     </row>
     <row r="151">
@@ -5578,21 +5476,21 @@
         <v>148</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G151" s="3" t="s">
         <v>178</v>
       </c>
       <c r="H151" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I151" s="4" t="n">
-        <v>23.39</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>179</v>
@@ -5616,12 +5514,12 @@
         <v>1</v>
       </c>
       <c r="I152" s="4" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>179</v>
@@ -5645,12 +5543,12 @@
         <v>1</v>
       </c>
       <c r="I153" s="4" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>179</v>
@@ -5674,12 +5572,12 @@
         <v>1</v>
       </c>
       <c r="I154" s="4" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>179</v>
@@ -5703,12 +5601,12 @@
         <v>1</v>
       </c>
       <c r="I155" s="4" t="n">
-        <v>3.32</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>179</v>
@@ -5732,12 +5630,12 @@
         <v>1</v>
       </c>
       <c r="I156" s="4" t="n">
-        <v>3.37</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>179</v>
@@ -5761,12 +5659,12 @@
         <v>1</v>
       </c>
       <c r="I157" s="4" t="n">
-        <v>3.74</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>179</v>
@@ -5790,12 +5688,12 @@
         <v>1</v>
       </c>
       <c r="I158" s="4" t="n">
-        <v>5.26</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>179</v>
@@ -5819,12 +5717,12 @@
         <v>1</v>
       </c>
       <c r="I159" s="4" t="n">
-        <v>5.26</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>179</v>
@@ -5848,12 +5746,12 @@
         <v>1</v>
       </c>
       <c r="I160" s="4" t="n">
-        <v>6.78</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>179</v>
@@ -5874,15 +5772,15 @@
         <v>192</v>
       </c>
       <c r="H161" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I161" s="4" t="n">
-        <v>8.76</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>179</v>
@@ -5903,15 +5801,15 @@
         <v>193</v>
       </c>
       <c r="H162" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I162" s="4" t="n">
-        <v>9.23</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>179</v>
@@ -5932,15 +5830,15 @@
         <v>194</v>
       </c>
       <c r="H163" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I163" s="4" t="n">
-        <v>9.72</v>
+        <v>9.37</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>179</v>
@@ -5964,12 +5862,12 @@
         <v>1</v>
       </c>
       <c r="I164" s="4" t="n">
-        <v>15.86</v>
+        <v>9.57</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>179</v>
@@ -5993,12 +5891,12 @@
         <v>0</v>
       </c>
       <c r="I165" s="4" t="n">
-        <v>25.48</v>
+        <v>20.15</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>179</v>
@@ -6013,21 +5911,21 @@
         <v>182</v>
       </c>
       <c r="F166" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G166" s="3" t="s">
         <v>197</v>
       </c>
       <c r="H166" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I166" s="4" t="n">
-        <v>2.09</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>179</v>
@@ -6042,21 +5940,21 @@
         <v>182</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G167" s="3" t="s">
         <v>198</v>
       </c>
       <c r="H167" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I167" s="4" t="n">
-        <v>2.17</v>
+        <v>25.78</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>179</v>
@@ -6080,12 +5978,12 @@
         <v>1</v>
       </c>
       <c r="I168" s="4" t="n">
-        <v>2.49</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>179</v>
@@ -6109,12 +6007,12 @@
         <v>1</v>
       </c>
       <c r="I169" s="4" t="n">
-        <v>2.76</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>179</v>
@@ -6138,12 +6036,12 @@
         <v>1</v>
       </c>
       <c r="I170" s="4" t="n">
-        <v>3.43</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>179</v>
@@ -6167,12 +6065,12 @@
         <v>1</v>
       </c>
       <c r="I171" s="4" t="n">
-        <v>3.69</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>179</v>
@@ -6196,12 +6094,12 @@
         <v>1</v>
       </c>
       <c r="I172" s="4" t="n">
-        <v>4.29</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B173" s="3" t="s">
         <v>179</v>
@@ -6225,12 +6123,12 @@
         <v>1</v>
       </c>
       <c r="I173" s="4" t="n">
-        <v>4.29</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>179</v>
@@ -6254,12 +6152,12 @@
         <v>1</v>
       </c>
       <c r="I174" s="4" t="n">
-        <v>4.51</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B175" s="3" t="s">
         <v>179</v>
@@ -6280,15 +6178,15 @@
         <v>206</v>
       </c>
       <c r="H175" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I175" s="4" t="n">
-        <v>6.14</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>179</v>
@@ -6312,12 +6210,12 @@
         <v>1</v>
       </c>
       <c r="I176" s="4" t="n">
-        <v>9.23</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>179</v>
@@ -6338,15 +6236,15 @@
         <v>208</v>
       </c>
       <c r="H177" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I177" s="4" t="n">
-        <v>13.69</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>179</v>
@@ -6367,15 +6265,15 @@
         <v>209</v>
       </c>
       <c r="H178" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I178" s="4" t="n">
-        <v>13.82</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>179</v>
@@ -6399,12 +6297,12 @@
         <v>0</v>
       </c>
       <c r="I179" s="4" t="n">
-        <v>16.67</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>179</v>
@@ -6425,15 +6323,15 @@
         <v>211</v>
       </c>
       <c r="H180" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I180" s="4" t="n">
-        <v>21.88</v>
+        <v>22.09</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>179</v>
@@ -6457,7 +6355,7 @@
         <v>1</v>
       </c>
       <c r="I181" s="4" t="n">
-        <v>24.67</v>
+        <v>22.09</v>
       </c>
     </row>
     <row r="182">
@@ -6486,7 +6384,7 @@
         <v>1</v>
       </c>
       <c r="I182" s="4" t="n">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="183">
@@ -6515,7 +6413,7 @@
         <v>1</v>
       </c>
       <c r="I183" s="4" t="n">
-        <v>3.09</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="184">
@@ -6544,7 +6442,7 @@
         <v>1</v>
       </c>
       <c r="I184" s="4" t="n">
-        <v>3.39</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="185">
@@ -6573,7 +6471,7 @@
         <v>1</v>
       </c>
       <c r="I185" s="4" t="n">
-        <v>3.66</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="186">
@@ -6602,7 +6500,7 @@
         <v>1</v>
       </c>
       <c r="I186" s="4" t="n">
-        <v>3.94</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="187">
@@ -6631,7 +6529,7 @@
         <v>1</v>
       </c>
       <c r="I187" s="4" t="n">
-        <v>4.37</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="188">
@@ -6660,7 +6558,7 @@
         <v>1</v>
       </c>
       <c r="I188" s="4" t="n">
-        <v>4.37</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="189">
@@ -6689,7 +6587,7 @@
         <v>1</v>
       </c>
       <c r="I189" s="4" t="n">
-        <v>4.48</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="190">
@@ -6718,7 +6616,7 @@
         <v>1</v>
       </c>
       <c r="I190" s="4" t="n">
-        <v>5.38</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="191">
@@ -6747,7 +6645,7 @@
         <v>1</v>
       </c>
       <c r="I191" s="4" t="n">
-        <v>8.52</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="192">
@@ -6776,7 +6674,7 @@
         <v>1</v>
       </c>
       <c r="I192" s="4" t="n">
-        <v>8.63</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="193">
@@ -6805,7 +6703,7 @@
         <v>0</v>
       </c>
       <c r="I193" s="4" t="n">
-        <v>9.8</v>
+        <v>12.11</v>
       </c>
     </row>
     <row r="194">
@@ -6834,7 +6732,7 @@
         <v>1</v>
       </c>
       <c r="I194" s="4" t="n">
-        <v>10.02</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="195">
@@ -6860,10 +6758,10 @@
         <v>230</v>
       </c>
       <c r="H195" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I195" s="4" t="n">
-        <v>10.41</v>
+        <v>14.06</v>
       </c>
     </row>
     <row r="196">
@@ -6892,7 +6790,7 @@
         <v>0</v>
       </c>
       <c r="I196" s="4" t="n">
-        <v>21.11</v>
+        <v>15.81</v>
       </c>
     </row>
     <row r="197">
@@ -6921,7 +6819,7 @@
         <v>0</v>
       </c>
       <c r="I197" s="4" t="n">
-        <v>21.69</v>
+        <v>19.31</v>
       </c>
     </row>
     <row r="198">
@@ -6950,7 +6848,7 @@
         <v>1</v>
       </c>
       <c r="I198" s="4" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="199">
@@ -6979,7 +6877,7 @@
         <v>1</v>
       </c>
       <c r="I199" s="4" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="200">
@@ -7008,7 +6906,7 @@
         <v>1</v>
       </c>
       <c r="I200" s="4" t="n">
-        <v>2.72</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="201">
@@ -7037,7 +6935,7 @@
         <v>1</v>
       </c>
       <c r="I201" s="4" t="n">
-        <v>2.9</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="202">
@@ -7066,7 +6964,7 @@
         <v>1</v>
       </c>
       <c r="I202" s="4" t="n">
-        <v>2.91</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="203">
@@ -7095,7 +6993,7 @@
         <v>1</v>
       </c>
       <c r="I203" s="4" t="n">
-        <v>4.55</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="204">
@@ -7124,7 +7022,7 @@
         <v>1</v>
       </c>
       <c r="I204" s="4" t="n">
-        <v>4.55</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="205">
@@ -7150,10 +7048,10 @@
         <v>240</v>
       </c>
       <c r="H205" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I205" s="4" t="n">
-        <v>5.99</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="206">
@@ -7182,7 +7080,7 @@
         <v>1</v>
       </c>
       <c r="I206" s="4" t="n">
-        <v>6.21</v>
+        <v>8.43</v>
       </c>
     </row>
     <row r="207">
@@ -7208,10 +7106,10 @@
         <v>242</v>
       </c>
       <c r="H207" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I207" s="4" t="n">
-        <v>6.62</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="208">
@@ -7240,7 +7138,7 @@
         <v>1</v>
       </c>
       <c r="I208" s="4" t="n">
-        <v>7.41</v>
+        <v>15.59</v>
       </c>
     </row>
     <row r="209">
@@ -7266,10 +7164,10 @@
         <v>244</v>
       </c>
       <c r="H209" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I209" s="4" t="n">
-        <v>10.73</v>
+        <v>18.15</v>
       </c>
     </row>
     <row r="210">
@@ -7295,10 +7193,10 @@
         <v>245</v>
       </c>
       <c r="H210" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I210" s="4" t="n">
-        <v>23.01</v>
+        <v>18.96</v>
       </c>
     </row>
     <row r="211">
@@ -7327,877 +7225,7 @@
         <v>1</v>
       </c>
       <c r="I211" s="4" t="n">
-        <v>23.01</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B212" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C212" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D212" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E212" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F212" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G212" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="H212" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I212" s="4" t="n">
-        <v>2.15</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B213" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C213" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D213" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E213" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F213" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G213" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="H213" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I213" s="4" t="n">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B214" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C214" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D214" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E214" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F214" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G214" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="H214" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I214" s="4" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B215" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C215" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D215" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E215" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F215" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G215" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H215" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I215" s="4" t="n">
-        <v>3.62</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B216" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C216" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D216" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E216" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F216" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G216" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="H216" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I216" s="4" t="n">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B217" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C217" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D217" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E217" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F217" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G217" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H217" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I217" s="4" t="n">
-        <v>4.17</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B218" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C218" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D218" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E218" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F218" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G218" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="H218" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I218" s="4" t="n">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B219" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C219" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D219" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E219" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F219" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G219" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="H219" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I219" s="4" t="n">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B220" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C220" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D220" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E220" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F220" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G220" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="H220" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I220" s="4" t="n">
-        <v>5.39</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B221" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C221" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D221" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E221" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F221" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G221" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="H221" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I221" s="4" t="n">
-        <v>6.32</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B222" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C222" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D222" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E222" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F222" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G222" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="H222" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I222" s="4" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B223" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C223" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D223" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E223" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F223" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G223" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="H223" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I223" s="4" t="n">
-        <v>12.3</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B224" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C224" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D224" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E224" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F224" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G224" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="H224" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I224" s="4" t="n">
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B225" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C225" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D225" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E225" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F225" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G225" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="H225" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I225" s="4" t="n">
-        <v>14.29</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B226" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C226" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D226" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E226" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F226" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G226" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="H226" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I226" s="4" t="n">
-        <v>16.07</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B227" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C227" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D227" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E227" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F227" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G227" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="H227" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I227" s="4" t="n">
-        <v>19.63</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B228" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C228" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D228" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E228" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F228" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="G228" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="H228" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I228" s="4" t="n">
-        <v>2.41</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B229" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C229" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D229" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E229" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F229" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="G229" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="H229" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I229" s="4" t="n">
-        <v>2.48</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B230" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C230" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D230" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E230" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F230" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="G230" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="H230" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I230" s="4" t="n">
-        <v>2.89</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B231" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C231" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D231" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E231" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F231" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="G231" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="H231" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I231" s="4" t="n">
-        <v>3.05</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B232" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C232" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D232" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E232" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F232" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="G232" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="H232" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I232" s="4" t="n">
-        <v>4.51</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B233" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C233" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D233" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E233" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F233" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="G233" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="H233" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I233" s="4" t="n">
-        <v>4.51</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B234" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C234" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D234" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E234" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F234" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="G234" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="H234" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I234" s="4" t="n">
-        <v>4.54</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B235" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C235" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D235" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E235" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F235" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="G235" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="H235" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I235" s="4" t="n">
-        <v>4.54</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B236" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C236" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D236" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E236" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F236" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="G236" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="H236" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I236" s="4" t="n">
-        <v>8.56</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B237" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C237" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D237" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E237" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F237" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="G237" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="H237" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I237" s="4" t="n">
-        <v>10.52</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B238" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C238" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D238" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E238" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F238" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="G238" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="H238" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I238" s="4" t="n">
-        <v>15.85</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B239" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C239" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D239" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E239" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F239" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="G239" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="H239" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I239" s="4" t="n">
-        <v>18.44</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B240" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C240" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D240" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E240" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F240" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="G240" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="H240" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I240" s="4" t="n">
-        <v>19.28</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B241" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C241" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D241" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E241" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F241" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="G241" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="H241" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I241" s="4" t="n">
-        <v>21.15</v>
+        <v>20.8</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_anytime_tryscorers.xlsx
+++ b/files/NRL_anytime_tryscorers.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="281">
   <si>
     <t xml:space="preserve">Date Local</t>
   </si>
@@ -41,157 +41,673 @@
     <t xml:space="preserve">Anytimeodds</t>
   </si>
   <si>
+    <t xml:space="preserve">19:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260730-1950-north-queensland-cowboys-sydney-roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braidon Burns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murray Taulagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scott Drinkwater</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Chester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zac Laybutt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heilum Luki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremiah Nanai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Clifford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaxon Purdue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soni Luke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reuben Cotter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam McIntyre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Sutton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark Nawaqanitawase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tommy Talau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Tedesco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugo Savala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robert Toia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nat Butcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siua Wong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daly Cherry-Evans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reece Robson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Victor Radley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Watson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egan Butcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spencer Leniu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naufahu Whyte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reece Foley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benaiah Ioelu</t>
+  </si>
+  <si>
     <t xml:space="preserve">18:00</t>
   </si>
   <si>
-    <t xml:space="preserve">sched-2026-20260724-1800-newcastle-knights-sydney-roosters</t>
+    <t xml:space="preserve">sched-2026-20260731-1800-st-george-illawarra-dragons-dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george-illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamiso Tabuai-Fidow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selwyn Cobbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamayne Isaako</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herbie Farnworth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Bostock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connelly Lemuelu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kulikefu Finefeuiaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kodi Nikorima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brad Schneider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremy Marshall-King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ray Stone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Plath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Flegler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiya Katoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Donoghoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Felise Kaufusi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morgan Knowles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Gilbert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyrell Sloan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setu Tu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mathew Feagai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valentine Holmes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinton Gutherson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Egan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamish Stewart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Liddle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyle Flanagan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Atkinson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damien Cook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luciano Leilua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260731-2000-melbourne-storm-canterbury-bankstown-bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jethro Rinakama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Kiraz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matt Burton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Tracey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enari Tuala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viliame Kikau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Preston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lachlan Galvin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stephen Crichton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jonathan Sua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Mann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bailey Hayward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Curran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moses Leo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sualauvi Faalogo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jahrome Hughes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siulagi Tuimalatu-Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manaia Waitere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyran Wishart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Clarke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oryn Keeley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nick Meaney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trent Toelau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stefano Utoikamanu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe Chan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shawn Blore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trent Loiero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hayden Watson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angus Hinchey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260801-1500-gold-coast-titans-warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phillip Sami</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dean Ieremia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jojo Fifita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Campbell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keano Kini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AJ Brimson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arama Hau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beau Fermor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver Pascoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zane Harrison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tino Fa'asuamaleaui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Bai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chris Randall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurtis Morrin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alofiana Khan-Pereira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dallin Watene-Zelezniak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ali Leiataua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charnze Nicoll-Klokstad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Capewell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Laban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leka Halasima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Pompey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chanel Harris-Tavita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Te Maire Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wayde Egan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Fisher-Harris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Healey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erin Clark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Metcalf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rocco Berry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260801-1730-penrith-panthers-canberra-raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penrith panthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Savage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaeo Weekes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jed Stuart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simi Sasagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Timoko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Strange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zac Hosking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ata Mariota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owen Pattie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Sanders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe Roddy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corey Horsburgh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Jenkins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian To'o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaxen Edgar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casey McLean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paul Alamoti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiah Papali'i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathan Cleary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freddy Lussick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lindsay Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Izack Tago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaah Yeo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Cogger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Henry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moses Leota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scott Sorensen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Phillips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Cole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260801-1935-brisbane-broncos-newcastle-knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
   </si>
   <si>
     <t xml:space="preserve">newcastle knights</t>
   </si>
   <si>
-    <t xml:space="preserve">sydney roosters</t>
+    <t xml:space="preserve">Josiah Karapani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grant Anderson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reece Walsh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezra Mam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kotoni Staggs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Willison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Riki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deine Mariner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Reynolds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Walters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Talty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cory Paix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gehamat Shibasaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payne Haas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Va'a Semu</t>
   </si>
   <si>
     <t xml:space="preserve">Dominic Young</t>
   </si>
   <si>
+    <t xml:space="preserve">Greg Marzhew</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fletcher Sharpe</t>
   </si>
   <si>
-    <t xml:space="preserve">Greg Marzhew</t>
+    <t xml:space="preserve">Bradman Best</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kalyn Ponga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jermaine McEwen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francis Manuleleua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dane Gagai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trey Mooney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandon Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harrison Graham</t>
   </si>
   <si>
     <t xml:space="preserve">Fletcher Hunt</t>
   </si>
   <si>
-    <t xml:space="preserve">Bradman Best</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Lucas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Francis Manuleleua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trey Mooney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandon Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harrison Graham</t>
-  </si>
-  <si>
     <t xml:space="preserve">Phoenix Crossland</t>
   </si>
   <si>
     <t xml:space="preserve">Tyson Frizell</t>
   </si>
   <si>
-    <t xml:space="preserve">Elijah Salesa-Leaumoana</t>
-  </si>
-  <si>
     <t xml:space="preserve">Brodie Jones</t>
   </si>
   <si>
-    <t xml:space="preserve">Mark Nawaqanitawase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel Tupou</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Tedesco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robert Toia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nat Butcher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siua Wong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daly Cherry-Evans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reece Robson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Victor Radley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Watson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Egan Butcher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spencer Leniu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Naufahu Whyte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched-2026-20260724-2000-south-sydney-rabbitohs-melbourne-storm</t>
+    <t xml:space="preserve">14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260802-1400-cronulla-sutherland-sharks-south-sydney-rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
   </si>
   <si>
     <t xml:space="preserve">south sydney rabbitohs</t>
   </si>
   <si>
-    <t xml:space="preserve">melbourne storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moses Leo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sualauvi Faalogo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jahrome Hughes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siulagi Tuimalatu-Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyran Wishart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Clarke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oryn Keeley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nick Meaney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Howarth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trent Toelau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harry Grant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stefano Utoikamanu</t>
+    <t xml:space="preserve">Ronaldo Mulitalo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sione Katoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">William Kennedy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayal Iro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braydon Trindall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesse Ramien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Briton Nikora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teig Wilton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicholas Hynes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Addin Fonua-Blake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Hazelton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siosifa Talakai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blayke Brailey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron McInnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braden Hamlin-Uele</t>
   </si>
   <si>
     <t xml:space="preserve">Alex Johnston</t>
@@ -212,103 +728,91 @@
     <t xml:space="preserve">Latrell Siegwalt</t>
   </si>
   <si>
+    <t xml:space="preserve">Keaon Koloamatangi</t>
+  </si>
+  <si>
     <t xml:space="preserve">Euan Aitken</t>
   </si>
   <si>
+    <t xml:space="preserve">Ashton Ward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Sullivan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brandon Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tevita Tatola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jye Gray</t>
+  </si>
+  <si>
     <t xml:space="preserve">John Radel</t>
   </si>
   <si>
-    <t xml:space="preserve">Ashton Ward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keaon Koloamatangi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Sullivan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brandon Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tevita Tatola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jye Gray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bronson Garlick</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jamie Humphreys</t>
   </si>
   <si>
-    <t xml:space="preserve">Thomas Fletcher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched-2026-20260725-1500-canberra-raiders-wests-tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
+    <t xml:space="preserve">16:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260802-1605-wests-tigers-parramatta-eels</t>
   </si>
   <si>
     <t xml:space="preserve">wests tigers</t>
   </si>
   <si>
-    <t xml:space="preserve">Xavier Savage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaeo Weekes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jed Stuart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simi Sasagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Timoko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan Strange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zac Hosking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ata Mariota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan Sanders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Starling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corey Horsburgh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joseph Tapine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daine Laurie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Papalii</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matty Nicholson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sebastian Kris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vena Patuki-Case</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Faaletino Tavana</t>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Addo-Carr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian Kelly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiah Iongi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Penisini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Samrani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitchell Moses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kelma Tuilagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kitione Kautoga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronald Volkman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tallyn Da Silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack De Belin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Paulo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joash Papalii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Tuivaiti</t>
   </si>
   <si>
     <t xml:space="preserve">Sunia Turuva</t>
@@ -317,16 +821,19 @@
     <t xml:space="preserve">Jahream Bula</t>
   </si>
   <si>
+    <t xml:space="preserve">Adam Doueihi</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior Tupou</t>
   </si>
   <si>
     <t xml:space="preserve">Samuela Fainu</t>
   </si>
   <si>
-    <t xml:space="preserve">Ethan Roberts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Javon Andrews</t>
+    <t xml:space="preserve">Sione Fainu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heamasi Makasini</t>
   </si>
   <si>
     <t xml:space="preserve">Patrick Herbert</t>
@@ -344,415 +851,10 @@
     <t xml:space="preserve">Fonua Pole</t>
   </si>
   <si>
-    <t xml:space="preserve">Sione Fainu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched-2026-20260725-1730-canterbury-bankstown-bulldogs-warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jethro Rinakama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Kiraz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matt Burton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Tracey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enari Tuala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viliame Kikau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Preston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lachlan Galvin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stephen Crichton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bailey Hayward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Curran</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaeman Salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gordon Chan Kum Tong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alofiana Khan-Pereira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dallin Watene-Zelezniak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ali Leiataua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurt Capewell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Laban</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leka Halasima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taine Tuaupiki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Pompey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chanel Harris-Tavita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Te Maire Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wayde Egan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Fisher-Harris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Healey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erin Clark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Metcalf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitchell Barnett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demitric Vaimauga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched-2026-20260725-1935-north-queensland-cowboys-brisbane-broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deine Mariner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josiah Karapani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reece Walsh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ezra Mam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gehamat Shibasaki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kotoni Staggs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Willison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan Riki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Reynolds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Walters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben Talty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cory Paix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payne Haas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Gale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Braidon Burns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Murray Taulagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scott Drinkwater</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Chester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zac Laybutt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heilum Luki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremiah Nanai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Clifford</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reed Mahoney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaxon Purdue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reuben Cotter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam McIntyre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Griffin Neame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soni Luke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Sutton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Mikaele</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched-2026-20260726-1400-st-george-illawarra-dragons-gold-coast-titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george-illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phillip Sami</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dean Ieremia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jojo Fifita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Campbell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keano Kini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arama Hau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beau Fermor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaylan De Groot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oliver Pascoe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zane Harrison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tino Fa'asuamaleaui</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Bai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chris Randall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Klese Haas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Verrills</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lachlan Ilias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyrell Sloan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Setu Tu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mathew Feagai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valentine Holmes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clinton Gutherson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Egan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamish Stewart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Liddle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyle Flanagan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel Atkinson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Damien Cook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luciano Leilua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loko Jnr Pasifiki Tonga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan Couchman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched-2026-20260726-1605-manly-warringah-sea-eagles-cronulla-sutherland-sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manly-warringah sea eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronaldo Mulitalo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sione Katoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">William Kennedy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kayal Iro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Braydon Trindall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jesse Ramien</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Briton Nikora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teig Wilton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicholas Hynes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Addin Fonua-Blake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Hazelton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siosifa Talakai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blayke Brailey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameron McInnes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tuku Hau Tapuha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jesse Colquhoun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jason Saab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lehi Hopoate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tolutau Koula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reuben Garrick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joey Walsh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Feledy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haumole Olakau'atu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben Trbojevic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamal Fogarty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan Bullemor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Simpkin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simione Laiafi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aaron Schoupp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Trbojevic</t>
+    <t xml:space="preserve">Alex Seyfarth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bunty Afoa</t>
   </si>
 </sst>
 </file>
@@ -1100,9 +1202,9 @@
   <cols>
     <col min="1" max="1" width="9.285" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="9.285" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="67.595" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="25.5775" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="23.005" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="64.165" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="23.8625" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="25.5775" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="25.5775" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="21.29" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="6.7125" hidden="0" customWidth="1"/>
@@ -1140,7 +1242,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>9</v>
@@ -1164,12 +1266,12 @@
         <v>1</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>2.34</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>9</v>
@@ -1193,12 +1295,12 @@
         <v>1</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>2.51</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>9</v>
@@ -1222,12 +1324,12 @@
         <v>1</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>2.76</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>9</v>
@@ -1251,12 +1353,12 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>3.05</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>9</v>
@@ -1280,12 +1382,12 @@
         <v>1</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.05</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>9</v>
@@ -1309,12 +1411,12 @@
         <v>1</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>5.46</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>9</v>
@@ -1338,12 +1440,12 @@
         <v>1</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>5.46</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>9</v>
@@ -1367,12 +1469,12 @@
         <v>1</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>6</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>9</v>
@@ -1396,12 +1498,12 @@
         <v>1</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>7.27</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>9</v>
@@ -1425,12 +1527,12 @@
         <v>1</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>7.91</v>
+        <v>9.16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>9</v>
@@ -1451,15 +1553,15 @@
         <v>23</v>
       </c>
       <c r="H12" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>10.96</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>9</v>
@@ -1480,15 +1582,15 @@
         <v>24</v>
       </c>
       <c r="H13" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>12.1</v>
+        <v>14.57</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>9</v>
@@ -1512,12 +1614,12 @@
         <v>0</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>17.13</v>
+        <v>23.31</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>9</v>
@@ -1532,21 +1634,21 @@
         <v>12</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H15" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>18.67</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>9</v>
@@ -1561,21 +1663,21 @@
         <v>12</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>27</v>
       </c>
       <c r="H16" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>19.31</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>9</v>
@@ -1599,12 +1701,12 @@
         <v>1</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.83</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>9</v>
@@ -1628,12 +1730,12 @@
         <v>1</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.13</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>9</v>
@@ -1657,12 +1759,12 @@
         <v>1</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2.78</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>9</v>
@@ -1686,12 +1788,12 @@
         <v>1</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.37</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>9</v>
@@ -1715,12 +1817,12 @@
         <v>1</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>3.83</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>9</v>
@@ -1744,12 +1846,12 @@
         <v>1</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>4.72</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>9</v>
@@ -1773,12 +1875,12 @@
         <v>1</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>4.72</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>9</v>
@@ -1802,12 +1904,12 @@
         <v>1</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4.74</v>
+        <v>8.22</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>9</v>
@@ -1831,12 +1933,12 @@
         <v>1</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>4.75</v>
+        <v>8.38</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>9</v>
@@ -1857,15 +1959,15 @@
         <v>37</v>
       </c>
       <c r="H26" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>8.37</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>9</v>
@@ -1886,15 +1988,15 @@
         <v>38</v>
       </c>
       <c r="H27" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>8.53</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>9</v>
@@ -1915,15 +2017,15 @@
         <v>39</v>
       </c>
       <c r="H28" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>10.81</v>
+        <v>16.38</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>9</v>
@@ -1944,15 +2046,15 @@
         <v>40</v>
       </c>
       <c r="H29" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>13.03</v>
+        <v>18.24</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>9</v>
@@ -1973,15 +2075,15 @@
         <v>41</v>
       </c>
       <c r="H30" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>16.68</v>
+        <v>25.55</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>9</v>
@@ -2002,15 +2104,15 @@
         <v>42</v>
       </c>
       <c r="H31" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>18.57</v>
+        <v>25.55</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>43</v>
@@ -2034,12 +2136,12 @@
         <v>1</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>43</v>
@@ -2063,12 +2165,12 @@
         <v>1</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>43</v>
@@ -2092,12 +2194,12 @@
         <v>1</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>3.15</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>43</v>
@@ -2121,12 +2223,12 @@
         <v>1</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>3.18</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>43</v>
@@ -2150,12 +2252,12 @@
         <v>1</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>3.67</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>43</v>
@@ -2179,12 +2281,12 @@
         <v>1</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>4.18</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>43</v>
@@ -2208,12 +2310,12 @@
         <v>1</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>4.18</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>43</v>
@@ -2237,12 +2339,12 @@
         <v>1</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>4.28</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>43</v>
@@ -2266,12 +2368,12 @@
         <v>1</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>4.29</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>43</v>
@@ -2295,12 +2397,12 @@
         <v>1</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>7.02</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>43</v>
@@ -2324,12 +2426,12 @@
         <v>0</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>8.59</v>
+        <v>9.23</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>43</v>
@@ -2350,15 +2452,15 @@
         <v>58</v>
       </c>
       <c r="H43" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>9.01</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>43</v>
@@ -2382,12 +2484,12 @@
         <v>1</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>10.77</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>43</v>
@@ -2402,21 +2504,21 @@
         <v>46</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>60</v>
       </c>
       <c r="H45" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>1.75</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>43</v>
@@ -2431,21 +2533,21 @@
         <v>46</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>61</v>
       </c>
       <c r="H46" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>2.55</v>
+        <v>14.55</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>43</v>
@@ -2460,21 +2562,21 @@
         <v>46</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>62</v>
       </c>
       <c r="H47" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>3.45</v>
+        <v>15.18</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>43</v>
@@ -2489,7 +2591,7 @@
         <v>46</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>63</v>
@@ -2498,12 +2600,12 @@
         <v>1</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>4.11</v>
+        <v>15.46</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>43</v>
@@ -2518,21 +2620,21 @@
         <v>46</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>64</v>
       </c>
       <c r="H49" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>4.11</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>43</v>
@@ -2556,12 +2658,12 @@
         <v>1</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>4.56</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>43</v>
@@ -2585,12 +2687,12 @@
         <v>1</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>4.59</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>43</v>
@@ -2614,12 +2716,12 @@
         <v>1</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>4.59</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>43</v>
@@ -2643,12 +2745,12 @@
         <v>1</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>6.92</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>43</v>
@@ -2672,12 +2774,12 @@
         <v>1</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>7.42</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>43</v>
@@ -2698,15 +2800,15 @@
         <v>70</v>
       </c>
       <c r="H55" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>10.32</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>43</v>
@@ -2730,12 +2832,12 @@
         <v>1</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>11.33</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>43</v>
@@ -2756,15 +2858,15 @@
         <v>72</v>
       </c>
       <c r="H57" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>12.16</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>43</v>
@@ -2785,15 +2887,15 @@
         <v>73</v>
       </c>
       <c r="H58" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>13.4</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>43</v>
@@ -2817,12 +2919,12 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>14.12</v>
+        <v>7.82</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>43</v>
@@ -2843,15 +2945,15 @@
         <v>75</v>
       </c>
       <c r="H60" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>14.76</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>43</v>
@@ -2875,12 +2977,12 @@
         <v>0</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>16.11</v>
+        <v>12.72</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>77</v>
@@ -2895,7 +2997,7 @@
         <v>80</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>81</v>
@@ -2904,12 +3006,12 @@
         <v>1</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>1.88</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>77</v>
@@ -2924,7 +3026,7 @@
         <v>80</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>82</v>
@@ -2933,12 +3035,12 @@
         <v>1</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>2.22</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>77</v>
@@ -2953,7 +3055,7 @@
         <v>80</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>83</v>
@@ -2962,12 +3064,12 @@
         <v>1</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>2.35</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>77</v>
@@ -2982,7 +3084,7 @@
         <v>80</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>84</v>
@@ -2991,12 +3093,12 @@
         <v>1</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>2.56</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>77</v>
@@ -3011,7 +3113,7 @@
         <v>80</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>85</v>
@@ -3020,12 +3122,12 @@
         <v>1</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>2.71</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>77</v>
@@ -3040,7 +3142,7 @@
         <v>80</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>86</v>
@@ -3049,12 +3151,12 @@
         <v>1</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>2.79</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>77</v>
@@ -3069,7 +3171,7 @@
         <v>80</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>87</v>
@@ -3078,12 +3180,12 @@
         <v>1</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>3.13</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>77</v>
@@ -3098,7 +3200,7 @@
         <v>80</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>88</v>
@@ -3107,12 +3209,12 @@
         <v>1</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>3.13</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>77</v>
@@ -3127,7 +3229,7 @@
         <v>80</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>89</v>
@@ -3136,12 +3238,12 @@
         <v>1</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>5.67</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>77</v>
@@ -3156,21 +3258,21 @@
         <v>80</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>90</v>
       </c>
       <c r="H71" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>6.43</v>
+        <v>13.56</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>77</v>
@@ -3185,21 +3287,21 @@
         <v>80</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>91</v>
       </c>
       <c r="H72" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>8.28</v>
+        <v>13.96</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>77</v>
@@ -3214,7 +3316,7 @@
         <v>80</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>92</v>
@@ -3223,12 +3325,12 @@
         <v>1</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>10.8</v>
+        <v>16.36</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>77</v>
@@ -3243,7 +3345,7 @@
         <v>80</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>93</v>
@@ -3252,12 +3354,12 @@
         <v>0</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>12.51</v>
+        <v>17.05</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>77</v>
@@ -3278,15 +3380,15 @@
         <v>94</v>
       </c>
       <c r="H75" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>14.81</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>77</v>
@@ -3307,15 +3409,15 @@
         <v>95</v>
       </c>
       <c r="H76" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>15.25</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>77</v>
@@ -3336,15 +3438,15 @@
         <v>96</v>
       </c>
       <c r="H77" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>17.35</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>77</v>
@@ -3365,15 +3467,15 @@
         <v>97</v>
       </c>
       <c r="H78" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>17.35</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>77</v>
@@ -3388,7 +3490,7 @@
         <v>80</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>98</v>
@@ -3397,12 +3499,12 @@
         <v>1</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>2.78</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>77</v>
@@ -3417,7 +3519,7 @@
         <v>80</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>99</v>
@@ -3426,12 +3528,12 @@
         <v>1</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>77</v>
@@ -3446,7 +3548,7 @@
         <v>80</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>100</v>
@@ -3455,12 +3557,12 @@
         <v>1</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>3.53</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>77</v>
@@ -3475,7 +3577,7 @@
         <v>80</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>101</v>
@@ -3484,12 +3586,12 @@
         <v>1</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>4.05</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>77</v>
@@ -3504,7 +3606,7 @@
         <v>80</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>102</v>
@@ -3513,12 +3615,12 @@
         <v>1</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>5.02</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>77</v>
@@ -3533,7 +3635,7 @@
         <v>80</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G84" s="3" t="s">
         <v>103</v>
@@ -3542,12 +3644,12 @@
         <v>1</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>5.02</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>77</v>
@@ -3562,7 +3664,7 @@
         <v>80</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G85" s="3" t="s">
         <v>104</v>
@@ -3571,12 +3673,12 @@
         <v>1</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>5.87</v>
+        <v>9.22</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>77</v>
@@ -3591,7 +3693,7 @@
         <v>80</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>105</v>
@@ -3600,12 +3702,12 @@
         <v>1</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>6.96</v>
+        <v>11.02</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>77</v>
@@ -3620,21 +3722,21 @@
         <v>80</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>106</v>
       </c>
       <c r="H87" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>7.1</v>
+        <v>16.27</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>77</v>
@@ -3649,21 +3751,21 @@
         <v>80</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G88" s="3" t="s">
         <v>107</v>
       </c>
       <c r="H88" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>7.11</v>
+        <v>18.03</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>77</v>
@@ -3678,7 +3780,7 @@
         <v>80</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>108</v>
@@ -3687,12 +3789,12 @@
         <v>1</v>
       </c>
       <c r="I89" s="4" t="n">
-        <v>13.44</v>
+        <v>18.78</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>77</v>
@@ -3707,21 +3809,21 @@
         <v>80</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>109</v>
       </c>
       <c r="H90" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>13.59</v>
+        <v>20.27</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>77</v>
@@ -3736,7 +3838,7 @@
         <v>80</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>110</v>
@@ -3745,12 +3847,12 @@
         <v>0</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>13.8</v>
+        <v>20.27</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>111</v>
@@ -3779,7 +3881,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>111</v>
@@ -3803,12 +3905,12 @@
         <v>1</v>
       </c>
       <c r="I93" s="4" t="n">
-        <v>2.98</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>111</v>
@@ -3832,12 +3934,12 @@
         <v>1</v>
       </c>
       <c r="I94" s="4" t="n">
-        <v>3.55</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>111</v>
@@ -3861,12 +3963,12 @@
         <v>1</v>
       </c>
       <c r="I95" s="4" t="n">
-        <v>4.57</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>111</v>
@@ -3890,12 +3992,12 @@
         <v>1</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>4.71</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>111</v>
@@ -3919,12 +4021,12 @@
         <v>1</v>
       </c>
       <c r="I97" s="4" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>111</v>
@@ -3948,12 +4050,12 @@
         <v>1</v>
       </c>
       <c r="I98" s="4" t="n">
-        <v>5</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>111</v>
@@ -3977,12 +4079,12 @@
         <v>1</v>
       </c>
       <c r="I99" s="4" t="n">
-        <v>5.94</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>111</v>
@@ -4006,12 +4108,12 @@
         <v>1</v>
       </c>
       <c r="I100" s="4" t="n">
-        <v>6.73</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>111</v>
@@ -4035,12 +4137,12 @@
         <v>1</v>
       </c>
       <c r="I101" s="4" t="n">
-        <v>15.02</v>
+        <v>9.87</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>111</v>
@@ -4061,15 +4163,15 @@
         <v>125</v>
       </c>
       <c r="H102" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I102" s="4" t="n">
-        <v>15.65</v>
+        <v>10</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>111</v>
@@ -4090,15 +4192,15 @@
         <v>126</v>
       </c>
       <c r="H103" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I103" s="4" t="n">
-        <v>20.71</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>111</v>
@@ -4119,15 +4221,15 @@
         <v>127</v>
       </c>
       <c r="H104" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I104" s="4" t="n">
-        <v>22.92</v>
+        <v>11.62</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>111</v>
@@ -4142,21 +4244,21 @@
         <v>114</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G105" s="3" t="s">
         <v>128</v>
       </c>
       <c r="H105" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I105" s="4" t="n">
-        <v>1.78</v>
+        <v>12.09</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>111</v>
@@ -4180,12 +4282,12 @@
         <v>1</v>
       </c>
       <c r="I106" s="4" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>111</v>
@@ -4209,12 +4311,12 @@
         <v>1</v>
       </c>
       <c r="I107" s="4" t="n">
-        <v>3.85</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>111</v>
@@ -4238,12 +4340,12 @@
         <v>1</v>
       </c>
       <c r="I108" s="4" t="n">
-        <v>4.56</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>111</v>
@@ -4267,12 +4369,12 @@
         <v>1</v>
       </c>
       <c r="I109" s="4" t="n">
-        <v>4.56</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>111</v>
@@ -4293,15 +4395,15 @@
         <v>133</v>
       </c>
       <c r="H110" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I110" s="4" t="n">
-        <v>4.84</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>111</v>
@@ -4325,12 +4427,12 @@
         <v>1</v>
       </c>
       <c r="I111" s="4" t="n">
-        <v>4.96</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>111</v>
@@ -4351,15 +4453,15 @@
         <v>135</v>
       </c>
       <c r="H112" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I112" s="4" t="n">
-        <v>5.12</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>111</v>
@@ -4383,12 +4485,12 @@
         <v>1</v>
       </c>
       <c r="I113" s="4" t="n">
-        <v>5.34</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>111</v>
@@ -4412,12 +4514,12 @@
         <v>1</v>
       </c>
       <c r="I114" s="4" t="n">
-        <v>5.37</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B115" s="3" t="s">
         <v>111</v>
@@ -4441,12 +4543,12 @@
         <v>1</v>
       </c>
       <c r="I115" s="4" t="n">
-        <v>7.78</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>111</v>
@@ -4470,12 +4572,12 @@
         <v>1</v>
       </c>
       <c r="I116" s="4" t="n">
-        <v>11.28</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>111</v>
@@ -4496,15 +4598,15 @@
         <v>140</v>
       </c>
       <c r="H117" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I117" s="4" t="n">
-        <v>11.97</v>
+        <v>11.01</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>111</v>
@@ -4525,15 +4627,15 @@
         <v>141</v>
       </c>
       <c r="H118" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I118" s="4" t="n">
-        <v>13.27</v>
+        <v>11.68</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>111</v>
@@ -4554,15 +4656,15 @@
         <v>142</v>
       </c>
       <c r="H119" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I119" s="4" t="n">
-        <v>15.34</v>
+        <v>12.94</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>111</v>
@@ -4583,15 +4685,15 @@
         <v>143</v>
       </c>
       <c r="H120" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I120" s="4" t="n">
-        <v>22.54</v>
+        <v>14.96</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>111</v>
@@ -4615,12 +4717,12 @@
         <v>0</v>
       </c>
       <c r="I121" s="4" t="n">
-        <v>23.01</v>
+        <v>21.26</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>145</v>
@@ -4644,12 +4746,12 @@
         <v>1</v>
       </c>
       <c r="I122" s="4" t="n">
-        <v>2.16</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>145</v>
@@ -4673,12 +4775,12 @@
         <v>1</v>
       </c>
       <c r="I123" s="4" t="n">
-        <v>2.72</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>145</v>
@@ -4702,12 +4804,12 @@
         <v>1</v>
       </c>
       <c r="I124" s="4" t="n">
-        <v>3.01</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>145</v>
@@ -4731,12 +4833,12 @@
         <v>1</v>
       </c>
       <c r="I125" s="4" t="n">
-        <v>3.09</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>145</v>
@@ -4760,12 +4862,12 @@
         <v>1</v>
       </c>
       <c r="I126" s="4" t="n">
-        <v>3.13</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>145</v>
@@ -4789,12 +4891,12 @@
         <v>1</v>
       </c>
       <c r="I127" s="4" t="n">
-        <v>3.47</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>145</v>
@@ -4818,12 +4920,12 @@
         <v>1</v>
       </c>
       <c r="I128" s="4" t="n">
-        <v>4.86</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>145</v>
@@ -4847,12 +4949,12 @@
         <v>1</v>
       </c>
       <c r="I129" s="4" t="n">
-        <v>4.86</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>145</v>
@@ -4876,12 +4978,12 @@
         <v>1</v>
       </c>
       <c r="I130" s="4" t="n">
-        <v>6.26</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>145</v>
@@ -4902,15 +5004,15 @@
         <v>158</v>
       </c>
       <c r="H131" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I131" s="4" t="n">
-        <v>8.07</v>
+        <v>10.73</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>145</v>
@@ -4934,12 +5036,12 @@
         <v>0</v>
       </c>
       <c r="I132" s="4" t="n">
-        <v>8.5</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>145</v>
@@ -4963,12 +5065,12 @@
         <v>1</v>
       </c>
       <c r="I133" s="4" t="n">
-        <v>8.94</v>
+        <v>15.92</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>145</v>
@@ -4983,7 +5085,7 @@
         <v>148</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G134" s="3" t="s">
         <v>161</v>
@@ -4992,12 +5094,12 @@
         <v>1</v>
       </c>
       <c r="I134" s="4" t="n">
-        <v>14.56</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>145</v>
@@ -5012,21 +5114,21 @@
         <v>148</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G135" s="3" t="s">
         <v>162</v>
       </c>
       <c r="H135" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I135" s="4" t="n">
-        <v>23.37</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>145</v>
@@ -5050,12 +5152,12 @@
         <v>1</v>
       </c>
       <c r="I136" s="4" t="n">
-        <v>1.99</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>145</v>
@@ -5079,12 +5181,12 @@
         <v>1</v>
       </c>
       <c r="I137" s="4" t="n">
-        <v>2.07</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>145</v>
@@ -5108,12 +5210,12 @@
         <v>1</v>
       </c>
       <c r="I138" s="4" t="n">
-        <v>2.61</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>145</v>
@@ -5137,12 +5239,12 @@
         <v>1</v>
       </c>
       <c r="I139" s="4" t="n">
-        <v>3.24</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>145</v>
@@ -5166,12 +5268,12 @@
         <v>1</v>
       </c>
       <c r="I140" s="4" t="n">
-        <v>3.41</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>145</v>
@@ -5195,12 +5297,12 @@
         <v>1</v>
       </c>
       <c r="I141" s="4" t="n">
-        <v>4.04</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>145</v>
@@ -5224,12 +5326,12 @@
         <v>1</v>
       </c>
       <c r="I142" s="4" t="n">
-        <v>4.04</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>145</v>
@@ -5253,12 +5355,12 @@
         <v>1</v>
       </c>
       <c r="I143" s="4" t="n">
-        <v>4.25</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>145</v>
@@ -5279,15 +5381,15 @@
         <v>171</v>
       </c>
       <c r="H144" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I144" s="4" t="n">
-        <v>5.77</v>
+        <v>7.87</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>145</v>
@@ -5311,12 +5413,12 @@
         <v>1</v>
       </c>
       <c r="I145" s="4" t="n">
-        <v>6.71</v>
+        <v>9.59</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>145</v>
@@ -5340,12 +5442,12 @@
         <v>1</v>
       </c>
       <c r="I146" s="4" t="n">
-        <v>8.66</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>145</v>
@@ -5369,12 +5471,12 @@
         <v>0</v>
       </c>
       <c r="I147" s="4" t="n">
-        <v>12.82</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>145</v>
@@ -5395,15 +5497,15 @@
         <v>175</v>
       </c>
       <c r="H148" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I148" s="4" t="n">
-        <v>12.94</v>
+        <v>16.66</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>145</v>
@@ -5427,12 +5529,12 @@
         <v>0</v>
       </c>
       <c r="I149" s="4" t="n">
-        <v>15.6</v>
+        <v>17.57</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>145</v>
@@ -5456,12 +5558,12 @@
         <v>0</v>
       </c>
       <c r="I150" s="4" t="n">
-        <v>20.47</v>
+        <v>18.43</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>145</v>
@@ -5482,15 +5584,15 @@
         <v>178</v>
       </c>
       <c r="H151" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I151" s="4" t="n">
-        <v>23.08</v>
+        <v>18.43</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>179</v>
@@ -5505,7 +5607,7 @@
         <v>182</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G152" s="3" t="s">
         <v>183</v>
@@ -5514,12 +5616,12 @@
         <v>1</v>
       </c>
       <c r="I152" s="4" t="n">
-        <v>2.14</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>179</v>
@@ -5534,7 +5636,7 @@
         <v>182</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G153" s="3" t="s">
         <v>184</v>
@@ -5543,12 +5645,12 @@
         <v>1</v>
       </c>
       <c r="I153" s="4" t="n">
-        <v>2.98</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>179</v>
@@ -5563,7 +5665,7 @@
         <v>182</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G154" s="3" t="s">
         <v>185</v>
@@ -5572,12 +5674,12 @@
         <v>1</v>
       </c>
       <c r="I154" s="4" t="n">
-        <v>3.26</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>179</v>
@@ -5592,7 +5694,7 @@
         <v>182</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G155" s="3" t="s">
         <v>186</v>
@@ -5601,12 +5703,12 @@
         <v>1</v>
       </c>
       <c r="I155" s="4" t="n">
-        <v>3.52</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>179</v>
@@ -5621,7 +5723,7 @@
         <v>182</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G156" s="3" t="s">
         <v>187</v>
@@ -5630,12 +5732,12 @@
         <v>1</v>
       </c>
       <c r="I156" s="4" t="n">
-        <v>3.78</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>179</v>
@@ -5650,7 +5752,7 @@
         <v>182</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G157" s="3" t="s">
         <v>188</v>
@@ -5659,12 +5761,12 @@
         <v>1</v>
       </c>
       <c r="I157" s="4" t="n">
-        <v>4.19</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>179</v>
@@ -5679,7 +5781,7 @@
         <v>182</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G158" s="3" t="s">
         <v>189</v>
@@ -5688,12 +5790,12 @@
         <v>1</v>
       </c>
       <c r="I158" s="4" t="n">
-        <v>4.19</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>179</v>
@@ -5708,7 +5810,7 @@
         <v>182</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G159" s="3" t="s">
         <v>190</v>
@@ -5717,12 +5819,12 @@
         <v>1</v>
       </c>
       <c r="I159" s="4" t="n">
-        <v>4.29</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>179</v>
@@ -5737,7 +5839,7 @@
         <v>182</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G160" s="3" t="s">
         <v>191</v>
@@ -5746,12 +5848,12 @@
         <v>1</v>
       </c>
       <c r="I160" s="4" t="n">
-        <v>5.15</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>179</v>
@@ -5766,21 +5868,21 @@
         <v>182</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G161" s="3" t="s">
         <v>192</v>
       </c>
       <c r="H161" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I161" s="4" t="n">
-        <v>8.15</v>
+        <v>7.01</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>179</v>
@@ -5795,21 +5897,21 @@
         <v>182</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G162" s="3" t="s">
         <v>193</v>
       </c>
       <c r="H162" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I162" s="4" t="n">
-        <v>8.25</v>
+        <v>7.38</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>179</v>
@@ -5824,21 +5926,21 @@
         <v>182</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G163" s="3" t="s">
         <v>194</v>
       </c>
       <c r="H163" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I163" s="4" t="n">
-        <v>9.37</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>179</v>
@@ -5853,21 +5955,21 @@
         <v>182</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G164" s="3" t="s">
         <v>195</v>
       </c>
       <c r="H164" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I164" s="4" t="n">
-        <v>9.57</v>
+        <v>9.22</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>179</v>
@@ -5882,21 +5984,21 @@
         <v>182</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G165" s="3" t="s">
         <v>196</v>
       </c>
       <c r="H165" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I165" s="4" t="n">
-        <v>20.15</v>
+        <v>12.59</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>179</v>
@@ -5911,21 +6013,21 @@
         <v>182</v>
       </c>
       <c r="F166" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G166" s="3" t="s">
         <v>197</v>
       </c>
       <c r="H166" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I166" s="4" t="n">
-        <v>20.7</v>
+        <v>14.04</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>179</v>
@@ -5946,15 +6048,15 @@
         <v>198</v>
       </c>
       <c r="H167" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I167" s="4" t="n">
-        <v>25.78</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>179</v>
@@ -5969,7 +6071,7 @@
         <v>182</v>
       </c>
       <c r="F168" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G168" s="3" t="s">
         <v>199</v>
@@ -5978,12 +6080,12 @@
         <v>1</v>
       </c>
       <c r="I168" s="4" t="n">
-        <v>2.42</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>179</v>
@@ -5998,7 +6100,7 @@
         <v>182</v>
       </c>
       <c r="F169" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G169" s="3" t="s">
         <v>200</v>
@@ -6007,12 +6109,12 @@
         <v>1</v>
       </c>
       <c r="I169" s="4" t="n">
-        <v>2.56</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>179</v>
@@ -6027,7 +6129,7 @@
         <v>182</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G170" s="3" t="s">
         <v>201</v>
@@ -6036,12 +6138,12 @@
         <v>1</v>
       </c>
       <c r="I170" s="4" t="n">
-        <v>2.63</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>179</v>
@@ -6056,7 +6158,7 @@
         <v>182</v>
       </c>
       <c r="F171" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G171" s="3" t="s">
         <v>202</v>
@@ -6065,12 +6167,12 @@
         <v>1</v>
       </c>
       <c r="I171" s="4" t="n">
-        <v>2.81</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>179</v>
@@ -6085,7 +6187,7 @@
         <v>182</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G172" s="3" t="s">
         <v>203</v>
@@ -6094,12 +6196,12 @@
         <v>1</v>
       </c>
       <c r="I172" s="4" t="n">
-        <v>2.82</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B173" s="3" t="s">
         <v>179</v>
@@ -6114,7 +6216,7 @@
         <v>182</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G173" s="3" t="s">
         <v>204</v>
@@ -6123,12 +6225,12 @@
         <v>1</v>
       </c>
       <c r="I173" s="4" t="n">
-        <v>4.39</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>179</v>
@@ -6143,7 +6245,7 @@
         <v>182</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G174" s="3" t="s">
         <v>205</v>
@@ -6152,12 +6254,12 @@
         <v>1</v>
       </c>
       <c r="I174" s="4" t="n">
-        <v>4.39</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B175" s="3" t="s">
         <v>179</v>
@@ -6172,21 +6274,21 @@
         <v>182</v>
       </c>
       <c r="F175" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G175" s="3" t="s">
         <v>206</v>
       </c>
       <c r="H175" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I175" s="4" t="n">
-        <v>5.77</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>179</v>
@@ -6201,7 +6303,7 @@
         <v>182</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G176" s="3" t="s">
         <v>207</v>
@@ -6210,12 +6312,12 @@
         <v>1</v>
       </c>
       <c r="I176" s="4" t="n">
-        <v>5.98</v>
+        <v>7.54</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>179</v>
@@ -6230,21 +6332,21 @@
         <v>182</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G177" s="3" t="s">
         <v>208</v>
       </c>
       <c r="H177" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I177" s="4" t="n">
-        <v>6.38</v>
+        <v>10.44</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>179</v>
@@ -6259,21 +6361,21 @@
         <v>182</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G178" s="3" t="s">
         <v>209</v>
       </c>
       <c r="H178" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I178" s="4" t="n">
-        <v>7.13</v>
+        <v>11.38</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>179</v>
@@ -6288,21 +6390,21 @@
         <v>182</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G179" s="3" t="s">
         <v>210</v>
       </c>
       <c r="H179" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I179" s="4" t="n">
-        <v>10.31</v>
+        <v>11.53</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>179</v>
@@ -6317,21 +6419,21 @@
         <v>182</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G180" s="3" t="s">
         <v>211</v>
       </c>
       <c r="H180" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I180" s="4" t="n">
-        <v>22.09</v>
+        <v>16.31</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>179</v>
@@ -6346,21 +6448,21 @@
         <v>182</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G181" s="3" t="s">
         <v>212</v>
       </c>
       <c r="H181" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I181" s="4" t="n">
-        <v>22.09</v>
+        <v>18.38</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B182" s="3" t="s">
         <v>213</v>
@@ -6375,7 +6477,7 @@
         <v>216</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G182" s="3" t="s">
         <v>217</v>
@@ -6384,12 +6486,12 @@
         <v>1</v>
       </c>
       <c r="I182" s="4" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B183" s="3" t="s">
         <v>213</v>
@@ -6404,7 +6506,7 @@
         <v>216</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G183" s="3" t="s">
         <v>218</v>
@@ -6413,12 +6515,12 @@
         <v>1</v>
       </c>
       <c r="I183" s="4" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B184" s="3" t="s">
         <v>213</v>
@@ -6433,7 +6535,7 @@
         <v>216</v>
       </c>
       <c r="F184" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G184" s="3" t="s">
         <v>219</v>
@@ -6442,12 +6544,12 @@
         <v>1</v>
       </c>
       <c r="I184" s="4" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B185" s="3" t="s">
         <v>213</v>
@@ -6462,7 +6564,7 @@
         <v>216</v>
       </c>
       <c r="F185" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G185" s="3" t="s">
         <v>220</v>
@@ -6471,12 +6573,12 @@
         <v>1</v>
       </c>
       <c r="I185" s="4" t="n">
-        <v>3.57</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B186" s="3" t="s">
         <v>213</v>
@@ -6491,7 +6593,7 @@
         <v>216</v>
       </c>
       <c r="F186" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G186" s="3" t="s">
         <v>221</v>
@@ -6500,12 +6602,12 @@
         <v>1</v>
       </c>
       <c r="I186" s="4" t="n">
-        <v>3.58</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>213</v>
@@ -6520,7 +6622,7 @@
         <v>216</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G187" s="3" t="s">
         <v>222</v>
@@ -6529,12 +6631,12 @@
         <v>1</v>
       </c>
       <c r="I187" s="4" t="n">
-        <v>4.11</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B188" s="3" t="s">
         <v>213</v>
@@ -6549,7 +6651,7 @@
         <v>216</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G188" s="3" t="s">
         <v>223</v>
@@ -6558,12 +6660,12 @@
         <v>1</v>
       </c>
       <c r="I188" s="4" t="n">
-        <v>4.68</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B189" s="3" t="s">
         <v>213</v>
@@ -6578,7 +6680,7 @@
         <v>216</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G189" s="3" t="s">
         <v>224</v>
@@ -6587,12 +6689,12 @@
         <v>1</v>
       </c>
       <c r="I189" s="4" t="n">
-        <v>4.68</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B190" s="3" t="s">
         <v>213</v>
@@ -6607,7 +6709,7 @@
         <v>216</v>
       </c>
       <c r="F190" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>225</v>
@@ -6616,12 +6718,12 @@
         <v>1</v>
       </c>
       <c r="I190" s="4" t="n">
-        <v>5.31</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B191" s="3" t="s">
         <v>213</v>
@@ -6636,7 +6738,7 @@
         <v>216</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G191" s="3" t="s">
         <v>226</v>
@@ -6645,12 +6747,12 @@
         <v>1</v>
       </c>
       <c r="I191" s="4" t="n">
-        <v>6.23</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>213</v>
@@ -6665,7 +6767,7 @@
         <v>216</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G192" s="3" t="s">
         <v>227</v>
@@ -6674,12 +6776,12 @@
         <v>1</v>
       </c>
       <c r="I192" s="4" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B193" s="3" t="s">
         <v>213</v>
@@ -6694,7 +6796,7 @@
         <v>216</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>228</v>
@@ -6703,12 +6805,12 @@
         <v>0</v>
       </c>
       <c r="I193" s="4" t="n">
-        <v>12.11</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B194" s="3" t="s">
         <v>213</v>
@@ -6723,7 +6825,7 @@
         <v>216</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G194" s="3" t="s">
         <v>229</v>
@@ -6732,12 +6834,12 @@
         <v>1</v>
       </c>
       <c r="I194" s="4" t="n">
-        <v>12.3</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B195" s="3" t="s">
         <v>213</v>
@@ -6752,7 +6854,7 @@
         <v>216</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>230</v>
@@ -6761,12 +6863,12 @@
         <v>1</v>
       </c>
       <c r="I195" s="4" t="n">
-        <v>14.06</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>213</v>
@@ -6781,7 +6883,7 @@
         <v>216</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G196" s="3" t="s">
         <v>231</v>
@@ -6790,12 +6892,12 @@
         <v>0</v>
       </c>
       <c r="I196" s="4" t="n">
-        <v>15.81</v>
+        <v>14.27</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B197" s="3" t="s">
         <v>213</v>
@@ -6816,15 +6918,15 @@
         <v>232</v>
       </c>
       <c r="H197" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I197" s="4" t="n">
-        <v>19.31</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>213</v>
@@ -6839,7 +6941,7 @@
         <v>216</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G198" s="3" t="s">
         <v>233</v>
@@ -6848,12 +6950,12 @@
         <v>1</v>
       </c>
       <c r="I198" s="4" t="n">
-        <v>2.38</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>213</v>
@@ -6868,7 +6970,7 @@
         <v>216</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G199" s="3" t="s">
         <v>234</v>
@@ -6877,12 +6979,12 @@
         <v>1</v>
       </c>
       <c r="I199" s="4" t="n">
-        <v>2.45</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>213</v>
@@ -6897,7 +6999,7 @@
         <v>216</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G200" s="3" t="s">
         <v>235</v>
@@ -6906,12 +7008,12 @@
         <v>1</v>
       </c>
       <c r="I200" s="4" t="n">
-        <v>2.85</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>213</v>
@@ -6926,7 +7028,7 @@
         <v>216</v>
       </c>
       <c r="F201" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G201" s="3" t="s">
         <v>236</v>
@@ -6935,12 +7037,12 @@
         <v>1</v>
       </c>
       <c r="I201" s="4" t="n">
-        <v>3.01</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>213</v>
@@ -6955,7 +7057,7 @@
         <v>216</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G202" s="3" t="s">
         <v>237</v>
@@ -6964,12 +7066,12 @@
         <v>1</v>
       </c>
       <c r="I202" s="4" t="n">
-        <v>4.44</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B203" s="3" t="s">
         <v>213</v>
@@ -6984,7 +7086,7 @@
         <v>216</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G203" s="3" t="s">
         <v>238</v>
@@ -6993,12 +7095,12 @@
         <v>1</v>
       </c>
       <c r="I203" s="4" t="n">
-        <v>4.45</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>213</v>
@@ -7013,7 +7115,7 @@
         <v>216</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G204" s="3" t="s">
         <v>239</v>
@@ -7022,12 +7124,12 @@
         <v>1</v>
       </c>
       <c r="I204" s="4" t="n">
-        <v>4.47</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>213</v>
@@ -7042,7 +7144,7 @@
         <v>216</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G205" s="3" t="s">
         <v>240</v>
@@ -7051,12 +7153,12 @@
         <v>1</v>
       </c>
       <c r="I205" s="4" t="n">
-        <v>4.47</v>
+        <v>7.54</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>213</v>
@@ -7071,21 +7173,21 @@
         <v>216</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G206" s="3" t="s">
         <v>241</v>
       </c>
       <c r="H206" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I206" s="4" t="n">
-        <v>8.43</v>
+        <v>11.28</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>213</v>
@@ -7100,21 +7202,21 @@
         <v>216</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G207" s="3" t="s">
         <v>242</v>
       </c>
       <c r="H207" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I207" s="4" t="n">
-        <v>10.35</v>
+        <v>12.38</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>213</v>
@@ -7129,7 +7231,7 @@
         <v>216</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G208" s="3" t="s">
         <v>243</v>
@@ -7138,12 +7240,12 @@
         <v>1</v>
       </c>
       <c r="I208" s="4" t="n">
-        <v>15.59</v>
+        <v>13.29</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>213</v>
@@ -7158,21 +7260,21 @@
         <v>216</v>
       </c>
       <c r="F209" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G209" s="3" t="s">
         <v>244</v>
       </c>
       <c r="H209" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I209" s="4" t="n">
-        <v>18.15</v>
+        <v>14.65</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B210" s="3" t="s">
         <v>213</v>
@@ -7187,21 +7289,21 @@
         <v>216</v>
       </c>
       <c r="F210" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G210" s="3" t="s">
         <v>245</v>
       </c>
       <c r="H210" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I210" s="4" t="n">
-        <v>18.96</v>
+        <v>15.45</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>46229</v>
+        <v>46236</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>213</v>
@@ -7216,16 +7318,886 @@
         <v>216</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G211" s="3" t="s">
         <v>246</v>
       </c>
       <c r="H211" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I211" s="4" t="n">
-        <v>20.8</v>
+        <v>16.14</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B212" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C212" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D212" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E212" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F212" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G212" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="H212" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I212" s="4" t="n">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E213" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F213" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G213" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="H213" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I213" s="4" t="n">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C214" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D214" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E214" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F214" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G214" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="H214" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I214" s="4" t="n">
+        <v>3.07</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D215" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E215" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F215" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G215" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H215" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I215" s="4" t="n">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C216" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E216" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F216" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G216" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="H216" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I216" s="4" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E217" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F217" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G217" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H217" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I217" s="4" t="n">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E218" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F218" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G218" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="H218" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I218" s="4" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E219" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F219" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G219" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="H219" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I219" s="4" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D220" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E220" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F220" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G220" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="H220" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I220" s="4" t="n">
+        <v>4.63</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C221" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D221" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E221" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F221" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G221" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="H221" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I221" s="4" t="n">
+        <v>4.94</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C222" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E222" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F222" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G222" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="H222" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I222" s="4" t="n">
+        <v>10.19</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C223" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E223" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F223" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G223" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="H223" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I223" s="4" t="n">
+        <v>12.09</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C224" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E224" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F224" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G224" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H224" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I224" s="4" t="n">
+        <v>12.48</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E225" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F225" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G225" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="H225" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I225" s="4" t="n">
+        <v>13.57</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E226" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F226" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G226" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="H226" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I226" s="4" t="n">
+        <v>13.64</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E227" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G227" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="H227" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I227" s="4" t="n">
+        <v>15.89</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E228" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G228" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="H228" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I228" s="4" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E229" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F229" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G229" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="H229" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I229" s="4" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C230" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E230" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F230" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G230" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="H230" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I230" s="4" t="n">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E231" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F231" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G231" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="H231" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I231" s="4" t="n">
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E232" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F232" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G232" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="H232" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I232" s="4" t="n">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E233" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F233" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G233" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="H233" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I233" s="4" t="n">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C234" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E234" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F234" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G234" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="H234" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I234" s="4" t="n">
+        <v>4.36</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B235" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C235" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E235" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F235" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G235" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="H235" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I235" s="4" t="n">
+        <v>5.26</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C236" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E236" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F236" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G236" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="H236" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I236" s="4" t="n">
+        <v>5.37</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B237" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C237" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E237" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F237" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G237" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H237" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I237" s="4" t="n">
+        <v>5.38</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C238" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E238" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F238" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G238" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="H238" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I238" s="4" t="n">
+        <v>10.03</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B239" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C239" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D239" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E239" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F239" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G239" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="H239" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I239" s="4" t="n">
+        <v>10.15</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B240" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C240" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D240" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E240" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F240" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G240" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="H240" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I240" s="4" t="n">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C241" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D241" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E241" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F241" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G241" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="H241" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I241" s="4" t="n">
+        <v>18.25</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_anytime_tryscorers.xlsx
+++ b/files/NRL_anytime_tryscorers.xlsx
@@ -89,7 +89,7 @@
     <t xml:space="preserve">Sam McIntyre</t>
   </si>
   <si>
-    <t xml:space="preserve">Liam Sutton</t>
+    <t xml:space="preserve">Thomas Mikaele</t>
   </si>
   <si>
     <t xml:space="preserve">Mark Nawaqanitawase</t>
@@ -128,19 +128,19 @@
     <t xml:space="preserve">Connor Watson</t>
   </si>
   <si>
+    <t xml:space="preserve">Salesi Foketi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spencer Leniu</t>
+  </si>
+  <si>
     <t xml:space="preserve">Egan Butcher</t>
   </si>
   <si>
-    <t xml:space="preserve">Spencer Leniu</t>
-  </si>
-  <si>
     <t xml:space="preserve">Naufahu Whyte</t>
   </si>
   <si>
     <t xml:space="preserve">Reece Foley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Benaiah Ioelu</t>
   </si>
   <si>
     <t xml:space="preserve">18:00</t>
@@ -1266,7 +1266,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="3">
@@ -1295,7 +1295,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="4">
@@ -1324,7 +1324,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="5">
@@ -1353,7 +1353,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>3.63</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="6">
@@ -1382,7 +1382,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>3.82</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="7">
@@ -1411,7 +1411,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.54</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="8">
@@ -1440,7 +1440,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4.54</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="9">
@@ -1469,7 +1469,7 @@
         <v>1</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.78</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="10">
@@ -1498,7 +1498,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>7.6</v>
+        <v>7.31</v>
       </c>
     </row>
     <row r="11">
@@ -1527,7 +1527,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>9.16</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="12">
@@ -1556,7 +1556,7 @@
         <v>1</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>9.82</v>
+        <v>9.45</v>
       </c>
     </row>
     <row r="13">
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>14.57</v>
+        <v>14.01</v>
       </c>
     </row>
     <row r="14">
@@ -1611,10 +1611,10 @@
         <v>25</v>
       </c>
       <c r="H14" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>23.31</v>
+        <v>25.26</v>
       </c>
     </row>
     <row r="15">
@@ -1759,7 +1759,7 @@
         <v>1</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="20">
@@ -1875,7 +1875,7 @@
         <v>1</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>4.67</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="24">
@@ -1904,7 +1904,7 @@
         <v>1</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>8.22</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="25">
@@ -1933,7 +1933,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>8.38</v>
+        <v>8.39</v>
       </c>
     </row>
     <row r="26">
@@ -1962,7 +1962,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>10.62</v>
+        <v>10.63</v>
       </c>
     </row>
     <row r="27">
@@ -1988,10 +1988,10 @@
         <v>38</v>
       </c>
       <c r="H27" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>12.8</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="28">
@@ -2017,10 +2017,10 @@
         <v>39</v>
       </c>
       <c r="H28" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>16.38</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="29">
@@ -2046,10 +2046,10 @@
         <v>40</v>
       </c>
       <c r="H29" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>18.24</v>
+        <v>12.81</v>
       </c>
     </row>
     <row r="30">
@@ -2075,10 +2075,10 @@
         <v>41</v>
       </c>
       <c r="H30" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>25.55</v>
+        <v>18.25</v>
       </c>
     </row>
     <row r="31">
@@ -2107,7 +2107,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>25.55</v>
+        <v>25.57</v>
       </c>
     </row>
     <row r="32">
@@ -2136,7 +2136,7 @@
         <v>1</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2165,7 +2165,7 @@
         <v>1</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="34">
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="35">
@@ -2223,7 +2223,7 @@
         <v>1</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="36">
@@ -2252,7 +2252,7 @@
         <v>1</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="37">
@@ -2281,7 +2281,7 @@
         <v>1</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>4.19</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="38">
@@ -2310,7 +2310,7 @@
         <v>1</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>4.19</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="39">
@@ -2339,7 +2339,7 @@
         <v>1</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>5.17</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="40">
@@ -2368,7 +2368,7 @@
         <v>1</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>5.8</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="41">
@@ -2397,7 +2397,7 @@
         <v>1</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>6.67</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="42">
@@ -2426,7 +2426,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>9.23</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="43">
@@ -2455,7 +2455,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>9.75</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="44">
@@ -2484,7 +2484,7 @@
         <v>1</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>10.01</v>
+        <v>10.11</v>
       </c>
     </row>
     <row r="45">
@@ -2513,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>10.91</v>
+        <v>11.01</v>
       </c>
     </row>
     <row r="46">
@@ -2542,7 +2542,7 @@
         <v>0</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>14.55</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="47">
@@ -2571,7 +2571,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>15.18</v>
+        <v>15.34</v>
       </c>
     </row>
     <row r="48">
@@ -2600,7 +2600,7 @@
         <v>1</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>15.46</v>
+        <v>15.61</v>
       </c>
     </row>
     <row r="49">
@@ -2629,7 +2629,7 @@
         <v>0</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>15.8</v>
+        <v>15.96</v>
       </c>
     </row>
     <row r="50">
@@ -2658,7 +2658,7 @@
         <v>1</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>2.87</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="51">
@@ -2687,7 +2687,7 @@
         <v>1</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="52">
@@ -2716,7 +2716,7 @@
         <v>1</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>3.14</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="53">
@@ -2745,7 +2745,7 @@
         <v>1</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>3.36</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="54">
@@ -2774,7 +2774,7 @@
         <v>1</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>3.37</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="55">
@@ -2803,7 +2803,7 @@
         <v>1</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>5.34</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="56">
@@ -2832,7 +2832,7 @@
         <v>1</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>5.34</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="57">
@@ -2861,7 +2861,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>7.06</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="58">
@@ -2890,7 +2890,7 @@
         <v>1</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>7.33</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="59">
@@ -2919,7 +2919,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>7.82</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="60">
@@ -2948,7 +2948,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>8.76</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="61">
@@ -2977,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>12.72</v>
+        <v>11.98</v>
       </c>
     </row>
     <row r="62">
@@ -3006,7 +3006,7 @@
         <v>1</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="63">
@@ -3035,7 +3035,7 @@
         <v>1</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="64">
@@ -3064,7 +3064,7 @@
         <v>1</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>3.83</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="65">
@@ -3093,7 +3093,7 @@
         <v>1</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>4.94</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="66">
@@ -3122,7 +3122,7 @@
         <v>1</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>5.09</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
@@ -3151,7 +3151,7 @@
         <v>1</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>5.41</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="68">
@@ -3180,7 +3180,7 @@
         <v>1</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>5.41</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="69">
@@ -3209,7 +3209,7 @@
         <v>1</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>6.44</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="70">
@@ -3238,7 +3238,7 @@
         <v>1</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>7.3</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="71">
@@ -3267,7 +3267,7 @@
         <v>0</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>13.56</v>
+        <v>13.29</v>
       </c>
     </row>
     <row r="72">
@@ -3296,7 +3296,7 @@
         <v>0</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>13.96</v>
+        <v>13.68</v>
       </c>
     </row>
     <row r="73">
@@ -3325,7 +3325,7 @@
         <v>1</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>16.36</v>
+        <v>16.03</v>
       </c>
     </row>
     <row r="74">
@@ -3354,7 +3354,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>17.05</v>
+        <v>16.71</v>
       </c>
     </row>
     <row r="75">
@@ -3383,7 +3383,7 @@
         <v>1</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="76">
@@ -3412,7 +3412,7 @@
         <v>1</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="77">
@@ -3441,7 +3441,7 @@
         <v>1</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="78">
@@ -3470,7 +3470,7 @@
         <v>1</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>3.25</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="79">
@@ -3499,7 +3499,7 @@
         <v>1</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>3.48</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="80">
@@ -3528,7 +3528,7 @@
         <v>1</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>3.75</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="81">
@@ -3557,7 +3557,7 @@
         <v>1</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>4.27</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="82">
@@ -3586,7 +3586,7 @@
         <v>1</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>4.27</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="83">
@@ -3615,7 +3615,7 @@
         <v>1</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>4.37</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="84">
@@ -3644,7 +3644,7 @@
         <v>1</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>7.18</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="85">
@@ -3673,7 +3673,7 @@
         <v>1</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>9.22</v>
+        <v>9.03</v>
       </c>
     </row>
     <row r="86">
@@ -3702,7 +3702,7 @@
         <v>1</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>11.02</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="87">
@@ -3731,7 +3731,7 @@
         <v>0</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>16.27</v>
+        <v>15.92</v>
       </c>
     </row>
     <row r="88">
@@ -3760,7 +3760,7 @@
         <v>0</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>18.03</v>
+        <v>17.64</v>
       </c>
     </row>
     <row r="89">
@@ -3789,7 +3789,7 @@
         <v>1</v>
       </c>
       <c r="I89" s="4" t="n">
-        <v>18.78</v>
+        <v>18.38</v>
       </c>
     </row>
     <row r="90">
@@ -3818,7 +3818,7 @@
         <v>0</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>20.27</v>
+        <v>19.84</v>
       </c>
     </row>
     <row r="91">
@@ -3847,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>20.27</v>
+        <v>19.84</v>
       </c>
     </row>
     <row r="92">
@@ -5674,7 +5674,7 @@
         <v>1</v>
       </c>
       <c r="I154" s="4" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="155">
@@ -5761,7 +5761,7 @@
         <v>1</v>
       </c>
       <c r="I157" s="4" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="158">
@@ -5790,7 +5790,7 @@
         <v>1</v>
       </c>
       <c r="I158" s="4" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="159">
@@ -5819,7 +5819,7 @@
         <v>1</v>
       </c>
       <c r="I159" s="4" t="n">
-        <v>4.67</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="160">
@@ -5848,7 +5848,7 @@
         <v>1</v>
       </c>
       <c r="I160" s="4" t="n">
-        <v>5.45</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="161">
@@ -5877,7 +5877,7 @@
         <v>0</v>
       </c>
       <c r="I161" s="4" t="n">
-        <v>7.01</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="162">
@@ -5906,7 +5906,7 @@
         <v>0</v>
       </c>
       <c r="I162" s="4" t="n">
-        <v>7.38</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="163">
@@ -5935,7 +5935,7 @@
         <v>1</v>
       </c>
       <c r="I163" s="4" t="n">
-        <v>7.76</v>
+        <v>7.74</v>
       </c>
     </row>
     <row r="164">
@@ -5964,7 +5964,7 @@
         <v>0</v>
       </c>
       <c r="I164" s="4" t="n">
-        <v>9.22</v>
+        <v>9.2</v>
       </c>
     </row>
     <row r="165">
@@ -5993,7 +5993,7 @@
         <v>1</v>
       </c>
       <c r="I165" s="4" t="n">
-        <v>12.59</v>
+        <v>12.55</v>
       </c>
     </row>
     <row r="166">
@@ -6022,7 +6022,7 @@
         <v>1</v>
       </c>
       <c r="I166" s="4" t="n">
-        <v>14.04</v>
+        <v>14</v>
       </c>
     </row>
     <row r="167">
@@ -6080,7 +6080,7 @@
         <v>1</v>
       </c>
       <c r="I168" s="4" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="169">
@@ -6109,7 +6109,7 @@
         <v>1</v>
       </c>
       <c r="I169" s="4" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="170">
@@ -6138,7 +6138,7 @@
         <v>1</v>
       </c>
       <c r="I170" s="4" t="n">
-        <v>3.88</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="171">
@@ -6167,7 +6167,7 @@
         <v>1</v>
       </c>
       <c r="I171" s="4" t="n">
-        <v>4.63</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="172">
@@ -6196,7 +6196,7 @@
         <v>1</v>
       </c>
       <c r="I172" s="4" t="n">
-        <v>5.22</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="173">
@@ -6225,7 +6225,7 @@
         <v>1</v>
       </c>
       <c r="I173" s="4" t="n">
-        <v>5.22</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="174">
@@ -6254,7 +6254,7 @@
         <v>1</v>
       </c>
       <c r="I174" s="4" t="n">
-        <v>6.76</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="175">
@@ -6283,7 +6283,7 @@
         <v>1</v>
       </c>
       <c r="I175" s="4" t="n">
-        <v>6.94</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="176">
@@ -6312,7 +6312,7 @@
         <v>1</v>
       </c>
       <c r="I176" s="4" t="n">
-        <v>7.54</v>
+        <v>7.52</v>
       </c>
     </row>
     <row r="177">
@@ -6341,7 +6341,7 @@
         <v>0</v>
       </c>
       <c r="I177" s="4" t="n">
-        <v>10.44</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="178">
@@ -6370,7 +6370,7 @@
         <v>0</v>
       </c>
       <c r="I178" s="4" t="n">
-        <v>11.38</v>
+        <v>11.33</v>
       </c>
     </row>
     <row r="179">
@@ -6399,7 +6399,7 @@
         <v>1</v>
       </c>
       <c r="I179" s="4" t="n">
-        <v>11.53</v>
+        <v>11.48</v>
       </c>
     </row>
     <row r="180">
@@ -6428,7 +6428,7 @@
         <v>0</v>
       </c>
       <c r="I180" s="4" t="n">
-        <v>16.31</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="181">
@@ -6457,7 +6457,7 @@
         <v>0</v>
       </c>
       <c r="I181" s="4" t="n">
-        <v>18.38</v>
+        <v>18.31</v>
       </c>
     </row>
     <row r="182">
@@ -7472,7 +7472,7 @@
         <v>1</v>
       </c>
       <c r="I216" s="4" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="217">
@@ -7530,7 +7530,7 @@
         <v>1</v>
       </c>
       <c r="I218" s="4" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="219">
@@ -7559,7 +7559,7 @@
         <v>1</v>
       </c>
       <c r="I219" s="4" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="220">
@@ -7588,7 +7588,7 @@
         <v>1</v>
       </c>
       <c r="I220" s="4" t="n">
-        <v>4.63</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="221">
@@ -7617,7 +7617,7 @@
         <v>1</v>
       </c>
       <c r="I221" s="4" t="n">
-        <v>4.94</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="222">
@@ -7646,7 +7646,7 @@
         <v>1</v>
       </c>
       <c r="I222" s="4" t="n">
-        <v>10.19</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="223">
@@ -7675,7 +7675,7 @@
         <v>0</v>
       </c>
       <c r="I223" s="4" t="n">
-        <v>12.09</v>
+        <v>12.07</v>
       </c>
     </row>
     <row r="224">
@@ -7704,7 +7704,7 @@
         <v>0</v>
       </c>
       <c r="I224" s="4" t="n">
-        <v>12.48</v>
+        <v>12.46</v>
       </c>
     </row>
     <row r="225">
@@ -7733,7 +7733,7 @@
         <v>0</v>
       </c>
       <c r="I225" s="4" t="n">
-        <v>13.57</v>
+        <v>13.55</v>
       </c>
     </row>
     <row r="226">
@@ -7762,7 +7762,7 @@
         <v>1</v>
       </c>
       <c r="I226" s="4" t="n">
-        <v>13.64</v>
+        <v>13.62</v>
       </c>
     </row>
     <row r="227">
@@ -7791,7 +7791,7 @@
         <v>1</v>
       </c>
       <c r="I227" s="4" t="n">
-        <v>15.89</v>
+        <v>15.86</v>
       </c>
     </row>
     <row r="228">
@@ -7907,7 +7907,7 @@
         <v>1</v>
       </c>
       <c r="I231" s="4" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="232">
@@ -7936,7 +7936,7 @@
         <v>1</v>
       </c>
       <c r="I232" s="4" t="n">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="233">
@@ -7965,7 +7965,7 @@
         <v>1</v>
       </c>
       <c r="I233" s="4" t="n">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="234">
@@ -8023,7 +8023,7 @@
         <v>1</v>
       </c>
       <c r="I235" s="4" t="n">
-        <v>5.26</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="236">
@@ -8052,7 +8052,7 @@
         <v>1</v>
       </c>
       <c r="I236" s="4" t="n">
-        <v>5.37</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="237">
@@ -8081,7 +8081,7 @@
         <v>1</v>
       </c>
       <c r="I237" s="4" t="n">
-        <v>5.38</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="238">
@@ -8110,7 +8110,7 @@
         <v>1</v>
       </c>
       <c r="I238" s="4" t="n">
-        <v>10.03</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="239">
@@ -8139,7 +8139,7 @@
         <v>1</v>
       </c>
       <c r="I239" s="4" t="n">
-        <v>10.15</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="240">
@@ -8168,7 +8168,7 @@
         <v>0</v>
       </c>
       <c r="I240" s="4" t="n">
-        <v>15.9</v>
+        <v>15.87</v>
       </c>
     </row>
     <row r="241">
@@ -8197,7 +8197,7 @@
         <v>0</v>
       </c>
       <c r="I241" s="4" t="n">
-        <v>18.25</v>
+        <v>18.22</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_anytime_tryscorers.xlsx
+++ b/files/NRL_anytime_tryscorers.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="290">
   <si>
     <t xml:space="preserve">Date Local</t>
   </si>
@@ -41,57 +41,792 @@
     <t xml:space="preserve">Anytimeodds</t>
   </si>
   <si>
+    <t xml:space="preserve">18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260731-1800-st-george-illawarra-dragons-dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george-illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamiso Tabuai-Fidow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selwyn Cobbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamayne Isaako</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herbie Farnworth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Bostock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connelly Lemuelu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kulikefu Finefeuiaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kodi Nikorima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremy Marshall-King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ray Stone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Plath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiya Katoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Flegler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Donoghoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Felise Kaufusi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morgan Knowles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Gilbert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyrell Sloan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setu Tu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valentine Holmes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinton Gutherson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Egan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamish Stewart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Liddle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mosese Suli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyle Flanagan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lyhkan King-Togia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damien Cook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luciano Leilua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Atkinson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260731-2000-melbourne-storm-canterbury-bankstown-bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jethro Rinakama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Kiraz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matt Burton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Tracey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enari Tuala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viliame Kikau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Preston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lachlan Galvin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stephen Crichton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jonathan Sua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Mann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bailey Hayward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Curran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaeman Salmon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moses Leo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sualauvi Faalogo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siulagi Tuimalatu-Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manaia Waitere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyran Wishart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Clarke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oryn Keeley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nick Meaney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hayden Watson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trent Toelau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stefano Utoikamanu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe Chan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shawn Blore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trent Loiero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angus Hinchey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260801-1500-gold-coast-titans-warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phillip Sami</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dean Ieremia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jojo Fifita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Campbell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keano Kini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AJ Brimson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arama Hau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beau Fermor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver Pascoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zane Harrison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tino Fa'asuamaleaui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Bai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chris Randall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurtis Morrin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alofiana Khan-Pereira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dallin Watene-Zelezniak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ali Leiataua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charnze Nicoll-Klokstad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Capewell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Laban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leka Halasima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Pompey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chanel Harris-Tavita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Te Maire Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wayde Egan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Fisher-Harris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Healey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erin Clark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Metcalf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitchell Barnett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260801-1730-penrith-panthers-canberra-raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penrith panthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Savage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaeo Weekes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sebastian Kris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jed Stuart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Timoko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Strange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zac Hosking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ata Mariota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owen Pattie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Sanders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe Roddy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corey Horsburgh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Jenkins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian To'o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaxen Edgar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casey McLean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paul Alamoti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiah Papali'i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathan Cleary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freddy Lussick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lindsay Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Izack Tago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaah Yeo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Cogger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Henry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moses Leota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scott Sorensen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Phillips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Cole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260801-1935-brisbane-broncos-newcastle-knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josiah Karapani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grant Anderson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reece Walsh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezra Mam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kotoni Staggs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Willison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Riki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deine Mariner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Reynolds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Walters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Talty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cory Paix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gehamat Shibasaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payne Haas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Va'a Semu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominic Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greg Marzhew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fletcher Sharpe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bradman Best</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kalyn Ponga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jermaine McEwen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francis Manuleleua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dane Gagai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trey Mooney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandon Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harrison Graham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fletcher Hunt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phoenix Crossland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyson Frizell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brodie Jones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260802-1400-cronulla-sutherland-sharks-south-sydney-rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronaldo Mulitalo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sione Katoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">William Kennedy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayal Iro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braydon Trindall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesse Ramien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Briton Nikora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teig Wilton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicholas Hynes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Addin Fonua-Blake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Hazelton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siosifa Talakai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blayke Brailey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron McInnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braden Hamlin-Uele</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Johnston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campbell Graham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cody Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Dufty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Wighton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latrell Siegwalt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keaon Koloamatangi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euan Aitken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashton Ward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Sullivan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brandon Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tevita Tatola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jye Gray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John Radel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamie Humphreys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260802-1605-wests-tigers-parramatta-eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wests tigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Addo-Carr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian Kelly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiah Iongi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Penisini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Samrani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitchell Moses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kelma Tuilagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kitione Kautoga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronald Volkman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tallyn Da Silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack De Belin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Paulo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joash Papalii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Tuivaiti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunia Turuva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jahream Bula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Doueihi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Tupou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samuela Fainu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sione Fainu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heamasi Makasini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick Herbert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jarome Luai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apisai Koroisau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terrell May</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fonua Pole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Seyfarth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bunty Afoa</t>
+  </si>
+  <si>
     <t xml:space="preserve">19:50</t>
   </si>
   <si>
-    <t xml:space="preserve">sched-2026-20260730-1950-north-queensland-cowboys-sydney-roosters</t>
+    <t xml:space="preserve">sched-2026-20260806-1950-gold-coast-titans-north-queensland-cowboys</t>
   </si>
   <si>
     <t xml:space="preserve">north queensland cowboys</t>
   </si>
   <si>
+    <t xml:space="preserve">Braidon Burns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murray Taulagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scott Drinkwater</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Chester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zac Laybutt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heilum Luki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremiah Nanai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Clifford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaxon Purdue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soni Luke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reuben Cotter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam McIntyre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Mikaele</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coen Hess</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaiden Lahrs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kai O'Donnell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jason Taumalolo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Lodge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260807-2000-sydney-roosters-canterbury-bankstown-bulldogs</t>
+  </si>
+  <si>
     <t xml:space="preserve">sydney roosters</t>
   </si>
   <si>
-    <t xml:space="preserve">Braidon Burns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Murray Taulagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scott Drinkwater</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Chester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zac Laybutt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heilum Luki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremiah Nanai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Clifford</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaxon Purdue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soni Luke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reuben Cotter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam McIntyre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Mikaele</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mark Nawaqanitawase</t>
   </si>
   <si>
@@ -143,718 +878,10 @@
     <t xml:space="preserve">Reece Foley</t>
   </si>
   <si>
-    <t xml:space="preserve">18:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched-2026-20260731-1800-st-george-illawarra-dragons-dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george-illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamiso Tabuai-Fidow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selwyn Cobbo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamayne Isaako</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herbie Farnworth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Bostock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connelly Lemuelu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kulikefu Finefeuiaki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kodi Nikorima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brad Schneider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremy Marshall-King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ray Stone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Plath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Flegler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiya Katoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurt Donoghoe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Felise Kaufusi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morgan Knowles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Gilbert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyrell Sloan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Setu Tu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mathew Feagai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valentine Holmes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clinton Gutherson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Egan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamish Stewart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Liddle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyle Flanagan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel Atkinson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Damien Cook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luciano Leilua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched-2026-20260731-2000-melbourne-storm-canterbury-bankstown-bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jethro Rinakama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Kiraz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matt Burton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Tracey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enari Tuala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viliame Kikau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Preston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lachlan Galvin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stephen Crichton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jonathan Sua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurt Mann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bailey Hayward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Curran</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moses Leo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sualauvi Faalogo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jahrome Hughes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siulagi Tuimalatu-Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manaia Waitere</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyran Wishart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Clarke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oryn Keeley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nick Meaney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trent Toelau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stefano Utoikamanu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joe Chan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shawn Blore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trent Loiero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hayden Watson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angus Hinchey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched-2026-20260801-1500-gold-coast-titans-warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phillip Sami</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dean Ieremia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jojo Fifita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Campbell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keano Kini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AJ Brimson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arama Hau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beau Fermor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oliver Pascoe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zane Harrison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tino Fa'asuamaleaui</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Bai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chris Randall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurtis Morrin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alofiana Khan-Pereira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dallin Watene-Zelezniak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ali Leiataua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charnze Nicoll-Klokstad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurt Capewell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Laban</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leka Halasima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Pompey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chanel Harris-Tavita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Te Maire Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wayde Egan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Fisher-Harris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Healey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erin Clark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Metcalf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rocco Berry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched-2026-20260801-1730-penrith-panthers-canberra-raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penrith panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Savage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaeo Weekes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jed Stuart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simi Sasagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Timoko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan Strange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zac Hosking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ata Mariota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owen Pattie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan Sanders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joe Roddy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corey Horsburgh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Jenkins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian To'o</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaxen Edgar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casey McLean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paul Alamoti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiah Papali'i</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nathan Cleary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freddy Lussick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lindsay Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Izack Tago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaah Yeo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Cogger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Henry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moses Leota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scott Sorensen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Phillips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Cole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched-2026-20260801-1935-brisbane-broncos-newcastle-knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josiah Karapani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grant Anderson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reece Walsh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ezra Mam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kotoni Staggs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Willison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan Riki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deine Mariner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Reynolds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Walters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben Talty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cory Paix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gehamat Shibasaki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payne Haas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Va'a Semu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dominic Young</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greg Marzhew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fletcher Sharpe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bradman Best</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kalyn Ponga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jermaine McEwen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Francis Manuleleua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dane Gagai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trey Mooney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandon Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harrison Graham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fletcher Hunt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phoenix Crossland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyson Frizell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brodie Jones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched-2026-20260802-1400-cronulla-sutherland-sharks-south-sydney-rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">south sydney rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronaldo Mulitalo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sione Katoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">William Kennedy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kayal Iro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Braydon Trindall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jesse Ramien</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Briton Nikora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teig Wilton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicholas Hynes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Addin Fonua-Blake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Hazelton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siosifa Talakai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blayke Brailey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameron McInnes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Braden Hamlin-Uele</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Johnston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campbell Graham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cody Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Dufty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Wighton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latrell Siegwalt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keaon Koloamatangi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Euan Aitken</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashton Ward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Sullivan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brandon Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tevita Tatola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jye Gray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">John Radel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamie Humphreys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched-2026-20260802-1605-wests-tigers-parramatta-eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Addo-Carr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian Kelly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiah Iongi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Will Penisini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan Samrani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitchell Moses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kelma Tuilagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitione Kautoga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronald Volkman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tallyn Da Silva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack De Belin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Paulo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joash Papalii</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Tuivaiti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunia Turuva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jahream Bula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Doueihi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Tupou</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samuela Fainu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sione Fainu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heamasi Makasini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patrick Herbert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jarome Luai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apisai Koroisau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terrell May</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fonua Pole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Seyfarth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bunty Afoa</t>
+    <t xml:space="preserve">Taylor Losalu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cody Ramsey</t>
   </si>
 </sst>
 </file>
@@ -1242,7 +1269,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>9</v>
@@ -1257,7 +1284,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>13</v>
@@ -1266,12 +1293,12 @@
         <v>1</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>9</v>
@@ -1286,7 +1313,7 @@
         <v>12</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>14</v>
@@ -1295,12 +1322,12 @@
         <v>1</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>9</v>
@@ -1315,7 +1342,7 @@
         <v>12</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>15</v>
@@ -1324,12 +1351,12 @@
         <v>1</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>2.81</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>9</v>
@@ -1344,7 +1371,7 @@
         <v>12</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>16</v>
@@ -1353,12 +1380,12 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>3.5</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>9</v>
@@ -1373,7 +1400,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>17</v>
@@ -1382,12 +1409,12 @@
         <v>1</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>3.69</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>9</v>
@@ -1402,7 +1429,7 @@
         <v>12</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>18</v>
@@ -1411,12 +1438,12 @@
         <v>1</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.38</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>9</v>
@@ -1431,7 +1458,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>19</v>
@@ -1440,12 +1467,12 @@
         <v>1</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4.38</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>9</v>
@@ -1460,7 +1487,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>20</v>
@@ -1469,12 +1496,12 @@
         <v>1</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.61</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>9</v>
@@ -1489,7 +1516,7 @@
         <v>12</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>21</v>
@@ -1498,12 +1525,12 @@
         <v>1</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>7.31</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>9</v>
@@ -1518,21 +1545,21 @@
         <v>12</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H11" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>8.81</v>
+        <v>9.28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>9</v>
@@ -1547,21 +1574,21 @@
         <v>12</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H12" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>9.45</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>9</v>
@@ -1576,21 +1603,21 @@
         <v>12</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H13" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>14.01</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>9</v>
@@ -1605,7 +1632,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>25</v>
@@ -1614,12 +1641,12 @@
         <v>1</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>25.26</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>9</v>
@@ -1640,15 +1667,15 @@
         <v>26</v>
       </c>
       <c r="H15" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.81</v>
+        <v>14.64</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>9</v>
@@ -1669,15 +1696,15 @@
         <v>27</v>
       </c>
       <c r="H16" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.52</v>
+        <v>15.27</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>9</v>
@@ -1701,12 +1728,12 @@
         <v>1</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.74</v>
+        <v>15.55</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>9</v>
@@ -1727,15 +1754,15 @@
         <v>29</v>
       </c>
       <c r="H18" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3.07</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>9</v>
@@ -1750,7 +1777,7 @@
         <v>12</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>30</v>
@@ -1759,12 +1786,12 @@
         <v>1</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3.32</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>9</v>
@@ -1779,7 +1806,7 @@
         <v>12</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>31</v>
@@ -1788,12 +1815,12 @@
         <v>1</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>4.64</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>9</v>
@@ -1808,7 +1835,7 @@
         <v>12</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>32</v>
@@ -1817,12 +1844,12 @@
         <v>1</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>4.64</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>9</v>
@@ -1837,7 +1864,7 @@
         <v>12</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>33</v>
@@ -1846,12 +1873,12 @@
         <v>1</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>4.66</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>9</v>
@@ -1866,7 +1893,7 @@
         <v>12</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>34</v>
@@ -1875,12 +1902,12 @@
         <v>1</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>4.68</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>9</v>
@@ -1895,7 +1922,7 @@
         <v>12</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>35</v>
@@ -1904,12 +1931,12 @@
         <v>1</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>8.23</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>9</v>
@@ -1924,21 +1951,21 @@
         <v>12</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>36</v>
       </c>
       <c r="H25" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>8.39</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>9</v>
@@ -1953,21 +1980,21 @@
         <v>12</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>37</v>
       </c>
       <c r="H26" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>10.63</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>9</v>
@@ -1982,7 +2009,7 @@
         <v>12</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>38</v>
@@ -1991,12 +2018,12 @@
         <v>1</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>12.1</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>9</v>
@@ -2011,21 +2038,21 @@
         <v>12</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>39</v>
       </c>
       <c r="H28" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>12.5</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>9</v>
@@ -2040,21 +2067,21 @@
         <v>12</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H29" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>12.81</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>9</v>
@@ -2069,21 +2096,21 @@
         <v>12</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>41</v>
       </c>
       <c r="H30" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>18.25</v>
+        <v>10.66</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>9</v>
@@ -2098,7 +2125,7 @@
         <v>12</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>42</v>
@@ -2107,7 +2134,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>25.57</v>
+        <v>15.24</v>
       </c>
     </row>
     <row r="32">
@@ -2136,7 +2163,7 @@
         <v>1</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="33">
@@ -2165,7 +2192,7 @@
         <v>1</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.08</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="34">
@@ -2194,7 +2221,7 @@
         <v>1</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>2.18</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="35">
@@ -2223,7 +2250,7 @@
         <v>1</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>2.49</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="36">
@@ -2252,7 +2279,7 @@
         <v>1</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>2.95</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="37">
@@ -2281,7 +2308,7 @@
         <v>1</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>4.23</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="38">
@@ -2310,7 +2337,7 @@
         <v>1</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>4.23</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="39">
@@ -2339,7 +2366,7 @@
         <v>1</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>5.22</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="40">
@@ -2368,7 +2395,7 @@
         <v>1</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>5.86</v>
+        <v>6.88</v>
       </c>
     </row>
     <row r="41">
@@ -2394,10 +2421,10 @@
         <v>56</v>
       </c>
       <c r="H41" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>6.73</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="42">
@@ -2426,7 +2453,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>9.32</v>
+        <v>13.13</v>
       </c>
     </row>
     <row r="43">
@@ -2452,10 +2479,10 @@
         <v>58</v>
       </c>
       <c r="H43" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>9.85</v>
+        <v>15.37</v>
       </c>
     </row>
     <row r="44">
@@ -2481,10 +2508,10 @@
         <v>59</v>
       </c>
       <c r="H44" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>10.11</v>
+        <v>16.03</v>
       </c>
     </row>
     <row r="45">
@@ -2510,10 +2537,10 @@
         <v>60</v>
       </c>
       <c r="H45" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>11.01</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="46">
@@ -2533,16 +2560,16 @@
         <v>46</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>61</v>
       </c>
       <c r="H46" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>14.7</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="47">
@@ -2562,16 +2589,16 @@
         <v>46</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>62</v>
       </c>
       <c r="H47" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>15.34</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="48">
@@ -2591,7 +2618,7 @@
         <v>46</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>63</v>
@@ -2600,7 +2627,7 @@
         <v>1</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>15.61</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="49">
@@ -2620,16 +2647,16 @@
         <v>46</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>64</v>
       </c>
       <c r="H49" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>15.96</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="50">
@@ -2658,7 +2685,7 @@
         <v>1</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>2.73</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="51">
@@ -2687,7 +2714,7 @@
         <v>1</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>2.9</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="52">
@@ -2716,7 +2743,7 @@
         <v>1</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>2.98</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="53">
@@ -2745,7 +2772,7 @@
         <v>1</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>3.19</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="54">
@@ -2774,7 +2801,7 @@
         <v>1</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>3.2</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="55">
@@ -2803,7 +2830,7 @@
         <v>1</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>5.04</v>
+        <v>6.88</v>
       </c>
     </row>
     <row r="56">
@@ -2832,7 +2859,7 @@
         <v>1</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>5.04</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="57">
@@ -2858,10 +2885,10 @@
         <v>72</v>
       </c>
       <c r="H57" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>6.66</v>
+        <v>10.55</v>
       </c>
     </row>
     <row r="58">
@@ -2887,10 +2914,10 @@
         <v>73</v>
       </c>
       <c r="H58" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>6.91</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="59">
@@ -2916,10 +2943,10 @@
         <v>74</v>
       </c>
       <c r="H59" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>7.37</v>
+        <v>17.25</v>
       </c>
     </row>
     <row r="60">
@@ -2948,7 +2975,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>8.26</v>
+        <v>17.97</v>
       </c>
     </row>
     <row r="61">
@@ -2977,12 +3004,12 @@
         <v>0</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>11.98</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>77</v>
@@ -2997,7 +3024,7 @@
         <v>80</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>81</v>
@@ -3006,12 +3033,12 @@
         <v>1</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>77</v>
@@ -3026,7 +3053,7 @@
         <v>80</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>82</v>
@@ -3035,12 +3062,12 @@
         <v>1</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>77</v>
@@ -3055,7 +3082,7 @@
         <v>80</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>83</v>
@@ -3064,12 +3091,12 @@
         <v>1</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>3.76</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>77</v>
@@ -3084,7 +3111,7 @@
         <v>80</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>84</v>
@@ -3093,12 +3120,12 @@
         <v>1</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>4.85</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>77</v>
@@ -3113,7 +3140,7 @@
         <v>80</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>85</v>
@@ -3122,12 +3149,12 @@
         <v>1</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>5</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>77</v>
@@ -3142,7 +3169,7 @@
         <v>80</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>86</v>
@@ -3151,12 +3178,12 @@
         <v>1</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>5.31</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>77</v>
@@ -3171,7 +3198,7 @@
         <v>80</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>87</v>
@@ -3180,12 +3207,12 @@
         <v>1</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>5.31</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>77</v>
@@ -3200,7 +3227,7 @@
         <v>80</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>88</v>
@@ -3209,12 +3236,12 @@
         <v>1</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>6.31</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>77</v>
@@ -3229,7 +3256,7 @@
         <v>80</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>89</v>
@@ -3238,12 +3265,12 @@
         <v>1</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>7.16</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>77</v>
@@ -3258,21 +3285,21 @@
         <v>80</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>90</v>
       </c>
       <c r="H71" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>13.29</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>77</v>
@@ -3287,21 +3314,21 @@
         <v>80</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>91</v>
       </c>
       <c r="H72" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>13.68</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>77</v>
@@ -3316,21 +3343,21 @@
         <v>80</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>92</v>
       </c>
       <c r="H73" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>16.03</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>77</v>
@@ -3345,21 +3372,21 @@
         <v>80</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>93</v>
       </c>
       <c r="H74" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>16.71</v>
+        <v>11.54</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>77</v>
@@ -3380,15 +3407,15 @@
         <v>94</v>
       </c>
       <c r="H75" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>2.12</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>77</v>
@@ -3403,7 +3430,7 @@
         <v>80</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>95</v>
@@ -3412,12 +3439,12 @@
         <v>1</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>2.25</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>77</v>
@@ -3432,7 +3459,7 @@
         <v>80</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>96</v>
@@ -3441,12 +3468,12 @@
         <v>1</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>3.15</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>77</v>
@@ -3461,7 +3488,7 @@
         <v>80</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>97</v>
@@ -3470,12 +3497,12 @@
         <v>1</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>3.19</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>77</v>
@@ -3490,7 +3517,7 @@
         <v>80</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>98</v>
@@ -3499,12 +3526,12 @@
         <v>1</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>3.41</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>77</v>
@@ -3519,7 +3546,7 @@
         <v>80</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>99</v>
@@ -3528,12 +3555,12 @@
         <v>1</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>3.68</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>77</v>
@@ -3548,7 +3575,7 @@
         <v>80</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>100</v>
@@ -3557,12 +3584,12 @@
         <v>1</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>4.19</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>77</v>
@@ -3577,21 +3604,21 @@
         <v>80</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>101</v>
       </c>
       <c r="H82" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>4.19</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>77</v>
@@ -3606,7 +3633,7 @@
         <v>80</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>102</v>
@@ -3615,12 +3642,12 @@
         <v>1</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>4.29</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>77</v>
@@ -3635,7 +3662,7 @@
         <v>80</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G84" s="3" t="s">
         <v>103</v>
@@ -3644,12 +3671,12 @@
         <v>1</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>7.03</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>77</v>
@@ -3664,7 +3691,7 @@
         <v>80</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G85" s="3" t="s">
         <v>104</v>
@@ -3673,12 +3700,12 @@
         <v>1</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>9.03</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>77</v>
@@ -3693,7 +3720,7 @@
         <v>80</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>105</v>
@@ -3702,12 +3729,12 @@
         <v>1</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>10.79</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>77</v>
@@ -3722,21 +3749,21 @@
         <v>80</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>106</v>
       </c>
       <c r="H87" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>15.92</v>
+        <v>10.43</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>77</v>
@@ -3751,7 +3778,7 @@
         <v>80</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G88" s="3" t="s">
         <v>107</v>
@@ -3760,12 +3787,12 @@
         <v>0</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>17.64</v>
+        <v>11.06</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>77</v>
@@ -3780,7 +3807,7 @@
         <v>80</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>108</v>
@@ -3789,12 +3816,12 @@
         <v>1</v>
       </c>
       <c r="I89" s="4" t="n">
-        <v>18.38</v>
+        <v>12.26</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>77</v>
@@ -3809,7 +3836,7 @@
         <v>80</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>109</v>
@@ -3818,12 +3845,12 @@
         <v>0</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>19.84</v>
+        <v>14.17</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>77</v>
@@ -3838,16 +3865,16 @@
         <v>80</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>110</v>
       </c>
       <c r="H91" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>19.84</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="92">
@@ -3867,7 +3894,7 @@
         <v>114</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>115</v>
@@ -3876,7 +3903,7 @@
         <v>1</v>
       </c>
       <c r="I92" s="4" t="n">
-        <v>2.49</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="93">
@@ -3896,7 +3923,7 @@
         <v>114</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>116</v>
@@ -3905,7 +3932,7 @@
         <v>1</v>
       </c>
       <c r="I93" s="4" t="n">
-        <v>3.52</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="94">
@@ -3925,7 +3952,7 @@
         <v>114</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>117</v>
@@ -3934,7 +3961,7 @@
         <v>1</v>
       </c>
       <c r="I94" s="4" t="n">
-        <v>3.87</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="95">
@@ -3954,7 +3981,7 @@
         <v>114</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G95" s="3" t="s">
         <v>118</v>
@@ -3963,7 +3990,7 @@
         <v>1</v>
       </c>
       <c r="I95" s="4" t="n">
-        <v>4.19</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="96">
@@ -3983,7 +4010,7 @@
         <v>114</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>119</v>
@@ -3992,7 +4019,7 @@
         <v>1</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>4.51</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="97">
@@ -4012,7 +4039,7 @@
         <v>114</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>120</v>
@@ -4021,7 +4048,7 @@
         <v>1</v>
       </c>
       <c r="I97" s="4" t="n">
-        <v>4.67</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="98">
@@ -4041,7 +4068,7 @@
         <v>114</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>121</v>
@@ -4050,7 +4077,7 @@
         <v>1</v>
       </c>
       <c r="I98" s="4" t="n">
-        <v>5.02</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="99">
@@ -4070,7 +4097,7 @@
         <v>114</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>122</v>
@@ -4079,7 +4106,7 @@
         <v>1</v>
       </c>
       <c r="I99" s="4" t="n">
-        <v>5.02</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="100">
@@ -4099,7 +4126,7 @@
         <v>114</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>123</v>
@@ -4108,7 +4135,7 @@
         <v>1</v>
       </c>
       <c r="I100" s="4" t="n">
-        <v>6.2</v>
+        <v>7.83</v>
       </c>
     </row>
     <row r="101">
@@ -4128,7 +4155,7 @@
         <v>114</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>124</v>
@@ -4137,7 +4164,7 @@
         <v>1</v>
       </c>
       <c r="I101" s="4" t="n">
-        <v>9.87</v>
+        <v>11.06</v>
       </c>
     </row>
     <row r="102">
@@ -4157,16 +4184,16 @@
         <v>114</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>125</v>
       </c>
       <c r="H102" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I102" s="4" t="n">
-        <v>10</v>
+        <v>11.13</v>
       </c>
     </row>
     <row r="103">
@@ -4186,16 +4213,16 @@
         <v>114</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G103" s="3" t="s">
         <v>126</v>
       </c>
       <c r="H103" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I103" s="4" t="n">
-        <v>11.37</v>
+        <v>16.42</v>
       </c>
     </row>
     <row r="104">
@@ -4224,7 +4251,7 @@
         <v>1</v>
       </c>
       <c r="I104" s="4" t="n">
-        <v>11.62</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="105">
@@ -4250,10 +4277,10 @@
         <v>128</v>
       </c>
       <c r="H105" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I105" s="4" t="n">
-        <v>12.09</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="106">
@@ -4273,7 +4300,7 @@
         <v>114</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G106" s="3" t="s">
         <v>129</v>
@@ -4282,7 +4309,7 @@
         <v>1</v>
       </c>
       <c r="I106" s="4" t="n">
-        <v>1.75</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="107">
@@ -4302,7 +4329,7 @@
         <v>114</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>130</v>
@@ -4311,7 +4338,7 @@
         <v>1</v>
       </c>
       <c r="I107" s="4" t="n">
-        <v>2.03</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="108">
@@ -4331,7 +4358,7 @@
         <v>114</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>131</v>
@@ -4340,7 +4367,7 @@
         <v>1</v>
       </c>
       <c r="I108" s="4" t="n">
-        <v>3.76</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="109">
@@ -4360,7 +4387,7 @@
         <v>114</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G109" s="3" t="s">
         <v>132</v>
@@ -4369,7 +4396,7 @@
         <v>1</v>
       </c>
       <c r="I109" s="4" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="110">
@@ -4389,7 +4416,7 @@
         <v>114</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>133</v>
@@ -4398,7 +4425,7 @@
         <v>1</v>
       </c>
       <c r="I110" s="4" t="n">
-        <v>4.46</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="111">
@@ -4418,7 +4445,7 @@
         <v>114</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>134</v>
@@ -4427,7 +4454,7 @@
         <v>1</v>
       </c>
       <c r="I111" s="4" t="n">
-        <v>4.46</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="112">
@@ -4447,16 +4474,16 @@
         <v>114</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>135</v>
       </c>
       <c r="H112" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I112" s="4" t="n">
-        <v>4.73</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="113">
@@ -4476,7 +4503,7 @@
         <v>114</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G113" s="3" t="s">
         <v>136</v>
@@ -4485,7 +4512,7 @@
         <v>1</v>
       </c>
       <c r="I113" s="4" t="n">
-        <v>5.01</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="114">
@@ -4505,16 +4532,16 @@
         <v>114</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>137</v>
       </c>
       <c r="H114" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I114" s="4" t="n">
-        <v>5.22</v>
+        <v>7.57</v>
       </c>
     </row>
     <row r="115">
@@ -4534,7 +4561,7 @@
         <v>114</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G115" s="3" t="s">
         <v>138</v>
@@ -4543,7 +4570,7 @@
         <v>1</v>
       </c>
       <c r="I115" s="4" t="n">
-        <v>5.25</v>
+        <v>9.22</v>
       </c>
     </row>
     <row r="116">
@@ -4563,7 +4590,7 @@
         <v>114</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G116" s="3" t="s">
         <v>139</v>
@@ -4572,7 +4599,7 @@
         <v>1</v>
       </c>
       <c r="I116" s="4" t="n">
-        <v>7.59</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="117">
@@ -4592,16 +4619,16 @@
         <v>114</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G117" s="3" t="s">
         <v>140</v>
       </c>
       <c r="H117" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I117" s="4" t="n">
-        <v>11.01</v>
+        <v>11.86</v>
       </c>
     </row>
     <row r="118">
@@ -4621,16 +4648,16 @@
         <v>114</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G118" s="3" t="s">
         <v>141</v>
       </c>
       <c r="H118" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I118" s="4" t="n">
-        <v>11.68</v>
+        <v>16</v>
       </c>
     </row>
     <row r="119">
@@ -4650,16 +4677,16 @@
         <v>114</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>142</v>
       </c>
       <c r="H119" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I119" s="4" t="n">
-        <v>12.94</v>
+        <v>16.87</v>
       </c>
     </row>
     <row r="120">
@@ -4679,7 +4706,7 @@
         <v>114</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G120" s="3" t="s">
         <v>143</v>
@@ -4688,7 +4715,7 @@
         <v>0</v>
       </c>
       <c r="I120" s="4" t="n">
-        <v>14.96</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="121">
@@ -4708,7 +4735,7 @@
         <v>114</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G121" s="3" t="s">
         <v>144</v>
@@ -4717,7 +4744,7 @@
         <v>0</v>
       </c>
       <c r="I121" s="4" t="n">
-        <v>21.26</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="122">
@@ -4737,7 +4764,7 @@
         <v>148</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G122" s="3" t="s">
         <v>149</v>
@@ -4746,7 +4773,7 @@
         <v>1</v>
       </c>
       <c r="I122" s="4" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="123">
@@ -4766,7 +4793,7 @@
         <v>148</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G123" s="3" t="s">
         <v>150</v>
@@ -4775,7 +4802,7 @@
         <v>1</v>
       </c>
       <c r="I123" s="4" t="n">
-        <v>3.84</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="124">
@@ -4795,7 +4822,7 @@
         <v>148</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>151</v>
@@ -4804,7 +4831,7 @@
         <v>1</v>
       </c>
       <c r="I124" s="4" t="n">
-        <v>4.1</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="125">
@@ -4824,7 +4851,7 @@
         <v>148</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G125" s="3" t="s">
         <v>152</v>
@@ -4833,7 +4860,7 @@
         <v>1</v>
       </c>
       <c r="I125" s="4" t="n">
-        <v>4.52</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="126">
@@ -4853,7 +4880,7 @@
         <v>148</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G126" s="3" t="s">
         <v>153</v>
@@ -4862,7 +4889,7 @@
         <v>1</v>
       </c>
       <c r="I126" s="4" t="n">
-        <v>4.82</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="127">
@@ -4882,7 +4909,7 @@
         <v>148</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G127" s="3" t="s">
         <v>154</v>
@@ -4891,7 +4918,7 @@
         <v>1</v>
       </c>
       <c r="I127" s="4" t="n">
-        <v>4.99</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="128">
@@ -4911,7 +4938,7 @@
         <v>148</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G128" s="3" t="s">
         <v>155</v>
@@ -4920,7 +4947,7 @@
         <v>1</v>
       </c>
       <c r="I128" s="4" t="n">
-        <v>5.67</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="129">
@@ -4940,7 +4967,7 @@
         <v>148</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G129" s="3" t="s">
         <v>156</v>
@@ -4949,7 +4976,7 @@
         <v>1</v>
       </c>
       <c r="I129" s="4" t="n">
-        <v>5.67</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="130">
@@ -4969,7 +4996,7 @@
         <v>148</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G130" s="3" t="s">
         <v>157</v>
@@ -4978,7 +5005,7 @@
         <v>1</v>
       </c>
       <c r="I130" s="4" t="n">
-        <v>7.6</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="131">
@@ -4998,16 +5025,16 @@
         <v>148</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G131" s="3" t="s">
         <v>158</v>
       </c>
       <c r="H131" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I131" s="4" t="n">
-        <v>10.73</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="132">
@@ -5027,7 +5054,7 @@
         <v>148</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G132" s="3" t="s">
         <v>159</v>
@@ -5036,7 +5063,7 @@
         <v>0</v>
       </c>
       <c r="I132" s="4" t="n">
-        <v>10.8</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="133">
@@ -5056,7 +5083,7 @@
         <v>148</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G133" s="3" t="s">
         <v>160</v>
@@ -5065,7 +5092,7 @@
         <v>1</v>
       </c>
       <c r="I133" s="4" t="n">
-        <v>15.92</v>
+        <v>7.74</v>
       </c>
     </row>
     <row r="134">
@@ -5091,10 +5118,10 @@
         <v>161</v>
       </c>
       <c r="H134" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I134" s="4" t="n">
-        <v>1.83</v>
+        <v>9.2</v>
       </c>
     </row>
     <row r="135">
@@ -5123,7 +5150,7 @@
         <v>1</v>
       </c>
       <c r="I135" s="4" t="n">
-        <v>2.15</v>
+        <v>12.56</v>
       </c>
     </row>
     <row r="136">
@@ -5152,7 +5179,7 @@
         <v>1</v>
       </c>
       <c r="I136" s="4" t="n">
-        <v>2.51</v>
+        <v>14.01</v>
       </c>
     </row>
     <row r="137">
@@ -5172,7 +5199,7 @@
         <v>148</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G137" s="3" t="s">
         <v>164</v>
@@ -5181,7 +5208,7 @@
         <v>1</v>
       </c>
       <c r="I137" s="4" t="n">
-        <v>2.66</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="138">
@@ -5201,7 +5228,7 @@
         <v>148</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G138" s="3" t="s">
         <v>165</v>
@@ -5210,7 +5237,7 @@
         <v>1</v>
       </c>
       <c r="I138" s="4" t="n">
-        <v>4.24</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="139">
@@ -5230,7 +5257,7 @@
         <v>148</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G139" s="3" t="s">
         <v>166</v>
@@ -5239,7 +5266,7 @@
         <v>1</v>
       </c>
       <c r="I139" s="4" t="n">
-        <v>4.36</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="140">
@@ -5259,7 +5286,7 @@
         <v>148</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G140" s="3" t="s">
         <v>167</v>
@@ -5268,7 +5295,7 @@
         <v>1</v>
       </c>
       <c r="I140" s="4" t="n">
-        <v>4.36</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="141">
@@ -5288,7 +5315,7 @@
         <v>148</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G141" s="3" t="s">
         <v>168</v>
@@ -5297,7 +5324,7 @@
         <v>1</v>
       </c>
       <c r="I141" s="4" t="n">
-        <v>4.39</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="142">
@@ -5317,7 +5344,7 @@
         <v>148</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G142" s="3" t="s">
         <v>169</v>
@@ -5326,7 +5353,7 @@
         <v>1</v>
       </c>
       <c r="I142" s="4" t="n">
-        <v>7</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="143">
@@ -5346,7 +5373,7 @@
         <v>148</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G143" s="3" t="s">
         <v>170</v>
@@ -5355,7 +5382,7 @@
         <v>1</v>
       </c>
       <c r="I143" s="4" t="n">
-        <v>7.75</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="144">
@@ -5375,16 +5402,16 @@
         <v>148</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G144" s="3" t="s">
         <v>171</v>
       </c>
       <c r="H144" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I144" s="4" t="n">
-        <v>7.87</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="145">
@@ -5404,7 +5431,7 @@
         <v>148</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G145" s="3" t="s">
         <v>172</v>
@@ -5413,7 +5440,7 @@
         <v>1</v>
       </c>
       <c r="I145" s="4" t="n">
-        <v>9.59</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="146">
@@ -5433,7 +5460,7 @@
         <v>148</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G146" s="3" t="s">
         <v>173</v>
@@ -5442,7 +5469,7 @@
         <v>1</v>
       </c>
       <c r="I146" s="4" t="n">
-        <v>10.91</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="147">
@@ -5462,7 +5489,7 @@
         <v>148</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G147" s="3" t="s">
         <v>174</v>
@@ -5471,7 +5498,7 @@
         <v>0</v>
       </c>
       <c r="I147" s="4" t="n">
-        <v>12.35</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="148">
@@ -5491,16 +5518,16 @@
         <v>148</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G148" s="3" t="s">
         <v>175</v>
       </c>
       <c r="H148" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I148" s="4" t="n">
-        <v>16.66</v>
+        <v>11.08</v>
       </c>
     </row>
     <row r="149">
@@ -5520,16 +5547,16 @@
         <v>148</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G149" s="3" t="s">
         <v>176</v>
       </c>
       <c r="H149" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I149" s="4" t="n">
-        <v>17.57</v>
+        <v>11.22</v>
       </c>
     </row>
     <row r="150">
@@ -5549,7 +5576,7 @@
         <v>148</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>177</v>
@@ -5558,7 +5585,7 @@
         <v>0</v>
       </c>
       <c r="I150" s="4" t="n">
-        <v>18.43</v>
+        <v>15.88</v>
       </c>
     </row>
     <row r="151">
@@ -5578,7 +5605,7 @@
         <v>148</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G151" s="3" t="s">
         <v>178</v>
@@ -5587,12 +5614,12 @@
         <v>0</v>
       </c>
       <c r="I151" s="4" t="n">
-        <v>18.43</v>
+        <v>17.89</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>179</v>
@@ -5616,12 +5643,12 @@
         <v>1</v>
       </c>
       <c r="I152" s="4" t="n">
-        <v>2.42</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>179</v>
@@ -5645,12 +5672,12 @@
         <v>1</v>
       </c>
       <c r="I153" s="4" t="n">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>179</v>
@@ -5674,12 +5701,12 @@
         <v>1</v>
       </c>
       <c r="I154" s="4" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>179</v>
@@ -5703,12 +5730,12 @@
         <v>1</v>
       </c>
       <c r="I155" s="4" t="n">
-        <v>2.73</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>179</v>
@@ -5732,12 +5759,12 @@
         <v>1</v>
       </c>
       <c r="I156" s="4" t="n">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>179</v>
@@ -5761,12 +5788,12 @@
         <v>1</v>
       </c>
       <c r="I157" s="4" t="n">
-        <v>4.24</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>179</v>
@@ -5790,12 +5817,12 @@
         <v>1</v>
       </c>
       <c r="I158" s="4" t="n">
-        <v>4.24</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>179</v>
@@ -5819,12 +5846,12 @@
         <v>1</v>
       </c>
       <c r="I159" s="4" t="n">
-        <v>4.66</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>179</v>
@@ -5848,12 +5875,12 @@
         <v>1</v>
       </c>
       <c r="I160" s="4" t="n">
-        <v>5.44</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>179</v>
@@ -5874,15 +5901,15 @@
         <v>192</v>
       </c>
       <c r="H161" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I161" s="4" t="n">
-        <v>6.99</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>179</v>
@@ -5903,15 +5930,15 @@
         <v>193</v>
       </c>
       <c r="H162" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I162" s="4" t="n">
-        <v>7.36</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>179</v>
@@ -5932,15 +5959,15 @@
         <v>194</v>
       </c>
       <c r="H163" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I163" s="4" t="n">
-        <v>7.74</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>179</v>
@@ -5961,15 +5988,15 @@
         <v>195</v>
       </c>
       <c r="H164" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I164" s="4" t="n">
-        <v>9.2</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>179</v>
@@ -5993,12 +6020,12 @@
         <v>1</v>
       </c>
       <c r="I165" s="4" t="n">
-        <v>12.55</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>179</v>
@@ -6019,15 +6046,15 @@
         <v>197</v>
       </c>
       <c r="H166" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I166" s="4" t="n">
-        <v>14</v>
+        <v>14.27</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>179</v>
@@ -6051,12 +6078,12 @@
         <v>1</v>
       </c>
       <c r="I167" s="4" t="n">
-        <v>2.25</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>179</v>
@@ -6080,12 +6107,12 @@
         <v>1</v>
       </c>
       <c r="I168" s="4" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>179</v>
@@ -6109,12 +6136,12 @@
         <v>1</v>
       </c>
       <c r="I169" s="4" t="n">
-        <v>3.29</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>179</v>
@@ -6138,12 +6165,12 @@
         <v>1</v>
       </c>
       <c r="I170" s="4" t="n">
-        <v>3.87</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>179</v>
@@ -6167,12 +6194,12 @@
         <v>1</v>
       </c>
       <c r="I171" s="4" t="n">
-        <v>4.61</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>179</v>
@@ -6196,12 +6223,12 @@
         <v>1</v>
       </c>
       <c r="I172" s="4" t="n">
-        <v>5.2</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B173" s="3" t="s">
         <v>179</v>
@@ -6225,12 +6252,12 @@
         <v>1</v>
       </c>
       <c r="I173" s="4" t="n">
-        <v>5.2</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>179</v>
@@ -6254,12 +6281,12 @@
         <v>1</v>
       </c>
       <c r="I174" s="4" t="n">
-        <v>6.73</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B175" s="3" t="s">
         <v>179</v>
@@ -6283,12 +6310,12 @@
         <v>1</v>
       </c>
       <c r="I175" s="4" t="n">
-        <v>6.92</v>
+        <v>7.54</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>179</v>
@@ -6309,15 +6336,15 @@
         <v>207</v>
       </c>
       <c r="H176" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I176" s="4" t="n">
-        <v>7.52</v>
+        <v>11.28</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>179</v>
@@ -6338,15 +6365,15 @@
         <v>208</v>
       </c>
       <c r="H177" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I177" s="4" t="n">
-        <v>10.4</v>
+        <v>12.38</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>179</v>
@@ -6367,15 +6394,15 @@
         <v>209</v>
       </c>
       <c r="H178" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I178" s="4" t="n">
-        <v>11.33</v>
+        <v>13.29</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>179</v>
@@ -6396,15 +6423,15 @@
         <v>210</v>
       </c>
       <c r="H179" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I179" s="4" t="n">
-        <v>11.48</v>
+        <v>14.65</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>179</v>
@@ -6425,15 +6452,15 @@
         <v>211</v>
       </c>
       <c r="H180" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I180" s="4" t="n">
-        <v>16.25</v>
+        <v>15.45</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>179</v>
@@ -6457,7 +6484,7 @@
         <v>0</v>
       </c>
       <c r="I181" s="4" t="n">
-        <v>18.31</v>
+        <v>16.14</v>
       </c>
     </row>
     <row r="182">
@@ -6477,7 +6504,7 @@
         <v>216</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G182" s="3" t="s">
         <v>217</v>
@@ -6486,7 +6513,7 @@
         <v>1</v>
       </c>
       <c r="I182" s="4" t="n">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="183">
@@ -6506,7 +6533,7 @@
         <v>216</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G183" s="3" t="s">
         <v>218</v>
@@ -6515,7 +6542,7 @@
         <v>1</v>
       </c>
       <c r="I183" s="4" t="n">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="184">
@@ -6535,7 +6562,7 @@
         <v>216</v>
       </c>
       <c r="F184" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G184" s="3" t="s">
         <v>219</v>
@@ -6544,7 +6571,7 @@
         <v>1</v>
       </c>
       <c r="I184" s="4" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="185">
@@ -6564,7 +6591,7 @@
         <v>216</v>
       </c>
       <c r="F185" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G185" s="3" t="s">
         <v>220</v>
@@ -6573,7 +6600,7 @@
         <v>1</v>
       </c>
       <c r="I185" s="4" t="n">
-        <v>3.11</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="186">
@@ -6593,7 +6620,7 @@
         <v>216</v>
       </c>
       <c r="F186" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G186" s="3" t="s">
         <v>221</v>
@@ -6602,7 +6629,7 @@
         <v>1</v>
       </c>
       <c r="I186" s="4" t="n">
-        <v>3.11</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="187">
@@ -6622,7 +6649,7 @@
         <v>216</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G187" s="3" t="s">
         <v>222</v>
@@ -6631,7 +6658,7 @@
         <v>1</v>
       </c>
       <c r="I187" s="4" t="n">
-        <v>3.56</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="188">
@@ -6651,7 +6678,7 @@
         <v>216</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G188" s="3" t="s">
         <v>223</v>
@@ -6660,7 +6687,7 @@
         <v>1</v>
       </c>
       <c r="I188" s="4" t="n">
-        <v>4.04</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="189">
@@ -6680,7 +6707,7 @@
         <v>216</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G189" s="3" t="s">
         <v>224</v>
@@ -6689,7 +6716,7 @@
         <v>1</v>
       </c>
       <c r="I189" s="4" t="n">
-        <v>4.04</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="190">
@@ -6709,7 +6736,7 @@
         <v>216</v>
       </c>
       <c r="F190" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>225</v>
@@ -6718,7 +6745,7 @@
         <v>1</v>
       </c>
       <c r="I190" s="4" t="n">
-        <v>4.57</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="191">
@@ -6738,7 +6765,7 @@
         <v>216</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G191" s="3" t="s">
         <v>226</v>
@@ -6747,7 +6774,7 @@
         <v>1</v>
       </c>
       <c r="I191" s="4" t="n">
-        <v>5.35</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="192">
@@ -6767,7 +6794,7 @@
         <v>216</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G192" s="3" t="s">
         <v>227</v>
@@ -6776,7 +6803,7 @@
         <v>1</v>
       </c>
       <c r="I192" s="4" t="n">
-        <v>5.5</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="193">
@@ -6796,7 +6823,7 @@
         <v>216</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>228</v>
@@ -6805,7 +6832,7 @@
         <v>0</v>
       </c>
       <c r="I193" s="4" t="n">
-        <v>10.32</v>
+        <v>12.07</v>
       </c>
     </row>
     <row r="194">
@@ -6825,16 +6852,16 @@
         <v>216</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G194" s="3" t="s">
         <v>229</v>
       </c>
       <c r="H194" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I194" s="4" t="n">
-        <v>10.48</v>
+        <v>12.46</v>
       </c>
     </row>
     <row r="195">
@@ -6854,16 +6881,16 @@
         <v>216</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>230</v>
       </c>
       <c r="H195" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I195" s="4" t="n">
-        <v>11.97</v>
+        <v>13.55</v>
       </c>
     </row>
     <row r="196">
@@ -6883,16 +6910,16 @@
         <v>216</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G196" s="3" t="s">
         <v>231</v>
       </c>
       <c r="H196" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I196" s="4" t="n">
-        <v>14.27</v>
+        <v>13.62</v>
       </c>
     </row>
     <row r="197">
@@ -6921,7 +6948,7 @@
         <v>1</v>
       </c>
       <c r="I197" s="4" t="n">
-        <v>1.86</v>
+        <v>15.86</v>
       </c>
     </row>
     <row r="198">
@@ -6941,7 +6968,7 @@
         <v>216</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G198" s="3" t="s">
         <v>233</v>
@@ -6950,7 +6977,7 @@
         <v>1</v>
       </c>
       <c r="I198" s="4" t="n">
-        <v>2.74</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="199">
@@ -6970,7 +6997,7 @@
         <v>216</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G199" s="3" t="s">
         <v>234</v>
@@ -6979,7 +7006,7 @@
         <v>1</v>
       </c>
       <c r="I199" s="4" t="n">
-        <v>3.73</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="200">
@@ -6999,7 +7026,7 @@
         <v>216</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G200" s="3" t="s">
         <v>235</v>
@@ -7008,7 +7035,7 @@
         <v>1</v>
       </c>
       <c r="I200" s="4" t="n">
-        <v>4.45</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="201">
@@ -7028,7 +7055,7 @@
         <v>216</v>
       </c>
       <c r="F201" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G201" s="3" t="s">
         <v>236</v>
@@ -7037,7 +7064,7 @@
         <v>1</v>
       </c>
       <c r="I201" s="4" t="n">
-        <v>4.46</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="202">
@@ -7057,7 +7084,7 @@
         <v>216</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G202" s="3" t="s">
         <v>237</v>
@@ -7066,7 +7093,7 @@
         <v>1</v>
       </c>
       <c r="I202" s="4" t="n">
-        <v>4.95</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="203">
@@ -7086,7 +7113,7 @@
         <v>216</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G203" s="3" t="s">
         <v>238</v>
@@ -7095,7 +7122,7 @@
         <v>1</v>
       </c>
       <c r="I203" s="4" t="n">
-        <v>4.98</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="204">
@@ -7115,7 +7142,7 @@
         <v>216</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G204" s="3" t="s">
         <v>239</v>
@@ -7124,7 +7151,7 @@
         <v>1</v>
       </c>
       <c r="I204" s="4" t="n">
-        <v>4.98</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="205">
@@ -7144,7 +7171,7 @@
         <v>216</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G205" s="3" t="s">
         <v>240</v>
@@ -7153,7 +7180,7 @@
         <v>1</v>
       </c>
       <c r="I205" s="4" t="n">
-        <v>7.54</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="206">
@@ -7173,16 +7200,16 @@
         <v>216</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G206" s="3" t="s">
         <v>241</v>
       </c>
       <c r="H206" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I206" s="4" t="n">
-        <v>11.28</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="207">
@@ -7202,7 +7229,7 @@
         <v>216</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G207" s="3" t="s">
         <v>242</v>
@@ -7211,7 +7238,7 @@
         <v>1</v>
       </c>
       <c r="I207" s="4" t="n">
-        <v>12.38</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="208">
@@ -7231,7 +7258,7 @@
         <v>216</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G208" s="3" t="s">
         <v>243</v>
@@ -7240,7 +7267,7 @@
         <v>1</v>
       </c>
       <c r="I208" s="4" t="n">
-        <v>13.29</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="209">
@@ -7260,16 +7287,16 @@
         <v>216</v>
       </c>
       <c r="F209" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G209" s="3" t="s">
         <v>244</v>
       </c>
       <c r="H209" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I209" s="4" t="n">
-        <v>14.65</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="210">
@@ -7289,16 +7316,16 @@
         <v>216</v>
       </c>
       <c r="F210" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G210" s="3" t="s">
         <v>245</v>
       </c>
       <c r="H210" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I210" s="4" t="n">
-        <v>15.45</v>
+        <v>15.87</v>
       </c>
     </row>
     <row r="211">
@@ -7318,7 +7345,7 @@
         <v>216</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G211" s="3" t="s">
         <v>246</v>
@@ -7327,12 +7354,12 @@
         <v>0</v>
       </c>
       <c r="I211" s="4" t="n">
-        <v>16.14</v>
+        <v>18.22</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="B212" s="3" t="s">
         <v>247</v>
@@ -7341,27 +7368,27 @@
         <v>248</v>
       </c>
       <c r="D212" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E212" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="E212" s="3" t="s">
+      <c r="F212" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G212" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="F212" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G212" s="3" t="s">
-        <v>251</v>
-      </c>
       <c r="H212" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I212" s="4" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="B213" s="3" t="s">
         <v>247</v>
@@ -7370,27 +7397,27 @@
         <v>248</v>
       </c>
       <c r="D213" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E213" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="E213" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="F213" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H213" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I213" s="4" t="n">
-        <v>2.52</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="B214" s="3" t="s">
         <v>247</v>
@@ -7399,27 +7426,27 @@
         <v>248</v>
       </c>
       <c r="D214" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E214" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="E214" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="F214" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H214" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I214" s="4" t="n">
-        <v>3.07</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="B215" s="3" t="s">
         <v>247</v>
@@ -7428,27 +7455,27 @@
         <v>248</v>
       </c>
       <c r="D215" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E215" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="E215" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="F215" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H215" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I215" s="4" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="B216" s="3" t="s">
         <v>247</v>
@@ -7457,27 +7484,27 @@
         <v>248</v>
       </c>
       <c r="D216" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E216" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="E216" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="F216" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H216" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I216" s="4" t="n">
-        <v>3.72</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="B217" s="3" t="s">
         <v>247</v>
@@ -7486,27 +7513,27 @@
         <v>248</v>
       </c>
       <c r="D217" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E217" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="E217" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="F217" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H217" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I217" s="4" t="n">
-        <v>3.89</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="B218" s="3" t="s">
         <v>247</v>
@@ -7515,27 +7542,27 @@
         <v>248</v>
       </c>
       <c r="D218" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E218" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="E218" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="F218" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H218" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I218" s="4" t="n">
-        <v>4.19</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="B219" s="3" t="s">
         <v>247</v>
@@ -7544,27 +7571,27 @@
         <v>248</v>
       </c>
       <c r="D219" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E219" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="E219" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="F219" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H219" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I219" s="4" t="n">
-        <v>4.19</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="B220" s="3" t="s">
         <v>247</v>
@@ -7573,27 +7600,27 @@
         <v>248</v>
       </c>
       <c r="D220" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E220" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="E220" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="F220" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H220" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I220" s="4" t="n">
-        <v>4.62</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="B221" s="3" t="s">
         <v>247</v>
@@ -7602,27 +7629,27 @@
         <v>248</v>
       </c>
       <c r="D221" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E221" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="E221" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="F221" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H221" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I221" s="4" t="n">
-        <v>4.93</v>
+        <v>7.81</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="B222" s="3" t="s">
         <v>247</v>
@@ -7631,27 +7658,27 @@
         <v>248</v>
       </c>
       <c r="D222" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E222" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="E222" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="F222" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H222" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I222" s="4" t="n">
-        <v>10.17</v>
+        <v>8.36</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="B223" s="3" t="s">
         <v>247</v>
@@ -7660,27 +7687,27 @@
         <v>248</v>
       </c>
       <c r="D223" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E223" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="E223" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="F223" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H223" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I223" s="4" t="n">
-        <v>12.07</v>
+        <v>12.37</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="B224" s="3" t="s">
         <v>247</v>
@@ -7689,27 +7716,27 @@
         <v>248</v>
       </c>
       <c r="D224" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E224" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="E224" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="F224" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H224" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I224" s="4" t="n">
-        <v>12.46</v>
+        <v>22.26</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="B225" s="3" t="s">
         <v>247</v>
@@ -7718,27 +7745,27 @@
         <v>248</v>
       </c>
       <c r="D225" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E225" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="E225" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="F225" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H225" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I225" s="4" t="n">
-        <v>13.55</v>
+        <v>27.08</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="B226" s="3" t="s">
         <v>247</v>
@@ -7747,27 +7774,27 @@
         <v>248</v>
       </c>
       <c r="D226" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E226" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="E226" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="F226" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H226" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I226" s="4" t="n">
-        <v>13.62</v>
+        <v>29.36</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="B227" s="3" t="s">
         <v>247</v>
@@ -7776,27 +7803,27 @@
         <v>248</v>
       </c>
       <c r="D227" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E227" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="E227" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="F227" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H227" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I227" s="4" t="n">
-        <v>15.86</v>
+        <v>41.73</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="B228" s="3" t="s">
         <v>247</v>
@@ -7805,27 +7832,27 @@
         <v>248</v>
       </c>
       <c r="D228" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E228" s="3" t="s">
         <v>249</v>
-      </c>
-      <c r="E228" s="3" t="s">
-        <v>250</v>
       </c>
       <c r="F228" s="3" t="s">
         <v>249</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H228" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I228" s="4" t="n">
-        <v>2.49</v>
+        <v>42.45</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="B229" s="3" t="s">
         <v>247</v>
@@ -7834,27 +7861,27 @@
         <v>248</v>
       </c>
       <c r="D229" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E229" s="3" t="s">
         <v>249</v>
-      </c>
-      <c r="E229" s="3" t="s">
-        <v>250</v>
       </c>
       <c r="F229" s="3" t="s">
         <v>249</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H229" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I229" s="4" t="n">
-        <v>2.75</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="B230" s="3" t="s">
         <v>247</v>
@@ -7863,341 +7890,573 @@
         <v>248</v>
       </c>
       <c r="D230" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E230" s="3" t="s">
         <v>249</v>
-      </c>
-      <c r="E230" s="3" t="s">
-        <v>250</v>
       </c>
       <c r="F230" s="3" t="s">
         <v>249</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H230" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I230" s="4" t="n">
-        <v>3.12</v>
+        <v>56.84</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>46236</v>
+        <v>46241</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>247</v>
+        <v>43</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>250</v>
+        <v>46</v>
       </c>
       <c r="F231" s="3" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H231" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I231" s="4" t="n">
-        <v>3.12</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>46236</v>
+        <v>46241</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>247</v>
+        <v>43</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>250</v>
+        <v>46</v>
       </c>
       <c r="F232" s="3" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H232" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I232" s="4" t="n">
-        <v>3.83</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>46236</v>
+        <v>46241</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>247</v>
+        <v>43</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>250</v>
+        <v>46</v>
       </c>
       <c r="F233" s="3" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="G233" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H233" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I233" s="4" t="n">
-        <v>3.83</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>46236</v>
+        <v>46241</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>247</v>
+        <v>43</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>250</v>
+        <v>46</v>
       </c>
       <c r="F234" s="3" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H234" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I234" s="4" t="n">
-        <v>4.36</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>46236</v>
+        <v>46241</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>247</v>
+        <v>43</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>250</v>
+        <v>46</v>
       </c>
       <c r="F235" s="3" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H235" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I235" s="4" t="n">
-        <v>5.25</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>46236</v>
+        <v>46241</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>247</v>
+        <v>43</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>250</v>
+        <v>46</v>
       </c>
       <c r="F236" s="3" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H236" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I236" s="4" t="n">
-        <v>5.36</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>46236</v>
+        <v>46241</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>247</v>
+        <v>43</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>250</v>
+        <v>46</v>
       </c>
       <c r="F237" s="3" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H237" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I237" s="4" t="n">
-        <v>5.37</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
-        <v>46236</v>
+        <v>46241</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>247</v>
+        <v>43</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>250</v>
+        <v>46</v>
       </c>
       <c r="F238" s="3" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H238" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I238" s="4" t="n">
-        <v>10.01</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
-        <v>46236</v>
+        <v>46241</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>247</v>
+        <v>43</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>250</v>
+        <v>46</v>
       </c>
       <c r="F239" s="3" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H239" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I239" s="4" t="n">
-        <v>10.13</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>46236</v>
+        <v>46241</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>247</v>
+        <v>43</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>250</v>
+        <v>46</v>
       </c>
       <c r="F240" s="3" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="G240" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H240" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I240" s="4" t="n">
-        <v>15.87</v>
+        <v>7.96</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>46236</v>
+        <v>46241</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>247</v>
+        <v>43</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>250</v>
+        <v>46</v>
       </c>
       <c r="F241" s="3" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H241" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I241" s="4" t="n">
+        <v>8.12</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C242" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D242" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E242" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F242" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="G242" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="H242" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="I241" s="4" t="n">
-        <v>18.22</v>
+      <c r="I242" s="4" t="n">
+        <v>10.28</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B243" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C243" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D243" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E243" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F243" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="G243" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="H243" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I243" s="4" t="n">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B244" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C244" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E244" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F244" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="G244" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="H244" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I244" s="4" t="n">
+        <v>12.09</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B245" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C245" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D245" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E245" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F245" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="G245" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="H245" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I245" s="4" t="n">
+        <v>12.39</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B246" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C246" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D246" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E246" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F246" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="G246" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="H246" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I246" s="4" t="n">
+        <v>17.64</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B247" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C247" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D247" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E247" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F247" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="G247" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="H247" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I247" s="4" t="n">
+        <v>24.71</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C248" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D248" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E248" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F248" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="G248" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="H248" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I248" s="4" t="n">
+        <v>32.77</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B249" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C249" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D249" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E249" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F249" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="G249" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="H249" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I249" s="4" t="n">
+        <v>34.39</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_anytime_tryscorers.xlsx
+++ b/files/NRL_anytime_tryscorers.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="289">
   <si>
     <t xml:space="preserve">Date Local</t>
   </si>
@@ -41,69 +41,789 @@
     <t xml:space="preserve">Anytimeodds</t>
   </si>
   <si>
-    <t xml:space="preserve">18:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched-2026-20260731-1800-st-george-illawarra-dragons-dolphins</t>
+    <t xml:space="preserve">14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260802-1400-cronulla-sutherland-sharks-south-sydney-rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronaldo Mulitalo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sione Katoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">William Kennedy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayal Iro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braydon Trindall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesse Ramien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Briton Nikora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teig Wilton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicholas Hynes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Hazelton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesse Colquhoun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siosifa Talakai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blayke Brailey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron McInnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oregon Kaufusi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Johnston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campbell Graham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cody Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Dufty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Wighton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latrell Siegwalt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keaon Koloamatangi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Elliott</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashton Ward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Sullivan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brandon Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tevita Tatola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jye Gray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John Radel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamie Humphreys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260802-1605-wests-tigers-parramatta-eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wests tigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Addo-Carr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian Kelly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiah Iongi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Penisini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Samrani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitchell Moses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kelma Tuilagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kitione Kautoga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronald Volkman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tallyn Da Silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack De Belin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Paulo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joash Papalii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Tuivaiti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunia Turuva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jahream Bula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Doueihi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Tupou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samuela Fainu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sione Fainu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heamasi Makasini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick Herbert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jarome Luai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apisai Koroisau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Seyfarth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terrell May</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fonua Pole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starford To'a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260806-1950-gold-coast-titans-north-queensland-cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phillip Sami</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dean Ieremia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jojo Fifita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Campbell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keano Kini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AJ Brimson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arama Hau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beau Fermor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver Pascoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zane Harrison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tino Fa'asuamaleaui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Bai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chris Randall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurtis Morrin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klese Haas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Verrills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braidon Burns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murray Taulagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scott Drinkwater</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Chester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zac Laybutt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heilum Luki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremiah Nanai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Clifford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaxon Purdue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soni Luke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reuben Cotter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam McIntyre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Mikaele</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coen Hess</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260807-2000-sydney-roosters-canterbury-bankstown-bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jethro Rinakama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Kiraz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matt Burton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Tracey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enari Tuala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viliame Kikau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Preston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lachlan Galvin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stephen Crichton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jonathan Sua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Mann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bailey Hayward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Curran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaeman Salmon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark Nawaqanitawase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tommy Talau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Tedesco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugo Savala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robert Toia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nat Butcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siua Wong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daly Cherry-Evans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reece Robson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Victor Radley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Watson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salesi Foketi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spencer Leniu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egan Butcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naufahu Whyte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260807-2000-warriors-penrith-panthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penrith panthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Jenkins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian To'o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaxen Edgar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casey McLean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paul Alamoti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiah Papali'i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathan Cleary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freddy Lussick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lindsay Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Izack Tago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaah Yeo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Cogger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Henry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moses Leota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scott Sorensen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alofiana Khan-Pereira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dallin Watene-Zelezniak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leka Halasima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ali Leiataua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charnze Nicoll-Klokstad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Capewell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Laban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chanel Harris-Tavita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Te Maire Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wayde Egan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Fisher-Harris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Healey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erin Clark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Metcalf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260808-1500-melbourne-storm-manly-warringah-sea-eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manly-warringah sea eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moses Leo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sualauvi Faalogo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siulagi Tuimalatu-Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manaia Waitere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyran Wishart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Clarke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oryn Keeley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nick Meaney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hayden Watson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trent Toelau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stefano Utoikamanu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe Chan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shawn Blore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trent Loiero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angus Hinchey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jai Bowden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alec MacDonald</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Hetherington</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260808-1730-dolphins-brisbane-broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josiah Karapani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grant Anderson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reece Walsh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezra Mam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kotoni Staggs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Willison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Riki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deine Mariner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Reynolds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Walters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Talty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cory Paix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gehamat Shibasaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payne Haas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Va'a Semu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamiso Tabuai-Fidow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selwyn Cobbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamayne Isaako</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herbie Farnworth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Bostock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connelly Lemuelu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kulikefu Finefeuiaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kodi Nikorima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremy Marshall-King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ray Stone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Plath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiya Katoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Flegler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Donoghoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Felise Kaufusi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260809-1400-canberra-raiders-newcastle-knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Savage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaeo Weekes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sebastian Kris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jed Stuart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Timoko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Strange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zac Hosking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ata Mariota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owen Pattie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Sanders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe Roddy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corey Horsburgh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Starling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joseph Tapine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daine Laurie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominic Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greg Marzhew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fletcher Sharpe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bradman Best</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kalyn Ponga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jermaine McEwen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francis Manuleleua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dane Gagai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trey Mooney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandon Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fletcher Hunt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phoenix Crossland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyson Frizell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brodie Jones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cody Hopwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched-2026-20260809-1605-st-george-illawarra-dragons-cronulla-sutherland-sharks</t>
   </si>
   <si>
     <t xml:space="preserve">st george-illawarra dragons</t>
   </si>
   <si>
-    <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamiso Tabuai-Fidow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selwyn Cobbo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamayne Isaako</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herbie Farnworth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Bostock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connelly Lemuelu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kulikefu Finefeuiaki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kodi Nikorima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremy Marshall-King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ray Stone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Plath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiya Katoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Flegler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurt Donoghoe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Felise Kaufusi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morgan Knowles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Gilbert</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tyrell Sloan</t>
   </si>
   <si>
@@ -143,745 +863,22 @@
     <t xml:space="preserve">Daniel Atkinson</t>
   </si>
   <si>
-    <t xml:space="preserve">20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched-2026-20260731-2000-melbourne-storm-canterbury-bankstown-bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jethro Rinakama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Kiraz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matt Burton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Tracey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enari Tuala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viliame Kikau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Preston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lachlan Galvin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stephen Crichton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jonathan Sua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurt Mann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bailey Hayward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Curran</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaeman Salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moses Leo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sualauvi Faalogo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siulagi Tuimalatu-Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manaia Waitere</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyran Wishart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Clarke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oryn Keeley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nick Meaney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hayden Watson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trent Toelau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stefano Utoikamanu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joe Chan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shawn Blore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trent Loiero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angus Hinchey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched-2026-20260801-1500-gold-coast-titans-warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phillip Sami</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dean Ieremia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jojo Fifita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Campbell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keano Kini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AJ Brimson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arama Hau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beau Fermor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oliver Pascoe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zane Harrison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tino Fa'asuamaleaui</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Bai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chris Randall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurtis Morrin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alofiana Khan-Pereira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dallin Watene-Zelezniak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ali Leiataua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charnze Nicoll-Klokstad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurt Capewell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Laban</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leka Halasima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Pompey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chanel Harris-Tavita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Te Maire Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wayde Egan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Fisher-Harris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Healey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erin Clark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Metcalf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitchell Barnett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched-2026-20260801-1730-penrith-panthers-canberra-raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penrith panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Savage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaeo Weekes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sebastian Kris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jed Stuart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Timoko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan Strange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zac Hosking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ata Mariota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owen Pattie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan Sanders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joe Roddy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corey Horsburgh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Jenkins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian To'o</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaxen Edgar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casey McLean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paul Alamoti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiah Papali'i</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nathan Cleary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freddy Lussick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lindsay Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Izack Tago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaah Yeo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Cogger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Henry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moses Leota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scott Sorensen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Phillips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Cole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched-2026-20260801-1935-brisbane-broncos-newcastle-knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josiah Karapani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grant Anderson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reece Walsh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ezra Mam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kotoni Staggs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Willison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan Riki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deine Mariner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Reynolds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Walters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben Talty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cory Paix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gehamat Shibasaki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payne Haas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Va'a Semu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dominic Young</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greg Marzhew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fletcher Sharpe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bradman Best</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kalyn Ponga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jermaine McEwen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Francis Manuleleua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dane Gagai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trey Mooney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandon Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harrison Graham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fletcher Hunt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phoenix Crossland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyson Frizell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brodie Jones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched-2026-20260802-1400-cronulla-sutherland-sharks-south-sydney-rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">south sydney rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronaldo Mulitalo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sione Katoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">William Kennedy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kayal Iro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Braydon Trindall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jesse Ramien</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Briton Nikora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teig Wilton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicholas Hynes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Addin Fonua-Blake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Hazelton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siosifa Talakai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blayke Brailey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameron McInnes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Braden Hamlin-Uele</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Johnston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campbell Graham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cody Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Dufty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Wighton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latrell Siegwalt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keaon Koloamatangi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Euan Aitken</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashton Ward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Sullivan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brandon Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tevita Tatola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jye Gray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">John Radel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamie Humphreys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched-2026-20260802-1605-wests-tigers-parramatta-eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Addo-Carr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian Kelly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiah Iongi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Will Penisini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan Samrani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitchell Moses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kelma Tuilagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitione Kautoga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronald Volkman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tallyn Da Silva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack De Belin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Paulo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joash Papalii</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Tuivaiti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunia Turuva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jahream Bula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Doueihi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Tupou</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samuela Fainu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sione Fainu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heamasi Makasini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patrick Herbert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jarome Luai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apisai Koroisau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terrell May</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fonua Pole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Seyfarth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bunty Afoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched-2026-20260806-1950-gold-coast-titans-north-queensland-cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Braidon Burns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Murray Taulagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scott Drinkwater</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Chester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zac Laybutt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heilum Luki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremiah Nanai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Clifford</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaxon Purdue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soni Luke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reuben Cotter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam McIntyre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Mikaele</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coen Hess</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaiden Lahrs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kai O'Donnell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jason Taumalolo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Lodge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched-2026-20260807-2000-sydney-roosters-canterbury-bankstown-bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mark Nawaqanitawase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tommy Talau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Tedesco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hugo Savala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robert Toia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nat Butcher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siua Wong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daly Cherry-Evans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reece Robson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Victor Radley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Watson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salesi Foketi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spencer Leniu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Egan Butcher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Naufahu Whyte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reece Foley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taylor Losalu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cody Ramsey</t>
+    <t xml:space="preserve">Loko Jnr Pasifiki Tonga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan Couchman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Kerr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Halangahu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toby Couchman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emre Guler</t>
   </si>
 </sst>
 </file>
@@ -1229,7 +1226,7 @@
   <cols>
     <col min="1" max="1" width="9.285" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="9.285" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="64.165" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="68.4525" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="23.8625" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="25.5775" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="25.5775" hidden="0" customWidth="1"/>
@@ -1269,7 +1266,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>9</v>
@@ -1284,7 +1281,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>13</v>
@@ -1293,12 +1290,12 @@
         <v>1</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>9</v>
@@ -1313,7 +1310,7 @@
         <v>12</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>14</v>
@@ -1322,12 +1319,12 @@
         <v>1</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>9</v>
@@ -1342,7 +1339,7 @@
         <v>12</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>15</v>
@@ -1351,12 +1348,12 @@
         <v>1</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>2.17</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>9</v>
@@ -1371,7 +1368,7 @@
         <v>12</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>16</v>
@@ -1380,12 +1377,12 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>2.48</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>9</v>
@@ -1400,7 +1397,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>17</v>
@@ -1409,12 +1406,12 @@
         <v>1</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>9</v>
@@ -1429,7 +1426,7 @@
         <v>12</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>18</v>
@@ -1438,12 +1435,12 @@
         <v>1</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.21</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>9</v>
@@ -1458,7 +1455,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>19</v>
@@ -1467,12 +1464,12 @@
         <v>1</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4.21</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>9</v>
@@ -1487,7 +1484,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>20</v>
@@ -1496,12 +1493,12 @@
         <v>1</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>5.2</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>9</v>
@@ -1516,7 +1513,7 @@
         <v>12</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>21</v>
@@ -1525,12 +1522,12 @@
         <v>1</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>6.7</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>9</v>
@@ -1545,7 +1542,7 @@
         <v>12</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>22</v>
@@ -1554,12 +1551,12 @@
         <v>0</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>9.28</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>9</v>
@@ -1574,21 +1571,21 @@
         <v>12</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H12" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>9.81</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>9</v>
@@ -1603,21 +1600,21 @@
         <v>12</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H13" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>10.05</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>9</v>
@@ -1632,7 +1629,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>25</v>
@@ -1641,12 +1638,12 @@
         <v>1</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>10.07</v>
+        <v>9.64</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>9</v>
@@ -1661,21 +1658,21 @@
         <v>12</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H15" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>14.64</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>9</v>
@@ -1690,21 +1687,21 @@
         <v>12</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>27</v>
       </c>
       <c r="H16" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>15.27</v>
+        <v>13.08</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>9</v>
@@ -1728,12 +1725,12 @@
         <v>1</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>15.55</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>9</v>
@@ -1754,15 +1751,15 @@
         <v>29</v>
       </c>
       <c r="H18" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>15.89</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>9</v>
@@ -1777,7 +1774,7 @@
         <v>12</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>30</v>
@@ -1786,12 +1783,12 @@
         <v>1</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2.48</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>9</v>
@@ -1806,7 +1803,7 @@
         <v>12</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>31</v>
@@ -1815,12 +1812,12 @@
         <v>1</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.63</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>9</v>
@@ -1835,7 +1832,7 @@
         <v>12</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>32</v>
@@ -1844,12 +1841,12 @@
         <v>1</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.89</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>9</v>
@@ -1864,7 +1861,7 @@
         <v>12</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>33</v>
@@ -1873,12 +1870,12 @@
         <v>1</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.9</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>9</v>
@@ -1893,7 +1890,7 @@
         <v>12</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>34</v>
@@ -1902,12 +1899,12 @@
         <v>1</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>4.53</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>9</v>
@@ -1922,7 +1919,7 @@
         <v>12</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>35</v>
@@ -1931,12 +1928,12 @@
         <v>1</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4.53</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>9</v>
@@ -1951,21 +1948,21 @@
         <v>12</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>36</v>
       </c>
       <c r="H25" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>5.95</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>9</v>
@@ -1980,21 +1977,21 @@
         <v>12</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>37</v>
       </c>
       <c r="H26" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>6.14</v>
+        <v>11.42</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>9</v>
@@ -2009,7 +2006,7 @@
         <v>12</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>38</v>
@@ -2018,12 +2015,12 @@
         <v>1</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>6.18</v>
+        <v>12.54</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>9</v>
@@ -2038,7 +2035,7 @@
         <v>12</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>39</v>
@@ -2047,12 +2044,12 @@
         <v>1</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>6.71</v>
+        <v>13.46</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>9</v>
@@ -2067,21 +2064,21 @@
         <v>12</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>40</v>
       </c>
       <c r="H29" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>7.37</v>
+        <v>14.84</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>9</v>
@@ -2096,21 +2093,21 @@
         <v>12</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>41</v>
       </c>
       <c r="H30" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>10.66</v>
+        <v>15.64</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>9</v>
@@ -2125,7 +2122,7 @@
         <v>12</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>42</v>
@@ -2134,12 +2131,12 @@
         <v>0</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>15.24</v>
+        <v>16.34</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>43</v>
@@ -2163,12 +2160,12 @@
         <v>1</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2.54</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>43</v>
@@ -2192,12 +2189,12 @@
         <v>1</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>3.04</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>43</v>
@@ -2221,12 +2218,12 @@
         <v>1</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>3.63</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>43</v>
@@ -2250,12 +2247,12 @@
         <v>1</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>4.67</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>43</v>
@@ -2279,12 +2276,12 @@
         <v>1</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>4.81</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>43</v>
@@ -2308,12 +2305,12 @@
         <v>1</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>5.11</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>43</v>
@@ -2337,12 +2334,12 @@
         <v>1</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>5.11</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>43</v>
@@ -2366,12 +2363,12 @@
         <v>1</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>6.07</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>43</v>
@@ -2395,12 +2392,12 @@
         <v>1</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>6.88</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>43</v>
@@ -2421,15 +2418,15 @@
         <v>56</v>
       </c>
       <c r="H41" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>12.75</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>43</v>
@@ -2450,15 +2447,15 @@
         <v>57</v>
       </c>
       <c r="H42" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>13.13</v>
+        <v>9.72</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>43</v>
@@ -2479,15 +2476,15 @@
         <v>58</v>
       </c>
       <c r="H43" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>15.37</v>
+        <v>11.53</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>43</v>
@@ -2511,12 +2508,12 @@
         <v>0</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>16.03</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>43</v>
@@ -2537,15 +2534,15 @@
         <v>60</v>
       </c>
       <c r="H45" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>21.21</v>
+        <v>12.94</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>43</v>
@@ -2560,7 +2557,7 @@
         <v>46</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>61</v>
@@ -2569,12 +2566,12 @@
         <v>1</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>2.08</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>43</v>
@@ -2589,7 +2586,7 @@
         <v>46</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>62</v>
@@ -2598,12 +2595,12 @@
         <v>1</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>2.22</v>
+        <v>15.14</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>43</v>
@@ -2627,12 +2624,12 @@
         <v>1</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>3.13</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>43</v>
@@ -2656,12 +2653,12 @@
         <v>1</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>3.35</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>43</v>
@@ -2685,12 +2682,12 @@
         <v>1</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>3.61</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>43</v>
@@ -2714,12 +2711,12 @@
         <v>1</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>4.11</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>43</v>
@@ -2743,12 +2740,12 @@
         <v>1</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>4.11</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>43</v>
@@ -2772,12 +2769,12 @@
         <v>1</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>4.2</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>43</v>
@@ -2801,12 +2798,12 @@
         <v>1</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>4.78</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>43</v>
@@ -2830,12 +2827,12 @@
         <v>1</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>6.88</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>43</v>
@@ -2859,12 +2856,12 @@
         <v>1</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>8.84</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>43</v>
@@ -2888,12 +2885,12 @@
         <v>1</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>10.55</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>43</v>
@@ -2914,15 +2911,15 @@
         <v>73</v>
       </c>
       <c r="H58" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>15.57</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>43</v>
@@ -2943,15 +2940,15 @@
         <v>74</v>
       </c>
       <c r="H59" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>17.25</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>43</v>
@@ -2972,15 +2969,15 @@
         <v>75</v>
       </c>
       <c r="H60" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>17.97</v>
+        <v>16.47</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>43</v>
@@ -3004,12 +3001,12 @@
         <v>0</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>19.4</v>
+        <v>23.28</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>77</v>
@@ -3033,12 +3030,12 @@
         <v>1</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>2.47</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>77</v>
@@ -3062,12 +3059,12 @@
         <v>1</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>3.5</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>77</v>
@@ -3091,12 +3088,12 @@
         <v>1</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>3.85</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>77</v>
@@ -3120,12 +3117,12 @@
         <v>1</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>4.17</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>77</v>
@@ -3149,12 +3146,12 @@
         <v>1</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>4.49</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>77</v>
@@ -3178,12 +3175,12 @@
         <v>1</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>4.64</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>77</v>
@@ -3207,12 +3204,12 @@
         <v>1</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>4.99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>77</v>
@@ -3236,12 +3233,12 @@
         <v>1</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>4.99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>77</v>
@@ -3265,12 +3262,12 @@
         <v>1</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>6.16</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>77</v>
@@ -3294,12 +3291,12 @@
         <v>1</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>9.81</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>77</v>
@@ -3323,12 +3320,12 @@
         <v>1</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>9.94</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>77</v>
@@ -3352,12 +3349,12 @@
         <v>0</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>11.3</v>
+        <v>8.92</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>77</v>
@@ -3381,12 +3378,12 @@
         <v>1</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>11.54</v>
+        <v>9.11</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>77</v>
@@ -3410,12 +3407,12 @@
         <v>0</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>12.01</v>
+        <v>9.47</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>77</v>
@@ -3430,21 +3427,21 @@
         <v>80</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>95</v>
       </c>
       <c r="H76" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>1.69</v>
+        <v>19.15</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>77</v>
@@ -3459,21 +3456,21 @@
         <v>80</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>96</v>
       </c>
       <c r="H77" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>1.95</v>
+        <v>19.67</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>77</v>
@@ -3497,12 +3494,12 @@
         <v>1</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>3.59</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>77</v>
@@ -3526,12 +3523,12 @@
         <v>1</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>3.62</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>77</v>
@@ -3555,12 +3552,12 @@
         <v>1</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>4.24</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>77</v>
@@ -3584,12 +3581,12 @@
         <v>1</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>4.24</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>77</v>
@@ -3610,15 +3607,15 @@
         <v>101</v>
       </c>
       <c r="H82" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>4.5</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>77</v>
@@ -3642,12 +3639,12 @@
         <v>1</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>4.76</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>77</v>
@@ -3671,12 +3668,12 @@
         <v>1</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>4.96</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>77</v>
@@ -3700,12 +3697,12 @@
         <v>1</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>4.99</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>77</v>
@@ -3729,12 +3726,12 @@
         <v>1</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>7.21</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>77</v>
@@ -3758,12 +3755,12 @@
         <v>1</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>10.43</v>
+        <v>7.85</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>77</v>
@@ -3784,15 +3781,15 @@
         <v>107</v>
       </c>
       <c r="H88" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>11.06</v>
+        <v>8.41</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>77</v>
@@ -3813,15 +3810,15 @@
         <v>108</v>
       </c>
       <c r="H89" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I89" s="4" t="n">
-        <v>12.26</v>
+        <v>12.44</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>77</v>
@@ -3842,15 +3839,15 @@
         <v>109</v>
       </c>
       <c r="H90" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>14.17</v>
+        <v>22.39</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>46235</v>
+        <v>46240</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>77</v>
@@ -3871,15 +3868,15 @@
         <v>110</v>
       </c>
       <c r="H91" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>20.8</v>
+        <v>27.24</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>111</v>
@@ -3903,12 +3900,12 @@
         <v>1</v>
       </c>
       <c r="I92" s="4" t="n">
-        <v>3.23</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>111</v>
@@ -3932,12 +3929,12 @@
         <v>1</v>
       </c>
       <c r="I93" s="4" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>111</v>
@@ -3961,12 +3958,12 @@
         <v>1</v>
       </c>
       <c r="I94" s="4" t="n">
-        <v>4.07</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>111</v>
@@ -3990,12 +3987,12 @@
         <v>1</v>
       </c>
       <c r="I95" s="4" t="n">
-        <v>4.22</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>111</v>
@@ -4019,12 +4016,12 @@
         <v>1</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>4.96</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>111</v>
@@ -4048,12 +4045,12 @@
         <v>1</v>
       </c>
       <c r="I97" s="4" t="n">
-        <v>5.14</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>111</v>
@@ -4077,12 +4074,12 @@
         <v>1</v>
       </c>
       <c r="I98" s="4" t="n">
-        <v>5.84</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>111</v>
@@ -4106,12 +4103,12 @@
         <v>1</v>
       </c>
       <c r="I99" s="4" t="n">
-        <v>5.84</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>111</v>
@@ -4135,12 +4132,12 @@
         <v>1</v>
       </c>
       <c r="I100" s="4" t="n">
-        <v>7.83</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>111</v>
@@ -4161,15 +4158,15 @@
         <v>124</v>
       </c>
       <c r="H101" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I101" s="4" t="n">
-        <v>11.06</v>
+        <v>14.05</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>111</v>
@@ -4193,12 +4190,12 @@
         <v>0</v>
       </c>
       <c r="I102" s="4" t="n">
-        <v>11.13</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>111</v>
@@ -4222,12 +4219,12 @@
         <v>1</v>
       </c>
       <c r="I103" s="4" t="n">
-        <v>16.42</v>
+        <v>16.94</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>111</v>
@@ -4242,21 +4239,21 @@
         <v>114</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G104" s="3" t="s">
         <v>127</v>
       </c>
       <c r="H104" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I104" s="4" t="n">
-        <v>1.78</v>
+        <v>17.67</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>111</v>
@@ -4271,7 +4268,7 @@
         <v>114</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G105" s="3" t="s">
         <v>128</v>
@@ -4280,12 +4277,12 @@
         <v>1</v>
       </c>
       <c r="I105" s="4" t="n">
-        <v>2.08</v>
+        <v>23.39</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>111</v>
@@ -4309,12 +4306,12 @@
         <v>1</v>
       </c>
       <c r="I106" s="4" t="n">
-        <v>2.43</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>111</v>
@@ -4338,12 +4335,12 @@
         <v>1</v>
       </c>
       <c r="I107" s="4" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>111</v>
@@ -4367,12 +4364,12 @@
         <v>1</v>
       </c>
       <c r="I108" s="4" t="n">
-        <v>4.09</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>111</v>
@@ -4396,12 +4393,12 @@
         <v>1</v>
       </c>
       <c r="I109" s="4" t="n">
-        <v>4.2</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>111</v>
@@ -4425,12 +4422,12 @@
         <v>1</v>
       </c>
       <c r="I110" s="4" t="n">
-        <v>4.2</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>111</v>
@@ -4454,12 +4451,12 @@
         <v>1</v>
       </c>
       <c r="I111" s="4" t="n">
-        <v>4.23</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>111</v>
@@ -4483,12 +4480,12 @@
         <v>1</v>
       </c>
       <c r="I112" s="4" t="n">
-        <v>6.73</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>111</v>
@@ -4512,12 +4509,12 @@
         <v>1</v>
       </c>
       <c r="I113" s="4" t="n">
-        <v>7.46</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>111</v>
@@ -4538,15 +4535,15 @@
         <v>137</v>
       </c>
       <c r="H114" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I114" s="4" t="n">
-        <v>7.57</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B115" s="3" t="s">
         <v>111</v>
@@ -4570,12 +4567,12 @@
         <v>1</v>
       </c>
       <c r="I115" s="4" t="n">
-        <v>9.22</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>111</v>
@@ -4599,12 +4596,12 @@
         <v>1</v>
       </c>
       <c r="I116" s="4" t="n">
-        <v>10.48</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>111</v>
@@ -4628,12 +4625,12 @@
         <v>0</v>
       </c>
       <c r="I117" s="4" t="n">
-        <v>11.86</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>111</v>
@@ -4657,12 +4654,12 @@
         <v>1</v>
       </c>
       <c r="I118" s="4" t="n">
-        <v>16</v>
+        <v>11.67</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>111</v>
@@ -4686,12 +4683,12 @@
         <v>0</v>
       </c>
       <c r="I119" s="4" t="n">
-        <v>16.87</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>111</v>
@@ -4715,12 +4712,12 @@
         <v>0</v>
       </c>
       <c r="I120" s="4" t="n">
-        <v>17.7</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>111</v>
@@ -4741,3722 +4738,3722 @@
         <v>144</v>
       </c>
       <c r="H121" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I121" s="4" t="n">
-        <v>17.7</v>
+        <v>17.59</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B122" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C122" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C122" s="3" t="s">
+      <c r="D122" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D122" s="3" t="s">
+      <c r="E122" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>147</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H122" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I122" s="4" t="n">
-        <v>2.42</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B123" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C123" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C123" s="3" t="s">
+      <c r="D123" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D123" s="3" t="s">
+      <c r="E123" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="E123" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>147</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H123" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I123" s="4" t="n">
-        <v>2.42</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B124" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C124" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C124" s="3" t="s">
+      <c r="D124" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D124" s="3" t="s">
+      <c r="E124" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="E124" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>147</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H124" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I124" s="4" t="n">
-        <v>2.66</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B125" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C125" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C125" s="3" t="s">
+      <c r="D125" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D125" s="3" t="s">
+      <c r="E125" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="E125" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>147</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H125" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I125" s="4" t="n">
-        <v>2.73</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B126" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C126" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C126" s="3" t="s">
+      <c r="D126" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D126" s="3" t="s">
+      <c r="E126" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="E126" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>147</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H126" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I126" s="4" t="n">
-        <v>3.06</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B127" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C127" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C127" s="3" t="s">
+      <c r="D127" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D127" s="3" t="s">
+      <c r="E127" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="E127" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>147</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H127" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I127" s="4" t="n">
-        <v>4.24</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B128" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C128" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C128" s="3" t="s">
+      <c r="D128" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D128" s="3" t="s">
+      <c r="E128" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="E128" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>147</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H128" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I128" s="4" t="n">
-        <v>4.24</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B129" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C129" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C129" s="3" t="s">
+      <c r="D129" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D129" s="3" t="s">
+      <c r="E129" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="E129" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>147</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H129" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I129" s="4" t="n">
-        <v>4.66</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B130" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C130" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C130" s="3" t="s">
+      <c r="D130" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D130" s="3" t="s">
+      <c r="E130" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="E130" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>147</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H130" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I130" s="4" t="n">
-        <v>5.44</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B131" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C131" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C131" s="3" t="s">
+      <c r="D131" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D131" s="3" t="s">
+      <c r="E131" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="E131" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>147</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H131" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I131" s="4" t="n">
-        <v>6.99</v>
+        <v>9.73</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B132" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C132" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C132" s="3" t="s">
+      <c r="D132" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D132" s="3" t="s">
+      <c r="E132" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="E132" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>147</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H132" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I132" s="4" t="n">
-        <v>7.36</v>
+        <v>9.87</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B133" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C133" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C133" s="3" t="s">
+      <c r="D133" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D133" s="3" t="s">
+      <c r="E133" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="E133" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>147</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H133" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I133" s="4" t="n">
-        <v>7.74</v>
+        <v>12.07</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B134" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C134" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C134" s="3" t="s">
+      <c r="D134" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D134" s="3" t="s">
+      <c r="E134" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="E134" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>147</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H134" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I134" s="4" t="n">
-        <v>9.2</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B135" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C135" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C135" s="3" t="s">
+      <c r="D135" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D135" s="3" t="s">
+      <c r="E135" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="E135" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>147</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H135" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I135" s="4" t="n">
-        <v>12.56</v>
+        <v>15.58</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B136" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C136" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C136" s="3" t="s">
+      <c r="D136" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D136" s="3" t="s">
+      <c r="E136" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="E136" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="F136" s="3" t="s">
         <v>147</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H136" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I136" s="4" t="n">
-        <v>14.01</v>
+        <v>21.07</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B137" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C137" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C137" s="3" t="s">
+      <c r="D137" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D137" s="3" t="s">
+      <c r="E137" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E137" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="F137" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H137" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I137" s="4" t="n">
-        <v>2.21</v>
+        <v>22.23</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B138" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C138" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C138" s="3" t="s">
+      <c r="D138" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D138" s="3" t="s">
+      <c r="E138" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E138" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="F138" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H138" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I138" s="4" t="n">
-        <v>2.59</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B139" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C139" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C139" s="3" t="s">
+      <c r="D139" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D139" s="3" t="s">
+      <c r="E139" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E139" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="F139" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H139" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I139" s="4" t="n">
-        <v>3.23</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B140" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C140" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C140" s="3" t="s">
+      <c r="D140" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D140" s="3" t="s">
+      <c r="E140" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E140" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="F140" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H140" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I140" s="4" t="n">
-        <v>3.79</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B141" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C141" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C141" s="3" t="s">
+      <c r="D141" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D141" s="3" t="s">
+      <c r="E141" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E141" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="F141" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H141" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I141" s="4" t="n">
-        <v>4.51</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B142" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C142" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C142" s="3" t="s">
+      <c r="D142" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D142" s="3" t="s">
+      <c r="E142" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E142" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="F142" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H142" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I142" s="4" t="n">
-        <v>5.09</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B143" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C143" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C143" s="3" t="s">
+      <c r="D143" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D143" s="3" t="s">
+      <c r="E143" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E143" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="F143" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H143" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I143" s="4" t="n">
-        <v>5.09</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B144" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C144" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C144" s="3" t="s">
+      <c r="D144" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D144" s="3" t="s">
+      <c r="E144" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E144" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="F144" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H144" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I144" s="4" t="n">
-        <v>6.58</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B145" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C145" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C145" s="3" t="s">
+      <c r="D145" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D145" s="3" t="s">
+      <c r="E145" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E145" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="F145" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H145" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I145" s="4" t="n">
-        <v>6.76</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B146" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C146" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C146" s="3" t="s">
+      <c r="D146" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D146" s="3" t="s">
+      <c r="E146" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E146" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="F146" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H146" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I146" s="4" t="n">
-        <v>7.35</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B147" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C147" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C147" s="3" t="s">
+      <c r="D147" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D147" s="3" t="s">
+      <c r="E147" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E147" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="F147" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H147" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I147" s="4" t="n">
-        <v>10.17</v>
+        <v>8.88</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B148" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C148" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C148" s="3" t="s">
+      <c r="D148" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D148" s="3" t="s">
+      <c r="E148" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E148" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="F148" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H148" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I148" s="4" t="n">
-        <v>11.08</v>
+        <v>12.92</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B149" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C149" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C149" s="3" t="s">
+      <c r="D149" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D149" s="3" t="s">
+      <c r="E149" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E149" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="F149" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H149" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I149" s="4" t="n">
-        <v>11.22</v>
+        <v>13.71</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B150" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C150" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C150" s="3" t="s">
+      <c r="D150" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D150" s="3" t="s">
+      <c r="E150" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E150" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="F150" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H150" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I150" s="4" t="n">
-        <v>15.88</v>
+        <v>15.21</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B151" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C151" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C151" s="3" t="s">
+      <c r="D151" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D151" s="3" t="s">
+      <c r="E151" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E151" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="F151" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H151" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I151" s="4" t="n">
-        <v>17.89</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B152" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C152" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C152" s="3" t="s">
+      <c r="D152" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D152" s="3" t="s">
+      <c r="E152" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E152" s="3" t="s">
+      <c r="F152" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G152" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F152" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="G152" s="3" t="s">
-        <v>183</v>
-      </c>
       <c r="H152" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I152" s="4" t="n">
-        <v>1.89</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B153" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C153" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C153" s="3" t="s">
+      <c r="D153" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D153" s="3" t="s">
+      <c r="E153" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E153" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="F153" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H153" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I153" s="4" t="n">
-        <v>2.1</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B154" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C154" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C154" s="3" t="s">
+      <c r="D154" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D154" s="3" t="s">
+      <c r="E154" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E154" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="F154" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H154" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I154" s="4" t="n">
-        <v>3</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B155" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C155" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C155" s="3" t="s">
+      <c r="D155" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D155" s="3" t="s">
+      <c r="E155" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E155" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="F155" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H155" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I155" s="4" t="n">
-        <v>3.11</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B156" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C156" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C156" s="3" t="s">
+      <c r="D156" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D156" s="3" t="s">
+      <c r="E156" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E156" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="F156" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H156" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I156" s="4" t="n">
-        <v>3.11</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B157" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C157" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C157" s="3" t="s">
+      <c r="D157" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D157" s="3" t="s">
+      <c r="E157" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E157" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="F157" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H157" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I157" s="4" t="n">
-        <v>3.56</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B158" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C158" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C158" s="3" t="s">
+      <c r="D158" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D158" s="3" t="s">
+      <c r="E158" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E158" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="F158" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H158" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I158" s="4" t="n">
-        <v>4.04</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B159" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C159" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C159" s="3" t="s">
+      <c r="D159" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D159" s="3" t="s">
+      <c r="E159" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E159" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="F159" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H159" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I159" s="4" t="n">
-        <v>4.04</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B160" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C160" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C160" s="3" t="s">
+      <c r="D160" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D160" s="3" t="s">
+      <c r="E160" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E160" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="F160" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H160" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I160" s="4" t="n">
-        <v>4.57</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B161" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C161" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C161" s="3" t="s">
+      <c r="D161" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D161" s="3" t="s">
+      <c r="E161" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E161" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="F161" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H161" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I161" s="4" t="n">
-        <v>5.35</v>
+        <v>7.97</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B162" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C162" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C162" s="3" t="s">
+      <c r="D162" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D162" s="3" t="s">
+      <c r="E162" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E162" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="F162" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H162" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I162" s="4" t="n">
-        <v>5.5</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B163" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C163" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C163" s="3" t="s">
+      <c r="D163" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D163" s="3" t="s">
+      <c r="E163" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E163" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="F163" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H163" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I163" s="4" t="n">
-        <v>10.32</v>
+        <v>12.27</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B164" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C164" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C164" s="3" t="s">
+      <c r="D164" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D164" s="3" t="s">
+      <c r="E164" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E164" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="F164" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H164" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I164" s="4" t="n">
-        <v>10.48</v>
+        <v>18.14</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B165" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C165" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C165" s="3" t="s">
+      <c r="D165" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D165" s="3" t="s">
+      <c r="E165" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E165" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="F165" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H165" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I165" s="4" t="n">
-        <v>11.97</v>
+        <v>20.11</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B166" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C166" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C166" s="3" t="s">
+      <c r="D166" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D166" s="3" t="s">
+      <c r="E166" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E166" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="F166" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H166" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I166" s="4" t="n">
-        <v>14.27</v>
+        <v>20.95</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B167" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C167" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C167" s="3" t="s">
+      <c r="D167" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D167" s="3" t="s">
+      <c r="E167" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E167" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="F167" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H167" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I167" s="4" t="n">
-        <v>1.86</v>
+        <v>22.62</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B168" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C168" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C168" s="3" t="s">
+      <c r="D168" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D168" s="3" t="s">
+      <c r="E168" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E168" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="F168" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H168" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I168" s="4" t="n">
-        <v>2.74</v>
+        <v>29.67</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B169" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C169" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C169" s="3" t="s">
+      <c r="D169" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D169" s="3" t="s">
+      <c r="E169" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E169" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="F169" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H169" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I169" s="4" t="n">
-        <v>3.73</v>
+        <v>29.78</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B170" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C170" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C170" s="3" t="s">
+      <c r="D170" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D170" s="3" t="s">
+      <c r="E170" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E170" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="F170" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H170" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I170" s="4" t="n">
-        <v>4.45</v>
+        <v>34.45</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="F171" s="3" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="G171" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="H171" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I171" s="4" t="n">
-        <v>4.46</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="H172" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I172" s="4" t="n">
-        <v>4.95</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="H173" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I173" s="4" t="n">
-        <v>4.98</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H174" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I174" s="4" t="n">
-        <v>4.98</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="F175" s="3" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H175" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I175" s="4" t="n">
-        <v>7.54</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="H176" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I176" s="4" t="n">
-        <v>11.28</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="H177" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I177" s="4" t="n">
-        <v>12.38</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H178" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I178" s="4" t="n">
-        <v>13.29</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="H179" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I179" s="4" t="n">
-        <v>14.65</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="H180" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I180" s="4" t="n">
-        <v>15.45</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="H181" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I181" s="4" t="n">
-        <v>16.14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="E182" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F182" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="G182" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="F182" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="G182" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="H182" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I182" s="4" t="n">
-        <v>2.08</v>
+        <v>8.41</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H183" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I183" s="4" t="n">
-        <v>2.52</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="F184" s="3" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H184" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I184" s="4" t="n">
-        <v>3.07</v>
+        <v>13.68</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="F185" s="3" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H185" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I185" s="4" t="n">
-        <v>3.34</v>
+        <v>15.26</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="F186" s="3" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H186" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I186" s="4" t="n">
-        <v>3.72</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H187" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I187" s="4" t="n">
-        <v>3.89</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H188" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I188" s="4" t="n">
-        <v>4.19</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H189" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I189" s="4" t="n">
-        <v>4.19</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="F190" s="3" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H190" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I190" s="4" t="n">
-        <v>4.62</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H191" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I191" s="4" t="n">
-        <v>4.93</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H192" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I192" s="4" t="n">
-        <v>10.17</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H193" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I193" s="4" t="n">
-        <v>12.07</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H194" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I194" s="4" t="n">
-        <v>12.46</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H195" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I195" s="4" t="n">
-        <v>13.55</v>
+        <v>9.41</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H196" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I196" s="4" t="n">
-        <v>13.62</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="F197" s="3" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H197" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I197" s="4" t="n">
-        <v>15.86</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H198" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I198" s="4" t="n">
-        <v>2.49</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H199" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I199" s="4" t="n">
-        <v>2.75</v>
+        <v>14.84</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>46236</v>
+        <v>46242</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H200" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I200" s="4" t="n">
-        <v>3.12</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>46236</v>
+        <v>46243</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>213</v>
+        <v>9</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="F201" s="3" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H201" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I201" s="4" t="n">
-        <v>3.12</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>46236</v>
+        <v>46243</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>213</v>
+        <v>9</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H202" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I202" s="4" t="n">
-        <v>3.83</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>46236</v>
+        <v>46243</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>213</v>
+        <v>9</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="H203" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I203" s="4" t="n">
-        <v>3.83</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>46236</v>
+        <v>46243</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>213</v>
+        <v>9</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H204" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I204" s="4" t="n">
-        <v>4.36</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>46236</v>
+        <v>46243</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>213</v>
+        <v>9</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="H205" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I205" s="4" t="n">
-        <v>5.25</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>46236</v>
+        <v>46243</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>213</v>
+        <v>9</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="H206" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I206" s="4" t="n">
-        <v>5.36</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>46236</v>
+        <v>46243</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>213</v>
+        <v>9</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H207" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I207" s="4" t="n">
-        <v>5.37</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>46236</v>
+        <v>46243</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>213</v>
+        <v>9</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H208" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I208" s="4" t="n">
-        <v>10.01</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>46236</v>
+        <v>46243</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>213</v>
+        <v>9</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="F209" s="3" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="H209" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I209" s="4" t="n">
-        <v>10.13</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>46236</v>
+        <v>46243</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>213</v>
+        <v>9</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="F210" s="3" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="H210" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I210" s="4" t="n">
-        <v>15.87</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>46236</v>
+        <v>46243</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>213</v>
+        <v>9</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H211" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I211" s="4" t="n">
-        <v>18.22</v>
+        <v>7.74</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>46240</v>
+        <v>46243</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>247</v>
+        <v>9</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="E212" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="F212" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G212" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="F212" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="G212" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="H212" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I212" s="4" t="n">
-        <v>1.94</v>
+        <v>11.34</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>46240</v>
+        <v>46243</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>247</v>
+        <v>9</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="F213" s="3" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H213" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I213" s="4" t="n">
-        <v>2.01</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>46240</v>
+        <v>46243</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>247</v>
+        <v>9</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="F214" s="3" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H214" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I214" s="4" t="n">
-        <v>2.54</v>
+        <v>14.85</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>46240</v>
+        <v>46243</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>247</v>
+        <v>9</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="F215" s="3" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H215" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I215" s="4" t="n">
-        <v>3.15</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>46240</v>
+        <v>46243</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>247</v>
+        <v>9</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="F216" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H216" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I216" s="4" t="n">
-        <v>3.31</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>46240</v>
+        <v>46243</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>247</v>
+        <v>9</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="F217" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H217" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I217" s="4" t="n">
-        <v>3.91</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>46240</v>
+        <v>46243</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>247</v>
+        <v>9</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="F218" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H218" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I218" s="4" t="n">
-        <v>3.91</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>46240</v>
+        <v>46243</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>247</v>
+        <v>9</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="F219" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H219" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I219" s="4" t="n">
-        <v>4.11</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>46240</v>
+        <v>46243</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>247</v>
+        <v>9</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="F220" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H220" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I220" s="4" t="n">
-        <v>6.49</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>46240</v>
+        <v>46243</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>247</v>
+        <v>9</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="F221" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H221" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I221" s="4" t="n">
-        <v>7.81</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>46240</v>
+        <v>46243</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>247</v>
+        <v>9</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="F222" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H222" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I222" s="4" t="n">
-        <v>8.36</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>46240</v>
+        <v>46243</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>247</v>
+        <v>9</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="F223" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H223" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I223" s="4" t="n">
-        <v>12.37</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>46240</v>
+        <v>46243</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>247</v>
+        <v>9</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="F224" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H224" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I224" s="4" t="n">
-        <v>22.26</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>46240</v>
+        <v>46243</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>247</v>
+        <v>9</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="F225" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H225" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I225" s="4" t="n">
-        <v>27.08</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>46240</v>
+        <v>46243</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>247</v>
+        <v>9</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="F226" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H226" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I226" s="4" t="n">
-        <v>29.36</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>46240</v>
+        <v>46243</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>247</v>
+        <v>9</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="F227" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H227" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I227" s="4" t="n">
-        <v>41.73</v>
+        <v>10.63</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>46240</v>
+        <v>46243</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>247</v>
+        <v>9</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="F228" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H228" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I228" s="4" t="n">
-        <v>42.45</v>
+        <v>15.03</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>46240</v>
+        <v>46243</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>247</v>
+        <v>9</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H229" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I229" s="4" t="n">
-        <v>51.35</v>
+        <v>16.93</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>46240</v>
+        <v>46243</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>247</v>
+        <v>9</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="F230" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H230" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I230" s="4" t="n">
-        <v>56.84</v>
+        <v>17.38</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B231" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C231" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D231" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D231" s="3" t="s">
+      <c r="E231" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F231" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="G231" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="E231" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F231" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="G231" s="3" t="s">
-        <v>271</v>
-      </c>
       <c r="H231" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I231" s="4" t="n">
-        <v>1.77</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B232" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C232" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D232" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D232" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="E232" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="F232" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H232" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I232" s="4" t="n">
-        <v>2.46</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B233" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C233" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D233" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D233" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="E233" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="F233" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G233" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H233" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I233" s="4" t="n">
-        <v>2.67</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B234" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C234" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D234" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D234" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="E234" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="F234" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H234" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I234" s="4" t="n">
-        <v>2.98</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B235" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C235" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D235" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D235" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="E235" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="F235" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H235" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I235" s="4" t="n">
-        <v>3.22</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B236" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C236" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D236" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D236" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="E236" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="F236" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H236" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I236" s="4" t="n">
-        <v>4.5</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B237" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C237" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D237" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D237" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="E237" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="F237" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H237" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I237" s="4" t="n">
-        <v>4.5</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B238" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C238" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D238" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D238" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="E238" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="F238" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H238" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I238" s="4" t="n">
-        <v>4.52</v>
+        <v>7.62</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B239" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C239" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D239" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D239" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="E239" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="F239" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H239" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I239" s="4" t="n">
-        <v>4.54</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B240" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C240" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D240" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D240" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="E240" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="F240" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G240" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H240" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I240" s="4" t="n">
-        <v>7.96</v>
+        <v>8.35</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B241" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C241" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D241" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D241" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="E241" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="F241" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H241" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I241" s="4" t="n">
-        <v>8.12</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B242" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C242" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D242" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D242" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="E242" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="F242" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H242" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I242" s="4" t="n">
-        <v>10.28</v>
+        <v>13.34</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B243" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C243" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D243" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D243" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="E243" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="F243" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H243" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I243" s="4" t="n">
-        <v>11.7</v>
+        <v>19.14</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B244" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C244" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D244" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D244" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="E244" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="F244" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H244" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I244" s="4" t="n">
-        <v>12.09</v>
+        <v>28.76</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B245" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C245" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D245" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D245" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="E245" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="F245" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G245" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H245" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I245" s="4" t="n">
-        <v>12.39</v>
+        <v>28.76</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B246" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C246" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D246" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D246" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="E246" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="F246" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G246" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H246" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I246" s="4" t="n">
-        <v>17.64</v>
+        <v>38.15</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B247" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C247" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D247" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D247" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="E247" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="F247" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H247" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I247" s="4" t="n">
-        <v>24.71</v>
+        <v>47.73</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B248" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C248" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D248" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D248" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="E248" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="F248" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H248" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I248" s="4" t="n">
-        <v>32.77</v>
+        <v>48.55</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="B249" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C249" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D249" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D249" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="E249" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="F249" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G249" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H249" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I249" s="4" t="n">
-        <v>34.39</v>
+        <v>55.43</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_anytime_tryscorers.xlsx
+++ b/files/NRL_anytime_tryscorers.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="300">
   <si>
     <t xml:space="preserve">Date Local</t>
   </si>
@@ -62,15 +62,15 @@
     <t xml:space="preserve">William Kennedy</t>
   </si>
   <si>
+    <t xml:space="preserve">Mawene Hiroti</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kayal Iro</t>
   </si>
   <si>
     <t xml:space="preserve">Braydon Trindall</t>
   </si>
   <si>
-    <t xml:space="preserve">Jesse Ramien</t>
-  </si>
-  <si>
     <t xml:space="preserve">Briton Nikora</t>
   </si>
   <si>
@@ -80,22 +80,19 @@
     <t xml:space="preserve">Nicholas Hynes</t>
   </si>
   <si>
+    <t xml:space="preserve">Addin Fonua-Blake</t>
+  </si>
+  <si>
     <t xml:space="preserve">Thomas Hazelton</t>
   </si>
   <si>
-    <t xml:space="preserve">Jesse Colquhoun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siosifa Talakai</t>
-  </si>
-  <si>
     <t xml:space="preserve">Blayke Brailey</t>
   </si>
   <si>
     <t xml:space="preserve">Cameron McInnes</t>
   </si>
   <si>
-    <t xml:space="preserve">Oregon Kaufusi</t>
+    <t xml:space="preserve">Tuku Hau Tapuha</t>
   </si>
   <si>
     <t xml:space="preserve">Alex Johnston</t>
@@ -104,6 +101,9 @@
     <t xml:space="preserve">Campbell Graham</t>
   </si>
   <si>
+    <t xml:space="preserve">Tallis Duncan</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cody Walker</t>
   </si>
   <si>
@@ -113,33 +113,33 @@
     <t xml:space="preserve">Jack Wighton</t>
   </si>
   <si>
-    <t xml:space="preserve">Latrell Siegwalt</t>
+    <t xml:space="preserve">David Fifita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euan Aitken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashton Ward</t>
   </si>
   <si>
     <t xml:space="preserve">Keaon Koloamatangi</t>
   </si>
   <si>
-    <t xml:space="preserve">Adam Elliott</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashton Ward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Sullivan</t>
+    <t xml:space="preserve">Cameron Murray</t>
   </si>
   <si>
     <t xml:space="preserve">Brandon Smith</t>
   </si>
   <si>
+    <t xml:space="preserve">John Radel</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tevita Tatola</t>
   </si>
   <si>
     <t xml:space="preserve">Jye Gray</t>
   </si>
   <si>
-    <t xml:space="preserve">John Radel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jamie Humphreys</t>
   </si>
   <si>
@@ -164,33 +164,30 @@
     <t xml:space="preserve">Isaiah Iongi</t>
   </si>
   <si>
-    <t xml:space="preserve">Will Penisini</t>
+    <t xml:space="preserve">Araz Nanva</t>
   </si>
   <si>
     <t xml:space="preserve">Jordan Samrani</t>
   </si>
   <si>
-    <t xml:space="preserve">Mitchell Moses</t>
+    <t xml:space="preserve">Ronald Volkman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jonah Pezet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tallyn Da Silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kitione Kautoga</t>
   </si>
   <si>
     <t xml:space="preserve">Kelma Tuilagi</t>
   </si>
   <si>
-    <t xml:space="preserve">Kitione Kautoga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronald Volkman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tallyn Da Silva</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jack De Belin</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Paulo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Joash Papalii</t>
   </si>
   <si>
@@ -203,6 +200,9 @@
     <t xml:space="preserve">Sam Tuivaiti</t>
   </si>
   <si>
+    <t xml:space="preserve">Jeral Skelton</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sunia Turuva</t>
   </si>
   <si>
@@ -212,7 +212,10 @@
     <t xml:space="preserve">Adam Doueihi</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Tupou</t>
+    <t xml:space="preserve">Starford To'a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heamasi Makasini</t>
   </si>
   <si>
     <t xml:space="preserve">Samuela Fainu</t>
@@ -221,30 +224,27 @@
     <t xml:space="preserve">Sione Fainu</t>
   </si>
   <si>
-    <t xml:space="preserve">Heamasi Makasini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patrick Herbert</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jarome Luai</t>
   </si>
   <si>
+    <t xml:space="preserve">Alex Seyfarth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jared Haywood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terrell May</t>
+  </si>
+  <si>
     <t xml:space="preserve">Apisai Koroisau</t>
   </si>
   <si>
-    <t xml:space="preserve">Alex Seyfarth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terrell May</t>
+    <t xml:space="preserve">Latu Fainu</t>
   </si>
   <si>
     <t xml:space="preserve">Fonua Pole</t>
   </si>
   <si>
-    <t xml:space="preserve">Starford To'a</t>
-  </si>
-  <si>
     <t xml:space="preserve">19:50</t>
   </si>
   <si>
@@ -272,15 +272,15 @@
     <t xml:space="preserve">Keano Kini</t>
   </si>
   <si>
+    <t xml:space="preserve">Arama Hau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beau Fermor</t>
+  </si>
+  <si>
     <t xml:space="preserve">AJ Brimson</t>
   </si>
   <si>
-    <t xml:space="preserve">Arama Hau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beau Fermor</t>
-  </si>
-  <si>
     <t xml:space="preserve">Oliver Pascoe</t>
   </si>
   <si>
@@ -296,21 +296,24 @@
     <t xml:space="preserve">Chris Randall</t>
   </si>
   <si>
-    <t xml:space="preserve">Kurtis Morrin</t>
-  </si>
-  <si>
     <t xml:space="preserve">Klese Haas</t>
   </si>
   <si>
     <t xml:space="preserve">Sam Verrills</t>
   </si>
   <si>
+    <t xml:space="preserve">Lachlan Ilias</t>
+  </si>
+  <si>
     <t xml:space="preserve">Braidon Burns</t>
   </si>
   <si>
     <t xml:space="preserve">Murray Taulagi</t>
   </si>
   <si>
+    <t xml:space="preserve">Jeremiah Nanai</t>
+  </si>
+  <si>
     <t xml:space="preserve">Scott Drinkwater</t>
   </si>
   <si>
@@ -320,31 +323,28 @@
     <t xml:space="preserve">Zac Laybutt</t>
   </si>
   <si>
+    <t xml:space="preserve">Tom Dearden</t>
+  </si>
+  <si>
     <t xml:space="preserve">Heilum Luki</t>
   </si>
   <si>
-    <t xml:space="preserve">Jeremiah Nanai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Clifford</t>
+    <t xml:space="preserve">Reed Mahoney</t>
   </si>
   <si>
     <t xml:space="preserve">Jaxon Purdue</t>
   </si>
   <si>
+    <t xml:space="preserve">Reuben Cotter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam McIntyre</t>
+  </si>
+  <si>
     <t xml:space="preserve">Soni Luke</t>
   </si>
   <si>
-    <t xml:space="preserve">Reuben Cotter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam McIntyre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Mikaele</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coen Hess</t>
+    <t xml:space="preserve">Griffin Neame</t>
   </si>
   <si>
     <t xml:space="preserve">20:00</t>
@@ -368,66 +368,66 @@
     <t xml:space="preserve">Matt Burton</t>
   </si>
   <si>
+    <t xml:space="preserve">Jacob Preston</t>
+  </si>
+  <si>
     <t xml:space="preserve">Connor Tracey</t>
   </si>
   <si>
     <t xml:space="preserve">Enari Tuala</t>
   </si>
   <si>
+    <t xml:space="preserve">Lachlan Galvin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaeman Salmon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Curran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sean O'Sullivan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bailey Hayward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gordon Chan Kum Tong</t>
+  </si>
+  <si>
     <t xml:space="preserve">Viliame Kikau</t>
   </si>
   <si>
-    <t xml:space="preserve">Jacob Preston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lachlan Galvin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stephen Crichton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jonathan Sua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurt Mann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bailey Hayward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Curran</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaeman Salmon</t>
+    <t xml:space="preserve">Harry Hayes</t>
   </si>
   <si>
     <t xml:space="preserve">Mark Nawaqanitawase</t>
   </si>
   <si>
-    <t xml:space="preserve">Tommy Talau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Tedesco</t>
+    <t xml:space="preserve">Daniel Tupou</t>
   </si>
   <si>
     <t xml:space="preserve">Hugo Savala</t>
   </si>
   <si>
-    <t xml:space="preserve">Robert Toia</t>
+    <t xml:space="preserve">Cody Ramsey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daly Cherry-Evans</t>
   </si>
   <si>
     <t xml:space="preserve">Nat Butcher</t>
   </si>
   <si>
+    <t xml:space="preserve">Sam Walker</t>
+  </si>
+  <si>
     <t xml:space="preserve">Siua Wong</t>
   </si>
   <si>
-    <t xml:space="preserve">Daly Cherry-Evans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Walker</t>
-  </si>
-  <si>
     <t xml:space="preserve">Reece Robson</t>
   </si>
   <si>
@@ -437,18 +437,18 @@
     <t xml:space="preserve">Connor Watson</t>
   </si>
   <si>
-    <t xml:space="preserve">Salesi Foketi</t>
+    <t xml:space="preserve">Egan Butcher</t>
   </si>
   <si>
     <t xml:space="preserve">Spencer Leniu</t>
   </si>
   <si>
-    <t xml:space="preserve">Egan Butcher</t>
-  </si>
-  <si>
     <t xml:space="preserve">Naufahu Whyte</t>
   </si>
   <si>
+    <t xml:space="preserve">Rex Bassingthwaighte</t>
+  </si>
+  <si>
     <t xml:space="preserve">sched-2026-20260807-2000-warriors-penrith-panthers</t>
   </si>
   <si>
@@ -464,24 +464,27 @@
     <t xml:space="preserve">Brian To'o</t>
   </si>
   <si>
-    <t xml:space="preserve">Jaxen Edgar</t>
-  </si>
-  <si>
     <t xml:space="preserve">Casey McLean</t>
   </si>
   <si>
+    <t xml:space="preserve">Dylan Edwards</t>
+  </si>
+  <si>
     <t xml:space="preserve">Paul Alamoti</t>
   </si>
   <si>
+    <t xml:space="preserve">Nathan Cleary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blaize Talagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Martin</t>
+  </si>
+  <si>
     <t xml:space="preserve">Isaiah Papali'i</t>
   </si>
   <si>
-    <t xml:space="preserve">Liam Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nathan Cleary</t>
-  </si>
-  <si>
     <t xml:space="preserve">Freddy Lussick</t>
   </si>
   <si>
@@ -494,9 +497,6 @@
     <t xml:space="preserve">Isaah Yeo</t>
   </si>
   <si>
-    <t xml:space="preserve">Jack Cogger</t>
-  </si>
-  <si>
     <t xml:space="preserve">Liam Henry</t>
   </si>
   <si>
@@ -512,27 +512,30 @@
     <t xml:space="preserve">Dallin Watene-Zelezniak</t>
   </si>
   <si>
+    <t xml:space="preserve">Ali Leiataua</t>
+  </si>
+  <si>
     <t xml:space="preserve">Leka Halasima</t>
   </si>
   <si>
-    <t xml:space="preserve">Ali Leiataua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charnze Nicoll-Klokstad</t>
+    <t xml:space="preserve">Taine Tuaupiki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Pompey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Laban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chanel Harris-Tavita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Te Maire Martin</t>
   </si>
   <si>
     <t xml:space="preserve">Kurt Capewell</t>
   </si>
   <si>
-    <t xml:space="preserve">Jacob Laban</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chanel Harris-Tavita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Te Maire Martin</t>
-  </si>
-  <si>
     <t xml:space="preserve">Wayde Egan</t>
   </si>
   <si>
@@ -545,9 +548,6 @@
     <t xml:space="preserve">Erin Clark</t>
   </si>
   <si>
-    <t xml:space="preserve">Luke Metcalf</t>
-  </si>
-  <si>
     <t xml:space="preserve">15:00</t>
   </si>
   <si>
@@ -560,7 +560,52 @@
     <t xml:space="preserve">manly-warringah sea eagles</t>
   </si>
   <si>
-    <t xml:space="preserve">Moses Leo</t>
+    <t xml:space="preserve">Tom Trbojevic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jason Saab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lehi Hopoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tolutau Koula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reuben Garrick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haumole Olakau'atu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joey Walsh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Bullemor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamal Fogarty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Simpkin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simione Laiafi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aaron Schoupp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Trbojevic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taniela Paseka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicholas Lenaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Warbrick</t>
   </si>
   <si>
     <t xml:space="preserve">Sualauvi Faalogo</t>
@@ -569,52 +614,40 @@
     <t xml:space="preserve">Siulagi Tuimalatu-Brown</t>
   </si>
   <si>
-    <t xml:space="preserve">Manaia Waitere</t>
+    <t xml:space="preserve">Harry Grant</t>
   </si>
   <si>
     <t xml:space="preserve">Tyran Wishart</t>
   </si>
   <si>
+    <t xml:space="preserve">Nick Meaney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Howarth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oryn Keeley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trent Toelau</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cooper Clarke</t>
   </si>
   <si>
-    <t xml:space="preserve">Oryn Keeley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nick Meaney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hayden Watson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trent Toelau</t>
-  </si>
-  <si>
     <t xml:space="preserve">Josh King</t>
   </si>
   <si>
     <t xml:space="preserve">Stefano Utoikamanu</t>
   </si>
   <si>
-    <t xml:space="preserve">Joe Chan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shawn Blore</t>
-  </si>
-  <si>
     <t xml:space="preserve">Trent Loiero</t>
   </si>
   <si>
-    <t xml:space="preserve">Angus Hinchey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jai Bowden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alec MacDonald</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Hetherington</t>
+    <t xml:space="preserve">Davvy Moale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gabriel Satrick</t>
   </si>
   <si>
     <t xml:space="preserve">17:30</t>
@@ -629,87 +662,78 @@
     <t xml:space="preserve">brisbane broncos</t>
   </si>
   <si>
+    <t xml:space="preserve">Deine Mariner</t>
+  </si>
+  <si>
     <t xml:space="preserve">Josiah Karapani</t>
   </si>
   <si>
-    <t xml:space="preserve">Grant Anderson</t>
-  </si>
-  <si>
     <t xml:space="preserve">Reece Walsh</t>
   </si>
   <si>
     <t xml:space="preserve">Ezra Mam</t>
   </si>
   <si>
+    <t xml:space="preserve">Gehamat Shibasaki</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kotoni Staggs</t>
   </si>
   <si>
+    <t xml:space="preserve">Adam Reynolds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Riki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brendan Piakura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Talty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cory Paix</t>
+  </si>
+  <si>
     <t xml:space="preserve">Xavier Willison</t>
   </si>
   <si>
-    <t xml:space="preserve">Jordan Riki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deine Mariner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Reynolds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Walters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben Talty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cory Paix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gehamat Shibasaki</t>
-  </si>
-  <si>
     <t xml:space="preserve">Payne Haas</t>
   </si>
   <si>
-    <t xml:space="preserve">Va'a Semu</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hamiso Tabuai-Fidow</t>
   </si>
   <si>
+    <t xml:space="preserve">Jamayne Isaako</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tevita Naufahu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herbie Farnworth</t>
+  </si>
+  <si>
     <t xml:space="preserve">Selwyn Cobbo</t>
   </si>
   <si>
-    <t xml:space="preserve">Jamayne Isaako</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herbie Farnworth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Bostock</t>
+    <t xml:space="preserve">Kodi Nikorima</t>
   </si>
   <si>
     <t xml:space="preserve">Connelly Lemuelu</t>
   </si>
   <si>
+    <t xml:space="preserve">Brad Schneider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremy Marshall-King</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kulikefu Finefeuiaki</t>
   </si>
   <si>
-    <t xml:space="preserve">Kodi Nikorima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremy Marshall-King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ray Stone</t>
-  </si>
-  <si>
     <t xml:space="preserve">Max Plath</t>
   </si>
   <si>
-    <t xml:space="preserve">Isaiya Katoa</t>
-  </si>
-  <si>
     <t xml:space="preserve">Thomas Flegler</t>
   </si>
   <si>
@@ -719,6 +743,15 @@
     <t xml:space="preserve">Felise Kaufusi</t>
   </si>
   <si>
+    <t xml:space="preserve">Morgan Knowles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Gilbert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francis Molo</t>
+  </si>
+  <si>
     <t xml:space="preserve">sched-2026-20260809-1400-canberra-raiders-newcastle-knights</t>
   </si>
   <si>
@@ -731,48 +764,51 @@
     <t xml:space="preserve">Xavier Savage</t>
   </si>
   <si>
+    <t xml:space="preserve">Hudson Young</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kaeo Weekes</t>
   </si>
   <si>
-    <t xml:space="preserve">Sebastian Kris</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jed Stuart</t>
   </si>
   <si>
+    <t xml:space="preserve">Noah Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simi Sasagi</t>
+  </si>
+  <si>
     <t xml:space="preserve">Matthew Timoko</t>
   </si>
   <si>
+    <t xml:space="preserve">Zac Hosking</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ethan Strange</t>
   </si>
   <si>
-    <t xml:space="preserve">Zac Hosking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ata Mariota</t>
-  </si>
-  <si>
     <t xml:space="preserve">Owen Pattie</t>
   </si>
   <si>
     <t xml:space="preserve">Ethan Sanders</t>
   </si>
   <si>
-    <t xml:space="preserve">Joe Roddy</t>
+    <t xml:space="preserve">Tom Starling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joseph Tapine</t>
   </si>
   <si>
     <t xml:space="preserve">Corey Horsburgh</t>
   </si>
   <si>
-    <t xml:space="preserve">Tom Starling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joseph Tapine</t>
-  </si>
-  <si>
     <t xml:space="preserve">Daine Laurie</t>
   </si>
   <si>
+    <t xml:space="preserve">Savelio Tamale</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dominic Young</t>
   </si>
   <si>
@@ -782,25 +818,28 @@
     <t xml:space="preserve">Fletcher Sharpe</t>
   </si>
   <si>
+    <t xml:space="preserve">Dylan Lucas</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bradman Best</t>
   </si>
   <si>
     <t xml:space="preserve">Kalyn Ponga</t>
   </si>
   <si>
-    <t xml:space="preserve">Jermaine McEwen</t>
+    <t xml:space="preserve">Dylan Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dane Gagai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trey Mooney</t>
   </si>
   <si>
     <t xml:space="preserve">Francis Manuleleua</t>
   </si>
   <si>
-    <t xml:space="preserve">Dane Gagai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trey Mooney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandon Smith</t>
+    <t xml:space="preserve">Harrison Graham</t>
   </si>
   <si>
     <t xml:space="preserve">Fletcher Hunt</t>
@@ -809,15 +848,9 @@
     <t xml:space="preserve">Phoenix Crossland</t>
   </si>
   <si>
-    <t xml:space="preserve">Tyson Frizell</t>
-  </si>
-  <si>
     <t xml:space="preserve">Brodie Jones</t>
   </si>
   <si>
-    <t xml:space="preserve">Cody Hopwood</t>
-  </si>
-  <si>
     <t xml:space="preserve">sched-2026-20260809-1605-st-george-illawarra-dragons-cronulla-sutherland-sharks</t>
   </si>
   <si>
@@ -830,6 +863,9 @@
     <t xml:space="preserve">Setu Tu</t>
   </si>
   <si>
+    <t xml:space="preserve">Mathew Feagai</t>
+  </si>
+  <si>
     <t xml:space="preserve">Valentine Holmes</t>
   </si>
   <si>
@@ -839,46 +875,43 @@
     <t xml:space="preserve">Dylan Egan</t>
   </si>
   <si>
+    <t xml:space="preserve">Jacob Liddle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyle Flanagan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Atkinson</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hamish Stewart</t>
   </si>
   <si>
-    <t xml:space="preserve">Jacob Liddle</t>
+    <t xml:space="preserve">Damien Cook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luciano Leilua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan Couchman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loko Jnr Pasifiki Tonga</t>
   </si>
   <si>
     <t xml:space="preserve">Mosese Suli</t>
   </si>
   <si>
-    <t xml:space="preserve">Kyle Flanagan</t>
+    <t xml:space="preserve">Josh Kerr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Halangahu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toby Couchman</t>
   </si>
   <si>
     <t xml:space="preserve">Lyhkan King-Togia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Damien Cook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luciano Leilua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel Atkinson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loko Jnr Pasifiki Tonga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan Couchman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Kerr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Halangahu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toby Couchman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emre Guler</t>
   </si>
 </sst>
 </file>
@@ -1290,7 +1323,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="3">
@@ -1319,7 +1352,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>1.97</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="4">
@@ -1348,7 +1381,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>2.79</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="5">
@@ -1377,7 +1410,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>2.89</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="6">
@@ -1406,7 +1439,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2.9</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="7">
@@ -1435,7 +1468,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.31</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="8">
@@ -1464,7 +1497,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>3.75</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="9">
@@ -1493,7 +1526,7 @@
         <v>1</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3.75</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="10">
@@ -1522,7 +1555,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.23</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="11">
@@ -1548,10 +1581,10 @@
         <v>22</v>
       </c>
       <c r="H11" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>7.76</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="12">
@@ -1580,7 +1613,7 @@
         <v>1</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>9</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="13">
@@ -1606,10 +1639,10 @@
         <v>24</v>
       </c>
       <c r="H13" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>9.49</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="14">
@@ -1638,7 +1671,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>9.64</v>
+        <v>12.07</v>
       </c>
     </row>
     <row r="15">
@@ -1664,10 +1697,10 @@
         <v>26</v>
       </c>
       <c r="H15" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>11</v>
+        <v>13.57</v>
       </c>
     </row>
     <row r="16">
@@ -1687,7 +1720,7 @@
         <v>12</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>27</v>
@@ -1696,7 +1729,7 @@
         <v>1</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>13.08</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="17">
@@ -1725,7 +1758,7 @@
         <v>1</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.87</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="18">
@@ -1754,7 +1787,7 @@
         <v>1</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.77</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="19">
@@ -1783,7 +1816,7 @@
         <v>1</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="20">
@@ -1812,7 +1845,7 @@
         <v>1</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>4.5</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="21">
@@ -1841,7 +1874,7 @@
         <v>1</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>4.51</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="22">
@@ -1870,7 +1903,7 @@
         <v>1</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>5.01</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="23">
@@ -1899,7 +1932,7 @@
         <v>1</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>5.04</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="24">
@@ -1928,7 +1961,7 @@
         <v>1</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>5.04</v>
+        <v>7.58</v>
       </c>
     </row>
     <row r="25">
@@ -1957,7 +1990,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>7.63</v>
+        <v>8.13</v>
       </c>
     </row>
     <row r="26">
@@ -1983,10 +2016,10 @@
         <v>37</v>
       </c>
       <c r="H26" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>11.42</v>
+        <v>8.14</v>
       </c>
     </row>
     <row r="27">
@@ -2015,7 +2048,7 @@
         <v>1</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>12.54</v>
+        <v>12.46</v>
       </c>
     </row>
     <row r="28">
@@ -2041,10 +2074,10 @@
         <v>39</v>
       </c>
       <c r="H28" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>13.46</v>
+        <v>13.24</v>
       </c>
     </row>
     <row r="29">
@@ -2070,10 +2103,10 @@
         <v>40</v>
       </c>
       <c r="H29" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>14.84</v>
+        <v>13.37</v>
       </c>
     </row>
     <row r="30">
@@ -2099,10 +2132,10 @@
         <v>41</v>
       </c>
       <c r="H30" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>15.64</v>
+        <v>14.74</v>
       </c>
     </row>
     <row r="31">
@@ -2131,7 +2164,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>16.34</v>
+        <v>16.24</v>
       </c>
     </row>
     <row r="32">
@@ -2160,7 +2193,7 @@
         <v>1</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="33">
@@ -2189,7 +2222,7 @@
         <v>1</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="34">
@@ -2218,7 +2251,7 @@
         <v>1</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>2.95</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="35">
@@ -2247,7 +2280,7 @@
         <v>1</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>3.21</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="36">
@@ -2276,7 +2309,7 @@
         <v>1</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>3.57</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="37">
@@ -2305,7 +2338,7 @@
         <v>1</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>3.73</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="38">
@@ -2334,7 +2367,7 @@
         <v>1</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>4.02</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="39">
@@ -2363,7 +2396,7 @@
         <v>1</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>4.02</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="40">
@@ -2392,7 +2425,7 @@
         <v>1</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>4.43</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="41">
@@ -2421,7 +2454,7 @@
         <v>1</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>4.73</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="42">
@@ -2450,7 +2483,7 @@
         <v>1</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>9.72</v>
+        <v>8.83</v>
       </c>
     </row>
     <row r="43">
@@ -2479,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>11.53</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="44">
@@ -2508,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>11.9</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="45">
@@ -2534,10 +2567,10 @@
         <v>60</v>
       </c>
       <c r="H45" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>12.94</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="46">
@@ -2566,7 +2599,7 @@
         <v>1</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>13</v>
+        <v>13.74</v>
       </c>
     </row>
     <row r="47">
@@ -2586,7 +2619,7 @@
         <v>46</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>62</v>
@@ -2595,7 +2628,7 @@
         <v>1</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>15.14</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="48">
@@ -2624,7 +2657,7 @@
         <v>1</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>2.49</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="49">
@@ -2653,7 +2686,7 @@
         <v>1</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>2.75</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="50">
@@ -2682,7 +2715,7 @@
         <v>1</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>3.12</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="51">
@@ -2711,7 +2744,7 @@
         <v>1</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>3.12</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="52">
@@ -2740,7 +2773,7 @@
         <v>1</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>3.83</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="53">
@@ -2769,7 +2802,7 @@
         <v>1</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>3.83</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="54">
@@ -2798,7 +2831,7 @@
         <v>1</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>4.35</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="55">
@@ -2827,7 +2860,7 @@
         <v>1</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>5.25</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="56">
@@ -2856,7 +2889,7 @@
         <v>1</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>5.36</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="57">
@@ -2885,7 +2918,7 @@
         <v>1</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>5.37</v>
+        <v>8.22</v>
       </c>
     </row>
     <row r="58">
@@ -2914,7 +2947,7 @@
         <v>1</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>6.73</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="59">
@@ -2940,10 +2973,10 @@
         <v>74</v>
       </c>
       <c r="H59" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>10.01</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="60">
@@ -2972,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>16.47</v>
+        <v>15.56</v>
       </c>
     </row>
     <row r="61">
@@ -3001,7 +3034,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>23.28</v>
+        <v>17.82</v>
       </c>
     </row>
     <row r="62">
@@ -3030,7 +3063,7 @@
         <v>1</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="63">
@@ -3059,7 +3092,7 @@
         <v>1</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="64">
@@ -3088,7 +3121,7 @@
         <v>1</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="65">
@@ -3117,7 +3150,7 @@
         <v>1</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>3.37</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="66">
@@ -3146,7 +3179,7 @@
         <v>1</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>3.62</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="67">
@@ -3175,7 +3208,7 @@
         <v>1</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>3.74</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="68">
@@ -3204,7 +3237,7 @@
         <v>1</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>4</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="69">
@@ -3233,7 +3266,7 @@
         <v>1</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>4</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="70">
@@ -3262,7 +3295,7 @@
         <v>1</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>4.92</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="71">
@@ -3291,7 +3324,7 @@
         <v>1</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>7.76</v>
+        <v>7.64</v>
       </c>
     </row>
     <row r="72">
@@ -3320,7 +3353,7 @@
         <v>1</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>7.86</v>
+        <v>7.73</v>
       </c>
     </row>
     <row r="73">
@@ -3349,7 +3382,7 @@
         <v>0</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>8.92</v>
+        <v>8.78</v>
       </c>
     </row>
     <row r="74">
@@ -3378,7 +3411,7 @@
         <v>1</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>9.11</v>
+        <v>8.97</v>
       </c>
     </row>
     <row r="75">
@@ -3407,7 +3440,7 @@
         <v>0</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>9.47</v>
+        <v>18.84</v>
       </c>
     </row>
     <row r="76">
@@ -3436,7 +3469,7 @@
         <v>0</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>19.15</v>
+        <v>19.35</v>
       </c>
     </row>
     <row r="77">
@@ -3465,7 +3498,7 @@
         <v>0</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>19.67</v>
+        <v>24.09</v>
       </c>
     </row>
     <row r="78">
@@ -3494,7 +3527,7 @@
         <v>1</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="79">
@@ -3523,7 +3556,7 @@
         <v>1</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>2.02</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="80">
@@ -3552,7 +3585,7 @@
         <v>1</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="81">
@@ -3581,7 +3614,7 @@
         <v>1</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>3.16</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="82">
@@ -3610,7 +3643,7 @@
         <v>1</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>3.33</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="83">
@@ -3639,7 +3672,7 @@
         <v>1</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>3.93</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="84">
@@ -3668,7 +3701,7 @@
         <v>1</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="85">
@@ -3697,7 +3730,7 @@
         <v>1</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>4.14</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="86">
@@ -3726,7 +3759,7 @@
         <v>1</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>6.52</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="87">
@@ -3755,7 +3788,7 @@
         <v>1</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>7.85</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="88">
@@ -3784,7 +3817,7 @@
         <v>1</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>8.41</v>
+        <v>9.56</v>
       </c>
     </row>
     <row r="89">
@@ -3813,7 +3846,7 @@
         <v>0</v>
       </c>
       <c r="I89" s="4" t="n">
-        <v>12.44</v>
+        <v>14.18</v>
       </c>
     </row>
     <row r="90">
@@ -3839,10 +3872,10 @@
         <v>109</v>
       </c>
       <c r="H90" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>22.39</v>
+        <v>17.28</v>
       </c>
     </row>
     <row r="91">
@@ -3868,10 +3901,10 @@
         <v>110</v>
       </c>
       <c r="H91" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>27.24</v>
+        <v>18.09</v>
       </c>
     </row>
     <row r="92">
@@ -3900,7 +3933,7 @@
         <v>1</v>
       </c>
       <c r="I92" s="4" t="n">
-        <v>2.74</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="93">
@@ -3929,7 +3962,7 @@
         <v>1</v>
       </c>
       <c r="I93" s="4" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="94">
@@ -3958,7 +3991,7 @@
         <v>1</v>
       </c>
       <c r="I94" s="4" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="95">
@@ -3987,7 +4020,7 @@
         <v>1</v>
       </c>
       <c r="I95" s="4" t="n">
-        <v>5.11</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="96">
@@ -4016,7 +4049,7 @@
         <v>1</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>5.26</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="97">
@@ -4045,7 +4078,7 @@
         <v>1</v>
       </c>
       <c r="I97" s="4" t="n">
-        <v>5.59</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="98">
@@ -4074,7 +4107,7 @@
         <v>1</v>
       </c>
       <c r="I98" s="4" t="n">
-        <v>5.59</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="99">
@@ -4103,7 +4136,7 @@
         <v>1</v>
       </c>
       <c r="I99" s="4" t="n">
-        <v>6.66</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="100">
@@ -4132,7 +4165,7 @@
         <v>1</v>
       </c>
       <c r="I100" s="4" t="n">
-        <v>7.55</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="101">
@@ -4158,10 +4191,10 @@
         <v>124</v>
       </c>
       <c r="H101" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I101" s="4" t="n">
-        <v>14.05</v>
+        <v>10.66</v>
       </c>
     </row>
     <row r="102">
@@ -4187,10 +4220,10 @@
         <v>125</v>
       </c>
       <c r="H102" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I102" s="4" t="n">
-        <v>14.46</v>
+        <v>15.95</v>
       </c>
     </row>
     <row r="103">
@@ -4216,10 +4249,10 @@
         <v>126</v>
       </c>
       <c r="H103" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I103" s="4" t="n">
-        <v>16.94</v>
+        <v>24.37</v>
       </c>
     </row>
     <row r="104">
@@ -4248,7 +4281,7 @@
         <v>0</v>
       </c>
       <c r="I104" s="4" t="n">
-        <v>17.67</v>
+        <v>25.63</v>
       </c>
     </row>
     <row r="105">
@@ -4274,10 +4307,10 @@
         <v>128</v>
       </c>
       <c r="H105" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I105" s="4" t="n">
-        <v>23.39</v>
+        <v>26.55</v>
       </c>
     </row>
     <row r="106">
@@ -4306,7 +4339,7 @@
         <v>1</v>
       </c>
       <c r="I106" s="4" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="107">
@@ -4335,7 +4368,7 @@
         <v>1</v>
       </c>
       <c r="I107" s="4" t="n">
-        <v>2.45</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="108">
@@ -4364,7 +4397,7 @@
         <v>1</v>
       </c>
       <c r="I108" s="4" t="n">
-        <v>2.66</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="109">
@@ -4393,7 +4426,7 @@
         <v>1</v>
       </c>
       <c r="I109" s="4" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="110">
@@ -4422,7 +4455,7 @@
         <v>1</v>
       </c>
       <c r="I110" s="4" t="n">
-        <v>3.21</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="111">
@@ -4451,7 +4484,7 @@
         <v>1</v>
       </c>
       <c r="I111" s="4" t="n">
-        <v>4.49</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="112">
@@ -4480,7 +4513,7 @@
         <v>1</v>
       </c>
       <c r="I112" s="4" t="n">
-        <v>4.49</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="113">
@@ -4509,7 +4542,7 @@
         <v>1</v>
       </c>
       <c r="I113" s="4" t="n">
-        <v>4.51</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="114">
@@ -4538,7 +4571,7 @@
         <v>1</v>
       </c>
       <c r="I114" s="4" t="n">
-        <v>4.52</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="115">
@@ -4567,7 +4600,7 @@
         <v>1</v>
       </c>
       <c r="I115" s="4" t="n">
-        <v>7.94</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="116">
@@ -4596,7 +4629,7 @@
         <v>1</v>
       </c>
       <c r="I116" s="4" t="n">
-        <v>8.09</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="117">
@@ -4625,7 +4658,7 @@
         <v>0</v>
       </c>
       <c r="I117" s="4" t="n">
-        <v>10.25</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="118">
@@ -4651,10 +4684,10 @@
         <v>141</v>
       </c>
       <c r="H118" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I118" s="4" t="n">
-        <v>11.67</v>
+        <v>12.11</v>
       </c>
     </row>
     <row r="119">
@@ -4680,10 +4713,10 @@
         <v>142</v>
       </c>
       <c r="H119" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I119" s="4" t="n">
-        <v>12.05</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="120">
@@ -4709,10 +4742,10 @@
         <v>143</v>
       </c>
       <c r="H120" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I120" s="4" t="n">
-        <v>12.35</v>
+        <v>17.25</v>
       </c>
     </row>
     <row r="121">
@@ -4738,10 +4771,10 @@
         <v>144</v>
       </c>
       <c r="H121" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I121" s="4" t="n">
-        <v>17.59</v>
+        <v>25.72</v>
       </c>
     </row>
     <row r="122">
@@ -4770,7 +4803,7 @@
         <v>1</v>
       </c>
       <c r="I122" s="4" t="n">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="123">
@@ -4799,7 +4832,7 @@
         <v>1</v>
       </c>
       <c r="I123" s="4" t="n">
-        <v>2.57</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="124">
@@ -4828,7 +4861,7 @@
         <v>1</v>
       </c>
       <c r="I124" s="4" t="n">
-        <v>3.03</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="125">
@@ -4857,7 +4890,7 @@
         <v>1</v>
       </c>
       <c r="I125" s="4" t="n">
-        <v>3.23</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="126">
@@ -4886,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="I126" s="4" t="n">
-        <v>5.25</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="127">
@@ -4915,7 +4948,7 @@
         <v>1</v>
       </c>
       <c r="I127" s="4" t="n">
-        <v>5.4</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="128">
@@ -4944,7 +4977,7 @@
         <v>1</v>
       </c>
       <c r="I128" s="4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="129">
@@ -4973,7 +5006,7 @@
         <v>1</v>
       </c>
       <c r="I129" s="4" t="n">
-        <v>5.44</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="130">
@@ -5002,7 +5035,7 @@
         <v>1</v>
       </c>
       <c r="I130" s="4" t="n">
-        <v>8.77</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="131">
@@ -5031,7 +5064,7 @@
         <v>1</v>
       </c>
       <c r="I131" s="4" t="n">
-        <v>9.73</v>
+        <v>8.42</v>
       </c>
     </row>
     <row r="132">
@@ -5057,10 +5090,10 @@
         <v>158</v>
       </c>
       <c r="H132" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I132" s="4" t="n">
-        <v>9.87</v>
+        <v>9.34</v>
       </c>
     </row>
     <row r="133">
@@ -5086,10 +5119,10 @@
         <v>159</v>
       </c>
       <c r="H133" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I133" s="4" t="n">
-        <v>12.07</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="134">
@@ -5118,7 +5151,7 @@
         <v>1</v>
       </c>
       <c r="I134" s="4" t="n">
-        <v>13.75</v>
+        <v>11.59</v>
       </c>
     </row>
     <row r="135">
@@ -5147,7 +5180,7 @@
         <v>0</v>
       </c>
       <c r="I135" s="4" t="n">
-        <v>15.58</v>
+        <v>14.94</v>
       </c>
     </row>
     <row r="136">
@@ -5176,7 +5209,7 @@
         <v>1</v>
       </c>
       <c r="I136" s="4" t="n">
-        <v>21.07</v>
+        <v>20.21</v>
       </c>
     </row>
     <row r="137">
@@ -5205,7 +5238,7 @@
         <v>0</v>
       </c>
       <c r="I137" s="4" t="n">
-        <v>22.23</v>
+        <v>21.31</v>
       </c>
     </row>
     <row r="138">
@@ -5234,7 +5267,7 @@
         <v>1</v>
       </c>
       <c r="I138" s="4" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="139">
@@ -5263,7 +5296,7 @@
         <v>1</v>
       </c>
       <c r="I139" s="4" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="140">
@@ -5292,7 +5325,7 @@
         <v>1</v>
       </c>
       <c r="I140" s="4" t="n">
-        <v>3.54</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="141">
@@ -5318,10 +5351,10 @@
         <v>167</v>
       </c>
       <c r="H141" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I141" s="4" t="n">
-        <v>4.35</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="142">
@@ -5350,7 +5383,7 @@
         <v>1</v>
       </c>
       <c r="I142" s="4" t="n">
-        <v>4.39</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="143">
@@ -5379,7 +5412,7 @@
         <v>1</v>
       </c>
       <c r="I143" s="4" t="n">
-        <v>5.17</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="144">
@@ -5408,7 +5441,7 @@
         <v>1</v>
       </c>
       <c r="I144" s="4" t="n">
-        <v>5.17</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="145">
@@ -5437,7 +5470,7 @@
         <v>1</v>
       </c>
       <c r="I145" s="4" t="n">
-        <v>6.07</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="146">
@@ -5466,7 +5499,7 @@
         <v>1</v>
       </c>
       <c r="I146" s="4" t="n">
-        <v>6.11</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="147">
@@ -5495,7 +5528,7 @@
         <v>1</v>
       </c>
       <c r="I147" s="4" t="n">
-        <v>8.88</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="148">
@@ -5524,7 +5557,7 @@
         <v>1</v>
       </c>
       <c r="I148" s="4" t="n">
-        <v>12.92</v>
+        <v>8.79</v>
       </c>
     </row>
     <row r="149">
@@ -5550,10 +5583,10 @@
         <v>175</v>
       </c>
       <c r="H149" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I149" s="4" t="n">
-        <v>13.71</v>
+        <v>12.79</v>
       </c>
     </row>
     <row r="150">
@@ -5579,10 +5612,10 @@
         <v>176</v>
       </c>
       <c r="H150" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I150" s="4" t="n">
-        <v>15.21</v>
+        <v>13.57</v>
       </c>
     </row>
     <row r="151">
@@ -5608,10 +5641,10 @@
         <v>177</v>
       </c>
       <c r="H151" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I151" s="4" t="n">
-        <v>17.6</v>
+        <v>15.05</v>
       </c>
     </row>
     <row r="152">
@@ -5631,7 +5664,7 @@
         <v>181</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G152" s="3" t="s">
         <v>182</v>
@@ -5640,7 +5673,7 @@
         <v>1</v>
       </c>
       <c r="I152" s="4" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="153">
@@ -5660,7 +5693,7 @@
         <v>181</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G153" s="3" t="s">
         <v>183</v>
@@ -5669,7 +5702,7 @@
         <v>1</v>
       </c>
       <c r="I153" s="4" t="n">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="154">
@@ -5689,7 +5722,7 @@
         <v>181</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G154" s="3" t="s">
         <v>184</v>
@@ -5698,7 +5731,7 @@
         <v>1</v>
       </c>
       <c r="I154" s="4" t="n">
-        <v>3.57</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="155">
@@ -5718,7 +5751,7 @@
         <v>181</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G155" s="3" t="s">
         <v>185</v>
@@ -5727,7 +5760,7 @@
         <v>1</v>
       </c>
       <c r="I155" s="4" t="n">
-        <v>3.82</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="156">
@@ -5747,7 +5780,7 @@
         <v>181</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G156" s="3" t="s">
         <v>186</v>
@@ -5756,7 +5789,7 @@
         <v>1</v>
       </c>
       <c r="I156" s="4" t="n">
-        <v>4.13</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="157">
@@ -5776,7 +5809,7 @@
         <v>181</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G157" s="3" t="s">
         <v>187</v>
@@ -5785,7 +5818,7 @@
         <v>1</v>
       </c>
       <c r="I157" s="4" t="n">
-        <v>4.72</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="158">
@@ -5805,7 +5838,7 @@
         <v>181</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G158" s="3" t="s">
         <v>188</v>
@@ -5814,7 +5847,7 @@
         <v>1</v>
       </c>
       <c r="I158" s="4" t="n">
-        <v>4.72</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="159">
@@ -5834,7 +5867,7 @@
         <v>181</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G159" s="3" t="s">
         <v>189</v>
@@ -5843,7 +5876,7 @@
         <v>1</v>
       </c>
       <c r="I159" s="4" t="n">
-        <v>4.83</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="160">
@@ -5863,7 +5896,7 @@
         <v>181</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G160" s="3" t="s">
         <v>190</v>
@@ -5872,7 +5905,7 @@
         <v>1</v>
       </c>
       <c r="I160" s="4" t="n">
-        <v>5.51</v>
+        <v>8.31</v>
       </c>
     </row>
     <row r="161">
@@ -5892,7 +5925,7 @@
         <v>181</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G161" s="3" t="s">
         <v>191</v>
@@ -5901,7 +5934,7 @@
         <v>1</v>
       </c>
       <c r="I161" s="4" t="n">
-        <v>7.97</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="162">
@@ -5921,7 +5954,7 @@
         <v>181</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G162" s="3" t="s">
         <v>192</v>
@@ -5930,7 +5963,7 @@
         <v>1</v>
       </c>
       <c r="I162" s="4" t="n">
-        <v>10.26</v>
+        <v>17.89</v>
       </c>
     </row>
     <row r="163">
@@ -5950,16 +5983,16 @@
         <v>181</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G163" s="3" t="s">
         <v>193</v>
       </c>
       <c r="H163" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I163" s="4" t="n">
-        <v>12.27</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="164">
@@ -5979,16 +6012,16 @@
         <v>181</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G164" s="3" t="s">
         <v>194</v>
       </c>
       <c r="H164" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I164" s="4" t="n">
-        <v>18.14</v>
+        <v>20.51</v>
       </c>
     </row>
     <row r="165">
@@ -6008,16 +6041,16 @@
         <v>181</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G165" s="3" t="s">
         <v>195</v>
       </c>
       <c r="H165" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I165" s="4" t="n">
-        <v>20.11</v>
+        <v>21.13</v>
       </c>
     </row>
     <row r="166">
@@ -6037,16 +6070,16 @@
         <v>181</v>
       </c>
       <c r="F166" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G166" s="3" t="s">
         <v>196</v>
       </c>
       <c r="H166" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I166" s="4" t="n">
-        <v>20.95</v>
+        <v>24.19</v>
       </c>
     </row>
     <row r="167">
@@ -6072,10 +6105,10 @@
         <v>197</v>
       </c>
       <c r="H167" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I167" s="4" t="n">
-        <v>22.62</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="168">
@@ -6101,10 +6134,10 @@
         <v>198</v>
       </c>
       <c r="H168" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I168" s="4" t="n">
-        <v>29.67</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="169">
@@ -6130,10 +6163,10 @@
         <v>199</v>
       </c>
       <c r="H169" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I169" s="4" t="n">
-        <v>29.78</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="170">
@@ -6159,10 +6192,10 @@
         <v>200</v>
       </c>
       <c r="H170" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I170" s="4" t="n">
-        <v>34.45</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="171">
@@ -6170,28 +6203,28 @@
         <v>46242</v>
       </c>
       <c r="B171" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E171" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F171" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G171" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C171" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="D171" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E171" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F171" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="G171" s="3" t="s">
-        <v>205</v>
-      </c>
       <c r="H171" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I171" s="4" t="n">
-        <v>2.59</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="172">
@@ -6199,28 +6232,28 @@
         <v>46242</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="C172" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E172" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F172" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G172" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="D172" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E172" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F172" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="G172" s="3" t="s">
-        <v>206</v>
-      </c>
       <c r="H172" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I172" s="4" t="n">
-        <v>2.59</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="173">
@@ -6228,28 +6261,28 @@
         <v>46242</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="D173" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E173" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F173" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G173" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="E173" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F173" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="G173" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="H173" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I173" s="4" t="n">
-        <v>2.86</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="174">
@@ -6257,28 +6290,28 @@
         <v>46242</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="E174" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F174" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G174" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F174" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="G174" s="3" t="s">
-        <v>208</v>
-      </c>
       <c r="H174" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I174" s="4" t="n">
-        <v>2.93</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="175">
@@ -6286,28 +6319,28 @@
         <v>46242</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="F175" s="3" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H175" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I175" s="4" t="n">
-        <v>3.29</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="176">
@@ -6315,28 +6348,28 @@
         <v>46242</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="H176" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I176" s="4" t="n">
-        <v>4.59</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="177">
@@ -6344,28 +6377,28 @@
         <v>46242</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="H177" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I177" s="4" t="n">
-        <v>4.59</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="178">
@@ -6373,28 +6406,28 @@
         <v>46242</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="H178" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I178" s="4" t="n">
-        <v>5.04</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="179">
@@ -6402,28 +6435,28 @@
         <v>46242</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="H179" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I179" s="4" t="n">
-        <v>5.9</v>
+        <v>20.66</v>
       </c>
     </row>
     <row r="180">
@@ -6431,28 +6464,28 @@
         <v>46242</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="H180" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I180" s="4" t="n">
-        <v>7.59</v>
+        <v>23.34</v>
       </c>
     </row>
     <row r="181">
@@ -6460,28 +6493,28 @@
         <v>46242</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="H181" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I181" s="4" t="n">
-        <v>8</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="182">
@@ -6489,19 +6522,19 @@
         <v>46242</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="G182" s="3" t="s">
         <v>216</v>
@@ -6510,7 +6543,7 @@
         <v>1</v>
       </c>
       <c r="I182" s="4" t="n">
-        <v>8.41</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="183">
@@ -6518,28 +6551,28 @@
         <v>46242</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="G183" s="3" t="s">
         <v>217</v>
       </c>
       <c r="H183" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I183" s="4" t="n">
-        <v>10.01</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="184">
@@ -6547,19 +6580,19 @@
         <v>46242</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="F184" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="G184" s="3" t="s">
         <v>218</v>
@@ -6568,7 +6601,7 @@
         <v>1</v>
       </c>
       <c r="I184" s="4" t="n">
-        <v>13.68</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="185">
@@ -6576,19 +6609,19 @@
         <v>46242</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="F185" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="G185" s="3" t="s">
         <v>219</v>
@@ -6597,7 +6630,7 @@
         <v>1</v>
       </c>
       <c r="I185" s="4" t="n">
-        <v>15.26</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="186">
@@ -6605,19 +6638,19 @@
         <v>46242</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="F186" s="3" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="G186" s="3" t="s">
         <v>220</v>
@@ -6626,7 +6659,7 @@
         <v>1</v>
       </c>
       <c r="I186" s="4" t="n">
-        <v>2.02</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="187">
@@ -6634,19 +6667,19 @@
         <v>46242</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="G187" s="3" t="s">
         <v>221</v>
@@ -6655,7 +6688,7 @@
         <v>1</v>
       </c>
       <c r="I187" s="4" t="n">
-        <v>2.09</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="188">
@@ -6663,19 +6696,19 @@
         <v>46242</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="G188" s="3" t="s">
         <v>222</v>
@@ -6684,7 +6717,7 @@
         <v>1</v>
       </c>
       <c r="I188" s="4" t="n">
-        <v>2.19</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="189">
@@ -6692,19 +6725,19 @@
         <v>46242</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="G189" s="3" t="s">
         <v>223</v>
@@ -6713,7 +6746,7 @@
         <v>1</v>
       </c>
       <c r="I189" s="4" t="n">
-        <v>2.51</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="190">
@@ -6721,19 +6754,19 @@
         <v>46242</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="F190" s="3" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>224</v>
@@ -6742,7 +6775,7 @@
         <v>1</v>
       </c>
       <c r="I190" s="4" t="n">
-        <v>2.97</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="191">
@@ -6750,28 +6783,28 @@
         <v>46242</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="G191" s="3" t="s">
         <v>225</v>
       </c>
       <c r="H191" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I191" s="4" t="n">
-        <v>4.26</v>
+        <v>8.31</v>
       </c>
     </row>
     <row r="192">
@@ -6779,19 +6812,19 @@
         <v>46242</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="G192" s="3" t="s">
         <v>226</v>
@@ -6800,7 +6833,7 @@
         <v>1</v>
       </c>
       <c r="I192" s="4" t="n">
-        <v>4.26</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="193">
@@ -6808,19 +6841,19 @@
         <v>46242</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>227</v>
@@ -6829,7 +6862,7 @@
         <v>1</v>
       </c>
       <c r="I193" s="4" t="n">
-        <v>5.27</v>
+        <v>9.19</v>
       </c>
     </row>
     <row r="194">
@@ -6837,19 +6870,19 @@
         <v>46242</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="G194" s="3" t="s">
         <v>228</v>
@@ -6858,7 +6891,7 @@
         <v>1</v>
       </c>
       <c r="I194" s="4" t="n">
-        <v>6.79</v>
+        <v>14.24</v>
       </c>
     </row>
     <row r="195">
@@ -6866,28 +6899,28 @@
         <v>46242</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>229</v>
       </c>
       <c r="H195" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I195" s="4" t="n">
-        <v>9.41</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="196">
@@ -6895,28 +6928,28 @@
         <v>46242</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="G196" s="3" t="s">
         <v>230</v>
       </c>
       <c r="H196" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I196" s="4" t="n">
-        <v>9.94</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="197">
@@ -6924,19 +6957,19 @@
         <v>46242</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="F197" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="G197" s="3" t="s">
         <v>231</v>
@@ -6945,7 +6978,7 @@
         <v>1</v>
       </c>
       <c r="I197" s="4" t="n">
-        <v>10.19</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="198">
@@ -6953,19 +6986,19 @@
         <v>46242</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="G198" s="3" t="s">
         <v>232</v>
@@ -6974,7 +7007,7 @@
         <v>1</v>
       </c>
       <c r="I198" s="4" t="n">
-        <v>10.21</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="199">
@@ -6982,28 +7015,28 @@
         <v>46242</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="G199" s="3" t="s">
         <v>233</v>
       </c>
       <c r="H199" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I199" s="4" t="n">
-        <v>14.84</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="200">
@@ -7011,347 +7044,347 @@
         <v>46242</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="G200" s="3" t="s">
         <v>234</v>
       </c>
       <c r="H200" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I200" s="4" t="n">
-        <v>15.49</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>46243</v>
+        <v>46242</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>9</v>
+        <v>212</v>
       </c>
       <c r="C201" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D201" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E201" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="F201" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G201" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="D201" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="E201" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="F201" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="G201" s="3" t="s">
-        <v>238</v>
-      </c>
       <c r="H201" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I201" s="4" t="n">
-        <v>2.38</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>46243</v>
+        <v>46242</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>9</v>
+        <v>212</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="D202" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E202" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="F202" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G202" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="E202" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="F202" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="G202" s="3" t="s">
-        <v>239</v>
-      </c>
       <c r="H202" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I202" s="4" t="n">
-        <v>2.87</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>46243</v>
+        <v>46242</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>9</v>
+        <v>212</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="E203" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="F203" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G203" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="F203" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="G203" s="3" t="s">
-        <v>240</v>
-      </c>
       <c r="H203" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I203" s="4" t="n">
-        <v>2.95</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>46243</v>
+        <v>46242</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>9</v>
+        <v>212</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="H204" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I204" s="4" t="n">
-        <v>3.05</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>46243</v>
+        <v>46242</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>9</v>
+        <v>212</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="H205" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I205" s="4" t="n">
-        <v>3.55</v>
+        <v>8.92</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>46243</v>
+        <v>46242</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>9</v>
+        <v>212</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H206" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I206" s="4" t="n">
-        <v>3.67</v>
+        <v>9.16</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>46243</v>
+        <v>46242</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>9</v>
+        <v>212</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="H207" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I207" s="4" t="n">
-        <v>4.14</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>46243</v>
+        <v>46242</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>9</v>
+        <v>212</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="H208" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I208" s="4" t="n">
-        <v>4.14</v>
+        <v>13.87</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>46243</v>
+        <v>46242</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>9</v>
+        <v>212</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="F209" s="3" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="H209" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I209" s="4" t="n">
-        <v>5.49</v>
+        <v>14.12</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>46243</v>
+        <v>46242</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>9</v>
+        <v>212</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="F210" s="3" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H210" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I210" s="4" t="n">
-        <v>7.69</v>
+        <v>14.43</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>46243</v>
+        <v>46242</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>9</v>
+        <v>212</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="H211" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I211" s="4" t="n">
-        <v>7.74</v>
+        <v>15.13</v>
       </c>
     </row>
     <row r="212">
@@ -7362,16 +7395,16 @@
         <v>9</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F212" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="G212" s="3" t="s">
         <v>249</v>
@@ -7380,7 +7413,7 @@
         <v>1</v>
       </c>
       <c r="I212" s="4" t="n">
-        <v>11.34</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="213">
@@ -7391,25 +7424,25 @@
         <v>9</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F213" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="G213" s="3" t="s">
         <v>250</v>
       </c>
       <c r="H213" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I213" s="4" t="n">
-        <v>14.2</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="214">
@@ -7420,16 +7453,16 @@
         <v>9</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F214" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="G214" s="3" t="s">
         <v>251</v>
@@ -7438,7 +7471,7 @@
         <v>1</v>
       </c>
       <c r="I214" s="4" t="n">
-        <v>14.85</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="215">
@@ -7449,25 +7482,25 @@
         <v>9</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F215" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="G215" s="3" t="s">
         <v>252</v>
       </c>
       <c r="H215" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I215" s="4" t="n">
-        <v>17.24</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="216">
@@ -7478,16 +7511,16 @@
         <v>9</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F216" s="3" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="G216" s="3" t="s">
         <v>253</v>
@@ -7496,7 +7529,7 @@
         <v>1</v>
       </c>
       <c r="I216" s="4" t="n">
-        <v>2.12</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="217">
@@ -7507,16 +7540,16 @@
         <v>9</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F217" s="3" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="G217" s="3" t="s">
         <v>254</v>
@@ -7525,7 +7558,7 @@
         <v>1</v>
       </c>
       <c r="I217" s="4" t="n">
-        <v>2.48</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="218">
@@ -7536,16 +7569,16 @@
         <v>9</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F218" s="3" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="G218" s="3" t="s">
         <v>255</v>
@@ -7554,7 +7587,7 @@
         <v>1</v>
       </c>
       <c r="I218" s="4" t="n">
-        <v>3.08</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="219">
@@ -7565,16 +7598,16 @@
         <v>9</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F219" s="3" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="G219" s="3" t="s">
         <v>256</v>
@@ -7583,7 +7616,7 @@
         <v>1</v>
       </c>
       <c r="I219" s="4" t="n">
-        <v>3.61</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="220">
@@ -7594,16 +7627,16 @@
         <v>9</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F220" s="3" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="G220" s="3" t="s">
         <v>257</v>
@@ -7612,7 +7645,7 @@
         <v>1</v>
       </c>
       <c r="I220" s="4" t="n">
-        <v>4.29</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="221">
@@ -7623,16 +7656,16 @@
         <v>9</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F221" s="3" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="G221" s="3" t="s">
         <v>258</v>
@@ -7641,7 +7674,7 @@
         <v>1</v>
       </c>
       <c r="I221" s="4" t="n">
-        <v>4.84</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="222">
@@ -7652,16 +7685,16 @@
         <v>9</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F222" s="3" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="G222" s="3" t="s">
         <v>259</v>
@@ -7670,7 +7703,7 @@
         <v>1</v>
       </c>
       <c r="I222" s="4" t="n">
-        <v>4.84</v>
+        <v>8.29</v>
       </c>
     </row>
     <row r="223">
@@ -7681,25 +7714,25 @@
         <v>9</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F223" s="3" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="G223" s="3" t="s">
         <v>260</v>
       </c>
       <c r="H223" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I223" s="4" t="n">
-        <v>6.25</v>
+        <v>15.33</v>
       </c>
     </row>
     <row r="224">
@@ -7710,16 +7743,16 @@
         <v>9</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F224" s="3" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="G224" s="3" t="s">
         <v>261</v>
@@ -7728,7 +7761,7 @@
         <v>1</v>
       </c>
       <c r="I224" s="4" t="n">
-        <v>6.42</v>
+        <v>16.04</v>
       </c>
     </row>
     <row r="225">
@@ -7739,25 +7772,25 @@
         <v>9</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F225" s="3" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="G225" s="3" t="s">
         <v>262</v>
       </c>
       <c r="H225" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I225" s="4" t="n">
-        <v>6.97</v>
+        <v>16.98</v>
       </c>
     </row>
     <row r="226">
@@ -7768,16 +7801,16 @@
         <v>9</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F226" s="3" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="G226" s="3" t="s">
         <v>263</v>
@@ -7786,7 +7819,7 @@
         <v>0</v>
       </c>
       <c r="I226" s="4" t="n">
-        <v>10.49</v>
+        <v>18.63</v>
       </c>
     </row>
     <row r="227">
@@ -7797,25 +7830,25 @@
         <v>9</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F227" s="3" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="G227" s="3" t="s">
         <v>264</v>
       </c>
       <c r="H227" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I227" s="4" t="n">
-        <v>10.63</v>
+        <v>21.17</v>
       </c>
     </row>
     <row r="228">
@@ -7826,25 +7859,25 @@
         <v>9</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F228" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="G228" s="3" t="s">
         <v>265</v>
       </c>
       <c r="H228" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I228" s="4" t="n">
-        <v>15.03</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="229">
@@ -7855,25 +7888,25 @@
         <v>9</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="G229" s="3" t="s">
         <v>266</v>
       </c>
       <c r="H229" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I229" s="4" t="n">
-        <v>16.93</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="230">
@@ -7884,16 +7917,16 @@
         <v>9</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F230" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="G230" s="3" t="s">
         <v>267</v>
@@ -7902,7 +7935,7 @@
         <v>1</v>
       </c>
       <c r="I230" s="4" t="n">
-        <v>17.38</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="231">
@@ -7910,28 +7943,28 @@
         <v>46243</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="C231" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="E231" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="F231" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="G231" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="D231" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="E231" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F231" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="G231" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="H231" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I231" s="4" t="n">
-        <v>2.99</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="232">
@@ -7939,28 +7972,28 @@
         <v>46243</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="D232" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="E232" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="F232" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="G232" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="E232" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F232" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="G232" s="3" t="s">
-        <v>271</v>
-      </c>
       <c r="H232" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I232" s="4" t="n">
-        <v>3.18</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="233">
@@ -7968,28 +8001,28 @@
         <v>46243</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>11</v>
+        <v>248</v>
       </c>
       <c r="F233" s="3" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="G233" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="H233" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I233" s="4" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="234">
@@ -7997,28 +8030,28 @@
         <v>46243</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>11</v>
+        <v>248</v>
       </c>
       <c r="F234" s="3" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H234" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I234" s="4" t="n">
-        <v>3.51</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="235">
@@ -8026,28 +8059,28 @@
         <v>46243</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>11</v>
+        <v>248</v>
       </c>
       <c r="F235" s="3" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="H235" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I235" s="4" t="n">
-        <v>5.58</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="236">
@@ -8055,28 +8088,28 @@
         <v>46243</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>11</v>
+        <v>248</v>
       </c>
       <c r="F236" s="3" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="H236" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I236" s="4" t="n">
-        <v>5.58</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="237">
@@ -8084,28 +8117,28 @@
         <v>46243</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>11</v>
+        <v>248</v>
       </c>
       <c r="F237" s="3" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H237" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I237" s="4" t="n">
-        <v>7.39</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="238">
@@ -8113,28 +8146,28 @@
         <v>46243</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>11</v>
+        <v>248</v>
       </c>
       <c r="F238" s="3" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="H238" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I238" s="4" t="n">
-        <v>7.62</v>
+        <v>9.73</v>
       </c>
     </row>
     <row r="239">
@@ -8142,28 +8175,28 @@
         <v>46243</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>11</v>
+        <v>248</v>
       </c>
       <c r="F239" s="3" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H239" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I239" s="4" t="n">
-        <v>7.67</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="240">
@@ -8171,28 +8204,28 @@
         <v>46243</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>11</v>
+        <v>248</v>
       </c>
       <c r="F240" s="3" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="G240" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="H240" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I240" s="4" t="n">
-        <v>8.35</v>
+        <v>10.74</v>
       </c>
     </row>
     <row r="241">
@@ -8200,28 +8233,28 @@
         <v>46243</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>11</v>
+        <v>248</v>
       </c>
       <c r="F241" s="3" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="H241" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I241" s="4" t="n">
-        <v>9.18</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="242">
@@ -8232,25 +8265,25 @@
         <v>43</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="E242" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F242" s="3" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="G242" s="3" t="s">
         <v>281</v>
       </c>
       <c r="H242" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I242" s="4" t="n">
-        <v>13.34</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="243">
@@ -8261,25 +8294,25 @@
         <v>43</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="E243" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F243" s="3" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="G243" s="3" t="s">
         <v>282</v>
       </c>
       <c r="H243" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I243" s="4" t="n">
-        <v>19.14</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="244">
@@ -8290,16 +8323,16 @@
         <v>43</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="E244" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F244" s="3" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="G244" s="3" t="s">
         <v>283</v>
@@ -8308,7 +8341,7 @@
         <v>1</v>
       </c>
       <c r="I244" s="4" t="n">
-        <v>28.76</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="245">
@@ -8319,16 +8352,16 @@
         <v>43</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="E245" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F245" s="3" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="G245" s="3" t="s">
         <v>284</v>
@@ -8337,7 +8370,7 @@
         <v>1</v>
       </c>
       <c r="I245" s="4" t="n">
-        <v>28.76</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="246">
@@ -8348,25 +8381,25 @@
         <v>43</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="E246" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F246" s="3" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="G246" s="3" t="s">
         <v>285</v>
       </c>
       <c r="H246" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I246" s="4" t="n">
-        <v>38.15</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="247">
@@ -8377,25 +8410,25 @@
         <v>43</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="E247" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F247" s="3" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="G247" s="3" t="s">
         <v>286</v>
       </c>
       <c r="H247" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I247" s="4" t="n">
-        <v>47.73</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="248">
@@ -8406,25 +8439,25 @@
         <v>43</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="E248" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F248" s="3" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="G248" s="3" t="s">
         <v>287</v>
       </c>
       <c r="H248" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I248" s="4" t="n">
-        <v>48.55</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="249">
@@ -8435,25 +8468,344 @@
         <v>43</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="E249" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F249" s="3" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="G249" s="3" t="s">
         <v>288</v>
       </c>
       <c r="H249" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I249" s="4" t="n">
+        <v>8.18</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n">
+        <v>46243</v>
+      </c>
+      <c r="B250" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C250" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D250" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E250" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F250" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="G250" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="H250" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I250" s="4" t="n">
+        <v>8.73</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="n">
+        <v>46243</v>
+      </c>
+      <c r="B251" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C251" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D251" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E251" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F251" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="G251" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="H251" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I251" s="4" t="n">
+        <v>9.51</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="n">
+        <v>46243</v>
+      </c>
+      <c r="B252" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C252" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D252" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E252" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F252" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="G252" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="H252" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I252" s="4" t="n">
+        <v>9.8</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="n">
+        <v>46243</v>
+      </c>
+      <c r="B253" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C253" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D253" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E253" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F253" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="G253" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="H253" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="I249" s="4" t="n">
-        <v>55.43</v>
+      <c r="I253" s="4" t="n">
+        <v>14.26</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="n">
+        <v>46243</v>
+      </c>
+      <c r="B254" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C254" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D254" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E254" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F254" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="G254" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="H254" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I254" s="4" t="n">
+        <v>30.79</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="n">
+        <v>46243</v>
+      </c>
+      <c r="B255" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C255" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D255" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E255" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F255" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="G255" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="H255" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I255" s="4" t="n">
+        <v>30.79</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="n">
+        <v>46243</v>
+      </c>
+      <c r="B256" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C256" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D256" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E256" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F256" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="G256" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="H256" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I256" s="4" t="n">
+        <v>38.22</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="n">
+        <v>46243</v>
+      </c>
+      <c r="B257" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C257" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D257" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E257" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F257" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="G257" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="H257" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I257" s="4" t="n">
+        <v>40.85</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="n">
+        <v>46243</v>
+      </c>
+      <c r="B258" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C258" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D258" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E258" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F258" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="G258" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="H258" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I258" s="4" t="n">
+        <v>51.11</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="n">
+        <v>46243</v>
+      </c>
+      <c r="B259" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C259" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D259" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E259" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F259" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="G259" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="H259" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I259" s="4" t="n">
+        <v>51.99</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n">
+        <v>46243</v>
+      </c>
+      <c r="B260" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C260" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D260" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E260" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F260" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="G260" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="H260" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I260" s="4" t="n">
+        <v>59.91</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_anytime_tryscorers.xlsx
+++ b/files/NRL_anytime_tryscorers.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="268">
   <si>
     <t xml:space="preserve">Game</t>
   </si>
@@ -26,7 +26,700 @@
     <t xml:space="preserve">Price</t>
   </si>
   <si>
-    <t xml:space="preserve">south sydney rabbitohs at cronulla-sutherland sharks</t>
+    <t xml:space="preserve">north queensland cowboys at gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phillip Sami</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dean Ieremia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jojo Fifita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Campbell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keano Kini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AJ Brimson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arama Hau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beau Fermor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver Pascoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lachlan Ilias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tino Fa'asuamaleaui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurtis Morrin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chris Randall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Bai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klese Haas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Verrills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braidon Burns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murray Taulagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scott Drinkwater</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Chester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zac Laybutt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heilum Luki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kai O'Donnell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Clifford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaxon Purdue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soni Luke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reuben Cotter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam McIntyre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Griffin Neame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Sutton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs at sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jethro Rinakama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Kiraz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matt Burton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stephen Crichton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Tracey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enari Tuala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viliame Kikau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Preston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lachlan Galvin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sitili Tupouniua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Mann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaeman Salmon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jonathan Sua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Curran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark Nawaqanitawase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Tedesco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugo Savala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robert Toia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salesi Foketi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siua Wong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daly Cherry-Evans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reece Robson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Victor Radley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nat Butcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Watson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egan Butcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lindsay Collins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cody Ramsey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penrith panthers at warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penrith panthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Jenkins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian To'o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaxen Edgar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Izack Tago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiah Papali'i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paul Alamoti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathan Cleary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freddy Lussick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lindsay Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Henry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaah Yeo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Cogger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moses Leota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scott Sorensen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alofiana Khan-Pereira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dallin Watene-Zelezniak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leka Halasima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charnze Nicoll-Klokstad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ali Leiataua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Capewell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Laban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Te Maire Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chanel Harris-Tavita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wayde Egan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Fisher-Harris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Healey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erin Clark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eddie Ieremia-Toeava</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Metcalf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manly-warringah sea eagles at melbourne storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manly-warringah sea eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jason Saab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lehi Hopoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blake Wilson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tolutau Koula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reuben Garrick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joey Walsh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haumole Olakau'atu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corey Waddell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamal Fogarty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brandon Wakeham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Trbojevic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Onitoni Large</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taniela Paseka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moses Leo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sualauvi Faalogo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siulagi Tuimalatu-Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyran Wishart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Clarke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oryn Keeley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nick Meaney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron Munster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Howarth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hayden Watson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angus Hinchey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stefano Utoikamanu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe Chan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shawn Blore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trent Toelau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trent Loiero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos at dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grant Anderson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josiah Karapani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reece Walsh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezra Mam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kotoni Staggs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaiyden Hunt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Riki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deine Mariner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Walters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Duffy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Talty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Willison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gehamat Shibasaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payne Haas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamiso Tabuai-Fidow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selwyn Cobbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamayne Isaako</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herbie Farnworth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Bostock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connelly Lemuelu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kulikefu Finefeuiaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kodi Nikorima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremy Marshall-King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Flegler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiya Katoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Plath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Donoghoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Felise Kaufusi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morgan Knowles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Gilbert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels at south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Addo-Carr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian Kelly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiah Iongi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Penisini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Samrani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitchell Moses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kitione Kautoga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tallyn Da Silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronald Volkman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack De Belin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luca Moretti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Paulo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Johnston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campbell Graham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tallis Duncan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cody Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Wighton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Dufty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">David Fifita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Elliott</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashton Ward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron Murray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keaon Koloamatangi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brandon Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Sullivan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John Radel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tevita Tatola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jye Gray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamie Humphreys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights at canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Savage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jed Stuart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaeo Weekes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simi Sasagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Timoko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Strange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zac Hosking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ata Mariota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owen Pattie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Sanders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe Roddy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daine Laurie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matty Nicholson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corey Horsburgh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Starling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joseph Tapine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominic Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greg Marzhew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fletcher Sharpe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bradman Best</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kalyn Ponga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jermaine McEwen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francis Manuleleua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dane Gagai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trey Mooney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandon Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phoenix Crossland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harrison Graham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fletcher Hunt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brodie Jones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks at st george-illawarra dragons</t>
   </si>
   <si>
     <t xml:space="preserve">cronulla-sutherland sharks</t>
@@ -44,12 +737,12 @@
     <t xml:space="preserve">Mawene Hiroti</t>
   </si>
   <si>
-    <t xml:space="preserve">Kayal Iro</t>
-  </si>
-  <si>
     <t xml:space="preserve">Braydon Trindall</t>
   </si>
   <si>
+    <t xml:space="preserve">Jesse Ramien</t>
+  </si>
+  <si>
     <t xml:space="preserve">Briton Nikora</t>
   </si>
   <si>
@@ -68,757 +761,19 @@
     <t xml:space="preserve">Blayke Brailey</t>
   </si>
   <si>
+    <t xml:space="preserve">Jesse Colquhoun</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cameron McInnes</t>
   </si>
   <si>
     <t xml:space="preserve">Tuku Hau Tapuha</t>
   </si>
   <si>
-    <t xml:space="preserve">south sydney rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Johnston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campbell Graham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tallis Duncan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cody Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Dufty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Wighton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">David Fifita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Euan Aitken</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashton Ward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keaon Koloamatangi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameron Murray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brandon Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">John Radel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tevita Tatola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jye Gray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamie Humphreys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels at wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Addo-Carr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian Kelly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiah Iongi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Araz Nanva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan Samrani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronald Volkman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jonah Pezet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tallyn Da Silva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitione Kautoga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kelma Tuilagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack De Belin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joash Papalii</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Tuivaiti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeral Skelton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunia Turuva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jahream Bula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Doueihi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Starford To'a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heamasi Makasini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samuela Fainu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sione Fainu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jarome Luai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Seyfarth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jared Haywood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terrell May</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apisai Koroisau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latu Fainu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fonua Pole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys at gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phillip Sami</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dean Ieremia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jojo Fifita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Campbell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keano Kini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arama Hau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beau Fermor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AJ Brimson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oliver Pascoe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zane Harrison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tino Fa'asuamaleaui</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Bai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chris Randall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Klese Haas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Verrills</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lachlan Ilias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Braidon Burns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Murray Taulagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremiah Nanai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scott Drinkwater</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Chester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zac Laybutt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Dearden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heilum Luki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reed Mahoney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaxon Purdue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reuben Cotter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam McIntyre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soni Luke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Griffin Neame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs at sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jethro Rinakama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Kiraz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matt Burton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Preston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Tracey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enari Tuala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lachlan Galvin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaeman Salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Curran</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sean O'Sullivan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bailey Hayward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gordon Chan Kum Tong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viliame Kikau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harry Hayes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mark Nawaqanitawase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel Tupou</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hugo Savala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cody Ramsey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daly Cherry-Evans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nat Butcher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siua Wong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reece Robson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Victor Radley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Watson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Egan Butcher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spencer Leniu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Naufahu Whyte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rex Bassingthwaighte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penrith panthers at warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penrith panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Jenkins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian To'o</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casey McLean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Edwards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paul Alamoti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nathan Cleary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blaize Talagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiah Papali'i</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freddy Lussick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lindsay Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Izack Tago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaah Yeo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Henry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moses Leota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scott Sorensen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alofiana Khan-Pereira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dallin Watene-Zelezniak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ali Leiataua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leka Halasima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taine Tuaupiki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Pompey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Laban</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chanel Harris-Tavita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Te Maire Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurt Capewell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wayde Egan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Fisher-Harris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Healey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erin Clark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manly-warringah sea eagles at melbourne storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manly-warringah sea eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Trbojevic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jason Saab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lehi Hopoate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tolutau Koula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reuben Garrick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haumole Olakau'atu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joey Walsh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan Bullemor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamal Fogarty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Simpkin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simione Laiafi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aaron Schoupp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Trbojevic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taniela Paseka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicholas Lenaz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Will Warbrick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sualauvi Faalogo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siulagi Tuimalatu-Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harry Grant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyran Wishart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nick Meaney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Howarth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oryn Keeley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trent Toelau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Clarke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stefano Utoikamanu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trent Loiero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Davvy Moale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gabriel Satrick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos at dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deine Mariner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josiah Karapani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reece Walsh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ezra Mam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gehamat Shibasaki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kotoni Staggs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Reynolds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan Riki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brendan Piakura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben Talty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cory Paix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Willison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payne Haas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamiso Tabuai-Fidow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamayne Isaako</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tevita Naufahu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herbie Farnworth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selwyn Cobbo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kodi Nikorima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connelly Lemuelu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brad Schneider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremy Marshall-King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kulikefu Finefeuiaki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Plath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Flegler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurt Donoghoe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Felise Kaufusi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morgan Knowles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Gilbert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Francis Molo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights at canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Savage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hudson Young</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaeo Weekes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jed Stuart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noah Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simi Sasagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Timoko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zac Hosking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan Strange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owen Pattie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan Sanders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Starling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joseph Tapine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corey Horsburgh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daine Laurie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Savelio Tamale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dominic Young</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greg Marzhew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fletcher Sharpe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Lucas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bradman Best</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kalyn Ponga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dane Gagai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trey Mooney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Francis Manuleleua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harrison Graham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fletcher Hunt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phoenix Crossland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brodie Jones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks at st george-illawarra dragons</t>
+    <t xml:space="preserve">Braden Hamlin-Uele</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niwhai Puru</t>
   </si>
   <si>
     <t xml:space="preserve">st george-illawarra dragons</t>
@@ -830,28 +785,28 @@
     <t xml:space="preserve">Setu Tu</t>
   </si>
   <si>
-    <t xml:space="preserve">Mathew Feagai</t>
+    <t xml:space="preserve">Clinton Gutherson</t>
   </si>
   <si>
     <t xml:space="preserve">Valentine Holmes</t>
   </si>
   <si>
-    <t xml:space="preserve">Clinton Gutherson</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dylan Egan</t>
   </si>
   <si>
+    <t xml:space="preserve">Hamish Stewart</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jacob Liddle</t>
   </si>
   <si>
     <t xml:space="preserve">Kyle Flanagan</t>
   </si>
   <si>
-    <t xml:space="preserve">Daniel Atkinson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamish Stewart</t>
+    <t xml:space="preserve">Mosese Suli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lyhkan King-Togia</t>
   </si>
   <si>
     <t xml:space="preserve">Damien Cook</t>
@@ -861,24 +816,6 @@
   </si>
   <si>
     <t xml:space="preserve">Ryan Couchman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loko Jnr Pasifiki Tonga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mosese Suli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Kerr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Halangahu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toby Couchman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lyhkan King-Togia</t>
   </si>
 </sst>
 </file>
@@ -1238,7 +1175,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="3">
@@ -1252,7 +1189,7 @@
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>2.11</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="4">
@@ -1266,7 +1203,7 @@
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -1280,7 +1217,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="6">
@@ -1294,7 +1231,7 @@
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>3.13</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="7">
@@ -1308,7 +1245,7 @@
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>3.13</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="8">
@@ -1322,7 +1259,7 @@
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>3.59</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="9">
@@ -1336,7 +1273,7 @@
         <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>3.89</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="10">
@@ -1350,7 +1287,7 @@
         <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>4.61</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="11">
@@ -1364,7 +1301,7 @@
         <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>5.39</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="12">
@@ -1378,7 +1315,7 @@
         <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>5.54</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="13">
@@ -1392,7 +1329,7 @@
         <v>17</v>
       </c>
       <c r="D13" t="n">
-        <v>10.57</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="14">
@@ -1406,7 +1343,7 @@
         <v>18</v>
       </c>
       <c r="D14" t="n">
-        <v>12.07</v>
+        <v>8.78</v>
       </c>
     </row>
     <row r="15">
@@ -1420,7 +1357,7 @@
         <v>19</v>
       </c>
       <c r="D15" t="n">
-        <v>13.57</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="16">
@@ -1428,13 +1365,13 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" t="s">
         <v>20</v>
       </c>
-      <c r="C16" t="s">
-        <v>21</v>
-      </c>
       <c r="D16" t="n">
-        <v>1.87</v>
+        <v>18.09</v>
       </c>
     </row>
     <row r="17">
@@ -1442,13 +1379,13 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D17" t="n">
-        <v>2.75</v>
+        <v>18.93</v>
       </c>
     </row>
     <row r="18">
@@ -1456,13 +1393,13 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
       </c>
       <c r="D18" t="n">
-        <v>3.05</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="19">
@@ -1470,13 +1407,13 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C19" t="s">
         <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>3.75</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="20">
@@ -1484,13 +1421,13 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C20" t="s">
         <v>25</v>
       </c>
       <c r="D20" t="n">
-        <v>4.48</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="21">
@@ -1498,13 +1435,13 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>4.48</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="22">
@@ -1512,13 +1449,13 @@
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C22" t="s">
         <v>27</v>
       </c>
       <c r="D22" t="n">
-        <v>4.96</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="23">
@@ -1526,13 +1463,13 @@
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C23" t="s">
         <v>28</v>
       </c>
       <c r="D23" t="n">
-        <v>7.1</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="24">
@@ -1540,13 +1477,13 @@
         <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C24" t="s">
         <v>29</v>
       </c>
       <c r="D24" t="n">
-        <v>7.58</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="25">
@@ -1554,13 +1491,13 @@
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C25" t="s">
         <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>8.13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1568,13 +1505,13 @@
         <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C26" t="s">
         <v>31</v>
       </c>
       <c r="D26" t="n">
-        <v>8.14</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="27">
@@ -1582,13 +1519,13 @@
         <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C27" t="s">
         <v>32</v>
       </c>
       <c r="D27" t="n">
-        <v>12.46</v>
+        <v>8.31</v>
       </c>
     </row>
     <row r="28">
@@ -1596,13 +1533,13 @@
         <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C28" t="s">
         <v>33</v>
       </c>
       <c r="D28" t="n">
-        <v>13.24</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="29">
@@ -1610,13 +1547,13 @@
         <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C29" t="s">
         <v>34</v>
       </c>
       <c r="D29" t="n">
-        <v>13.37</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="30">
@@ -1624,13 +1561,13 @@
         <v>4</v>
       </c>
       <c r="B30" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C30" t="s">
         <v>35</v>
       </c>
       <c r="D30" t="n">
-        <v>14.74</v>
+        <v>16.14</v>
       </c>
     </row>
     <row r="31">
@@ -1638,13 +1575,13 @@
         <v>4</v>
       </c>
       <c r="B31" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C31" t="s">
         <v>36</v>
       </c>
       <c r="D31" t="n">
-        <v>16.24</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="32">
@@ -1658,7 +1595,7 @@
         <v>39</v>
       </c>
       <c r="D32" t="n">
-        <v>1.88</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="33">
@@ -1672,7 +1609,7 @@
         <v>40</v>
       </c>
       <c r="D33" t="n">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="34">
@@ -1686,7 +1623,7 @@
         <v>41</v>
       </c>
       <c r="D34" t="n">
-        <v>2.72</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="35">
@@ -1700,7 +1637,7 @@
         <v>42</v>
       </c>
       <c r="D35" t="n">
-        <v>2.98</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="36">
@@ -1714,7 +1651,7 @@
         <v>43</v>
       </c>
       <c r="D36" t="n">
-        <v>3.28</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="37">
@@ -1728,7 +1665,7 @@
         <v>44</v>
       </c>
       <c r="D37" t="n">
-        <v>4.06</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="38">
@@ -1742,7 +1679,7 @@
         <v>45</v>
       </c>
       <c r="D38" t="n">
-        <v>4.06</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="39">
@@ -1756,7 +1693,7 @@
         <v>46</v>
       </c>
       <c r="D39" t="n">
-        <v>4.33</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="40">
@@ -1770,7 +1707,7 @@
         <v>47</v>
       </c>
       <c r="D40" t="n">
-        <v>5.55</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="41">
@@ -1784,7 +1721,7 @@
         <v>48</v>
       </c>
       <c r="D41" t="n">
-        <v>6.84</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="42">
@@ -1798,7 +1735,7 @@
         <v>49</v>
       </c>
       <c r="D42" t="n">
-        <v>8.83</v>
+        <v>14.38</v>
       </c>
     </row>
     <row r="43">
@@ -1812,7 +1749,7 @@
         <v>50</v>
       </c>
       <c r="D43" t="n">
-        <v>10.8</v>
+        <v>14.55</v>
       </c>
     </row>
     <row r="44">
@@ -1826,7 +1763,7 @@
         <v>51</v>
       </c>
       <c r="D44" t="n">
-        <v>11.75</v>
+        <v>14.56</v>
       </c>
     </row>
     <row r="45">
@@ -1840,7 +1777,7 @@
         <v>52</v>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>15.22</v>
       </c>
     </row>
     <row r="46">
@@ -1848,13 +1785,13 @@
         <v>37</v>
       </c>
       <c r="B46" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C46" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D46" t="n">
-        <v>13.74</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="47">
@@ -1862,13 +1799,13 @@
         <v>37</v>
       </c>
       <c r="B47" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C47" t="s">
         <v>55</v>
       </c>
       <c r="D47" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="48">
@@ -1876,13 +1813,13 @@
         <v>37</v>
       </c>
       <c r="B48" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C48" t="s">
         <v>56</v>
       </c>
       <c r="D48" t="n">
-        <v>2.65</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="49">
@@ -1890,13 +1827,13 @@
         <v>37</v>
       </c>
       <c r="B49" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C49" t="s">
         <v>57</v>
       </c>
       <c r="D49" t="n">
-        <v>2.93</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="50">
@@ -1904,13 +1841,13 @@
         <v>37</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50" t="s">
         <v>58</v>
       </c>
       <c r="D50" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="51">
@@ -1918,13 +1855,13 @@
         <v>37</v>
       </c>
       <c r="B51" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C51" t="s">
         <v>59</v>
       </c>
       <c r="D51" t="n">
-        <v>3.69</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="52">
@@ -1932,13 +1869,13 @@
         <v>37</v>
       </c>
       <c r="B52" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C52" t="s">
         <v>60</v>
       </c>
       <c r="D52" t="n">
-        <v>4.68</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="53">
@@ -1946,13 +1883,13 @@
         <v>37</v>
       </c>
       <c r="B53" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C53" t="s">
         <v>61</v>
       </c>
       <c r="D53" t="n">
-        <v>5.1</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="54">
@@ -1960,13 +1897,13 @@
         <v>37</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C54" t="s">
         <v>62</v>
       </c>
       <c r="D54" t="n">
-        <v>5.64</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="55">
@@ -1974,13 +1911,13 @@
         <v>37</v>
       </c>
       <c r="B55" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C55" t="s">
         <v>63</v>
       </c>
       <c r="D55" t="n">
-        <v>5.77</v>
+        <v>7.93</v>
       </c>
     </row>
     <row r="56">
@@ -1988,13 +1925,13 @@
         <v>37</v>
       </c>
       <c r="B56" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C56" t="s">
         <v>64</v>
       </c>
       <c r="D56" t="n">
-        <v>7.25</v>
+        <v>8.13</v>
       </c>
     </row>
     <row r="57">
@@ -2002,13 +1939,13 @@
         <v>37</v>
       </c>
       <c r="B57" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C57" t="s">
         <v>65</v>
       </c>
       <c r="D57" t="n">
-        <v>8.22</v>
+        <v>10.36</v>
       </c>
     </row>
     <row r="58">
@@ -2016,13 +1953,13 @@
         <v>37</v>
       </c>
       <c r="B58" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C58" t="s">
         <v>66</v>
       </c>
       <c r="D58" t="n">
-        <v>10.81</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="59">
@@ -2030,13 +1967,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C59" t="s">
         <v>67</v>
       </c>
       <c r="D59" t="n">
-        <v>12.47</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="60">
@@ -2044,13 +1981,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C60" t="s">
         <v>68</v>
       </c>
       <c r="D60" t="n">
-        <v>15.56</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="61">
@@ -2058,13 +1995,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C61" t="s">
         <v>69</v>
       </c>
       <c r="D61" t="n">
-        <v>17.82</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="62">
@@ -2078,7 +2015,7 @@
         <v>72</v>
       </c>
       <c r="D62" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="63">
@@ -2092,7 +2029,7 @@
         <v>73</v>
       </c>
       <c r="D63" t="n">
-        <v>2.81</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="64">
@@ -2106,7 +2043,7 @@
         <v>74</v>
       </c>
       <c r="D64" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="65">
@@ -2120,7 +2057,7 @@
         <v>75</v>
       </c>
       <c r="D65" t="n">
-        <v>3.32</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="66">
@@ -2134,7 +2071,7 @@
         <v>76</v>
       </c>
       <c r="D66" t="n">
-        <v>3.57</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="67">
@@ -2148,7 +2085,7 @@
         <v>77</v>
       </c>
       <c r="D67" t="n">
-        <v>3.63</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="68">
@@ -2162,7 +2099,7 @@
         <v>78</v>
       </c>
       <c r="D68" t="n">
-        <v>3.64</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="69">
@@ -2176,7 +2113,7 @@
         <v>79</v>
       </c>
       <c r="D69" t="n">
-        <v>3.69</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="70">
@@ -2190,7 +2127,7 @@
         <v>80</v>
       </c>
       <c r="D70" t="n">
-        <v>4.84</v>
+        <v>8.79</v>
       </c>
     </row>
     <row r="71">
@@ -2204,7 +2141,7 @@
         <v>81</v>
       </c>
       <c r="D71" t="n">
-        <v>7.64</v>
+        <v>9.61</v>
       </c>
     </row>
     <row r="72">
@@ -2218,7 +2155,7 @@
         <v>82</v>
       </c>
       <c r="D72" t="n">
-        <v>7.73</v>
+        <v>11.51</v>
       </c>
     </row>
     <row r="73">
@@ -2232,7 +2169,7 @@
         <v>83</v>
       </c>
       <c r="D73" t="n">
-        <v>8.78</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="74">
@@ -2246,7 +2183,7 @@
         <v>84</v>
       </c>
       <c r="D74" t="n">
-        <v>8.97</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="75">
@@ -2260,7 +2197,7 @@
         <v>85</v>
       </c>
       <c r="D75" t="n">
-        <v>18.84</v>
+        <v>20.49</v>
       </c>
     </row>
     <row r="76">
@@ -2274,7 +2211,7 @@
         <v>86</v>
       </c>
       <c r="D76" t="n">
-        <v>19.35</v>
+        <v>21.95</v>
       </c>
     </row>
     <row r="77">
@@ -2282,13 +2219,13 @@
         <v>70</v>
       </c>
       <c r="B77" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="C77" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D77" t="n">
-        <v>24.09</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="78">
@@ -2296,13 +2233,13 @@
         <v>70</v>
       </c>
       <c r="B78" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C78" t="s">
         <v>89</v>
       </c>
       <c r="D78" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="79">
@@ -2310,13 +2247,13 @@
         <v>70</v>
       </c>
       <c r="B79" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C79" t="s">
         <v>90</v>
       </c>
       <c r="D79" t="n">
-        <v>2.23</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="80">
@@ -2324,13 +2261,13 @@
         <v>70</v>
       </c>
       <c r="B80" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C80" t="s">
         <v>91</v>
       </c>
       <c r="D80" t="n">
-        <v>2.46</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="81">
@@ -2338,13 +2275,13 @@
         <v>70</v>
       </c>
       <c r="B81" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C81" t="s">
         <v>92</v>
       </c>
       <c r="D81" t="n">
-        <v>2.84</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="82">
@@ -2352,13 +2289,13 @@
         <v>70</v>
       </c>
       <c r="B82" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C82" t="s">
         <v>93</v>
       </c>
       <c r="D82" t="n">
-        <v>3.54</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="83">
@@ -2366,13 +2303,13 @@
         <v>70</v>
       </c>
       <c r="B83" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C83" t="s">
         <v>94</v>
       </c>
       <c r="D83" t="n">
-        <v>3.73</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="84">
@@ -2380,13 +2317,13 @@
         <v>70</v>
       </c>
       <c r="B84" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C84" t="s">
         <v>95</v>
       </c>
       <c r="D84" t="n">
-        <v>3.8</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="85">
@@ -2394,13 +2331,13 @@
         <v>70</v>
       </c>
       <c r="B85" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C85" t="s">
         <v>96</v>
       </c>
       <c r="D85" t="n">
-        <v>4.07</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="86">
@@ -2408,13 +2345,13 @@
         <v>70</v>
       </c>
       <c r="B86" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C86" t="s">
         <v>97</v>
       </c>
       <c r="D86" t="n">
-        <v>6.35</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="87">
@@ -2422,13 +2359,13 @@
         <v>70</v>
       </c>
       <c r="B87" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C87" t="s">
         <v>98</v>
       </c>
       <c r="D87" t="n">
-        <v>7.4</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="88">
@@ -2436,13 +2373,13 @@
         <v>70</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C88" t="s">
         <v>99</v>
       </c>
       <c r="D88" t="n">
-        <v>9.56</v>
+        <v>14.21</v>
       </c>
     </row>
     <row r="89">
@@ -2450,13 +2387,13 @@
         <v>70</v>
       </c>
       <c r="B89" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C89" t="s">
         <v>100</v>
       </c>
       <c r="D89" t="n">
-        <v>14.18</v>
+        <v>15.16</v>
       </c>
     </row>
     <row r="90">
@@ -2464,13 +2401,13 @@
         <v>70</v>
       </c>
       <c r="B90" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C90" t="s">
         <v>101</v>
       </c>
       <c r="D90" t="n">
-        <v>17.28</v>
+        <v>17.52</v>
       </c>
     </row>
     <row r="91">
@@ -2478,13 +2415,13 @@
         <v>70</v>
       </c>
       <c r="B91" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C91" t="s">
         <v>102</v>
       </c>
       <c r="D91" t="n">
-        <v>18.09</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="92">
@@ -2498,7 +2435,7 @@
         <v>105</v>
       </c>
       <c r="D92" t="n">
-        <v>2.61</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="93">
@@ -2512,7 +2449,7 @@
         <v>106</v>
       </c>
       <c r="D93" t="n">
-        <v>3.14</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="94">
@@ -2526,7 +2463,7 @@
         <v>107</v>
       </c>
       <c r="D94" t="n">
-        <v>3.75</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="95">
@@ -2540,7 +2477,7 @@
         <v>108</v>
       </c>
       <c r="D95" t="n">
-        <v>4.37</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="96">
@@ -2554,7 +2491,7 @@
         <v>109</v>
       </c>
       <c r="D96" t="n">
-        <v>4.83</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="97">
@@ -2568,7 +2505,7 @@
         <v>110</v>
       </c>
       <c r="D97" t="n">
-        <v>4.97</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="98">
@@ -2582,7 +2519,7 @@
         <v>111</v>
       </c>
       <c r="D98" t="n">
-        <v>6.29</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="99">
@@ -2596,7 +2533,7 @@
         <v>112</v>
       </c>
       <c r="D99" t="n">
-        <v>6.71</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="100">
@@ -2610,7 +2547,7 @@
         <v>113</v>
       </c>
       <c r="D100" t="n">
-        <v>7.06</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="101">
@@ -2624,7 +2561,7 @@
         <v>114</v>
       </c>
       <c r="D101" t="n">
-        <v>10.66</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="102">
@@ -2638,7 +2575,7 @@
         <v>115</v>
       </c>
       <c r="D102" t="n">
-        <v>15.95</v>
+        <v>20.33</v>
       </c>
     </row>
     <row r="103">
@@ -2652,7 +2589,7 @@
         <v>116</v>
       </c>
       <c r="D103" t="n">
-        <v>24.37</v>
+        <v>20.51</v>
       </c>
     </row>
     <row r="104">
@@ -2666,7 +2603,7 @@
         <v>117</v>
       </c>
       <c r="D104" t="n">
-        <v>25.63</v>
+        <v>21.02</v>
       </c>
     </row>
     <row r="105">
@@ -2674,13 +2611,13 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="C105" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D105" t="n">
-        <v>26.55</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="106">
@@ -2688,13 +2625,13 @@
         <v>103</v>
       </c>
       <c r="B106" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C106" t="s">
         <v>120</v>
       </c>
       <c r="D106" t="n">
-        <v>1.74</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="107">
@@ -2702,13 +2639,13 @@
         <v>103</v>
       </c>
       <c r="B107" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C107" t="s">
         <v>121</v>
       </c>
       <c r="D107" t="n">
-        <v>2.02</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="108">
@@ -2716,13 +2653,13 @@
         <v>103</v>
       </c>
       <c r="B108" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C108" t="s">
         <v>122</v>
       </c>
       <c r="D108" t="n">
-        <v>2.93</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="109">
@@ -2730,13 +2667,13 @@
         <v>103</v>
       </c>
       <c r="B109" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C109" t="s">
         <v>123</v>
       </c>
       <c r="D109" t="n">
-        <v>3.2</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="110">
@@ -2744,13 +2681,13 @@
         <v>103</v>
       </c>
       <c r="B110" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C110" t="s">
         <v>124</v>
       </c>
       <c r="D110" t="n">
-        <v>3.59</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="111">
@@ -2758,13 +2695,13 @@
         <v>103</v>
       </c>
       <c r="B111" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C111" t="s">
         <v>125</v>
       </c>
       <c r="D111" t="n">
-        <v>4.43</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="112">
@@ -2772,13 +2709,13 @@
         <v>103</v>
       </c>
       <c r="B112" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C112" t="s">
         <v>126</v>
       </c>
       <c r="D112" t="n">
-        <v>4.43</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="113">
@@ -2786,13 +2723,13 @@
         <v>103</v>
       </c>
       <c r="B113" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C113" t="s">
         <v>127</v>
       </c>
       <c r="D113" t="n">
-        <v>4.44</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="114">
@@ -2800,13 +2737,13 @@
         <v>103</v>
       </c>
       <c r="B114" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C114" t="s">
         <v>128</v>
       </c>
       <c r="D114" t="n">
-        <v>7.05</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="115">
@@ -2814,13 +2751,13 @@
         <v>103</v>
       </c>
       <c r="B115" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C115" t="s">
         <v>129</v>
       </c>
       <c r="D115" t="n">
-        <v>7.79</v>
+        <v>9.61</v>
       </c>
     </row>
     <row r="116">
@@ -2828,13 +2765,13 @@
         <v>103</v>
       </c>
       <c r="B116" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C116" t="s">
         <v>130</v>
       </c>
       <c r="D116" t="n">
-        <v>7.94</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="117">
@@ -2842,13 +2779,13 @@
         <v>103</v>
       </c>
       <c r="B117" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C117" t="s">
         <v>131</v>
       </c>
       <c r="D117" t="n">
-        <v>10.05</v>
+        <v>11.53</v>
       </c>
     </row>
     <row r="118">
@@ -2856,13 +2793,13 @@
         <v>103</v>
       </c>
       <c r="B118" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C118" t="s">
         <v>132</v>
       </c>
       <c r="D118" t="n">
-        <v>12.11</v>
+        <v>17.08</v>
       </c>
     </row>
     <row r="119">
@@ -2870,13 +2807,13 @@
         <v>103</v>
       </c>
       <c r="B119" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C119" t="s">
         <v>133</v>
       </c>
       <c r="D119" t="n">
-        <v>15.49</v>
+        <v>19.11</v>
       </c>
     </row>
     <row r="120">
@@ -2884,13 +2821,13 @@
         <v>103</v>
       </c>
       <c r="B120" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C120" t="s">
         <v>134</v>
       </c>
       <c r="D120" t="n">
-        <v>17.25</v>
+        <v>19.75</v>
       </c>
     </row>
     <row r="121">
@@ -2898,13 +2835,13 @@
         <v>103</v>
       </c>
       <c r="B121" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C121" t="s">
         <v>135</v>
       </c>
       <c r="D121" t="n">
-        <v>25.72</v>
+        <v>19.83</v>
       </c>
     </row>
     <row r="122">
@@ -2918,7 +2855,7 @@
         <v>138</v>
       </c>
       <c r="D122" t="n">
-        <v>2.09</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="123">
@@ -2932,7 +2869,7 @@
         <v>139</v>
       </c>
       <c r="D123" t="n">
-        <v>2.49</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="124">
@@ -2946,7 +2883,7 @@
         <v>140</v>
       </c>
       <c r="D124" t="n">
-        <v>3.12</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="125">
@@ -2960,7 +2897,7 @@
         <v>141</v>
       </c>
       <c r="D125" t="n">
-        <v>3.5</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="126">
@@ -2974,7 +2911,7 @@
         <v>142</v>
       </c>
       <c r="D126" t="n">
-        <v>5.06</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="127">
@@ -2988,7 +2925,7 @@
         <v>143</v>
       </c>
       <c r="D127" t="n">
-        <v>5.23</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="128">
@@ -3002,7 +2939,7 @@
         <v>144</v>
       </c>
       <c r="D128" t="n">
-        <v>5.5</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="129">
@@ -3016,7 +2953,7 @@
         <v>145</v>
       </c>
       <c r="D129" t="n">
-        <v>6.04</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="130">
@@ -3030,7 +2967,7 @@
         <v>146</v>
       </c>
       <c r="D130" t="n">
-        <v>7.24</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="131">
@@ -3044,7 +2981,7 @@
         <v>147</v>
       </c>
       <c r="D131" t="n">
-        <v>8.42</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="132">
@@ -3058,7 +2995,7 @@
         <v>148</v>
       </c>
       <c r="D132" t="n">
-        <v>9.34</v>
+        <v>8.54</v>
       </c>
     </row>
     <row r="133">
@@ -3072,7 +3009,7 @@
         <v>149</v>
       </c>
       <c r="D133" t="n">
-        <v>9.48</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="134">
@@ -3086,7 +3023,7 @@
         <v>150</v>
       </c>
       <c r="D134" t="n">
-        <v>11.59</v>
+        <v>10.84</v>
       </c>
     </row>
     <row r="135">
@@ -3100,7 +3037,7 @@
         <v>151</v>
       </c>
       <c r="D135" t="n">
-        <v>14.94</v>
+        <v>14.18</v>
       </c>
     </row>
     <row r="136">
@@ -3108,13 +3045,13 @@
         <v>136</v>
       </c>
       <c r="B136" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="C136" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D136" t="n">
-        <v>20.21</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="137">
@@ -3122,13 +3059,13 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="C137" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D137" t="n">
-        <v>21.31</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138">
@@ -3136,13 +3073,13 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C138" t="s">
         <v>155</v>
       </c>
       <c r="D138" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="139">
@@ -3150,13 +3087,13 @@
         <v>136</v>
       </c>
       <c r="B139" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C139" t="s">
         <v>156</v>
       </c>
       <c r="D139" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="140">
@@ -3164,13 +3101,13 @@
         <v>136</v>
       </c>
       <c r="B140" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C140" t="s">
         <v>157</v>
       </c>
       <c r="D140" t="n">
-        <v>4.31</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="141">
@@ -3178,13 +3115,13 @@
         <v>136</v>
       </c>
       <c r="B141" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C141" t="s">
         <v>158</v>
       </c>
       <c r="D141" t="n">
-        <v>5.44</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="142">
@@ -3192,13 +3129,13 @@
         <v>136</v>
       </c>
       <c r="B142" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C142" t="s">
         <v>159</v>
       </c>
       <c r="D142" t="n">
-        <v>5.58</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="143">
@@ -3206,13 +3143,13 @@
         <v>136</v>
       </c>
       <c r="B143" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C143" t="s">
         <v>160</v>
       </c>
       <c r="D143" t="n">
-        <v>5.76</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="144">
@@ -3220,13 +3157,13 @@
         <v>136</v>
       </c>
       <c r="B144" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C144" t="s">
         <v>161</v>
       </c>
       <c r="D144" t="n">
-        <v>5.92</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="145">
@@ -3234,13 +3171,13 @@
         <v>136</v>
       </c>
       <c r="B145" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C145" t="s">
         <v>162</v>
       </c>
       <c r="D145" t="n">
-        <v>6.02</v>
+        <v>8.64</v>
       </c>
     </row>
     <row r="146">
@@ -3248,13 +3185,13 @@
         <v>136</v>
       </c>
       <c r="B146" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C146" t="s">
         <v>163</v>
       </c>
       <c r="D146" t="n">
-        <v>6.05</v>
+        <v>9.88</v>
       </c>
     </row>
     <row r="147">
@@ -3262,13 +3199,13 @@
         <v>136</v>
       </c>
       <c r="B147" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C147" t="s">
         <v>164</v>
       </c>
       <c r="D147" t="n">
-        <v>6.43</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="148">
@@ -3276,13 +3213,13 @@
         <v>136</v>
       </c>
       <c r="B148" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C148" t="s">
         <v>165</v>
       </c>
       <c r="D148" t="n">
-        <v>8.79</v>
+        <v>14.52</v>
       </c>
     </row>
     <row r="149">
@@ -3290,13 +3227,13 @@
         <v>136</v>
       </c>
       <c r="B149" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C149" t="s">
         <v>166</v>
       </c>
       <c r="D149" t="n">
-        <v>12.79</v>
+        <v>15.44</v>
       </c>
     </row>
     <row r="150">
@@ -3304,13 +3241,13 @@
         <v>136</v>
       </c>
       <c r="B150" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C150" t="s">
         <v>167</v>
       </c>
       <c r="D150" t="n">
-        <v>13.57</v>
+        <v>15.64</v>
       </c>
     </row>
     <row r="151">
@@ -3318,13 +3255,13 @@
         <v>136</v>
       </c>
       <c r="B151" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C151" t="s">
         <v>168</v>
       </c>
       <c r="D151" t="n">
-        <v>15.05</v>
+        <v>16.03</v>
       </c>
     </row>
     <row r="152">
@@ -3338,7 +3275,7 @@
         <v>171</v>
       </c>
       <c r="D152" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="153">
@@ -3352,7 +3289,7 @@
         <v>172</v>
       </c>
       <c r="D153" t="n">
-        <v>2.35</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="154">
@@ -3366,7 +3303,7 @@
         <v>173</v>
       </c>
       <c r="D154" t="n">
-        <v>2.42</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="155">
@@ -3380,7 +3317,7 @@
         <v>174</v>
       </c>
       <c r="D155" t="n">
-        <v>2.86</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="156">
@@ -3394,7 +3331,7 @@
         <v>175</v>
       </c>
       <c r="D156" t="n">
-        <v>2.97</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="157">
@@ -3408,7 +3345,7 @@
         <v>176</v>
       </c>
       <c r="D157" t="n">
-        <v>3.32</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="158">
@@ -3422,7 +3359,7 @@
         <v>177</v>
       </c>
       <c r="D158" t="n">
-        <v>4.38</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="159">
@@ -3436,7 +3373,7 @@
         <v>178</v>
       </c>
       <c r="D159" t="n">
-        <v>6.31</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="160">
@@ -3450,7 +3387,7 @@
         <v>179</v>
       </c>
       <c r="D160" t="n">
-        <v>8.31</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="161">
@@ -3464,7 +3401,7 @@
         <v>180</v>
       </c>
       <c r="D161" t="n">
-        <v>15.38</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="162">
@@ -3478,7 +3415,7 @@
         <v>181</v>
       </c>
       <c r="D162" t="n">
-        <v>17.89</v>
+        <v>11.58</v>
       </c>
     </row>
     <row r="163">
@@ -3492,7 +3429,7 @@
         <v>182</v>
       </c>
       <c r="D163" t="n">
-        <v>18.7</v>
+        <v>13.82</v>
       </c>
     </row>
     <row r="164">
@@ -3506,7 +3443,7 @@
         <v>183</v>
       </c>
       <c r="D164" t="n">
-        <v>20.51</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="165">
@@ -3514,13 +3451,13 @@
         <v>169</v>
       </c>
       <c r="B165" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="C165" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D165" t="n">
-        <v>21.13</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="166">
@@ -3528,13 +3465,13 @@
         <v>169</v>
       </c>
       <c r="B166" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="C166" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D166" t="n">
-        <v>24.19</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="167">
@@ -3542,13 +3479,13 @@
         <v>169</v>
       </c>
       <c r="B167" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C167" t="s">
         <v>187</v>
       </c>
       <c r="D167" t="n">
-        <v>2.24</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="168">
@@ -3556,13 +3493,13 @@
         <v>169</v>
       </c>
       <c r="B168" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C168" t="s">
         <v>188</v>
       </c>
       <c r="D168" t="n">
-        <v>2.47</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="169">
@@ -3570,13 +3507,13 @@
         <v>169</v>
       </c>
       <c r="B169" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C169" t="s">
         <v>189</v>
       </c>
       <c r="D169" t="n">
-        <v>3.53</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="170">
@@ -3584,13 +3521,13 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C170" t="s">
         <v>190</v>
       </c>
       <c r="D170" t="n">
-        <v>3.77</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="171">
@@ -3598,13 +3535,13 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C171" t="s">
         <v>191</v>
       </c>
       <c r="D171" t="n">
-        <v>4.08</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="172">
@@ -3612,13 +3549,13 @@
         <v>169</v>
       </c>
       <c r="B172" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C172" t="s">
         <v>192</v>
       </c>
       <c r="D172" t="n">
-        <v>4.76</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="173">
@@ -3626,13 +3563,13 @@
         <v>169</v>
       </c>
       <c r="B173" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C173" t="s">
         <v>193</v>
       </c>
       <c r="D173" t="n">
-        <v>4.78</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="174">
@@ -3640,13 +3577,13 @@
         <v>169</v>
       </c>
       <c r="B174" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C174" t="s">
         <v>194</v>
       </c>
       <c r="D174" t="n">
-        <v>5.55</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="175">
@@ -3654,13 +3591,13 @@
         <v>169</v>
       </c>
       <c r="B175" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C175" t="s">
         <v>195</v>
       </c>
       <c r="D175" t="n">
-        <v>6.26</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="176">
@@ -3668,13 +3605,13 @@
         <v>169</v>
       </c>
       <c r="B176" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C176" t="s">
         <v>196</v>
       </c>
       <c r="D176" t="n">
-        <v>7.37</v>
+        <v>9.13</v>
       </c>
     </row>
     <row r="177">
@@ -3682,13 +3619,13 @@
         <v>169</v>
       </c>
       <c r="B177" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C177" t="s">
         <v>197</v>
       </c>
       <c r="D177" t="n">
-        <v>10.12</v>
+        <v>9.64</v>
       </c>
     </row>
     <row r="178">
@@ -3696,13 +3633,13 @@
         <v>169</v>
       </c>
       <c r="B178" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C178" t="s">
         <v>198</v>
       </c>
       <c r="D178" t="n">
-        <v>12.1</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="179">
@@ -3710,13 +3647,13 @@
         <v>169</v>
       </c>
       <c r="B179" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C179" t="s">
         <v>199</v>
       </c>
       <c r="D179" t="n">
-        <v>20.66</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="180">
@@ -3724,13 +3661,13 @@
         <v>169</v>
       </c>
       <c r="B180" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C180" t="s">
         <v>200</v>
       </c>
       <c r="D180" t="n">
-        <v>23.34</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="181">
@@ -3738,13 +3675,13 @@
         <v>169</v>
       </c>
       <c r="B181" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C181" t="s">
         <v>201</v>
       </c>
       <c r="D181" t="n">
-        <v>23.99</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="182">
@@ -3758,7 +3695,7 @@
         <v>204</v>
       </c>
       <c r="D182" t="n">
-        <v>2.13</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="183">
@@ -3772,7 +3709,7 @@
         <v>205</v>
       </c>
       <c r="D183" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="184">
@@ -3786,7 +3723,7 @@
         <v>206</v>
       </c>
       <c r="D184" t="n">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="185">
@@ -3800,7 +3737,7 @@
         <v>207</v>
       </c>
       <c r="D185" t="n">
-        <v>3.03</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="186">
@@ -3814,7 +3751,7 @@
         <v>208</v>
       </c>
       <c r="D186" t="n">
-        <v>3.07</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="187">
@@ -3828,7 +3765,7 @@
         <v>209</v>
       </c>
       <c r="D187" t="n">
-        <v>3.41</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="188">
@@ -3842,7 +3779,7 @@
         <v>210</v>
       </c>
       <c r="D188" t="n">
-        <v>6.12</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="189">
@@ -3856,7 +3793,7 @@
         <v>211</v>
       </c>
       <c r="D189" t="n">
-        <v>6.64</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="190">
@@ -3870,7 +3807,7 @@
         <v>212</v>
       </c>
       <c r="D190" t="n">
-        <v>7.21</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="191">
@@ -3884,7 +3821,7 @@
         <v>213</v>
       </c>
       <c r="D191" t="n">
-        <v>8.31</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="192">
@@ -3898,7 +3835,7 @@
         <v>214</v>
       </c>
       <c r="D192" t="n">
-        <v>8.75</v>
+        <v>7.96</v>
       </c>
     </row>
     <row r="193">
@@ -3912,7 +3849,7 @@
         <v>215</v>
       </c>
       <c r="D193" t="n">
-        <v>9.19</v>
+        <v>8.63</v>
       </c>
     </row>
     <row r="194">
@@ -3926,7 +3863,7 @@
         <v>216</v>
       </c>
       <c r="D194" t="n">
-        <v>14.24</v>
+        <v>9.96</v>
       </c>
     </row>
     <row r="195">
@@ -3934,13 +3871,13 @@
         <v>202</v>
       </c>
       <c r="B195" t="s">
+        <v>203</v>
+      </c>
+      <c r="C195" t="s">
         <v>217</v>
       </c>
-      <c r="C195" t="s">
-        <v>218</v>
-      </c>
       <c r="D195" t="n">
-        <v>1.86</v>
+        <v>11.41</v>
       </c>
     </row>
     <row r="196">
@@ -3948,13 +3885,13 @@
         <v>202</v>
       </c>
       <c r="B196" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="C196" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D196" t="n">
-        <v>2.02</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="197">
@@ -3962,13 +3899,13 @@
         <v>202</v>
       </c>
       <c r="B197" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="C197" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D197" t="n">
-        <v>2.21</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="198">
@@ -3976,13 +3913,13 @@
         <v>202</v>
       </c>
       <c r="B198" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C198" t="s">
         <v>221</v>
       </c>
       <c r="D198" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="199">
@@ -3990,13 +3927,13 @@
         <v>202</v>
       </c>
       <c r="B199" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C199" t="s">
         <v>222</v>
       </c>
       <c r="D199" t="n">
-        <v>3.43</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="200">
@@ -4004,13 +3941,13 @@
         <v>202</v>
       </c>
       <c r="B200" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C200" t="s">
         <v>223</v>
       </c>
       <c r="D200" t="n">
-        <v>4.76</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="201">
@@ -4018,13 +3955,13 @@
         <v>202</v>
       </c>
       <c r="B201" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C201" t="s">
         <v>224</v>
       </c>
       <c r="D201" t="n">
-        <v>5.26</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="202">
@@ -4032,13 +3969,13 @@
         <v>202</v>
       </c>
       <c r="B202" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C202" t="s">
         <v>225</v>
       </c>
       <c r="D202" t="n">
-        <v>5.33</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="203">
@@ -4046,13 +3983,13 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C203" t="s">
         <v>226</v>
       </c>
       <c r="D203" t="n">
-        <v>6.12</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="204">
@@ -4060,13 +3997,13 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C204" t="s">
         <v>227</v>
       </c>
       <c r="D204" t="n">
-        <v>6.43</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="205">
@@ -4074,13 +4011,13 @@
         <v>202</v>
       </c>
       <c r="B205" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C205" t="s">
         <v>228</v>
       </c>
       <c r="D205" t="n">
-        <v>8.92</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="206">
@@ -4088,13 +4025,13 @@
         <v>202</v>
       </c>
       <c r="B206" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C206" t="s">
         <v>229</v>
       </c>
       <c r="D206" t="n">
-        <v>9.16</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="207">
@@ -4102,13 +4039,13 @@
         <v>202</v>
       </c>
       <c r="B207" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C207" t="s">
         <v>230</v>
       </c>
       <c r="D207" t="n">
-        <v>13.3</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="208">
@@ -4116,13 +4053,13 @@
         <v>202</v>
       </c>
       <c r="B208" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C208" t="s">
         <v>231</v>
       </c>
       <c r="D208" t="n">
-        <v>13.87</v>
+        <v>9.86</v>
       </c>
     </row>
     <row r="209">
@@ -4130,13 +4067,13 @@
         <v>202</v>
       </c>
       <c r="B209" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C209" t="s">
         <v>232</v>
       </c>
       <c r="D209" t="n">
-        <v>14.12</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="210">
@@ -4144,13 +4081,13 @@
         <v>202</v>
       </c>
       <c r="B210" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C210" t="s">
         <v>233</v>
       </c>
       <c r="D210" t="n">
-        <v>14.43</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="211">
@@ -4158,13 +4095,13 @@
         <v>202</v>
       </c>
       <c r="B211" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C211" t="s">
         <v>234</v>
       </c>
       <c r="D211" t="n">
-        <v>15.13</v>
+        <v>17.46</v>
       </c>
     </row>
     <row r="212">
@@ -4178,7 +4115,7 @@
         <v>237</v>
       </c>
       <c r="D212" t="n">
-        <v>2.53</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="213">
@@ -4192,7 +4129,7 @@
         <v>238</v>
       </c>
       <c r="D213" t="n">
-        <v>3.05</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="214">
@@ -4206,7 +4143,7 @@
         <v>239</v>
       </c>
       <c r="D214" t="n">
-        <v>3.06</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="215">
@@ -4220,7 +4157,7 @@
         <v>240</v>
       </c>
       <c r="D215" t="n">
-        <v>3.25</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="216">
@@ -4234,7 +4171,7 @@
         <v>241</v>
       </c>
       <c r="D216" t="n">
-        <v>3.54</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="217">
@@ -4248,7 +4185,7 @@
         <v>242</v>
       </c>
       <c r="D217" t="n">
-        <v>3.57</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="218">
@@ -4262,7 +4199,7 @@
         <v>243</v>
       </c>
       <c r="D218" t="n">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="219">
@@ -4276,7 +4213,7 @@
         <v>244</v>
       </c>
       <c r="D219" t="n">
-        <v>3.85</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="220">
@@ -4290,7 +4227,7 @@
         <v>245</v>
       </c>
       <c r="D220" t="n">
-        <v>3.93</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="221">
@@ -4304,7 +4241,7 @@
         <v>246</v>
       </c>
       <c r="D221" t="n">
-        <v>5.91</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="222">
@@ -4318,7 +4255,7 @@
         <v>247</v>
       </c>
       <c r="D222" t="n">
-        <v>8.29</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="223">
@@ -4332,7 +4269,7 @@
         <v>248</v>
       </c>
       <c r="D223" t="n">
-        <v>15.33</v>
+        <v>8.64</v>
       </c>
     </row>
     <row r="224">
@@ -4346,7 +4283,7 @@
         <v>249</v>
       </c>
       <c r="D224" t="n">
-        <v>16.04</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="225">
@@ -4360,7 +4297,7 @@
         <v>250</v>
       </c>
       <c r="D225" t="n">
-        <v>16.98</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="226">
@@ -4374,7 +4311,7 @@
         <v>251</v>
       </c>
       <c r="D226" t="n">
-        <v>18.63</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="227">
@@ -4388,7 +4325,7 @@
         <v>252</v>
       </c>
       <c r="D227" t="n">
-        <v>21.17</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="228">
@@ -4396,13 +4333,13 @@
         <v>235</v>
       </c>
       <c r="B228" t="s">
+        <v>236</v>
+      </c>
+      <c r="C228" t="s">
         <v>253</v>
       </c>
-      <c r="C228" t="s">
-        <v>254</v>
-      </c>
       <c r="D228" t="n">
-        <v>2.14</v>
+        <v>17.67</v>
       </c>
     </row>
     <row r="229">
@@ -4410,13 +4347,13 @@
         <v>235</v>
       </c>
       <c r="B229" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C229" t="s">
         <v>255</v>
       </c>
       <c r="D229" t="n">
-        <v>2.5</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="230">
@@ -4424,13 +4361,13 @@
         <v>235</v>
       </c>
       <c r="B230" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C230" t="s">
         <v>256</v>
       </c>
       <c r="D230" t="n">
-        <v>3.11</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="231">
@@ -4438,13 +4375,13 @@
         <v>235</v>
       </c>
       <c r="B231" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C231" t="s">
         <v>257</v>
       </c>
       <c r="D231" t="n">
-        <v>3.63</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="232">
@@ -4452,13 +4389,13 @@
         <v>235</v>
       </c>
       <c r="B232" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C232" t="s">
         <v>258</v>
       </c>
       <c r="D232" t="n">
-        <v>3.64</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="233">
@@ -4466,13 +4403,13 @@
         <v>235</v>
       </c>
       <c r="B233" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C233" t="s">
         <v>259</v>
       </c>
       <c r="D233" t="n">
-        <v>4.33</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="234">
@@ -4480,13 +4417,13 @@
         <v>235</v>
       </c>
       <c r="B234" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C234" t="s">
         <v>260</v>
       </c>
       <c r="D234" t="n">
-        <v>5.36</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="235">
@@ -4494,13 +4431,13 @@
         <v>235</v>
       </c>
       <c r="B235" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C235" t="s">
         <v>261</v>
       </c>
       <c r="D235" t="n">
-        <v>6.31</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="236">
@@ -4508,13 +4445,13 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C236" t="s">
         <v>262</v>
       </c>
       <c r="D236" t="n">
-        <v>6.48</v>
+        <v>8.45</v>
       </c>
     </row>
     <row r="237">
@@ -4522,13 +4459,13 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C237" t="s">
         <v>263</v>
       </c>
       <c r="D237" t="n">
-        <v>7.68</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="238">
@@ -4536,13 +4473,13 @@
         <v>235</v>
       </c>
       <c r="B238" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C238" t="s">
         <v>264</v>
       </c>
       <c r="D238" t="n">
-        <v>9.73</v>
+        <v>9.71</v>
       </c>
     </row>
     <row r="239">
@@ -4550,13 +4487,13 @@
         <v>235</v>
       </c>
       <c r="B239" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C239" t="s">
         <v>265</v>
       </c>
       <c r="D239" t="n">
-        <v>10.6</v>
+        <v>10.59</v>
       </c>
     </row>
     <row r="240">
@@ -4564,13 +4501,13 @@
         <v>235</v>
       </c>
       <c r="B240" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C240" t="s">
         <v>266</v>
       </c>
       <c r="D240" t="n">
-        <v>10.74</v>
+        <v>15.86</v>
       </c>
     </row>
     <row r="241">
@@ -4578,279 +4515,13 @@
         <v>235</v>
       </c>
       <c r="B241" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C241" t="s">
         <v>267</v>
       </c>
       <c r="D241" t="n">
-        <v>17.1</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="s">
-        <v>268</v>
-      </c>
-      <c r="B242" t="s">
-        <v>269</v>
-      </c>
-      <c r="C242" t="s">
-        <v>270</v>
-      </c>
-      <c r="D242" t="n">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="s">
-        <v>268</v>
-      </c>
-      <c r="B243" t="s">
-        <v>269</v>
-      </c>
-      <c r="C243" t="s">
-        <v>271</v>
-      </c>
-      <c r="D243" t="n">
-        <v>3.37</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="s">
-        <v>268</v>
-      </c>
-      <c r="B244" t="s">
-        <v>269</v>
-      </c>
-      <c r="C244" t="s">
-        <v>272</v>
-      </c>
-      <c r="D244" t="n">
-        <v>3.47</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="s">
-        <v>268</v>
-      </c>
-      <c r="B245" t="s">
-        <v>269</v>
-      </c>
-      <c r="C245" t="s">
-        <v>273</v>
-      </c>
-      <c r="D245" t="n">
-        <v>3.71</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="s">
-        <v>268</v>
-      </c>
-      <c r="B246" t="s">
-        <v>269</v>
-      </c>
-      <c r="C246" t="s">
-        <v>274</v>
-      </c>
-      <c r="D246" t="n">
-        <v>3.73</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="s">
-        <v>268</v>
-      </c>
-      <c r="B247" t="s">
-        <v>269</v>
-      </c>
-      <c r="C247" t="s">
-        <v>275</v>
-      </c>
-      <c r="D247" t="n">
-        <v>7.45</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="s">
-        <v>268</v>
-      </c>
-      <c r="B248" t="s">
-        <v>269</v>
-      </c>
-      <c r="C248" t="s">
-        <v>276</v>
-      </c>
-      <c r="D248" t="n">
-        <v>7.88</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="s">
-        <v>268</v>
-      </c>
-      <c r="B249" t="s">
-        <v>269</v>
-      </c>
-      <c r="C249" t="s">
-        <v>277</v>
-      </c>
-      <c r="D249" t="n">
-        <v>8.18</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="s">
-        <v>268</v>
-      </c>
-      <c r="B250" t="s">
-        <v>269</v>
-      </c>
-      <c r="C250" t="s">
-        <v>278</v>
-      </c>
-      <c r="D250" t="n">
-        <v>8.73</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="s">
-        <v>268</v>
-      </c>
-      <c r="B251" t="s">
-        <v>269</v>
-      </c>
-      <c r="C251" t="s">
-        <v>279</v>
-      </c>
-      <c r="D251" t="n">
-        <v>9.51</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="s">
-        <v>268</v>
-      </c>
-      <c r="B252" t="s">
-        <v>269</v>
-      </c>
-      <c r="C252" t="s">
-        <v>280</v>
-      </c>
-      <c r="D252" t="n">
-        <v>9.8</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="s">
-        <v>268</v>
-      </c>
-      <c r="B253" t="s">
-        <v>269</v>
-      </c>
-      <c r="C253" t="s">
-        <v>281</v>
-      </c>
-      <c r="D253" t="n">
-        <v>14.26</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="s">
-        <v>268</v>
-      </c>
-      <c r="B254" t="s">
-        <v>269</v>
-      </c>
-      <c r="C254" t="s">
-        <v>282</v>
-      </c>
-      <c r="D254" t="n">
-        <v>30.79</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="s">
-        <v>268</v>
-      </c>
-      <c r="B255" t="s">
-        <v>269</v>
-      </c>
-      <c r="C255" t="s">
-        <v>283</v>
-      </c>
-      <c r="D255" t="n">
-        <v>30.79</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="s">
-        <v>268</v>
-      </c>
-      <c r="B256" t="s">
-        <v>269</v>
-      </c>
-      <c r="C256" t="s">
-        <v>284</v>
-      </c>
-      <c r="D256" t="n">
-        <v>38.22</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="s">
-        <v>268</v>
-      </c>
-      <c r="B257" t="s">
-        <v>269</v>
-      </c>
-      <c r="C257" t="s">
-        <v>285</v>
-      </c>
-      <c r="D257" t="n">
-        <v>40.85</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="s">
-        <v>268</v>
-      </c>
-      <c r="B258" t="s">
-        <v>269</v>
-      </c>
-      <c r="C258" t="s">
-        <v>286</v>
-      </c>
-      <c r="D258" t="n">
-        <v>51.11</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="s">
-        <v>268</v>
-      </c>
-      <c r="B259" t="s">
-        <v>269</v>
-      </c>
-      <c r="C259" t="s">
-        <v>287</v>
-      </c>
-      <c r="D259" t="n">
-        <v>51.99</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="s">
-        <v>268</v>
-      </c>
-      <c r="B260" t="s">
-        <v>269</v>
-      </c>
-      <c r="C260" t="s">
-        <v>288</v>
-      </c>
-      <c r="D260" t="n">
-        <v>59.91</v>
+        <v>18.41</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_anytime_tryscorers.xlsx
+++ b/files/NRL_anytime_tryscorers.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="277">
   <si>
     <t xml:space="preserve">Game</t>
   </si>
@@ -26,7 +26,700 @@
     <t xml:space="preserve">Price</t>
   </si>
   <si>
-    <t xml:space="preserve">north queensland cowboys at gold coast titans</t>
+    <t xml:space="preserve">newcastle knights at canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Savage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jed Stuart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaeo Weekes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sebastian Kris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Timoko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Strange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owen Pattie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ata Mariota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zac Hosking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Sanders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe Roddy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daine Laurie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matty Nicholson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corey Horsburgh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Starling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joseph Tapine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominic Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greg Marzhew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fletcher Sharpe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bradman Best</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kalyn Ponga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dane Gagai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francis Manuleleua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trey Mooney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandon Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jermaine McEwen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phoenix Crossland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fletcher Hunt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyson Frizell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brodie Jones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks at st george-illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronaldo Mulitalo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sione Katoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">William Kennedy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayal Iro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braydon Trindall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Briton Nikora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesse Ramien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teig Wilton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicholas Hynes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siosifa Talakai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Hazelton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blayke Brailey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesse Colquhoun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Addin Fonua-Blake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron McInnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oregon Kaufusi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samuel Stonestreet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george-illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyrell Sloan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setu Tu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinton Gutherson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valentine Holmes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Liddle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyle Flanagan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Egan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mosese Suli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lyhkan King-Togia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damien Cook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamish Stewart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luciano Leilua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan Couchman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters at penrith panthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penrith panthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Jenkins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian To'o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaxen Edgar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casey McLean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paul Alamoti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathan Cleary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiah Papali'i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freddy Lussick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lindsay Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Izack Tago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Henry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaah Yeo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Cogger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark Nawaqanitawase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tommy Talau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Tedesco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugo Savala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robert Toia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daly Cherry-Evans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nat Butcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siua Wong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reece Robson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Victor Radley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salesi Foketi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Watson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spencer Leniu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egan Butcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cody Ramsey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolphins at manly-warringah sea eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamiso Tabuai-Fidow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selwyn Cobbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamayne Isaako</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herbie Farnworth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Bostock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kodi Nikorima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connelly Lemuelu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremy Marshall-King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kulikefu Finefeuiaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ray Stone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Flegler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiya Katoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Plath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Donoghoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Felise Kaufusi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morgan Knowles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Gilbert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francis Molo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manly-warringah sea eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jason Saab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lehi Hopoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tolutau Koula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reuben Garrick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haumole Olakau'atu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joey Walsh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Feledy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Trbojevic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamal Fogarty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicholas Lenaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Bullemor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simione Laiafi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs at canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jethro Rinakama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Kiraz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matt Burton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stephen Crichton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Preston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Tracey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enari Tuala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viliame Kikau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lachlan Galvin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Mann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaeman Salmon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jonathan Sua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Curran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bailey Hayward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Johnston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campbell Graham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cody Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Wighton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latrell Siegwalt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Dufty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keaon Koloamatangi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Elliott</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashton Ward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brandon Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Sullivan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tevita Tatola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jye Gray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John Radel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamie Humphreys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Fletcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys at parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braidon Burns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murray Taulagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremiah Nanai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scott Drinkwater</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Chester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zac Laybutt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heilum Luki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Clifford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaxon Purdue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soni Luke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reuben Cotter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam McIntyre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Mikaele</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Addo-Carr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian Kelly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiah Iongi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Penisini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Samrani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitchell Moses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tallyn Da Silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronald Volkman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kitione Kautoga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kelma Tuilagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack De Belin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Paulo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joash Papalii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Tuivaiti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teancum Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors at brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grant Anderson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josiah Karapani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reece Walsh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezra Mam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kotoni Staggs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Willison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deine Mariner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Reynolds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Riki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Walters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Talty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cory Paix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gehamat Shibasaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payne Haas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Va'a Semu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alofiana Khan-Pereira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dallin Watene-Zelezniak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leka Halasima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charnze Nicoll-Klokstad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ali Leiataua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Te Maire Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Laban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chanel Harris-Tavita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Capewell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wayde Egan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Fisher-Harris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Healey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erin Clark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eddie Ieremia-Toeava</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Metcalf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans at newcastle knights</t>
   </si>
   <si>
     <t xml:space="preserve">gold coast titans</t>
@@ -44,27 +737,27 @@
     <t xml:space="preserve">Jayden Campbell</t>
   </si>
   <si>
+    <t xml:space="preserve">Arama Hau</t>
+  </si>
+  <si>
     <t xml:space="preserve">Keano Kini</t>
   </si>
   <si>
+    <t xml:space="preserve">Beau Fermor</t>
+  </si>
+  <si>
     <t xml:space="preserve">AJ Brimson</t>
   </si>
   <si>
-    <t xml:space="preserve">Arama Hau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beau Fermor</t>
-  </si>
-  <si>
     <t xml:space="preserve">Oliver Pascoe</t>
   </si>
   <si>
-    <t xml:space="preserve">Lachlan Ilias</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tino Fa'asuamaleaui</t>
   </si>
   <si>
+    <t xml:space="preserve">Zane Harrison</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kurtis Morrin</t>
   </si>
   <si>
@@ -80,742 +773,76 @@
     <t xml:space="preserve">Sam Verrills</t>
   </si>
   <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Braidon Burns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Murray Taulagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scott Drinkwater</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Chester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zac Laybutt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heilum Luki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kai O'Donnell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Clifford</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaxon Purdue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soni Luke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reuben Cotter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam McIntyre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Griffin Neame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Sutton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs at sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jethro Rinakama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Kiraz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matt Burton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stephen Crichton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Tracey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enari Tuala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viliame Kikau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Preston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lachlan Galvin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sitili Tupouniua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurt Mann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaeman Salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jonathan Sua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Curran</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mark Nawaqanitawase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Tedesco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hugo Savala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robert Toia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salesi Foketi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siua Wong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daly Cherry-Evans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reece Robson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Victor Radley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nat Butcher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Watson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Egan Butcher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lindsay Collins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cody Ramsey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penrith panthers at warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penrith panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Jenkins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian To'o</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaxen Edgar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Izack Tago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiah Papali'i</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paul Alamoti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nathan Cleary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freddy Lussick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lindsay Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Henry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaah Yeo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Cogger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moses Leota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scott Sorensen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alofiana Khan-Pereira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dallin Watene-Zelezniak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leka Halasima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charnze Nicoll-Klokstad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ali Leiataua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurt Capewell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Laban</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Te Maire Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chanel Harris-Tavita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wayde Egan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Fisher-Harris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Healey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erin Clark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eddie Ieremia-Toeava</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Metcalf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manly-warringah sea eagles at melbourne storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manly-warringah sea eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jason Saab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lehi Hopoate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blake Wilson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tolutau Koula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reuben Garrick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joey Walsh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haumole Olakau'atu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corey Waddell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamal Fogarty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brandon Wakeham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Trbojevic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Onitoni Large</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taniela Paseka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moses Leo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sualauvi Faalogo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siulagi Tuimalatu-Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyran Wishart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Clarke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oryn Keeley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nick Meaney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameron Munster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Howarth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hayden Watson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angus Hinchey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stefano Utoikamanu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joe Chan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shawn Blore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trent Toelau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trent Loiero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos at dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grant Anderson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josiah Karapani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reece Walsh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ezra Mam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kotoni Staggs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaiyden Hunt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan Riki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deine Mariner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Walters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Duffy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben Talty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Willison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gehamat Shibasaki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payne Haas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamiso Tabuai-Fidow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selwyn Cobbo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamayne Isaako</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herbie Farnworth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Bostock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connelly Lemuelu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kulikefu Finefeuiaki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kodi Nikorima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremy Marshall-King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Flegler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiya Katoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Plath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurt Donoghoe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Felise Kaufusi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morgan Knowles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Gilbert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels at south sydney rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Addo-Carr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian Kelly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiah Iongi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Will Penisini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan Samrani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitchell Moses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitione Kautoga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tallyn Da Silva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronald Volkman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack De Belin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luca Moretti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Paulo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">south sydney rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Johnston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campbell Graham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tallis Duncan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cody Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Wighton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Dufty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">David Fifita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Elliott</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashton Ward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameron Murray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keaon Koloamatangi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brandon Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Sullivan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">John Radel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tevita Tatola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jye Gray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamie Humphreys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights at canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Savage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jed Stuart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaeo Weekes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simi Sasagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Timoko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan Strange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zac Hosking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ata Mariota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owen Pattie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan Sanders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joe Roddy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daine Laurie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matty Nicholson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corey Horsburgh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Starling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joseph Tapine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dominic Young</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greg Marzhew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fletcher Sharpe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bradman Best</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kalyn Ponga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jermaine McEwen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Francis Manuleleua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dane Gagai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trey Mooney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandon Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phoenix Crossland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harrison Graham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fletcher Hunt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brodie Jones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks at st george-illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronaldo Mulitalo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sione Katoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">William Kennedy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mawene Hiroti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Braydon Trindall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jesse Ramien</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Briton Nikora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teig Wilton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicholas Hynes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Addin Fonua-Blake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Hazelton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blayke Brailey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jesse Colquhoun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameron McInnes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tuku Hau Tapuha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Braden Hamlin-Uele</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niwhai Puru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george-illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyrell Sloan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Setu Tu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clinton Gutherson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valentine Holmes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Egan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamish Stewart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Liddle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyle Flanagan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mosese Suli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lyhkan King-Togia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Damien Cook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luciano Leilua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan Couchman</t>
+    <t xml:space="preserve">Moeaki Fotuaika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaylan De Groot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Patston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george-illawarra dragons at wests tigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wests tigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunia Turuva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jahream Bula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Doueihi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Tupou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heamasi Makasini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samuela Fainu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sione Fainu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jarome Luai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apisai Koroisau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick Herbert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Seyfarth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terrell May</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fonua Pole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starford To'a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Twal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charlie Murray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tristan Hope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heath Mason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tony Sukkar</t>
   </si>
 </sst>
 </file>
@@ -1175,7 +1202,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>1.94</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="3">
@@ -1189,7 +1216,7 @@
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>2.81</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="4">
@@ -1203,7 +1230,7 @@
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="5">
@@ -1217,7 +1244,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>3.08</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="6">
@@ -1231,7 +1258,7 @@
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="7">
@@ -1245,7 +1272,7 @@
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>3.54</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="8">
@@ -1259,7 +1286,7 @@
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>3.69</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="9">
@@ -1273,7 +1300,7 @@
         <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>3.69</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="10">
@@ -1287,7 +1314,7 @@
         <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>4.14</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="11">
@@ -1301,7 +1328,7 @@
         <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>6.41</v>
+        <v>6.22</v>
       </c>
     </row>
     <row r="12">
@@ -1315,7 +1342,7 @@
         <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>6.79</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="13">
@@ -1329,7 +1356,7 @@
         <v>17</v>
       </c>
       <c r="D13" t="n">
-        <v>8.76</v>
+        <v>8.04</v>
       </c>
     </row>
     <row r="14">
@@ -1343,7 +1370,7 @@
         <v>18</v>
       </c>
       <c r="D14" t="n">
-        <v>8.78</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="15">
@@ -1357,7 +1384,7 @@
         <v>19</v>
       </c>
       <c r="D15" t="n">
-        <v>8.81</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="16">
@@ -1371,7 +1398,7 @@
         <v>20</v>
       </c>
       <c r="D16" t="n">
-        <v>18.09</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="17">
@@ -1385,7 +1412,7 @@
         <v>21</v>
       </c>
       <c r="D17" t="n">
-        <v>18.93</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="18">
@@ -1399,7 +1426,7 @@
         <v>23</v>
       </c>
       <c r="D18" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="19">
@@ -1413,7 +1440,7 @@
         <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>2.03</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="20">
@@ -1427,7 +1454,7 @@
         <v>25</v>
       </c>
       <c r="D20" t="n">
-        <v>2.56</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="21">
@@ -1441,7 +1468,7 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="22">
@@ -1455,7 +1482,7 @@
         <v>27</v>
       </c>
       <c r="D22" t="n">
-        <v>3.44</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="23">
@@ -1469,7 +1496,7 @@
         <v>28</v>
       </c>
       <c r="D23" t="n">
-        <v>3.89</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="24">
@@ -1483,7 +1510,7 @@
         <v>29</v>
       </c>
       <c r="D24" t="n">
-        <v>3.89</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="25">
@@ -1497,7 +1524,7 @@
         <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="26">
@@ -1511,7 +1538,7 @@
         <v>31</v>
       </c>
       <c r="D26" t="n">
-        <v>6.91</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="27">
@@ -1525,7 +1552,7 @@
         <v>32</v>
       </c>
       <c r="D27" t="n">
-        <v>8.31</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="28">
@@ -1539,7 +1566,7 @@
         <v>33</v>
       </c>
       <c r="D28" t="n">
-        <v>8.49</v>
+        <v>9.23</v>
       </c>
     </row>
     <row r="29">
@@ -1553,7 +1580,7 @@
         <v>34</v>
       </c>
       <c r="D29" t="n">
-        <v>12.7</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="30">
@@ -1567,7 +1594,7 @@
         <v>35</v>
       </c>
       <c r="D30" t="n">
-        <v>16.14</v>
+        <v>14.89</v>
       </c>
     </row>
     <row r="31">
@@ -1581,7 +1608,7 @@
         <v>36</v>
       </c>
       <c r="D31" t="n">
-        <v>19.49</v>
+        <v>16.32</v>
       </c>
     </row>
     <row r="32">
@@ -1595,7 +1622,7 @@
         <v>39</v>
       </c>
       <c r="D32" t="n">
-        <v>2.74</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="33">
@@ -1609,7 +1636,7 @@
         <v>40</v>
       </c>
       <c r="D33" t="n">
-        <v>3.25</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="34">
@@ -1623,7 +1650,7 @@
         <v>41</v>
       </c>
       <c r="D34" t="n">
-        <v>3.82</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="35">
@@ -1637,7 +1664,7 @@
         <v>42</v>
       </c>
       <c r="D35" t="n">
-        <v>4.35</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="36">
@@ -1651,7 +1678,7 @@
         <v>43</v>
       </c>
       <c r="D36" t="n">
-        <v>5.12</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="37">
@@ -1665,7 +1692,7 @@
         <v>44</v>
       </c>
       <c r="D37" t="n">
-        <v>5.4</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="38">
@@ -1679,7 +1706,7 @@
         <v>45</v>
       </c>
       <c r="D38" t="n">
-        <v>5.48</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="39">
@@ -1693,7 +1720,7 @@
         <v>46</v>
       </c>
       <c r="D39" t="n">
-        <v>5.48</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="40">
@@ -1707,7 +1734,7 @@
         <v>47</v>
       </c>
       <c r="D40" t="n">
-        <v>6.69</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="41">
@@ -1721,7 +1748,7 @@
         <v>48</v>
       </c>
       <c r="D41" t="n">
-        <v>7.19</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="42">
@@ -1735,7 +1762,7 @@
         <v>49</v>
       </c>
       <c r="D42" t="n">
-        <v>14.38</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="43">
@@ -1749,7 +1776,7 @@
         <v>50</v>
       </c>
       <c r="D43" t="n">
-        <v>14.55</v>
+        <v>8.7</v>
       </c>
     </row>
     <row r="44">
@@ -1763,7 +1790,7 @@
         <v>51</v>
       </c>
       <c r="D44" t="n">
-        <v>14.56</v>
+        <v>9.16</v>
       </c>
     </row>
     <row r="45">
@@ -1777,7 +1804,7 @@
         <v>52</v>
       </c>
       <c r="D45" t="n">
-        <v>15.22</v>
+        <v>9.19</v>
       </c>
     </row>
     <row r="46">
@@ -1785,13 +1812,13 @@
         <v>37</v>
       </c>
       <c r="B46" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" t="s">
         <v>53</v>
       </c>
-      <c r="C46" t="s">
-        <v>54</v>
-      </c>
       <c r="D46" t="n">
-        <v>1.71</v>
+        <v>10.72</v>
       </c>
     </row>
     <row r="47">
@@ -1799,13 +1826,13 @@
         <v>37</v>
       </c>
       <c r="B47" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C47" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>2.49</v>
+        <v>12.83</v>
       </c>
     </row>
     <row r="48">
@@ -1813,13 +1840,13 @@
         <v>37</v>
       </c>
       <c r="B48" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C48" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D48" t="n">
-        <v>2.51</v>
+        <v>20.27</v>
       </c>
     </row>
     <row r="49">
@@ -1827,13 +1854,13 @@
         <v>37</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C49" t="s">
         <v>57</v>
       </c>
       <c r="D49" t="n">
-        <v>2.63</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="50">
@@ -1841,13 +1868,13 @@
         <v>37</v>
       </c>
       <c r="B50" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C50" t="s">
         <v>58</v>
       </c>
       <c r="D50" t="n">
-        <v>3.14</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="51">
@@ -1855,13 +1882,13 @@
         <v>37</v>
       </c>
       <c r="B51" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C51" t="s">
         <v>59</v>
       </c>
       <c r="D51" t="n">
-        <v>4.12</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="52">
@@ -1869,13 +1896,13 @@
         <v>37</v>
       </c>
       <c r="B52" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C52" t="s">
         <v>60</v>
       </c>
       <c r="D52" t="n">
-        <v>4.41</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="53">
@@ -1883,13 +1910,13 @@
         <v>37</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C53" t="s">
         <v>61</v>
       </c>
       <c r="D53" t="n">
-        <v>4.41</v>
+        <v>7.38</v>
       </c>
     </row>
     <row r="54">
@@ -1897,13 +1924,13 @@
         <v>37</v>
       </c>
       <c r="B54" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C54" t="s">
         <v>62</v>
       </c>
       <c r="D54" t="n">
-        <v>4.5</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="55">
@@ -1911,13 +1938,13 @@
         <v>37</v>
       </c>
       <c r="B55" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C55" t="s">
         <v>63</v>
       </c>
       <c r="D55" t="n">
-        <v>7.93</v>
+        <v>7.82</v>
       </c>
     </row>
     <row r="56">
@@ -1925,13 +1952,13 @@
         <v>37</v>
       </c>
       <c r="B56" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C56" t="s">
         <v>64</v>
       </c>
       <c r="D56" t="n">
-        <v>8.13</v>
+        <v>7.97</v>
       </c>
     </row>
     <row r="57">
@@ -1939,13 +1966,13 @@
         <v>37</v>
       </c>
       <c r="B57" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C57" t="s">
         <v>65</v>
       </c>
       <c r="D57" t="n">
-        <v>10.36</v>
+        <v>8.95</v>
       </c>
     </row>
     <row r="58">
@@ -1953,13 +1980,13 @@
         <v>37</v>
       </c>
       <c r="B58" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C58" t="s">
         <v>66</v>
       </c>
       <c r="D58" t="n">
-        <v>10.39</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="59">
@@ -1967,13 +1994,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C59" t="s">
         <v>67</v>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="60">
@@ -1981,13 +2008,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C60" t="s">
         <v>68</v>
       </c>
       <c r="D60" t="n">
-        <v>14.1</v>
+        <v>14.58</v>
       </c>
     </row>
     <row r="61">
@@ -1995,13 +2022,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C61" t="s">
         <v>69</v>
       </c>
       <c r="D61" t="n">
-        <v>15.4</v>
+        <v>16.91</v>
       </c>
     </row>
     <row r="62">
@@ -2015,7 +2042,7 @@
         <v>72</v>
       </c>
       <c r="D62" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="63">
@@ -2029,7 +2056,7 @@
         <v>73</v>
       </c>
       <c r="D63" t="n">
-        <v>2.52</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="64">
@@ -2043,7 +2070,7 @@
         <v>74</v>
       </c>
       <c r="D64" t="n">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="65">
@@ -2057,7 +2084,7 @@
         <v>75</v>
       </c>
       <c r="D65" t="n">
-        <v>3.74</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="66">
@@ -2071,7 +2098,7 @@
         <v>76</v>
       </c>
       <c r="D66" t="n">
-        <v>5.18</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="67">
@@ -2085,7 +2112,7 @@
         <v>77</v>
       </c>
       <c r="D67" t="n">
-        <v>5.18</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="68">
@@ -2099,7 +2126,7 @@
         <v>78</v>
       </c>
       <c r="D68" t="n">
-        <v>5.19</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="69">
@@ -2113,7 +2140,7 @@
         <v>79</v>
       </c>
       <c r="D69" t="n">
-        <v>5.31</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="70">
@@ -2127,7 +2154,7 @@
         <v>80</v>
       </c>
       <c r="D70" t="n">
-        <v>8.79</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="71">
@@ -2141,7 +2168,7 @@
         <v>81</v>
       </c>
       <c r="D71" t="n">
-        <v>9.61</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="72">
@@ -2155,7 +2182,7 @@
         <v>82</v>
       </c>
       <c r="D72" t="n">
-        <v>11.51</v>
+        <v>9.13</v>
       </c>
     </row>
     <row r="73">
@@ -2169,7 +2196,7 @@
         <v>83</v>
       </c>
       <c r="D73" t="n">
-        <v>11.75</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="74">
@@ -2183,7 +2210,7 @@
         <v>84</v>
       </c>
       <c r="D74" t="n">
-        <v>13.33</v>
+        <v>10.55</v>
       </c>
     </row>
     <row r="75">
@@ -2197,7 +2224,7 @@
         <v>85</v>
       </c>
       <c r="D75" t="n">
-        <v>20.49</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="76">
@@ -2205,13 +2232,13 @@
         <v>70</v>
       </c>
       <c r="B76" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="C76" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D76" t="n">
-        <v>21.95</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="77">
@@ -2219,13 +2246,13 @@
         <v>70</v>
       </c>
       <c r="B77" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C77" t="s">
         <v>88</v>
       </c>
       <c r="D77" t="n">
-        <v>1.93</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="78">
@@ -2233,13 +2260,13 @@
         <v>70</v>
       </c>
       <c r="B78" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C78" t="s">
         <v>89</v>
       </c>
       <c r="D78" t="n">
-        <v>2.25</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="79">
@@ -2247,13 +2274,13 @@
         <v>70</v>
       </c>
       <c r="B79" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C79" t="s">
         <v>90</v>
       </c>
       <c r="D79" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -2261,13 +2288,13 @@
         <v>70</v>
       </c>
       <c r="B80" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C80" t="s">
         <v>91</v>
       </c>
       <c r="D80" t="n">
-        <v>4.31</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="81">
@@ -2275,13 +2302,13 @@
         <v>70</v>
       </c>
       <c r="B81" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C81" t="s">
         <v>92</v>
       </c>
       <c r="D81" t="n">
-        <v>4.41</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="82">
@@ -2289,13 +2316,13 @@
         <v>70</v>
       </c>
       <c r="B82" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C82" t="s">
         <v>93</v>
       </c>
       <c r="D82" t="n">
-        <v>5.02</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="83">
@@ -2303,13 +2330,13 @@
         <v>70</v>
       </c>
       <c r="B83" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C83" t="s">
         <v>94</v>
       </c>
       <c r="D83" t="n">
-        <v>5.02</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="84">
@@ -2317,13 +2344,13 @@
         <v>70</v>
       </c>
       <c r="B84" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C84" t="s">
         <v>95</v>
       </c>
       <c r="D84" t="n">
-        <v>5.28</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="85">
@@ -2331,13 +2358,13 @@
         <v>70</v>
       </c>
       <c r="B85" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C85" t="s">
         <v>96</v>
       </c>
       <c r="D85" t="n">
-        <v>5.46</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="86">
@@ -2345,13 +2372,13 @@
         <v>70</v>
       </c>
       <c r="B86" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C86" t="s">
         <v>97</v>
       </c>
       <c r="D86" t="n">
-        <v>8.77</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="87">
@@ -2359,13 +2386,13 @@
         <v>70</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C87" t="s">
         <v>98</v>
       </c>
       <c r="D87" t="n">
-        <v>12.74</v>
+        <v>9.56</v>
       </c>
     </row>
     <row r="88">
@@ -2373,13 +2400,13 @@
         <v>70</v>
       </c>
       <c r="B88" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C88" t="s">
         <v>99</v>
       </c>
       <c r="D88" t="n">
-        <v>14.21</v>
+        <v>12.14</v>
       </c>
     </row>
     <row r="89">
@@ -2387,13 +2414,13 @@
         <v>70</v>
       </c>
       <c r="B89" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C89" t="s">
         <v>100</v>
       </c>
       <c r="D89" t="n">
-        <v>15.16</v>
+        <v>14.01</v>
       </c>
     </row>
     <row r="90">
@@ -2401,13 +2428,13 @@
         <v>70</v>
       </c>
       <c r="B90" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C90" t="s">
         <v>101</v>
       </c>
       <c r="D90" t="n">
-        <v>17.52</v>
+        <v>14.64</v>
       </c>
     </row>
     <row r="91">
@@ -2415,13 +2442,13 @@
         <v>70</v>
       </c>
       <c r="B91" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C91" t="s">
         <v>102</v>
       </c>
       <c r="D91" t="n">
-        <v>18.5</v>
+        <v>18.05</v>
       </c>
     </row>
     <row r="92">
@@ -2435,7 +2462,7 @@
         <v>105</v>
       </c>
       <c r="D92" t="n">
-        <v>2.34</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="93">
@@ -2449,7 +2476,7 @@
         <v>106</v>
       </c>
       <c r="D93" t="n">
-        <v>2.42</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="94">
@@ -2463,7 +2490,7 @@
         <v>107</v>
       </c>
       <c r="D94" t="n">
-        <v>2.69</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="95">
@@ -2477,7 +2504,7 @@
         <v>108</v>
       </c>
       <c r="D95" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="96">
@@ -2491,7 +2518,7 @@
         <v>109</v>
       </c>
       <c r="D96" t="n">
-        <v>2.97</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="97">
@@ -2505,7 +2532,7 @@
         <v>110</v>
       </c>
       <c r="D97" t="n">
-        <v>3.84</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="98">
@@ -2519,7 +2546,7 @@
         <v>111</v>
       </c>
       <c r="D98" t="n">
-        <v>4.34</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="99">
@@ -2533,7 +2560,7 @@
         <v>112</v>
       </c>
       <c r="D99" t="n">
-        <v>4.34</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="100">
@@ -2547,7 +2574,7 @@
         <v>113</v>
       </c>
       <c r="D100" t="n">
-        <v>8.23</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="101">
@@ -2561,7 +2588,7 @@
         <v>114</v>
       </c>
       <c r="D101" t="n">
-        <v>8.9</v>
+        <v>8.89</v>
       </c>
     </row>
     <row r="102">
@@ -2575,7 +2602,7 @@
         <v>115</v>
       </c>
       <c r="D102" t="n">
-        <v>20.33</v>
+        <v>9.28</v>
       </c>
     </row>
     <row r="103">
@@ -2589,7 +2616,7 @@
         <v>116</v>
       </c>
       <c r="D103" t="n">
-        <v>20.51</v>
+        <v>10.63</v>
       </c>
     </row>
     <row r="104">
@@ -2603,7 +2630,7 @@
         <v>117</v>
       </c>
       <c r="D104" t="n">
-        <v>21.02</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="105">
@@ -2611,13 +2638,13 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
+        <v>104</v>
+      </c>
+      <c r="C105" t="s">
         <v>118</v>
       </c>
-      <c r="C105" t="s">
-        <v>119</v>
-      </c>
       <c r="D105" t="n">
-        <v>2.12</v>
+        <v>15.64</v>
       </c>
     </row>
     <row r="106">
@@ -2625,13 +2652,13 @@
         <v>103</v>
       </c>
       <c r="B106" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C106" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D106" t="n">
-        <v>2.3</v>
+        <v>16.63</v>
       </c>
     </row>
     <row r="107">
@@ -2639,13 +2666,13 @@
         <v>103</v>
       </c>
       <c r="B107" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C107" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D107" t="n">
-        <v>3.25</v>
+        <v>16.85</v>
       </c>
     </row>
     <row r="108">
@@ -2653,13 +2680,13 @@
         <v>103</v>
       </c>
       <c r="B108" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C108" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D108" t="n">
-        <v>4.35</v>
+        <v>17.27</v>
       </c>
     </row>
     <row r="109">
@@ -2667,13 +2694,13 @@
         <v>103</v>
       </c>
       <c r="B109" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C109" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D109" t="n">
-        <v>4.38</v>
+        <v>17.68</v>
       </c>
     </row>
     <row r="110">
@@ -2681,13 +2708,13 @@
         <v>103</v>
       </c>
       <c r="B110" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C110" t="s">
         <v>124</v>
       </c>
       <c r="D110" t="n">
-        <v>4.38</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="111">
@@ -2695,13 +2722,13 @@
         <v>103</v>
       </c>
       <c r="B111" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C111" t="s">
         <v>125</v>
       </c>
       <c r="D111" t="n">
-        <v>4.38</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="112">
@@ -2709,13 +2736,13 @@
         <v>103</v>
       </c>
       <c r="B112" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C112" t="s">
         <v>126</v>
       </c>
       <c r="D112" t="n">
-        <v>4.47</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="113">
@@ -2723,13 +2750,13 @@
         <v>103</v>
       </c>
       <c r="B113" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C113" t="s">
         <v>127</v>
       </c>
       <c r="D113" t="n">
-        <v>4.57</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="114">
@@ -2737,13 +2764,13 @@
         <v>103</v>
       </c>
       <c r="B114" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C114" t="s">
         <v>128</v>
       </c>
       <c r="D114" t="n">
-        <v>5.44</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="115">
@@ -2751,13 +2778,13 @@
         <v>103</v>
       </c>
       <c r="B115" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C115" t="s">
         <v>129</v>
       </c>
       <c r="D115" t="n">
-        <v>9.61</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="116">
@@ -2765,13 +2792,13 @@
         <v>103</v>
       </c>
       <c r="B116" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C116" t="s">
         <v>130</v>
       </c>
       <c r="D116" t="n">
-        <v>10.13</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="117">
@@ -2779,13 +2806,13 @@
         <v>103</v>
       </c>
       <c r="B117" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C117" t="s">
         <v>131</v>
       </c>
       <c r="D117" t="n">
-        <v>11.53</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="118">
@@ -2793,13 +2820,13 @@
         <v>103</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C118" t="s">
         <v>132</v>
       </c>
       <c r="D118" t="n">
-        <v>17.08</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="119">
@@ -2807,13 +2834,13 @@
         <v>103</v>
       </c>
       <c r="B119" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C119" t="s">
         <v>133</v>
       </c>
       <c r="D119" t="n">
-        <v>19.11</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="120">
@@ -2821,13 +2848,13 @@
         <v>103</v>
       </c>
       <c r="B120" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C120" t="s">
         <v>134</v>
       </c>
       <c r="D120" t="n">
-        <v>19.75</v>
+        <v>8.87</v>
       </c>
     </row>
     <row r="121">
@@ -2835,13 +2862,13 @@
         <v>103</v>
       </c>
       <c r="B121" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C121" t="s">
         <v>135</v>
       </c>
       <c r="D121" t="n">
-        <v>19.83</v>
+        <v>16.24</v>
       </c>
     </row>
     <row r="122">
@@ -2855,7 +2882,7 @@
         <v>138</v>
       </c>
       <c r="D122" t="n">
-        <v>2.67</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="123">
@@ -2869,7 +2896,7 @@
         <v>139</v>
       </c>
       <c r="D123" t="n">
-        <v>2.72</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="124">
@@ -2883,7 +2910,7 @@
         <v>140</v>
       </c>
       <c r="D124" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="125">
@@ -2897,7 +2924,7 @@
         <v>141</v>
       </c>
       <c r="D125" t="n">
-        <v>2.97</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="126">
@@ -2911,7 +2938,7 @@
         <v>142</v>
       </c>
       <c r="D126" t="n">
-        <v>3.39</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="127">
@@ -2925,7 +2952,7 @@
         <v>143</v>
       </c>
       <c r="D127" t="n">
-        <v>4.66</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="128">
@@ -2939,7 +2966,7 @@
         <v>144</v>
       </c>
       <c r="D128" t="n">
-        <v>4.66</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="129">
@@ -2953,7 +2980,7 @@
         <v>145</v>
       </c>
       <c r="D129" t="n">
-        <v>5.3</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="130">
@@ -2967,7 +2994,7 @@
         <v>146</v>
       </c>
       <c r="D130" t="n">
-        <v>6.74</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="131">
@@ -2981,7 +3008,7 @@
         <v>147</v>
       </c>
       <c r="D131" t="n">
-        <v>6.86</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="132">
@@ -2995,7 +3022,7 @@
         <v>148</v>
       </c>
       <c r="D132" t="n">
-        <v>8.54</v>
+        <v>10.74</v>
       </c>
     </row>
     <row r="133">
@@ -3009,7 +3036,7 @@
         <v>149</v>
       </c>
       <c r="D133" t="n">
-        <v>8.99</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="134">
@@ -3023,7 +3050,7 @@
         <v>150</v>
       </c>
       <c r="D134" t="n">
-        <v>10.84</v>
+        <v>11.23</v>
       </c>
     </row>
     <row r="135">
@@ -3037,7 +3064,7 @@
         <v>151</v>
       </c>
       <c r="D135" t="n">
-        <v>14.18</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="136">
@@ -3051,7 +3078,7 @@
         <v>153</v>
       </c>
       <c r="D136" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="137">
@@ -3065,7 +3092,7 @@
         <v>154</v>
       </c>
       <c r="D137" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="138">
@@ -3079,7 +3106,7 @@
         <v>155</v>
       </c>
       <c r="D138" t="n">
-        <v>2.14</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="139">
@@ -3093,7 +3120,7 @@
         <v>156</v>
       </c>
       <c r="D139" t="n">
-        <v>2.45</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="140">
@@ -3107,7 +3134,7 @@
         <v>157</v>
       </c>
       <c r="D140" t="n">
-        <v>2.99</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="141">
@@ -3121,7 +3148,7 @@
         <v>158</v>
       </c>
       <c r="D141" t="n">
-        <v>4.11</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="142">
@@ -3135,7 +3162,7 @@
         <v>159</v>
       </c>
       <c r="D142" t="n">
-        <v>4.11</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="143">
@@ -3149,7 +3176,7 @@
         <v>160</v>
       </c>
       <c r="D143" t="n">
-        <v>5.13</v>
+        <v>5.74</v>
       </c>
     </row>
     <row r="144">
@@ -3163,7 +3190,7 @@
         <v>161</v>
       </c>
       <c r="D144" t="n">
-        <v>6.6</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="145">
@@ -3177,7 +3204,7 @@
         <v>162</v>
       </c>
       <c r="D145" t="n">
-        <v>8.64</v>
+        <v>9.21</v>
       </c>
     </row>
     <row r="146">
@@ -3191,7 +3218,7 @@
         <v>163</v>
       </c>
       <c r="D146" t="n">
-        <v>9.88</v>
+        <v>9.72</v>
       </c>
     </row>
     <row r="147">
@@ -3205,7 +3232,7 @@
         <v>164</v>
       </c>
       <c r="D147" t="n">
-        <v>9.92</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="148">
@@ -3219,7 +3246,7 @@
         <v>165</v>
       </c>
       <c r="D148" t="n">
-        <v>14.52</v>
+        <v>13.22</v>
       </c>
     </row>
     <row r="149">
@@ -3233,7 +3260,7 @@
         <v>166</v>
       </c>
       <c r="D149" t="n">
-        <v>15.44</v>
+        <v>13.69</v>
       </c>
     </row>
     <row r="150">
@@ -3247,7 +3274,7 @@
         <v>167</v>
       </c>
       <c r="D150" t="n">
-        <v>15.64</v>
+        <v>14.43</v>
       </c>
     </row>
     <row r="151">
@@ -3261,7 +3288,7 @@
         <v>168</v>
       </c>
       <c r="D151" t="n">
-        <v>16.03</v>
+        <v>15.64</v>
       </c>
     </row>
     <row r="152">
@@ -3275,7 +3302,7 @@
         <v>171</v>
       </c>
       <c r="D152" t="n">
-        <v>2.29</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="153">
@@ -3289,7 +3316,7 @@
         <v>172</v>
       </c>
       <c r="D153" t="n">
-        <v>2.94</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="154">
@@ -3303,7 +3330,7 @@
         <v>173</v>
       </c>
       <c r="D154" t="n">
-        <v>3.35</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="155">
@@ -3317,7 +3344,7 @@
         <v>174</v>
       </c>
       <c r="D155" t="n">
-        <v>3.74</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="156">
@@ -3331,7 +3358,7 @@
         <v>175</v>
       </c>
       <c r="D156" t="n">
-        <v>3.98</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="157">
@@ -3345,7 +3372,7 @@
         <v>176</v>
       </c>
       <c r="D157" t="n">
-        <v>4.24</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="158">
@@ -3359,7 +3386,7 @@
         <v>177</v>
       </c>
       <c r="D158" t="n">
-        <v>4.64</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="159">
@@ -3373,7 +3400,7 @@
         <v>178</v>
       </c>
       <c r="D159" t="n">
-        <v>4.64</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="160">
@@ -3387,7 +3414,7 @@
         <v>179</v>
       </c>
       <c r="D160" t="n">
-        <v>5.02</v>
+        <v>7.54</v>
       </c>
     </row>
     <row r="161">
@@ -3401,7 +3428,7 @@
         <v>180</v>
       </c>
       <c r="D161" t="n">
-        <v>5.4</v>
+        <v>9.08</v>
       </c>
     </row>
     <row r="162">
@@ -3415,7 +3442,7 @@
         <v>181</v>
       </c>
       <c r="D162" t="n">
-        <v>11.58</v>
+        <v>9.28</v>
       </c>
     </row>
     <row r="163">
@@ -3429,7 +3456,7 @@
         <v>182</v>
       </c>
       <c r="D163" t="n">
-        <v>13.82</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="164">
@@ -3443,7 +3470,7 @@
         <v>183</v>
       </c>
       <c r="D164" t="n">
-        <v>13.89</v>
+        <v>25.26</v>
       </c>
     </row>
     <row r="165">
@@ -3457,7 +3484,7 @@
         <v>185</v>
       </c>
       <c r="D165" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="166">
@@ -3471,7 +3498,7 @@
         <v>186</v>
       </c>
       <c r="D166" t="n">
-        <v>2.12</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="167">
@@ -3485,7 +3512,7 @@
         <v>187</v>
       </c>
       <c r="D167" t="n">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="168">
@@ -3499,7 +3526,7 @@
         <v>188</v>
       </c>
       <c r="D168" t="n">
-        <v>3.17</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="169">
@@ -3513,7 +3540,7 @@
         <v>189</v>
       </c>
       <c r="D169" t="n">
-        <v>3.64</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="170">
@@ -3527,7 +3554,7 @@
         <v>190</v>
       </c>
       <c r="D170" t="n">
-        <v>3.92</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="171">
@@ -3541,7 +3568,7 @@
         <v>191</v>
       </c>
       <c r="D171" t="n">
-        <v>4.13</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="172">
@@ -3555,7 +3582,7 @@
         <v>192</v>
       </c>
       <c r="D172" t="n">
-        <v>4.13</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="173">
@@ -3569,7 +3596,7 @@
         <v>193</v>
       </c>
       <c r="D173" t="n">
-        <v>6.58</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="174">
@@ -3583,7 +3610,7 @@
         <v>194</v>
       </c>
       <c r="D174" t="n">
-        <v>6.64</v>
+        <v>7</v>
       </c>
     </row>
     <row r="175">
@@ -3597,7 +3624,7 @@
         <v>195</v>
       </c>
       <c r="D175" t="n">
-        <v>6.76</v>
+        <v>7.74</v>
       </c>
     </row>
     <row r="176">
@@ -3611,7 +3638,7 @@
         <v>196</v>
       </c>
       <c r="D176" t="n">
-        <v>9.13</v>
+        <v>9.11</v>
       </c>
     </row>
     <row r="177">
@@ -3625,7 +3652,7 @@
         <v>197</v>
       </c>
       <c r="D177" t="n">
-        <v>9.64</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="178">
@@ -3639,7 +3666,7 @@
         <v>198</v>
       </c>
       <c r="D178" t="n">
-        <v>10.71</v>
+        <v>11.57</v>
       </c>
     </row>
     <row r="179">
@@ -3653,7 +3680,7 @@
         <v>199</v>
       </c>
       <c r="D179" t="n">
-        <v>11.1</v>
+        <v>12.13</v>
       </c>
     </row>
     <row r="180">
@@ -3667,7 +3694,7 @@
         <v>200</v>
       </c>
       <c r="D180" t="n">
-        <v>13.1</v>
+        <v>15.64</v>
       </c>
     </row>
     <row r="181">
@@ -3681,7 +3708,7 @@
         <v>201</v>
       </c>
       <c r="D181" t="n">
-        <v>14.3</v>
+        <v>30.08</v>
       </c>
     </row>
     <row r="182">
@@ -3695,7 +3722,7 @@
         <v>204</v>
       </c>
       <c r="D182" t="n">
-        <v>2.35</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="183">
@@ -3709,7 +3736,7 @@
         <v>205</v>
       </c>
       <c r="D183" t="n">
-        <v>2.8</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="184">
@@ -3723,7 +3750,7 @@
         <v>206</v>
       </c>
       <c r="D184" t="n">
-        <v>2.81</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="185">
@@ -3737,7 +3764,7 @@
         <v>207</v>
       </c>
       <c r="D185" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="186">
@@ -3751,7 +3778,7 @@
         <v>208</v>
       </c>
       <c r="D186" t="n">
-        <v>3.4</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="187">
@@ -3765,7 +3792,7 @@
         <v>209</v>
       </c>
       <c r="D187" t="n">
-        <v>3.44</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="188">
@@ -3779,7 +3806,7 @@
         <v>210</v>
       </c>
       <c r="D188" t="n">
-        <v>4.07</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="189">
@@ -3793,7 +3820,7 @@
         <v>211</v>
       </c>
       <c r="D189" t="n">
-        <v>4.07</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="190">
@@ -3807,7 +3834,7 @@
         <v>212</v>
       </c>
       <c r="D190" t="n">
-        <v>5.67</v>
+        <v>7.57</v>
       </c>
     </row>
     <row r="191">
@@ -3821,7 +3848,7 @@
         <v>213</v>
       </c>
       <c r="D191" t="n">
-        <v>6.67</v>
+        <v>9.34</v>
       </c>
     </row>
     <row r="192">
@@ -3835,7 +3862,7 @@
         <v>214</v>
       </c>
       <c r="D192" t="n">
-        <v>7.96</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="193">
@@ -3849,7 +3876,7 @@
         <v>215</v>
       </c>
       <c r="D193" t="n">
-        <v>8.63</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="194">
@@ -3863,7 +3890,7 @@
         <v>216</v>
       </c>
       <c r="D194" t="n">
-        <v>9.96</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="195">
@@ -3877,7 +3904,7 @@
         <v>217</v>
       </c>
       <c r="D195" t="n">
-        <v>11.41</v>
+        <v>16.36</v>
       </c>
     </row>
     <row r="196">
@@ -3891,7 +3918,7 @@
         <v>218</v>
       </c>
       <c r="D196" t="n">
-        <v>14.1</v>
+        <v>19.23</v>
       </c>
     </row>
     <row r="197">
@@ -3899,13 +3926,13 @@
         <v>202</v>
       </c>
       <c r="B197" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="C197" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D197" t="n">
-        <v>14.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="198">
@@ -3913,13 +3940,13 @@
         <v>202</v>
       </c>
       <c r="B198" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C198" t="s">
         <v>221</v>
       </c>
       <c r="D198" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="199">
@@ -3927,13 +3954,13 @@
         <v>202</v>
       </c>
       <c r="B199" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C199" t="s">
         <v>222</v>
       </c>
       <c r="D199" t="n">
-        <v>2.46</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="200">
@@ -3941,13 +3968,13 @@
         <v>202</v>
       </c>
       <c r="B200" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C200" t="s">
         <v>223</v>
       </c>
       <c r="D200" t="n">
-        <v>2.87</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="201">
@@ -3955,13 +3982,13 @@
         <v>202</v>
       </c>
       <c r="B201" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C201" t="s">
         <v>224</v>
       </c>
       <c r="D201" t="n">
-        <v>3.6</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="202">
@@ -3969,13 +3996,13 @@
         <v>202</v>
       </c>
       <c r="B202" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C202" t="s">
         <v>225</v>
       </c>
       <c r="D202" t="n">
-        <v>4.35</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="203">
@@ -3983,13 +4010,13 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C203" t="s">
         <v>226</v>
       </c>
       <c r="D203" t="n">
-        <v>4.84</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="204">
@@ -3997,13 +4024,13 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C204" t="s">
         <v>227</v>
       </c>
       <c r="D204" t="n">
-        <v>4.84</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="205">
@@ -4011,13 +4038,13 @@
         <v>202</v>
       </c>
       <c r="B205" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C205" t="s">
         <v>228</v>
       </c>
       <c r="D205" t="n">
-        <v>6.31</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="206">
@@ -4025,13 +4052,13 @@
         <v>202</v>
       </c>
       <c r="B206" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C206" t="s">
         <v>229</v>
       </c>
       <c r="D206" t="n">
-        <v>6.83</v>
+        <v>7.28</v>
       </c>
     </row>
     <row r="207">
@@ -4039,13 +4066,13 @@
         <v>202</v>
       </c>
       <c r="B207" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C207" t="s">
         <v>230</v>
       </c>
       <c r="D207" t="n">
-        <v>7.21</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="208">
@@ -4053,13 +4080,13 @@
         <v>202</v>
       </c>
       <c r="B208" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C208" t="s">
         <v>231</v>
       </c>
       <c r="D208" t="n">
-        <v>9.86</v>
+        <v>11.73</v>
       </c>
     </row>
     <row r="209">
@@ -4067,13 +4094,13 @@
         <v>202</v>
       </c>
       <c r="B209" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C209" t="s">
         <v>232</v>
       </c>
       <c r="D209" t="n">
-        <v>9.9</v>
+        <v>12.51</v>
       </c>
     </row>
     <row r="210">
@@ -4081,13 +4108,13 @@
         <v>202</v>
       </c>
       <c r="B210" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C210" t="s">
         <v>233</v>
       </c>
       <c r="D210" t="n">
-        <v>10.94</v>
+        <v>14.44</v>
       </c>
     </row>
     <row r="211">
@@ -4095,13 +4122,13 @@
         <v>202</v>
       </c>
       <c r="B211" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C211" t="s">
         <v>234</v>
       </c>
       <c r="D211" t="n">
-        <v>17.46</v>
+        <v>15.24</v>
       </c>
     </row>
     <row r="212">
@@ -4115,7 +4142,7 @@
         <v>237</v>
       </c>
       <c r="D212" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="213">
@@ -4129,7 +4156,7 @@
         <v>238</v>
       </c>
       <c r="D213" t="n">
-        <v>1.9</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="214">
@@ -4143,7 +4170,7 @@
         <v>239</v>
       </c>
       <c r="D214" t="n">
-        <v>2.66</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="215">
@@ -4157,7 +4184,7 @@
         <v>240</v>
       </c>
       <c r="D215" t="n">
-        <v>2.72</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="216">
@@ -4171,7 +4198,7 @@
         <v>241</v>
       </c>
       <c r="D216" t="n">
-        <v>2.82</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="217">
@@ -4185,7 +4212,7 @@
         <v>242</v>
       </c>
       <c r="D217" t="n">
-        <v>3.2</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="218">
@@ -4199,7 +4226,7 @@
         <v>243</v>
       </c>
       <c r="D218" t="n">
-        <v>3.57</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="219">
@@ -4213,7 +4240,7 @@
         <v>244</v>
       </c>
       <c r="D219" t="n">
-        <v>3.57</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="220">
@@ -4227,7 +4254,7 @@
         <v>245</v>
       </c>
       <c r="D220" t="n">
-        <v>4.03</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="221">
@@ -4241,7 +4268,7 @@
         <v>246</v>
       </c>
       <c r="D221" t="n">
-        <v>4.7</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="222">
@@ -4255,7 +4282,7 @@
         <v>247</v>
       </c>
       <c r="D222" t="n">
-        <v>7.46</v>
+        <v>9.34</v>
       </c>
     </row>
     <row r="223">
@@ -4269,7 +4296,7 @@
         <v>248</v>
       </c>
       <c r="D223" t="n">
-        <v>8.64</v>
+        <v>10.69</v>
       </c>
     </row>
     <row r="224">
@@ -4283,7 +4310,7 @@
         <v>249</v>
       </c>
       <c r="D224" t="n">
-        <v>9.1</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="225">
@@ -4297,7 +4324,7 @@
         <v>250</v>
       </c>
       <c r="D225" t="n">
-        <v>10.64</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="226">
@@ -4311,7 +4338,7 @@
         <v>251</v>
       </c>
       <c r="D226" t="n">
-        <v>12.01</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="227">
@@ -4325,7 +4352,7 @@
         <v>252</v>
       </c>
       <c r="D227" t="n">
-        <v>12.4</v>
+        <v>23.26</v>
       </c>
     </row>
     <row r="228">
@@ -4339,7 +4366,7 @@
         <v>253</v>
       </c>
       <c r="D228" t="n">
-        <v>17.67</v>
+        <v>36.86</v>
       </c>
     </row>
     <row r="229">
@@ -4347,13 +4374,13 @@
         <v>235</v>
       </c>
       <c r="B229" t="s">
+        <v>236</v>
+      </c>
+      <c r="C229" t="s">
         <v>254</v>
       </c>
-      <c r="C229" t="s">
-        <v>255</v>
-      </c>
       <c r="D229" t="n">
-        <v>3.29</v>
+        <v>41.38</v>
       </c>
     </row>
     <row r="230">
@@ -4361,167 +4388,279 @@
         <v>235</v>
       </c>
       <c r="B230" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="C230" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D230" t="n">
-        <v>3.57</v>
+        <v>52.38</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="B231" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C231" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D231" t="n">
-        <v>3.94</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="B232" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C232" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D232" t="n">
-        <v>3.99</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="B233" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D233" t="n">
-        <v>6.3</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="B234" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C234" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D234" t="n">
-        <v>6.3</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="B235" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C235" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D235" t="n">
-        <v>8.01</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="B236" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C236" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D236" t="n">
-        <v>8.45</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="B237" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C237" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D237" t="n">
-        <v>8.65</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="B238" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C238" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D238" t="n">
-        <v>9.71</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="B239" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C239" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D239" t="n">
-        <v>10.59</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="B240" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C240" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D240" t="n">
-        <v>15.86</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="B241" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C241" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D241" t="n">
-        <v>18.41</v>
+        <v>6.59</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s">
+        <v>256</v>
+      </c>
+      <c r="B242" t="s">
+        <v>257</v>
+      </c>
+      <c r="C242" t="s">
+        <v>269</v>
+      </c>
+      <c r="D242" t="n">
+        <v>9.65</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s">
+        <v>256</v>
+      </c>
+      <c r="B243" t="s">
+        <v>257</v>
+      </c>
+      <c r="C243" t="s">
+        <v>270</v>
+      </c>
+      <c r="D243" t="n">
+        <v>11.59</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s">
+        <v>256</v>
+      </c>
+      <c r="B244" t="s">
+        <v>257</v>
+      </c>
+      <c r="C244" t="s">
+        <v>271</v>
+      </c>
+      <c r="D244" t="n">
+        <v>24.04</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s">
+        <v>256</v>
+      </c>
+      <c r="B245" t="s">
+        <v>257</v>
+      </c>
+      <c r="C245" t="s">
+        <v>272</v>
+      </c>
+      <c r="D245" t="n">
+        <v>27.34</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s">
+        <v>256</v>
+      </c>
+      <c r="B246" t="s">
+        <v>257</v>
+      </c>
+      <c r="C246" t="s">
+        <v>273</v>
+      </c>
+      <c r="D246" t="n">
+        <v>30.24</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s">
+        <v>256</v>
+      </c>
+      <c r="B247" t="s">
+        <v>257</v>
+      </c>
+      <c r="C247" t="s">
+        <v>274</v>
+      </c>
+      <c r="D247" t="n">
+        <v>35.19</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s">
+        <v>256</v>
+      </c>
+      <c r="B248" t="s">
+        <v>257</v>
+      </c>
+      <c r="C248" t="s">
+        <v>275</v>
+      </c>
+      <c r="D248" t="n">
+        <v>38.91</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s">
+        <v>256</v>
+      </c>
+      <c r="B249" t="s">
+        <v>257</v>
+      </c>
+      <c r="C249" t="s">
+        <v>276</v>
+      </c>
+      <c r="D249" t="n">
+        <v>40.15</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_anytime_tryscorers.xlsx
+++ b/files/NRL_anytime_tryscorers.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="268">
   <si>
     <t xml:space="preserve">Game</t>
   </si>
@@ -26,7 +26,304 @@
     <t xml:space="preserve">Price</t>
   </si>
   <si>
-    <t xml:space="preserve">newcastle knights at canberra raiders</t>
+    <t xml:space="preserve">sydney roosters at penrith panthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penrith panthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Jenkins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian To'o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaxen Edgar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Izack Tago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiah Papali'i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paul Alamoti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathan Cleary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freddy Lussick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lindsay Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Henry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Cogger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moses Leota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark Nawaqanitawase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Tedesco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugo Savala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robert Toia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salesi Foketi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siua Wong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daly Cherry-Evans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reece Robson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Victor Radley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nat Butcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Watson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egan Butcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lindsay Collins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cody Ramsey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spencer Leniu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolphins at manly-warringah sea eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamiso Tabuai-Fidow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selwyn Cobbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamayne Isaako</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herbie Farnworth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Bostock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connelly Lemuelu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kulikefu Finefeuiaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kodi Nikorima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremy Marshall-King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ray Stone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Flegler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiya Katoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Plath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Felise Kaufusi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morgan Knowles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Gilbert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francis Molo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manly-warringah sea eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clayton Faulalo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jason Saab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lehi Hopoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tolutau Koula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reuben Garrick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joey Walsh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haumole Olakau'atu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corey Waddell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamal Fogarty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brandon Wakeham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathan Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caleb Navale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simione Laiafi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs at canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jethro Rinakama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Kiraz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matt Burton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stephen Crichton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Tracey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enari Tuala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viliame Kikau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Preston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lachlan Galvin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Mann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaeman Salmon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jonathan Sua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Curran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bailey Hayward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Johnston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campbell Graham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tallis Duncan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cody Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Wighton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Dufty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">David Fifita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Elliott</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron Murray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keaon Koloamatangi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Sullivan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brandon Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John Radel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tevita Tatola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euan Aitken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jye Gray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders at cronulla-sutherland sharks</t>
   </si>
   <si>
     <t xml:space="preserve">canberra raiders</t>
@@ -41,24 +338,24 @@
     <t xml:space="preserve">Kaeo Weekes</t>
   </si>
   <si>
-    <t xml:space="preserve">Sebastian Kris</t>
-  </si>
-  <si>
     <t xml:space="preserve">Matthew Timoko</t>
   </si>
   <si>
     <t xml:space="preserve">Ethan Strange</t>
   </si>
   <si>
+    <t xml:space="preserve">Savelio Tamale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zac Hosking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matty Nicholson</t>
+  </si>
+  <si>
     <t xml:space="preserve">Owen Pattie</t>
   </si>
   <si>
-    <t xml:space="preserve">Ata Mariota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zac Hosking</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ethan Sanders</t>
   </si>
   <si>
@@ -68,16 +365,307 @@
     <t xml:space="preserve">Daine Laurie</t>
   </si>
   <si>
-    <t xml:space="preserve">Matty Nicholson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corey Horsburgh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Starling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joseph Tapine</t>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronaldo Mulitalo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sione Katoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">William Kennedy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mawene Hiroti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayal Iro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braydon Trindall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Briton Nikora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teig Wilton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicholas Hynes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siosifa Talakai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Hazelton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blayke Brailey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesse Colquhoun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron McInnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuku Hau Tapuha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braden Hamlin-Uele</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oregon Kaufusi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niwhai Puru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys at parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north queensland cowboys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braidon Burns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murray Taulagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scott Drinkwater</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Chester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zac Laybutt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heilum Luki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kai O'Donnell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Clifford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reed Mahoney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaxon Purdue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reuben Cotter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam McIntyre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soni Luke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Griffin Neame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Sutton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Addo-Carr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apa Twidle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian Kelly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Penisini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Samrani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitchell Moses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kitione Kautoga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tallyn Da Silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronald Volkman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack De Belin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luca Moretti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kelma Tuilagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Paulo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors at brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grant Anderson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josiah Karapani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reece Walsh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezra Mam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kotoni Staggs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaiyden Hunt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Riki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deine Mariner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Walters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Duffy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Talty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Willison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gehamat Shibasaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payne Haas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Gosiewski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blake Mozer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alofiana Khan-Pereira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dallin Watene-Zelezniak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leka Halasima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Metcalf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charnze Nicoll-Klokstad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ali Leiataua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Capewell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Laban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chanel Harris-Tavita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wayde Egan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Fisher-Harris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Healey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erin Clark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eddie Ieremia-Toeava</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans at newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phillip Sami</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dean Ieremia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jojo Fifita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Campbell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keano Kini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AJ Brimson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Patston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beau Fermor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver Pascoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lachlan Ilias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tino Fa'asuamaleaui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurtis Morrin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chris Randall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Bai</t>
   </si>
   <si>
     <t xml:space="preserve">newcastle knights</t>
@@ -98,88 +686,40 @@
     <t xml:space="preserve">Kalyn Ponga</t>
   </si>
   <si>
+    <t xml:space="preserve">Jermaine McEwen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francis Manuleleua</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dane Gagai</t>
   </si>
   <si>
-    <t xml:space="preserve">Francis Manuleleua</t>
-  </si>
-  <si>
     <t xml:space="preserve">Trey Mooney</t>
   </si>
   <si>
     <t xml:space="preserve">Sandon Smith</t>
   </si>
   <si>
-    <t xml:space="preserve">Jermaine McEwen</t>
-  </si>
-  <si>
     <t xml:space="preserve">Phoenix Crossland</t>
   </si>
   <si>
+    <t xml:space="preserve">Harrison Graham</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fletcher Hunt</t>
   </si>
   <si>
     <t xml:space="preserve">Tyson Frizell</t>
   </si>
   <si>
-    <t xml:space="preserve">Brodie Jones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks at st george-illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronaldo Mulitalo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sione Katoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">William Kennedy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kayal Iro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Braydon Trindall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Briton Nikora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jesse Ramien</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teig Wilton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicholas Hynes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siosifa Talakai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Hazelton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blayke Brailey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jesse Colquhoun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Addin Fonua-Blake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameron McInnes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oregon Kaufusi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samuel Stonestreet</t>
+    <t xml:space="preserve">Mat Croker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cody Hopwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george-illawarra dragons at wests tigers</t>
   </si>
   <si>
     <t xml:space="preserve">st george-illawarra dragons</t>
@@ -197,15 +737,18 @@
     <t xml:space="preserve">Valentine Holmes</t>
   </si>
   <si>
+    <t xml:space="preserve">Dylan Egan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamish Stewart</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jacob Liddle</t>
   </si>
   <si>
     <t xml:space="preserve">Kyle Flanagan</t>
   </si>
   <si>
-    <t xml:space="preserve">Dylan Egan</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mosese Suli</t>
   </si>
   <si>
@@ -215,574 +758,16 @@
     <t xml:space="preserve">Damien Cook</t>
   </si>
   <si>
-    <t xml:space="preserve">Hamish Stewart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luciano Leilua</t>
+    <t xml:space="preserve">Toby Couchman</t>
   </si>
   <si>
     <t xml:space="preserve">Ryan Couchman</t>
   </si>
   <si>
-    <t xml:space="preserve">sydney roosters at penrith panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penrith panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Jenkins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian To'o</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaxen Edgar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casey McLean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paul Alamoti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nathan Cleary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiah Papali'i</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freddy Lussick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lindsay Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Izack Tago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Henry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaah Yeo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Cogger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mark Nawaqanitawase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tommy Talau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Tedesco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hugo Savala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robert Toia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daly Cherry-Evans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nat Butcher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siua Wong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reece Robson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Victor Radley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salesi Foketi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Watson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spencer Leniu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Egan Butcher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cody Ramsey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins at manly-warringah sea eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamiso Tabuai-Fidow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selwyn Cobbo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamayne Isaako</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herbie Farnworth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Bostock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kodi Nikorima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connelly Lemuelu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremy Marshall-King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kulikefu Finefeuiaki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ray Stone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Flegler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiya Katoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Plath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurt Donoghoe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Felise Kaufusi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morgan Knowles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Gilbert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Francis Molo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manly-warringah sea eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jason Saab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lehi Hopoate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tolutau Koula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reuben Garrick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haumole Olakau'atu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joey Walsh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Feledy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben Trbojevic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamal Fogarty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicholas Lenaz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan Bullemor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simione Laiafi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">south sydney rabbitohs at canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jethro Rinakama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Kiraz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matt Burton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stephen Crichton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Preston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Tracey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enari Tuala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viliame Kikau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lachlan Galvin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurt Mann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaeman Salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jonathan Sua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Curran</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bailey Hayward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">south sydney rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Johnston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campbell Graham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cody Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Wighton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latrell Siegwalt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Dufty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keaon Koloamatangi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Elliott</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashton Ward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brandon Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Sullivan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tevita Tatola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jye Gray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">John Radel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamie Humphreys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Fletcher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys at parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Braidon Burns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Murray Taulagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremiah Nanai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scott Drinkwater</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Chester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zac Laybutt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heilum Luki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Clifford</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaxon Purdue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soni Luke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reuben Cotter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam McIntyre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Mikaele</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Addo-Carr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian Kelly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiah Iongi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Will Penisini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan Samrani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitchell Moses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tallyn Da Silva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronald Volkman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitione Kautoga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kelma Tuilagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack De Belin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Paulo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joash Papalii</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Tuivaiti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teancum Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors at brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grant Anderson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josiah Karapani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reece Walsh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ezra Mam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kotoni Staggs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Willison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deine Mariner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Reynolds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan Riki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Walters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben Talty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cory Paix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gehamat Shibasaki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payne Haas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Va'a Semu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alofiana Khan-Pereira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dallin Watene-Zelezniak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leka Halasima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charnze Nicoll-Klokstad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ali Leiataua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Te Maire Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Laban</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chanel Harris-Tavita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurt Capewell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wayde Egan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Fisher-Harris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Healey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erin Clark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eddie Ieremia-Toeava</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Metcalf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans at newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phillip Sami</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dean Ieremia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jojo Fifita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Campbell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arama Hau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keano Kini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beau Fermor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AJ Brimson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oliver Pascoe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tino Fa'asuamaleaui</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zane Harrison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurtis Morrin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chris Randall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Bai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Klese Haas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Verrills</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moeaki Fotuaika</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaylan De Groot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Patston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george-illawarra dragons at wests tigers</t>
+    <t xml:space="preserve">Emre Guler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Atkinson</t>
   </si>
   <si>
     <t xml:space="preserve">wests tigers</t>
@@ -800,49 +785,37 @@
     <t xml:space="preserve">Junior Tupou</t>
   </si>
   <si>
-    <t xml:space="preserve">Heamasi Makasini</t>
+    <t xml:space="preserve">Solomone Saukuru</t>
   </si>
   <si>
     <t xml:space="preserve">Samuela Fainu</t>
   </si>
   <si>
+    <t xml:space="preserve">Tony Sukkar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jarome Luai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apisai Koroisau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick Herbert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fonua Pole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terrell May</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sione Fainu</t>
   </si>
   <si>
-    <t xml:space="preserve">Jarome Luai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apisai Koroisau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patrick Herbert</t>
-  </si>
-  <si>
     <t xml:space="preserve">Alex Seyfarth</t>
   </si>
   <si>
-    <t xml:space="preserve">Terrell May</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fonua Pole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Starford To'a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Twal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charlie Murray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tristan Hope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heath Mason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tony Sukkar</t>
+    <t xml:space="preserve">Bunty Afoa</t>
   </si>
 </sst>
 </file>
@@ -1171,7 +1144,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="57.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="29.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="24.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="5.71" hidden="0" customWidth="1"/>
@@ -1202,7 +1175,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>2.22</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="3">
@@ -1216,7 +1189,7 @@
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>2.64</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="4">
@@ -1230,7 +1203,7 @@
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="5">
@@ -1244,7 +1217,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>2.76</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="6">
@@ -1258,7 +1231,7 @@
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="7">
@@ -1272,7 +1245,7 @@
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>3.23</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="8">
@@ -1286,7 +1259,7 @@
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>5.29</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="9">
@@ -1300,7 +1273,7 @@
         <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>5.48</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="10">
@@ -1314,7 +1287,7 @@
         <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>5.89</v>
+        <v>8.06</v>
       </c>
     </row>
     <row r="11">
@@ -1328,7 +1301,7 @@
         <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>6.22</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="12">
@@ -1342,7 +1315,7 @@
         <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>7.41</v>
+        <v>11.87</v>
       </c>
     </row>
     <row r="13">
@@ -1356,7 +1329,7 @@
         <v>17</v>
       </c>
       <c r="D13" t="n">
-        <v>8.04</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="14">
@@ -1370,7 +1343,7 @@
         <v>18</v>
       </c>
       <c r="D14" t="n">
-        <v>9.27</v>
+        <v>18.72</v>
       </c>
     </row>
     <row r="15">
@@ -1378,13 +1351,13 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D15" t="n">
-        <v>10.62</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="16">
@@ -1392,13 +1365,13 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D16" t="n">
-        <v>13.1</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="17">
@@ -1406,13 +1379,13 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D17" t="n">
-        <v>13.75</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="18">
@@ -1420,13 +1393,13 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
       </c>
       <c r="D18" t="n">
-        <v>2.01</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="19">
@@ -1434,13 +1407,13 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C19" t="s">
         <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>2.34</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="20">
@@ -1448,13 +1421,13 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
         <v>25</v>
       </c>
       <c r="D20" t="n">
-        <v>2.71</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="21">
@@ -1462,13 +1435,13 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C21" t="s">
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>3.4</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="22">
@@ -1476,13 +1449,13 @@
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C22" t="s">
         <v>27</v>
       </c>
       <c r="D22" t="n">
-        <v>4.09</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="23">
@@ -1490,13 +1463,13 @@
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C23" t="s">
         <v>28</v>
       </c>
       <c r="D23" t="n">
-        <v>5.92</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="24">
@@ -1504,13 +1477,13 @@
         <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C24" t="s">
         <v>29</v>
       </c>
       <c r="D24" t="n">
-        <v>5.99</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="25">
@@ -1518,13 +1491,13 @@
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C25" t="s">
         <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>6.41</v>
+        <v>9.57</v>
       </c>
     </row>
     <row r="26">
@@ -1532,13 +1505,13 @@
         <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C26" t="s">
         <v>31</v>
       </c>
       <c r="D26" t="n">
-        <v>6.77</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="27">
@@ -1546,13 +1519,13 @@
         <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C27" t="s">
         <v>32</v>
       </c>
       <c r="D27" t="n">
-        <v>7.46</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="28">
@@ -1560,13 +1533,13 @@
         <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C28" t="s">
         <v>33</v>
       </c>
       <c r="D28" t="n">
-        <v>9.23</v>
+        <v>14.77</v>
       </c>
     </row>
     <row r="29">
@@ -1574,13 +1547,13 @@
         <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C29" t="s">
         <v>34</v>
       </c>
       <c r="D29" t="n">
-        <v>10.24</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="30">
@@ -1588,13 +1561,13 @@
         <v>4</v>
       </c>
       <c r="B30" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C30" t="s">
         <v>35</v>
       </c>
       <c r="D30" t="n">
-        <v>14.89</v>
+        <v>18.21</v>
       </c>
     </row>
     <row r="31">
@@ -1602,13 +1575,13 @@
         <v>4</v>
       </c>
       <c r="B31" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C31" t="s">
         <v>36</v>
       </c>
       <c r="D31" t="n">
-        <v>16.32</v>
+        <v>18.77</v>
       </c>
     </row>
     <row r="32">
@@ -1622,7 +1595,7 @@
         <v>39</v>
       </c>
       <c r="D32" t="n">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="33">
@@ -1636,7 +1609,7 @@
         <v>40</v>
       </c>
       <c r="D33" t="n">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="34">
@@ -1650,7 +1623,7 @@
         <v>41</v>
       </c>
       <c r="D34" t="n">
-        <v>2.68</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="35">
@@ -1664,7 +1637,7 @@
         <v>42</v>
       </c>
       <c r="D35" t="n">
-        <v>2.78</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="36">
@@ -1678,7 +1651,7 @@
         <v>43</v>
       </c>
       <c r="D36" t="n">
-        <v>2.83</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="37">
@@ -1692,7 +1665,7 @@
         <v>44</v>
       </c>
       <c r="D37" t="n">
-        <v>3.16</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="38">
@@ -1706,7 +1679,7 @@
         <v>45</v>
       </c>
       <c r="D38" t="n">
-        <v>3.22</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="39">
@@ -1720,7 +1693,7 @@
         <v>46</v>
       </c>
       <c r="D39" t="n">
-        <v>3.4</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="40">
@@ -1734,7 +1707,7 @@
         <v>47</v>
       </c>
       <c r="D40" t="n">
-        <v>4.05</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="41">
@@ -1748,7 +1721,7 @@
         <v>48</v>
       </c>
       <c r="D41" t="n">
-        <v>7.07</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="42">
@@ -1762,7 +1735,7 @@
         <v>49</v>
       </c>
       <c r="D42" t="n">
-        <v>7.51</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="43">
@@ -1776,7 +1749,7 @@
         <v>50</v>
       </c>
       <c r="D43" t="n">
-        <v>8.7</v>
+        <v>11.06</v>
       </c>
     </row>
     <row r="44">
@@ -1790,7 +1763,7 @@
         <v>51</v>
       </c>
       <c r="D44" t="n">
-        <v>9.16</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="45">
@@ -1804,7 +1777,7 @@
         <v>52</v>
       </c>
       <c r="D45" t="n">
-        <v>9.19</v>
+        <v>17.31</v>
       </c>
     </row>
     <row r="46">
@@ -1818,7 +1791,7 @@
         <v>53</v>
       </c>
       <c r="D46" t="n">
-        <v>10.72</v>
+        <v>17.55</v>
       </c>
     </row>
     <row r="47">
@@ -1832,7 +1805,7 @@
         <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>12.83</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="48">
@@ -1846,7 +1819,7 @@
         <v>55</v>
       </c>
       <c r="D48" t="n">
-        <v>20.27</v>
+        <v>18.41</v>
       </c>
     </row>
     <row r="49">
@@ -1860,7 +1833,7 @@
         <v>57</v>
       </c>
       <c r="D49" t="n">
-        <v>3.07</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="50">
@@ -1874,7 +1847,7 @@
         <v>58</v>
       </c>
       <c r="D50" t="n">
-        <v>3.32</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="51">
@@ -1888,7 +1861,7 @@
         <v>59</v>
       </c>
       <c r="D51" t="n">
-        <v>3.65</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="52">
@@ -1902,7 +1875,7 @@
         <v>60</v>
       </c>
       <c r="D52" t="n">
-        <v>3.7</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="53">
@@ -1916,7 +1889,7 @@
         <v>61</v>
       </c>
       <c r="D53" t="n">
-        <v>7.38</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="54">
@@ -1930,7 +1903,7 @@
         <v>62</v>
       </c>
       <c r="D54" t="n">
-        <v>7.79</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="55">
@@ -1944,7 +1917,7 @@
         <v>63</v>
       </c>
       <c r="D55" t="n">
-        <v>7.82</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="56">
@@ -1958,7 +1931,7 @@
         <v>64</v>
       </c>
       <c r="D56" t="n">
-        <v>7.97</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="57">
@@ -1972,7 +1945,7 @@
         <v>65</v>
       </c>
       <c r="D57" t="n">
-        <v>8.95</v>
+        <v>8.06</v>
       </c>
     </row>
     <row r="58">
@@ -1986,7 +1959,7 @@
         <v>66</v>
       </c>
       <c r="D58" t="n">
-        <v>9.74</v>
+        <v>8.71</v>
       </c>
     </row>
     <row r="59">
@@ -2000,7 +1973,7 @@
         <v>67</v>
       </c>
       <c r="D59" t="n">
-        <v>10.1</v>
+        <v>14.17</v>
       </c>
     </row>
     <row r="60">
@@ -2014,7 +1987,7 @@
         <v>68</v>
       </c>
       <c r="D60" t="n">
-        <v>14.58</v>
+        <v>15.43</v>
       </c>
     </row>
     <row r="61">
@@ -2028,7 +2001,7 @@
         <v>69</v>
       </c>
       <c r="D61" t="n">
-        <v>16.91</v>
+        <v>18.22</v>
       </c>
     </row>
     <row r="62">
@@ -2042,7 +2015,7 @@
         <v>72</v>
       </c>
       <c r="D62" t="n">
-        <v>1.9</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="63">
@@ -2056,7 +2029,7 @@
         <v>73</v>
       </c>
       <c r="D63" t="n">
-        <v>2.31</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="64">
@@ -2070,7 +2043,7 @@
         <v>74</v>
       </c>
       <c r="D64" t="n">
-        <v>2.7</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="65">
@@ -2084,7 +2057,7 @@
         <v>75</v>
       </c>
       <c r="D65" t="n">
-        <v>2.85</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="66">
@@ -2098,7 +2071,7 @@
         <v>76</v>
       </c>
       <c r="D66" t="n">
-        <v>4.7</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="67">
@@ -2112,7 +2085,7 @@
         <v>77</v>
       </c>
       <c r="D67" t="n">
-        <v>4.81</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="68">
@@ -2126,7 +2099,7 @@
         <v>78</v>
       </c>
       <c r="D68" t="n">
-        <v>4.98</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="69">
@@ -2140,7 +2113,7 @@
         <v>79</v>
       </c>
       <c r="D69" t="n">
-        <v>6.32</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="70">
@@ -2154,7 +2127,7 @@
         <v>80</v>
       </c>
       <c r="D70" t="n">
-        <v>7.91</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="71">
@@ -2168,7 +2141,7 @@
         <v>81</v>
       </c>
       <c r="D71" t="n">
-        <v>8.65</v>
+        <v>11.39</v>
       </c>
     </row>
     <row r="72">
@@ -2182,7 +2155,7 @@
         <v>82</v>
       </c>
       <c r="D72" t="n">
-        <v>9.13</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="73">
@@ -2196,7 +2169,7 @@
         <v>83</v>
       </c>
       <c r="D73" t="n">
-        <v>10.34</v>
+        <v>11.53</v>
       </c>
     </row>
     <row r="74">
@@ -2210,7 +2183,7 @@
         <v>84</v>
       </c>
       <c r="D74" t="n">
-        <v>10.55</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="75">
@@ -2224,7 +2197,7 @@
         <v>85</v>
       </c>
       <c r="D75" t="n">
-        <v>11.97</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="76">
@@ -2238,7 +2211,7 @@
         <v>87</v>
       </c>
       <c r="D76" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="77">
@@ -2252,7 +2225,7 @@
         <v>88</v>
       </c>
       <c r="D77" t="n">
-        <v>2.7</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="78">
@@ -2266,7 +2239,7 @@
         <v>89</v>
       </c>
       <c r="D78" t="n">
-        <v>2.85</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="79">
@@ -2280,7 +2253,7 @@
         <v>90</v>
       </c>
       <c r="D79" t="n">
-        <v>3</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="80">
@@ -2294,7 +2267,7 @@
         <v>91</v>
       </c>
       <c r="D80" t="n">
-        <v>3.61</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="81">
@@ -2308,7 +2281,7 @@
         <v>92</v>
       </c>
       <c r="D81" t="n">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="82">
@@ -2322,7 +2295,7 @@
         <v>93</v>
       </c>
       <c r="D82" t="n">
-        <v>5.2</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="83">
@@ -2336,7 +2309,7 @@
         <v>94</v>
       </c>
       <c r="D83" t="n">
-        <v>5.28</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="84">
@@ -2350,7 +2323,7 @@
         <v>95</v>
       </c>
       <c r="D84" t="n">
-        <v>8.52</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="85">
@@ -2364,7 +2337,7 @@
         <v>96</v>
       </c>
       <c r="D85" t="n">
-        <v>9.25</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="86">
@@ -2378,7 +2351,7 @@
         <v>97</v>
       </c>
       <c r="D86" t="n">
-        <v>9.49</v>
+        <v>9.72</v>
       </c>
     </row>
     <row r="87">
@@ -2392,7 +2365,7 @@
         <v>98</v>
       </c>
       <c r="D87" t="n">
-        <v>9.56</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="88">
@@ -2406,7 +2379,7 @@
         <v>99</v>
       </c>
       <c r="D88" t="n">
-        <v>12.14</v>
+        <v>11.73</v>
       </c>
     </row>
     <row r="89">
@@ -2420,7 +2393,7 @@
         <v>100</v>
       </c>
       <c r="D89" t="n">
-        <v>14.01</v>
+        <v>12.16</v>
       </c>
     </row>
     <row r="90">
@@ -2434,7 +2407,7 @@
         <v>101</v>
       </c>
       <c r="D90" t="n">
-        <v>14.64</v>
+        <v>12.39</v>
       </c>
     </row>
     <row r="91">
@@ -2448,7 +2421,7 @@
         <v>102</v>
       </c>
       <c r="D91" t="n">
-        <v>18.05</v>
+        <v>14.37</v>
       </c>
     </row>
     <row r="92">
@@ -2462,7 +2435,7 @@
         <v>105</v>
       </c>
       <c r="D92" t="n">
-        <v>2.06</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="93">
@@ -2476,7 +2449,7 @@
         <v>106</v>
       </c>
       <c r="D93" t="n">
-        <v>2.11</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="94">
@@ -2490,7 +2463,7 @@
         <v>107</v>
       </c>
       <c r="D94" t="n">
-        <v>2.27</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="95">
@@ -2504,7 +2477,7 @@
         <v>108</v>
       </c>
       <c r="D95" t="n">
-        <v>2.6</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="96">
@@ -2518,7 +2491,7 @@
         <v>109</v>
       </c>
       <c r="D96" t="n">
-        <v>3.18</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="97">
@@ -2532,7 +2505,7 @@
         <v>110</v>
       </c>
       <c r="D97" t="n">
-        <v>5.5</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="98">
@@ -2546,7 +2519,7 @@
         <v>111</v>
       </c>
       <c r="D98" t="n">
-        <v>6.11</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="99">
@@ -2560,7 +2533,7 @@
         <v>112</v>
       </c>
       <c r="D99" t="n">
-        <v>7.09</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="100">
@@ -2574,7 +2547,7 @@
         <v>113</v>
       </c>
       <c r="D100" t="n">
-        <v>7.49</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="101">
@@ -2588,7 +2561,7 @@
         <v>114</v>
       </c>
       <c r="D101" t="n">
-        <v>8.89</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="102">
@@ -2602,7 +2575,7 @@
         <v>115</v>
       </c>
       <c r="D102" t="n">
-        <v>9.28</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="103">
@@ -2616,7 +2589,7 @@
         <v>116</v>
       </c>
       <c r="D103" t="n">
-        <v>10.63</v>
+        <v>11.01</v>
       </c>
     </row>
     <row r="104">
@@ -2624,13 +2597,13 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="C104" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D104" t="n">
-        <v>10.67</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="105">
@@ -2638,13 +2611,13 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="C105" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D105" t="n">
-        <v>15.64</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="106">
@@ -2652,13 +2625,13 @@
         <v>103</v>
       </c>
       <c r="B106" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="C106" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D106" t="n">
-        <v>16.63</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="107">
@@ -2666,13 +2639,13 @@
         <v>103</v>
       </c>
       <c r="B107" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="C107" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D107" t="n">
-        <v>16.85</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="108">
@@ -2680,13 +2653,13 @@
         <v>103</v>
       </c>
       <c r="B108" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="C108" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D108" t="n">
-        <v>17.27</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="109">
@@ -2694,13 +2667,13 @@
         <v>103</v>
       </c>
       <c r="B109" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="C109" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D109" t="n">
-        <v>17.68</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="110">
@@ -2708,13 +2681,13 @@
         <v>103</v>
       </c>
       <c r="B110" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C110" t="s">
         <v>124</v>
       </c>
       <c r="D110" t="n">
-        <v>2.11</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="111">
@@ -2722,13 +2695,13 @@
         <v>103</v>
       </c>
       <c r="B111" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C111" t="s">
         <v>125</v>
       </c>
       <c r="D111" t="n">
-        <v>2.18</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="112">
@@ -2736,13 +2709,13 @@
         <v>103</v>
       </c>
       <c r="B112" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C112" t="s">
         <v>126</v>
       </c>
       <c r="D112" t="n">
-        <v>2.4</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="113">
@@ -2750,13 +2723,13 @@
         <v>103</v>
       </c>
       <c r="B113" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C113" t="s">
         <v>127</v>
       </c>
       <c r="D113" t="n">
-        <v>2.65</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="114">
@@ -2764,13 +2737,13 @@
         <v>103</v>
       </c>
       <c r="B114" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C114" t="s">
         <v>128</v>
       </c>
       <c r="D114" t="n">
-        <v>2.94</v>
+        <v>7.56</v>
       </c>
     </row>
     <row r="115">
@@ -2778,13 +2751,13 @@
         <v>103</v>
       </c>
       <c r="B115" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C115" t="s">
         <v>129</v>
       </c>
       <c r="D115" t="n">
-        <v>3.41</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="116">
@@ -2792,13 +2765,13 @@
         <v>103</v>
       </c>
       <c r="B116" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C116" t="s">
         <v>130</v>
       </c>
       <c r="D116" t="n">
-        <v>4.02</v>
+        <v>9.22</v>
       </c>
     </row>
     <row r="117">
@@ -2806,13 +2779,13 @@
         <v>103</v>
       </c>
       <c r="B117" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C117" t="s">
         <v>131</v>
       </c>
       <c r="D117" t="n">
-        <v>4.19</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="118">
@@ -2820,13 +2793,13 @@
         <v>103</v>
       </c>
       <c r="B118" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C118" t="s">
         <v>132</v>
       </c>
       <c r="D118" t="n">
-        <v>7.22</v>
+        <v>12.17</v>
       </c>
     </row>
     <row r="119">
@@ -2834,13 +2807,13 @@
         <v>103</v>
       </c>
       <c r="B119" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C119" t="s">
         <v>133</v>
       </c>
       <c r="D119" t="n">
-        <v>7.65</v>
+        <v>12.57</v>
       </c>
     </row>
     <row r="120">
@@ -2848,13 +2821,13 @@
         <v>103</v>
       </c>
       <c r="B120" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C120" t="s">
         <v>134</v>
       </c>
       <c r="D120" t="n">
-        <v>8.87</v>
+        <v>12.91</v>
       </c>
     </row>
     <row r="121">
@@ -2862,13 +2835,13 @@
         <v>103</v>
       </c>
       <c r="B121" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C121" t="s">
         <v>135</v>
       </c>
       <c r="D121" t="n">
-        <v>16.24</v>
+        <v>17.91</v>
       </c>
     </row>
     <row r="122">
@@ -2882,7 +2855,7 @@
         <v>138</v>
       </c>
       <c r="D122" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="123">
@@ -2896,7 +2869,7 @@
         <v>139</v>
       </c>
       <c r="D123" t="n">
-        <v>2.52</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="124">
@@ -2910,7 +2883,7 @@
         <v>140</v>
       </c>
       <c r="D124" t="n">
-        <v>2.94</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="125">
@@ -2924,7 +2897,7 @@
         <v>141</v>
       </c>
       <c r="D125" t="n">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="126">
@@ -2938,7 +2911,7 @@
         <v>142</v>
       </c>
       <c r="D126" t="n">
-        <v>3.42</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="127">
@@ -2952,7 +2925,7 @@
         <v>143</v>
       </c>
       <c r="D127" t="n">
-        <v>3.88</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="128">
@@ -2966,7 +2939,7 @@
         <v>144</v>
       </c>
       <c r="D128" t="n">
-        <v>4.08</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="129">
@@ -2980,7 +2953,7 @@
         <v>145</v>
       </c>
       <c r="D129" t="n">
-        <v>4.67</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="130">
@@ -2994,7 +2967,7 @@
         <v>146</v>
       </c>
       <c r="D130" t="n">
-        <v>5.02</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="131">
@@ -3008,7 +2981,7 @@
         <v>147</v>
       </c>
       <c r="D131" t="n">
-        <v>10.62</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="132">
@@ -3022,7 +2995,7 @@
         <v>148</v>
       </c>
       <c r="D132" t="n">
-        <v>10.74</v>
+        <v>9.14</v>
       </c>
     </row>
     <row r="133">
@@ -3036,7 +3009,7 @@
         <v>149</v>
       </c>
       <c r="D133" t="n">
-        <v>10.75</v>
+        <v>13.68</v>
       </c>
     </row>
     <row r="134">
@@ -3050,7 +3023,7 @@
         <v>150</v>
       </c>
       <c r="D134" t="n">
-        <v>11.23</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="135">
@@ -3064,7 +3037,7 @@
         <v>151</v>
       </c>
       <c r="D135" t="n">
-        <v>12.99</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="136">
@@ -3072,13 +3045,13 @@
         <v>136</v>
       </c>
       <c r="B136" t="s">
+        <v>137</v>
+      </c>
+      <c r="C136" t="s">
         <v>152</v>
       </c>
-      <c r="C136" t="s">
-        <v>153</v>
-      </c>
       <c r="D136" t="n">
-        <v>1.63</v>
+        <v>21.03</v>
       </c>
     </row>
     <row r="137">
@@ -3086,13 +3059,13 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C137" t="s">
         <v>154</v>
       </c>
       <c r="D137" t="n">
-        <v>2.14</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="138">
@@ -3100,13 +3073,13 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C138" t="s">
         <v>155</v>
       </c>
       <c r="D138" t="n">
-        <v>3.19</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="139">
@@ -3114,13 +3087,13 @@
         <v>136</v>
       </c>
       <c r="B139" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C139" t="s">
         <v>156</v>
       </c>
       <c r="D139" t="n">
-        <v>3.67</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="140">
@@ -3128,13 +3101,13 @@
         <v>136</v>
       </c>
       <c r="B140" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C140" t="s">
         <v>157</v>
       </c>
       <c r="D140" t="n">
-        <v>3.9</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="141">
@@ -3142,13 +3115,13 @@
         <v>136</v>
       </c>
       <c r="B141" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C141" t="s">
         <v>158</v>
       </c>
       <c r="D141" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="142">
@@ -3156,13 +3129,13 @@
         <v>136</v>
       </c>
       <c r="B142" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C142" t="s">
         <v>159</v>
       </c>
       <c r="D142" t="n">
-        <v>5.22</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="143">
@@ -3170,13 +3143,13 @@
         <v>136</v>
       </c>
       <c r="B143" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C143" t="s">
         <v>160</v>
       </c>
       <c r="D143" t="n">
-        <v>5.74</v>
+        <v>4</v>
       </c>
     </row>
     <row r="144">
@@ -3184,13 +3157,13 @@
         <v>136</v>
       </c>
       <c r="B144" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C144" t="s">
         <v>161</v>
       </c>
       <c r="D144" t="n">
-        <v>6.64</v>
+        <v>4</v>
       </c>
     </row>
     <row r="145">
@@ -3198,13 +3171,13 @@
         <v>136</v>
       </c>
       <c r="B145" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C145" t="s">
         <v>162</v>
       </c>
       <c r="D145" t="n">
-        <v>9.21</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="146">
@@ -3212,13 +3185,13 @@
         <v>136</v>
       </c>
       <c r="B146" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C146" t="s">
         <v>163</v>
       </c>
       <c r="D146" t="n">
-        <v>9.72</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="147">
@@ -3226,13 +3199,13 @@
         <v>136</v>
       </c>
       <c r="B147" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C147" t="s">
         <v>164</v>
       </c>
       <c r="D147" t="n">
-        <v>11.19</v>
+        <v>9.86</v>
       </c>
     </row>
     <row r="148">
@@ -3240,13 +3213,13 @@
         <v>136</v>
       </c>
       <c r="B148" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C148" t="s">
         <v>165</v>
       </c>
       <c r="D148" t="n">
-        <v>13.22</v>
+        <v>11.74</v>
       </c>
     </row>
     <row r="149">
@@ -3254,13 +3227,13 @@
         <v>136</v>
       </c>
       <c r="B149" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C149" t="s">
         <v>166</v>
       </c>
       <c r="D149" t="n">
-        <v>13.69</v>
+        <v>12.53</v>
       </c>
     </row>
     <row r="150">
@@ -3268,13 +3241,13 @@
         <v>136</v>
       </c>
       <c r="B150" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C150" t="s">
         <v>167</v>
       </c>
       <c r="D150" t="n">
-        <v>14.43</v>
+        <v>13.15</v>
       </c>
     </row>
     <row r="151">
@@ -3282,13 +3255,13 @@
         <v>136</v>
       </c>
       <c r="B151" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C151" t="s">
         <v>168</v>
       </c>
       <c r="D151" t="n">
-        <v>15.64</v>
+        <v>13.29</v>
       </c>
     </row>
     <row r="152">
@@ -3302,7 +3275,7 @@
         <v>171</v>
       </c>
       <c r="D152" t="n">
-        <v>2.08</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="153">
@@ -3316,7 +3289,7 @@
         <v>172</v>
       </c>
       <c r="D153" t="n">
-        <v>2.17</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="154">
@@ -3330,7 +3303,7 @@
         <v>173</v>
       </c>
       <c r="D154" t="n">
-        <v>2.41</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="155">
@@ -3344,7 +3317,7 @@
         <v>174</v>
       </c>
       <c r="D155" t="n">
-        <v>2.76</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="156">
@@ -3358,7 +3331,7 @@
         <v>175</v>
       </c>
       <c r="D156" t="n">
-        <v>3.33</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="157">
@@ -3372,7 +3345,7 @@
         <v>176</v>
       </c>
       <c r="D157" t="n">
-        <v>3.73</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="158">
@@ -3386,7 +3359,7 @@
         <v>177</v>
       </c>
       <c r="D158" t="n">
-        <v>3.82</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="159">
@@ -3400,7 +3373,7 @@
         <v>178</v>
       </c>
       <c r="D159" t="n">
-        <v>4.34</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="160">
@@ -3414,7 +3387,7 @@
         <v>179</v>
       </c>
       <c r="D160" t="n">
-        <v>7.54</v>
+        <v>8.03</v>
       </c>
     </row>
     <row r="161">
@@ -3428,7 +3401,7 @@
         <v>180</v>
       </c>
       <c r="D161" t="n">
-        <v>9.08</v>
+        <v>8.17</v>
       </c>
     </row>
     <row r="162">
@@ -3442,7 +3415,7 @@
         <v>181</v>
       </c>
       <c r="D162" t="n">
-        <v>9.28</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="163">
@@ -3456,7 +3429,7 @@
         <v>182</v>
       </c>
       <c r="D163" t="n">
-        <v>13.9</v>
+        <v>10.74</v>
       </c>
     </row>
     <row r="164">
@@ -3470,7 +3443,7 @@
         <v>183</v>
       </c>
       <c r="D164" t="n">
-        <v>25.26</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="165">
@@ -3478,13 +3451,13 @@
         <v>169</v>
       </c>
       <c r="B165" t="s">
+        <v>170</v>
+      </c>
+      <c r="C165" t="s">
         <v>184</v>
       </c>
-      <c r="C165" t="s">
-        <v>185</v>
-      </c>
       <c r="D165" t="n">
-        <v>1.91</v>
+        <v>17.02</v>
       </c>
     </row>
     <row r="166">
@@ -3492,13 +3465,13 @@
         <v>169</v>
       </c>
       <c r="B166" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="C166" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D166" t="n">
-        <v>2.41</v>
+        <v>20.95</v>
       </c>
     </row>
     <row r="167">
@@ -3506,13 +3479,13 @@
         <v>169</v>
       </c>
       <c r="B167" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="C167" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D167" t="n">
-        <v>2.72</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="168">
@@ -3520,13 +3493,13 @@
         <v>169</v>
       </c>
       <c r="B168" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C168" t="s">
         <v>188</v>
       </c>
       <c r="D168" t="n">
-        <v>3.02</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="169">
@@ -3534,13 +3507,13 @@
         <v>169</v>
       </c>
       <c r="B169" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C169" t="s">
         <v>189</v>
       </c>
       <c r="D169" t="n">
-        <v>3.21</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="170">
@@ -3548,13 +3521,13 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C170" t="s">
         <v>190</v>
       </c>
       <c r="D170" t="n">
-        <v>3.42</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="171">
@@ -3562,13 +3535,13 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C171" t="s">
         <v>191</v>
       </c>
       <c r="D171" t="n">
-        <v>4.01</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="172">
@@ -3576,13 +3549,13 @@
         <v>169</v>
       </c>
       <c r="B172" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C172" t="s">
         <v>192</v>
       </c>
       <c r="D172" t="n">
-        <v>4.31</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="173">
@@ -3590,13 +3563,13 @@
         <v>169</v>
       </c>
       <c r="B173" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C173" t="s">
         <v>193</v>
       </c>
       <c r="D173" t="n">
-        <v>5.88</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="174">
@@ -3604,13 +3577,13 @@
         <v>169</v>
       </c>
       <c r="B174" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C174" t="s">
         <v>194</v>
       </c>
       <c r="D174" t="n">
-        <v>7</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="175">
@@ -3618,13 +3591,13 @@
         <v>169</v>
       </c>
       <c r="B175" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C175" t="s">
         <v>195</v>
       </c>
       <c r="D175" t="n">
-        <v>7.74</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="176">
@@ -3632,13 +3605,13 @@
         <v>169</v>
       </c>
       <c r="B176" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C176" t="s">
         <v>196</v>
       </c>
       <c r="D176" t="n">
-        <v>9.11</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="177">
@@ -3646,13 +3619,13 @@
         <v>169</v>
       </c>
       <c r="B177" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C177" t="s">
         <v>197</v>
       </c>
       <c r="D177" t="n">
-        <v>10.9</v>
+        <v>7.85</v>
       </c>
     </row>
     <row r="178">
@@ -3660,13 +3633,13 @@
         <v>169</v>
       </c>
       <c r="B178" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C178" t="s">
         <v>198</v>
       </c>
       <c r="D178" t="n">
-        <v>11.57</v>
+        <v>11.38</v>
       </c>
     </row>
     <row r="179">
@@ -3674,13 +3647,13 @@
         <v>169</v>
       </c>
       <c r="B179" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C179" t="s">
         <v>199</v>
       </c>
       <c r="D179" t="n">
-        <v>12.13</v>
+        <v>12.69</v>
       </c>
     </row>
     <row r="180">
@@ -3688,13 +3661,13 @@
         <v>169</v>
       </c>
       <c r="B180" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C180" t="s">
         <v>200</v>
       </c>
       <c r="D180" t="n">
-        <v>15.64</v>
+        <v>13.54</v>
       </c>
     </row>
     <row r="181">
@@ -3702,13 +3675,13 @@
         <v>169</v>
       </c>
       <c r="B181" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C181" t="s">
         <v>201</v>
       </c>
       <c r="D181" t="n">
-        <v>30.08</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="182">
@@ -3722,7 +3695,7 @@
         <v>204</v>
       </c>
       <c r="D182" t="n">
-        <v>3.01</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="183">
@@ -3736,7 +3709,7 @@
         <v>205</v>
       </c>
       <c r="D183" t="n">
-        <v>3.07</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="184">
@@ -3750,7 +3723,7 @@
         <v>206</v>
       </c>
       <c r="D184" t="n">
-        <v>3.27</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="185">
@@ -3764,7 +3737,7 @@
         <v>207</v>
       </c>
       <c r="D185" t="n">
-        <v>3.35</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="186">
@@ -3778,7 +3751,7 @@
         <v>208</v>
       </c>
       <c r="D186" t="n">
-        <v>3.84</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="187">
@@ -3792,7 +3765,7 @@
         <v>209</v>
       </c>
       <c r="D187" t="n">
-        <v>5.35</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="188">
@@ -3806,7 +3779,7 @@
         <v>210</v>
       </c>
       <c r="D188" t="n">
-        <v>6.06</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="189">
@@ -3820,7 +3793,7 @@
         <v>211</v>
       </c>
       <c r="D189" t="n">
-        <v>6.98</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="190">
@@ -3834,7 +3807,7 @@
         <v>212</v>
       </c>
       <c r="D190" t="n">
-        <v>7.57</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="191">
@@ -3848,7 +3821,7 @@
         <v>213</v>
       </c>
       <c r="D191" t="n">
-        <v>9.34</v>
+        <v>8.36</v>
       </c>
     </row>
     <row r="192">
@@ -3862,7 +3835,7 @@
         <v>214</v>
       </c>
       <c r="D192" t="n">
-        <v>9.82</v>
+        <v>8.87</v>
       </c>
     </row>
     <row r="193">
@@ -3876,7 +3849,7 @@
         <v>215</v>
       </c>
       <c r="D193" t="n">
-        <v>10.24</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="194">
@@ -3890,7 +3863,7 @@
         <v>216</v>
       </c>
       <c r="D194" t="n">
-        <v>12.49</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="195">
@@ -3904,7 +3877,7 @@
         <v>217</v>
       </c>
       <c r="D195" t="n">
-        <v>16.36</v>
+        <v>11.56</v>
       </c>
     </row>
     <row r="196">
@@ -3912,13 +3885,13 @@
         <v>202</v>
       </c>
       <c r="B196" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="C196" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D196" t="n">
-        <v>19.23</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="197">
@@ -3926,13 +3899,13 @@
         <v>202</v>
       </c>
       <c r="B197" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C197" t="s">
         <v>220</v>
       </c>
       <c r="D197" t="n">
-        <v>1.7</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="198">
@@ -3940,13 +3913,13 @@
         <v>202</v>
       </c>
       <c r="B198" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C198" t="s">
         <v>221</v>
       </c>
       <c r="D198" t="n">
-        <v>1.95</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="199">
@@ -3954,13 +3927,13 @@
         <v>202</v>
       </c>
       <c r="B199" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C199" t="s">
         <v>222</v>
       </c>
       <c r="D199" t="n">
-        <v>2.74</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="200">
@@ -3968,7 +3941,7 @@
         <v>202</v>
       </c>
       <c r="B200" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C200" t="s">
         <v>223</v>
@@ -3982,13 +3955,13 @@
         <v>202</v>
       </c>
       <c r="B201" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C201" t="s">
         <v>224</v>
       </c>
       <c r="D201" t="n">
-        <v>3.71</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="202">
@@ -3996,13 +3969,13 @@
         <v>202</v>
       </c>
       <c r="B202" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C202" t="s">
         <v>225</v>
       </c>
       <c r="D202" t="n">
-        <v>4.42</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="203">
@@ -4010,13 +3983,13 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C203" t="s">
         <v>226</v>
       </c>
       <c r="D203" t="n">
-        <v>4.57</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="204">
@@ -4024,13 +3997,13 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C204" t="s">
         <v>227</v>
       </c>
       <c r="D204" t="n">
-        <v>4.57</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="205">
@@ -4038,13 +4011,13 @@
         <v>202</v>
       </c>
       <c r="B205" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C205" t="s">
         <v>228</v>
       </c>
       <c r="D205" t="n">
-        <v>5.36</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="206">
@@ -4052,13 +4025,13 @@
         <v>202</v>
       </c>
       <c r="B206" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C206" t="s">
         <v>229</v>
       </c>
       <c r="D206" t="n">
-        <v>7.28</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="207">
@@ -4066,13 +4039,13 @@
         <v>202</v>
       </c>
       <c r="B207" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C207" t="s">
         <v>230</v>
       </c>
       <c r="D207" t="n">
-        <v>10.53</v>
+        <v>8.13</v>
       </c>
     </row>
     <row r="208">
@@ -4080,13 +4053,13 @@
         <v>202</v>
       </c>
       <c r="B208" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C208" t="s">
         <v>231</v>
       </c>
       <c r="D208" t="n">
-        <v>11.73</v>
+        <v>8.98</v>
       </c>
     </row>
     <row r="209">
@@ -4094,13 +4067,13 @@
         <v>202</v>
       </c>
       <c r="B209" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C209" t="s">
         <v>232</v>
       </c>
       <c r="D209" t="n">
-        <v>12.51</v>
+        <v>13.02</v>
       </c>
     </row>
     <row r="210">
@@ -4108,13 +4081,13 @@
         <v>202</v>
       </c>
       <c r="B210" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C210" t="s">
         <v>233</v>
       </c>
       <c r="D210" t="n">
-        <v>14.44</v>
+        <v>15.02</v>
       </c>
     </row>
     <row r="211">
@@ -4122,13 +4095,13 @@
         <v>202</v>
       </c>
       <c r="B211" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C211" t="s">
         <v>234</v>
       </c>
       <c r="D211" t="n">
-        <v>15.24</v>
+        <v>16.15</v>
       </c>
     </row>
     <row r="212">
@@ -4142,7 +4115,7 @@
         <v>237</v>
       </c>
       <c r="D212" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="213">
@@ -4156,7 +4129,7 @@
         <v>238</v>
       </c>
       <c r="D213" t="n">
-        <v>3.34</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="214">
@@ -4170,7 +4143,7 @@
         <v>239</v>
       </c>
       <c r="D214" t="n">
-        <v>3.57</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="215">
@@ -4184,7 +4157,7 @@
         <v>240</v>
       </c>
       <c r="D215" t="n">
-        <v>3.67</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="216">
@@ -4198,7 +4171,7 @@
         <v>241</v>
       </c>
       <c r="D216" t="n">
-        <v>3.93</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="217">
@@ -4212,7 +4185,7 @@
         <v>242</v>
       </c>
       <c r="D217" t="n">
-        <v>4.13</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="218">
@@ -4226,7 +4199,7 @@
         <v>243</v>
       </c>
       <c r="D218" t="n">
-        <v>4.16</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="219">
@@ -4240,7 +4213,7 @@
         <v>244</v>
       </c>
       <c r="D219" t="n">
-        <v>4.24</v>
+        <v>5.74</v>
       </c>
     </row>
     <row r="220">
@@ -4254,7 +4227,7 @@
         <v>245</v>
       </c>
       <c r="D220" t="n">
-        <v>4.98</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="221">
@@ -4268,7 +4241,7 @@
         <v>246</v>
       </c>
       <c r="D221" t="n">
-        <v>8.26</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="222">
@@ -4282,7 +4255,7 @@
         <v>247</v>
       </c>
       <c r="D222" t="n">
-        <v>9.34</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="223">
@@ -4296,7 +4269,7 @@
         <v>248</v>
       </c>
       <c r="D223" t="n">
-        <v>10.69</v>
+        <v>11.53</v>
       </c>
     </row>
     <row r="224">
@@ -4310,7 +4283,7 @@
         <v>249</v>
       </c>
       <c r="D224" t="n">
-        <v>10.71</v>
+        <v>12.28</v>
       </c>
     </row>
     <row r="225">
@@ -4324,7 +4297,7 @@
         <v>250</v>
       </c>
       <c r="D225" t="n">
-        <v>10.75</v>
+        <v>12.33</v>
       </c>
     </row>
     <row r="226">
@@ -4338,7 +4311,7 @@
         <v>251</v>
       </c>
       <c r="D226" t="n">
-        <v>22.22</v>
+        <v>14.79</v>
       </c>
     </row>
     <row r="227">
@@ -4346,13 +4319,13 @@
         <v>235</v>
       </c>
       <c r="B227" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="C227" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D227" t="n">
-        <v>23.26</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="228">
@@ -4360,13 +4333,13 @@
         <v>235</v>
       </c>
       <c r="B228" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="C228" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D228" t="n">
-        <v>36.86</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="229">
@@ -4374,13 +4347,13 @@
         <v>235</v>
       </c>
       <c r="B229" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="C229" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D229" t="n">
-        <v>41.38</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="230">
@@ -4388,279 +4361,167 @@
         <v>235</v>
       </c>
       <c r="B230" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="C230" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D230" t="n">
-        <v>52.38</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="B231" t="s">
+        <v>252</v>
+      </c>
+      <c r="C231" t="s">
         <v>257</v>
       </c>
-      <c r="C231" t="s">
-        <v>258</v>
-      </c>
       <c r="D231" t="n">
-        <v>2.38</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="B232" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D232" t="n">
-        <v>2.65</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="B233" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C233" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D233" t="n">
-        <v>2.84</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="B234" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C234" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D234" t="n">
-        <v>3.05</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="B235" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C235" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D235" t="n">
-        <v>4.27</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C236" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D236" t="n">
-        <v>4.58</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C237" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D237" t="n">
-        <v>5.1</v>
+        <v>10.54</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="B238" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C238" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D238" t="n">
-        <v>5.11</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="B239" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C239" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D239" t="n">
-        <v>5.13</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="B240" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C240" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D240" t="n">
-        <v>5.22</v>
+        <v>16.49</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="B241" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C241" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D241" t="n">
-        <v>6.59</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="s">
-        <v>256</v>
-      </c>
-      <c r="B242" t="s">
-        <v>257</v>
-      </c>
-      <c r="C242" t="s">
-        <v>269</v>
-      </c>
-      <c r="D242" t="n">
-        <v>9.65</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="s">
-        <v>256</v>
-      </c>
-      <c r="B243" t="s">
-        <v>257</v>
-      </c>
-      <c r="C243" t="s">
-        <v>270</v>
-      </c>
-      <c r="D243" t="n">
-        <v>11.59</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="s">
-        <v>256</v>
-      </c>
-      <c r="B244" t="s">
-        <v>257</v>
-      </c>
-      <c r="C244" t="s">
-        <v>271</v>
-      </c>
-      <c r="D244" t="n">
-        <v>24.04</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="s">
-        <v>256</v>
-      </c>
-      <c r="B245" t="s">
-        <v>257</v>
-      </c>
-      <c r="C245" t="s">
-        <v>272</v>
-      </c>
-      <c r="D245" t="n">
-        <v>27.34</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="s">
-        <v>256</v>
-      </c>
-      <c r="B246" t="s">
-        <v>257</v>
-      </c>
-      <c r="C246" t="s">
-        <v>273</v>
-      </c>
-      <c r="D246" t="n">
-        <v>30.24</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="s">
-        <v>256</v>
-      </c>
-      <c r="B247" t="s">
-        <v>257</v>
-      </c>
-      <c r="C247" t="s">
-        <v>274</v>
-      </c>
-      <c r="D247" t="n">
-        <v>35.19</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="s">
-        <v>256</v>
-      </c>
-      <c r="B248" t="s">
-        <v>257</v>
-      </c>
-      <c r="C248" t="s">
-        <v>275</v>
-      </c>
-      <c r="D248" t="n">
-        <v>38.91</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="s">
-        <v>256</v>
-      </c>
-      <c r="B249" t="s">
-        <v>257</v>
-      </c>
-      <c r="C249" t="s">
-        <v>276</v>
-      </c>
-      <c r="D249" t="n">
-        <v>40.15</v>
+        <v>19.04</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_anytime_tryscorers.xlsx
+++ b/files/NRL_anytime_tryscorers.xlsx
@@ -50,12 +50,12 @@
     <t xml:space="preserve">Liam Martin</t>
   </si>
   <si>
+    <t xml:space="preserve">Nathan Cleary</t>
+  </si>
+  <si>
     <t xml:space="preserve">Paul Alamoti</t>
   </si>
   <si>
-    <t xml:space="preserve">Nathan Cleary</t>
-  </si>
-  <si>
     <t xml:space="preserve">Freddy Lussick</t>
   </si>
   <si>
@@ -71,6 +71,9 @@
     <t xml:space="preserve">Moses Leota</t>
   </si>
   <si>
+    <t xml:space="preserve">Scott Sorensen</t>
+  </si>
+  <si>
     <t xml:space="preserve">sydney roosters</t>
   </si>
   <si>
@@ -80,15 +83,15 @@
     <t xml:space="preserve">Billy Smith</t>
   </si>
   <si>
-    <t xml:space="preserve">James Tedesco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hugo Savala</t>
   </si>
   <si>
     <t xml:space="preserve">Robert Toia</t>
   </si>
   <si>
+    <t xml:space="preserve">Cody Ramsey</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sam Walker</t>
   </si>
   <si>
@@ -119,9 +122,6 @@
     <t xml:space="preserve">Lindsay Collins</t>
   </si>
   <si>
-    <t xml:space="preserve">Cody Ramsey</t>
-  </si>
-  <si>
     <t xml:space="preserve">Spencer Leniu</t>
   </si>
   <si>
@@ -176,12 +176,12 @@
     <t xml:space="preserve">Morgan Knowles</t>
   </si>
   <si>
+    <t xml:space="preserve">Francis Molo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tom Gilbert</t>
   </si>
   <si>
-    <t xml:space="preserve">Francis Molo</t>
-  </si>
-  <si>
     <t xml:space="preserve">manly-warringah sea eagles</t>
   </si>
   <si>
@@ -209,12 +209,12 @@
     <t xml:space="preserve">Corey Waddell</t>
   </si>
   <si>
+    <t xml:space="preserve">Brandon Wakeham</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jamal Fogarty</t>
   </si>
   <si>
-    <t xml:space="preserve">Brandon Wakeham</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nathan Brown</t>
   </si>
   <si>
@@ -245,27 +245,27 @@
     <t xml:space="preserve">Connor Tracey</t>
   </si>
   <si>
+    <t xml:space="preserve">Viliame Kikau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Preston</t>
+  </si>
+  <si>
     <t xml:space="preserve">Enari Tuala</t>
   </si>
   <si>
-    <t xml:space="preserve">Viliame Kikau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Preston</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lachlan Galvin</t>
   </si>
   <si>
+    <t xml:space="preserve">Jonathan Sua</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kurt Mann</t>
   </si>
   <si>
     <t xml:space="preserve">Jaeman Salmon</t>
   </si>
   <si>
-    <t xml:space="preserve">Jonathan Sua</t>
-  </si>
-  <si>
     <t xml:space="preserve">Josh Curran</t>
   </si>
   <si>
@@ -305,18 +305,18 @@
     <t xml:space="preserve">Keaon Koloamatangi</t>
   </si>
   <si>
+    <t xml:space="preserve">Brandon Smith</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jayden Sullivan</t>
   </si>
   <si>
-    <t xml:space="preserve">Brandon Smith</t>
+    <t xml:space="preserve">Tevita Tatola</t>
   </si>
   <si>
     <t xml:space="preserve">John Radel</t>
   </si>
   <si>
-    <t xml:space="preserve">Tevita Tatola</t>
-  </si>
-  <si>
     <t xml:space="preserve">Euan Aitken</t>
   </si>
   <si>
@@ -377,12 +377,12 @@
     <t xml:space="preserve">William Kennedy</t>
   </si>
   <si>
+    <t xml:space="preserve">Kayal Iro</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mawene Hiroti</t>
   </si>
   <si>
-    <t xml:space="preserve">Kayal Iro</t>
-  </si>
-  <si>
     <t xml:space="preserve">Braydon Trindall</t>
   </si>
   <si>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">Oregon Kaufusi</t>
   </si>
   <si>
-    <t xml:space="preserve">Niwhai Puru</t>
+    <t xml:space="preserve">Billy Burns</t>
   </si>
   <si>
     <t xml:space="preserve">north queensland cowboys at parramatta eels</t>
@@ -443,15 +443,15 @@
     <t xml:space="preserve">Zac Laybutt</t>
   </si>
   <si>
+    <t xml:space="preserve">Jake Clifford</t>
+  </si>
+  <si>
     <t xml:space="preserve">Heilum Luki</t>
   </si>
   <si>
     <t xml:space="preserve">Kai O'Donnell</t>
   </si>
   <si>
-    <t xml:space="preserve">Jake Clifford</t>
-  </si>
-  <si>
     <t xml:space="preserve">Reed Mahoney</t>
   </si>
   <si>
@@ -470,9 +470,6 @@
     <t xml:space="preserve">Griffin Neame</t>
   </si>
   <si>
-    <t xml:space="preserve">Liam Sutton</t>
-  </si>
-  <si>
     <t xml:space="preserve">parramatta eels</t>
   </si>
   <si>
@@ -485,12 +482,12 @@
     <t xml:space="preserve">Brian Kelly</t>
   </si>
   <si>
+    <t xml:space="preserve">Jordan Samrani</t>
+  </si>
+  <si>
     <t xml:space="preserve">Will Penisini</t>
   </si>
   <si>
-    <t xml:space="preserve">Jordan Samrani</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mitchell Moses</t>
   </si>
   <si>
@@ -500,12 +497,12 @@
     <t xml:space="preserve">Kitione Kautoga</t>
   </si>
   <si>
+    <t xml:space="preserve">Ronald Volkman</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tallyn Da Silva</t>
   </si>
   <si>
-    <t xml:space="preserve">Ronald Volkman</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jack De Belin</t>
   </si>
   <si>
@@ -521,6 +518,9 @@
     <t xml:space="preserve">Junior Paulo</t>
   </si>
   <si>
+    <t xml:space="preserve">Jezaiah Funa-Iuta</t>
+  </si>
+  <si>
     <t xml:space="preserve">warriors at brisbane broncos</t>
   </si>
   <si>
@@ -533,12 +533,12 @@
     <t xml:space="preserve">Josiah Karapani</t>
   </si>
   <si>
+    <t xml:space="preserve">Ezra Mam</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reece Walsh</t>
   </si>
   <si>
-    <t xml:space="preserve">Ezra Mam</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kotoni Staggs</t>
   </si>
   <si>
@@ -557,12 +557,12 @@
     <t xml:space="preserve">Thomas Duffy</t>
   </si>
   <si>
+    <t xml:space="preserve">Xavier Willison</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ben Talty</t>
   </si>
   <si>
-    <t xml:space="preserve">Xavier Willison</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gehamat Shibasaki</t>
   </si>
   <si>
@@ -584,12 +584,12 @@
     <t xml:space="preserve">Dallin Watene-Zelezniak</t>
   </si>
   <si>
+    <t xml:space="preserve">Luke Metcalf</t>
+  </si>
+  <si>
     <t xml:space="preserve">Leka Halasima</t>
   </si>
   <si>
-    <t xml:space="preserve">Luke Metcalf</t>
-  </si>
-  <si>
     <t xml:space="preserve">Charnze Nicoll-Klokstad</t>
   </si>
   <si>
@@ -611,12 +611,12 @@
     <t xml:space="preserve">James Fisher-Harris</t>
   </si>
   <si>
+    <t xml:space="preserve">Erin Clark</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sam Healey</t>
   </si>
   <si>
-    <t xml:space="preserve">Erin Clark</t>
-  </si>
-  <si>
     <t xml:space="preserve">Eddie Ieremia-Toeava</t>
   </si>
   <si>
@@ -731,12 +731,12 @@
     <t xml:space="preserve">Setu Tu</t>
   </si>
   <si>
+    <t xml:space="preserve">Valentine Holmes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Clinton Gutherson</t>
   </si>
   <si>
-    <t xml:space="preserve">Valentine Holmes</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dylan Egan</t>
   </si>
   <si>
@@ -761,10 +761,10 @@
     <t xml:space="preserve">Toby Couchman</t>
   </si>
   <si>
+    <t xml:space="preserve">Emre Guler</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ryan Couchman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emre Guler</t>
   </si>
   <si>
     <t xml:space="preserve">Daniel Atkinson</t>
@@ -1175,7 +1175,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="3">
@@ -1189,7 +1189,7 @@
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="4">
@@ -1203,7 +1203,7 @@
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="5">
@@ -1217,7 +1217,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>3.46</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="6">
@@ -1231,7 +1231,7 @@
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>4.77</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="7">
@@ -1245,7 +1245,7 @@
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>4.77</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="8">
@@ -1259,7 +1259,7 @@
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>4.78</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="9">
@@ -1273,7 +1273,7 @@
         <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>4.89</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="10">
@@ -1287,7 +1287,7 @@
         <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>8.06</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="11">
@@ -1301,7 +1301,7 @@
         <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>8.81</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="12">
@@ -1315,7 +1315,7 @@
         <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>11.87</v>
+        <v>11.39</v>
       </c>
     </row>
     <row r="13">
@@ -1329,7 +1329,7 @@
         <v>17</v>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>11.67</v>
       </c>
     </row>
     <row r="14">
@@ -1343,7 +1343,7 @@
         <v>18</v>
       </c>
       <c r="D14" t="n">
-        <v>18.72</v>
+        <v>18.09</v>
       </c>
     </row>
     <row r="15">
@@ -1351,13 +1351,13 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" t="s">
         <v>19</v>
       </c>
-      <c r="C15" t="s">
-        <v>20</v>
-      </c>
       <c r="D15" t="n">
-        <v>1.92</v>
+        <v>19.55</v>
       </c>
     </row>
     <row r="16">
@@ -1365,13 +1365,13 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" t="s">
         <v>21</v>
       </c>
       <c r="D16" t="n">
-        <v>2.85</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="17">
@@ -1379,13 +1379,13 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" t="s">
         <v>22</v>
       </c>
       <c r="D17" t="n">
-        <v>2.87</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="18">
@@ -1393,13 +1393,13 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
       </c>
       <c r="D18" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1407,13 +1407,13 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C19" t="s">
         <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>3.63</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="20">
@@ -1421,13 +1421,13 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C20" t="s">
         <v>25</v>
       </c>
       <c r="D20" t="n">
-        <v>4.79</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="21">
@@ -1435,13 +1435,13 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C21" t="s">
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>5.14</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="22">
@@ -1449,13 +1449,13 @@
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C22" t="s">
         <v>27</v>
       </c>
       <c r="D22" t="n">
-        <v>5.14</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="23">
@@ -1463,13 +1463,13 @@
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C23" t="s">
         <v>28</v>
       </c>
       <c r="D23" t="n">
-        <v>5.24</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="24">
@@ -1477,13 +1477,13 @@
         <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C24" t="s">
         <v>29</v>
       </c>
       <c r="D24" t="n">
-        <v>9.33</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="25">
@@ -1491,13 +1491,13 @@
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C25" t="s">
         <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>9.57</v>
+        <v>8.95</v>
       </c>
     </row>
     <row r="26">
@@ -1505,13 +1505,13 @@
         <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C26" t="s">
         <v>31</v>
       </c>
       <c r="D26" t="n">
-        <v>12.22</v>
+        <v>9.23</v>
       </c>
     </row>
     <row r="27">
@@ -1519,13 +1519,13 @@
         <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C27" t="s">
         <v>32</v>
       </c>
       <c r="D27" t="n">
-        <v>12.25</v>
+        <v>11.65</v>
       </c>
     </row>
     <row r="28">
@@ -1533,13 +1533,13 @@
         <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C28" t="s">
         <v>33</v>
       </c>
       <c r="D28" t="n">
-        <v>14.77</v>
+        <v>11.86</v>
       </c>
     </row>
     <row r="29">
@@ -1547,13 +1547,13 @@
         <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C29" t="s">
         <v>34</v>
       </c>
       <c r="D29" t="n">
-        <v>16.67</v>
+        <v>14.28</v>
       </c>
     </row>
     <row r="30">
@@ -1561,13 +1561,13 @@
         <v>4</v>
       </c>
       <c r="B30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C30" t="s">
         <v>35</v>
       </c>
       <c r="D30" t="n">
-        <v>18.21</v>
+        <v>16.63</v>
       </c>
     </row>
     <row r="31">
@@ -1575,13 +1575,13 @@
         <v>4</v>
       </c>
       <c r="B31" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C31" t="s">
         <v>36</v>
       </c>
       <c r="D31" t="n">
-        <v>18.77</v>
+        <v>17.86</v>
       </c>
     </row>
     <row r="32">
@@ -1595,7 +1595,7 @@
         <v>39</v>
       </c>
       <c r="D32" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="33">
@@ -1609,7 +1609,7 @@
         <v>40</v>
       </c>
       <c r="D33" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="34">
@@ -1623,7 +1623,7 @@
         <v>41</v>
       </c>
       <c r="D34" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="35">
@@ -1637,7 +1637,7 @@
         <v>42</v>
       </c>
       <c r="D35" t="n">
-        <v>2.69</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="36">
@@ -1651,7 +1651,7 @@
         <v>43</v>
       </c>
       <c r="D36" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="37">
@@ -1665,7 +1665,7 @@
         <v>44</v>
       </c>
       <c r="D37" t="n">
-        <v>4.56</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="38">
@@ -1679,7 +1679,7 @@
         <v>45</v>
       </c>
       <c r="D38" t="n">
-        <v>4.56</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="39">
@@ -1693,7 +1693,7 @@
         <v>46</v>
       </c>
       <c r="D39" t="n">
-        <v>5.71</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="40">
@@ -1707,7 +1707,7 @@
         <v>47</v>
       </c>
       <c r="D40" t="n">
-        <v>7.37</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="41">
@@ -1721,7 +1721,7 @@
         <v>48</v>
       </c>
       <c r="D41" t="n">
-        <v>9.25</v>
+        <v>8.88</v>
       </c>
     </row>
     <row r="42">
@@ -1735,7 +1735,7 @@
         <v>49</v>
       </c>
       <c r="D42" t="n">
-        <v>9.66</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="43">
@@ -1749,7 +1749,7 @@
         <v>50</v>
       </c>
       <c r="D43" t="n">
-        <v>11.06</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="44">
@@ -1763,7 +1763,7 @@
         <v>51</v>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.07</v>
       </c>
     </row>
     <row r="45">
@@ -1777,7 +1777,7 @@
         <v>52</v>
       </c>
       <c r="D45" t="n">
-        <v>17.31</v>
+        <v>17.27</v>
       </c>
     </row>
     <row r="46">
@@ -1791,7 +1791,7 @@
         <v>53</v>
       </c>
       <c r="D46" t="n">
-        <v>17.55</v>
+        <v>17.37</v>
       </c>
     </row>
     <row r="47">
@@ -1805,7 +1805,7 @@
         <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>17.99</v>
+        <v>17.83</v>
       </c>
     </row>
     <row r="48">
@@ -1819,7 +1819,7 @@
         <v>55</v>
       </c>
       <c r="D48" t="n">
-        <v>18.41</v>
+        <v>17.91</v>
       </c>
     </row>
     <row r="49">
@@ -1833,7 +1833,7 @@
         <v>57</v>
       </c>
       <c r="D49" t="n">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="50">
@@ -1847,7 +1847,7 @@
         <v>58</v>
       </c>
       <c r="D50" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="51">
@@ -1861,7 +1861,7 @@
         <v>59</v>
       </c>
       <c r="D51" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="52">
@@ -1875,7 +1875,7 @@
         <v>60</v>
       </c>
       <c r="D52" t="n">
-        <v>2.77</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="53">
@@ -1889,7 +1889,7 @@
         <v>61</v>
       </c>
       <c r="D53" t="n">
-        <v>2.91</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="54">
@@ -1903,7 +1903,7 @@
         <v>62</v>
       </c>
       <c r="D54" t="n">
-        <v>3.77</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="55">
@@ -1917,7 +1917,7 @@
         <v>63</v>
       </c>
       <c r="D55" t="n">
-        <v>4.26</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="56">
@@ -1931,7 +1931,7 @@
         <v>64</v>
       </c>
       <c r="D56" t="n">
-        <v>4.26</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="57">
@@ -1945,7 +1945,7 @@
         <v>65</v>
       </c>
       <c r="D57" t="n">
-        <v>8.06</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="58">
@@ -1959,7 +1959,7 @@
         <v>66</v>
       </c>
       <c r="D58" t="n">
-        <v>8.71</v>
+        <v>7.53</v>
       </c>
     </row>
     <row r="59">
@@ -1973,7 +1973,7 @@
         <v>67</v>
       </c>
       <c r="D59" t="n">
-        <v>14.17</v>
+        <v>13.11</v>
       </c>
     </row>
     <row r="60">
@@ -1987,7 +1987,7 @@
         <v>68</v>
       </c>
       <c r="D60" t="n">
-        <v>15.43</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="61">
@@ -2001,7 +2001,7 @@
         <v>69</v>
       </c>
       <c r="D61" t="n">
-        <v>18.22</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="62">
@@ -2015,7 +2015,7 @@
         <v>72</v>
       </c>
       <c r="D62" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="63">
@@ -2029,7 +2029,7 @@
         <v>73</v>
       </c>
       <c r="D63" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="64">
@@ -2043,7 +2043,7 @@
         <v>74</v>
       </c>
       <c r="D64" t="n">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="65">
@@ -2057,7 +2057,7 @@
         <v>75</v>
       </c>
       <c r="D65" t="n">
-        <v>3.53</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="66">
@@ -2071,7 +2071,7 @@
         <v>76</v>
       </c>
       <c r="D66" t="n">
-        <v>4.13</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="67">
@@ -2085,7 +2085,7 @@
         <v>77</v>
       </c>
       <c r="D67" t="n">
-        <v>4.35</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="68">
@@ -2099,7 +2099,7 @@
         <v>78</v>
       </c>
       <c r="D68" t="n">
-        <v>4.42</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="69">
@@ -2113,7 +2113,7 @@
         <v>79</v>
       </c>
       <c r="D69" t="n">
-        <v>4.42</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="70">
@@ -2127,7 +2127,7 @@
         <v>80</v>
       </c>
       <c r="D70" t="n">
-        <v>5.36</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71">
@@ -2141,7 +2141,7 @@
         <v>81</v>
       </c>
       <c r="D71" t="n">
-        <v>11.39</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="72">
@@ -2155,7 +2155,7 @@
         <v>82</v>
       </c>
       <c r="D72" t="n">
-        <v>11.52</v>
+        <v>11.21</v>
       </c>
     </row>
     <row r="73">
@@ -2169,7 +2169,7 @@
         <v>83</v>
       </c>
       <c r="D73" t="n">
-        <v>11.53</v>
+        <v>11.38</v>
       </c>
     </row>
     <row r="74">
@@ -2183,7 +2183,7 @@
         <v>84</v>
       </c>
       <c r="D74" t="n">
-        <v>12.05</v>
+        <v>11.84</v>
       </c>
     </row>
     <row r="75">
@@ -2197,7 +2197,7 @@
         <v>85</v>
       </c>
       <c r="D75" t="n">
-        <v>13.94</v>
+        <v>13.86</v>
       </c>
     </row>
     <row r="76">
@@ -2211,7 +2211,7 @@
         <v>87</v>
       </c>
       <c r="D76" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="77">
@@ -2225,7 +2225,7 @@
         <v>88</v>
       </c>
       <c r="D77" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="78">
@@ -2239,7 +2239,7 @@
         <v>89</v>
       </c>
       <c r="D78" t="n">
-        <v>2.76</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="79">
@@ -2253,7 +2253,7 @@
         <v>90</v>
       </c>
       <c r="D79" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="80">
@@ -2267,7 +2267,7 @@
         <v>91</v>
       </c>
       <c r="D80" t="n">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="81">
@@ -2281,7 +2281,7 @@
         <v>92</v>
       </c>
       <c r="D81" t="n">
-        <v>4.25</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="82">
@@ -2295,7 +2295,7 @@
         <v>93</v>
       </c>
       <c r="D82" t="n">
-        <v>4.49</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="83">
@@ -2309,7 +2309,7 @@
         <v>94</v>
       </c>
       <c r="D83" t="n">
-        <v>4.49</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="84">
@@ -2323,7 +2323,7 @@
         <v>95</v>
       </c>
       <c r="D84" t="n">
-        <v>7.26</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="85">
@@ -2337,7 +2337,7 @@
         <v>96</v>
       </c>
       <c r="D85" t="n">
-        <v>7.39</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="86">
@@ -2351,7 +2351,7 @@
         <v>97</v>
       </c>
       <c r="D86" t="n">
-        <v>9.72</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="87">
@@ -2365,7 +2365,7 @@
         <v>98</v>
       </c>
       <c r="D87" t="n">
-        <v>9.99</v>
+        <v>9.56</v>
       </c>
     </row>
     <row r="88">
@@ -2379,7 +2379,7 @@
         <v>99</v>
       </c>
       <c r="D88" t="n">
-        <v>11.73</v>
+        <v>10.84</v>
       </c>
     </row>
     <row r="89">
@@ -2393,7 +2393,7 @@
         <v>100</v>
       </c>
       <c r="D89" t="n">
-        <v>12.16</v>
+        <v>11.58</v>
       </c>
     </row>
     <row r="90">
@@ -2407,7 +2407,7 @@
         <v>101</v>
       </c>
       <c r="D90" t="n">
-        <v>12.39</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="91">
@@ -2421,7 +2421,7 @@
         <v>102</v>
       </c>
       <c r="D91" t="n">
-        <v>14.37</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="92">
@@ -2449,7 +2449,7 @@
         <v>106</v>
       </c>
       <c r="D93" t="n">
-        <v>3.46</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="94">
@@ -2463,7 +2463,7 @@
         <v>107</v>
       </c>
       <c r="D94" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="95">
@@ -2477,7 +2477,7 @@
         <v>108</v>
       </c>
       <c r="D95" t="n">
-        <v>4.24</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="96">
@@ -2505,7 +2505,7 @@
         <v>110</v>
       </c>
       <c r="D97" t="n">
-        <v>4.94</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="98">
@@ -2519,7 +2519,7 @@
         <v>111</v>
       </c>
       <c r="D98" t="n">
-        <v>5.11</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="99">
@@ -2533,7 +2533,7 @@
         <v>112</v>
       </c>
       <c r="D99" t="n">
-        <v>5.11</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="100">
@@ -2547,7 +2547,7 @@
         <v>113</v>
       </c>
       <c r="D100" t="n">
-        <v>7.17</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="101">
@@ -2561,7 +2561,7 @@
         <v>114</v>
       </c>
       <c r="D101" t="n">
-        <v>8.48</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="102">
@@ -2575,7 +2575,7 @@
         <v>115</v>
       </c>
       <c r="D102" t="n">
-        <v>10.14</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="103">
@@ -2589,7 +2589,7 @@
         <v>116</v>
       </c>
       <c r="D103" t="n">
-        <v>11.01</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="104">
@@ -2603,7 +2603,7 @@
         <v>118</v>
       </c>
       <c r="D104" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="105">
@@ -2617,7 +2617,7 @@
         <v>119</v>
       </c>
       <c r="D105" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="106">
@@ -2631,7 +2631,7 @@
         <v>120</v>
       </c>
       <c r="D106" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="107">
@@ -2673,7 +2673,7 @@
         <v>123</v>
       </c>
       <c r="D109" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="110">
@@ -2687,7 +2687,7 @@
         <v>124</v>
       </c>
       <c r="D110" t="n">
-        <v>3.62</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="111">
@@ -2701,7 +2701,7 @@
         <v>125</v>
       </c>
       <c r="D111" t="n">
-        <v>3.62</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="112">
@@ -2715,7 +2715,7 @@
         <v>126</v>
       </c>
       <c r="D112" t="n">
-        <v>4.08</v>
+        <v>4</v>
       </c>
     </row>
     <row r="113">
@@ -2729,7 +2729,7 @@
         <v>127</v>
       </c>
       <c r="D113" t="n">
-        <v>7.11</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="114">
@@ -2743,7 +2743,7 @@
         <v>128</v>
       </c>
       <c r="D114" t="n">
-        <v>7.56</v>
+        <v>7.52</v>
       </c>
     </row>
     <row r="115">
@@ -2757,7 +2757,7 @@
         <v>129</v>
       </c>
       <c r="D115" t="n">
-        <v>8.76</v>
+        <v>8.64</v>
       </c>
     </row>
     <row r="116">
@@ -2771,7 +2771,7 @@
         <v>130</v>
       </c>
       <c r="D116" t="n">
-        <v>9.22</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="117">
@@ -2785,7 +2785,7 @@
         <v>131</v>
       </c>
       <c r="D117" t="n">
-        <v>10.79</v>
+        <v>10.68</v>
       </c>
     </row>
     <row r="118">
@@ -2799,7 +2799,7 @@
         <v>132</v>
       </c>
       <c r="D118" t="n">
-        <v>12.17</v>
+        <v>11.95</v>
       </c>
     </row>
     <row r="119">
@@ -2813,7 +2813,7 @@
         <v>133</v>
       </c>
       <c r="D119" t="n">
-        <v>12.57</v>
+        <v>12.34</v>
       </c>
     </row>
     <row r="120">
@@ -2827,7 +2827,7 @@
         <v>134</v>
       </c>
       <c r="D120" t="n">
-        <v>12.91</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="121">
@@ -2841,7 +2841,7 @@
         <v>135</v>
       </c>
       <c r="D121" t="n">
-        <v>17.91</v>
+        <v>13.22</v>
       </c>
     </row>
     <row r="122">
@@ -2855,7 +2855,7 @@
         <v>138</v>
       </c>
       <c r="D122" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="123">
@@ -2869,7 +2869,7 @@
         <v>139</v>
       </c>
       <c r="D123" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="124">
@@ -2883,7 +2883,7 @@
         <v>140</v>
       </c>
       <c r="D124" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="125">
@@ -2897,7 +2897,7 @@
         <v>141</v>
       </c>
       <c r="D125" t="n">
-        <v>3.29</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="126">
@@ -2911,7 +2911,7 @@
         <v>142</v>
       </c>
       <c r="D126" t="n">
-        <v>3.68</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="127">
@@ -2925,7 +2925,7 @@
         <v>143</v>
       </c>
       <c r="D127" t="n">
-        <v>4.16</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="128">
@@ -2939,7 +2939,7 @@
         <v>144</v>
       </c>
       <c r="D128" t="n">
-        <v>4.16</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="129">
@@ -2953,7 +2953,7 @@
         <v>145</v>
       </c>
       <c r="D129" t="n">
-        <v>4.28</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="130">
@@ -2967,7 +2967,7 @@
         <v>146</v>
       </c>
       <c r="D130" t="n">
-        <v>6.01</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="131">
@@ -2981,7 +2981,7 @@
         <v>147</v>
       </c>
       <c r="D131" t="n">
-        <v>7.43</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="132">
@@ -2995,7 +2995,7 @@
         <v>148</v>
       </c>
       <c r="D132" t="n">
-        <v>9.14</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="133">
@@ -3009,7 +3009,7 @@
         <v>149</v>
       </c>
       <c r="D133" t="n">
-        <v>13.68</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="134">
@@ -3023,7 +3023,7 @@
         <v>150</v>
       </c>
       <c r="D134" t="n">
-        <v>16.4</v>
+        <v>15.81</v>
       </c>
     </row>
     <row r="135">
@@ -3037,7 +3037,7 @@
         <v>151</v>
       </c>
       <c r="D135" t="n">
-        <v>17.4</v>
+        <v>17.25</v>
       </c>
     </row>
     <row r="136">
@@ -3045,13 +3045,13 @@
         <v>136</v>
       </c>
       <c r="B136" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="C136" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D136" t="n">
-        <v>21.03</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="137">
@@ -3059,13 +3059,13 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C137" t="s">
         <v>154</v>
       </c>
       <c r="D137" t="n">
-        <v>2.03</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="138">
@@ -3073,13 +3073,13 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C138" t="s">
         <v>155</v>
       </c>
       <c r="D138" t="n">
-        <v>2.32</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="139">
@@ -3087,13 +3087,13 @@
         <v>136</v>
       </c>
       <c r="B139" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C139" t="s">
         <v>156</v>
       </c>
       <c r="D139" t="n">
-        <v>2.57</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="140">
@@ -3101,13 +3101,13 @@
         <v>136</v>
       </c>
       <c r="B140" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C140" t="s">
         <v>157</v>
       </c>
       <c r="D140" t="n">
-        <v>3.24</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="141">
@@ -3115,13 +3115,13 @@
         <v>136</v>
       </c>
       <c r="B141" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C141" t="s">
         <v>158</v>
       </c>
       <c r="D141" t="n">
-        <v>3.45</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="142">
@@ -3129,13 +3129,13 @@
         <v>136</v>
       </c>
       <c r="B142" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C142" t="s">
         <v>159</v>
       </c>
       <c r="D142" t="n">
-        <v>3.67</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="143">
@@ -3143,13 +3143,13 @@
         <v>136</v>
       </c>
       <c r="B143" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C143" t="s">
         <v>160</v>
       </c>
       <c r="D143" t="n">
-        <v>4</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="144">
@@ -3157,13 +3157,13 @@
         <v>136</v>
       </c>
       <c r="B144" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C144" t="s">
         <v>161</v>
       </c>
       <c r="D144" t="n">
-        <v>4</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="145">
@@ -3171,13 +3171,13 @@
         <v>136</v>
       </c>
       <c r="B145" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C145" t="s">
         <v>162</v>
       </c>
       <c r="D145" t="n">
-        <v>4.32</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="146">
@@ -3185,13 +3185,13 @@
         <v>136</v>
       </c>
       <c r="B146" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C146" t="s">
         <v>163</v>
       </c>
       <c r="D146" t="n">
-        <v>4.64</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="147">
@@ -3199,13 +3199,13 @@
         <v>136</v>
       </c>
       <c r="B147" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C147" t="s">
         <v>164</v>
       </c>
       <c r="D147" t="n">
-        <v>9.86</v>
+        <v>12.69</v>
       </c>
     </row>
     <row r="148">
@@ -3213,13 +3213,13 @@
         <v>136</v>
       </c>
       <c r="B148" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C148" t="s">
         <v>165</v>
       </c>
       <c r="D148" t="n">
-        <v>11.74</v>
+        <v>13.02</v>
       </c>
     </row>
     <row r="149">
@@ -3227,13 +3227,13 @@
         <v>136</v>
       </c>
       <c r="B149" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C149" t="s">
         <v>166</v>
       </c>
       <c r="D149" t="n">
-        <v>12.53</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="150">
@@ -3241,13 +3241,13 @@
         <v>136</v>
       </c>
       <c r="B150" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C150" t="s">
         <v>167</v>
       </c>
       <c r="D150" t="n">
-        <v>13.15</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="151">
@@ -3255,13 +3255,13 @@
         <v>136</v>
       </c>
       <c r="B151" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C151" t="s">
         <v>168</v>
       </c>
       <c r="D151" t="n">
-        <v>13.29</v>
+        <v>19.48</v>
       </c>
     </row>
     <row r="152">
@@ -3275,7 +3275,7 @@
         <v>171</v>
       </c>
       <c r="D152" t="n">
-        <v>3.11</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="153">
@@ -3289,7 +3289,7 @@
         <v>172</v>
       </c>
       <c r="D153" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="154">
@@ -3303,7 +3303,7 @@
         <v>173</v>
       </c>
       <c r="D154" t="n">
-        <v>3.38</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="155">
@@ -3317,7 +3317,7 @@
         <v>174</v>
       </c>
       <c r="D155" t="n">
-        <v>3.47</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="156">
@@ -3331,7 +3331,7 @@
         <v>175</v>
       </c>
       <c r="D156" t="n">
-        <v>3.98</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="157">
@@ -3345,7 +3345,7 @@
         <v>176</v>
       </c>
       <c r="D157" t="n">
-        <v>5.51</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="158">
@@ -3359,7 +3359,7 @@
         <v>177</v>
       </c>
       <c r="D158" t="n">
-        <v>5.51</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="159">
@@ -3373,7 +3373,7 @@
         <v>178</v>
       </c>
       <c r="D159" t="n">
-        <v>6.29</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="160">
@@ -3387,7 +3387,7 @@
         <v>179</v>
       </c>
       <c r="D160" t="n">
-        <v>8.03</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="161">
@@ -3401,7 +3401,7 @@
         <v>180</v>
       </c>
       <c r="D161" t="n">
-        <v>8.17</v>
+        <v>8.12</v>
       </c>
     </row>
     <row r="162">
@@ -3415,7 +3415,7 @@
         <v>181</v>
       </c>
       <c r="D162" t="n">
-        <v>10.2</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="163">
@@ -3429,7 +3429,7 @@
         <v>182</v>
       </c>
       <c r="D163" t="n">
-        <v>10.74</v>
+        <v>9.97</v>
       </c>
     </row>
     <row r="164">
@@ -3443,7 +3443,7 @@
         <v>183</v>
       </c>
       <c r="D164" t="n">
-        <v>12.98</v>
+        <v>13.19</v>
       </c>
     </row>
     <row r="165">
@@ -3457,7 +3457,7 @@
         <v>184</v>
       </c>
       <c r="D165" t="n">
-        <v>17.02</v>
+        <v>16.36</v>
       </c>
     </row>
     <row r="166">
@@ -3471,7 +3471,7 @@
         <v>185</v>
       </c>
       <c r="D166" t="n">
-        <v>20.95</v>
+        <v>20.48</v>
       </c>
     </row>
     <row r="167">
@@ -3485,7 +3485,7 @@
         <v>186</v>
       </c>
       <c r="D167" t="n">
-        <v>21.3</v>
+        <v>21.11</v>
       </c>
     </row>
     <row r="168">
@@ -3499,7 +3499,7 @@
         <v>188</v>
       </c>
       <c r="D168" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="169">
@@ -3513,7 +3513,7 @@
         <v>189</v>
       </c>
       <c r="D169" t="n">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="170">
@@ -3527,7 +3527,7 @@
         <v>190</v>
       </c>
       <c r="D170" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="171">
@@ -3541,7 +3541,7 @@
         <v>191</v>
       </c>
       <c r="D171" t="n">
-        <v>3.27</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="172">
@@ -3555,7 +3555,7 @@
         <v>192</v>
       </c>
       <c r="D172" t="n">
-        <v>3.9</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="173">
@@ -3569,7 +3569,7 @@
         <v>193</v>
       </c>
       <c r="D173" t="n">
-        <v>3.98</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="174">
@@ -3583,7 +3583,7 @@
         <v>194</v>
       </c>
       <c r="D174" t="n">
-        <v>4.53</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="175">
@@ -3597,7 +3597,7 @@
         <v>195</v>
       </c>
       <c r="D175" t="n">
-        <v>4.53</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="176">
@@ -3611,7 +3611,7 @@
         <v>196</v>
       </c>
       <c r="D176" t="n">
-        <v>4.91</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="177">
@@ -3625,7 +3625,7 @@
         <v>197</v>
       </c>
       <c r="D177" t="n">
-        <v>7.85</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="178">
@@ -3639,7 +3639,7 @@
         <v>198</v>
       </c>
       <c r="D178" t="n">
-        <v>11.38</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="179">
@@ -3653,7 +3653,7 @@
         <v>199</v>
       </c>
       <c r="D179" t="n">
-        <v>12.69</v>
+        <v>11.13</v>
       </c>
     </row>
     <row r="180">
@@ -3667,7 +3667,7 @@
         <v>200</v>
       </c>
       <c r="D180" t="n">
-        <v>13.54</v>
+        <v>12.33</v>
       </c>
     </row>
     <row r="181">
@@ -3681,7 +3681,7 @@
         <v>201</v>
       </c>
       <c r="D181" t="n">
-        <v>15.63</v>
+        <v>15.09</v>
       </c>
     </row>
     <row r="182">
@@ -3695,7 +3695,7 @@
         <v>204</v>
       </c>
       <c r="D182" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="183">
@@ -3709,7 +3709,7 @@
         <v>205</v>
       </c>
       <c r="D183" t="n">
-        <v>3.56</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="184">
@@ -3723,7 +3723,7 @@
         <v>206</v>
       </c>
       <c r="D184" t="n">
-        <v>3.81</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="185">
@@ -3737,7 +3737,7 @@
         <v>207</v>
       </c>
       <c r="D185" t="n">
-        <v>3.91</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="186">
@@ -3751,7 +3751,7 @@
         <v>208</v>
       </c>
       <c r="D186" t="n">
-        <v>4.42</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="187">
@@ -3765,7 +3765,7 @@
         <v>209</v>
       </c>
       <c r="D187" t="n">
-        <v>4.54</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="188">
@@ -3779,7 +3779,7 @@
         <v>210</v>
       </c>
       <c r="D188" t="n">
-        <v>4.73</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="189">
@@ -3793,7 +3793,7 @@
         <v>211</v>
       </c>
       <c r="D189" t="n">
-        <v>4.73</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="190">
@@ -3807,7 +3807,7 @@
         <v>212</v>
       </c>
       <c r="D190" t="n">
-        <v>5.33</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="191">
@@ -3821,7 +3821,7 @@
         <v>213</v>
       </c>
       <c r="D191" t="n">
-        <v>8.36</v>
+        <v>9.13</v>
       </c>
     </row>
     <row r="192">
@@ -3835,7 +3835,7 @@
         <v>214</v>
       </c>
       <c r="D192" t="n">
-        <v>8.87</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="193">
@@ -3849,7 +3849,7 @@
         <v>215</v>
       </c>
       <c r="D193" t="n">
-        <v>11.5</v>
+        <v>12.76</v>
       </c>
     </row>
     <row r="194">
@@ -3863,7 +3863,7 @@
         <v>216</v>
       </c>
       <c r="D194" t="n">
-        <v>11.52</v>
+        <v>12.95</v>
       </c>
     </row>
     <row r="195">
@@ -3877,7 +3877,7 @@
         <v>217</v>
       </c>
       <c r="D195" t="n">
-        <v>11.56</v>
+        <v>13.17</v>
       </c>
     </row>
     <row r="196">
@@ -3891,7 +3891,7 @@
         <v>219</v>
       </c>
       <c r="D196" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="197">
@@ -3905,7 +3905,7 @@
         <v>220</v>
       </c>
       <c r="D197" t="n">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="198">
@@ -3919,7 +3919,7 @@
         <v>221</v>
       </c>
       <c r="D198" t="n">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="199">
@@ -3933,7 +3933,7 @@
         <v>222</v>
       </c>
       <c r="D199" t="n">
-        <v>3.03</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="200">
@@ -3947,7 +3947,7 @@
         <v>223</v>
       </c>
       <c r="D200" t="n">
-        <v>3.63</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="201">
@@ -3961,7 +3961,7 @@
         <v>224</v>
       </c>
       <c r="D201" t="n">
-        <v>4.03</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="202">
@@ -3975,7 +3975,7 @@
         <v>225</v>
       </c>
       <c r="D202" t="n">
-        <v>4.03</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="203">
@@ -3989,7 +3989,7 @@
         <v>226</v>
       </c>
       <c r="D203" t="n">
-        <v>5.22</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="204">
@@ -4003,7 +4003,7 @@
         <v>227</v>
       </c>
       <c r="D204" t="n">
-        <v>5.64</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="205">
@@ -4017,7 +4017,7 @@
         <v>228</v>
       </c>
       <c r="D205" t="n">
-        <v>5.95</v>
+        <v>5.52</v>
       </c>
     </row>
     <row r="206">
@@ -4031,7 +4031,7 @@
         <v>229</v>
       </c>
       <c r="D206" t="n">
-        <v>8.09</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="207">
@@ -4045,7 +4045,7 @@
         <v>230</v>
       </c>
       <c r="D207" t="n">
-        <v>8.13</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="208">
@@ -4059,7 +4059,7 @@
         <v>231</v>
       </c>
       <c r="D208" t="n">
-        <v>8.98</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="209">
@@ -4073,7 +4073,7 @@
         <v>232</v>
       </c>
       <c r="D209" t="n">
-        <v>13.02</v>
+        <v>12.17</v>
       </c>
     </row>
     <row r="210">
@@ -4087,7 +4087,7 @@
         <v>233</v>
       </c>
       <c r="D210" t="n">
-        <v>15.02</v>
+        <v>13.93</v>
       </c>
     </row>
     <row r="211">
@@ -4101,7 +4101,7 @@
         <v>234</v>
       </c>
       <c r="D211" t="n">
-        <v>16.15</v>
+        <v>15.55</v>
       </c>
     </row>
     <row r="212">
@@ -4115,7 +4115,7 @@
         <v>237</v>
       </c>
       <c r="D212" t="n">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="213">
@@ -4129,7 +4129,7 @@
         <v>238</v>
       </c>
       <c r="D213" t="n">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="214">
@@ -4143,7 +4143,7 @@
         <v>239</v>
       </c>
       <c r="D214" t="n">
-        <v>2.78</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="215">
@@ -4157,7 +4157,7 @@
         <v>240</v>
       </c>
       <c r="D215" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="216">
@@ -4171,7 +4171,7 @@
         <v>241</v>
       </c>
       <c r="D216" t="n">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="217">
@@ -4185,7 +4185,7 @@
         <v>242</v>
       </c>
       <c r="D217" t="n">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="218">
@@ -4199,7 +4199,7 @@
         <v>243</v>
       </c>
       <c r="D218" t="n">
-        <v>5.45</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="219">
@@ -4213,7 +4213,7 @@
         <v>244</v>
       </c>
       <c r="D219" t="n">
-        <v>5.74</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="220">
@@ -4227,7 +4227,7 @@
         <v>245</v>
       </c>
       <c r="D220" t="n">
-        <v>5.87</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="221">
@@ -4241,7 +4241,7 @@
         <v>246</v>
       </c>
       <c r="D221" t="n">
-        <v>6.57</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="222">
@@ -4255,7 +4255,7 @@
         <v>247</v>
       </c>
       <c r="D222" t="n">
-        <v>7.14</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="223">
@@ -4269,7 +4269,7 @@
         <v>248</v>
       </c>
       <c r="D223" t="n">
-        <v>11.53</v>
+        <v>11.03</v>
       </c>
     </row>
     <row r="224">
@@ -4283,7 +4283,7 @@
         <v>249</v>
       </c>
       <c r="D224" t="n">
-        <v>12.28</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="225">
@@ -4297,7 +4297,7 @@
         <v>250</v>
       </c>
       <c r="D225" t="n">
-        <v>12.33</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="226">
@@ -4311,7 +4311,7 @@
         <v>251</v>
       </c>
       <c r="D226" t="n">
-        <v>14.79</v>
+        <v>14.42</v>
       </c>
     </row>
     <row r="227">
@@ -4325,7 +4325,7 @@
         <v>253</v>
       </c>
       <c r="D227" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="228">
@@ -4339,7 +4339,7 @@
         <v>254</v>
       </c>
       <c r="D228" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="229">
@@ -4353,7 +4353,7 @@
         <v>255</v>
       </c>
       <c r="D229" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="230">
@@ -4367,7 +4367,7 @@
         <v>256</v>
       </c>
       <c r="D230" t="n">
-        <v>3.31</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="231">
@@ -4381,7 +4381,7 @@
         <v>257</v>
       </c>
       <c r="D231" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="232">
@@ -4395,7 +4395,7 @@
         <v>258</v>
       </c>
       <c r="D232" t="n">
-        <v>3.92</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="233">
@@ -4409,7 +4409,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="n">
-        <v>3.92</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="234">
@@ -4423,7 +4423,7 @@
         <v>260</v>
       </c>
       <c r="D234" t="n">
-        <v>5.58</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="235">
@@ -4437,7 +4437,7 @@
         <v>261</v>
       </c>
       <c r="D235" t="n">
-        <v>5.6</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="236">
@@ -4451,7 +4451,7 @@
         <v>262</v>
       </c>
       <c r="D236" t="n">
-        <v>5.71</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="237">
@@ -4465,7 +4465,7 @@
         <v>263</v>
       </c>
       <c r="D237" t="n">
-        <v>10.54</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="238">
@@ -4479,7 +4479,7 @@
         <v>264</v>
       </c>
       <c r="D238" t="n">
-        <v>10.6</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="239">
@@ -4493,7 +4493,7 @@
         <v>265</v>
       </c>
       <c r="D239" t="n">
-        <v>10.75</v>
+        <v>10.61</v>
       </c>
     </row>
     <row r="240">
@@ -4507,7 +4507,7 @@
         <v>266</v>
       </c>
       <c r="D240" t="n">
-        <v>16.49</v>
+        <v>16.27</v>
       </c>
     </row>
     <row r="241">
@@ -4521,7 +4521,7 @@
         <v>267</v>
       </c>
       <c r="D241" t="n">
-        <v>19.04</v>
+        <v>18.79</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_anytime_tryscorers.xlsx
+++ b/files/NRL_anytime_tryscorers.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="286">
   <si>
     <t xml:space="preserve">Game</t>
   </si>
@@ -26,7 +26,250 @@
     <t xml:space="preserve">Price</t>
   </si>
   <si>
-    <t xml:space="preserve">sydney roosters at penrith panthers</t>
+    <t xml:space="preserve">gold coast titans at newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phillip Sami</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaylan De Groot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Campbell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jojo Fifita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beau Fermor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keano Kini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AJ Brimson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Patston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver Pascoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lachlan Ilias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tino Fa'asuamaleaui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurtis Morrin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chris Randall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Bai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominic Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greg Marzhew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fletcher Sharpe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fletcher Hunt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kalyn Ponga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dane Gagai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francis Manuleleua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trey Mooney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandon Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jermaine McEwen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phoenix Crossland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harrison Graham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyson Frizell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mat Croker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cody Hopwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toby Winter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george-illawarra dragons at wests tigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george-illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyrell Sloan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Atkinson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valentine Holmes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mathew Feagai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamish Stewart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyle Flanagan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mosese Suli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lyhkan King-Togia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Egan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Liddle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setu Tu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toby Couchman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emre Guler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan Couchman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Webster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wests tigers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunia Turuva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solomone Saukuru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jahream Bula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Doueihi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Tupou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samuela Fainu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jarome Luai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apisai Koroisau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick Herbert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tony Sukkar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fonua Pole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terrell May</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sione Fainu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Seyfarth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Javon Andrews</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penrith panthers at melbourne storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moses Leo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sualauvi Faalogo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siulagi Tuimalatu-Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyran Wishart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hayden Watson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nick Meaney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron Munster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oryn Keeley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe Chan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angus Hinchey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stefano Utoikamanu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shawn Blore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Clarke</t>
   </si>
   <si>
     <t xml:space="preserve">penrith panthers</t>
@@ -38,42 +281,537 @@
     <t xml:space="preserve">Brian To'o</t>
   </si>
   <si>
-    <t xml:space="preserve">Jaxen Edgar</t>
+    <t xml:space="preserve">Dylan Edwards</t>
   </si>
   <si>
     <t xml:space="preserve">Izack Tago</t>
   </si>
   <si>
+    <t xml:space="preserve">Nathan Cleary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paul Alamoti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Martin</t>
+  </si>
+  <si>
     <t xml:space="preserve">Isaiah Papali'i</t>
   </si>
   <si>
-    <t xml:space="preserve">Liam Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nathan Cleary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paul Alamoti</t>
-  </si>
-  <si>
     <t xml:space="preserve">Freddy Lussick</t>
   </si>
   <si>
     <t xml:space="preserve">Lindsay Smith</t>
   </si>
   <si>
+    <t xml:space="preserve">Jack Cogger</t>
+  </si>
+  <si>
     <t xml:space="preserve">Liam Henry</t>
   </si>
   <si>
-    <t xml:space="preserve">Jack Cogger</t>
-  </si>
-  <si>
     <t xml:space="preserve">Moses Leota</t>
   </si>
   <si>
     <t xml:space="preserve">Scott Sorensen</t>
   </si>
   <si>
+    <t xml:space="preserve">Billy Phillips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luron Patea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos at canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grant Anderson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josiah Karapani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezra Mam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reece Walsh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kotoni Staggs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deine Mariner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Willison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Riki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Walters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Duffy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaiyden Hunt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gehamat Shibasaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payne Haas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Gosiewski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blake Mozer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Savage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jed Stuart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaeo Weekes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Timoko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Strange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Savelio Tamale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matty Nicholson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owen Pattie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zac Hosking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Sanders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe Roddy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daine Laurie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joseph Tapine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Starling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ata Mariota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels at dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamiso Tabuai-Fidow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selwyn Cobbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamayne Isaako</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herbie Farnworth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Bostock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kodi Nikorima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connelly Lemuelu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremy Marshall-King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kulikefu Finefeuiaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ray Stone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Flegler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiya Katoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Plath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Gilbert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morgan Knowles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Felise Kaufusi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Addo-Carr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apa Twidle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian Kelly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Samrani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Penisini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tallyn Da Silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitchell Moses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronald Volkman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kitione Kautoga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luca Moretti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saxon Pryke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Paulo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manly-warringah sea eagles at newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manly-warringah sea eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clayton Faulalo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jason Saab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lehi Hopoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tolutau Koula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reuben Garrick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haumole Olakau'atu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joey Walsh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corey Waddell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brandon Wakeham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamal Fogarty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Trbojevic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simione Laiafi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugo Hart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Simpkin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fletcher Baker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicholas Lenaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson Shereb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Feledy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathan Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors at south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Johnston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campbell Graham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tallis Duncan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cody Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Wighton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Dufty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">David Fifita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Elliott</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron Murray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keaon Koloamatangi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brandon Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Sullivan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tevita Tatola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euan Aitken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jye Gray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peter Mamouzelos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alofiana Khan-Pereira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dallin Watene-Zelezniak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leka Halasima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Metcalf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charnze Nicoll-Klokstad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ali Leiataua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chanel Harris-Tavita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Laban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Capewell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wayde Egan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Fisher-Harris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erin Clark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Healey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eddie Ieremia-Toeava</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs at st george-illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jethro Rinakama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Kiraz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matt Burton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Preston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stephen Crichton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Tracey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enari Tuala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viliame Kikau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lachlan Galvin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Mann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaeman Salmon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Curran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bailey Hayward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harry Hayes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leo Thompson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bronson Xerri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alekolasimi Jones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Turpin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks at gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronaldo Mulitalo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sione Katoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">William Kennedy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayal Iro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braydon Trindall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mawene Hiroti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Briton Nikora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teig Wilton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicholas Hynes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siosifa Talakai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Hazelton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blayke Brailey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesse Colquhoun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron McInnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braden Hamlin-Uele</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oregon Kaufusi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Burns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samuel Stonestreet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hohepa Puru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wests tigers at sydney roosters</t>
+  </si>
+  <si>
     <t xml:space="preserve">sydney roosters</t>
   </si>
   <si>
@@ -95,15 +833,15 @@
     <t xml:space="preserve">Sam Walker</t>
   </si>
   <si>
+    <t xml:space="preserve">Daly Cherry-Evans</t>
+  </si>
+  <si>
     <t xml:space="preserve">Salesi Foketi</t>
   </si>
   <si>
     <t xml:space="preserve">Siua Wong</t>
   </si>
   <si>
-    <t xml:space="preserve">Daly Cherry-Evans</t>
-  </si>
-  <si>
     <t xml:space="preserve">Reece Robson</t>
   </si>
   <si>
@@ -125,697 +863,13 @@
     <t xml:space="preserve">Spencer Leniu</t>
   </si>
   <si>
-    <t xml:space="preserve">dolphins at manly-warringah sea eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamiso Tabuai-Fidow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selwyn Cobbo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamayne Isaako</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herbie Farnworth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Bostock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connelly Lemuelu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kulikefu Finefeuiaki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kodi Nikorima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremy Marshall-King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ray Stone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Flegler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiya Katoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Plath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Felise Kaufusi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morgan Knowles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Francis Molo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Gilbert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manly-warringah sea eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clayton Faulalo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jason Saab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lehi Hopoate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tolutau Koula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reuben Garrick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joey Walsh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haumole Olakau'atu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corey Waddell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brandon Wakeham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamal Fogarty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nathan Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caleb Navale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simione Laiafi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">south sydney rabbitohs at canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jethro Rinakama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Kiraz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matt Burton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stephen Crichton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Tracey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viliame Kikau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Preston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enari Tuala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lachlan Galvin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jonathan Sua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurt Mann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaeman Salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Curran</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bailey Hayward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">south sydney rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Johnston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campbell Graham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tallis Duncan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cody Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Wighton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Dufty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">David Fifita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Elliott</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameron Murray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keaon Koloamatangi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brandon Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Sullivan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tevita Tatola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">John Radel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Euan Aitken</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jye Gray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders at cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Savage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jed Stuart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaeo Weekes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Timoko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan Strange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Savelio Tamale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zac Hosking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matty Nicholson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owen Pattie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan Sanders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joe Roddy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daine Laurie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronaldo Mulitalo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sione Katoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">William Kennedy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kayal Iro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mawene Hiroti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Braydon Trindall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Briton Nikora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teig Wilton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicholas Hynes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siosifa Talakai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Hazelton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blayke Brailey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jesse Colquhoun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameron McInnes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tuku Hau Tapuha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Braden Hamlin-Uele</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oregon Kaufusi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Burns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys at parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north queensland cowboys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Braidon Burns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Murray Taulagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scott Drinkwater</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Chester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zac Laybutt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Clifford</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heilum Luki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kai O'Donnell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reed Mahoney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaxon Purdue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reuben Cotter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam McIntyre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soni Luke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Griffin Neame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Addo-Carr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apa Twidle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian Kelly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan Samrani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Will Penisini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitchell Moses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitione Kautoga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronald Volkman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tallyn Da Silva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack De Belin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luca Moretti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kelma Tuilagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Paulo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jezaiah Funa-Iuta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors at brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grant Anderson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josiah Karapani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ezra Mam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reece Walsh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kotoni Staggs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaiyden Hunt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan Riki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deine Mariner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Walters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Duffy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Willison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben Talty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gehamat Shibasaki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payne Haas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Gosiewski</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blake Mozer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alofiana Khan-Pereira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dallin Watene-Zelezniak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Metcalf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leka Halasima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charnze Nicoll-Klokstad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ali Leiataua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurt Capewell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Laban</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chanel Harris-Tavita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wayde Egan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Fisher-Harris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erin Clark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Healey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eddie Ieremia-Toeava</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans at newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phillip Sami</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dean Ieremia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jojo Fifita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Campbell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keano Kini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AJ Brimson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Patston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beau Fermor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oliver Pascoe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lachlan Ilias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tino Fa'asuamaleaui</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurtis Morrin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chris Randall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Bai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dominic Young</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greg Marzhew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fletcher Sharpe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bradman Best</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kalyn Ponga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jermaine McEwen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Francis Manuleleua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dane Gagai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trey Mooney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandon Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phoenix Crossland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harrison Graham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fletcher Hunt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyson Frizell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mat Croker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cody Hopwood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george-illawarra dragons at wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george-illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyrell Sloan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Setu Tu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valentine Holmes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clinton Gutherson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Egan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamish Stewart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Liddle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyle Flanagan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mosese Suli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lyhkan King-Togia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Damien Cook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toby Couchman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emre Guler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan Couchman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel Atkinson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunia Turuva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jahream Bula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Doueihi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Tupou</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solomone Saukuru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samuela Fainu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tony Sukkar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jarome Luai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apisai Koroisau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patrick Herbert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fonua Pole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terrell May</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sione Fainu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Seyfarth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bunty Afoa</t>
+    <t xml:space="preserve">Naufahu Whyte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rex Bassingthwaighte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tommy Talau</t>
   </si>
 </sst>
 </file>
@@ -1144,7 +1198,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="55.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="60.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="29.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="24.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="5.71" hidden="0" customWidth="1"/>
@@ -1175,7 +1229,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>1.89</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="3">
@@ -1189,7 +1243,7 @@
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>2.29</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="4">
@@ -1203,7 +1257,7 @@
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>2.55</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="5">
@@ -1217,7 +1271,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>3.36</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="6">
@@ -1231,7 +1285,7 @@
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>4.59</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="7">
@@ -1245,7 +1299,7 @@
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>4.59</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="8">
@@ -1259,7 +1313,7 @@
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>4.6</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="9">
@@ -1273,7 +1327,7 @@
         <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>4.67</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="10">
@@ -1287,7 +1341,7 @@
         <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>7.9</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="11">
@@ -1301,7 +1355,7 @@
         <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>8.58</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="12">
@@ -1315,7 +1369,7 @@
         <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>11.39</v>
+        <v>8.98</v>
       </c>
     </row>
     <row r="13">
@@ -1329,7 +1383,7 @@
         <v>17</v>
       </c>
       <c r="D13" t="n">
-        <v>11.67</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="14">
@@ -1343,7 +1397,7 @@
         <v>18</v>
       </c>
       <c r="D14" t="n">
-        <v>18.09</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="15">
@@ -1357,7 +1411,7 @@
         <v>19</v>
       </c>
       <c r="D15" t="n">
-        <v>19.55</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="16">
@@ -1371,7 +1425,7 @@
         <v>21</v>
       </c>
       <c r="D16" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="17">
@@ -1385,7 +1439,7 @@
         <v>22</v>
       </c>
       <c r="D17" t="n">
-        <v>2.47</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="18">
@@ -1399,7 +1453,7 @@
         <v>23</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="19">
@@ -1413,7 +1467,7 @@
         <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>3.54</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="20">
@@ -1427,7 +1481,7 @@
         <v>25</v>
       </c>
       <c r="D20" t="n">
-        <v>3.63</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="21">
@@ -1441,7 +1495,7 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>4.62</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="22">
@@ -1455,7 +1509,7 @@
         <v>27</v>
       </c>
       <c r="D22" t="n">
-        <v>4.91</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="23">
@@ -1469,7 +1523,7 @@
         <v>28</v>
       </c>
       <c r="D23" t="n">
-        <v>4.91</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="24">
@@ -1483,7 +1537,7 @@
         <v>29</v>
       </c>
       <c r="D24" t="n">
-        <v>5.04</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="25">
@@ -1497,7 +1551,7 @@
         <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>8.95</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="26">
@@ -1511,7 +1565,7 @@
         <v>31</v>
       </c>
       <c r="D26" t="n">
-        <v>9.23</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="27">
@@ -1525,7 +1579,7 @@
         <v>32</v>
       </c>
       <c r="D27" t="n">
-        <v>11.65</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="28">
@@ -1539,7 +1593,7 @@
         <v>33</v>
       </c>
       <c r="D28" t="n">
-        <v>11.86</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="29">
@@ -1553,7 +1607,7 @@
         <v>34</v>
       </c>
       <c r="D29" t="n">
-        <v>14.28</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="30">
@@ -1567,7 +1621,7 @@
         <v>35</v>
       </c>
       <c r="D30" t="n">
-        <v>16.63</v>
+        <v>15.76</v>
       </c>
     </row>
     <row r="31">
@@ -1581,7 +1635,7 @@
         <v>36</v>
       </c>
       <c r="D31" t="n">
-        <v>17.86</v>
+        <v>19.07</v>
       </c>
     </row>
     <row r="32">
@@ -1595,7 +1649,7 @@
         <v>39</v>
       </c>
       <c r="D32" t="n">
-        <v>2.03</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="33">
@@ -1623,7 +1677,7 @@
         <v>41</v>
       </c>
       <c r="D34" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="35">
@@ -1637,7 +1691,7 @@
         <v>42</v>
       </c>
       <c r="D35" t="n">
-        <v>2.58</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="36">
@@ -1651,7 +1705,7 @@
         <v>43</v>
       </c>
       <c r="D36" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="37">
@@ -1665,7 +1719,7 @@
         <v>44</v>
       </c>
       <c r="D37" t="n">
-        <v>4.39</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="38">
@@ -1679,7 +1733,7 @@
         <v>45</v>
       </c>
       <c r="D38" t="n">
-        <v>4.39</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="39">
@@ -1693,7 +1747,7 @@
         <v>46</v>
       </c>
       <c r="D39" t="n">
-        <v>5.54</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="40">
@@ -1707,7 +1761,7 @@
         <v>47</v>
       </c>
       <c r="D40" t="n">
-        <v>7.14</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="41">
@@ -1721,7 +1775,7 @@
         <v>48</v>
       </c>
       <c r="D41" t="n">
-        <v>8.88</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="42">
@@ -1735,7 +1789,7 @@
         <v>49</v>
       </c>
       <c r="D42" t="n">
-        <v>9.42</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="43">
@@ -1749,7 +1803,7 @@
         <v>50</v>
       </c>
       <c r="D43" t="n">
-        <v>10.7</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="44">
@@ -1763,7 +1817,7 @@
         <v>51</v>
       </c>
       <c r="D44" t="n">
-        <v>11.07</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="45">
@@ -1777,7 +1831,7 @@
         <v>52</v>
       </c>
       <c r="D45" t="n">
-        <v>17.27</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="46">
@@ -1791,7 +1845,7 @@
         <v>53</v>
       </c>
       <c r="D46" t="n">
-        <v>17.37</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="47">
@@ -1799,13 +1853,13 @@
         <v>37</v>
       </c>
       <c r="B47" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="C47" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D47" t="n">
-        <v>17.83</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="48">
@@ -1813,13 +1867,13 @@
         <v>37</v>
       </c>
       <c r="B48" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="C48" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D48" t="n">
-        <v>17.91</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="49">
@@ -1827,13 +1881,13 @@
         <v>37</v>
       </c>
       <c r="B49" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C49" t="s">
         <v>57</v>
       </c>
       <c r="D49" t="n">
-        <v>1.99</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="50">
@@ -1841,13 +1895,13 @@
         <v>37</v>
       </c>
       <c r="B50" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C50" t="s">
         <v>58</v>
       </c>
       <c r="D50" t="n">
-        <v>2.18</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="51">
@@ -1855,13 +1909,13 @@
         <v>37</v>
       </c>
       <c r="B51" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C51" t="s">
         <v>59</v>
       </c>
       <c r="D51" t="n">
-        <v>2.26</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="52">
@@ -1869,13 +1923,13 @@
         <v>37</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C52" t="s">
         <v>60</v>
       </c>
       <c r="D52" t="n">
-        <v>2.58</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="53">
@@ -1883,13 +1937,13 @@
         <v>37</v>
       </c>
       <c r="B53" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C53" t="s">
         <v>61</v>
       </c>
       <c r="D53" t="n">
-        <v>2.76</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="54">
@@ -1897,13 +1951,13 @@
         <v>37</v>
       </c>
       <c r="B54" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C54" t="s">
         <v>62</v>
       </c>
       <c r="D54" t="n">
-        <v>3.67</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="55">
@@ -1911,13 +1965,13 @@
         <v>37</v>
       </c>
       <c r="B55" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C55" t="s">
         <v>63</v>
       </c>
       <c r="D55" t="n">
-        <v>3.97</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="56">
@@ -1925,13 +1979,13 @@
         <v>37</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C56" t="s">
         <v>64</v>
       </c>
       <c r="D56" t="n">
-        <v>3.97</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="57">
@@ -1939,13 +1993,13 @@
         <v>37</v>
       </c>
       <c r="B57" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C57" t="s">
         <v>65</v>
       </c>
       <c r="D57" t="n">
-        <v>6.29</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="58">
@@ -1953,13 +2007,13 @@
         <v>37</v>
       </c>
       <c r="B58" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C58" t="s">
         <v>66</v>
       </c>
       <c r="D58" t="n">
-        <v>7.53</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="59">
@@ -1967,13 +2021,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C59" t="s">
         <v>67</v>
       </c>
       <c r="D59" t="n">
-        <v>13.11</v>
+        <v>17.06</v>
       </c>
     </row>
     <row r="60">
@@ -1981,13 +2035,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C60" t="s">
         <v>68</v>
       </c>
       <c r="D60" t="n">
-        <v>14.3</v>
+        <v>17.18</v>
       </c>
     </row>
     <row r="61">
@@ -1995,13 +2049,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C61" t="s">
         <v>69</v>
       </c>
       <c r="D61" t="n">
-        <v>17.8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62">
@@ -2015,7 +2069,7 @@
         <v>72</v>
       </c>
       <c r="D62" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="63">
@@ -2029,7 +2083,7 @@
         <v>73</v>
       </c>
       <c r="D63" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="64">
@@ -2043,7 +2097,7 @@
         <v>74</v>
       </c>
       <c r="D64" t="n">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="65">
@@ -2057,7 +2111,7 @@
         <v>75</v>
       </c>
       <c r="D65" t="n">
-        <v>3.61</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -2071,7 +2125,7 @@
         <v>76</v>
       </c>
       <c r="D66" t="n">
-        <v>4.06</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="67">
@@ -2085,7 +2139,7 @@
         <v>77</v>
       </c>
       <c r="D67" t="n">
-        <v>4.29</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="68">
@@ -2099,7 +2153,7 @@
         <v>78</v>
       </c>
       <c r="D68" t="n">
-        <v>4.29</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="69">
@@ -2113,7 +2167,7 @@
         <v>79</v>
       </c>
       <c r="D69" t="n">
-        <v>4.32</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="70">
@@ -2127,7 +2181,7 @@
         <v>80</v>
       </c>
       <c r="D70" t="n">
-        <v>5</v>
+        <v>6.22</v>
       </c>
     </row>
     <row r="71">
@@ -2141,7 +2195,7 @@
         <v>81</v>
       </c>
       <c r="D71" t="n">
-        <v>11.2</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="72">
@@ -2155,7 +2209,7 @@
         <v>82</v>
       </c>
       <c r="D72" t="n">
-        <v>11.21</v>
+        <v>11.59</v>
       </c>
     </row>
     <row r="73">
@@ -2169,7 +2223,7 @@
         <v>83</v>
       </c>
       <c r="D73" t="n">
-        <v>11.38</v>
+        <v>12.48</v>
       </c>
     </row>
     <row r="74">
@@ -2183,7 +2237,7 @@
         <v>84</v>
       </c>
       <c r="D74" t="n">
-        <v>11.84</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="75">
@@ -2197,7 +2251,7 @@
         <v>85</v>
       </c>
       <c r="D75" t="n">
-        <v>13.86</v>
+        <v>14.36</v>
       </c>
     </row>
     <row r="76">
@@ -2211,7 +2265,7 @@
         <v>87</v>
       </c>
       <c r="D76" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="77">
@@ -2225,7 +2279,7 @@
         <v>88</v>
       </c>
       <c r="D77" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="78">
@@ -2239,7 +2293,7 @@
         <v>89</v>
       </c>
       <c r="D78" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="79">
@@ -2253,7 +2307,7 @@
         <v>90</v>
       </c>
       <c r="D79" t="n">
-        <v>3.41</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="80">
@@ -2267,7 +2321,7 @@
         <v>91</v>
       </c>
       <c r="D80" t="n">
-        <v>3.97</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="81">
@@ -2281,7 +2335,7 @@
         <v>92</v>
       </c>
       <c r="D81" t="n">
-        <v>4.31</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="82">
@@ -2295,7 +2349,7 @@
         <v>93</v>
       </c>
       <c r="D82" t="n">
-        <v>4.43</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="83">
@@ -2309,7 +2363,7 @@
         <v>94</v>
       </c>
       <c r="D83" t="n">
-        <v>4.43</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="84">
@@ -2323,7 +2377,7 @@
         <v>95</v>
       </c>
       <c r="D84" t="n">
-        <v>7.24</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="85">
@@ -2337,7 +2391,7 @@
         <v>96</v>
       </c>
       <c r="D85" t="n">
-        <v>7.43</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="86">
@@ -2351,7 +2405,7 @@
         <v>97</v>
       </c>
       <c r="D86" t="n">
-        <v>8.9</v>
+        <v>10.78</v>
       </c>
     </row>
     <row r="87">
@@ -2365,7 +2419,7 @@
         <v>98</v>
       </c>
       <c r="D87" t="n">
-        <v>9.56</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="88">
@@ -2379,7 +2433,7 @@
         <v>99</v>
       </c>
       <c r="D88" t="n">
-        <v>10.84</v>
+        <v>14.79</v>
       </c>
     </row>
     <row r="89">
@@ -2393,7 +2447,7 @@
         <v>100</v>
       </c>
       <c r="D89" t="n">
-        <v>11.58</v>
+        <v>18.07</v>
       </c>
     </row>
     <row r="90">
@@ -2407,7 +2461,7 @@
         <v>101</v>
       </c>
       <c r="D90" t="n">
-        <v>12.23</v>
+        <v>20.26</v>
       </c>
     </row>
     <row r="91">
@@ -2421,7 +2475,7 @@
         <v>102</v>
       </c>
       <c r="D91" t="n">
-        <v>14.19</v>
+        <v>20.88</v>
       </c>
     </row>
     <row r="92">
@@ -2435,7 +2489,7 @@
         <v>105</v>
       </c>
       <c r="D92" t="n">
-        <v>2.87</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="93">
@@ -2449,7 +2503,7 @@
         <v>106</v>
       </c>
       <c r="D93" t="n">
-        <v>3.32</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="94">
@@ -2463,7 +2517,7 @@
         <v>107</v>
       </c>
       <c r="D94" t="n">
-        <v>3.48</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="95">
@@ -2477,7 +2531,7 @@
         <v>108</v>
       </c>
       <c r="D95" t="n">
-        <v>4.22</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="96">
@@ -2491,7 +2545,7 @@
         <v>109</v>
       </c>
       <c r="D96" t="n">
-        <v>4.29</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="97">
@@ -2505,7 +2559,7 @@
         <v>110</v>
       </c>
       <c r="D97" t="n">
-        <v>4.89</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="98">
@@ -2519,7 +2573,7 @@
         <v>111</v>
       </c>
       <c r="D98" t="n">
-        <v>5.05</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="99">
@@ -2533,7 +2587,7 @@
         <v>112</v>
       </c>
       <c r="D99" t="n">
-        <v>5.05</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="100">
@@ -2547,7 +2601,7 @@
         <v>113</v>
       </c>
       <c r="D100" t="n">
-        <v>7.07</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="101">
@@ -2561,7 +2615,7 @@
         <v>114</v>
       </c>
       <c r="D101" t="n">
-        <v>8.57</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="102">
@@ -2575,7 +2629,7 @@
         <v>115</v>
       </c>
       <c r="D102" t="n">
-        <v>10.5</v>
+        <v>9.39</v>
       </c>
     </row>
     <row r="103">
@@ -2589,7 +2643,7 @@
         <v>116</v>
       </c>
       <c r="D103" t="n">
-        <v>11.11</v>
+        <v>10.77</v>
       </c>
     </row>
     <row r="104">
@@ -2597,13 +2651,13 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
+        <v>104</v>
+      </c>
+      <c r="C104" t="s">
         <v>117</v>
       </c>
-      <c r="C104" t="s">
-        <v>118</v>
-      </c>
       <c r="D104" t="n">
-        <v>1.7</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="105">
@@ -2611,13 +2665,13 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C105" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D105" t="n">
-        <v>1.89</v>
+        <v>16.07</v>
       </c>
     </row>
     <row r="106">
@@ -2625,13 +2679,13 @@
         <v>103</v>
       </c>
       <c r="B106" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C106" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D106" t="n">
-        <v>2.67</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="107">
@@ -2639,13 +2693,13 @@
         <v>103</v>
       </c>
       <c r="B107" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C107" t="s">
         <v>121</v>
       </c>
       <c r="D107" t="n">
-        <v>2.75</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="108">
@@ -2653,13 +2707,13 @@
         <v>103</v>
       </c>
       <c r="B108" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C108" t="s">
         <v>122</v>
       </c>
       <c r="D108" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="109">
@@ -2667,13 +2721,13 @@
         <v>103</v>
       </c>
       <c r="B109" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C109" t="s">
         <v>123</v>
       </c>
       <c r="D109" t="n">
-        <v>2.82</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="110">
@@ -2681,13 +2735,13 @@
         <v>103</v>
       </c>
       <c r="B110" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C110" t="s">
         <v>124</v>
       </c>
       <c r="D110" t="n">
-        <v>3.55</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="111">
@@ -2695,13 +2749,13 @@
         <v>103</v>
       </c>
       <c r="B111" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C111" t="s">
         <v>125</v>
       </c>
       <c r="D111" t="n">
-        <v>3.55</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="112">
@@ -2709,13 +2763,13 @@
         <v>103</v>
       </c>
       <c r="B112" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C112" t="s">
         <v>126</v>
       </c>
       <c r="D112" t="n">
-        <v>4</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="113">
@@ -2723,13 +2777,13 @@
         <v>103</v>
       </c>
       <c r="B113" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C113" t="s">
         <v>127</v>
       </c>
       <c r="D113" t="n">
-        <v>6.98</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="114">
@@ -2737,13 +2791,13 @@
         <v>103</v>
       </c>
       <c r="B114" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C114" t="s">
         <v>128</v>
       </c>
       <c r="D114" t="n">
-        <v>7.52</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="115">
@@ -2751,13 +2805,13 @@
         <v>103</v>
       </c>
       <c r="B115" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C115" t="s">
         <v>129</v>
       </c>
       <c r="D115" t="n">
-        <v>8.64</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="116">
@@ -2765,13 +2819,13 @@
         <v>103</v>
       </c>
       <c r="B116" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C116" t="s">
         <v>130</v>
       </c>
       <c r="D116" t="n">
-        <v>9.33</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="117">
@@ -2779,13 +2833,13 @@
         <v>103</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C117" t="s">
         <v>131</v>
       </c>
       <c r="D117" t="n">
-        <v>10.68</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="118">
@@ -2793,13 +2847,13 @@
         <v>103</v>
       </c>
       <c r="B118" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C118" t="s">
         <v>132</v>
       </c>
       <c r="D118" t="n">
-        <v>11.95</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="119">
@@ -2807,13 +2861,13 @@
         <v>103</v>
       </c>
       <c r="B119" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C119" t="s">
         <v>133</v>
       </c>
       <c r="D119" t="n">
-        <v>12.34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="120">
@@ -2821,13 +2875,13 @@
         <v>103</v>
       </c>
       <c r="B120" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C120" t="s">
         <v>134</v>
       </c>
       <c r="D120" t="n">
-        <v>12.66</v>
+        <v>11.57</v>
       </c>
     </row>
     <row r="121">
@@ -2835,13 +2889,13 @@
         <v>103</v>
       </c>
       <c r="B121" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C121" t="s">
         <v>135</v>
       </c>
       <c r="D121" t="n">
-        <v>13.22</v>
+        <v>17.98</v>
       </c>
     </row>
     <row r="122">
@@ -2855,7 +2909,7 @@
         <v>138</v>
       </c>
       <c r="D122" t="n">
-        <v>2.03</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="123">
@@ -2869,7 +2923,7 @@
         <v>139</v>
       </c>
       <c r="D123" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="124">
@@ -2883,7 +2937,7 @@
         <v>140</v>
       </c>
       <c r="D124" t="n">
-        <v>2.66</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="125">
@@ -2897,7 +2951,7 @@
         <v>141</v>
       </c>
       <c r="D125" t="n">
-        <v>3.26</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="126">
@@ -2911,7 +2965,7 @@
         <v>142</v>
       </c>
       <c r="D126" t="n">
-        <v>3.63</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="127">
@@ -2925,7 +2979,7 @@
         <v>143</v>
       </c>
       <c r="D127" t="n">
-        <v>3.99</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="128">
@@ -2939,7 +2993,7 @@
         <v>144</v>
       </c>
       <c r="D128" t="n">
-        <v>4.02</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="129">
@@ -2953,7 +3007,7 @@
         <v>145</v>
       </c>
       <c r="D129" t="n">
-        <v>4.02</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="130">
@@ -2967,7 +3021,7 @@
         <v>146</v>
       </c>
       <c r="D130" t="n">
-        <v>5.79</v>
+        <v>6</v>
       </c>
     </row>
     <row r="131">
@@ -2981,7 +3035,7 @@
         <v>147</v>
       </c>
       <c r="D131" t="n">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="132">
@@ -2995,7 +3049,7 @@
         <v>148</v>
       </c>
       <c r="D132" t="n">
-        <v>8.9</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="133">
@@ -3009,7 +3063,7 @@
         <v>149</v>
       </c>
       <c r="D133" t="n">
-        <v>13.4</v>
+        <v>8.37</v>
       </c>
     </row>
     <row r="134">
@@ -3023,7 +3077,7 @@
         <v>150</v>
       </c>
       <c r="D134" t="n">
-        <v>15.81</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="135">
@@ -3037,7 +3091,7 @@
         <v>151</v>
       </c>
       <c r="D135" t="n">
-        <v>17.25</v>
+        <v>10.78</v>
       </c>
     </row>
     <row r="136">
@@ -3045,13 +3099,13 @@
         <v>136</v>
       </c>
       <c r="B136" t="s">
+        <v>137</v>
+      </c>
+      <c r="C136" t="s">
         <v>152</v>
       </c>
-      <c r="C136" t="s">
-        <v>153</v>
-      </c>
       <c r="D136" t="n">
-        <v>2.1</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="137">
@@ -3059,13 +3113,13 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="C137" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D137" t="n">
-        <v>2.39</v>
+        <v>13.84</v>
       </c>
     </row>
     <row r="138">
@@ -3073,13 +3127,13 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C138" t="s">
         <v>155</v>
       </c>
       <c r="D138" t="n">
-        <v>2.72</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="139">
@@ -3087,13 +3141,13 @@
         <v>136</v>
       </c>
       <c r="B139" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C139" t="s">
         <v>156</v>
       </c>
       <c r="D139" t="n">
-        <v>3.36</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="140">
@@ -3101,13 +3155,13 @@
         <v>136</v>
       </c>
       <c r="B140" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C140" t="s">
         <v>157</v>
       </c>
       <c r="D140" t="n">
-        <v>3.37</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="141">
@@ -3115,13 +3169,13 @@
         <v>136</v>
       </c>
       <c r="B141" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C141" t="s">
         <v>158</v>
       </c>
       <c r="D141" t="n">
-        <v>3.82</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="142">
@@ -3129,13 +3183,13 @@
         <v>136</v>
       </c>
       <c r="B142" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C142" t="s">
         <v>159</v>
       </c>
       <c r="D142" t="n">
-        <v>4.13</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="143">
@@ -3143,13 +3197,13 @@
         <v>136</v>
       </c>
       <c r="B143" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C143" t="s">
         <v>160</v>
       </c>
       <c r="D143" t="n">
-        <v>4.13</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="144">
@@ -3157,13 +3211,13 @@
         <v>136</v>
       </c>
       <c r="B144" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C144" t="s">
         <v>161</v>
       </c>
       <c r="D144" t="n">
-        <v>4.43</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="145">
@@ -3171,13 +3225,13 @@
         <v>136</v>
       </c>
       <c r="B145" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C145" t="s">
         <v>162</v>
       </c>
       <c r="D145" t="n">
-        <v>4.46</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="146">
@@ -3185,13 +3239,13 @@
         <v>136</v>
       </c>
       <c r="B146" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C146" t="s">
         <v>163</v>
       </c>
       <c r="D146" t="n">
-        <v>10.33</v>
+        <v>8</v>
       </c>
     </row>
     <row r="147">
@@ -3199,13 +3253,13 @@
         <v>136</v>
       </c>
       <c r="B147" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C147" t="s">
         <v>164</v>
       </c>
       <c r="D147" t="n">
-        <v>12.69</v>
+        <v>10.44</v>
       </c>
     </row>
     <row r="148">
@@ -3213,13 +3267,13 @@
         <v>136</v>
       </c>
       <c r="B148" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C148" t="s">
         <v>165</v>
       </c>
       <c r="D148" t="n">
-        <v>13.02</v>
+        <v>15.46</v>
       </c>
     </row>
     <row r="149">
@@ -3227,13 +3281,13 @@
         <v>136</v>
       </c>
       <c r="B149" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C149" t="s">
         <v>166</v>
       </c>
       <c r="D149" t="n">
-        <v>13.65</v>
+        <v>15.93</v>
       </c>
     </row>
     <row r="150">
@@ -3241,13 +3295,13 @@
         <v>136</v>
       </c>
       <c r="B150" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C150" t="s">
         <v>167</v>
       </c>
       <c r="D150" t="n">
-        <v>13.79</v>
+        <v>16.19</v>
       </c>
     </row>
     <row r="151">
@@ -3255,13 +3309,13 @@
         <v>136</v>
       </c>
       <c r="B151" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C151" t="s">
         <v>168</v>
       </c>
       <c r="D151" t="n">
-        <v>19.48</v>
+        <v>16.33</v>
       </c>
     </row>
     <row r="152">
@@ -3275,7 +3329,7 @@
         <v>171</v>
       </c>
       <c r="D152" t="n">
-        <v>3.04</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="153">
@@ -3289,7 +3343,7 @@
         <v>172</v>
       </c>
       <c r="D153" t="n">
-        <v>3.1</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="154">
@@ -3303,7 +3357,7 @@
         <v>173</v>
       </c>
       <c r="D154" t="n">
-        <v>3.18</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="155">
@@ -3317,7 +3371,7 @@
         <v>174</v>
       </c>
       <c r="D155" t="n">
-        <v>3.27</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="156">
@@ -3331,7 +3385,7 @@
         <v>175</v>
       </c>
       <c r="D156" t="n">
-        <v>3.84</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="157">
@@ -3345,7 +3399,7 @@
         <v>176</v>
       </c>
       <c r="D157" t="n">
-        <v>5.27</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="158">
@@ -3359,7 +3413,7 @@
         <v>177</v>
       </c>
       <c r="D158" t="n">
-        <v>5.27</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="159">
@@ -3373,7 +3427,7 @@
         <v>178</v>
       </c>
       <c r="D159" t="n">
-        <v>5.5</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="160">
@@ -3387,7 +3441,7 @@
         <v>179</v>
       </c>
       <c r="D160" t="n">
-        <v>7.75</v>
+        <v>7.56</v>
       </c>
     </row>
     <row r="161">
@@ -3401,7 +3455,7 @@
         <v>180</v>
       </c>
       <c r="D161" t="n">
-        <v>8.12</v>
+        <v>8.8</v>
       </c>
     </row>
     <row r="162">
@@ -3415,7 +3469,7 @@
         <v>181</v>
       </c>
       <c r="D162" t="n">
-        <v>8.58</v>
+        <v>21.82</v>
       </c>
     </row>
     <row r="163">
@@ -3429,7 +3483,7 @@
         <v>182</v>
       </c>
       <c r="D163" t="n">
-        <v>9.97</v>
+        <v>21.89</v>
       </c>
     </row>
     <row r="164">
@@ -3443,7 +3497,7 @@
         <v>183</v>
       </c>
       <c r="D164" t="n">
-        <v>13.19</v>
+        <v>25.16</v>
       </c>
     </row>
     <row r="165">
@@ -3457,7 +3511,7 @@
         <v>184</v>
       </c>
       <c r="D165" t="n">
-        <v>16.36</v>
+        <v>25.98</v>
       </c>
     </row>
     <row r="166">
@@ -3471,7 +3525,7 @@
         <v>185</v>
       </c>
       <c r="D166" t="n">
-        <v>20.48</v>
+        <v>27.51</v>
       </c>
     </row>
     <row r="167">
@@ -3485,7 +3539,7 @@
         <v>186</v>
       </c>
       <c r="D167" t="n">
-        <v>21.11</v>
+        <v>28.45</v>
       </c>
     </row>
     <row r="168">
@@ -3493,13 +3547,13 @@
         <v>169</v>
       </c>
       <c r="B168" t="s">
+        <v>170</v>
+      </c>
+      <c r="C168" t="s">
         <v>187</v>
       </c>
-      <c r="C168" t="s">
-        <v>188</v>
-      </c>
       <c r="D168" t="n">
-        <v>1.73</v>
+        <v>33.38</v>
       </c>
     </row>
     <row r="169">
@@ -3507,13 +3561,13 @@
         <v>169</v>
       </c>
       <c r="B169" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="C169" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D169" t="n">
-        <v>1.99</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="170">
@@ -3521,1007 +3575,1231 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="C170" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D170" t="n">
-        <v>2.92</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="B171" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C171" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D171" t="n">
-        <v>2.93</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="B172" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C172" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D172" t="n">
-        <v>3.62</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="B173" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C173" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D173" t="n">
-        <v>3.84</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="B174" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C174" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D174" t="n">
-        <v>4.27</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="B175" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C175" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D175" t="n">
-        <v>4.27</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="B176" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C176" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D176" t="n">
-        <v>4.48</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="B177" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C177" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D177" t="n">
-        <v>7.45</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="B178" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C178" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D178" t="n">
-        <v>10.79</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="B179" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C179" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D179" t="n">
-        <v>11.13</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="B180" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C180" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D180" t="n">
-        <v>12.33</v>
+        <v>8.95</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="B181" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C181" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D181" t="n">
-        <v>15.09</v>
+        <v>10.68</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B182" t="s">
+        <v>191</v>
+      </c>
+      <c r="C182" t="s">
         <v>203</v>
       </c>
-      <c r="C182" t="s">
-        <v>204</v>
-      </c>
       <c r="D182" t="n">
-        <v>2.5</v>
+        <v>11.58</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B183" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="C183" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D183" t="n">
-        <v>3.98</v>
+        <v>13.01</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B184" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="C184" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D184" t="n">
-        <v>4.21</v>
+        <v>15.36</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B185" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="C185" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D185" t="n">
-        <v>4.31</v>
+        <v>17.71</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B186" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="C186" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D186" t="n">
-        <v>4.89</v>
+        <v>19.53</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B187" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C187" t="s">
         <v>209</v>
       </c>
       <c r="D187" t="n">
-        <v>4.94</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B188" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C188" t="s">
         <v>210</v>
       </c>
       <c r="D188" t="n">
-        <v>5.15</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B189" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C189" t="s">
         <v>211</v>
       </c>
       <c r="D189" t="n">
-        <v>5.15</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B190" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C190" t="s">
         <v>212</v>
       </c>
       <c r="D190" t="n">
-        <v>5.8</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C191" t="s">
         <v>213</v>
       </c>
       <c r="D191" t="n">
-        <v>9.13</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C192" t="s">
         <v>214</v>
       </c>
       <c r="D192" t="n">
-        <v>9.82</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B193" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C193" t="s">
         <v>215</v>
       </c>
       <c r="D193" t="n">
-        <v>12.76</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B194" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C194" t="s">
         <v>216</v>
       </c>
       <c r="D194" t="n">
-        <v>12.95</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B195" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C195" t="s">
         <v>217</v>
       </c>
       <c r="D195" t="n">
-        <v>13.17</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B196" t="s">
+        <v>208</v>
+      </c>
+      <c r="C196" t="s">
         <v>218</v>
       </c>
-      <c r="C196" t="s">
-        <v>219</v>
-      </c>
       <c r="D196" t="n">
-        <v>1.7</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B197" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="C197" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D197" t="n">
-        <v>1.98</v>
+        <v>10.63</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B198" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="C198" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D198" t="n">
-        <v>2.22</v>
+        <v>11.03</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B199" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="C199" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D199" t="n">
-        <v>2.79</v>
+        <v>12.46</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B200" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="C200" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D200" t="n">
-        <v>3.27</v>
+        <v>15.16</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="B201" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C201" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D201" t="n">
-        <v>3.7</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="B202" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C202" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D202" t="n">
-        <v>3.7</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="B203" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C203" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D203" t="n">
-        <v>4.64</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="B204" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C204" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D204" t="n">
-        <v>5.31</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="B205" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C205" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D205" t="n">
-        <v>5.52</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="B206" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C206" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D206" t="n">
-        <v>7.36</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="B207" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C207" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D207" t="n">
-        <v>7.41</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="B208" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C208" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D208" t="n">
-        <v>8.18</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="B209" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C209" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D209" t="n">
-        <v>12.17</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="B210" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C210" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D210" t="n">
-        <v>13.93</v>
+        <v>9.88</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="B211" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C211" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D211" t="n">
-        <v>15.55</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="B212" t="s">
+        <v>224</v>
+      </c>
+      <c r="C212" t="s">
         <v>236</v>
       </c>
-      <c r="C212" t="s">
-        <v>237</v>
-      </c>
       <c r="D212" t="n">
-        <v>2.27</v>
+        <v>10.43</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="B213" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="C213" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D213" t="n">
-        <v>2.45</v>
+        <v>12.31</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="B214" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="C214" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D214" t="n">
-        <v>2.69</v>
+        <v>19.66</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="B215" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="C215" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D215" t="n">
-        <v>2.7</v>
+        <v>22.32</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="B216" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="C216" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D216" t="n">
-        <v>4.15</v>
+        <v>24.15</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="B217" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="C217" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D217" t="n">
-        <v>4.15</v>
+        <v>24.34</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="B218" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="C218" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D218" t="n">
-        <v>5.22</v>
+        <v>28.31</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="B219" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="C219" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D219" t="n">
-        <v>5.54</v>
+        <v>46.85</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B220" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C220" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D220" t="n">
-        <v>5.62</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B221" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C221" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D221" t="n">
-        <v>6.45</v>
+        <v>2</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B222" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C222" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D222" t="n">
-        <v>6.83</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B223" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C223" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D223" t="n">
-        <v>11.03</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B224" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C224" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D224" t="n">
-        <v>12.05</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B225" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C225" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D225" t="n">
-        <v>12.25</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B226" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C226" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D226" t="n">
-        <v>14.42</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B227" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C227" t="s">
         <v>253</v>
       </c>
       <c r="D227" t="n">
-        <v>2.54</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B228" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C228" t="s">
         <v>254</v>
       </c>
       <c r="D228" t="n">
-        <v>2.83</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B229" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C229" t="s">
         <v>255</v>
       </c>
       <c r="D229" t="n">
-        <v>3.04</v>
+        <v>7.58</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B230" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C230" t="s">
         <v>256</v>
       </c>
       <c r="D230" t="n">
-        <v>3.27</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B231" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C231" t="s">
         <v>257</v>
       </c>
       <c r="D231" t="n">
-        <v>3.3</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B232" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C232" t="s">
         <v>258</v>
       </c>
       <c r="D232" t="n">
-        <v>3.87</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B233" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C233" t="s">
         <v>259</v>
       </c>
       <c r="D233" t="n">
-        <v>3.87</v>
+        <v>11.56</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B234" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C234" t="s">
         <v>260</v>
       </c>
       <c r="D234" t="n">
-        <v>5.51</v>
+        <v>13.24</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B235" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C235" t="s">
         <v>261</v>
       </c>
       <c r="D235" t="n">
-        <v>5.53</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B236" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C236" t="s">
         <v>262</v>
       </c>
       <c r="D236" t="n">
-        <v>5.64</v>
+        <v>14.53</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B237" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C237" t="s">
         <v>263</v>
       </c>
       <c r="D237" t="n">
-        <v>10.39</v>
+        <v>23.02</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B238" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C238" t="s">
         <v>264</v>
       </c>
       <c r="D238" t="n">
-        <v>10.45</v>
+        <v>50.83</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="B239" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="C239" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D239" t="n">
-        <v>10.61</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="B240" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="C240" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D240" t="n">
-        <v>16.27</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="B241" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="C241" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D241" t="n">
-        <v>18.79</v>
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s">
+        <v>265</v>
+      </c>
+      <c r="B242" t="s">
+        <v>266</v>
+      </c>
+      <c r="C242" t="s">
+        <v>270</v>
+      </c>
+      <c r="D242" t="n">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s">
+        <v>265</v>
+      </c>
+      <c r="B243" t="s">
+        <v>266</v>
+      </c>
+      <c r="C243" t="s">
+        <v>271</v>
+      </c>
+      <c r="D243" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s">
+        <v>265</v>
+      </c>
+      <c r="B244" t="s">
+        <v>266</v>
+      </c>
+      <c r="C244" t="s">
+        <v>272</v>
+      </c>
+      <c r="D244" t="n">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s">
+        <v>265</v>
+      </c>
+      <c r="B245" t="s">
+        <v>266</v>
+      </c>
+      <c r="C245" t="s">
+        <v>273</v>
+      </c>
+      <c r="D245" t="n">
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s">
+        <v>265</v>
+      </c>
+      <c r="B246" t="s">
+        <v>266</v>
+      </c>
+      <c r="C246" t="s">
+        <v>274</v>
+      </c>
+      <c r="D246" t="n">
+        <v>4.48</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s">
+        <v>265</v>
+      </c>
+      <c r="B247" t="s">
+        <v>266</v>
+      </c>
+      <c r="C247" t="s">
+        <v>275</v>
+      </c>
+      <c r="D247" t="n">
+        <v>5.02</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s">
+        <v>265</v>
+      </c>
+      <c r="B248" t="s">
+        <v>266</v>
+      </c>
+      <c r="C248" t="s">
+        <v>276</v>
+      </c>
+      <c r="D248" t="n">
+        <v>5.87</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s">
+        <v>265</v>
+      </c>
+      <c r="B249" t="s">
+        <v>266</v>
+      </c>
+      <c r="C249" t="s">
+        <v>277</v>
+      </c>
+      <c r="D249" t="n">
+        <v>6.06</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s">
+        <v>265</v>
+      </c>
+      <c r="B250" t="s">
+        <v>266</v>
+      </c>
+      <c r="C250" t="s">
+        <v>278</v>
+      </c>
+      <c r="D250" t="n">
+        <v>7.69</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="s">
+        <v>265</v>
+      </c>
+      <c r="B251" t="s">
+        <v>266</v>
+      </c>
+      <c r="C251" t="s">
+        <v>279</v>
+      </c>
+      <c r="D251" t="n">
+        <v>7.77</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s">
+        <v>265</v>
+      </c>
+      <c r="B252" t="s">
+        <v>266</v>
+      </c>
+      <c r="C252" t="s">
+        <v>280</v>
+      </c>
+      <c r="D252" t="n">
+        <v>9.32</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s">
+        <v>265</v>
+      </c>
+      <c r="B253" t="s">
+        <v>266</v>
+      </c>
+      <c r="C253" t="s">
+        <v>281</v>
+      </c>
+      <c r="D253" t="n">
+        <v>11.14</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s">
+        <v>265</v>
+      </c>
+      <c r="B254" t="s">
+        <v>266</v>
+      </c>
+      <c r="C254" t="s">
+        <v>282</v>
+      </c>
+      <c r="D254" t="n">
+        <v>11.68</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="s">
+        <v>265</v>
+      </c>
+      <c r="B255" t="s">
+        <v>266</v>
+      </c>
+      <c r="C255" t="s">
+        <v>283</v>
+      </c>
+      <c r="D255" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s">
+        <v>265</v>
+      </c>
+      <c r="B256" t="s">
+        <v>266</v>
+      </c>
+      <c r="C256" t="s">
+        <v>284</v>
+      </c>
+      <c r="D256" t="n">
+        <v>20.77</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="s">
+        <v>265</v>
+      </c>
+      <c r="B257" t="s">
+        <v>266</v>
+      </c>
+      <c r="C257" t="s">
+        <v>285</v>
+      </c>
+      <c r="D257" t="n">
+        <v>32.03</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_anytime_tryscorers.xlsx
+++ b/files/NRL_anytime_tryscorers.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="268">
   <si>
     <t xml:space="preserve">Game</t>
   </si>
@@ -26,7 +26,658 @@
     <t xml:space="preserve">Price</t>
   </si>
   <si>
-    <t xml:space="preserve">gold coast titans at newcastle knights</t>
+    <t xml:space="preserve">penrith panthers at melbourne storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moses Leo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sualauvi Faalogo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siulagi Tuimalatu-Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harry Grant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shawn Blore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oryn Keeley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nick Meaney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron Munster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Howarth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trent Toelau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyran Wishart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angus Hinchey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stefano Utoikamanu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Clarke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penrith panthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Jenkins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian To'o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casey McLean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Edwards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Izack Tago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiah Papali'i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathan Cleary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freddy Lussick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lindsay Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Cogger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Henry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Garner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moses Leota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scott Sorensen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos at canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane broncos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grant Anderson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josiah Karapani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezra Mam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kotoni Staggs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hayze Perham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaiyden Hunt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Riki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deine Mariner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Hunt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Willison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Walters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Talty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gehamat Shibasaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payne Haas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canberra raiders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Savage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jed Stuart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaeo Weekes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simi Sasagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Timoko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Strange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zac Hosking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matty Nicholson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owen Pattie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Sanders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Papalii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe Roddy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daine Laurie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joseph Tapine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Starling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corey Horsburgh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels at dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamiso Tabuai-Fidow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selwyn Cobbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamayne Isaako</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herbie Farnworth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Bostock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Plath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kulikefu Finefeuiaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kodi Nikorima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremy Marshall-King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ray Stone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Flegler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiya Katoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Gilbert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morgan Knowles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Felise Kaufusi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Elliott</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parramatta eels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Addo-Carr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apa Twidle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian Kelly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Samrani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Penisini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tallyn Da Silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitchell Moses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kitione Kautoga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronald Volkman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack De Belin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kelma Tuilagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luca Moretti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Paulo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manly-warringah sea eagles at newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manly-warringah sea eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Trbojevic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jason Saab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lehi Hopoate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tolutau Koula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reuben Garrick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haumole Olakau'atu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Trbojevic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clayton Faulalo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brandon Wakeham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamal Fogarty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corey Waddell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathan Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caleb Navale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Trbojevic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Onitoni Large</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simione Laiafi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominic Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greg Marzhew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fletcher Sharpe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fletcher Hunt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bradman Best</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kalyn Ponga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jermaine McEwen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyson Frizell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trey Mooney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandon Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phoenix Crossland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harrison Graham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elijah Salesa-Leaumoana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mat Croker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors at south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south sydney rabbitohs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Johnston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campbell Graham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tallis Duncan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cody Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Wighton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Dufty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">David Fifita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euan Aitken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron Murray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keaon Koloamatangi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brandon Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Sullivan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tevita Tatola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jye Gray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peter Mamouzelos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Fletcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warriors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alofiana Khan-Pereira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dallin Watene-Zelezniak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leka Halasima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ali Leiataua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Hanson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Capewell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Laban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chanel Harris-Tavita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taine Tuaupiki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wayde Egan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Fisher-Harris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erin Clark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Healey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eddie Ieremia-Toeava</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs at st george-illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Kiraz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enari Tuala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matt Burton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bronson Xerri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stephen Crichton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Tracey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viliame Kikau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Preston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lachlan Galvin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jonathan Sua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurt Mann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaeman Salmon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Curran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bailey Hayward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harry Hayes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st george-illawarra dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyrell Sloan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Atkinson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valentine Holmes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mathew Feagai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Egan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamish Stewart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyle Flanagan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mosese Suli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lyhkan King-Togia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Liddle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setu Tu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luciano Leilua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toby Couchman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emre Guler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan Couchman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks at gold coast titans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cronulla-sutherland sharks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronaldo Mulitalo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sione Katoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">William Kennedy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayal Iro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mawene Hiroti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Briton Nikora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teig Wilton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niwhai Puru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicholas Hynes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Addin Fonua-Blake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siosifa Talakai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Hazelton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blayke Brailey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesse Colquhoun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron McInnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braden Hamlin-Uele</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Burns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samuel Stonestreet</t>
   </si>
   <si>
     <t xml:space="preserve">gold coast titans</t>
@@ -44,18 +695,18 @@
     <t xml:space="preserve">Jojo Fifita</t>
   </si>
   <si>
+    <t xml:space="preserve">Keano Kini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AJ Brimson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arama Hau</t>
+  </si>
+  <si>
     <t xml:space="preserve">Beau Fermor</t>
   </si>
   <si>
-    <t xml:space="preserve">Keano Kini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AJ Brimson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Patston</t>
-  </si>
-  <si>
     <t xml:space="preserve">Oliver Pascoe</t>
   </si>
   <si>
@@ -68,118 +719,70 @@
     <t xml:space="preserve">Kurtis Morrin</t>
   </si>
   <si>
-    <t xml:space="preserve">Chris Randall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Bai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dominic Young</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greg Marzhew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fletcher Sharpe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fletcher Hunt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kalyn Ponga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dane Gagai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Francis Manuleleua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trey Mooney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandon Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jermaine McEwen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phoenix Crossland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harrison Graham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyson Frizell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mat Croker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cody Hopwood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toby Winter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george-illawarra dragons at wests tigers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st george-illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyrell Sloan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel Atkinson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valentine Holmes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mathew Feagai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamish Stewart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyle Flanagan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mosese Suli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lyhkan King-Togia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Egan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Liddle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Setu Tu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toby Couchman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emre Guler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan Couchman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Webster</t>
+    <t xml:space="preserve">wests tigers at sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark Nawaqanitawase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Tedesco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugo Savala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robert Toia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daly Cherry-Evans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salesi Foketi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siua Wong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reece Robson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Victor Radley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nat Butcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Watson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egan Butcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lindsay Collins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cody Ramsey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spencer Leniu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naufahu Whyte</t>
   </si>
   <si>
     <t xml:space="preserve">wests tigers</t>
   </si>
   <si>
-    <t xml:space="preserve">Sunia Turuva</t>
+    <t xml:space="preserve">Jeral Skelton</t>
   </si>
   <si>
     <t xml:space="preserve">Solomone Saukuru</t>
@@ -188,15 +791,18 @@
     <t xml:space="preserve">Jahream Bula</t>
   </si>
   <si>
-    <t xml:space="preserve">Adam Doueihi</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior Tupou</t>
   </si>
   <si>
     <t xml:space="preserve">Samuela Fainu</t>
   </si>
   <si>
+    <t xml:space="preserve">Tony Sukkar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jock Madden</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jarome Luai</t>
   </si>
   <si>
@@ -206,670 +812,10 @@
     <t xml:space="preserve">Patrick Herbert</t>
   </si>
   <si>
-    <t xml:space="preserve">Tony Sukkar</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fonua Pole</t>
   </si>
   <si>
     <t xml:space="preserve">Terrell May</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sione Fainu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Seyfarth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Javon Andrews</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penrith panthers at melbourne storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne storm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moses Leo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sualauvi Faalogo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siulagi Tuimalatu-Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyran Wishart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hayden Watson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nick Meaney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameron Munster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oryn Keeley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joe Chan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angus Hinchey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stefano Utoikamanu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shawn Blore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Clarke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penrith panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Jenkins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian To'o</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Edwards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Izack Tago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nathan Cleary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paul Alamoti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiah Papali'i</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freddy Lussick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lindsay Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Cogger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Henry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moses Leota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scott Sorensen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Phillips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luron Patea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos at canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane broncos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grant Anderson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josiah Karapani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ezra Mam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reece Walsh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kotoni Staggs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deine Mariner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Willison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan Riki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Walters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Duffy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaiyden Hunt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gehamat Shibasaki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payne Haas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Gosiewski</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blake Mozer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canberra raiders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Savage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jed Stuart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaeo Weekes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Timoko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan Strange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Savelio Tamale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matty Nicholson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owen Pattie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zac Hosking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethan Sanders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joe Roddy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daine Laurie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joseph Tapine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Starling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ata Mariota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels at dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamiso Tabuai-Fidow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selwyn Cobbo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamayne Isaako</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herbie Farnworth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Bostock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kodi Nikorima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connelly Lemuelu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremy Marshall-King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kulikefu Finefeuiaki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ray Stone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Flegler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiya Katoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Plath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Gilbert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morgan Knowles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Felise Kaufusi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parramatta eels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Addo-Carr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apa Twidle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian Kelly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan Samrani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Will Penisini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tallyn Da Silva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitchell Moses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronald Volkman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitione Kautoga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luca Moretti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saxon Pryke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Paulo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manly-warringah sea eagles at newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manly-warringah sea eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clayton Faulalo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jason Saab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lehi Hopoate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tolutau Koula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reuben Garrick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haumole Olakau'atu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joey Walsh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corey Waddell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brandon Wakeham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamal Fogarty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Trbojevic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simione Laiafi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hugo Hart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Simpkin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fletcher Baker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicholas Lenaz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson Shereb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Feledy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nathan Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors at south sydney rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">south sydney rabbitohs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Johnston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campbell Graham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tallis Duncan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cody Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Wighton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Dufty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">David Fifita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Elliott</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameron Murray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keaon Koloamatangi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brandon Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Sullivan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tevita Tatola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Euan Aitken</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jye Gray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peter Mamouzelos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alofiana Khan-Pereira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dallin Watene-Zelezniak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leka Halasima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Metcalf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charnze Nicoll-Klokstad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ali Leiataua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chanel Harris-Tavita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Laban</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurt Capewell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wayde Egan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Fisher-Harris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erin Clark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Healey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eddie Ieremia-Toeava</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs at st george-illawarra dragons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canterbury-bankstown bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jethro Rinakama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Kiraz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matt Burton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Preston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stephen Crichton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Tracey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enari Tuala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viliame Kikau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lachlan Galvin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurt Mann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaeman Salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Curran</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bailey Hayward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harry Hayes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leo Thompson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bronson Xerri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alekolasimi Jones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Turpin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks at gold coast titans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronaldo Mulitalo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sione Katoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">William Kennedy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kayal Iro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Braydon Trindall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mawene Hiroti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Briton Nikora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teig Wilton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicholas Hynes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siosifa Talakai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Hazelton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blayke Brailey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jesse Colquhoun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameron McInnes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Braden Hamlin-Uele</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oregon Kaufusi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Burns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samuel Stonestreet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hohepa Puru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wests tigers at sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mark Nawaqanitawase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hugo Savala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robert Toia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cody Ramsey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daly Cherry-Evans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salesi Foketi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siua Wong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reece Robson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Victor Radley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nat Butcher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Watson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Egan Butcher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lindsay Collins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spencer Leniu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Naufahu Whyte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rex Bassingthwaighte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tommy Talau</t>
   </si>
 </sst>
 </file>
@@ -1229,7 +1175,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="3">
@@ -1243,7 +1189,7 @@
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>3.43</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="4">
@@ -1257,7 +1203,7 @@
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>3.83</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="5">
@@ -1271,7 +1217,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>3.91</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="6">
@@ -1285,7 +1231,7 @@
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>4.22</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="7">
@@ -1299,7 +1245,7 @@
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>4.53</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="8">
@@ -1313,7 +1259,7 @@
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>4.61</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="9">
@@ -1327,7 +1273,7 @@
         <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>5.23</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="10">
@@ -1341,7 +1287,7 @@
         <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>5.47</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="11">
@@ -1355,7 +1301,7 @@
         <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>7.75</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="12">
@@ -1369,7 +1315,7 @@
         <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>8.98</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="13">
@@ -1383,7 +1329,7 @@
         <v>17</v>
       </c>
       <c r="D13" t="n">
-        <v>10.51</v>
+        <v>11.71</v>
       </c>
     </row>
     <row r="14">
@@ -1397,7 +1343,7 @@
         <v>18</v>
       </c>
       <c r="D14" t="n">
-        <v>11.99</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="15">
@@ -1411,7 +1357,7 @@
         <v>19</v>
       </c>
       <c r="D15" t="n">
-        <v>12.35</v>
+        <v>14.11</v>
       </c>
     </row>
     <row r="16">
@@ -1419,13 +1365,13 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" t="s">
         <v>20</v>
       </c>
-      <c r="C16" t="s">
-        <v>21</v>
-      </c>
       <c r="D16" t="n">
-        <v>1.67</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="17">
@@ -1433,13 +1379,13 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C17" t="s">
         <v>22</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="18">
@@ -1447,13 +1393,13 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
       </c>
       <c r="D18" t="n">
-        <v>2.04</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="19">
@@ -1461,13 +1407,13 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C19" t="s">
         <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>2.19</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="20">
@@ -1475,13 +1421,13 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C20" t="s">
         <v>25</v>
       </c>
       <c r="D20" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="21">
@@ -1489,13 +1435,13 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C21" t="s">
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>4.21</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="22">
@@ -1503,13 +1449,13 @@
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C22" t="s">
         <v>27</v>
       </c>
       <c r="D22" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="23">
@@ -1517,13 +1463,13 @@
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C23" t="s">
         <v>28</v>
       </c>
       <c r="D23" t="n">
-        <v>5.25</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="24">
@@ -1531,13 +1477,13 @@
         <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C24" t="s">
         <v>29</v>
       </c>
       <c r="D24" t="n">
-        <v>5.39</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="25">
@@ -1545,13 +1491,13 @@
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C25" t="s">
         <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>6.05</v>
+        <v>8.27</v>
       </c>
     </row>
     <row r="26">
@@ -1559,13 +1505,13 @@
         <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C26" t="s">
         <v>31</v>
       </c>
       <c r="D26" t="n">
-        <v>7.15</v>
+        <v>8.94</v>
       </c>
     </row>
     <row r="27">
@@ -1573,13 +1519,13 @@
         <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C27" t="s">
         <v>32</v>
       </c>
       <c r="D27" t="n">
-        <v>7.3</v>
+        <v>12.16</v>
       </c>
     </row>
     <row r="28">
@@ -1587,13 +1533,13 @@
         <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C28" t="s">
         <v>33</v>
       </c>
       <c r="D28" t="n">
-        <v>12.02</v>
+        <v>12.28</v>
       </c>
     </row>
     <row r="29">
@@ -1601,13 +1547,13 @@
         <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C29" t="s">
         <v>34</v>
       </c>
       <c r="D29" t="n">
-        <v>13.65</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="30">
@@ -1615,13 +1561,13 @@
         <v>4</v>
       </c>
       <c r="B30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C30" t="s">
         <v>35</v>
       </c>
       <c r="D30" t="n">
-        <v>15.76</v>
+        <v>16.71</v>
       </c>
     </row>
     <row r="31">
@@ -1629,13 +1575,13 @@
         <v>4</v>
       </c>
       <c r="B31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C31" t="s">
         <v>36</v>
       </c>
       <c r="D31" t="n">
-        <v>19.07</v>
+        <v>20.43</v>
       </c>
     </row>
     <row r="32">
@@ -1649,7 +1595,7 @@
         <v>39</v>
       </c>
       <c r="D32" t="n">
-        <v>1.96</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="33">
@@ -1663,7 +1609,7 @@
         <v>40</v>
       </c>
       <c r="D33" t="n">
-        <v>2.1</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="34">
@@ -1677,7 +1623,7 @@
         <v>41</v>
       </c>
       <c r="D34" t="n">
-        <v>2.33</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="35">
@@ -1691,7 +1637,7 @@
         <v>42</v>
       </c>
       <c r="D35" t="n">
-        <v>2.97</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="36">
@@ -1705,7 +1651,7 @@
         <v>43</v>
       </c>
       <c r="D36" t="n">
-        <v>4.33</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="37">
@@ -1719,7 +1665,7 @@
         <v>44</v>
       </c>
       <c r="D37" t="n">
-        <v>4.68</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="38">
@@ -1733,7 +1679,7 @@
         <v>45</v>
       </c>
       <c r="D38" t="n">
-        <v>4.71</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="39">
@@ -1747,7 +1693,7 @@
         <v>46</v>
       </c>
       <c r="D39" t="n">
-        <v>4.8</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="40">
@@ -1761,7 +1707,7 @@
         <v>47</v>
       </c>
       <c r="D40" t="n">
-        <v>4.92</v>
+        <v>5.96</v>
       </c>
     </row>
     <row r="41">
@@ -1775,7 +1721,7 @@
         <v>48</v>
       </c>
       <c r="D41" t="n">
-        <v>6.13</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="42">
@@ -1789,7 +1735,7 @@
         <v>49</v>
       </c>
       <c r="D42" t="n">
-        <v>7.49</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="43">
@@ -1803,7 +1749,7 @@
         <v>50</v>
       </c>
       <c r="D43" t="n">
-        <v>9.33</v>
+        <v>9.28</v>
       </c>
     </row>
     <row r="44">
@@ -1817,7 +1763,7 @@
         <v>51</v>
       </c>
       <c r="D44" t="n">
-        <v>10.19</v>
+        <v>13.01</v>
       </c>
     </row>
     <row r="45">
@@ -1831,7 +1777,7 @@
         <v>52</v>
       </c>
       <c r="D45" t="n">
-        <v>10.57</v>
+        <v>15.32</v>
       </c>
     </row>
     <row r="46">
@@ -1839,13 +1785,13 @@
         <v>37</v>
       </c>
       <c r="B46" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C46" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D46" t="n">
-        <v>17.5</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="47">
@@ -1853,13 +1799,13 @@
         <v>37</v>
       </c>
       <c r="B47" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C47" t="s">
         <v>55</v>
       </c>
       <c r="D47" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="48">
@@ -1867,13 +1813,13 @@
         <v>37</v>
       </c>
       <c r="B48" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C48" t="s">
         <v>56</v>
       </c>
       <c r="D48" t="n">
-        <v>2.64</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="49">
@@ -1881,13 +1827,13 @@
         <v>37</v>
       </c>
       <c r="B49" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C49" t="s">
         <v>57</v>
       </c>
       <c r="D49" t="n">
-        <v>2.95</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="50">
@@ -1895,13 +1841,13 @@
         <v>37</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50" t="s">
         <v>58</v>
       </c>
       <c r="D50" t="n">
-        <v>3.21</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="51">
@@ -1909,13 +1855,13 @@
         <v>37</v>
       </c>
       <c r="B51" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C51" t="s">
         <v>59</v>
       </c>
       <c r="D51" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="52">
@@ -1923,13 +1869,13 @@
         <v>37</v>
       </c>
       <c r="B52" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C52" t="s">
         <v>60</v>
       </c>
       <c r="D52" t="n">
-        <v>4.88</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="53">
@@ -1937,13 +1883,13 @@
         <v>37</v>
       </c>
       <c r="B53" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C53" t="s">
         <v>61</v>
       </c>
       <c r="D53" t="n">
-        <v>5.76</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="54">
@@ -1951,13 +1897,13 @@
         <v>37</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C54" t="s">
         <v>62</v>
       </c>
       <c r="D54" t="n">
-        <v>5.79</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="55">
@@ -1965,13 +1911,13 @@
         <v>37</v>
       </c>
       <c r="B55" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C55" t="s">
         <v>63</v>
       </c>
       <c r="D55" t="n">
-        <v>6.02</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="56">
@@ -1979,13 +1925,13 @@
         <v>37</v>
       </c>
       <c r="B56" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C56" t="s">
         <v>64</v>
       </c>
       <c r="D56" t="n">
-        <v>6.3</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="57">
@@ -1993,13 +1939,13 @@
         <v>37</v>
       </c>
       <c r="B57" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C57" t="s">
         <v>65</v>
       </c>
       <c r="D57" t="n">
-        <v>10.96</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="58">
@@ -2007,13 +1953,13 @@
         <v>37</v>
       </c>
       <c r="B58" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C58" t="s">
         <v>66</v>
       </c>
       <c r="D58" t="n">
-        <v>11.05</v>
+        <v>7.64</v>
       </c>
     </row>
     <row r="59">
@@ -2021,13 +1967,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C59" t="s">
         <v>67</v>
       </c>
       <c r="D59" t="n">
-        <v>17.06</v>
+        <v>11.48</v>
       </c>
     </row>
     <row r="60">
@@ -2035,13 +1981,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C60" t="s">
         <v>68</v>
       </c>
       <c r="D60" t="n">
-        <v>17.18</v>
+        <v>12.09</v>
       </c>
     </row>
     <row r="61">
@@ -2049,13 +1995,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C61" t="s">
         <v>69</v>
       </c>
       <c r="D61" t="n">
-        <v>19</v>
+        <v>13.05</v>
       </c>
     </row>
     <row r="62">
@@ -2069,7 +2015,7 @@
         <v>72</v>
       </c>
       <c r="D62" t="n">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="63">
@@ -2083,7 +2029,7 @@
         <v>73</v>
       </c>
       <c r="D63" t="n">
-        <v>2.4</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="64">
@@ -2097,7 +2043,7 @@
         <v>74</v>
       </c>
       <c r="D64" t="n">
-        <v>3.25</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="65">
@@ -2111,7 +2057,7 @@
         <v>75</v>
       </c>
       <c r="D65" t="n">
-        <v>4</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="66">
@@ -2125,7 +2071,7 @@
         <v>76</v>
       </c>
       <c r="D66" t="n">
-        <v>4.72</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="67">
@@ -2139,7 +2085,7 @@
         <v>77</v>
       </c>
       <c r="D67" t="n">
-        <v>4.74</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="68">
@@ -2153,7 +2099,7 @@
         <v>78</v>
       </c>
       <c r="D68" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="69">
@@ -2167,7 +2113,7 @@
         <v>79</v>
       </c>
       <c r="D69" t="n">
-        <v>4.81</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="70">
@@ -2181,7 +2127,7 @@
         <v>80</v>
       </c>
       <c r="D70" t="n">
-        <v>6.22</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="71">
@@ -2195,7 +2141,7 @@
         <v>81</v>
       </c>
       <c r="D71" t="n">
-        <v>10.37</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="72">
@@ -2209,7 +2155,7 @@
         <v>82</v>
       </c>
       <c r="D72" t="n">
-        <v>11.59</v>
+        <v>7.83</v>
       </c>
     </row>
     <row r="73">
@@ -2223,7 +2169,7 @@
         <v>83</v>
       </c>
       <c r="D73" t="n">
-        <v>12.48</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="74">
@@ -2237,7 +2183,7 @@
         <v>84</v>
       </c>
       <c r="D74" t="n">
-        <v>12.49</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="75">
@@ -2251,7 +2197,7 @@
         <v>85</v>
       </c>
       <c r="D75" t="n">
-        <v>14.36</v>
+        <v>14.56</v>
       </c>
     </row>
     <row r="76">
@@ -2259,13 +2205,13 @@
         <v>70</v>
       </c>
       <c r="B76" t="s">
+        <v>71</v>
+      </c>
+      <c r="C76" t="s">
         <v>86</v>
       </c>
-      <c r="C76" t="s">
-        <v>87</v>
-      </c>
       <c r="D76" t="n">
-        <v>1.79</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="77">
@@ -2273,13 +2219,13 @@
         <v>70</v>
       </c>
       <c r="B77" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="C77" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D77" t="n">
-        <v>2.15</v>
+        <v>17.04</v>
       </c>
     </row>
     <row r="78">
@@ -2287,13 +2233,13 @@
         <v>70</v>
       </c>
       <c r="B78" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C78" t="s">
         <v>89</v>
       </c>
       <c r="D78" t="n">
-        <v>2.9</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="79">
@@ -2301,13 +2247,13 @@
         <v>70</v>
       </c>
       <c r="B79" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C79" t="s">
         <v>90</v>
       </c>
       <c r="D79" t="n">
-        <v>3.12</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="80">
@@ -2315,13 +2261,13 @@
         <v>70</v>
       </c>
       <c r="B80" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C80" t="s">
         <v>91</v>
       </c>
       <c r="D80" t="n">
-        <v>4.25</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="81">
@@ -2329,13 +2275,13 @@
         <v>70</v>
       </c>
       <c r="B81" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C81" t="s">
         <v>92</v>
       </c>
       <c r="D81" t="n">
-        <v>4.34</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="82">
@@ -2343,13 +2289,13 @@
         <v>70</v>
       </c>
       <c r="B82" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C82" t="s">
         <v>93</v>
       </c>
       <c r="D82" t="n">
-        <v>4.55</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="83">
@@ -2357,13 +2303,13 @@
         <v>70</v>
       </c>
       <c r="B83" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C83" t="s">
         <v>94</v>
       </c>
       <c r="D83" t="n">
-        <v>5.76</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="84">
@@ -2371,13 +2317,13 @@
         <v>70</v>
       </c>
       <c r="B84" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C84" t="s">
         <v>95</v>
       </c>
       <c r="D84" t="n">
-        <v>7.35</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="85">
@@ -2385,13 +2331,13 @@
         <v>70</v>
       </c>
       <c r="B85" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C85" t="s">
         <v>96</v>
       </c>
       <c r="D85" t="n">
-        <v>7.95</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="86">
@@ -2399,13 +2345,13 @@
         <v>70</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C86" t="s">
         <v>97</v>
       </c>
       <c r="D86" t="n">
-        <v>10.78</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="87">
@@ -2413,13 +2359,13 @@
         <v>70</v>
       </c>
       <c r="B87" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C87" t="s">
         <v>98</v>
       </c>
       <c r="D87" t="n">
-        <v>10.89</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="88">
@@ -2427,13 +2373,13 @@
         <v>70</v>
       </c>
       <c r="B88" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C88" t="s">
         <v>99</v>
       </c>
       <c r="D88" t="n">
-        <v>14.79</v>
+        <v>13.24</v>
       </c>
     </row>
     <row r="89">
@@ -2441,13 +2387,13 @@
         <v>70</v>
       </c>
       <c r="B89" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C89" t="s">
         <v>100</v>
       </c>
       <c r="D89" t="n">
-        <v>18.07</v>
+        <v>16.77</v>
       </c>
     </row>
     <row r="90">
@@ -2455,13 +2401,13 @@
         <v>70</v>
       </c>
       <c r="B90" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C90" t="s">
         <v>101</v>
       </c>
       <c r="D90" t="n">
-        <v>20.26</v>
+        <v>16.97</v>
       </c>
     </row>
     <row r="91">
@@ -2469,13 +2415,13 @@
         <v>70</v>
       </c>
       <c r="B91" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C91" t="s">
         <v>102</v>
       </c>
       <c r="D91" t="n">
-        <v>20.88</v>
+        <v>17.93</v>
       </c>
     </row>
     <row r="92">
@@ -2489,7 +2435,7 @@
         <v>105</v>
       </c>
       <c r="D92" t="n">
-        <v>2.49</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="93">
@@ -2503,7 +2449,7 @@
         <v>106</v>
       </c>
       <c r="D93" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="94">
@@ -2517,7 +2463,7 @@
         <v>107</v>
       </c>
       <c r="D94" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="95">
@@ -2531,7 +2477,7 @@
         <v>108</v>
       </c>
       <c r="D95" t="n">
-        <v>2.64</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="96">
@@ -2545,7 +2491,7 @@
         <v>109</v>
       </c>
       <c r="D96" t="n">
-        <v>3.07</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="97">
@@ -2559,7 +2505,7 @@
         <v>110</v>
       </c>
       <c r="D97" t="n">
-        <v>4.43</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="98">
@@ -2573,7 +2519,7 @@
         <v>111</v>
       </c>
       <c r="D98" t="n">
-        <v>5.79</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="99">
@@ -2587,7 +2533,7 @@
         <v>112</v>
       </c>
       <c r="D99" t="n">
-        <v>5.91</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="100">
@@ -2601,7 +2547,7 @@
         <v>113</v>
       </c>
       <c r="D100" t="n">
-        <v>6.07</v>
+        <v>7.64</v>
       </c>
     </row>
     <row r="101">
@@ -2615,7 +2561,7 @@
         <v>114</v>
       </c>
       <c r="D101" t="n">
-        <v>6.53</v>
+        <v>8.89</v>
       </c>
     </row>
     <row r="102">
@@ -2629,7 +2575,7 @@
         <v>115</v>
       </c>
       <c r="D102" t="n">
-        <v>9.39</v>
+        <v>13.32</v>
       </c>
     </row>
     <row r="103">
@@ -2643,7 +2589,7 @@
         <v>116</v>
       </c>
       <c r="D103" t="n">
-        <v>10.77</v>
+        <v>15.42</v>
       </c>
     </row>
     <row r="104">
@@ -2657,7 +2603,7 @@
         <v>117</v>
       </c>
       <c r="D104" t="n">
-        <v>12.66</v>
+        <v>16.88</v>
       </c>
     </row>
     <row r="105">
@@ -2671,7 +2617,7 @@
         <v>118</v>
       </c>
       <c r="D105" t="n">
-        <v>16.07</v>
+        <v>22.05</v>
       </c>
     </row>
     <row r="106">
@@ -2685,7 +2631,7 @@
         <v>119</v>
       </c>
       <c r="D106" t="n">
-        <v>16.8</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="107">
@@ -2693,13 +2639,13 @@
         <v>103</v>
       </c>
       <c r="B107" t="s">
+        <v>104</v>
+      </c>
+      <c r="C107" t="s">
         <v>120</v>
       </c>
-      <c r="C107" t="s">
-        <v>121</v>
-      </c>
       <c r="D107" t="n">
-        <v>2.01</v>
+        <v>22.12</v>
       </c>
     </row>
     <row r="108">
@@ -2707,13 +2653,13 @@
         <v>103</v>
       </c>
       <c r="B108" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C108" t="s">
         <v>122</v>
       </c>
       <c r="D108" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="109">
@@ -2721,13 +2667,13 @@
         <v>103</v>
       </c>
       <c r="B109" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C109" t="s">
         <v>123</v>
       </c>
       <c r="D109" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="110">
@@ -2735,13 +2681,13 @@
         <v>103</v>
       </c>
       <c r="B110" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C110" t="s">
         <v>124</v>
       </c>
       <c r="D110" t="n">
-        <v>2.88</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="111">
@@ -2749,13 +2695,13 @@
         <v>103</v>
       </c>
       <c r="B111" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C111" t="s">
         <v>125</v>
       </c>
       <c r="D111" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="112">
@@ -2763,13 +2709,13 @@
         <v>103</v>
       </c>
       <c r="B112" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C112" t="s">
         <v>126</v>
       </c>
       <c r="D112" t="n">
-        <v>3.47</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="113">
@@ -2777,13 +2723,13 @@
         <v>103</v>
       </c>
       <c r="B113" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C113" t="s">
         <v>127</v>
       </c>
       <c r="D113" t="n">
-        <v>3.61</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="114">
@@ -2791,13 +2737,13 @@
         <v>103</v>
       </c>
       <c r="B114" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C114" t="s">
         <v>128</v>
       </c>
       <c r="D114" t="n">
-        <v>3.94</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="115">
@@ -2805,13 +2751,13 @@
         <v>103</v>
       </c>
       <c r="B115" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C115" t="s">
         <v>129</v>
       </c>
       <c r="D115" t="n">
-        <v>4.91</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="116">
@@ -2819,13 +2765,13 @@
         <v>103</v>
       </c>
       <c r="B116" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C116" t="s">
         <v>130</v>
       </c>
       <c r="D116" t="n">
-        <v>5.71</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117">
@@ -2833,13 +2779,13 @@
         <v>103</v>
       </c>
       <c r="B117" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C117" t="s">
         <v>131</v>
       </c>
       <c r="D117" t="n">
-        <v>7.11</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="118">
@@ -2847,13 +2793,13 @@
         <v>103</v>
       </c>
       <c r="B118" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C118" t="s">
         <v>132</v>
       </c>
       <c r="D118" t="n">
-        <v>7.32</v>
+        <v>9.62</v>
       </c>
     </row>
     <row r="119">
@@ -2861,13 +2807,13 @@
         <v>103</v>
       </c>
       <c r="B119" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C119" t="s">
         <v>133</v>
       </c>
       <c r="D119" t="n">
-        <v>11</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="120">
@@ -2875,13 +2821,13 @@
         <v>103</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C120" t="s">
         <v>134</v>
       </c>
       <c r="D120" t="n">
-        <v>11.57</v>
+        <v>16.55</v>
       </c>
     </row>
     <row r="121">
@@ -2889,13 +2835,13 @@
         <v>103</v>
       </c>
       <c r="B121" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C121" t="s">
         <v>135</v>
       </c>
       <c r="D121" t="n">
-        <v>17.98</v>
+        <v>18.54</v>
       </c>
     </row>
     <row r="122">
@@ -2909,7 +2855,7 @@
         <v>138</v>
       </c>
       <c r="D122" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="123">
@@ -2923,7 +2869,7 @@
         <v>139</v>
       </c>
       <c r="D123" t="n">
-        <v>1.75</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="124">
@@ -2937,7 +2883,7 @@
         <v>140</v>
       </c>
       <c r="D124" t="n">
-        <v>1.86</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="125">
@@ -2951,7 +2897,7 @@
         <v>141</v>
       </c>
       <c r="D125" t="n">
-        <v>2.12</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="126">
@@ -2965,7 +2911,7 @@
         <v>142</v>
       </c>
       <c r="D126" t="n">
-        <v>2.53</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="127">
@@ -2979,7 +2925,7 @@
         <v>143</v>
       </c>
       <c r="D127" t="n">
-        <v>4.2</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="128">
@@ -2993,7 +2939,7 @@
         <v>144</v>
       </c>
       <c r="D128" t="n">
-        <v>4.35</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="129">
@@ -3007,7 +2953,7 @@
         <v>145</v>
       </c>
       <c r="D129" t="n">
-        <v>5.63</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="130">
@@ -3021,7 +2967,7 @@
         <v>146</v>
       </c>
       <c r="D130" t="n">
-        <v>6</v>
+        <v>8.41</v>
       </c>
     </row>
     <row r="131">
@@ -3035,7 +2981,7 @@
         <v>147</v>
       </c>
       <c r="D131" t="n">
-        <v>6.99</v>
+        <v>8.69</v>
       </c>
     </row>
     <row r="132">
@@ -3049,7 +2995,7 @@
         <v>148</v>
       </c>
       <c r="D132" t="n">
-        <v>7.44</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="133">
@@ -3063,7 +3009,7 @@
         <v>149</v>
       </c>
       <c r="D133" t="n">
-        <v>8.37</v>
+        <v>11.24</v>
       </c>
     </row>
     <row r="134">
@@ -3077,7 +3023,7 @@
         <v>150</v>
       </c>
       <c r="D134" t="n">
-        <v>8.9</v>
+        <v>12.63</v>
       </c>
     </row>
     <row r="135">
@@ -3091,7 +3037,7 @@
         <v>151</v>
       </c>
       <c r="D135" t="n">
-        <v>10.78</v>
+        <v>17.18</v>
       </c>
     </row>
     <row r="136">
@@ -3105,7 +3051,7 @@
         <v>152</v>
       </c>
       <c r="D136" t="n">
-        <v>13.79</v>
+        <v>18.94</v>
       </c>
     </row>
     <row r="137">
@@ -3119,7 +3065,7 @@
         <v>153</v>
       </c>
       <c r="D137" t="n">
-        <v>13.84</v>
+        <v>20.21</v>
       </c>
     </row>
     <row r="138">
@@ -3133,7 +3079,7 @@
         <v>155</v>
       </c>
       <c r="D138" t="n">
-        <v>2.36</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="139">
@@ -3147,7 +3093,7 @@
         <v>156</v>
       </c>
       <c r="D139" t="n">
-        <v>2.6</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="140">
@@ -3161,7 +3107,7 @@
         <v>157</v>
       </c>
       <c r="D140" t="n">
-        <v>3.21</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="141">
@@ -3175,7 +3121,7 @@
         <v>158</v>
       </c>
       <c r="D141" t="n">
-        <v>3.67</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="142">
@@ -3189,7 +3135,7 @@
         <v>159</v>
       </c>
       <c r="D142" t="n">
-        <v>3.9</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="143">
@@ -3203,7 +3149,7 @@
         <v>160</v>
       </c>
       <c r="D143" t="n">
-        <v>4.11</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="144">
@@ -3217,7 +3163,7 @@
         <v>161</v>
       </c>
       <c r="D144" t="n">
-        <v>4.45</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="145">
@@ -3231,7 +3177,7 @@
         <v>162</v>
       </c>
       <c r="D145" t="n">
-        <v>4.78</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="146">
@@ -3245,7 +3191,7 @@
         <v>163</v>
       </c>
       <c r="D146" t="n">
-        <v>8</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="147">
@@ -3259,7 +3205,7 @@
         <v>164</v>
       </c>
       <c r="D147" t="n">
-        <v>10.44</v>
+        <v>7.66</v>
       </c>
     </row>
     <row r="148">
@@ -3273,7 +3219,7 @@
         <v>165</v>
       </c>
       <c r="D148" t="n">
-        <v>15.46</v>
+        <v>11.09</v>
       </c>
     </row>
     <row r="149">
@@ -3287,7 +3233,7 @@
         <v>166</v>
       </c>
       <c r="D149" t="n">
-        <v>15.93</v>
+        <v>11.51</v>
       </c>
     </row>
     <row r="150">
@@ -3301,7 +3247,7 @@
         <v>167</v>
       </c>
       <c r="D150" t="n">
-        <v>16.19</v>
+        <v>13.01</v>
       </c>
     </row>
     <row r="151">
@@ -3315,7 +3261,7 @@
         <v>168</v>
       </c>
       <c r="D151" t="n">
-        <v>16.33</v>
+        <v>15.83</v>
       </c>
     </row>
     <row r="152">
@@ -3329,7 +3275,7 @@
         <v>171</v>
       </c>
       <c r="D152" t="n">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="153">
@@ -3343,7 +3289,7 @@
         <v>172</v>
       </c>
       <c r="D153" t="n">
-        <v>2.48</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="154">
@@ -3357,7 +3303,7 @@
         <v>173</v>
       </c>
       <c r="D154" t="n">
-        <v>2.58</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="155">
@@ -3371,7 +3317,7 @@
         <v>174</v>
       </c>
       <c r="D155" t="n">
-        <v>2.94</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="156">
@@ -3385,7 +3331,7 @@
         <v>175</v>
       </c>
       <c r="D156" t="n">
-        <v>3.17</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="157">
@@ -3399,7 +3345,7 @@
         <v>176</v>
       </c>
       <c r="D157" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="158">
@@ -3413,7 +3359,7 @@
         <v>177</v>
       </c>
       <c r="D158" t="n">
-        <v>4.39</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="159">
@@ -3427,7 +3373,7 @@
         <v>178</v>
       </c>
       <c r="D159" t="n">
-        <v>6.96</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="160">
@@ -3441,7 +3387,7 @@
         <v>179</v>
       </c>
       <c r="D160" t="n">
-        <v>7.56</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="161">
@@ -3455,7 +3401,7 @@
         <v>180</v>
       </c>
       <c r="D161" t="n">
-        <v>8.8</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="162">
@@ -3469,7 +3415,7 @@
         <v>181</v>
       </c>
       <c r="D162" t="n">
-        <v>21.82</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="163">
@@ -3483,7 +3429,7 @@
         <v>182</v>
       </c>
       <c r="D163" t="n">
-        <v>21.89</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="164">
@@ -3497,7 +3443,7 @@
         <v>183</v>
       </c>
       <c r="D164" t="n">
-        <v>25.16</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="165">
@@ -3511,7 +3457,7 @@
         <v>184</v>
       </c>
       <c r="D165" t="n">
-        <v>25.98</v>
+        <v>12.86</v>
       </c>
     </row>
     <row r="166">
@@ -3525,7 +3471,7 @@
         <v>185</v>
       </c>
       <c r="D166" t="n">
-        <v>27.51</v>
+        <v>20.55</v>
       </c>
     </row>
     <row r="167">
@@ -3533,13 +3479,13 @@
         <v>169</v>
       </c>
       <c r="B167" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="C167" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D167" t="n">
-        <v>28.45</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="168">
@@ -3547,13 +3493,13 @@
         <v>169</v>
       </c>
       <c r="B168" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="C168" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D168" t="n">
-        <v>33.38</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="169">
@@ -3561,13 +3507,13 @@
         <v>169</v>
       </c>
       <c r="B169" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="C169" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D169" t="n">
-        <v>41.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="170">
@@ -3575,1231 +3521,1007 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="C170" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D170" t="n">
-        <v>49.78</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="B171" t="s">
+        <v>186</v>
+      </c>
+      <c r="C171" t="s">
         <v>191</v>
       </c>
-      <c r="C171" t="s">
-        <v>192</v>
-      </c>
       <c r="D171" t="n">
-        <v>1.89</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="172">
       <c r="A